--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0001.xlsx
@@ -1473,7 +1473,7 @@
         <is>
           <t>Trang điểm như thế này... Haha, chỉ là đội vương miện giả để che giấu sự hèn nhát của mi mà thôi.
 Còn gì mà mi không bỏ được khi đã vứt bỏ cả quê hương lẫn tên tuổi của mình!
-R?i ?i ngay, mau!</t>
+Cút đi ngay, mau!</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Ý chí của ngươi đã sụp đổ. Ngươi đứng đó, ngước nhìn đỉnh núi cao chót vót mà người đời gọi là "Strength", lại bị đóng băng ngay dưới chân đồi.
+          <t>Ý chí của ngươi đã sụp đổ. Ngươi đứng đó, ngước nhìn đỉnh núi cao chót vót mà người đời gọi là "Sức Mạnh", lại bị đóng băng ngay dưới chân đồi.
 Có lẽ một cuộc sống bình dị mới là lựa chọn tốt nhất cho ngươi.</t>
         </is>
       </c>
@@ -1677,10 +1677,10 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Trong The World Ảo, các định luật vật lý hoạt động theo cách kỳ lạ.
-- Skills của &lt;color=#ffd12f&gt;Synergy Giả&lt;/color&gt; vẫn &lt;color=#ffd12f&gt;hiệu quả&lt;/color&gt; trong The World Ảo.
-- Chỉ số và hiệu ứng của &lt;color=#ffd12f&gt;Vũ Qi&lt;/color&gt; vẫn &lt;color=#ffd12f&gt;hiệu quả&lt;/color&gt; trong The World Ảo.
-- Chỉ số và kỹ năng của &lt;color=#ffd12f&gt;Echoes&lt;/color&gt; &lt;color=#ffd12f&gt;không hiệu quả&lt;/color&gt; trong The World Ảo.</t>
+          <t>Trong Thế Giới Ảo, các định luật vật lý hoạt động theo cách kỳ lạ.
+- Kỹ năng của &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; vẫn &lt;color=#ffd12f&gt;hiệu quả&lt;/color&gt; trong Thế Giới Ảo.
+- Chỉ số và hiệu ứng của &lt;color=#ffd12f&gt;Vũ Khí&lt;/color&gt; vẫn &lt;color=#ffd12f&gt;hiệu quả&lt;/color&gt; trong Thế Giới Ảo.
+- Chỉ số và kỹ năng của &lt;color=#ffd12f&gt;Echo&lt;/color&gt; &lt;color=#ffd12f&gt;không hiệu quả&lt;/color&gt; trong Thế Giới Ảo.</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Quyển sketchbook kỳ quái, từng trang ghi lại một khúc ca ám ảnh, Dodget chữ xoắn vặn như bị ma ám. Những tưởng tượng sống động ngày nào giờ chỉ còn là giọt nước mắt lặng thầm, nhỏ xuống bề mặt, để lại những vết ố mờ nhạt nhưng đau lòng.</t>
+          <t>Quyển sketchbook kỳ quái, từng trang ghi lại một khúc ca ám ảnh, nét chữ xoắn vặn như bị ma ám. Những tưởng tượng sống động ngày nào giờ chỉ còn là giọt nước mắt lặng thầm, nhỏ xuống bề mặt, để lại những vết ố mờ nhạt nhưng đau lòng.</t>
         </is>
       </c>
     </row>
@@ -2150,10 +2150,10 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>Ngày: [--02]
-Phòng thí nghiệm &lt;ano=CSC&gt;Tòa án Savantae&lt;/ano&gt; là một địa điểm bỏ hoang tại Đầm Lầy Whining Aix. Nhờ sử dụng vật liệu chuyên dụng do CSC phát triển trong cấu trúc chính, tòa nhà được bảo quản tốt và chịu ít tác động từ thời tiết cũng như ăn mòn. Sau khi đánh giá rủi ro, ủy ban nghiên cứu quyết định sử dụng các tầng dưới của địa điểm này để tạo ra một Tacet Field nhân tạo phục vụ mục đích thử nghiệm.
+Phòng thí nghiệm &lt;ano=CSC&gt;Tòa án Savantae&lt;/ano&gt; là một địa điểm bỏ hoang tại Whining Aix's Mire. Nhờ sử dụng vật liệu chuyên dụng do CSC phát triển trong cấu trúc chính, tòa nhà được bảo quản tốt và chịu ít tác động từ thời tiết cũng như ăn mòn. Sau khi đánh giá rủi ro, ủy ban nghiên cứu quyết định sử dụng các tầng dưới của địa điểm này để tạo ra một Tổ Tacet nhân tạo phục vụ mục đích thử nghiệm.
 Trong khu vực thí nghiệm vẫn còn sót lại một số thiết bị bỏ hoang. Hệ thống chiếu sáng tần số thấp được bố trí ở khoảng cách và góc độ nhất định, đảm bảo ánh sáng đồng đều trong khu vực thí nghiệm.
 Tại trung tâm khu thí nghiệm, nhiều sợi cáp được bó lại để cố định một thiết bị kim loại hình cầu. Những sợi cáp này cũng truyền tải dữ liệu đầu vào và đầu ra từ thiết bị kim loại hình cầu, và các thiết bị phát hiện tần số giống hệt nhau được bố trí xung quanh nó.
-Những thiết bị này thường được vận hành bằng bảng điều khiển xoay. Rotate theo chiều kim đồng hồ sẽ tăng năng lượng điện, khiến khung kim loại quay nhanh quanh thiết bị trung tâm để phát hiện tần số.</t>
+Những thiết bị này thường được vận hành bằng bảng điều khiển xoay. Xoay theo chiều kim đồng hồ sẽ tăng năng lượng điện, khiến khung kim loại quay nhanh quanh thiết bị trung tâm để phát hiện tần số.</t>
         </is>
       </c>
     </row>
@@ -2302,15 +2302,15 @@
         <is>
           <t>KHÔNG. SY-A038
 Ngày: [---]
-Đối tượng A038 đã được đưa vào Tacet Field nhân tạo có thể kiểm soát với kích thước 6m x 6m x 6m. Test môi trường định kỳ phải được tiến hành mỗi 6 giờ đối với Tacet Field nhân tạo.
+Đối tượng A038 đã được đưa vào Tổ Tacet nhân tạo có thể kiểm soát với kích thước 6m x 6m x 6m. Kiểm tra môi trường định kỳ phải được tiến hành mỗi 6 giờ đối với Tổ Tacet nhân tạo.
 Việc ra vào khu vực chỉ định chỉ giới hạn cho nhân viên thí nghiệm và nghiêm cấm mọi thiết bị hoặc công cụ không đạt tiêu chuẩn để tránh gây nhiễu đối với đối tượng.
-Guan sát ban đầu cho thấy Đối tượng A038, sinh ra trong Tacet Field nhân tạo, có thể sống ổn định.
+Quan sát ban đầu cho thấy Đối tượng A038, sinh ra trong Tổ Tacet nhân tạo, có thể sống ổn định.
 Tuy nhiên, cần lưu ý rằng đối tượng chưa biểu hiện bất kỳ đặc điểm vật lý cụ thể hay hành vi phát âm nào. Nó dường như không có hình dạng vật lý và chỉ có thể quan sát được thông qua các phương tiện chuyên dụng.
 Hiện tại, A038 không thể hiện mục tiêu hành vi rõ ràng và hầu như đứng yên với mức độ hung hăng và hoạt động thấp.
 Do có sự sai lệch đáng kể so với dự đoán ban đầu, cần tiến hành nghiên cứu sâu hơn để hiểu rõ hơn về đối tượng.
 Lưu ý: Đã phát hiện độ nhạy cao với tần số. Việc kiểm soát nghiêm ngặt các thông số tần số tiêu chuẩn trong khu vực thí nghiệm là bắt buộc.
 Với bản chất đặc biệt của A038, cần thêm thời gian để thiết lập các thông số phù hợp và ngôn ngữ dữ liệu nhằm thu thập thông tin giá trị về nó. Quá trình này sẽ mất nhiều thời gian với công nghệ và dữ liệu hiện có.
-CẢNH BÁO: Nghiêm cấm mọi hình thức rò rỉ thông tin thí nghiệm. Ban chụp ảnh hoặc ghi hình đối tượng khi chưa có sự cho phép của Giáo sư Heisen.
+CẢNH BÁO: Nghiêm cấm mọi hình thức rò rỉ thông tin thí nghiệm. Cấm chụp ảnh hoặc ghi hình đối tượng khi chưa có sự cho phép của Giáo sư Heisen.
 Đây là kết thúc báo cáo quan sát ban đầu về Đối tượng A038. Để có thông tin toàn diện hơn, các thí nghiệm và phân tích trong tương lai là vô cùng cần thiết.</t>
         </is>
       </c>
@@ -2393,15 +2393,15 @@
           <t>Ngày: [--08]
 Chúng ta đã đến giai đoạn cuối của nghiên cứu, nhưng tiến độ có vẻ chậm lại. Đồng nghiệp lần lượt rời đi. Ngay cả Giáo sư Heisen cũng nói sẽ về bên gia đình... Ông ấy có nói thế thật không?
 Không hiểu sao, ta không chắc lắm. Ta chỉ nhớ lờ mờ ông ấy từng nhắc đến điều gì đó như vậy, nhưng có thật ông ấy đã nói với chúng ta không? Hay ông ấy chỉ thì thầm bên tai ta thôi?
-Trong những đêm dài buồn tẻ như thế này, chỉ có vật thể nhỏ này bầu bạn cùng ta. Thật sự khó tin nó đã lớn và thay đổi đến vậy. Những mảnh kim loại giờ đây phủ kín hình dáng từng đơn sơ của nó: tấm thép, bánh răng, đồng hồ, thiết bị dò tìm, chất lỏng xanh, áo khoác phòng thí nghiệm trắng... và... đó là máy phát điện diesel à? Dù sao thì giờ ta cũng được tận mắt nhìn thấy nó, không cần thông qua thiết bị quan sát.
+Trong những đêm dài buồn tẻ như thế này, chỉ có vật thể nhỏ này bầu bạn cùng ta. Thật khó tin nó đã lớn và thay đổi đến vậy. Những mảnh kim loại giờ đây phủ kín hình dáng từng đơn sơ của nó: tấm thép, bánh răng, đồng hồ, thiết bị dò tìm, chất lỏng xanh, áo khoác phòng thí nghiệm trắng... và... đó là máy phát điện diesel à? Dù sao thì giờ ta cũng được tận mắt nhìn thấy nó, không cần thông qua thiết bị quan sát.
 Này, hôm nay ngươi thế nào? Trông ngươi tràn đầy năng lượng bất ngờ. Nhưng cũng phải thôi, bị giam cầm cả đời, chắc hẳn ngươi khao khát tự do lắm.
 Phòng thí nghiệm hiếm khi yên tĩnh đến thế. Chắc chẳng ai để ý nếu ta phá lệ một chút.
-À... I see. Thì ra cơ thể ngươi sờ vào là thế này.
+À... Ra vậy. Thì ra cơ thể ngươi sờ vào là thế này.
 Đó là tiếng cười của ngươi à? Đây là lần đầu ta nghe thấy giọng ngươi... Nghe quen quen, giống đồng nghiệp của ta.
 Ta thấy rồi... Đó chính là Cánh Cổng mà chúng ta tìm kiếm bấy lâu.
 Sao ta thấy chóng mặt thế này? Cơ thể ta mềm nhũn như nước... không phải của ta nữa.
 Ý thức ta đang trôi nổi trong không khí...
-Hi mọi người... Hóa ra các người đã vào Cánh Cổng trước ta rồi...
+Chào mọi người... Hóa ra các người đã vào Cánh Cổng trước ta rồi...
 "Đừng bước qua," ngươi nói... Ý ngươi là sao?
 Không, có gì đó không ổn...
 Phép màu mà chúng ta chứng kiến... Không thể như thế này được...</t>
@@ -2766,14 +2766,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Đang thu thập... Current Progress 19%... 46%... 78%... 99%... 
+          <t>Đang thu thập... Tiến độ hiện tại 19%... 46%... 78%... 99%... 
 Đã xác định nguồn âm tại tần số khớp với dữ liệu nhập vào.
 Nguồn âm thuộc về, báo cáo phổ RA1819-G.
 Chủ thể: Qianxin
-Profile: Người Hoàng Long - KU-Roro B, Synergy Giả thức tỉnh tự nhiên, lịch sử cộng hưởng 5 năm, hát để xoa dịu tần số hỗn loạn của người khác, tăng cường Forte cho Synergy Giả khác trong khoảng thời gian nhất định mà không gây tổn thất cho người được tăng cường.
-Từng là ca sĩ thường trú tại Nhà hát KU-Roro B, được mệnh danh là "Họa Mi Hoàng Hôn", biểu diễn các ca khúc "Tiếng Ve Mùa Hè Whisperins Băng Giá", "Khúc Ballad Của Bầu Trời", và "Khúc Ballad Ngàn Sao". Sau này gia nhập đội văn nghệ do Ichor và Irv thành lập để hỗ trợ Midnight Rangers chống lại làn sóng TD. Nghi ngờ thất bại Forte do phối hợp cùng đội trong chiến dịch hỗ trợ hậu cần ở phía bắc Midnight Rangers.
+Hồ sơ: Người Huanglong - Jinzhou, Resonator thức tỉnh tự nhiên, lịch sử cộng hưởng 5 năm, hát để xoa dịu tần số hỗn loạn của người khác, tăng cường Forte cho Resonator khác trong khoảng thời gian nhất định mà không gây tổn thất cho người được tăng cường.
+Từng là ca sĩ thường trú tại Nhà hát Jinzhou, được mệnh danh là "Họa Mi Hoàng Hôn", biểu diễn các ca khúc "Tiếng Ve Mùa Hè Thì Thầm Băng Giá", "Khúc Ballad Của Bầu Trời", và "Khúc Ballad Ngàn Sao". Sau này gia nhập đội văn nghệ do Ichor và Irv thành lập để hỗ trợ Midnight Rangers chống lại làn sóng TD. Nghi ngờ thất bại Forte do phối hợp cùng đội trong chiến dịch hỗ trợ hậu cần ở phía bắc Midnight Rangers.
 Hiện chưa có thông tin cập nhật.
-Save trữ: Người tương ứng với tần số này hiện đang "mất tích" và không thể liên lạc.</t>
+Lưu trữ: Người tương ứng với tần số này hiện đang "mất tích" và không thể liên lạc.</t>
         </is>
       </c>
     </row>
@@ -2850,18 +2850,18 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Teahouse Hoa Anh Đào – lựa chọn hoàn hảo cho buổi trà chiều.
-Tea Đặc Sản:
+          <t>Quán Trà Hoa Anh Đào – lựa chọn hoàn hảo cho buổi trà chiều.
+Trà Đặc Sản:
 Lapsang Souchong
 Qingting Maojian
-Tea Homei Thành Nguyên
-Món Tráng Miệng Special:
+Trà Nhài Thành Nguyên
+Món Tráng Miệng Đặc Biệt:
 Sương Sa Xoài
-Sellh Milk Cris
-Chè Beans Đỏ Vỏ Cam
-Dishes Đặc Sắc:
+Bánh Sữa Giòn
+Chè Đậu Đỏ Vỏ Cam
+Món Ăn Đặc Sắc:
 Cá Muối Kho Cà Tím
-Beans Hũ Mapo
+Đậu Hũ Mapo
 Sườn Xào Tiêu Đen</t>
         </is>
       </c>
@@ -2931,8 +2931,8 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Tòa nhà kỷ lục gây lo ngại về môi trường? Zhuyên gia khẳng định Tower Trung Tâm an toàn
-Sau khi Tower Trung Tâm hoàn thành, nhiều người lo ngại tòa nhà cao hơn nghìn mét này có thể gây hại cho môi trường hoặc gặp vấn đề về kết cấu. Giáo sư Anderson, chuyên gia từ Viện Kiến trúc, đã đưa ra một số giải thích.
+          <t>Tòa nhà kỷ lục gây lo ngại về môi trường? Chuyên gia khẳng định Tháp Trung Tâm an toàn
+Sau khi Tháp Trung Tâm hoàn thành, nhiều người lo ngại tòa nhà cao hơn nghìn mét này có thể gây hại cho môi trường hoặc gặp vấn đề về kết cấu. Giáo sư Anderson, chuyên gia từ Viện Kiến trúc, đã đưa ra một số giải thích.
 “Chúng tôi đã nghiên cứu đất và nước ngầm tại khu vực này trong mười năm,” Anderson cho biết. “Với một công trình khổng lồ như vậy, chúng tôi phải đảm bảo nền móng có thể chịu được trọng lượng lâu dài. Nghiên cứu của chúng tôi cho thấy điều kiện địa chất ở đây có thể duy trì tòa nhà trong hơn một thế kỷ, với độ nghiêng và lún tối thiểu.”
 Anderson cũng đề cập đến việc sử dụng vật liệu mới, cho phép nền móng chịu được tòa nhà cao tới hai nghìn mét. “Tuy nhiên, chiều cao hiện tại đã đáp ứng mọi nhu cầu.”
 Về lo ngại về việc che bóng, Anderson nói thêm: “Chúng tôi đã đảm bảo khoảng cách năm mươi mét giữa tháp và các tòa nhà lân cận. Các tầng trên được thiết kế theo hình xoắn ốc để tối đa hóa ánh sáng tự nhiên.”</t>
@@ -3087,7 +3087,7 @@
 Mẹ ơi, mẹ nghĩ khi con đứng trên sân thượng, con có gần bố hơn không?
 Bố có nhìn thấy con từ trên đó như một vì sao không nhỉ?
 Hôm nay con có hỏi cô hướng dẫn, nhưng cô ấy không trả lời.
-Food tối nay ngon quá. Đây là lần đầu con được ăn ở nhà hàng cao thế này! Yao nĩa ở đây cũng khác với ở nhà mình...</t>
+Thức ăn tối nay ngon quá. Đây là lần đầu con được ăn ở nhà hàng cao thế này! Dao nĩa ở đây cũng khác với ở nhà mình...</t>
         </is>
       </c>
     </row>
@@ -3174,19 +3174,19 @@
         <is>
           <t>Mở đầu:
 Đêm đầy sao, hai cuộc biệt ly, lá rơi không tiếng trên đất khách.
-Đêm gió sầu ai nhỏ lệ, lá đá chứng minh tình thù dài lâu.
-Sau Chiến tranh Threnodian, bên bờ sông Tinh Thối ở làng Kỳ Xí, có đôi thanh mai trúc mã. Chí Sinh mười lăm tuổi, dũng mãnh, giỏi bơi lội, không sợ Tacet Field trong thời chiến, từng dẫn dân vượt qua Đêm Đầy Sao, là một anh hùng trẻ. Dã Sinh mười ba tuổi, thông tuệ, thấu hiểu đại cục, mỗi quyết định đều giúp dân thoát hiểm. Hai người rất thân thiết, luôn hỗ trợ nhau.
-Ở khúc sông có một cây cổ thụ xanh tốt, nơi Huanglong từng đại thắng Threnodian, dân làng cho là điềm lành, muốn xây dựng lại quê hương để cầu phúc. Chiến tranh đã kết thúc, lẽ ra hai người được tự do, nhưng lại gặp việc này. Dã Sinh nói: "Dù chiến tranh đã qua, lòng người vẫn còn đau thương. Nếu cây cổ thụ có thể an ủi, đó cũng là điều tốt, ta quyết định cùng họ đi." Ngay lúc đó, họ chia xa, mỗi người giúp xây dựng lại một làng. May mắn thay, thư từ vẫn liên tục, tình cảm không phai nhạt. Đúng như:
+Đêm đêm gió sầu ai nhỏ lệ, lá đá chứng minh tình thù dài lâu.
+Sau Chiến tranh Threnodian, bên bờ sông Tinh Thối ở làng Kỳ Xí, có đôi thanh mai trúc mã. Chí Sinh mười lăm tuổi, dũng mãnh, giỏi bơi lội, không sợ Tổ Tacet trong thời chiến, từng dẫn dân vượt qua Đêm Đầy Sao, là một anh hùng trẻ. Dã Sinh mười ba tuổi, thông tuệ, thấu hiểu đại cục, mỗi quyết định đều giúp dân thoát hiểm. Hai người rất thân thiết, luôn hỗ trợ nhau.
+Giữa khúc sông có một cây cổ thụ xanh tốt, nơi Huanglong từng đại thắng Threnodian, dân làng cho là điềm lành, muốn xây dựng lại quê hương để cầu phúc. Chiến tranh đã kết thúc, lẽ ra hai người được tự do, nhưng lại gặp việc này. Dã Sinh nói: "Dù chiến tranh đã qua, lòng người vẫn còn đau thương. Nếu cây cổ thụ có thể an ủi, đó cũng là điều tốt, ta quyết định cùng họ đi." Ngay lúc đó, họ chia xa, mỗi người giúp xây dựng lại một làng. May mắn thay, thư từ vẫn liên tục, tình cảm không phai nhạt. Đúng như:
 Cành lá cao ngất trời xanh, rễ sâu xa cách vẫn liên thông.
-Dã Sinh cùng đoàn người đến bên cây cổ thụ, rồi tiến hành quy hoạch xây dựng. Villager muốn lấy phúc lành từ cây, nên đặt tên làng kết hợp với tên cây, gọi là Khai Tầm, nghĩa là mở đất mới, từ biệt quá khứ. Một hôm, dân làng bất ngờ phát hiện một chiếc lá lạ. Lá rất tươi, không héo, nhưng trắng xanh. Villager mừng rỡ: "Đây hẳn là đáp ứng của Khai Tầm, là điềm báo thưởng công cho chúng ta. Hãy làm một chiếc bàn nhỏ, đặt trong nhà, sẽ luôn cảm nhận được sự che chở của Khai Tầm." Những người khác nhặt được lá cũng làm theo. Đúng như:
+Dã Sinh cùng đoàn người đến bên cây cổ thụ, rồi tiến hành quy hoạch xây dựng. Dân làng muốn lấy phúc lành từ cây, nên đặt tên làng kết hợp với tên cây, gọi là Khai Tầm, nghĩa là mở đất mới, từ biệt quá khứ. Một hôm, dân làng bất ngờ phát hiện một chiếc lá lạ. Lá rất tươi, không héo, nhưng trắng xanh. Dân làng mừng rỡ: "Đây hẳn là đáp ứng của Khai Tầm, là điềm báo thưởng công cho chúng ta. Hãy làm một chiếc bàn nhỏ, đặt trong nhà, sẽ luôn cảm nhận được sự che chở của Khai Tầm." Những người khác nhặt được lá cũng làm theo. Đúng như:
 Lá sáng trắng trong, lòng mang bao suy nghĩ buồn vui.
 Điềm lành luôn hiện hữu, phúc lộc sẽ dài lâu.
-Không lâu sau, làng xuất hiện một căn bệnh lạ. Người bệnh ban đêm co giật, đau đớn khắp người, như bị búa đập, như bị kiếm đâm. Kỳ lạ hơn, họ nói nghe thấy Lời Than, như tiếng khóc, như tiếng hú, không dứt. Người bệnh không quá năm ngày, tinh thần suy sụp, kiệt quệ. Villager bảo: "Khi chặt cây bên cạnh, ta đã cầu phúc từ Khai Tầm, cành lá truyền khí qua rễ. Nay mạng sống ngắn ngủi, hẳn là Khai Tầm cảnh báo; tiếng than đêm ấy chính là tiếng kêu cứu của Khai Tầm!" Villager cho là đúng, tự kiểm điểm việc chặt cây, không còn dám đốn hạ nữa.
+Không lâu sau, làng xuất hiện một căn bệnh lạ. Người bệnh ban đêm co giật, đau đớn khắp người, như bị búa đập, như bị kiếm đâm. Kỳ lạ hơn, họ nói nghe thấy Lời Than, như tiếng khóc, như tiếng hú, không dứt. Người bệnh không quá năm ngày, tinh thần suy sụp, kiệt quệ. Dân làng bảo: "Khi chặt cây bên cạnh, ta đã cầu phúc từ Khai Tầm, cành lá truyền khí qua rễ. Nay mạng sống ngắn ngủi, hẳn là Khai Tầm cảnh báo; tiếng than đêm ấy chính là tiếng kêu cứu của Khai Tầm!" Dân làng cho là đúng, tự kiểm điểm việc chặt cây, không còn dám đốn hạ nữa.
 Nhưng Dã Sinh ở Khai Tầm cũng không thoát khỏi căn bệnh "đau đêm" này. Chí Sinh ở Bể Cầu Nguyện nghe tin, lo lắng, không đợi trời sáng, vượt Đêm Đầy Sao, xuôi dòng đến Khai Tầm. Khi thấy bên nhà có cây, lá trắng rơi theo mái, lòng anh bất an. Anh còn thấy đầu lá chuyển trắng, không phải điềm lành. Gặp Dã Sinh, thấy nàng gầy guộc, không kìm được nước mắt, nói: "Ngươi biết ngày đó cây cổ thụ chỉ là an ủi lòng người, sao lại tin vào điềm lành? Nay cây có dấu hiệu bất thường, sao không ngăn dân làng dừng những hành động ngu muội, từ bỏ sớm, cùng ta trở về Bể Cầu Nguyện!" Dã Sinh muốn nói nhưng đau đớn không thốt nên lời, chỉ nhìn nhau trong nước mắt. Đúng như:
-Yesterday sao biết việc hôm nay, không thể quay lại nói điều bất thường.
-Vừa dứt lời, đã có người xông vào kéo Chí Sinh đi. Họ nghe lời anh, cho là phỉ báng Khai Tầm, nhốt anh vào phòng trống, cấm túc để tránh gây rối. Night đó, Chí Sinh cũng nghe thấy Lời Than. Nghe tiếng xào xạc ngoài cửa sổ, như có người mở cửa. Cửa mở, Chí Sinh giật mình, người đó chính là Dã Sinh, Dodget mặt nghiêm nghị, không buồn không vui, khẽ gọi anh: "Theo ta, đi tìm nguồn gốc Lời Than."
+Hôm qua sao biết việc hôm nay, không thể quay lại nói điều bất thường.
+Vừa dứt lời, đã có người xông vào kéo Chí Sinh đi. Họ nghe lời anh, cho là phỉ báng Khai Tầm, nhốt anh vào phòng trống, cấm túc để tránh gây rối. Đêm đó, Chí Sinh cũng nghe thấy Lời Than. Nghe tiếng xào xạc ngoài cửa sổ, như có người mở cửa. Cửa mở, Chí Sinh giật mình, người đó chính là Dã Sinh, nét mặt nghiêm nghị, không buồn không vui, khẽ gọi anh: "Theo ta, đi tìm nguồn gốc Lời Than."
 Anh theo Dã Sinh đi khắp làng, bước lên những bậc thang, đi chầm chậm. Họ gặp một linh hồn nói nhà mình ở Bể Cầu Nguyện, lạc đường nên lang thang ở đây. Dã Sinh dẫn linh hồn ra bờ sông Tinh Thối, bảo có thể về nhà bằng cách ngược dòng. Linh hồn cảm kích, chào tạm biệt theo lễ nghi của một chiến binh, hóa ra đó là linh hồn tử sĩ Threnodian.
-Nguồn gốc Lời Than đã được giải quyết, căn bệnh lạ không còn xuất hiện. Dân làng vui mừng, tụ tập ở làng, chỉ có Dã Sinh ngày càng gầy mòn, bệnh tình nặng hơn. Dùng trăm phương không khỏi, ngày càng buồn ngủ, không đầy mười ngày, khó mà tỉnh táo. Night hôm đó, gió lạnh thấu xương, Chí Sinh cảm thấy kiệt sức, đành cầu nguyện Khai Tầm: "Nếu thần mộc có linh, xin hãy thương xót Dã Sinh, cứu mạng nàng." Càng nói càng đau lòng, không ngờ đã rơi lệ. Bỗng nghe tiếng phụ nữ khóc, ngẩng đầu lên, lá trắng chính là khuôn mặt Dã Sinh, cùng anh khóc than.
+Nguồn gốc Lời Than đã được giải quyết, căn bệnh lạ không còn xuất hiện. Dân làng vui mừng, tụ tập ở làng, chỉ có Dã Sinh ngày càng gầy mòn, bệnh tình nặng hơn. Dùng trăm phương không khỏi, ngày càng buồn ngủ, không đầy mười ngày, khó mà tỉnh táo. Đêm hôm đó, gió lạnh thấu xương, Chí Sinh cảm thấy kiệt sức, đành cầu nguyện Khai Tầm: "Nếu thần mộc có linh, xin hãy thương xót Dã Sinh, cứu mạng nàng." Càng nói càng đau lòng, không ngờ đã rơi lệ. Bỗng nghe tiếng phụ nữ khóc, ngẩng đầu lên, lá trắng chính là khuôn mặt Dã Sinh, cùng anh khóc than.
 Chí Sinh nhìn lên cây, bóng Dã Sinh mờ ảo, đưa tay chạm vào, chỉ cảm nhận được vỏ cây sần sùi, mọi chuyện đã rõ ràng. Dã Sinh nói: "Dù chiến tranh đã qua, hậu quả vẫn còn. Người sống và người chết đều bị giam cầm. Thần mộc có linh, linh hồn ta đã kết nối và hòa nhập, dẫn dắt chúng sinh tìm con đường mới. Nay đã hoàn thành, đêm nay là cuộc biệt ly vĩnh viễn." Nói xong, hai người nhìn nhau, không lời. Đúng như:
 Biết là khó cưỡng mệnh trời, lệ rơi mờ mắt lúc chia ly.
 Sống chết, nước chảy, sao phải hỏi Diêm Vương nghiêm khắc.
@@ -3271,21 +3271,21 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Broken Radio: (Tiếng nhiễu sóng)
-Giọng nói Máy: Hệ thống kích hoạt... Analyzing trên bo mạch... Cảnh báo: Bộ phận chân, không tìm thấy. Mô-đun động cơ chính, lỗi... Yêu cầu tắt máy...
-Giọng nói Bực Bội: Chết tiệt, vẫn không được. Tổng hành dinh, đây là Rabbit 2, nghe rõ trả lời. Rabbit 2 gọi Tổng hành dinh, có ai nghe không? Trả lời...
+          <t>Bộ Đàm Hỏng: (Radio Static)
+Robotic Voice: Systems Activating... Performing Onboard Analysis... Alert: Leg Components, Not Found. Main Motor Module, Malfunctioning... Requesting Shutdown...
+Annoyed Voice: Dang it, still not working. HQ, this is Rabbit 2, over. Rabbit 2 to HQ, do you copy? Over...
 —
-Giọng nói Bực Bội: Rabbit 2 đây, đã thử liên lạc vô tuyến với Tổng hành dinh nhiều lần mà vẫn không thấy phản hồi... Tất cả những gì tôi nghe được ở đây là Blu tự kiểm tra đi kiểm tra lại, và... tiếng gió.
-Giọng nói Mệt Mỏi: Sau bao năm chiến đấu với lũ TD, tôi không ngờ lại mắc kẹt ở cái nơi này... Giờ Blu thì hỏng, không đứng dậy được, đi lại cũng không, nói gì đến việc chở tôi về...
-Giọng nói Mệt Mỏi: Home... Lâu lắm rồi tôi chưa về. Hy vọng gia đình vẫn ổn... Trời đang mưa, mà mưa cũng chẳng trả lời tôi được.
-Giọng nói Mệt Mỏi: Lũ Lưu Đày kia, chúng chẳng thèm quan tâm nhà của ngươi ở đâu. Chúng chỉ muốn chặn tín hiệu liên lạc của ngươi và cướp động cơ cùng bộ nguồn khi ngươi không đề phòng thôi...
-Giọng nói Mệt Mỏi: Đỉnh nhất là tôi đã đi tìm chân cho Blu khắp nơi, hóa ra lại bị lũ Excarat cướp mất... Haha...
-Giọng nói Mệt Mỏi: Chắc là mình tránh vận xui không nổi rồi. Blu, chạy kiểm tra lại đi.
-Giọng nói Máy: Hệ thống kích hoạt... Analyzing trên bo mạch... Cảnh báo: Bộ phận chân, không tìm thấy. Đơn vị động cơ chính, lỗi... Yêu cầu tắt máy...
-Giọng nói Mệt Mỏi: Đừng có mà ngủ gục lúc này, ông bạn già. Giờ cậu là người duy nhất trò chuyện với tôi đấy.
-Giọng nói Mệt Mỏi: ... *thở dài* Giờ phải đi tìm động cơ cho cậu thôi. Dù thế nào cũng phải thức nhé, được chứ?
+Annoyed Voice: Rabbit 2 here, I've attempted multiple radio contacts with HQ and received zero response so far... All I can hear out here is Blu checking itself over and over again, and... the wind.
+Exhausted Voice: After fighting those TDs for so many years, I never expected to get stuck in this kind of place... Now Blu's busted, can't stand up or walk, let alone carry me back...
+Exhausted Voice: Home... It's been a while since I last went home. I hope my family's still doing okay... It's raining, and the rain won't even give me an answer.
+Exhausted Voice: Those Exiles, heh, they don't give a darn where your home is. All they care about is how to intercept your comms and steal your motor and power unit when you're least suspecting...
+Exhausted Voice: Best of all, I've been looking for Blu's legs all over the place, and turns out they were snatched by Excarats... Haha...
+Exhausted Voice: You can't run away from bad luck, I guess. Blu, run another check.
+Robotic Voice: Systems Activating... Performing Onboard Analysis... Alert: Leg Components, Not Found. Main Motor Unit, Malfunctioning... Requesting Shutdown...
+Exhausted Voice: Don't you fall asleep on me just yet, old pal. You're the only chat buddy I have right now.
+Exhausted Voice: ... *sigh* Time to go find that motor of yours. You stay awake no matter what, all right?
 —
-Rover: Traces Excarat. Right theo dõi thôi. Còn lũ Lưu Đày chắc chắn có thiết bị liên lạc quanh trại. Test luôn xem sao.</t>
+Rover: Excarats traces. I should follow it. And those Exiles must have their communication device around the camp. Should as well check it out.</t>
         </is>
       </c>
     </row>
@@ -3444,9 +3444,9 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Hướng dẫn sử dụng Mô-đun Save trữ Năng lượng Cảm ứng
-    1. Người vận hành cần lưu ý rằng các màu sắc khác nhau của Battery Cảm ứng tương ứng với điện áp khác nhau và phải được lắp vào khe lưu trữ năng lượng phù hợp.
-    2. Điện áp của Battery Cảm ứng có thể thay đổi thông qua thiết bị cảm biến biến đổi để đáp ứng nhu cầu.
+          <t>Hướng dẫn sử dụng Mô-đun Lưu trữ Năng lượng Cảm ứng
+    1. Người vận hành cần lưu ý rằng các màu sắc khác nhau của Pin Cảm ứng tương ứng với điện áp khác nhau và phải được lắp vào khe lưu trữ năng lượng phù hợp.
+    2. Điện áp của Pin Cảm ứng có thể thay đổi thông qua thiết bị cảm biến biến đổi để đáp ứng nhu cầu.
     3. Do thiếu bảo trì, có thể có chướng ngại vật gần mô-đun, cần dọn dẹp trước khi sử dụng.
     Ví dụ:
     Tàn tích (có thể dọn trực tiếp)
@@ -3524,13 +3524,13 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Sau khi sư phụ qua đời, ta đã luyện kiếm trên ngọn núi này suốt hai mươi năm. Dù nắng gió hay mưa tuyết, ta vẫn không ngừng vung kiếm, mong một ngày đạt tới cảnh giới tối thượng của kiếm đạo. Trong thời gian đó, ta đã đánh bại vô số kẻ thù bằng thanh kiếm này—những kẻ coi thường ta như ta coi thường chúng, và cả những Discord đáng sợ bất ngờ xuất hiện. Ngày qua ngày, ta phải chịu đựng những trận chiến bất tận và lòng thù hận.
+          <t>Sau khi sư phụ qua đời, ta đã luyện kiếm trên ngọn núi này suốt hai mươi năm. Dù nắng gió hay mưa tuyết, ta vẫn không ngừng vung kiếm, mong một ngày đạt tới cảnh giới tối thượng của kiếm đạo. Trong thời gian đó, ta đã đánh bại vô số kẻ thù bằng thanh kiếm này—những kẻ coi thường ta như ta coi thường chúng, và cả những Tacet Discord đáng sợ bất ngờ xuất hiện. Ngày qua ngày, ta phải chịu đựng những trận chiến bất tận và lòng thù hận.
 Ta tin rằng thanh kiếm này đủ sắc bén để đánh bại kẻ thù, nhưng không thể giải tỏa được sự hỗn loạn trong lòng... Có lẽ ta cần một vũ khí mới. Còn thanh kiếm này, ta sẽ để lại cho người có duyên với nó.
-Hai mươi năm trôi qua, ta tin mình đã thấu hiểu sâu sắc hơn về kiếm đạo. Ta đã từ bỏ thanh kiếm nhẹ nhàng, sắc bén, thay vào đó chọn cây Greatsword nặng nề này. Nó thiếu đi sự mãnh liệt và linh hoạt của kiếm, thậm chí có phần vụng về. Nhưng đó chỉ là định kiến do thiếu hiểu biết về lưỡi kiếm. Thực ra, sự kết hợp giữa đà và quán tính của Greatsword giống như một điệu nhảy, luôn khiến kẻ thù bất ngờ. Những chiêu thức tưởng chừng đơn giản, không hoa mỹ, thực chất là kết quả của sự điều khiển sức mạnh tinh tế.
-Tuy nhiên, khi nhìn vào cây Greatsword trong tay, ta nhận ra rằng cả nó lẫn ta đều không thể đạt tới đỉnh cao hoàn hảo, và ta vẫn phải tiếp tục tìm kiếm... Thanh kiếm này, ta sẽ để lại cho người xứng đáng hơn.
+Hai mươi năm trôi qua, ta tin mình đã thấu hiểu sâu sắc hơn về kiếm đạo. Ta đã từ bỏ thanh kiếm nhẹ nhàng, sắc bén, thay vào đó chọn cây Đại Kiếm nặng nề này. Nó thiếu đi sự mãnh liệt và linh hoạt của kiếm, thậm chí có phần vụng về. Nhưng đó chỉ là định kiến do thiếu hiểu biết về lưỡi kiếm. Thực ra, sự kết hợp giữa đà và quán tính của Đại Kiếm giống như một điệu nhảy, luôn khiến kẻ thù bất ngờ. Những chiêu thức tưởng chừng đơn giản, không hoa mỹ, thực chất là kết quả của sự điều khiển sức mạnh tinh tế.
+Tuy nhiên, khi nhìn vào cây Đại Kiếm trong tay, ta nhận ra rằng cả nó lẫn ta đều không thể đạt tới đỉnh cao hoàn hảo, và ta vẫn phải tiếp tục tìm kiếm... Thanh kiếm này, ta sẽ để lại cho người xứng đáng hơn.
 Trong hai mươi năm vội vã đó, ta dần hiểu ra bản chất của kiếm đạo. Nó không bị gò bó bởi hình thức của vũ khí trong tay, cũng không phải là vô số kỹ thuật ta đã dày công luyện tập.
 Chỉ cần trong tâm có một lưỡi kiếm, bất kỳ loại vũ khí và kỹ thuật nào cũng có thể đánh bại kẻ thù.
-Get "lưỡi kiếm" này làm ví dụ. Dù kẻ thù có ở xa đến đâu, chúng cũng không thoát khỏi lưỡi sắc bén của nó. Hơn nữa, nó còn nhanh hơn bất kỳ kỹ thuật nào! Có thể nói, đây chính là hình mẫu hoàn hảo của một lưỡi kiếm. Đáng tiếc là ta nhận ra điều này quá muộn. Thân thể già nua này không còn điều khiển được nó lâu nữa. Vì vậy, ta đã giấu nó ở một nơi sâu trong Thị trấn Cảng Guixu. Hy vọng sẽ có người đủ linh hoạt để tìm thấy nó.
+Lấy "lưỡi kiếm" này làm ví dụ. Dù kẻ thù có ở xa đến đâu, chúng cũng không thoát khỏi lưỡi sắc bén của nó. Hơn nữa, nó còn nhanh hơn bất kỳ kỹ thuật nào! Có thể nói, đây chính là hình mẫu hoàn hảo của một lưỡi kiếm. Đáng tiếc là ta nhận ra điều này quá muộn. Thân thể già nua này không còn điều khiển được nó lâu nữa. Vì vậy, ta đã giấu nó ở một nơi sâu trong Thị trấn Cảng Guixu. Hy vọng sẽ có người đủ linh hoạt để tìm thấy nó.
 Còn bản thân ta, có lẽ trong những ngày cuối đời, ta sẽ nhận một đệ tử và truyền lại những hiểu biết cả đời về kiếm thuật.
 Để ghi nhớ nơi ta chôn chúng, &lt;color=Highlight&gt;ta đã chụp ba bức ảnh từ đỉnh đồi này&lt;/color&gt;—nếu thực sự có người có duyên, có lẽ họ có thể dùng những bức ảnh này để tìm ra ba thanh đao ghi dấu cuộc đời ta.</t>
         </is>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>...Đừng chỉ chú trọng vào những chi tiết bề ngoài, chúng ta phải nhìn xa hơn để tìm ra sự thật. Đây là điều tôi luôn dạy học trò mình. Thế nhưng, phải thừa nhận rằng, chính tôi cũng đã bị đánh lừa bởi vẻ ngoài đó. Lâu nay, tôi cố gắng cải tiến kháng thể, hy vọng chúng có thể giúp chúng ta khám phá Khu Rừng Mờ hiệu quả hơn. Tôi cũng muốn dùng chúng để chữa bệnh cho Hoohoo. Nhưng đến giờ, nghiên cứu của tôi vẫn chưa có kết quả. Tôi phải làm sao đây? Có vẻ như thời gian của Hoohoo không còn nhiều. Nó không chỉ là một Discord, mà còn là một người bạn thực sự. Những kháng thể tôi tạo ra chỉ có thể trì hoãn triệu chứng, chứ không thể chữa khỏi hoàn toàn. Liệu sự ô nhiễm này có không thể đảo ngược? Tôi có thể tìm ra cách trung hòa nó không?
+          <t>...Đừng chỉ chú trọng vào những chi tiết bề ngoài, chúng ta phải nhìn xa hơn để tìm ra sự thật. Đây là điều tôi luôn dạy học trò mình. Thế nhưng, phải thừa nhận rằng, chính tôi cũng đã bị đánh lừa bởi vẻ ngoài đó. Lâu nay, tôi cố gắng cải tiến kháng thể, hy vọng chúng có thể giúp chúng ta khám phá Khu Rừng Mờ hiệu quả hơn. Tôi cũng muốn dùng chúng để chữa bệnh cho Hoohoo. Nhưng đến giờ, nghiên cứu của tôi vẫn chưa có kết quả. Tôi phải làm sao đây? Có vẻ như thời gian của Hoohoo không còn nhiều. Nó không chỉ là một Tacet Discord, mà còn là một người bạn thực sự. Những kháng thể tôi tạo ra chỉ có thể trì hoãn triệu chứng, chứ không thể chữa khỏi hoàn toàn. Liệu sự ô nhiễm này có không thể đảo ngược? Tôi có thể tìm ra cách trung hòa nó không?
 ...Gần đây, tôi phát hiện ra rằng lõi bào tử tinh khiết chúng ta chiết xuất không còn gây ô nhiễm môi trường xung quanh nữa, nên tôi đã thử thêm chúng vào kháng thể. Hoohoo không có phản ứng phụ nào sau khi dùng, thậm chí tình trạng sức khỏe còn cải thiện. Có lẽ lần này tôi đã tạo ra được kháng thể hiệu quả! Nhưng gần đây, bào tử xung quanh lại tăng đột biến. Đó không phải dấu hiệu tốt...</t>
         </is>
       </c>
@@ -3678,7 +3678,7 @@
         <is>
           <t>Một chiếc máy bay vận tải quân sự nhỏ gặp nạn trong chuyến bay tới ■■■. Nguyên nhân vụ tai nạn vẫn đang được điều tra. Ở độ cao khoảng 8.000 feet, chuyến bay bắt đầu hạ cánh xuống ■■■. Máy bay vỡ tan khi đâm xuống đất. Toàn bộ phi hành đoàn đều thiệt mạng trong vụ tai nạn.
 Ngay sau khi cất cánh, chuyến bay đạt độ cao 8.400 feet lúc 13:46. Đến 14:40:25, máy bay phát cảnh báo "Lệch khỏi lộ trình", sau đó rời khỏi độ cao hành trình. Phi hành đoàn không phản hồi cảnh báo.
-Status ghi nhận cuối cùng:
+Trạng thái ghi nhận cuối cùng:
 Độ cao áp suất tiêu chuẩn: 4.234 mét; Hướng bay: 108 độ.
 Không còn tín hiệu radar sau đó.
 Máy bay có giấy chứng nhận bay hợp lệ, không cần sửa chữa lớn trong lần kiểm tra gần nhất. Tất cả phi hành đoàn đều có giấy phép điều khiển hợp pháp. Quy trình kiểm tra an toàn trước khi lên máy bay diễn ra bình thường.
@@ -3686,9 +3686,9 @@
 Cuộc điều tra tiếp theo vẫn đang diễn ra.
 ...
 30 ngày sau vụ tai nạn của chuyến bay vận tải ■■■, hộp đen được thu hồi để phân tích băng ghi âm và dữ liệu. Được biết, phi hành đoàn đã thực hiện các biện pháp an toàn để ghi lại mọi hiện tượng bất thường.
-Theo dữ liệu hộp đen, một lỗi xuất hiện trên màn hình tại ■■■. Họ gặp phải một thành phố lộn ngược giữa không trung, trong khi sương mù dày đặc ngăn cản máy bay tiếp tục hành trình. Đây được báo cáo là hiện tượng điển hình của Etheric Seaic. Phi hành đoàn đã cố gắng điều chỉnh nhưng vô ích. Mất kiểm soát, cơ trưởng bị va đập vào đầu do trọng lực bất thường. Cơ phó cố gắng phanh khẩn cấp nhưng không thành, máy bay lao thẳng xuống ■■■.
+Theo dữ liệu hộp đen, một lỗi xuất hiện trên màn hình tại ■■■. Họ gặp phải một thành phố lộn ngược giữa không trung, trong khi sương mù dày đặc ngăn cản máy bay tiếp tục hành trình. Đây được báo cáo là hiện tượng điển hình của Biển Etheric. Phi hành đoàn đã cố gắng điều chỉnh nhưng vô ích. Mất kiểm soát, cơ trưởng bị va đập vào đầu do trọng lực bất thường. Cơ phó cố gắng phanh khẩn cấp nhưng không thành, máy bay lao thẳng xuống ■■■.
 ...
-Kết luận, tất cả đều thừa nhận rằng tác động tai hại của Lament đang thách thức công nghệ của chúng ta, khi không có cơ sở khoa học nào có thể giải thích những vụ tai nạn như vậy. Trong các báo cáo gần đây, Etheric Seaic đang lan rộng cùng với những cơn Rainy Retroact đáng lo ngại, ảnh hưởng đến cư dân. Để sống sót qua những thảm họa này, chúng ta cần phải tìm ra sự thật ẩn giấu của thế giới này.</t>
+Kết luận, tất cả đều thừa nhận rằng tác động tai hại của Lament đang thách thức công nghệ của chúng ta, khi không có cơ sở khoa học nào có thể giải thích những vụ tai nạn như vậy. Trong các báo cáo gần đây, Biển Etheric đang lan rộng cùng với những cơn Mưa Retroact đáng lo ngại, ảnh hưởng đến cư dân. Để sống sót qua những thảm họa này, chúng ta cần phải tìm ra sự thật ẩn giấu của thế giới này.</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khi Đoàn Tàu Xuyên Rainy I
+          <t xml:space="preserve">Khi Đoàn Tàu Xuyên Mưa I
 </t>
         </is>
       </c>
@@ -3852,21 +3852,21 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>KU-Roro B Folklore Journal I
-KU-Roro B là thành phố mới nhất của Huanglong. Nơi đây nằm ở vùng biên giới, nơi quái vật nguy hiểm rình rập. Dốc hết sức lực, KU-Roro B vẫn vươn lên thịnh vượng bất chấp những mối đe dọa liên tục và kiên định tiến bước trên con đường đầy hứa hẹn.
-Nằm cạnh các thành phố khác, Gorge of Spirits là yết hầu và cửa ngõ bất khả kháng trên mọi tuyến đường. Qua KU-Roro B, du khách có thể tìm đường đến khắp vùng Huanglong. Với vị thế địa lý ưu việt, KU-Roro B tiếp tục khơi nguồn cảm hứng cho thi nhân và mang lại vận may cho thương nhân.
-Văn hóa và tinh thần của KU-Roro B, tất cả đều được ghi lại trong cuốn sách này, mở đầu bằng trận chiến tại Gorge of Spirits.
-KU-Roro B Folklore Journal II
-Trong quá khứ xa xưa, Gorge of Spirits từng được biết đến là ổ Discord tràn lan. Với ý chí kiên cường trước cái chết, những người lính Huanglong đã bảo vệ quê hương khỏi cơn bão hủy diệt đang ập đến. Máu đổ hội tụ thành một mái vòm vững chắc, chặn đứng kẻ thù trước khi chúng kịp giáng đòn quyết định.
+          <t>Biên Niên Ký Văn Hóa Dân Gian Jinzhou I
+Jinzhou là thành phố mới nhất của Huanglong. Nơi đây nằm ở vùng biên giới, nơi quái vật nguy hiểm rình rập. Dốc hết sức lực, Jinzhou vẫn vươn lên thịnh vượng bất chấp những mối đe dọa liên tục và kiên định tiến bước trên con đường đầy hứa hẹn.
+Nằm cạnh các thành phố khác, Gorge of Spirits là yết hầu và cửa ngõ bất khả kháng trên mọi tuyến đường. Qua Jinzhou, du khách có thể tìm đường đến khắp vùng Huanglong. Với vị thế địa lý ưu việt, Jinzhou tiếp tục khơi nguồn cảm hứng cho thi nhân và mang lại vận may cho thương nhân.
+Văn hóa và tinh thần của Jinzhou, tất cả đều được ghi lại trong cuốn sách này, mở đầu bằng trận chiến tại Gorge of Spirits.
+Biên Niên Ký Văn Hóa Dân Gian Jinzhou II
+Trong quá khứ xa xưa, Gorge of Spirits từng được biết đến là ổ Tacet Discord tràn lan. Với ý chí kiên cường trước cái chết, những người lính Huanglong đã bảo vệ quê hương khỏi cơn bão hủy diệt đang ập đến. Máu đổ hội tụ thành một mái vòm vững chắc, chặn đứng kẻ thù trước khi chúng kịp giáng đòn quyết định.
 Bỗng nhiên, một tiếng gầm vang lên từ dưới vực sâu, làm đất trời rung chuyển bởi sự hiện diện hùng mạnh của Loong. Vạch một đường rạch trên bầu trời, sinh vật này xuất hiện giữa ánh sáng chói lòa. Khi tiếng chuông ngân vang, một chiến binh với đôi mắt vàng từ trên cao hạ xuống, đâm xuyên lưỡi kiếm sắc bén qua kẻ Crownless. Tiếng tù và vang dội từ khắp nơi, tiếp thêm sức mạnh và niềm hân hoan cho chiến trường.
-Sau trận chiến này, Gorge of Spirits được chỉ định làm biên giới phòng thủ, bảo vệ KU-Roro B và người dân Huanglong.
-KU-Roro B Folklore Journal III
-Tượng Sentinel nằm ở lối ra của Gorge, một biểu tượng uy nghi và bùa hộ pháp được phép đứng giữa mọi hỗn loạn. Sentinel của KU-Roro B - "Jué" - đại diện cho một vì sao của Qingloong, mang sứ mệnh thanh tẩy cái ác và ban phước lành tinh khiết cho KU-Roro B.
-Mỗi khi một vị Guan Chấp Chính được chọn hay một quyết định quan trọng sắp được đưa ra, Jué sẽ hiện diện như một bàn tay dẫn lối.
-KU-Roro B Folklore Journal IV
-Điểm hẹn chung cho các lễ hội của KU-Roro B bắt đầu từ Quảng Trường Knell đến Tượng Sentinel. Người dân cầu nguyện trước bức tượng im lặng, dù là để cầu mùa màng bội thu hay bình yên.
-Trong Carnival Loong Spring, phố phường KU-Roro B trở nên nhộn nhịp với hoa tươi và tiếng trống múa lân. Thông thường, người dân đón mừng bằng cách dọn dẹp nhà cửa, trong khi các thương nhân tung ra sản phẩm mới để chào đón một năm mới.
-Ngay cả Midnight Rangers cũng tuân theo những nghi thức này. Khi họ không mệt mỏi chống lại Discord trong những đêm dài đằng đẵng, người dân KU-Roro B vẫn có thể sum vầy trong niềm vui.</t>
+Sau trận chiến này, Gorge of Spirits được chỉ định làm biên giới phòng thủ, bảo vệ Jinzhou và người dân Huanglong.
+Biên Niên Ký Văn Hóa Dân Gian Jinzhou III
+Tượng Sentinel nằm ở lối ra của Gorge, một biểu tượng uy nghi và bùa hộ pháp được phép đứng giữa mọi hỗn loạn. Sentinel của Jinzhou - "Jué" - đại diện cho một vì sao của Qingloong, mang sứ mệnh thanh tẩy cái ác và ban phước lành tinh khiết cho Jinzhou.
+Mỗi khi một vị Quan Chấp Chính được chọn hay một quyết định quan trọng sắp được đưa ra, Jué sẽ hiện diện như một bàn tay dẫn lối.
+Biên Niên Ký Văn Hóa Dân Gian Jinzhou IV
+Điểm hẹn chung cho các lễ hội của Jinzhou bắt đầu từ Quảng Trường Knell đến Tượng Sentinel. Người dân cầu nguyện trước bức tượng im lặng, dù là để cầu mùa màng bội thu hay bình yên.
+Trong Lễ Hội Loong Mùa Xuân, phố phường Jinzhou trở nên nhộn nhịp với hoa tươi và tiếng trống múa lân. Thông thường, người dân đón mừng bằng cách dọn dẹp nhà cửa, trong khi các thương nhân tung ra sản phẩm mới để chào đón một năm mới.
+Ngay cả Midnight Rangers cũng tuân theo những nghi thức này. Khi họ không mệt mỏi chống lại Tacet Discord trong những đêm dài đằng đẵng, người dân Jinzhou vẫn có thể sum vầy trong niềm vui.</t>
         </is>
       </c>
     </row>
@@ -3948,20 +3948,20 @@
         <is>
           <t>"Kìa, một con thú giống như sư tử. Nó toát lên sức mạnh và trí tuệ, hành xử như con người...
 Ngày xưa, một loài thú ẩn dật tên Suan'ni sinh sống trong khu rừng xa xôi ở Huanglong.
-Truyền thuyết kể rằng những chiến binh vĩ đại này căm ghét cái ác như kẻ thù không đội trời chung, ban tặng lòng dũng cảm cho con người. Hình ảnh của chúng thường dẫn đầu đoàn quân chiến đấu, áp đảo kẻ địch bằng sức mạnh phi thường. Một chống trăm, chúng phá vỡ cuộc tấn công của Discord, nên được tôn vinh như linh thú may mắn và người bạn trung thành của loài người.
+Truyền thuyết kể rằng những chiến binh vĩ đại này căm ghét cái ác như kẻ thù không đội trời chung, ban tặng lòng dũng cảm cho con người. Hình ảnh của chúng thường dẫn đầu đoàn quân chiến đấu, áp đảo kẻ địch bằng sức mạnh phi thường. Một chống trăm, chúng phá vỡ cuộc tấn công của Tacet Discord, nên được tôn vinh như linh thú may mắn và người bạn trung thành của loài người.
 Để tưởng nhớ chiến công ấy và truyền lại phước lành, con người đã sáng tạo ra múa Lân, mô phỏng những bước di chuyển của chúng thành điệu nhảy. Đến nay, múa Lân vẫn còn nhiều người kế tục ở Huanglong.
-Friendship quý giá ấy đã kéo dài hàng trăm năm sau đó.
-Thật sự không may, Hiện Tượng Waveworn bắt đầu hoành hành, nuốt chửng sinh vật và những khu rừng tươi tốt nơi mối quan hệ giữa con người và Suan'ni gắn bó.
+Tình bạn quý giá ấy đã kéo dài hàng trăm năm sau đó.
+Thật không may, Hiện Tượng Waveworn bắt đầu hoành hành, nuốt chửng sinh vật và những khu rừng tươi tốt nơi mối quan hệ giữa con người và Suan'ni gắn bó.
 Sau này, lời đồn đoán lan truyền rằng Suan'ni đã trở nên hung dữ.
-Người ta nói chúng xâm chiếm lãnh thổ con người và xua đuổi mọi sinh vật trong tầm với... Chúng còn là điềm báo của Tacet Field.
-Một số người phản đối, cho rằng Suan'ni là tín hiệu cảnh báo sớm, bảo vệ con người khỏi hiểm họa Tacet Field đang đến gần.
+Người ta nói chúng xâm chiếm lãnh thổ con người và xua đuổi mọi sinh vật trong tầm với... Chúng còn là điềm báo của Tổ Tacet.
+Một số người phản đối, cho rằng Suan'ni là tín hiệu cảnh báo sớm, bảo vệ con người khỏi hiểm họa Tổ Tacet đang đến gần.
 Khó mà phân định bản chất của chúng, người ta đặt một dấu hỏi lớn về sự tồn tại của Suan'ni... Trong những suy đoán, ta chỉ có thể coi những kẻ độc ác kia là một phần nhỏ của Suan'ni.
 Còn lý do... có lẽ liên quan đến việc mất lãnh thổ, tranh giành quyền lực do tài nguyên cạn kiệt... Hoặc Hiện Tượng Waveworn chính là nguyên nhân chính dẫn đến sự đột biến hung hãn của chúng.
-Khi các nhà nghiên cứu đạt được những phát hiện sâu hơn, hầu hết đều công nhận Năng Lực Synergy là sức mạnh có thể đạt được từ chính trái tim mỗi người. Nếu không được kiểm soát, nó sẽ dẫn đến sự hủy diệt. Trong các nghiên cứu sau này, người ta xác nhận Suan'ni sở hữu một loại sức mạnh đặc biệt tương tự Năng Lực Synergy. Thậm chí, một con Suan'ni mạnh còn có thể "Overclock" như Synergy Giả.
+Khi các nhà nghiên cứu đạt được những phát hiện sâu hơn, hầu hết đều công nhận Năng Lực Cộng Hưởng là sức mạnh có thể đạt được từ chính trái tim mỗi người. Nếu không được kiểm soát, nó sẽ dẫn đến sự hủy diệt. Trong các nghiên cứu sau này, người ta xác nhận Suan'ni sở hữu một loại sức mạnh đặc biệt tương tự Năng Lực Cộng Hưởng. Thậm chí, một con Suan'ni mạnh còn có thể "Overclock" như Resonator.
 Nhiều nhà khoa học tin rằng Suan'ni đã chấp nhận diệt vong khi thất bại trong cuộc chiến chống lại bản năng hung bạo bên trong.
 Nhưng ta tin rằng những kẻ sống sót của Suan'ni vẫn sẽ nhớ về tình bạn xưa với loài người.
 Vì tò mò tự nhiên về truyền thuyết loài thú, ta quyết định mạo hiểm vào vùng đất từng là nơi cư ngụ của Suan'ni. Nếu ai đó thấy thú vị qua bài viết này, thì công sức của ta cũng không uổng phí.
-Điểm đến tiếp theo: Violet Banyan."</t>
+Điểm đến tiếp theo: Cây Đa Tím."</t>
         </is>
       </c>
     </row>
@@ -4046,21 +4046,21 @@
         <is>
           <t>Lo, Lo, Lô Lô Vận Tải! Phần Một
 Lo, Lo, Lô Lô Vận Tải! Hôm nay mình muốn trở thành một người giao hàng đáng tự hào!
-Là một người giao hàng, âm thanh êm dịu nhất chính là tiếng còi tàu buổi sớm khi cập bến. Mỗi ngày, Port Gunchao chứng kiến những tuyến đường thủy nhộn nhịp nhất ở Huanglong, chở theo cả hàng hóa lẫn những câu chuyện từ phương xa—tất cả những điều này mình đều biết từ cô Lumi!
-Theo cô Lumi, Port Gunchao là cảng vận tải hàng hóa lớn nhất ở Huanglong! Mọi kiện hàng đến KU-Roro B đều phải đi qua cảng này! Khi những con tàu neo đậu bên bờ vào buổi sáng, tiếng còi dài vang lên báo hiệu sự xuất hiện của hàng hóa mới và khởi đầu cho một ngày bận rộn.
+Là một người giao hàng, âm thanh êm dịu nhất chính là tiếng còi tàu buổi sớm khi cập bến. Mỗi ngày, Cảng Gunchao chứng kiến những tuyến đường thủy nhộn nhịp nhất ở Huanglong, chở theo cả hàng hóa lẫn những câu chuyện từ phương xa—tất cả những điều này mình đều biết từ cô Lumi!
+Theo cô Lumi, Cảng Gunchao là cảng vận tải hàng hóa lớn nhất ở Huanglong! Mọi kiện hàng đến Jinzhou đều phải đi qua cảng này! Khi những con tàu neo đậu bên bờ vào buổi sáng, tiếng còi dài vang lên báo hiệu sự xuất hiện của hàng hóa mới và khởi đầu cho một ngày bận rộn.
 Những người giao hàng như mình phải hoàn thành mọi đơn hàng mà không được sai sót, vì chúng mang theo cả sự mong đợi từ mọi ngóc ngách của SOL3, vượt núi băng biển. Gần đây, danh sách đơn hàng của mình thường xuyên xuất hiện những yêu cầu giao hàng từ Mỏ Hổ Nham. Nghĩ đến việc mình có thể giúp chuyển những phương tiện chứa đựng tình yêu và tiếng nói quý giá đến Thục Châu, Thiệu Châu, và những nơi xa xôi khác ở Huanglong, mình lại thấy phấn khích.
 Và các tiền bối trong chi nhánh còn kể cho mình nghe về một hòn đảo huyền thoại nằm ở nơi xa xôi nhất trên hành tinh. Chỉ những người tài giỏi nhất mới có thể tiếp cận cánh cổng bí ẩn dẫn đến đó! Nếu thư từ của mình cuối cùng cũng đến được bờ biển ấy, có lẽ mình sẽ được tôn vinh là một người giao hàng xuất sắc! Mình tin chắc mình sẽ có cơ hội! Hehe!
-Bởi vì chủ đề của chúng ta hôm nay là: Lo, Lo, Lô Lô Vận Tải! Hôm nay mình muốn trở thành một người giao hàng đáng tự hào! Hmm, suýt nữa thì quên... Address... Address đơn hàng tiếp theo của mình là gì nhỉ...
+Bởi vì chủ đề của chúng ta hôm nay là: Lo, Lo, Lô Lô Vận Tải! Hôm nay mình muốn trở thành một người giao hàng đáng tự hào! Hmm, suýt nữa thì quên... Địa chỉ... Địa chỉ đơn hàng tiếp theo của mình là gì nhỉ...
 Lo, Lo, Lô Lô Vận Tải! Phần Hai
 Lo, Lo, Lô Lô Vận Tải! Hôm nay mình muốn trở thành một người giao hàng đáng tự hào!
 Vừa nhắc đến âm thanh, có lẽ tiếng gió nhẹ lướt qua bộ đồng phục của chúng ta cũng xứng đáng được nhắc đến! Mình có thể nghe thấy tiếng gió gào thét khi lái xe giao hàng để chuyển đơn. Đó như một lời nhắc nhở trên hành trình, thúc giục mình phải nhanh chân hơn với những tiếng hô vang.
-Nhưng hãy nhớ rằng an toàn là trên hết! Bởi vì bạn có thể gặp phải những Discord nguy hiểm trông giống hệt đèn giao thông. Chỉ cần tuân thủ quy tắc: đỏ dừng, xanh đi, ghi nhớ điều này mọi lúc! Nếu không, bạn sẽ thu hút sự chú ý của những con quái vật hung dữ! Không ai có thể đoán trước được tình hình quanh cảng, vì Discord luôn rình rập với sự hiện diện đáng sợ... Tình hình còn tồi tệ hơn khi chúng ta phải di chuyển giữa đây và cảng cũ...
-Ồ, theo cô Lumi, nơi đó từng lộng lẫy như Port Gunchao. Nhưng hoạt động vận tải đã bị phá hủy bởi sự xuất hiện đột ngột của vùng đứt gãy. Tệ hơn nữa, Discord bắt đầu xuất hiện từ hư không... Sau đó, cảng chỉ còn biết chia tay những ngày tháng nhộn nhịp và chìm vào quên lãng. Thật sự đáng tiếc. Mình nghĩ vẫn còn rất nhiều kiện hàng bị kẹt lại ở đó cho đến ngày nay... Chà, đó không phải điều mà một dịch vụ giao hàng nhanh mong đợi. Không biết những kiện hàng ấy có thể đến tay người nhận không...
+Nhưng hãy nhớ rằng an toàn là trên hết! Bởi vì bạn có thể gặp phải những Tacet Discord nguy hiểm trông giống hệt đèn giao thông. Chỉ cần tuân thủ quy tắc: đỏ dừng, xanh đi, ghi nhớ điều này mọi lúc! Nếu không, bạn sẽ thu hút sự chú ý của những con quái vật hung dữ! Không ai có thể đoán trước được tình hình quanh cảng, vì Tacet Discord luôn rình rập với sự hiện diện đáng sợ... Tình hình còn tồi tệ hơn khi chúng ta phải di chuyển giữa đây và cảng cũ...
+Ồ, theo cô Lumi, nơi đó từng lộng lẫy như Cảng Gunchao. Nhưng hoạt động vận tải đã bị phá hủy bởi sự xuất hiện đột ngột của vùng đứt gãy. Tệ hơn nữa, Tacet Discord bắt đầu xuất hiện từ hư không... Sau đó, cảng chỉ còn biết chia tay những ngày tháng nhộn nhịp và chìm vào quên lãng. Thật đáng tiếc. Mình nghĩ vẫn còn rất nhiều kiện hàng bị kẹt lại ở đó cho đến ngày nay... Chà, đó không phải điều mà một dịch vụ giao hàng nhanh mong đợi. Không biết những kiện hàng ấy có thể đến tay người nhận không...
 Có lẽ trạm cung ứng mới của chúng ta sẽ giải quyết được vấn đề? Được rồi, nơi làm việc tiếp theo của mình đã được quyết định! Lo, Lo, Lô Lô Vận Tải! Hôm nay mình muốn trở thành một người giao hàng đáng tự hào!
 Lo, Lo, Lô Lô Vận Tải! Phần Ba
 Lo, Lo, Lô Lô Vận Tải! Hôm nay mình muốn trở thành một người giao hàng đáng tự hào!
 Tiếp tục chủ đề về âm thanh... Mình nghĩ không thể bỏ qua những tiếng thì thầm kỳ lạ từ Đầm Than Vãn của Aix. Không, những âm thanh đó hoàn toàn KINH KHỦNG!
-Để mình giải thích chi tiết: Mình đã yêu cầu chuyển đến trạm cung ứng mới. Nhưng một số kẻ Lưu Đày ẩn nấp gần đó đã đột kích trại của chúng ta và cướp sạch. Không thể tin được... Mình biết đây không chỉ là những kiện hàng thông thường, chúng là biểu tượng mạnh mẽ của tình cảm. Cô Lumi cũng đồng ý với mình. Từ lần gặp đầu tiên, mình đã biết cô ấy là một hoa tiêu ấn tượng. Dù còn trẻ, cô ấy xử lý mọi đơn hàng một cách tỉ mỉ, và điều đó giúp cô ấy tìm ra lộ trình nhanh nhất bất chấp mọi chướng ngại vật và đống đổ nát trên đường. Khi giao hàng đến tay khách hàng trong tình trạng nguyên vẹn, cô ấy kết thúc công việc với một nụ cười rạng rỡ. Thật sự dễ thương...
+Để mình giải thích chi tiết: Mình đã yêu cầu chuyển đến trạm cung ứng mới. Nhưng một số kẻ Lưu Đày ẩn nấp gần đó đã đột kích trại của chúng ta và cướp sạch. Không thể tin được... Mình biết đây không chỉ là những kiện hàng thông thường, chúng là biểu tượng mạnh mẽ của tình cảm. Cô Lumi cũng đồng ý với mình. Từ lần gặp đầu tiên, mình đã biết cô ấy là một hoa tiêu ấn tượng. Dù còn trẻ, cô ấy xử lý mọi đơn hàng một cách tỉ mỉ, và điều đó giúp cô ấy tìm ra lộ trình nhanh nhất bất chấp mọi chướng ngại vật và đống đổ nát trên đường. Khi giao hàng đến tay khách hàng trong tình trạng nguyên vẹn, cô ấy kết thúc công việc với một nụ cười rạng rỡ. Thật dễ thương...
 Nhân tiện, những kẻ Lưu Đày chỉ là một phần nhỏ trong khó khăn của chúng ta. Ví dụ như sương mù dày đặc ở Đầm Than Vãn của Aix. Nó thường báo hiệu một cơn giông kèm theo những tiếng thét chói tai, mang đến cảm giác buồn bã và... một nỗi nhớ da diết. Đó là nơi định vị thường xuyên thất bại khi sương mù dần nuốt chửng bạn.
 Những sự kiện tàn khốc. Mình không thể tưởng tượng nổi bản thân bị bao phủ bởi lớp sương mù dày đặc và tiếng Siren... Eek! Không thể nghĩ tiếp được. Đến lúc quay lại làm việc và trở thành một người giao hàng đáng tự hào hôm nay!</t>
         </is>
@@ -4151,21 +4151,21 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Untitled Family Letters IV
+          <t>Những lá thư gia đình vô đề IV
 ...Tôi không biết bắt đầu lá thư này như thế nào. Đại tướng Jiyan, tôi muốn nói lời cảm ơn. Nhờ ngài, tin nhắn của anh ấy cuối cùng cũng đến được với chúng tôi như thế này.
 Thỉnh thoảng tôi vẫn nhớ về những ngày tháng bên anh. Anh từng nói rằng ai đó phải trở thành người bảo vệ, dù điều đó có nghĩa là phải hy sinh. Trong những bức tranh xa xôi về chiến trường, ngài đã đứng vững trước kẻ thù, dùng sức mạnh của mình hỗ trợ anh và những người lính khác. Anh bảo ngài đã cứu mạng anh vô số lần. Ngài là hình mẫu của anh, người lính xuất sắc nhất, mang trong mình trái tim của chiến binh và ý chí của người cho đi. Anh muốn trở thành như ngài. Dù anh đã hy sinh mạng sống để bảo vệ đồng đội, tôi không nghĩ anh sẽ hối tiếc.
 Đó là những gì ngài đã nói với tôi, rằng anh luôn bảo vệ những người lính khác ngay cả khi đối mặt với hiểm nguy lớn nhất, rằng anh xứng đáng là một anh hùng.
-Night đó, tôi gặp anh trong một giấc mơ mưa đau lòng, giống hệt ngày cha tôi qua đời. Anh mở cửa, chào tôi như thể vừa trở về. Cuộc hội ngộ sớm khiến tôi phải hỏi: Sao anh về được? Tôi tưởng chiến tranh vẫn còn đang diễn ra.
-Anh đáp: Anh chỉ muốn xem em và Xiaobao có ổn không thôi. Xiaobao ngủ rồi chứ? Nếu mọi thứ ổn, anh sẽ đi ngay.
+Đêm đó, tôi gặp anh trong một giấc mơ mưa đau lòng, giống hệt ngày cha tôi qua đời. Anh mở cửa, chào tôi như thể vừa trở về. Cuộc hội ngộ sớm khiến tôi phải hỏi: Sao anh về được? Tôi tưởng chiến tranh vẫn còn đang diễn ra.
+Anh đáp: Anh chỉ muốn xem em và Tiểu Bảo có ổn không thôi. Tiểu Bảo ngủ rồi chứ? Nếu mọi thứ ổn, anh sẽ đi ngay.
 Rồi anh nói thêm: Mọi người trên chiến trường không thể nào thư giãn được khi chiến tranh sắp kết thúc. Họ đã sẵn sàng tung đòn quyết định.
-Tôi gật đầu: Anh cứ làm nhiệm vụ đi, đừng lo cho chúng tôi. Hãy là một chiến binh dũng cảm và đánh bại lũ quái vật đó. Steps anh chững lại, như thể do dự. Tôi giục anh quay lại, và trong lo lắng, tôi lao vào vòng tay anh. Anh hỏi: Nếu anh chết trong trận chiến thì sao? Em và Xiaobao sẽ ra sao?
+Tôi gật đầu: Anh cứ làm nhiệm vụ đi, đừng lo cho chúng tôi. Hãy là một chiến binh dũng cảm và đánh bại lũ quái vật đó. Bước chân anh chững lại, như thể do dự. Tôi giục anh quay lại, và trong lo lắng, tôi lao vào vòng tay anh. Anh hỏi: Nếu anh chết trong trận chiến thì sao? Em và Tiểu Bảo sẽ ra sao?
 Bị đặt trước tình thế khó xử, tôi hỏi lại: Anh có bao giờ hối hận khi gia nhập quân đội không?
 Anh nói không, nếu điều đó giúp bảo vệ quê hương.
 "Em cũng vậy." Tôi đáp.
-Khi tỉnh dậy từ giấc mơ đó, tôi chợt nảy ra ý định đưa Xiaobao đi xem Vở Kịch Anh Hùng. Trong Nhà hát, nữ anh hùng ở Fiamma cầm kiếm chiến đấu dũng cảm với Fluffernox trong khi sân khấu chìm trong lửa. Bị quái vật tấn công, cô ngã xuống đất hết lần này đến lần khác. Khi cô gượng dậy sau những đau đớn liên tiếp, nước mắt tôi tuôn rơi. Tôi nói với Xiaobao rằng bố con là một anh hùng có thể sánh ngang với Fiamma.
-Xiaobao hào hứng đáp lại: Con muốn trở thành anh hùng như bố!
+Khi tỉnh dậy từ giấc mơ đó, tôi chợt nảy ra ý định đưa Tiểu Bảo đi xem Vở Kịch Anh Hùng. Trong Nhà hát, nữ anh hùng ở Fiamma cầm kiếm chiến đấu dũng cảm với Fluffernox trong khi sân khấu chìm trong lửa. Bị quái vật tấn công, cô ngã xuống đất hết lần này đến lần khác. Khi cô gượng dậy sau những đau đớn liên tiếp, nước mắt tôi tuôn rơi. Tôi nói với Tiểu Bảo rằng bố con là một anh hùng có thể sánh ngang với Fiamma.
+Tiểu Bảo hào hứng đáp lại: Con muốn trở thành anh hùng như bố!
 Tôi hứa sẽ kể lại tất cả những câu chuyện này cho con và mọi linh hồn còn sống.
-Maila Đại tướng, tôi sẽ ghi nhớ điều này đến cuối đời, và khắc tên họ lên tảng đá vĩnh cửu.</t>
+Thưa Đại tướng, tôi sẽ ghi nhớ điều này đến cuối đời, và khắc tên họ lên tảng đá vĩnh cửu.</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
           <t>Hôm nọ tôi nhận được một tin nhắn.
 Chẳng có gì đặc biệt, chỉ là thông báo từ ga tàu gửi đến những hành khách bị trễ chuyến. Nội dung thế này: "Tàu Tương Lai chân thành xin lỗi quý khách. Chúng tôi sẽ đảm bảo dịch vụ trọn vẹn cho đến khi quý khách đến đích." Tôi đọc xong rồi xóa đi, nghĩ bụng: "Chắc ga tàu gửi nhầm. Lâu lắm rồi tôi không đi tàu."
 Nhưng đó mới chỉ là khởi đầu. Những tin nhắn kỳ lạ về con tàu Tương Lai này cứ liên tục gửi đến. Ban đầu tôi chuyển chúng vào mục spam. Tôi sống cho hiện tại. Những chuyến đi dài và tương lai xa vời ấy không thuộc về thế giới của tôi. Tôi bận rộn chạy việc quanh mỏ, nghe đủ thứ phàn nàn từ mấy nhà nghiên cứu. Đến cả một thợ mỏ nhỏ như tôi cũng thấy hơi thấp thỏm khi năm sắp hết.
-Nhưng những tin nhắn này đang giết tôi dần. Một lần tranh thủ lúc nghỉ việc, tôi kiểm tra lại và một đoạn tin đặc biệt đã thu hút sự chú ý của tôi (có lẽ là của một đứa trẻ): "Bố ơi. Người phục vụ bảo con ngồi yên vì tàu sắp rời ga rồi. Chúng ta sẽ đến tương lai ngay thôi! Cô ấy sẽ niệm một câu thần chú để bảo vệ chúng ta cho đến khi tàu đến nơi. Nhưng con không biết tương lai là gì..." Những lời này khiến tôi nhớ đến con gái mình, cùng sự tò mò háo hức như thế khi còn nhỏ. Dù đã lâu không gặp con bé, tôi không muốn làm đứa trẻ gửi tin này thất vọng vì những trì hoãn và chờ đợi. Thế nên tôi trả lời: Bố biết tương lai là gì. Tương lai là nơi con được ăn Sellh Sao và thực hiện mọi ước mơ của mình.
+Nhưng những tin nhắn này đang giết tôi dần. Một lần tranh thủ lúc nghỉ việc, tôi kiểm tra lại và một đoạn tin đặc biệt đã thu hút sự chú ý của tôi (có lẽ là của một đứa trẻ): "Bố ơi. Người phục vụ bảo con ngồi yên vì tàu sắp rời ga rồi. Chúng ta sẽ đến tương lai ngay thôi! Cô ấy sẽ niệm một câu thần chú để bảo vệ chúng ta cho đến khi tàu đến nơi. Nhưng con không biết tương lai là gì..." Những lời này khiến tôi nhớ đến con gái mình, cùng sự tò mò háo hức như thế khi còn nhỏ. Dù đã lâu không gặp con bé, tôi không muốn làm đứa trẻ gửi tin này thất vọng vì những trì hoãn và chờ đợi. Thế nên tôi trả lời: Bố biết tương lai là gì. Tương lai là nơi con được ăn Bánh Sao và thực hiện mọi ước mơ của mình.
 Vài ngày sau, tin nhắn lại ập đến thiết bị đầu cuối của tôi với thông báo trễ chuyến: "Chúng tôi chân thành xin lỗi vì sự trì hoãn. Tàu Tương Lai sẽ sớm khởi hành và đảm bảo mang đến cho quý khách một hành trình an toàn, hạnh phúc nhất." Tin nhắn còn kết thúc bằng câu: "Tàu Tương Lai sẽ gặp lại quý khách ở tương lai." Ngay sau đó là một tin khác: "Khi nào chúng ta mới được đi? Lil cứ hỏi tôi mãi. Tôi chỉ biết trả lời bằng những lời hứa suông, rằng 'Sắp rồi, chúng ta sẽ sớm đến tương lai.' Sảnh ga đầy những hành khách lo lắng, mỗi người đều ôm nỗi khát khao rời đi. Và tôi cũng vậy. May mắn là có một người tốt bụng cho tôi chút thức ăn, giúp tôi bình tĩnh lại đôi chút. *thở dài* Khi nào chúng ta mới được đi..." Tin này trông như gửi đến ga tàu, nhưng lại lọt vào thiết bị của tôi. May mà những ngày đó tôi có chút thời gian rảnh. Với suy nghĩ muốn động viên người gửi, tôi trả lời: Tàu sắp rời ga rồi. Hãy kiên nhẫn chờ đợi.
 Những tin nhắn ấy vẫn không ngừng gửi đến. Thỉnh thoảng tôi vẫn nhận được. Trong một bữa ăn với đồng nghiệp, tôi nhắc đến chủ đề này và những tin nhắn rối rắm, kỳ lạ trong thiết bị của mình. Đôi lúc tôi thấy mình như bị thôi thúc phải an ủi những hành khách đang thất vọng.
 Họ nói với vẻ nghi ngờ tuyệt đối, rằng chẳng có thứ gì gọi là Tàu Tương Lai cả.
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>A Diary Đội Khảo Sát Rừng Âm U: VIII
+          <t>Nhật Ký Đội Khảo Sát Rừng Âm U: VIII
 Một loạt biến cố, như sự quấy nhiễu của Hoochief, đã dẫn đến mất mát phần lớn dữ liệu nghiên cứu của chúng tôi.
 Tuy nhiên, trong khi thu thập lại dữ liệu, chúng tôi vẫn được chứng kiến những nỗ lực dũng cảm của những người đi trước tại Rừng Âm U.
 Nghiên cứu &lt;ano=Ecoacoustics&gt;sinh thái&lt;/ano&gt; là một lĩnh vực phức tạp. Những vấn đề như tìm điểm đột phá then chốt và cách bắt đầu nghiên cứu đều là những điều chúng ta cần lưu tâm.
@@ -4431,13 +4431,13 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>AL110 SentinelSentinel đánh bại Threnodian, và một cô bé tên Xinyi dùng ngọn lửa nhỏ để thắp lại niềm hy vọng trong lòng mọi người. Cô đứng trước đám đông tại nơi tạm trú, truyền đi thông điệp đầy cảm hứng, khơi dậy khát vọng tái thiết khắp Huanglong. Xinyi dẫn dắt bước đầu tiên của công cuộc xây dựng lại quanh Núi Firmament – nơi yên nghỉ của Sentinel.
-AL115 Sau khi Resonance Nexus chiếu hình ảnh của Resonance Beacon, địa điểm xây dựng thủ đô mới được xác định – chính là KU-Roro B.
-AL116 Enter ngày đầu tiên của năm mới, công trình xây dựng thủ đô mới KU-Roro B chính thức khởi công.
-AL120 Giai đoạn đầu xây dựng KU-Roro B hoàn thành, phần lớn cư dân từ khắp nơi trên thế giới đã chuyển đến sinh sống. Trong những thập kỷ sau, cơ sở hạ tầng của KU-Roro B không ngừng được cải thiện.
-AL134 KU-Roro B lần đầu hứng chịu Dịch Bùng Play TDTD, và kể từ đó, dịch bệnh này thường xuyên tái diễn, trở thành một trong những mối đe dọa lớn nhất đối với Huanglong.
+AL115 Sau khi Resonance Nexus chiếu hình ảnh của Resonance Beacon, địa điểm xây dựng thủ đô mới được xác định – chính là Jinzhou.
+AL116 Vào ngày đầu tiên của năm mới, công trình xây dựng thủ đô mới Jinzhou chính thức khởi công.
+AL120 Giai đoạn đầu xây dựng Jinzhou hoàn thành, phần lớn cư dân từ khắp nơi trên thế giới đã chuyển đến sinh sống. Trong những thập kỷ sau, cơ sở hạ tầng của Jinzhou không ngừng được cải thiện.
+AL134 Jinzhou lần đầu hứng chịu Dịch Bùng Phát TDTD, và kể từ đó, dịch bệnh này thường xuyên tái diễn, trở thành một trong những mối đe dọa lớn nhất đối với Huanglong.
 AL155 Để cổ vũ tinh thần nhân dân, một buổi lễ tôn vinh Tứ Anh Hùng của Huanglong được tổ chức. Cùng năm đó, Jinhsi – người cộng hưởng với Sentinel – trở thành Tân Long Chủ.
-AL157 Huanglong hứng chịu cuộc tấn công TD lớn nhất kể từ khi tái thiết, được gọi là "Đại Sóng TD Bùng Play", buộc người dân phải trả một cái giá đắt. Cuối cùng, Jinhsi đã đánh thức Sentinel để cứu vớt KU-Roro B khỏi thảm họa.
-Ngày nay, Huanglong đang dần hồi phục sau những tổn thương, và KU-Roro B đã trở thành biểu tượng của hy vọng đối với tất cả người dân nơi đây.</t>
+AL157 Huanglong hứng chịu cuộc tấn công TD lớn nhất kể từ khi tái thiết, được gọi là "Đại Sóng TD Bùng Phát", buộc người dân phải trả một cái giá đắt. Cuối cùng, Jinhsi đã đánh thức Sentinel để cứu vớt Jinzhou khỏi thảm họa.
+Ngày nay, Huanglong đang dần hồi phục sau những tổn thương, và Jinzhou đã trở thành biểu tượng của hy vọng đối với tất cả người dân nơi đây.</t>
         </is>
       </c>
     </row>
@@ -4507,11 +4507,11 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Phiếu Exchange Loong Bun, giải thưởng lưu niệm của Carnival Ẩm Thực KU-Roro B.
-Mang phiếu này đến Home Hàng Phan Hoa có thể đổi 5 chiếc Loong Bun miễn phí, trong khi còn hàng.
+          <t>Phiếu Đổi Bánh Lồng Đèn, giải thưởng lưu niệm của Lễ Hội Ẩm Thực Jinzhou.
+Mang phiếu này đến Nhà Hàng Phan Hoa có thể đổi 5 chiếc Bánh Lồng Đèn miễn phí, trong khi còn hàng.
 Thời hạn sử dụng: 10/10/AL159 ~ 10/11/AL159
 Lưu ý: Giải thưởng này không được giảm giá hay hoàn trả, vui lòng giữ cẩn thận và sẽ không được đổi lại nếu làm mất.
-Uncle thích ẩn danh:
+Chú thích ẩn danh:
 Xong rồi! Hết hạn. t_t</t>
         </is>
       </c>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Sentinel của chúng ta gần đây không phản hồi gì cả. Không biết có phải do mình chọc giận nó khi dụ nó bằng Sellh Dragon hôm qua không? Lần sau, mình sẽ mang bánh từ tiệm Panhua đến trước khi lên Núi Firmament. Nhưng mà, Sentinel có ăn bánh được không nhỉ? Chà, chỉ có cách thử mới biết được thôi.</t>
+          <t>Sentinel của chúng ta gần đây không phản hồi gì cả. Không biết có phải do mình chọc giận nó khi dụ nó bằng Bánh Rồng hôm qua không? Lần sau, mình sẽ mang bánh từ tiệm Panhua đến trước khi lên Núi Firmament. Nhưng mà, Sentinel có ăn bánh được không nhỉ? Chà, chỉ có cách thử mới biết được thôi.</t>
         </is>
       </c>
     </row>
@@ -4723,13 +4723,13 @@
           <t>Ngày: AL159
 Mức độ bảo mật: cấp S
 Biên niên vụ án:
-Năm AL159, cựu thủ lĩnh Mornguard Syuwan bị ám sát tại ngoại ô Sảnh Điều Hành Nexus Synergy và tử vong sau khi hồi sức.
-Qua điều tra, hiện trường có dấu hiệu giao tranh rõ ràng, nhiều người chứng kiến lửa cháy cùng tiếng nổ đêm đó, và dựa trên phân tích dữ liệu còn sót lại, nghi phạm là một Synergy Giả sở hữu Lực Forte.
+Năm AL159, cựu thủ lĩnh Mornguard Syuwan bị ám sát tại ngoại ô Sảnh Điều Hành Nexus Cộng Hưởng và tử vong sau khi hồi sức.
+Qua điều tra, hiện trường có dấu hiệu giao tranh rõ ràng, nhiều người chứng kiến lửa cháy cùng tiếng nổ đêm đó, và dựa trên phân tích dữ liệu còn sót lại, nghi phạm là một Resonator sở hữu Lực Forte.
 Đội tuần tra Mornguard đến hiện trường thì nghi phạm đã biến mất, phong tỏa các lối vào thành phố không phát hiện người khả nghi, nghi phạm được cho là có phương thức di chuyển bất thường.
 Một mảnh vỡ màu đỏ được tìm thấy trong tay thủ lĩnh Seokan, nghi là đầu mối, nhưng do kích thước quá nhỏ nên chưa thể xác định mục tiêu.
 Vì đây là vụ việc nghiêm trọng, đề xuất tạm thời giữ kín chi tiết vụ án và tiến hành điều tra bí mật.
 Ý kiến phê duyệt của Jinhsi:
-Agreed. Thủ lĩnh Syoguan rất được tin tưởng, vụ việc này có thể gây chấn động lòng người và hoảng loạn, vì vậy cần làm tốt công tác trấn an dư luận.</t>
+Đồng ý. Thủ lĩnh Syoguan rất được tin tưởng, vụ việc này có thể gây chấn động lòng người và hoảng loạn, vì vậy cần làm tốt công tác trấn an dư luận.</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>Bức tranh dài tới 400 cm, rộng 30 cm, nhiều chỗ bị hư hại, khó xác định nội dung.
-Left có ba vết sửa chữa, phần đã phục chế tái hiện khung cảnh chợ đông đúc, yên bình, Cổng Ting Ruosi, giao thông tấp nập, nhắm mắt lại như thể đang đứng giữa đó, tiếng ồn ào náo nhiệt của đám đông vẫn văng vẳng bên tai.</t>
+Bên trái có ba vết sửa chữa, phần đã phục chế tái hiện khung cảnh chợ đông đúc, yên bình, Cổng Ting Ruosi, giao thông tấp nập, nhắm mắt lại như thể đang đứng giữa đó, tiếng ồn ào náo nhiệt của đám đông vẫn văng vẳng bên tai.</t>
         </is>
       </c>
     </row>
@@ -4870,14 +4870,14 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>Ngày phục chế: AL158
-Người phục chế: Malee mã Ma Liang
+Người phục chế: Tên mã Ma Liang
 Biên bản phục chế:
 Bộ tranh này khai quật từ tàn tích cổ khá nguyên vẹn, chỉ bị hư hại 47 điểm.
 Bức tranh cuộn này khá thú vị, ghi lại đời sống của một vùng qua một cuộn ngang, và có những điều chưa từng nghe thấy. Nếu phục chế xong, chắc chắn sẽ hé lộ được phần nào di tích thời kỳ trước Lament.
 Phản hồi ẩn danh:
-Dish ở quầy thứ ba bên trái trông ngon quá, phải nhờ cô Phan Hua thử làm mới được.
+Món ăn ở quầy thứ ba bên trái trông ngon quá, phải nhờ cô Phan Hua thử làm mới được.
 À, còn món đồ trang trí ở cổng quầy thứ sáu, cái đó là... đồ chơi à?
-Người dân vùng này thật thú vị! Mong là bức tranh này sẽ được trưng bày ở KU-Roro B vào lễ hội tới!</t>
+Người dân vùng này thật thú vị! Mong là bức tranh này sẽ được trưng bày ở Jinzhou vào lễ hội tới!</t>
         </is>
       </c>
     </row>
@@ -4944,9 +4944,9 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Một bức tranh cuộn dài nằm ngang, với những Dodget mực mờ ảo chảy tràn.
+          <t>Một bức tranh cuộn dài nằm ngang, với những nét mực mờ ảo chảy tràn.
 Nhờ những bức ảnh chụp các bức họa cũ của Lament do ông Trần Phi cung cấp, quá trình phục chế tác phẩm này diễn ra suôn sẻ và hiệu quả.
-Lãnh Unclea Dragon đã đặt tên cho tác phẩm là "Văn Dạ", và dự định sẽ trưng bày khắp thành phố vào năm AL160.</t>
+Lãnh Chúa Rồng đã đặt tên cho tác phẩm là "Văn Dạ", và dự định sẽ trưng bày khắp thành phố vào năm AL160.</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5017,7 @@
           <t>Những bức ảnh đã phai màu. Mặt trời lặn bị nuốt chửng sau dãy núi, lũ chim bay vòng vòng, con người chạy trốn tán loạn, thế giới chìm trong hỗn loạn.
 Có lẽ chụp vào thời điểm Lament, bức ảnh này là biểu tượng cho thảm họa của nhân loại đương thời.
 Dưới dòng chảy lịch sử, chúng ta phải cảnh giác trong hòa bình và không quên ngọn lửa phản kháng.
-Lãnh Unclea Dragon đã đặt tên cho nó là "Cuộc Chiến Câm Lặng", và dự định sẽ trưng bày khắp thành phố vào năm AL160.</t>
+Lãnh Chúa Rồng đã đặt tên cho nó là "Cuộc Chiến Câm Lặng", và dự định sẽ trưng bày khắp thành phố vào năm AL160.</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>Vật phẩm: YL-001
-Tên: "Tình Bổ Sung Tử"
+Tên: "Tình Phụ Tử"
 Mô tả: YL-001 là một cảnh đặc biệt được tạo thành từ nhiều con rối, trong đó các thành phần chính gồm một con rối tượng trưng cho "người cha", một con rối tượng trưng cho "con gái", và một nhóm con rối tượng trưng cho "con mồi" của họ.
 Có thể thấy cảnh này miêu tả "con gái" giành chiến thắng trước những "con mồi" xung quanh dưới sự chỉ dẫn của "người cha". Đây là một cảnh đơn giản thể hiện sự hỗ trợ và kế thừa lẫn nhau giữa cha và con, cũng như ảnh hưởng to lớn của người cha đối với con gái.
 Tuy nhiên, điều kỳ lạ là với tư cách kẻ chiến thắng duy nhất còn đứng vững, "người cha" lại có dáng vẻ thẳng đứng hơn hẳn so với "con gái", khác hẳn với hình ảnh người cha như một người bảo vệ thông thường. Có vẻ như "người cha" trong cảnh này không đơn thuần là cha của "con gái"...
@@ -5381,8 +5381,8 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>Vật phẩm: YL-003-c
-Tên: "Sự Khác Biệt Trong Con Sugar"
-Mô tả: YL-003-c là một cảnh đặc biệt được tạo nên từ những con rối, trong đó nhân vật chính là con rối "bạn thân" trong "Divergence".
+Tên: "Sự Khác Biệt Trong Con Đường"
+Mô tả: YL-003-c là một cảnh đặc biệt được tạo nên từ những con rối, trong đó nhân vật chính là con rối "bạn thân" trong "Sự Phân Kỳ".
 Qua quan sát, có thể thấy dù con rối "bạn thân" có tư thế quay đầu lại, nhưng nó không bao giờ thực sự quay đầu được. Điều cố định ở đây là khoảnh khắc ích kỷ nhất thời của cô ấy, hay chỉ là giấc mơ hão huyền đã bị thời gian xóa bỏ?
 Cái gọi là "bạn thân" có lẽ đã mãi mãi rời xa, ngày càng xa hơn.</t>
         </is>
@@ -5459,7 +5459,7 @@
 Kết quả phân tích được đối chiếu dựa trên mẫu Chromeshell thu thập tại hiện trường làm tài liệu tham chiếu chính:
 ① Chất lượng nước tại hiện trường nằm trong ngưỡng pH và nồng độ clorua bình thường
 ① Chất lượng nước tại hiện trường nằm trong ngưỡng pH và nồng độ clorua bình thường ② Nguồn nước có hàm lượng chất không tan cao, nghi ngờ vấn đề ô nhiễm tiềm ẩn
-(iii) Hàm lượng chất cao trong Sóng Vút do các Creatures Đột Biến thủy sinh hoạt động mạnh trong khu vực.
+(iii) Hàm lượng chất cao trong Sóng Vút do các Sinh Vật Đột Biến thủy sinh hoạt động mạnh trong khu vực.
 ④ ......
 Tổng kết từ các kết quả trên, có thể kết luận dữ liệu tại hiện trường vượt quá tiêu chuẩn môi trường sống và không phù hợp để xây dựng địa điểm mới.</t>
         </is>
@@ -5607,9 +5607,9 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>Đã hoàn tất phát hiện và phân tích mẫu sinh học.
-Kết quả phân tích được đối chiếu với Templates Bird Egg thu thập tại hiện trường:
+Kết quả phân tích được đối chiếu với Mẫu Trứng Chim thu thập tại hiện trường:
 ① Các sinh vật tại đây hoạt động cực kỳ mạnh mẽ và có khả năng mang ý đồ tấn công con người.
-② Hàm lượng chất Wuthering Waves trong cơ thể chúng vượt xa mức bình thường, nghi ngờ có Tacet Field hoạt động mạnh hơn trong khu vực.
+② Hàm lượng chất Wuthering Waves trong cơ thể chúng vượt xa mức bình thường, nghi ngờ có Tổ Tacet hoạt động mạnh hơn trong khu vực.
 ③ ...
 Tổng kết lại, dữ liệu từ hiện trường vượt quá tiêu chuẩn môi trường sống, không phù hợp để làm địa điểm tái định cư.</t>
         </is>
@@ -5681,7 +5681,7 @@
         <is>
           <t>Phóng viên: Phỏng vấn nào, cậu có biết tại sao chỗ này gọi là Miệng Cọp không?
 Bác thợ mỏ: Kiếm sống thôi! Chỗ này mà nuôi nổi gia đình à!
-Đứa trẻ: Vì có cái hố to như miệng cọp ấy! Ouye--
+Đứa trẻ: Vì có cái hố to như miệng cọp ấy! Ui da--
 Dân đi đường: Cọp cọp gì chứ! À, cái này gọi là múa lân à? Chẳng khác gì nhau cả. ...... (Tiếng cười xung quanh)</t>
         </is>
       </c>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Mọi người nghe đây. Cuộc Examine Định Kỳ hàng năm cho các xe tải vận chuyển mỏ sắp bắt đầu. Khi đi kiểm tra, hãy mang theo giấy phép lái xe. Giấy phép phải còn hiệu lực.
+          <t>Mọi người nghe đây. Cuộc Kiểm Tra Định Kỳ hàng năm cho các xe tải vận chuyển mỏ sắp bắt đầu. Khi đi kiểm tra, hãy mang theo giấy phép lái xe. Giấy phép phải còn hiệu lực.
 Bất kỳ ai có giấy phép hết hạn sẽ bị coi là nhân viên không có chứng chỉ. Các bạn sẽ bị từ chối quyền điều khiển phương tiện, dù có kinh nghiệm lái xe đến đâu.
 Cuộc kiểm tra sẽ diễn ra từ cuối tháng này đến giữa tháng sau. Mang theo giấy tờ tùy thân và nộp đơn đăng ký tại Bộ Phát Triển. Thời gian thi sẽ được công bố vào dịp khác.
 Hãy đọc kỹ các tài liệu đính kèm trước khi đi và chuẩn bị sẵn sàng. Các bạn sẽ phải cảm ơn tôi đấy.
-Tài liệu đính kèm: 1) &lt;i&gt;Thông tin chi tiết về Examine Định Kỳ Xe Tải Vận Switch tại Mỏ&lt;/i&gt;
-2) &lt;i&gt;Tiêu Chuẩn Basic Review Skills Lái Xe&lt;/i&gt;</t>
+Tài liệu đính kèm: 1) &lt;i&gt;Thông tin chi tiết về Kiểm Tra Định Kỳ Xe Tải Vận Chuyển tại Mỏ&lt;/i&gt;
+2) &lt;i&gt;Tiêu Chuẩn Cơ Bản Đánh Giá Kỹ Năng Lái Xe&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Một số điều khoản bổ sung đã được thêm vào Regulation An Toàn Mỏ Hổ Hàm:
+          <t>Một số điều khoản bổ sung đã được thêm vào Quy Định An Toàn Mỏ Hổ Hàm:
 43. Không tin vào tin đồn về những giọng nói; anh không nên và sẽ không nghe thấy bất kỳ âm thanh kỳ lạ nào trong mỏ. Đặc biệt là tiếng gọi của người thân. (Những người thân đã khuất khó lòng nói chuyện với anh)
 44. Không được lại gần sương mù bất cứ lúc nào. Dù có ai gọi trong sương.
 45. Nếu nghe thấy âm thanh kỳ lạ, hãy phớt lờ, lập tức dừng mọi công việc và đến phòng y tế để được điều trị tâm lý và thể chất.</t>
@@ -6032,12 +6032,8 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Chisu đã giao balo cho mình
-, và mình
- biết cậu ấy chuẩn bị cho một cuộc giải cứu đầy rủi ro. mình
- sợ đến mức tim đập thình thịch, sợ rằng cậu ấy có thể không trở về, và còn sợ hơn nữa là cậu ấy sẽ trở về... nhưng không còn là chính mình nữa. Weapons Tacetite không bao giờ được dùng để chống lại đồng đội.
-Đặc biệt là thứ cậu ấy để lại cho mình
-.</t>
+          <t>Chisu đã giao balo cho tao, và tao biết cậu ấy chuẩn bị cho một cuộc giải cứu đầy rủi ro. Tao sợ đến mức tim đập thình thịch, sợ rằng cậu ấy có thể không trở về, và còn sợ hơn nữa là cậu ấy sẽ trở về... nhưng không còn là chính mình nữa. Vũ khí Tacetite không bao giờ được dùng để chống lại đồng đội.
+Đặc biệt là thứ cậu ấy để lại cho tao.</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6102,7 @@
         <is>
           <t>Hmm... Giọng đó... giống Chisu thật. Cậu ấy nói rất bình tĩnh, y như lúc nào cũng an ủi ta, "Không sao đâu"... 
 Tâm trạng ta bất ngờ lắng dịu theo giọng nói ấy, nhưng đôi tay lại run rẩy không ngừng.
-Clock đo decibel vẫn không hề nhúc nhích. Ta biết đó không phải cậu ấy. Chỉ là trò lừa bịp rẻ tiền của TD thôi.</t>
+Đồng hồ đo decibel vẫn không hề nhúc nhích. Ta biết đó không phải cậu ấy. Chỉ là trò lừa bịp rẻ tiền của TD thôi.</t>
         </is>
       </c>
     </row>
@@ -6174,8 +6170,8 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>Mẹ của Jack hỏi cậu muốn làm nghề gì. Jack bảo cậu muốn làm thợ mỏ.
-Mẹ không hiểu vì Jack đâu phải đứa chịu khó. Jack nói: “Do thợ mỏ thì con có thể lấy mọi thứ là ‘của con’ ấy ạ.”
-Uncle thích cỡ chữ nhỏ: Hay đấy. Nhưng cẩn thận mấy con “hisser” dưới lòng đất nhé.</t>
+Mẹ không hiểu vì Jack đâu phải đứa chịu khó. Jack nói: “Làm thợ mỏ thì con có thể lấy mọi thứ là ‘của con’ ấy ạ.”
+Chú thích cỡ chữ nhỏ: Hay đấy. Nhưng cẩn thận mấy con “hisser” dưới lòng đất nhé.</t>
         </is>
       </c>
     </row>
@@ -6260,11 +6256,11 @@
 Jing: Tớ cũng không biết. Để tớ kiểm tra bằng Forte thích ứng bảo vệ ban đêm của mình.
 Jing: Chắc chắn có gì đó không ổn...
 Tan: Sao thế?
-Jing: None ai trong thang máy. Tớ kiểm tra các sàn ở các tầng rồi. Không ai đứng đợi cả... Tớ phải tự mình đi xem.
-Tan: Eee ê. Đừng có mà lao vào trước. Nếu đây là phim, thứ đang đợi cậu ngoài kia chắc chắn không phải thứ cậu nghĩ đâu.
-Jing: Không phải đâu. Giờ tớ làm việc này, tớ còn phải lo nhiều hơn cả mạng sống của mình. Mà cậu cũng nên tỉnh táo đi. Không phải cậu tự hào là thế hệ mới của KU-Roro B sao? Sao lại tin vào những thứ này hơn mấy ông già vậy?
+Jing: Không có ai trong thang máy. Tớ kiểm tra các sàn ở các tầng rồi. Không ai đứng đợi cả... Tớ phải tự mình đi xem.
+Tan: Ê ê ê. Đừng có mà lao vào trước. Nếu đây là phim, thứ đang đợi cậu ngoài kia chắc chắn không phải thứ cậu nghĩ đâu.
+Jing: Không phải đâu. Giờ tớ làm việc này, tớ còn phải lo nhiều hơn cả mạng sống của mình. Mà cậu cũng nên tỉnh táo đi. Không phải cậu tự hào là thế hệ mới của Jinzhou sao? Sao lại tin vào những thứ này hơn mấy ông già vậy?
 Jing: Hay là máy móc trục trặc, hoặc mấy đồng nghiệp nghịch ngợm? Công việc ở đây chán quá, biết đâu họ muốn "chơi khăm" tớ một chút?
-Tan: Sentinel phù hộ cho cậu. Unclec may mắn nhé.</t>
+Tan: Sentinel phù hộ cho cậu. Chúc may mắn nhé.</t>
         </is>
       </c>
     </row>
@@ -6336,14 +6332,13 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Malee trang bị: Cáp treo chở người và hàng hóa
-Số hiệu: HLHk-09
-Đơn vị sử dụng: Phòng Vận tải Mỏ Hổ Hàm
-Điều kiện hỏng hóc: Mức độ mài mòn dây cáp và số sợi đứt tăng bất thường, khiến khung cabin nối mềm, cabin không thể hoạt động bình thường.
-Bảo trì: Đã thay dây cáp mới.
-Phân tích nguyên nhân: Đã kiểm tra bánh kéo, trục bánh dẫn hướng, bộ giới hạn tốc độ và các bộ phận liên quan khác, nhưng không xác định được nguyên nhân bất thường. Nghi ngờ do thao tác sai của con người.
-Được đề xuất: Để tôi bắt thằng nào dám chất hàng bừa bãi gây quá tải, tôi sẽ treo nó lên cáp luôn, cho nó nếm trải cảm giác cabin quá tải là thế nào!
-Người bảo trì: Lão Thành</t>
+          <t>Tên trang bị: HLHk-09
+Used by: Tiger's Maw Mine Transportation Department
+Failure conditions: Abnormal increase in the amount of wear and tear of the wire rope and the number of broken wires, resulting in a soft connection between the gondola frame, the gondola can not operate normally.
+Maintenance: The wire rope has been replaced.
+Cause analysis: Have checked the traction sheave, guide sheave shaft, speed limiter and other related parts, did not lock the cause of the abnormality, suspected to be caused by improper human operation.
+Suggestions: Let me catch which bastard dares to load indiscriminately resulting in overloading, I'll hang him on the cable, so that he can experience the overloaded cable car is what feeling!
+Maintainer: Lao Cheng</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6483,7 @@
 1, Nó sẽ không được bán trên thị trường đại chúng đâu.
 2, Nó không chịu được vận chuyển mạnh.
 3, Nó không thể bảo quản lâu dài.
-4, Guan trọng nhất, đừng có ngốc mà mở bừa một hộp NaruLiquid như đồ ăn, nó có thể giết chết cậu đấy!</t>
+4, Quan trọng nhất, đừng có ngốc mà mở bừa một hộp NaruLiquid như đồ ăn, nó có thể giết chết cậu đấy!</t>
         </is>
       </c>
     </row>
@@ -6558,11 +6553,11 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Bức Xạ Tacet Field
-Tác Động Bức Xạ Tacet Field
-Bệnh Do Phơi Nhiễm Lâu Dài Tacet Field
-Bệnh Tacet Field: Suy Decrease Nhận Thức
-Phương Pháp Chữa Bệnh Tacet Field
+          <t>Bức Xạ Tổ Tacet
+Tác Động Bức Xạ Tổ Tacet
+Bệnh Do Phơi Nhiễm Lâu Dài Tổ Tacet
+Bệnh Tổ Tacet: Suy Giảm Nhận Thức
+Phương Pháp Chữa Bệnh Tổ Tacet
 ......</t>
         </is>
       </c>
@@ -6633,10 +6628,10 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>Ai nói âm nhạc phải do nhạc cụ tạo ra chứ?
-Hồi còn làm việc trong mỏ, ta luôn nghe thấy những âm thanh kỳ lạ. Lúc đầu, ta tưởng đó là "âm thanh" huyền bí mà mọi người đồn đại… Nhưng sau này, ta phát hiện ra rằng những âm thanh kỳ lạ ấy thực ra phát ra từ chính các khoáng vật, và điều đáng kinh ngạc hơn là chúng tạo thành một giai điệu độc đáo!
+Hồi còn làm việc trong mỏ, tao luôn nghe thấy những âm thanh kỳ lạ. Lúc đầu, tao tưởng đó là "âm thanh" huyền bí mà mọi người đồn đại… Nhưng sau này, tao phát hiện ra rằng những âm thanh kỳ lạ ấy thực ra phát ra từ chính các khoáng vật, và điều đáng kinh ngạc hơn là chúng tạo thành một giai điệu độc đáo!
 Hình dáng và chất lượng của Tacetite khi được cắt gọt sẽ quyết định giai điệu ấy ra sao.
-Ta đã sắp xếp lại những bản ghi âm suốt bao năm và biên soạn thành một bản nhạc, giờ được gọi là "Song Đá".
-Dạo này ta không còn khỏe như trước… Nhưng may mắn thay, Đài Play thanh Pioneer Association đã nhận được bản gốc của "Song Đá". Wishing của ta đã thành hiện thực!</t>
+Tao đã sắp xếp lại những bản ghi âm suốt bao năm và biên soạn thành một bản nhạc, giờ được gọi là "Khúc Ca Đá".
+Dạo này tao không còn khỏe như trước… Nhưng may mắn thay, Đài Phát thanh Hiệp hội Pioneer đã nhận được bản gốc của "Khúc Ca Đá". Ước nguyện của tao đã thành hiện thực!</t>
         </is>
       </c>
     </row>
@@ -6706,10 +6701,10 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>Truy Nã! Truy Nã!
-Discord hùng mạnh đang lao qua cánh đồng lửa cháy rực của Biển Lửa…
+Tacet Discord hùng mạnh đang lao qua cánh đồng lửa cháy rực của Biển Lửa…
 Thách đấu, đánh bại, tiêu diệt nó!
-Nhận Rewards hậu hĩnh 100.000 SHC!
-Trung tâm Nghiên cứu Qi hậu Wutherology, Huaxu Academy</t>
+Nhận thưởng hậu hĩnh 100.000 SHC!
+Trung tâm Nghiên cứu Khí hậu Wutherology, Học viện Huaxu</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6901,7 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>Gần đây, mỏ ngày càng lạnh hơn, và những người thợ mỏ làm việc dưới đáy vẫn thỉnh thoảng nghe thấy những âm thanh kỳ lạ. Những lời đồn đại như vậy giờ đã trở thành câu chuyện đêm của dân mỏ, nhưng tốt hơn hết là nên xuống đáy điều tra.
-Bận rộn cả ngày, rồi ăn một bát cháo KU-Roro B, vị... thôi đừng nhắc nữa, lạ thay dưới đáy bát lại dính một mảnh giấy, trên đó vẽ nguệch ngoạc một họa tiết đá, không cần nghĩ cũng biết thằng nhóc ngồi đối diện bàn ăn viết, học theo chuyện "Bầu ơi thương lấy bí cùng" mà vẽ đại cho tiện giao tiếp ngôn ngữ riêng. Không ngờ cả bác sĩ Hua điềm tĩnh cũng bị cuốn vào, nhưng vui thật khi được ăn uống ồn ào thế này với ba người.</t>
+Bận rộn cả ngày, rồi ăn một bát cháo Jinzhou, vị... thôi đừng nhắc nữa, lạ thay dưới đáy bát lại dính một mảnh giấy, trên đó vẽ nguệch ngoạc một họa tiết đá, không cần nghĩ cũng biết thằng nhóc ngồi đối diện bàn ăn viết, học theo chuyện "Bầu ơi thương lấy bí cùng" mà vẽ đại cho tiện giao tiếp ngôn ngữ riêng. Không ngờ cả bác sĩ Hua điềm tĩnh cũng bị cuốn vào, nhưng vui thật khi được ăn uống ồn ào thế này với ba người.</t>
         </is>
       </c>
     </row>
@@ -7132,8 +7127,8 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>1 Giỏ Hạt-1
-Bộ Phận Không Read Được-12
-Sách Không Read Được-5
+Bộ Phận Không Đọc Được-12
+Sách Không Đọc Được-5
 …
 Họ bỏ lại cả đống đồ! Sắp trúng số đây này!</t>
         </is>
@@ -7211,15 +7206,15 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>[Gợi Ý The Present]
+          <t>[Gợi Ý Hiện Tại]
 "Cờ phấp phới tự hào, chiến binh xung trận dũng mãnh; ngọn giáo cô đơn xuyên thủng ánh trăng tàn."
 Hãy sống lại những giấc mơ xưa và du hành qua không gian, thời gian. Vở kịch nhập vai &lt;i&gt;Ánh Trăng Vẫn Sáng&lt;/i&gt; sắp ra mắt.
 "Ngọn lửa ta phóng ra sẽ thiêu rụi mọi dấu vết của cái ác, chỉ để lại tro tàn."
-Re xuất kinh điển: Vở kịch anh hùng &lt;i&gt;Fiamma&lt;/i&gt;
-[Quy Tắc Khán Giả Tại Home Hát]
-1. Nhà hát KU-Roro B là không gian biểu diễn ngoài trời. Vui lòng giữ trật tự nơi công cộng.
+Tái xuất kinh điển: Vở kịch anh hùng &lt;i&gt;Fiamma&lt;/i&gt;
+[Quy Tắc Khán Giả Tại Nhà Hát]
+1. Nhà hát Jinzhou là không gian biểu diễn ngoài trời. Vui lòng giữ trật tự nơi công cộng.
 2. Hãy đến nhà hát đúng giờ và ngồi yên tại chỗ trong suốt buổi diễn. Nếu phải rời đi, hãy ra về nhẹ nhàng để không làm phiền khán giả khác.
-3. Trong suốt buổi diễn, hãy tắt Terminal hoặc chuyển sang chế độ rung nếu cần thiết.
+3. Trong suốt buổi diễn, hãy tắt Thiết bị đầu cuối hoặc chuyển sang chế độ rung nếu cần thiết.
 4. Không được chụp ảnh hoặc quay phim trong nhà hát.
 5. Nghiêm cấm xâm nhập sân khấu. Người vi phạm sẽ bị xử lý bởi Đội Tuần Tra.
 6. Sau buổi diễn, vui lòng mang rác của bạn theo.</t>
@@ -7297,11 +7292,11 @@
           <t>"Hoa nở theo mùa, dấu thời gian. Cây cảnh nhỏ, nơi gọi là nhà."
 [Chủ Đề Penjing Hôm Nay: Trăng]
 Đề Bài 1: Tạo một cây cảnh với chủ đề "Biển Đom Đóm và Vầng Trăng";
-—Người Đăng: Chenyue, Tiền Mailởng: 1000 SHC
-Đề Bài 2: Tạo một cây cảnh với chủ đề "Thiên Sugar Đào Nguyên và Vầng Trăng";
-—Người Đăng: Wanqiu, Tiền Mailởng: 5000 SHC
-Đề Bài 3: Tạo một cây cảnh với chủ đề "Dragon Không Vuốt".
-—Người Đăng: Moonless, Tiền Mailởng: 9999 SHC</t>
+—Người Đăng: Chenyue, Tiền Thưởng: 1000 SHC
+Đề Bài 2: Tạo một cây cảnh với chủ đề "Thiên Đường Đào Nguyên và Vầng Trăng";
+—Người Đăng: Wanqiu, Tiền Thưởng: 5000 SHC
+Đề Bài 3: Tạo một cây cảnh với chủ đề "Rồng Không Vuốt".
+—Người Đăng: Moonless, Tiền Thưởng: 9999 SHC</t>
         </is>
       </c>
     </row>
@@ -7440,8 +7435,8 @@
       <c r="M93" t="inlineStr">
         <is>
           <t>Ngày: 31 tháng 12, AL 159
-Report Giver: Huaijin
-Phối hợp với Huaxu Academy, Bộ Play triển đã ban hành ấn bản mới nhất của &lt;i&gt;Cẩm nang Shipping An toàn Năng lượng&lt;/i&gt;.
+Người báo cáo: Huaijin
+Phối hợp với Học viện Huaxu, Bộ Phát triển đã ban hành ấn bản mới nhất của &lt;i&gt;Cẩm nang Vận chuyển An toàn Năng lượng&lt;/i&gt;.
 Nhận thức được tầm quan trọng của việc nắm vững toàn diện, tổ trưởng giao tôi nghiên cứu sơ bộ, nhấn mạnh việc đào tạo sau này cho các thợ mỏ đồng nghiệp. Ngoài ra, tôi đang biên soạn các phân tích trường hợp tai nạn để củng cố ý thức an toàn chung.
 Để giúp đồng nghiệp dễ hiểu hơn, tôi tự nguyện tóm lược và làm nổi bật các điểm chính cho cả đội.</t>
         </is>
@@ -7515,7 +7510,7 @@
           <t>Dù bóng đêm có nhấn chìm dấu vết, chỉ cần ta luôn giữ vững lòng dũng cảm khám phá những điều chưa biết, rồi ta sẽ đến được nơi xa xôi ấy.
  --Gửi những chiến binh của đêm trường.
  Bối cảnh
-Garden Zhuông được thành lập vào năm AL155 để tưởng nhớ những chiến binh đã hy sinh vì nền văn minh nhân loại. Mỗi đóa hoa trong vườn đều được Jiyan, thủ lĩnh thứ năm của Midnight Rangers, gieo trồng và chăm sóc. Hạt giống hoa được Verina, nhà nghiên cứu thực vật, lai tạo đặc biệt phù hợp với địa chất và khí hậu Huanglong, đảm bảo tỷ lệ sống sót 100% ngay cả trong điều kiện thời tiết khắc nghiệt, tượng trưng cho tinh thần bất khuất của Huanglong.
+Vườn Chuông được thành lập vào năm AL155 để tưởng nhớ những chiến binh đã hy sinh vì nền văn minh nhân loại. Mỗi đóa hoa trong vườn đều được Jiyan, thủ lĩnh thứ năm của Midnight Rangers, gieo trồng và chăm sóc. Hạt giống hoa được Verina, nhà nghiên cứu thực vật, lai tạo đặc biệt phù hợp với địa chất và khí hậu Huanglong, đảm bảo tỷ lệ sống sót 100% ngay cả trong điều kiện thời tiết khắc nghiệt, tượng trưng cho tinh thần bất khuất của Huanglong.
 Công chúng được yêu cầu tôn trọng người đã khuất, không giẫm đạp lên hoa khi đến viếng, kẻ vi phạm sẽ bị chuyển giao cho Mornguard xử lý.</t>
         </is>
       </c>
@@ -7585,7 +7580,7 @@
         <is>
           <t>KANG: Xin hãy tôn trọng người đã khuất, đừng giẫm đạp lên họ!
 KANG: Cảnh cáo lần cuối, không được! Giẫm đạp! Dẫm lên!
-Kangen: lại tái phạm rồi...... Thật sự là quá quắt! Tôi đã báo cho Mornguard rồi.</t>
+Kangen: lại tái phạm rồi...... Thật là quá quắt! Tôi đã báo cho Mornguard rồi.</t>
         </is>
       </c>
     </row>
@@ -7745,13 +7740,14 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>&lt;Petal Rating: Five Stars&gt;
+          <t xml:space="preserve">&lt;Petal Rating: Five Stars&gt;
 Tôi đã khóc hết nước mắt!
-&lt;i&gt;Moonlight Shines as Ever&lt;/i&gt; quả là một vở kịch xé lòng! Thật sự tuyệt vời cho biên kịch tài ba đã tạo nên một câu chuyện đau lòng đến thế. Nước mắt tôi cứ tuôn rơi không ngừng ngay cả sau khi vở kịch kết thúc!
-Phản hồi từ nhà hát: Vở kịch Anh Hùng này dựa trên những sự kiện lịch sử có thật. Cảm ơn bạn đã chia sẻ cảm nhận của mình.
+&lt;i&gt;Ánh Trăng Vẫn Sáng&lt;/i&gt; đúng là một vở kịch xé lòng! Thật sự ngả mũ trước biên kịch tài ba đã tạo nên câu chuyện đầy cảm xúc đến thế. Nước mắt tôi cứ tuôn mãi ngay cả khi vở kịch đã kết thúc!
+Phản hồi từ Nhà hát: Vở Anh Hùng Kịch này dựa trên sự kiện lịch sử có thật. Cảm ơn bạn đã chia sẻ trải nghiệm của mình.
 &lt;Petal Rating: Four Stars&gt;
-&lt;i&gt;Fiamma&lt;/i&gt; thực sự đã kích thích vị giác của tôi! Lần tới tôi dự định mang theo chút Victor Savor tự làm của dì để thưởng thức trong lúc xem. Háo hức quá!
-Phản hồi từ nhà hát: Cảm ơn bình luận của bạn. Bạn có thể mang theo đồ ăn nhẹ của riêng mình, nhưng xin hãy lưu ý đến mùi hương nồng.</t>
+&lt;i&gt;Fiamma&lt;/i&gt; khiến tôi thèm thuồng quá! Lần sau chắc chắn phải mang theo món Victor Savor tự làm của dì đến thưởng thức trong lúc xem. Háo hức quá đi!
+Phản hồi từ Nhà hát: Cảm ơn nhận xét của bạn. Bạn có thể mang đồ ăn nhẹ của riêng mình, nhưng xin lưu ý tránh những mùi quá nồng.
+</t>
         </is>
       </c>
     </row>
@@ -7822,10 +7818,10 @@
       <c r="M98" t="inlineStr">
         <is>
           <t>Sau khi vở kịch &lt;i&gt;Fiamma&lt;/i&gt; kết thúc lúc 9 giờ tối hai đêm trước, một số khán giả đã tìm thấy đồ thất lạc trong rạp và nhanh chóng báo cáo. Danh sách đồ vật như sau:
-Khuyên tai xanh: Hàng 5, Chair 9, số lượng: 1
-Thẻ làm việc Bộ Play triển: Hàng 6, Chair 9, số lượng: 1
-Phiếu đổi bánh Loong (có hoa văn rồng đặc biệt): Hàng 8, Chair 10, số lượng: 2
-Băng đô thủ công (đỏ và xanh, tết một phần): Hàng 16, Chair 11, số lượng: 1
+Khuyên tai xanh: Hàng 5, Ghế 9, số lượng: 1
+Thẻ làm việc Bộ Phát triển: Hàng 6, Ghế 9, số lượng: 1
+Phiếu đổi bánh Loong (có hoa văn rồng đặc biệt): Hàng 8, Ghế 10, số lượng: 2
+Băng đô thủ công (đỏ và xanh, tết một phần): Hàng 16, Ghế 11, số lượng: 1
 Chủ nhân của các món đồ trên vui lòng đến nhận trong vòng 10 ngày kể từ ngày thông báo này.</t>
         </is>
       </c>
@@ -7907,11 +7903,11 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Position:
+          <t>Vị trí:
 [Nhân Viên Giao Hàng Tận Nơi]
 Yêu cầu:
 Tuổi: Không giới hạn; ứng viên ở mọi độ tuổi đều được khuyến khích ứng tuyển.
-Bằng lái: Có bằng lái xe hợp lệ từ bất kỳ quốc gia nào.
+Bằng lái: Phải có bằng lái xe hợp lệ từ bất kỳ quốc gia nào.
 Trách nhiệm: Ứng viên lý tưởng sẽ tuân thủ tiêu chuẩn công ty, đảm bảo hoàn thành công việc thu gom và giao hàng hàng ngày một cách an toàn, hiệu quả và chính xác.
 Địa điểm làm việc:
 Ứng viên sẽ được phân công đến điểm phân phối gần nhất dựa trên nguyện vọng và tình trạng tuyển dụng hiện tại tại các điểm.
@@ -7996,15 +7992,14 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Lịch diễn thuyết Tuần lễ Giao lưu Học thuật Huaxu Academy:
-Malee bài giảng: Phân loại Weapons Tacet Field và Ý nghĩa trong Nghiên cứu Năng lượng – Nghiên cứu Trường hợp Weapons Huanglong
-Địa điểm: Lecture Hall Số 1
-Plays giả: Mortefi
-Tiểu sử diễn giả: Zhuyên gia về Weapons Tacet Field, chuyên viên đánh giá thuộc Department An toàn, và nhà nghiên cứu xuất sắc tại Huaxu Academy.
-Malee bài giảng: Logic Thuật toán Phân bổ Tuyến đường trong Lollo Logistics
-Địa điểm: Lecture Hall Nhiều tầng
-Plays giả: Rubert
-Tiểu sử diễn giả: Kỹ sư front-end tại Lollo Logistics và giảng viên thỉnh giảng tại Huaxu Academy.</t>
+          <t>Lịch diễn thuyết Tuần lễ Giao lưu Học thuật Học viện Huaxu: Lecture Title: Classification of Tacetite Weapon and Its Significance in Energy Studies—A Case Study of Huanglong Weaponary
+Lecture Venue: First Lecture Hall
+Speaker: Mortefi
+Speaker Bio: Expert in Tacetite Weaponary, assessment specialist in the Department of Safety, and distinguished researcher at the Huaxu Academy.
+Lecture Title: Logic of the Front-End Algorithm for Route Allocation in Lollo Logistics
+Lecture Venue: Tiered Lecture Hall
+Speaker: Rubert
+Speaker Bio: Front-end engineer at Lollo Logistics and guest lecturer at the Huaxu Academy.</t>
         </is>
       </c>
     </row>
@@ -8075,11 +8070,11 @@
       <c r="M101" t="inlineStr">
         <is>
           <t>["Mùa Này Đặc Sắc"]
-Tea Xuân được tuyển chọn kỹ lưỡng, kết hợp cùng "Sương Mai Đỉnh Sen" nổi tiếng với công dụng làm dịu và thư giãn. Invite quý khách vào thưởng thức.
-[Save Ý]
-Những chú mèo và chó đáng yêu bên ngoài quán không chỉ là khách viếng thăm; chúng là thành viên thân yêu của gia đình quán trà Save Hiền. Quý khách được mời âu yếm và đối xử tử tế với chúng. Với những ai nhạy cảm với lông thú, chúng tôi khuyên nên lên sân thượng tầng hai, nơi có thể ngắm nhìn toàn cảnh Tấn Châu tuyệt đẹp và tận hưởng không khí sôi động của thành phố.
+Trà Xuân được tuyển chọn kỹ lưỡng, kết hợp cùng "Sương Mai Đỉnh Sen" nổi tiếng với công dụng làm dịu và thư giãn. Mời quý khách vào thưởng thức.
+[Lưu Ý]
+Những chú mèo và chó đáng yêu bên ngoài quán không chỉ là khách viếng thăm; chúng là thành viên thân yêu của gia đình quán trà Lưu Hiền. Quý khách được mời âu yếm và đối xử tử tế với chúng. Với những ai nhạy cảm với lông thú, chúng tôi khuyên nên lên sân thượng tầng hai, nơi có thể ngắm nhìn toàn cảnh Tấn Châu tuyệt đẹp và tận hưởng không khí sôi động của thành phố.
 [Tuyển Dụng]
-Refreshment Tea và trà kết nối tâm hồn. Quán trà Save Hiền đang tuyển dụng những người đam mê trà để gia nhập đội ngũ, mức lương thương lượng.</t>
+Trà giải khát và trà kết nối tâm hồn. Quán trà Lưu Hiền đang tuyển dụng những người đam mê trà để gia nhập đội ngũ, mức lương thương lượng.</t>
         </is>
       </c>
     </row>
@@ -8147,8 +8142,8 @@
       <c r="M102" t="inlineStr">
         <is>
           <t>Đá phụ trách lô 10200 đến 10299: đã kiểm tra, vận chuyển và lắp ráp xong.
-Lianke phụ trách lô 10300 đến 10399: đã kiểm tra xong, đang vận chuyển.
-Lô 10400 đến 10449: &lt;s&gt;Không Information kiểm tra, tình trạng chưa rõ.&lt;/s&gt; Đã kiểm tra thủ công, liên hệ tôi để xử lý các vấn đề liên quan.</t>
+Liên Khả phụ trách lô 10300 đến 10399: đã kiểm tra xong, đang vận chuyển.
+Lô 10400 đến 10449: &lt;s&gt;Không có thông tin kiểm tra, tình trạng chưa rõ.&lt;/s&gt; Đã kiểm tra thủ công, liên hệ tôi để xử lý các vấn đề liên quan.</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8210,7 @@
       <c r="M103" t="inlineStr">
         <is>
           <t>Đây là dấu xác nhận của Shiyu: Shixia đã chính thức chinh phục đỉnh núi nơi lá thư này đang nằm!
-Shixia gần đây đã đỗ vào trường top ở KU-Roro B và đặt mục tiêu làm việc cho Bộ Phát Triển. Nó đã tiến xa đến thế, mình không thể không tự hào và hơi ghen tị một chút. Trong khi mình vẫn đang loay hoay tìm hướng đi cho bản thân, Shixia lại đùa về thói quen học tập căng thẳng của nó hôm nay, nhưng mình biết nó sẽ vượt qua kỳ thi một cách xuất sắc—nó luôn tận tâm và thậm chí không nghỉ ngơi để đi chơi với mình trong kỳ nghỉ. Thật sự khó tin là nó lại gặp may như vậy, nhưng mình không thể không mừng cho nó.</t>
+Shixia gần đây đã đỗ vào trường top ở Jinzhou và đặt mục tiêu làm việc cho Bộ Phát Triển. Nó đã tiến xa đến thế, mình không thể không tự hào và hơi ghen tị một chút. Trong khi mình vẫn đang loay hoay tìm hướng đi cho bản thân, Shixia lại đùa về thói quen học tập căng thẳng của nó hôm nay, nhưng mình biết nó sẽ vượt qua kỳ thi một cách xuất sắc—nó luôn tận tâm và thậm chí không nghỉ ngơi để đi chơi với mình trong kỳ nghỉ. Thật khó tin là nó lại gặp may như vậy, nhưng mình không thể không mừng cho nó.</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8279,7 @@
       <c r="M104" t="inlineStr">
         <is>
           <t>Đây là dấu xác nhận của Shiyu: Shixia đã chính thức chinh phục đỉnh núi nơi lá thư này đang nằm!
-Shixia vừa đỗ vào trường top ở KU-Roro B và đặt mục tiêu làm việc tại Bộ Phát Triển. Mình mừng cho con bé, nhưng cũng hơi ghen tị với sự quyết tâm và thành công của nó. Trong khi mình vẫn chưa biết tương lai sẽ làm gì, Shixia cứ khoe mãi về việc nó sẽ vượt qua kỳ thi một cách xuất sắc. Thực tế thì nó học ngày học đêm, còn mình thì đi chơi suốt kỳ nghỉ. Nó như một nhà leo núi, mỗi thành tựu lại đưa nó lên một tầm cao mới. Đáng nể thật!
+Shixia vừa đỗ vào trường top ở Jinzhou và đặt mục tiêu làm việc tại Bộ Phát Triển. Mình mừng cho con bé, nhưng cũng hơi ghen tị với sự quyết tâm và thành công của nó. Trong khi mình vẫn chưa biết tương lai sẽ làm gì, Shixia cứ khoe mãi về việc nó sẽ vượt qua kỳ thi một cách xuất sắc. Thực tế thì nó học ngày học đêm, còn mình thì đi chơi suốt kỳ nghỉ. Nó như một nhà leo núi, mỗi thành tựu lại đưa nó lên một tầm cao mới. Đáng nể thật!
 Dù ban đầu Shixia có chút do dự, cuối cùng nó vẫn cùng mình leo lên địa hình hiểm trở này. Sau khi cùng nhau chinh phục được độ cao như vậy, rõ ràng là nó sẽ không dễ dàng bỏ cuộc. May mà nó đỗ vào Học viện Leyi, nếu không chân nó chắc sẽ dính chặt vào phòng ngủ vì học quá nhiều. Mình chưa thấy ai có nhiều sách giáo khoa đến thế và phòng lúc nào cũng sáng đèn suốt cả năm... chắc là học sinh cá biệt ở trường đáng sợ lắm! Nhưng Shixia có vẻ rất thích. 
 Mình không hiểu tại sao nó lại bỗng dưng cáu kỉnh sau khi đỗ đạt... Nên tranh thủ hỏi nó lúc này, vì giờ nó đang bận ngắm cảnh rồi.</t>
         </is>
@@ -8374,13 +8369,13 @@
 Toán Xuân: giao tiếp bằng tiếng lóng.
 Chân dài: kẻ được ngưỡng mộ.
 Bọ rùa: sếp, đại ca.
-Toán Shui Hỏa: giao nộp tiền SHC.
+Toán Thủy Hỏa: giao nộp tiền SHC.
 Chiếu lộ trang hạc: để mắt tới, quan sát kỹ.
-Move Left táo: mắt.
+Trái táo: mắt.
 Thằng gió: tai.
 Cây vàng: chân.
 Thanh tử: kiếm và vũ khí.
-Stick: súng.
+Gậy: súng.
 ....</t>
         </is>
       </c>
@@ -8452,7 +8447,7 @@
       <c r="M106" t="inlineStr">
         <is>
           <t>Nói đến việc "văng tên" một người: là báo cáo tên của họ
-Thép không sáng, bị kìm Dodgen: thật phiền khi phải khai tên
+Thép không sáng, bị kìm nén: thật phiền khi phải khai tên
 "Empty": kẻ da trắng chẳng biết tiếng lóng là gì
 "Tuanchun": giao tiếp bằng tiếng lóng
 "Tuan Shui": giao nộp tiền SHC
@@ -8595,7 +8590,7 @@
       <c r="M108" t="inlineStr">
         <is>
           <t>Kỳ lạ thật, sao nước vẫn cứ rỉ ra từ cái ống lớn này dù tụi mình đã lấy đá chặn lại rồi?
-Từ khi thằng A chui vào đường ống mà không thấy ra, đến mảnh da nhỏ của nó cũng biến mất, ông sếp không cho ai vào nữa. Gang hội thành phố cũ của chúng ta mới thành lập được một thời gian ngắn, nhân lực không đủ để mất thêm người trong những đường hầm kỳ lạ này.
+Từ khi thằng A chui vào đường ống mà không thấy ra, đến mảnh da nhỏ của nó cũng biến mất, ông sếp không cho ai vào nữa. Bang hội thành phố cũ của chúng ta mới thành lập được một thời gian ngắn, nhân lực không đủ để mất thêm người trong những đường hầm kỳ lạ này.
 Nghe ông sếp có học thức nói, các thành phố lớn trước đây có cả mê cung đường thủy ngầm, không biết chỗ này cũng dẫn đến một mê cung như thế không nhỉ?</t>
         </is>
       </c>
@@ -8804,10 +8799,10 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Ta muốn nước! Dù có đắt đến mấy ta cũng mua!
-Đã năm ngày rồi ta bị nhốt ở đây vì nước biển, ngay cả những căn phòng sửa chữa kỹ nhất cũng bắt đầu rỉ nước......
-Nhưng ta không muốn nước biển mặn chát này, đưa ta nước uống được đi!
-Get hết SHC này đi! Chỉ cần đưa nước cho ta thôi (tờ giấy rách từ đây)</t>
+          <t>Tao muốn nước! Dù có đắt đến mấy tao cũng mua!
+Đã năm ngày rồi tao bị nhốt ở đây vì nước biển, ngay cả những căn phòng sửa chữa kỹ nhất cũng bắt đầu rỉ nước......
+Nhưng tao không muốn nước biển mặn chát này, đưa tao nước uống được đi!
+Lấy hết SHC này đi! Chỉ cần đưa nước cho tao thôi (tờ giấy rách từ đây)</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8884,7 @@
 ......
 Ông trùm kiểm tra quanh khu vực và phát hiện đèn ở đây vẫn còn điện một cách bất ngờ.
 Dù người trước đây đã làm gì với tòa tháp này, chỉ cần thay bóng đèn là tụi mình có thể biến nó thành căn cứ đầu tiên của băng Old City ở đây!
-Thật sự sự rất mong chờ được thắp sáng nó vào tối nay.
+Thật sự rất mong chờ được thắp sáng nó vào tối nay.
 ......
 Thằng đần Four Eyes lại làm rơi một cái đèn, may mà giờ chẳng nhìn rõ nó từng trông như thế nào.
 Nhưng vẫn phải xin lỗi hộ nó, hy vọng ông trùm không mong chờ như mình…</t>
@@ -8961,7 +8956,7 @@
       <c r="M113" t="inlineStr">
         <is>
           <t>Từ đây có thể nhìn thấy cả khu phố, và tớ thích nằm dài thư giãn ở đây...
-Để noi gương Anh Hai, tớ đã rời bỏ KU-Roro B và gia nhập băng Đảng Thành Cổ.
+Để noi gương Anh Hai, tớ đã rời bỏ Jinzhou và gia nhập băng Đảng Thành Cổ.
 Nơi này tượng trưng cho những tàn tích của một vùng đất mà sự phồn vinh dễ dàng tan biến, nhưng Anh Hai tin rằng nó có thể mang đến một thời kỳ phục hưng vượt xa cả Huanglong. Tớ tin vào Anh Hai và mong chờ được cùng anh ấy làm việc!
 Tớ tin vào Anh Hai và cùng anh ấy hướng về phía trước, để được chứng kiến khung cảnh tuyệt đẹp của con phố dài này một lần nữa được thắp sáng bởi những ngọn đèn đường.</t>
         </is>
@@ -9032,7 +9027,7 @@
         <is>
           <t>Những cá nhân đạt "thành tích" tháng này gồm:
 Yue Jing, Lu Yue, Ban Yu, Leng Yi......
-Oz được vinh danh là Ngôi Sao This month nhờ thành tích xuất sắc trong việc mang về hai thùng vũ khí.</t>
+Oz được vinh danh là Ngôi Sao Tháng này nhờ thành tích xuất sắc trong việc mang về hai thùng vũ khí.</t>
         </is>
       </c>
     </row>
@@ -9395,9 +9390,9 @@
 Tôi từng nghĩ Thành phố Biển là một khối thép, nhưng không ngờ nó lại mong manh đến thế trước thảm họa.
 Vì vậy, tôi tuyên bố mở lối đi cho tất cả công dân lên đây. Dĩ nhiên, cứu hết mọi người là điều không tưởng. Cứu được một người là một người, kéo dài thêm một khoảnh khắc là một khoảnh khắc—đó là tất cả những gì tôi còn nghĩ tới.
 Đây là tòa thị chính của Haymarket, và trong những giờ phút nguy cấp, nó phải phục vụ những người đã cùng nhau xây dựng nên nó.
-Survivors tụ họp tại đây, và ngày ngắm sao ban đầu biến thành ngày chạy trốn thực sự. Với những đám mây mờ ảo trên đầu và biển nước vô tận dưới chân, chúng tôi chờ đợi số phận trên một hòn đảo cô lập. Mặt trời và mặt trăng biến mất, tín hiệu cũng đứt đoạn. Cuối cùng, tôi đành phải vẽ lại những bản đồ sao khác nhau về cảnh đêm của các khu phố ở Thành phố Biển và chiếu cho mọi người xem.
-Đó là đoạn phim quảng cáo mới cho Thành phố Hai vừa ra mắt, một cảnh đêm tuyệt đẹp, được quay từ độ cao hàng nghìn mét.
-Previous thảm họa, con người đã mất quyền ngước nhìn bầu trời sao. Nhưng tôi hy vọng chúng ta vẫn có thể chiêm ngưỡng bầu trời sao của riêng mình và giữ gìn nó như một ký ức chung.</t>
+Những người sống sót tụ họp tại đây, và ngày ngắm sao ban đầu biến thành ngày chạy trốn thực sự. Với những đám mây mờ ảo trên đầu và biển nước vô tận dưới chân, chúng tôi chờ đợi số phận trên một hòn đảo cô lập. Mặt trời và mặt trăng biến mất, tín hiệu cũng đứt đoạn. Cuối cùng, tôi đành phải vẽ lại những bản đồ sao khác nhau về cảnh đêm của các khu phố ở Thành phố Biển và chiếu cho mọi người xem.
+Đó là đoạn phim quảng cáo mới cho Thành phố Hải vừa ra mắt, một cảnh đêm tuyệt đẹp, được quay từ độ cao hàng nghìn mét.
+Trước thảm họa, con người đã mất quyền ngước nhìn bầu trời sao. Nhưng tôi hy vọng chúng ta vẫn có thể chiêm ngưỡng bầu trời sao của riêng mình và giữ gìn nó như một ký ức chung.</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9461,7 @@
         <is>
           <t>GIỌNG MÁY: Đây là thông báo quan trọng, chúng tôi sẽ mở Cung Thành Phố để tổ chức một đêm ngắm sao chưa từng có.
 Tất cả công dân trúng xổ số của thành phố đều được mời chiêm ngưỡng biển sao!
-GIỌNG NỮ: Enter lúc 12 giờ đêm nay, xin hãy đến đúng giờ.</t>
+GIỌNG NỮ: Vào lúc 12 giờ đêm nay, xin hãy đến đúng giờ.</t>
         </is>
       </c>
     </row>
@@ -9533,9 +9528,9 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Giọng nói đàn ông hoảng loạn: Các khu phía đông đều ngập hết rồi......
-Giọng nói đàn ông hoảng loạn: Ôi trời! Releasem họa lan nhanh hơn ta tưởng! Đồ tiếp tế? Đồ tiếp tế giờ chẳng còn ý nghĩa gì nữa!
-Giọng nói đàn ông hoảng loạn: Cố bám lấy mái nhà trước khi chạy trốn...... Hello? Alo! Nghe rõ không!</t>
+          <t>Giọng đàn ông hoảng loạn: Các khu phía đông đều ngập hết rồi......
+Giọng đàn ông hoảng loạn: Ôi trời! Thảm họa lan nhanh hơn ta tưởng! Đồ tiếp tế? Đồ tiếp tế giờ chẳng còn ý nghĩa gì nữa!
+Giọng đàn ông hoảng loạn: Cố bám lấy mái nhà trước khi chạy trốn...... Alo? Alo! Nghe rõ không!</t>
         </is>
       </c>
     </row>
@@ -9606,7 +9601,7 @@
           <t>Giọng đàn ông hoảng loạn: Quá nhiều tai nạn! Để giành đồ cứu trợ và chiếm vị trí cao, cả thành phố biển đang hỗn loạn!
 GIỌNG PHỤ NỮ UY QUYỀN: Mở các lối đi và cho người dân lên đây.
 Giọng đàn ông hoảng loạn: Cái gì? Lỡ có kẻ xấu lẻn vào thì sao...... Với lại, chúng ta không chứa nổi nhiều người như vậy!
-GIỌNG PHỤ NỮ UY QUYỀN: Đừng quên, đây là tòa thị chính của Hai Thành, và nó sẽ luôn thuộc về những người...... đã cùng nhau xây dựng nên nó.</t>
+GIỌNG PHỤ NỮ UY QUYỀN: Đừng quên, đây là tòa thị chính của Hải Thành, và nó sẽ luôn thuộc về những người...... đã cùng nhau xây dựng nên nó.</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9670,7 @@
         <is>
           <t>Thành phố thông minh nhất! Bộ não phát triển nhất!
 Haymarket sẽ sở hữu khung xe và hệ thống năng lượng tiên tiến nhất!
-Place tên là... Tương Lai!</t>
+Đặt tên là... Tương Lai!</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9737,7 @@
       <c r="M124" t="inlineStr">
         <is>
           <t>Ngôi sao của bầu trời rộng lớn, màu sắc thực sự của nó? Nhìn từ trên cao xuống cũng giống như nhìn từ dưới lên.
-Hãy chọn Hàng Không Hai Thị, để ngắm nhìn bầu trời sao của riêng người dân Hai Thị.</t>
+Hãy chọn Hàng Không Hải Thị, để ngắm nhìn bầu trời sao của riêng người dân Hải Thị.</t>
         </is>
       </c>
     </row>
@@ -9825,14 +9820,14 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Report bởi Sách Ngỗng
-Kể từ khi Bùng phát TD (130-155 năm trước), sương mù tại vực sâu dưới Họng Cọp đã tăng đột biến, và Viện đã phát hiện một lượng lớn tín hiệu phụ của Sound Wave Cloudy hoạt động tại đây. Nhiều đội thám hiểm đã được cử xuống vực để điều tra, nhưng nhân sự đều chịu tổn thất nghiêm trọng, dữ liệu thất lạc, và tiến độ điều tra không thể tiến triển.
+          <t>Báo cáo bởi Sách Ngỗng
+Kể từ khi Bùng phát TD (130-155 năm trước), sương mù tại vực sâu dưới Họng Cọp đã tăng đột biến, và Viện đã phát hiện một lượng lớn tín hiệu phụ của Sóng Âm U Ám hoạt động tại đây. Nhiều đội thám hiểm đã được cử xuống vực để điều tra, nhưng nhân sự đều chịu tổn thất nghiêm trọng, dữ liệu thất lạc, và tiến độ điều tra không thể tiến triển.
 Mục đích của cuộc thám hiểm lần này là tiếp tục điều tra sương mù và giải cứu nhân sự bị mắc kẹt. Những người liên quan bao gồm:
-Đội Tiên Phong Lữ Đoàn Midnight Ranger (111162)
+Đội Tiên Phong Lữ Đoàn Kỵ Sĩ Bóng Đêm (111162)
 Đội Thám Hiểm Địa Chỉ Viện
 ......
-Phân tích kết quả khảo sát về Misty Bí Ẩn:
-Cuộc thám hiểm đã thu thập mẫu sương mù trong đường hầm nối Mỏ Họng Cọp và Vực Misty, phân tích tại hiện trường bằng [Máy Guang Phổ Đơn Giản] của đội. Kết quả cho thấy sương mù có thể là một thành phần sinh học, tương tự như vảy bột trên cánh loài bướm Lepidoptera, không độc hại và có tính chất nhiệt độ thấp.
+Phân tích kết quả khảo sát về Sương Mù Bí Ẩn:
+Cuộc thám hiểm đã thu thập mẫu sương mù trong đường hầm nối Mỏ Họng Cọp và Vực Sương Mù, phân tích tại hiện trường bằng [Máy Quang Phổ Đơn Giản] của đội. Kết quả cho thấy sương mù có thể là một thành phần sinh học, tương tự như vảy bột trên cánh loài bướm Lepidoptera, không độc hại và có tính chất nhiệt độ thấp.
 Chúng tôi đánh giá mối nguy hiểm của sương mù chủ yếu đến từ đặc tính nhiệt độ thấp:
 ① Sự ngưng tụ hơi nước do nhiệt độ thấp sẽ cản trở tầm nhìn, khiến người điều tra mất phương hướng trong vùng sương mù.
 ② Nhiệt độ thấp trực tiếp ảnh hưởng đến sức khỏe, làm giảm sinh lực, không kịp phản ứng trước nguy hiểm.
@@ -9843,7 +9838,7 @@
 Leyun
 Chonin
 ..................
-(Người thân của những cá nhân trên gần đây có dấu hiệu ảo giác ở nhiều mức độ khác nhau. Họ nghe thấy tiếng gọi vào vực sâu sương mù dưới mỏ, nghi ngờ có liên quan đến đột biến của sương mù. Do Vực Misty đã bị phong tỏa và không thể điều tra thêm, chúng tôi đề nghị thông báo cho tất cả nhân viên tránh xa sương mù và tạm dừng khai thác quanh khu vực này.)</t>
+(Người thân của những cá nhân trên gần đây có dấu hiệu ảo giác ở nhiều mức độ khác nhau. Họ nghe thấy tiếng gọi vào vực sâu sương mù dưới mỏ, nghi ngờ có liên quan đến đột biến của sương mù. Do Vực Sương Mù đã bị phong tỏa và không thể điều tra thêm, chúng tôi đề nghị thông báo cho tất cả nhân viên tránh xa sương mù và tạm dừng khai thác quanh khu vực này.)</t>
         </is>
       </c>
     </row>
@@ -9917,12 +9912,12 @@
         <is>
           <t>Báo Cáo Sự Cố
 Mã Dự Án: ■■■■
-Investigate Viên: ■■■
-Người Bổ Sung Trách: ■■■, ■■■
-Địa Điểm: Ga Sugar Sắt Đô Thị Liên Thành ■■■
-Ngày Month: Ngày ■■■ Month ■■ Năm ■■■
-Tóm Turn Off Sự Cố: Các bất thường và thông tin về sóng âm tập trung phụ của Wuthering Waves trong khu vực đã được thiết bị ■■■ phát hiện phù hợp với địa điểm thí nghiệm lý tưởng cho "nguyên nhân tập trung", do đó đội ■■■ bắt đầu công việc ngay trong ngày. Home nghiên cứu ■■■ đã sử dụng sức mạnh của "Yếu Tố Tập Thể" và kết nối thành công với ■■, thu thập thông tin về lịch sử nơi này cũng như cách xoa dịu ■■. Tuy nhiên, kết nối quá mạnh khiến ■■ không thể tự cắt đứt, nên các thành viên khác đã buộc phải đánh thức ■■ trong khi trấn an ■■. Sau khi ■■■ hoàn tất ghi chép báo cáo, anh ta bắt đầu xuất hiện ảo giác, ý thức mờ nhạt, mất ý thức và tử vong sau một giờ.
-Ga Sugar Sắt Đô Thị Liên Thành ■■■ được đánh giá là cực kỳ nguy hiểm và đã bị phong tỏa, dọn dẹp ngay lập tức, tất cả những người sống sót trong đội ■■■ đều được theo dõi đặc biệt.</t>
+Điều Tra Viên: ■■■
+Người Phụ Trách: ■■■, ■■■
+Địa Điểm: Ga Đường Sắt Đô Thị Liên Thành ■■■
+Ngày Tháng: Ngày ■■■ Tháng ■■ Năm ■■■
+Tóm Tắt Sự Cố: Các bất thường và thông tin về sóng âm tập trung phụ của Wuthering Waves trong khu vực đã được thiết bị ■■■ phát hiện phù hợp với địa điểm thí nghiệm lý tưởng cho "nguyên nhân tập trung", do đó đội ■■■ bắt đầu công việc ngay trong ngày. Nhà nghiên cứu ■■■ đã sử dụng sức mạnh của "Yếu Tố Tập Thể" và kết nối thành công với ■■, thu thập thông tin về lịch sử nơi này cũng như cách xoa dịu ■■. Tuy nhiên, kết nối quá mạnh khiến ■■ không thể tự cắt đứt, nên các thành viên khác đã buộc phải đánh thức ■■ trong khi trấn an ■■. Sau khi ■■■ hoàn tất ghi chép báo cáo, anh ta bắt đầu xuất hiện ảo giác, ý thức mờ nhạt, mất ý thức và tử vong sau một giờ.
+Ga Đường Sắt Đô Thị Liên Thành ■■■ được đánh giá là cực kỳ nguy hiểm và đã bị phong tỏa, dọn dẹp ngay lập tức, tất cả những người sống sót trong đội ■■■ đều được theo dõi đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -9994,11 +9989,11 @@
         <is>
           <t>[
 Biên Bản Sự Kiện Lịch Sử
-Recorder: ■■■
+Người ghi chép: ■■■
 Người kể chuyện: ■■■■
-Địa điểm: Ga Sugar Sắt Liên Thành ■■■
-Ngày tháng: Năm ■■ Month ■■ Ngày ■■
-Tóm tắt: Event này xảy ra vào những ngày đầu của Lament, thời điểm chính xác không rõ. Đoàn tàu Tương Lai được sử dụng để vận chuyển nhóm tinh nhuệ của thành phố ■■■ rời khỏi vùng bị ảnh hưởng nặng nề nhất, nhưng do số lượng người có hạn, rất nhiều thường dân bị bỏ lại trong khu vực chờ, dẫn đến một cuộc xung đột quy mô lớn. Nghệ sĩ piano nổi tiếng của đoàn tàu, ■■■, đã quyết định xuống tàu để đồng hành cùng những thường dân khác và bắt đầu biểu diễn ngay tại phòng chờ VIP. Tiếng đàn của ông đã xoa dịu đám đông và hòa cùng tiếng khóc than của mọi người. Sau khi đoàn tàu bị niêm phong tại Cổng, thông báo bằng giọng nói của hệ thống "■■■■■■■■■■■■■■■■■■■" một lần nữa châm ngòi cho sự phẫn nộ của đám đông, họ xô đẩy khiến đoàn tàu trật bánh và đâm vào núi, gây ra một vụ sạt lở lớn hơn, không ai sống sót.</t>
+Địa điểm: Ga Đường Sắt Liên Thành ■■■
+Ngày tháng: Năm ■■ Tháng ■■ Ngày ■■
+Tóm tắt: Sự kiện này xảy ra vào những ngày đầu của Lời Than Vãn, thời điểm chính xác không rõ. Đoàn tàu Tương Lai được sử dụng để vận chuyển nhóm tinh nhuệ của thành phố ■■■ rời khỏi vùng bị ảnh hưởng nặng nề nhất, nhưng do số lượng người có hạn, rất nhiều thường dân bị bỏ lại trong khu vực chờ, dẫn đến một cuộc xung đột quy mô lớn. Nghệ sĩ piano nổi tiếng của đoàn tàu, ■■■, đã quyết định xuống tàu để đồng hành cùng những thường dân khác và bắt đầu biểu diễn ngay tại phòng chờ VIP. Tiếng đàn của ông đã xoa dịu đám đông và hòa cùng tiếng khóc than của mọi người. Sau khi đoàn tàu bị niêm phong tại Cổng, thông báo bằng giọng nói của hệ thống "■■■■■■■■■■■■■■■■■■■" một lần nữa châm ngòi cho sự phẫn nộ của đám đông, họ xô đẩy khiến đoàn tàu trật bánh và đâm vào núi, gây ra một vụ sạt lở lớn hơn, không ai sống sót.</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10058,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Gửi toàn thể dân làng và nhân viên trú đóng tại khu vực điều tra: Đã có báo cáo về việc phát hiện tần số bất thường ở các khu vực xung quanh làng (bao gồm khu điều tra số chín). Huaxu Academy ước tính có sự tích tụ của Etheric Sea và xác suất cao xuất hiện Tacet Field tại những khu vực này. Để đảm bảo an toàn tính mạng và tài sản của các người, hãy chuẩn bị sơ tán ngay lập tức khi nhận được thông báo này. Chỉ mang theo những vật dụng thiết yếu. Đội Kỵ Binh Night sẽ được điều động hỗ trợ sơ tán. NHẮC LẠI. CHỈ MANG THEO VẬT DỤNG THIẾT YẾU. SƠ TÁN NGAY LẬP TỨC! Hướng dẫn bổ sung: Tất cả nhân viên trú đóng tại khu vực điều tra phải chú ý theo dõi các cảnh báo/thông báo tiếp theo.</t>
+          <t>Gửi toàn thể dân làng và nhân viên trú đóng tại khu vực điều tra: Đã có báo cáo về việc phát hiện tần số bất thường ở các khu vực xung quanh làng (bao gồm khu điều tra số chín). Học Viện Huaxu ước tính có sự tích tụ của Biển Ether và xác suất cao xuất hiện Tổ Tacet tại những khu vực này. Để đảm bảo an toàn tính mạng và tài sản của các người, hãy chuẩn bị sơ tán ngay lập tức khi nhận được thông báo này. Chỉ mang theo những vật dụng thiết yếu. Đội Kỵ Binh Đêm sẽ được điều động hỗ trợ sơ tán. NHẮC LẠI. CHỈ MANG THEO VẬT DỤNG THIẾT YẾU. SƠ TÁN NGAY LẬP TỨC! Hướng dẫn bổ sung: Tất cả nhân viên trú đóng tại khu vực điều tra phải chú ý theo dõi các cảnh báo/thông báo tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -10139,14 +10134,14 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>1 phần Spicy Meat Slices, 1 phần Sellh Màn Thầu, 10 xiên
+          <t>1 phần Thịt Lát Cay, 1 phần Bánh Màn Thầu, 10 xiên
 -Mang theo thanh lương khô đi. 
 -Con không thích lương khô... Có thể mang bánh mì nón bảo hiểm không ạ?
--Gomen con yêu, mẹ không có thời gian làm bánh mì nón bảo hiểm đâu.
+-Xin lỗi con yêu, mẹ không có thời gian làm bánh mì nón bảo hiểm đâu.
 10 lon nước tăng lực
 -Sao lại mang mấy thứ này... Mang vài viên ức chế đi cho rồi!
 -Nhưng nếu khát thì sao?
--Cố chịu đi. Ra tới KU-Roro B, bố sẽ mua trà sữa muối cho con.
+-Cố chịu đi. Ra tới Jinzhou, bố sẽ mua trà sữa muối cho con.
 1 bộ Mạt Chược, 1 lều cắm trại
 -Con yêu à, chúng ta không đi cắm trại đâu.
 -Nhưng bố bảo là đi cắm trại mà?
@@ -10217,9 +10212,9 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Cây cổ thụ "Long Nhãn" nằm ở phía bắc vùng Long's Gaze Suburbs, Trung Nguyên. Theo ghi chép trong "Thực Vật Chí Jinzhou", Long Nhãn ước tính đã 1400-1500 năm tuổi, trải qua Lời Than mà vẫn hiên ngang. Rễ cây uốn lượn như mãng xà quấn quanh cờ rồng, cành lá như vuốt sắc, thể hiện bản tính bất khuất của cây.
+          <t>Cây cổ thụ "Long Nhãn" nằm ở phía bắc vùng Ngoại Ô Long Nhãn, Trung Nguyên. Theo ghi chép trong "Thực Vật Chí Cẩm Châu", Long Nhãn ước tính đã 1400-1500 năm tuổi, trải qua Lời Than mà vẫn hiên ngang. Rễ cây uốn lượn như mãng xà quấn quanh cờ rồng, cành lá như vuốt sắc, thể hiện bản tính bất khuất của cây.
 Cây cổ thụ bất động này từ lâu đã trở thành biểu tượng của vùng đất, là ngọn hải đăng hy vọng cho mọi người. Chừng nào Long Nhãn còn đứng vững, ngày Trung Nguyên hồi sinh nhất định sẽ đến.
-Chú ý: Xin đừng khắc lên vỏ hay cành cây. Chúng ta đều có trách nhiệm bảo vệ cây cổ thụ này.</t>
+Lưu ý: Xin đừng khắc lên vỏ hay cành cây. Chúng ta đều có trách nhiệm bảo vệ cây cổ thụ này.</t>
         </is>
       </c>
     </row>
@@ -10289,9 +10284,9 @@
       <c r="M131" t="inlineStr">
         <is>
           <t>Ngày 27
-Shoot phá kéo dài ba tiếng. Nghỉ hai tiếng, rồi lại bắn phá tiếp ba tiếng.
+Bắn phá kéo dài ba tiếng. Nghỉ hai tiếng, rồi lại bắn phá tiếp ba tiếng.
 Ngày 28
-Shoot phá vẫn tiếp tục ba tiếng. Nghỉ hai tiếng, rồi lại ba tiếng bắn phá. Sansui bảo tôi đừng ghi chép nữa, không chính xác đâu. Nhưng tôi thấy Gui thở dài rồi bấm giờ, thường là nửa tiếng thì hắn lại rên lên. Tôi biết thói quen của hắn, vẫn vậy từ trước đến giờ.
+Bắn phá vẫn tiếp tục ba tiếng. Nghỉ hai tiếng, rồi lại ba tiếng bắn phá. Sansui bảo tôi đừng ghi chép nữa, không chính xác đâu. Nhưng tôi thấy Gui thở dài rồi bấm giờ, thường là nửa tiếng thì hắn lại rên lên. Tôi biết thói quen của hắn, vẫn vậy từ trước đến giờ.
 Ghi chép thời gian là cần thiết. Một ngày nào đó, chúng ta sẽ phải ra ngoài.</t>
         </is>
       </c>
@@ -10437,7 +10432,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Đứa con của Tiểu Quỷ ra đời vào ban đêm. Ánh trăng chiếu qua cái lỗ lớn trên trần hang do đạn pháo tạo ra, sáng đến lạ. Chúng tôi bàn nhau đặt tên cho đứa bé, cuối cùng chọn "Changming". Đứa trẻ khóc lên khi nghe cái tên ấy, rồi Tiểu Quỷ cũng òa theo, sau đó là mọi người, kể cả Tam Shui, người cứ liên tục lau mắt.
+          <t>Đứa con của Tiểu Quỷ ra đời vào ban đêm. Ánh trăng chiếu qua cái lỗ lớn trên trần hang do đạn pháo tạo ra, sáng đến lạ. Chúng tôi bàn nhau đặt tên cho đứa bé, cuối cùng chọn "Changming". Đứa trẻ khóc lên khi nghe cái tên ấy, rồi Tiểu Quỷ cũng òa theo, sau đó là mọi người, kể cả Tam Thủy, người cứ liên tục lau mắt.
 Trước khi mái hang bị phá vỡ, bầu trời chẳng hề có ánh sáng. Nghe tiếng pháo kích bên ngoài, ngoài nỗi sợ hãi, còn có một chút... thoải mái khó tả. Giờ thì tốt hơn nhiều, ít nhất cũng biết khi nào trời sáng, khi nào trời tối, khi nào mưa. Mọi người đã quyết định sống ở đây, Threnody rồi sẽ ra sao, tôi không muốn nghĩ tới. Ở đây cũng tốt mà.
 Biết đâu sau này, sẽ có ai đó đến đây điều tra và tìm thấy "người hang động" gì đó. Tôi chỉ viết lại những dòng này với hy vọng nhà thám hiểm đừng làm chúng tôi xấu hổ bằng cách đối xử như với đám vượn cổ, rồi nghiên cứu này nọ.
 Chúng tôi chỉ là những dân làng chạy nạn đến đây thôi, chẳng có gì đặc biệt, không cần phải nhớ đến chúng tôi đâu.</t>
@@ -10507,7 +10502,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Việc xây dựng Mảng Focus sẽ chính thức bắt đầu vào ngày 10 tháng 9, khi Ga Vận Switch Công Nghiệp Tacetite chịu trách nhiệm vận chuyển. Các nhân viên liên quan được yêu cầu chú ý đảm bảo an toàn giao thông, kiểm tra kỹ lưỡng vật liệu và thường xuyên giám sát môi trường để đảm bảo việc lưu trữ an toàn cho dung dịch âm thanh.
+          <t>Việc xây dựng Mảng Tập Trung sẽ chính thức bắt đầu vào ngày 10 tháng 9, khi Ga Vận Chuyển Công Nghiệp Tacetite chịu trách nhiệm vận chuyển. Các nhân viên liên quan được yêu cầu chú ý đảm bảo an toàn giao thông, kiểm tra kỹ lưỡng vật liệu và thường xuyên giám sát môi trường để đảm bảo việc lưu trữ an toàn cho dung dịch âm thanh.
 Trong quá trình thi công, nhân viên không chuyên môn phải tránh xa công trường và nghiêm cấm tiếp xúc trực tiếp với dung dịch khi không có đồ bảo hộ. Nếu cảm thấy khó chịu, hãy báo cáo ngay.
 AL158 – 30 tháng 8 năm 2008</t>
         </is>
@@ -10660,22 +10655,22 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>"~Home Trọ Serenity~
-Kỷ yếu Read Hằng Tuần - Số Special Kỷ Niệm 100
-*Tin Tức New Mẻ Hằng Tuần* Giới Hạn Của Sự Tụ Họp
-Carnival Throw Hoa đầu tiên của làng Qichi đã kết thúc tốt đẹp. Khác với những năm trước, để kỷ niệm việc hoàn thành ngôi làng phía bắc, làng Qichi đã mời nhiều dân làng lân cận tham gia như một lời tri ân cho sự hỗ trợ của mọi người.
-Throw Hoa là một phong tục của dân làng Qichi từ xa xưa. Enter tháng Ba, những cành hoa mới gấp và cánh hoa tươi được Dodgem xuống hồ Yuhua để nước cảm nhận được sức sống của mùa xuân sớm, và cầu nguyện niềm vui của sự sống mới sẽ lan tỏa vào lòng người, giúp họ không bị giam cầm bởi sự hủy diệt của Lament.
-Gần quán trọ của chúng ta cũng có một cái ao nhỏ, nếu bạn quan tâm, hãy thử Dodgem một nắm cánh hoa xuống đó khi đi dạo sau bữa tối. Dù không rộng lớn như hồ Yuhua ở làng Qichi, nhưng những lời cầu nguyện và niềm vui chắc chắn sẽ được chia sẻ.
-*Read khi đi vệ sinh
+          <t>"~Nhà Trọ Bình Yên~
+Kỷ yếu Đọc Hằng Tuần - Số Đặc Biệt Kỷ Niệm 100
+*Tin Tức Mới Mẻ Hằng Tuần* Giới Hạn Của Sự Tụ Họp
+Lễ Hội Ném Hoa đầu tiên của làng Qichi đã kết thúc tốt đẹp. Khác với những năm trước, để kỷ niệm việc hoàn thành ngôi làng phía bắc, làng Qichi đã mời nhiều dân làng lân cận tham gia như một lời tri ân cho sự hỗ trợ của mọi người.
+Ném Hoa là một phong tục của dân làng Qichi từ xa xưa. Vào tháng Ba, những cành hoa mới gấp và cánh hoa tươi được ném xuống hồ Yuhua để nước cảm nhận được sức sống của mùa xuân sớm, và cầu nguyện niềm vui của sự sống mới sẽ lan tỏa vào lòng người, giúp họ không bị giam cầm bởi sự hủy diệt của Lament.
+Gần quán trọ của chúng ta cũng có một cái ao nhỏ, nếu bạn quan tâm, hãy thử ném một nắm cánh hoa xuống đó khi đi dạo sau bữa tối. Dù không rộng lớn như hồ Yuhua ở làng Qichi, nhưng những lời cầu nguyện và niềm vui chắc chắn sẽ được chia sẻ.
+*Đọc khi đi vệ sinh
 \"Tại sao Hổ Hàm lại chẳng giống miệng hổ chút nào?\"
 \"Bởi vì từ rất lâu rồi, có một con dê lạc vào núi...\"
-Các nhà khoa học phân tích thành phần Tacetite và phát hiện ra nó chính là ước nguyện của Synergy Giả.
-Chirpuff đang trôi theo dòng sông thì bắt gặp một con Diệc Feather đang kiếm ăn và reo lên: \"Chirpuff!!!\"
+Các nhà khoa học phân tích thành phần Tacetite và phát hiện ra nó chính là ước nguyện của Resonator.
+Chirpuff đang trôi theo dòng sông thì bắt gặp một con Diệc Lông Vũ đang kiếm ăn và reo lên: \"Chirpuff!!!\"
 (Trang này cũ hơn những trang khác và có vẻ đã bị giở đi giở lại nhiều lần)
-*Lời Bạt Special* Lời Parting Cuối Cùng
-Không ngờ rằng *Focus* đã đồng hành cùng các vị khách du hành được hai năm hai tháng, và đã xuất bản thành công số thứ 100. Ở cuối số *Focus* này, chúng tôi muốn nói lời tạm biệt với tất cả các bạn.
+*Lời Bạt Đặc Biệt* Lời Chia Tay Cuối Cùng
+Không ngờ rằng *Tập Trung* đã đồng hành cùng các vị khách du hành được hai năm hai tháng, và đã xuất bản thành công số thứ 100. Ở cuối số *Tập Trung* này, chúng tôi muốn nói lời tạm biệt với tất cả các bạn.
 Cuộc chiến kiểu LamentSonata đã cách mạng hóa vùng Trung Nguyên, và những thảm họa bất ngờ liên tiếp khiến chúng ta khó lòng chống đỡ. Với tốc độ này, ComfortSonata sẽ không thể sống đúng với tên gọi của mình, mang đến cho du khách một trải nghiệm sống thực sự an toàn và thoải mái.
-Nhưng lời chia tay của chúng tôi sẽ không đột ngột như của Lament. Chúng tôi sẽ tiếp tục hoạt động thêm một tháng nữa, và khi việc bàn giao hoàn tất, tòa nhà sẽ được giữ lại và chuyển giao cho KU-Roro B. Còn tương lai của nó sẽ ra sao, hãy cùng chờ xem nhé!</t>
+Nhưng lời chia tay của chúng tôi sẽ không đột ngột như của Lament. Chúng tôi sẽ tiếp tục hoạt động thêm một tháng nữa, và khi việc bàn giao hoàn tất, tòa nhà sẽ được giữ lại và chuyển giao cho Jinzhou. Còn tương lai của nó sẽ ra sao, hãy cùng chờ xem nhé!</t>
         </is>
       </c>
     </row>
@@ -10745,11 +10740,11 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>...... Có rất nhiều lời đồn về nó, không chỉ từ thế giới bên ngoài mà ngay cả trong Pioneer Association.
+          <t>...... Có rất nhiều lời đồn về nó, không chỉ từ thế giới bên ngoài mà ngay cả trong Hiệp Hội Tiên Phong.
 Kể từ khi bắt đầu quan tâm đến nó, ta đã đọc gần như tất cả thông tin mà các thế hệ trước để lại, và cũng đã hỏi thăm các tiền bối từng đảm nhận nhiệm vụ điều tra, nhưng vẫn chưa có kết luận nào rõ ràng, chỉ còn lại vài mảnh ký ức vụn vặt.
 "Trên ngọn hải đăng gió thổi là ngôi sao soi sáng vũ trụ."
-"Rare khi thấy một cổ vật hồi sinh như vậy; như những thi nhân từng nói, đó là ngọn đèn của nền văn minh."
-"Vùng đất này ngập tràn Scar, nhưng nó chưa bao giờ từ bỏ việc tự chữa lành, và ánh sáng bừng lên mỗi đêm chính là biểu hiện của sự Restoration, từng hơi thở, từng hơi thở, từng hơi thở...... Nếu một ngày ánh sáng này tắt lịm, có lẽ......"
+"Hiếm khi thấy một cổ vật hồi sinh như vậy; như những thi nhân từng nói, đó là ngọn đèn của nền văn minh."
+"Vùng đất này ngập tràn Vết Sẹo, nhưng nó chưa bao giờ từ bỏ việc tự chữa lành, và ánh sáng bừng lên mỗi đêm chính là biểu hiện của sự Phục Hồi, từng hơi thở, từng hơi thở, từng hơi thở...... Nếu một ngày ánh sáng này tắt lịm, có lẽ......"
 "Ngọn hải đăng, ngọn hải đăng! Rốt cuộc nó soi sáng điều gì? Niềm hy vọng của ánh sáng, hay một bí ẩn tối tăm, vô danh dẫn lối vào bóng đêm?"</t>
         </is>
       </c>
@@ -10825,7 +10820,7 @@
 Những ai được chọn đi cùng hãy báo danh và gạch tên mình ra (ai không đến sẽ bị trừ khẩu phần ba ngày).
 Danh sách: &lt;s&gt;Mashan&lt;/s&gt;, Zhiyan, &lt;s&gt;Shekishui&lt;/s&gt;.
 Còn lại tự lo liệu.
-Uncle ý.
+Chú ý.
 Không gây sự với quan lại Huanglong, không gây sự với băng nhóm khác, trừ khi đủ sức đánh bại tất cả.
 Nhớ cân nhắc khả năng của mình trước khi ra tay.</t>
         </is>
@@ -10969,13 +10964,13 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Hi người qua đường.
+          <t>Chào người qua đường.
 Nếu có thể, hãy dành hai phút thử nghiệm thiết bị trước mặt cậu nhé. Nó sẽ giúp cậu trải nghiệm cảm giác biến thành bướm và tự do bay lượn, đồng thời việc sử dụng của cậu sẽ giúp tớ thu thập dữ liệu thí nghiệm.
 [Giải thích Nguyên lý Thí nghiệm
 &lt;i&gt;Dài quá, không đọc nổi.&lt;/i&gt;
-Tớ đã phân tích một Echoes bay ổn định từ nhiều Tingyos, phân rã phổ thông tin thành giải pháp ở cấp độ thông tin di truyền, rồi dùng Naritsugu kết hợp với thông tin đó để tái tạo lực Forte của một TD, lúc này người dùng Echoes sẽ có thể điều khiển Naritsugu để tái tạo lực Forte của TD hoặc Creatures Đột Biến tương ứng.
-&lt;i&gt;Nếu cậu quan tâm, có thể đến Viện nghe tớ giảng về Echoes.&lt;/i&gt;
-Thông tin liên hệ: None địa điểm hay thời gian cụ thể, cứ đến hỏi là được (buổi học thường đóng cửa vì vắng khách).</t>
+Tớ đã phân tích một Echo bay ổn định từ nhiều Tingyos, phân rã phổ thông tin thành giải pháp ở cấp độ thông tin di truyền, rồi dùng Naritsugu kết hợp với thông tin đó để tái tạo lực Forte của một TD, lúc này người dùng Echo sẽ có thể điều khiển Naritsugu để tái tạo lực Forte của TD hoặc Sinh Vật Đột Biến tương ứng.
+&lt;i&gt;Nếu cậu quan tâm, có thể đến Viện nghe tớ giảng về Echo.&lt;/i&gt;
+Thông tin liên hệ: Không có địa điểm hay thời gian cụ thể, cứ đến hỏi là được (buổi học thường đóng cửa vì vắng khách).</t>
         </is>
       </c>
     </row>
@@ -11066,19 +11061,19 @@
 Những người trong Chelsea Crowd không giống như những kẻ Lưu Đày bình thường, họ quá phức tạp, không phải loại chỉ biết dùng vũ lực. Họ có luật lệ riêng, và thương lượng có lẽ không phải là lựa chọn tốt.
 Nhưng nếu cậu thực sự quyết tâm, tôi sẽ thử cùng cậu.
 (một mảnh giấy nhàu nát)
-...... Tôi nghĩ cậu cũng đã chịu đựng đủ rồi. Night nào tôi cũng lo lắng, dằn vặt. Tôi nhớ cậu và muốn được sống bên cậu. Chính những sai lầm trong quá khứ của tôi đã dẫn đến kết cục này... Tôi không thể cứ trốn mãi ở KU-Roro B để cậu phải chịu đựng ở nơi như thế...... Tôi hối hận biết bao, giá như người bị bắt làm con tin là tôi......
+...... Tôi nghĩ cậu cũng đã chịu đựng đủ rồi. Đêm nào tôi cũng lo lắng, dằn vặt. Tôi nhớ cậu và muốn được sống bên cậu. Chính những sai lầm trong quá khứ của tôi đã dẫn đến kết cục này... Tôi không thể cứ trốn mãi ở Jinzhou để cậu phải chịu đựng ở nơi như thế...... Tôi hối hận biết bao, giá như người bị bắt làm con tin là tôi......
 Tôi nên nói chuyện với họ...... Dù phải trả nợ thế nào, tôi cũng phải giải quyết xong. Những móc câu đê tiện đó, hãy tìm người khác mà sai khiến. Tôi muốn thanh toán mọi chuyện với họ.
-Sau đó, chúng ta sẽ rời KU-Roro B và Huanglong. Chỉ cần có nhau, tôi sẽ đi bất cứ đâu.
+Sau đó, chúng ta sẽ rời Jinzhou và Huanglong. Chỉ cần có nhau, tôi sẽ đi bất cứ đâu.
 (Ở mặt sau tờ giấy ghi &lt;color=#ffd12f&gt;1012&lt;/color&gt;, có vẻ là ngày tháng.)
 Ngày 20 tháng 10.
 Luật lệ của giáo đoàn Chelating vẫn không đổi so với bảy năm trước. Nhưng hai ta...... chắc chắn không thể vượt qua.
 Tôi đã chứng kiến trò hề này quá nhiều lần. Dù gọi là đấu tay đôi nghe có vẻ công bằng, nhưng họ sẽ không bao giờ tuân theo luật lệ.
 Cần nhiều sức mạnh hơn...... Chúng ta chỉ còn cách đánh cược.
 (Tài liệu và mẩu báo dán lại)
-"Một phụ nữ ở KU-Roro B vô tình nuốt phải Tacetite trở thành Synergy Giả và ngay lập tức gia nhập Midnight Rangers!
+"Một phụ nữ ở Jinzhou vô tình nuốt phải Tacetite trở thành Resonator và ngay lập tức gia nhập Midnight Rangers!
 Những rủi ro khi Overclock do tiếp xúc lâu dài với Tacetite: Theo dõi kết quả nghiên cứu.
 Ngày 21 tháng 10.
-Read River khỏe hơn tôi nhiều. Anh ấy may mắn hơn tôi......
+Read River khỏe hơn tôi nhiều. Hắn may mắn hơn tôi......
 Vậy là tốt, chỉ cần một trong hai ta thắng, chúng ta sẽ có cơ hội lấy được vật liệu âm thanh...... để cứu vãn mọi thứ trước khi hoàn toàn Overclock......
 Ngày 22 tháng 10.
 Không còn thời gian...... tôi......
@@ -11226,17 +11221,17 @@
       <c r="M143" t="inlineStr">
         <is>
           <t>&lt;alignleft/&gt;Người giữ kỷ lục:               "Đội Tạm Thời"
-&lt;alignleft/&gt;Race thứ 1                            Đội Không Sợ Hãi
-&lt;alignleft/&gt;Race thứ 2                          Đội Phép Màu
+&lt;alignleft/&gt;Đua thứ 1                            Đội Không Sợ Hãi
+&lt;alignleft/&gt;Đua thứ 2                          Đội Phép Màu
 &lt;alignleft/&gt;...
 &lt;alignleft/&gt;...
-&lt;alignleft/&gt;Race thứ 22                        Đội Tạm Thời
-&lt;alignleft/&gt;Race thứ 23                        Đội Về Home
-&lt;alignleft/&gt;Race thứ 24                        Đội Sự Thật sự
-&lt;alignleft/&gt;Race thứ 25                        Đội Puffaloos
-&lt;alignleft/&gt;Race thứ 26                        Đội U Sầu
-&lt;alignleft/&gt;Race thứ 27                        Đội Đừng Sad
-&lt;alignleft/&gt;Race thứ 28                        Đội Malee Lạ Quá</t>
+&lt;alignleft/&gt;Đua thứ 22                        Đội Tạm Thời
+&lt;alignleft/&gt;Đua thứ 23                        Đội Về Nhà
+&lt;alignleft/&gt;Đua thứ 24                        Đội Sự Thật
+&lt;alignleft/&gt;Đua thứ 25                        Đội Puffaloos
+&lt;alignleft/&gt;Đua thứ 26                        Đội U Sầu
+&lt;alignleft/&gt;Đua thứ 27                        Đội Đừng Buồn
+&lt;alignleft/&gt;Đua thứ 28                        Đội Tên Lạ Quá</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11296,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Có vẻ như các tộc trưởng Hoochief ở đây đã chia thành hai phe, hai thủ lĩnh của phe cũ và mới đang tranh giành quyền kiểm soát lãnh địa hang động này! Phe bên trái đang tấn công dữ dội vào phe bên phải! Một cú uppercut đẹp mắt! Bravo Giờ thì con khỉ đột bên phải loạng choạng, xem nào... Xuất sắc! Jian định, kiên định! Nó lấy lại thăng bằng bằng ý chí kiên cường! Do tốt lắm! Một cú đá quét... ôi không, trượt rồi! Đối thủ Dodge được và con khỉ đột bên phải lại ngã xuống. Ái chà... View tiếp diễn biến thế nào nhé...</t>
+          <t>Có vẻ như các tộc trưởng Hoochief ở đây đã chia thành hai phe, hai thủ lĩnh của phe cũ và mới đang tranh giành quyền kiểm soát lãnh địa hang động này! Phe bên trái đang tấn công dữ dội vào phe bên phải! Một cú uppercut đẹp mắt! Tuyệt vời! Giờ thì con khỉ đột bên phải loạng choạng, xem nào... Xuất sắc! Kiên định, kiên định! Nó lấy lại thăng bằng bằng ý chí kiên cường! Làm tốt lắm! Một cú đá quét... ôi không, trượt rồi! Đối thủ né được và con khỉ đột bên phải lại ngã xuống. Ái chà... Xem tiếp diễn biến thế nào nhé...</t>
         </is>
       </c>
     </row>
@@ -11370,7 +11365,7 @@
       <c r="M145" t="inlineStr">
         <is>
           <t>Ta lập liên minh, tấn công Hải Tinh vào đúng thời điểm.
-Triumph trong tay, chia lãnh địa 60/40, kho báu 50/50.
+Chiến thắng trong tay, chia lãnh địa 60/40, kho báu 50/50.
 Nếu muốn tham gia, gặp ta bên bờ sông, nửa đêm, ngày mười lăm.
 Năm đồng.</t>
         </is>
@@ -11447,7 +11442,7 @@
 Ngày sinh: 4 tháng 5
 Gia đình: Cha - Qiao Er’shou (nghề mổ thịt, mất cách đây 5 năm). Mẹ - Lin Ru (giáo viên, mất tích 10 năm). Anh trai - Qiao Sheng (thành viên trại này). Em gái - Qiao Qiao (đang đi học ở quê).
 Mối quan hệ xã hội: Bạn - Bo’jun (người bán trái cây ở quê). Bạn - Yizhou (người lưu đày).
-Trải nghiệm cá nhân: Bắt đầu đi học năm 8 tuổi. Bị giam tại trung tâm giáo dưỡng vì cố ý gây thương tích trong một vụ tranh cãi với bạn cùng lớp. Bị đưa vào trại trẻ mồ côi năm 12 tuổi do không có người giám hộ. Bị đuổi học năm 15 tuổi vì đánh nhau nghiêm trọng. Năm 16 tuổi, phải nằm viện một năm để phục hồi. Sau khi xuất viện, làm công nhân thời vụ ở KU-Roro B cho đến khi tìm đến anh trai để nương nhờ.</t>
+Trải nghiệm cá nhân: Bắt đầu đi học năm 8 tuổi. Bị giam tại trung tâm giáo dưỡng vì cố ý gây thương tích trong một vụ tranh cãi với bạn cùng lớp. Bị đưa vào trại trẻ mồ côi năm 12 tuổi do không có người giám hộ. Bị đuổi học năm 15 tuổi vì đánh nhau nghiêm trọng. Năm 16 tuổi, phải nằm viện một năm để phục hồi. Sau khi xuất viện, làm công nhân thời vụ ở Jinzhou cho đến khi tìm đến anh trai để nương nhờ.</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11529,7 @@
 Bắt đầu ăn trộm từ năm 6 tuổi để giúp đỡ gia đình. Bị bắt khi ăn cắp vặt năm 9 tuổi, làm gãy chân chủ cửa hàng khi bỏ chạy và để lại thương tật vĩnh viễn. Gia nhập băng đảng buôn vũ khí đường phố năm 10 tuổi.
 Bị bắt và giam giữ tại trung tâm giáo dưỡng năm 11 tuổi vì tiết lộ thông tin hoạt động của băng. Trốn thoát và rời khỏi nước để gia nhập chi nhánh phía đông của Hall of Six năm 13 tuổi. Sống sót sau khi bị bắn ba phát trong một phi vụ giao dịch năm 15 tuổi và phải ghép gan.
 Năm 17 tuổi, trở thành đội trưởng một đội trong chi nhánh phía đông nhưng bị đình chỉ năm 18 tuổi do cuộc thanh trừng nội bộ. Chuyển sang chi nhánh trung tâm năm 20 tuổi nhưng bị giáng chức sau xung đột với cấp trên và bị kỷ luật để lại vết sẹo trên mặt. Chuyển đi nơi khác.
-Định cư tại trại Lưu Đày Biển Đom Đóm năm 22 tuổi và tiếp tục vận chuyển vũ khí lẻ tẻ cho Hall of Six ra vào KU-Roro B. Năm 23 tuổi, trở thành một kẻ lưu đày bình thường trong đợt truy quét đầu tiên của Cục An Ninh Công Cộng, khiến mọi hoạt động vận chuyển vũ khí phải dừng lại trong hai năm.
+Định cư tại trại Lưu Đày Biển Đom Đóm năm 22 tuổi và tiếp tục vận chuyển vũ khí lẻ tẻ cho Hall of Six ra vào Jinzhou. Năm 23 tuổi, trở thành một kẻ lưu đày bình thường trong đợt truy quét đầu tiên của Cục An Ninh Công Cộng, khiến mọi hoạt động vận chuyển vũ khí phải dừng lại trong hai năm.
 Mối quan hệ xã hội:
 Bạn bè:
 Auspice (Nam, lính canh trại, anh trai của Prosper. Không suy nghĩ nhiều, thích chiến đấu. Thường canh gác cổng trại)
@@ -11612,9 +11607,9 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Cấp tiến: Jian, Yanfeng, Zaijia, Fuze, Bo, Bạn.
+          <t>Cấp tiến: Jian, Yanfeng, Zaijia, Fuze, Bo, You.
 Bảo thủ: Zhao’an, Huai, Auspice, Prosper.
-Neutral: Kuixiao, Yu'er, Tianhai, Xinyuan, Zhao.
+Trung lập: Kuixiao, Yu'er, Tianhai, Xinyuan, Zhao.
 (Thái độ của các thành viên khác hiện chưa rõ)
 Người thực hiện: Shenhai</t>
         </is>
@@ -11751,7 +11746,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Qua đây xác nhận Fuze đã vay Kuixiao số tiền 10.000 Credit để thay thế Terminal. Hai bên thống nhất khoản nợ sẽ được hoàn trả trước ngày 11 tháng 3 năm 2502, tính lãi một lần duy nhất. Lãi suất được thỏa thuận là 7% mỗi tháng. Chứng giám, chúng tôi ký tên dưới đây.
+          <t>Qua đây xác nhận Fuze đã vay Kuixiao số tiền 10.000 Credit để thay thế Thiết bị đầu cuối. Hai bên thống nhất khoản nợ sẽ được hoàn trả trước ngày 11 tháng 3 năm 2502, tính lãi một lần duy nhất. Lãi suất được thỏa thuận là 7% mỗi tháng. Chứng giám, chúng tôi ký tên dưới đây.
 Người vay: Fuze
 Nhân chứng: Bo</t>
         </is>
@@ -11826,13 +11821,13 @@
       <c r="M151" t="inlineStr">
         <is>
           <t>Chương 13: Khế Ước Tử Thần
-Ánh mắt đe dọa của Guan tòa xuyên thủng người phụ nữ đang run rẩy như dao nóng cắt qua bơ. "Ký vào bản hợp đồng này đi, em yêu. Từ giờ, em sẽ thuộc về ta. Chỉ cần em không phá vỡ bất kỳ điều khoản nào trong ba năm tới, ta sẽ khiến gã chồng cũ của em phải cầu xin sự thương xót và mong cho cái chết đến thật nhanh."
+Ánh mắt đe dọa của Quan tòa xuyên thủng người phụ nữ đang run rẩy như dao nóng cắt qua bơ. "Ký vào bản hợp đồng này đi, em yêu. Từ giờ, em sẽ thuộc về ta. Chỉ cần em không phá vỡ bất kỳ điều khoản nào trong ba năm tới, ta sẽ khiến gã chồng cũ của em phải cầu xin sự thương xót và mong cho cái chết đến thật nhanh."
 Người phụ nữ gục xuống sàn, nước mắt lăn dài trên khuôn mặt từng lộng lẫy, giờ đây lem luốc vết mascara. Cô nắm chặt tờ giấy như đó là cơ hội cuối cùng để chuộc lỗi. Trong một sự trớ trêu của số phận, kẻ thù cũ giờ lại trở thành ân nhân của cô. Mái tóc từng khiến bao người ghen tị giờ chỉ còn xơ xác buông xuống như một đóa hoa héo úa. "Được," cô nghẹn ngào, "nhưng ta có một điều kiện."
-Guan tòa ngả người ra sau, nụ cười tự mãn hiện rõ trên môi. "Nói đi," ông ta thì thầm.
-"Người đàn bà đó? Right biến mất khỏi thế giới này," cô đòi hỏi, ánh mắt lóe lên ngọn lửa báo thù.
-Guan tòa cau ngươi, khó hiểu nhìn cô khóc. "Được thôi," ông ta nhanh chóng đáp, một tay nâng cô dậy khiến cô loạng choạng ngã vào lòng ông. Khi cô vùng vẫy chống cự, Dodget mặt Guan tòa dịu lại, đôi mắt thoáng chút thích thú.
+Quan tòa ngả người ra sau, nụ cười tự mãn hiện rõ trên môi. "Nói đi," ông ta thì thầm.
+"Người đàn bà đó? Phải biến mất khỏi thế giới này," cô đòi hỏi, ánh mắt lóe lên ngọn lửa báo thù.
+Quan tòa cau mày, khó hiểu nhìn cô khóc. "Được thôi," ông ta nhanh chóng đáp, một tay nâng cô dậy khiến cô loạng choạng ngã vào lòng ông. Khi cô vùng vẫy chống cự, nét mặt Quan tòa dịu lại, đôi mắt thoáng chút thích thú.
 "Đừng đụng vào tôi!"
-"Ha! Đừng tự mãn quá, em yêu," Guan tòa cười khẩy. "Ta còn chẳng thèm đụng vào em bằng cái sào dài ba mét đâu.""</t>
+"Ha! Đừng tự mãn quá, em yêu," Quan tòa cười khẩy. "Ta còn chẳng thèm đụng vào em bằng cái sào dài ba mét đâu.""</t>
         </is>
       </c>
     </row>
@@ -11897,7 +11892,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Tấn Châu là một thành phố pháo đài nằm ở biên giới đông nam Huanglong. Đây là cảng đất liền đầu tiên mà mọi tàu thuyền nước ngoài phải cập bến khi vào lãnh thổ. Nhân sự và hàng hóa ngoại quốc đều phải được kiểm tra và dỡ hàng tại Cảng Quân Triều. Cảng Quân Triều sở hữu hệ thống quản lý container hoàn thiện cùng cơ sở neo đậu quy mô lớn. Đây là một cảng trung chuyển tổng hợp và cảng container chính với lưu lượng hàng hóa cao nhất Huanglong. Hiện tại, Cảng Quân Triều đã thiết lập quan hệ đối tác chiến lược dài hạn với Lollo Logistics và Pioneer Association. Chúng tôi hoan nghênh mọi hình thức hợp tác kinh doanh.    Văn phòng Mailơng mại, Cảng Quân Triều</t>
+          <t>Tấn Châu là một thành phố pháo đài nằm ở biên giới đông nam Huanglong. Đây là cảng đất liền đầu tiên mà mọi tàu thuyền nước ngoài phải cập bến khi vào lãnh thổ. Nhân sự và hàng hóa ngoại quốc đều phải được kiểm tra và dỡ hàng tại Cảng Quân Triều. Cảng Quân Triều sở hữu hệ thống quản lý container hoàn thiện cùng cơ sở neo đậu quy mô lớn. Đây là một cảng trung chuyển tổng hợp và cảng container chính với lưu lượng hàng hóa cao nhất Huanglong. Hiện tại, Cảng Quân Triều đã thiết lập quan hệ đối tác chiến lược dài hạn với Lollo Logistics và Hiệp hội Pioneer. Chúng tôi hoan nghênh mọi hình thức hợp tác kinh doanh.    Văn phòng Thương mại, Cảng Quân Triều</t>
         </is>
       </c>
     </row>
@@ -11962,7 +11957,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Ta nhớ có lẽ là một buổi chiều tháng trước, khi ta đang kiểm hàng ở kho. Ta cúi xuống thì thấy một bông hoa đen lạ hoắc, chưa bao giờ thấy. Vừa định nhặt lên thì bỗng dưng nó biến thành sương khói và biến mất với tiếng "bụp". Ta có ảo giác không nhỉ?</t>
+          <t>Tao nhớ có lẽ là một buổi chiều tháng trước, khi tao đang kiểm hàng ở kho. Tao cúi xuống thì thấy một bông hoa đen lạ hoắc, chưa bao giờ thấy. Vừa định nhặt lên thì bỗng dưng nó biến thành sương khói và biến mất với tiếng "bụp". Tao có ảo giác không nhỉ?</t>
         </is>
       </c>
     </row>
@@ -12028,8 +12023,8 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Cảm ơn quý khách đã chọn đường cao tốc. Tuyến đường này kết nối trực tiếp giữa Port Gunchao, Mỏ Hổ Nham và Thành phố KU-Roro B. Vui lòng xác nhận điểm đến của quý khách. Lưu ý: Có thể xuất hiện kẻ lưu đày và Discord quanh khu vực này. Hãy cảnh giác và lái xe an toàn khi vận chuyển hàng hóa. (UI Updates: Những ai cố tình phá hoại hoặc làm hư hại cơ sở hạ tầng đường cao tốc sẽ bị truy tố!)
-Bảo trì định kỳ: Đội Bảy, Bộ Play triển</t>
+          <t>Cảm ơn quý khách đã chọn đường cao tốc. Tuyến đường này kết nối trực tiếp giữa Cảng Gunchao, Mỏ Hổ Nham và Thành phố Jinzhou. Vui lòng xác nhận điểm đến của quý khách. Lưu ý: Có thể xuất hiện kẻ lưu đày và Tacet Discord quanh khu vực này. Hãy cảnh giác và lái xe an toàn khi vận chuyển hàng hóa. (Cập nhật: Những ai cố tình phá hoại hoặc làm hư hại cơ sở hạ tầng đường cao tốc sẽ bị truy tố!)
+Bảo trì định kỳ: Đội Bảy, Bộ Phát triển</t>
         </is>
       </c>
     </row>
@@ -12094,7 +12089,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Mẫu đơn yêu cầu vật tư    Người yêu cầu: Yizhu (ví dụ)   Bộ phận yêu cầu: Tuần Tra KU-Roro B (ví dụ)    Vật tư yêu cầu và số lượng: 10 đạn mồi hiện đại (ví dụ)    Lý do yêu cầu: Phát hiện nhóm Save Dân gần đường cao tốc cảng (ví dụ, tóm tắt trong 80 từ trở xuống.)    Vui lòng nộp đơn qua Terminal của bạn.    Vật tư yêu cầu sẽ được cấp trong ngày nộp đơn. Trong trường hợp khẩn cấp, hãy đến kho để xử lý nhanh.</t>
+          <t>Mẫu Đơn Yêu Cầu Vật Tư    Người yêu cầu: Yizhu (ví dụ)   Bộ phận yêu cầu: Tuần Tra Jinzhou (ví dụ)    Vật tư yêu cầu và số lượng: 10 đạn mồi hiện đại (ví dụ)    Lý do yêu cầu: Phát hiện nhóm Lưu Dân gần đường cao tốc cảng (ví dụ, tóm tắt trong 80 từ trở xuống.)    Vui lòng nộp đơn qua Thiết bị đầu cuối của bạn.    Vật tư yêu cầu sẽ được cấp trong ngày nộp đơn. Trong trường hợp khẩn cấp, hãy đến kho để xử lý nhanh.</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12157,7 @@
       <c r="M156" t="inlineStr">
         <is>
           <t>...Rèn luyện chăm chỉ. Thách thức các Tuần Tra Giả.
-...Failed là mẹ thành công.
+...Thất bại là mẹ thành công.
 ...Rèn luyện sức bền. Nâng cao kỹ năng!</t>
         </is>
       </c>
@@ -12228,7 +12223,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>"Ghi chép Điều tra Hiện trường Tàn tích CSC - Số 13" Bí ẩn về sự biến mất của CSC vẫn chưa được làm sáng tỏ sau cuộc tái điều tra địa điểm. Tài liệu về khu vực, lời khai của cư dân xung quanh, và kho lưu trữ của Huaxu Academy... Tất cả gộp lại vẫn rất ít ỏi. Có người nói CSC phải trả giá cho sự ngạo mạn của mình, kẻ khác lại bảo CSC đã mở đường cho tương lai nhân loại. Nhưng rốt cuộc, viện nghiên cứu tiên tiến nhất thời đó đã muốn đạt được điều gì khi để lại những cơ sở bí ẩn này khắp KU-Roro B? (None ý xúc phạm! Cá nhân tôi cho rằng việc CSC để lại thiết bị khắp nơi không hề thân thiện với môi trường. Tôi chỉ lên án họ từ góc nhìn riêng của mình thôi.)</t>
+          <t>"Ghi chép Điều tra Hiện trường Tàn tích CSC - Số 13" Bí ẩn về sự biến mất của CSC vẫn chưa được làm sáng tỏ sau cuộc tái điều tra địa điểm. Tài liệu về khu vực, lời khai của cư dân xung quanh, và kho lưu trữ của Học viện Huaxu... Tất cả gộp lại vẫn rất ít ỏi. Có người nói CSC phải trả giá cho sự ngạo mạn của mình, kẻ khác lại bảo CSC đã mở đường cho tương lai nhân loại. Nhưng rốt cuộc, viện nghiên cứu tiên tiến nhất thời đó đã muốn đạt được điều gì khi để lại những cơ sở bí ẩn này khắp Jinzhou? (Không có ý xúc phạm! Cá nhân tôi cho rằng việc CSC để lại thiết bị khắp nơi không hề thân thiện với môi trường. Tôi chỉ lên án họ từ góc nhìn riêng của mình thôi.)</t>
         </is>
       </c>
     </row>
@@ -12296,10 +12291,10 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Danh hiệu: Tìm Kiếm Thiếu Nữ Bí Ẩn Với Round Jade!
+          <t>Danh hiệu: Tìm Kiếm Thiếu Nữ Bí Ẩn Với Vòng Jade!
 u/MaidenS8vedMyL1fe
 Bọn Lưu Đày như bầy sói đói rình rập các tuyến vận tải, và chúng tàn nhẫn lắm đấy!
-Đội của tôi bị phục kích, may mà có một Thiếu Nữ tóc đỏ xuất hiện giải cứu. Tôi mãi biết ơn cô ấy và muốn tìm lại. Malee cô ấy hình như là "Jin" thì phải? Có ai biết tên thật hay cách liên lạc qua mạng Lollo không? Tôi muốn đích thân cảm ơn cô ấy!</t>
+Đội của tôi bị phục kích, may mà có một Thiếu Nữ tóc đỏ xuất hiện giải cứu. Tôi mãi biết ơn cô ấy và muốn tìm lại. Tên cô ấy hình như là "Jin" thì phải? Có ai biết tên thật hay cách liên lạc qua mạng Lollo không? Tôi muốn đích thân cảm ơn cô ấy!</t>
         </is>
       </c>
     </row>
@@ -12436,10 +12431,10 @@
         <is>
           <t>Độ cứng: 6
 Mật độ: 3.0-3.5 g/cm³
-Intensity Dodgen: 3000-5000 kg/cm²
-Templates vật này được gọi là Đá Moire, đặc trưng bởi cấu trúc tinh xảo, độ cứng cao và khả năng chịu Dodgen mạnh mẽ. Nó có tính ổn định hóa học tuyệt vời và chịu được sự biến đổi nhiệt độ khắc nghiệt.
+Cường độ nén: 3000-5000 kg/cm²
+Mẫu vật này được gọi là Đá Moire, đặc trưng bởi cấu trúc tinh xảo, độ cứng cao và khả năng chịu nén mạnh mẽ. Nó có tính ổn định hóa học tuyệt vời và chịu được sự biến đổi nhiệt độ khắc nghiệt.
 Đá Moire phân bố rộng rãi tại Gorges of Spirits, hình thành các mỏ quy mô lớn dễ khai thác. Có thể dễ dàng khai thác được những khối đá kích thước lớn. Những yếu tố này khiến Đá Moire trở thành vật liệu xây dựng lý tưởng cho các tác phẩm điêu khắc quy mô lớn, tường ngoài công trình và lát nền cứng.
-&lt;i&gt;Ghi chú: Được sử dụng trong xây dựng KU-Roro B và tạo tác pho tượng Sentinel.&lt;/i&gt;</t>
+&lt;i&gt;Ghi chú: Được sử dụng trong xây dựng Jinzhou và tạo tác pho tượng Sentinel.&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12500,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Tổng Guan Công Việc: Giai đoạn đầu lập bản đồ phân bố Đơn vị Exploration đã hoàn thành, cho phép xác định sơ bộ hướng xây dựng tuyến đường mới dẫn vào nội địa Huanglong. Trong quá trình thu thập dữ liệu hình ảnh, đội khảo sát đã chạm trán một đợt tấn công quy mô nhỏ của Discord. Nhờ lực lượng đặc nhiệm Midnight Rangers kịp thời hỗ trợ, chỉ có hai thành viên bị thương nhẹ. Tuy nhiên, thiết bị thám hiểm chịu thiệt hại nặng nề.
+          <t>Tổng Quan Công Việc: Giai đoạn đầu lập bản đồ phân bố Đơn vị Thám Hiểm đã hoàn thành, cho phép xác định sơ bộ hướng xây dựng tuyến đường mới dẫn vào nội địa Huanglong. Trong quá trình thu thập dữ liệu hình ảnh, đội khảo sát đã chạm trán một đợt tấn công quy mô nhỏ của Tacet Discord. Nhờ lực lượng đặc nhiệm Midnight Rangers kịp thời hỗ trợ, chỉ có hai thành viên bị thương nhẹ. Tuy nhiên, thiết bị thám hiểm chịu thiệt hại nặng nề.
 &lt;i&gt;Thiết bị mới dự kiến sẽ đến trong một tuần tới. Trong thời gian này, mọi hoạt động thám hiểm sẽ tạm ngừng.&lt;/i&gt;</t>
         </is>
       </c>
@@ -12572,8 +12567,8 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Hôm nay, đội trưởng lại thảo luận với tôi. Ông ấy hy vọng, với tư cách là trụ cột kỹ thuật, tôi có thể đưa ra ý kiến quyết định liệu công tác thám hiểm có thể hoàn thành đúng tiến độ hay không. Cả ông ấy và tôi, thậm chí tất cả mọi người, đều hiểu tầm quan trọng của việc khai quật tuyến vận chuyển đường dài thứ hai. Tuyến này khởi đầu từ KU-Roro B, đi qua Gorges of Spirits để kết nối các khu vực còn lại ở Huanglong. Nó giúp KU-Roro B có thể tương tác gần gũi và thuận tiện hơn với các vùng lãnh thổ khác trong Huanglong. Nói thẳng ra, nếu một tuyến vận chuyển gặp vấn đề trong tương lai, chúng ta vẫn còn tuyến khác để dựa vào, tránh rơi vào tình thế tuyệt vọng.
-Gần đây, các báo cáo giám sát cho thấy Tacet Field có thể xuất hiện bất cứ lúc nào quanh Gorges of Spirits, nhưng chúng ta không thể dừng lại lúc này khi đã đi được đến đây. Nếu dừng lại, mọi thành quả vất vả kiếm được sẽ đổ sông đổ biển. Nhưng nếu không dừng, chúng ta có thể phải đánh đổi bằng mạng sống của các thành viên trong đội.</t>
+          <t>Hôm nay, đội trưởng lại thảo luận với tôi. Ông ấy hy vọng, với tư cách là trụ cột kỹ thuật, tôi có thể đưa ra ý kiến quyết định liệu công tác thám hiểm có thể hoàn thành đúng tiến độ hay không. Cả ông ấy và tôi, thậm chí tất cả mọi người, đều hiểu tầm quan trọng của việc khai quật tuyến vận chuyển đường dài thứ hai. Tuyến này khởi đầu từ Jinzhou, đi qua Gorges of Spirits để kết nối các khu vực còn lại ở Huanglong. Nó giúp Jinzhou có thể tương tác gần gũi và thuận tiện hơn với các vùng lãnh thổ khác trong Huanglong. Nói thẳng ra, nếu một tuyến vận chuyển gặp vấn đề trong tương lai, chúng ta vẫn còn tuyến khác để dựa vào, tránh rơi vào tình thế tuyệt vọng.
+Gần đây, các báo cáo giám sát cho thấy Tổ Tacet có thể xuất hiện bất cứ lúc nào quanh Gorges of Spirits, nhưng chúng ta không thể dừng lại lúc này khi đã đi được đến đây. Nếu dừng lại, mọi thành quả vất vả kiếm được sẽ đổ sông đổ biển. Nhưng nếu không dừng, chúng ta có thể phải đánh đổi bằng mạng sống của các thành viên trong đội.</t>
         </is>
       </c>
     </row>
@@ -12639,8 +12634,8 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Thông báo mới&lt;/b&gt;
-Do sự hội tụ gần đây của Etheric Sea và các tần số bất thường trong khu vực, việc xây dựng tuyến giao thông thứ hai tạm thời đình chỉ ngay lập tức. Tất cả thành viên của Bộ Phát Triển và Midnight Rangers phải sơ tán ngay, ngày khởi động lại chưa được xác định.</t>
+          <t>&lt;b&gt;Thông Báo Mới Nhất&lt;/b&gt;
+Do sự hội tụ gần đây của Biển Ether và các tần số bất thường trong khu vực, việc xây dựng tuyến giao thông thứ hai tạm thời đình chỉ ngay lập tức. Tất cả thành viên của Bộ Phát Triển và Midnight Rangers phải sơ tán ngay, ngày khởi động lại chưa được xác định.</t>
         </is>
       </c>
     </row>
@@ -12709,8 +12704,8 @@
       <c r="M164" t="inlineStr">
         <is>
           <t>Giao Tiếp Bị Nhiễu
-Yesterday, trong cuộc gọi video với con gái, bé không ngừng kể về việc muốn tận mắt thấy thác nước hùng vĩ và con rùa khổng lồ! Ôi, con yêu của mẹ... Mẹ đã phải thương lượng rất nhiều để bé chịu đồng ý rằng xem ảnh cũng thú vị không kém.
-Lạ thay, quanh đây chẳng thấy bóng dáng Discord nào, có lẽ vì có một con trùm đang thống trị hồ nước.
+Hôm qua, trong cuộc gọi video với con gái, bé không ngừng kể về việc muốn tận mắt thấy thác nước hùng vĩ và con rùa khổng lồ! Ôi, con yêu của mẹ... Mẹ đã phải thương lượng rất nhiều để bé chịu đồng ý rằng xem ảnh cũng thú vị không kém.
+Lạ thay, quanh đây chẳng thấy bóng dáng Tacet Discord nào, có lẽ vì có một con trùm đang thống trị hồ nước.
 Ta phải cẩn thận, đừng để làm phiền nó.</t>
         </is>
       </c>
@@ -12787,17 +12782,17 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>[Gợi Ý The Present]
+          <t>[Gợi Ý Hiện Tại]
 "Ngọn cờ phấp phới, chiến binh dũng mãnh tiến lên; ngọn giáo đơn độc xuyên qua ánh trăng tàn."
-Recall giấc mơ xưa và du hành qua thời gian, không gian. Vở diễn nhập vai &lt;i&gt;Ánh Trăng Vẫn Sáng Như Xưa&lt;/i&gt; sắp ra mắt.
+Hồi tưởng giấc mơ xưa và du hành qua thời gian, không gian. Vở diễn nhập vai &lt;i&gt;Ánh Trăng Vẫn Sáng Như Xưa&lt;/i&gt; sắp ra mắt.
 "Ngọn lửa ta phóng ra sẽ thiêu rụi mọi dấu vết của cái ác, chỉ để lại tro tàn."
-Re bản kinh điển: Vở kịch anh hùng &lt;i&gt;Fiamma&lt;/i&gt;
+Tái bản kinh điển: Vở kịch anh hùng &lt;i&gt;Fiamma&lt;/i&gt;
 [Nội Quy Khán Giả Rạp Hát]
-1. Nhà hát KU-Roro B là không gian mở. Vui lòng giữ trật tự nơi công cộng.
+1. Nhà hát Jinzhou là không gian mở. Vui lòng giữ trật tự nơi công cộng.
 2. Vui lòng đến rạp đúng giờ và ngồi yên tại chỗ trong suốt buổi diễn. Nếu phải ra ngoài, xin đi nhẹ nhàng để không làm phiền khán giả khác.
-3. Trong suốt buổi diễn, vui lòng tắt Terminal hoặc chuyển sang chế độ rung nếu cần thiết.
-4. Ban chụp ảnh hoặc quay phim trong rạp.
-5. Ban xâm nhập sân khấu, người vi phạm sẽ bị xử lý bởi Đội Tuần Tra.
+3. Trong suốt buổi diễn, vui lòng tắt Thiết bị đầu cuối hoặc chuyển sang chế độ rung nếu cần thiết.
+4. Cấm chụp ảnh hoặc quay phim trong rạp.
+5. Cấm xâm nhập sân khấu, người vi phạm sẽ bị xử lý bởi Đội Tuần Tra.
 6. Sau buổi diễn, vui lòng mang rác của bạn theo.</t>
         </is>
       </c>
@@ -12869,9 +12864,9 @@
         <is>
           <t>"Hoa tự nhiên, dấu thời gian. Một tiểu cảnh nhỏ, ôm trọn mái nhà."
 [Chủ đề Penjing theo mùa: Trăng]
-Suggestion Một: Tạo một penjing với chủ đề "Biển Đom Đóm và Vầng Trăng";
-Suggestion Hai: Tạo một penjing với chủ đề "Thiên Sugar Đào ở Trung Nguyên và Vầng Trăng";
-Suggestion Ba: Tạo một penjing với chủ đề "Dragon Không Vuốt".</t>
+Gợi ý Một: Tạo một penjing với chủ đề "Biển Đom Đóm và Vầng Trăng";
+Gợi ý Hai: Tạo một penjing với chủ đề "Thiên Đường Đào ở Trung Nguyên và Vầng Trăng";
+Gợi ý Ba: Tạo một penjing với chủ đề "Rồng Không Vuốt".</t>
         </is>
       </c>
     </row>
@@ -13010,8 +13005,8 @@
       <c r="M168" t="inlineStr">
         <is>
           <t>Ngày: 31 tháng 12, AL 159
-Report Giver: Huaijin
-Phối hợp với Huaxu Academy, Bộ Play triển đã ban hành ấn bản mới nhất của &lt;i&gt;Cẩm nang Shipping An toàn Năng lượng&lt;/i&gt;.
+Người báo cáo: Huaijin
+Phối hợp với Học viện Huaxu, Bộ Phát triển đã ban hành ấn bản mới nhất của &lt;i&gt;Cẩm nang Vận chuyển An toàn Năng lượng&lt;/i&gt;.
 Nhận thức được tầm quan trọng của việc nắm vững toàn diện, tổ trưởng giao tôi nghiên cứu sơ bộ, nhấn mạnh việc đào tạo sau này cho các thợ mỏ đồng nghiệp. Ngoài ra, tôi đang biên soạn các phân tích trường hợp tai nạn để củng cố ý thức an toàn chung.
 Để giúp đồng nghiệp dễ hiểu hơn, tôi tự nguyện tóm lược và làm nổi bật các điểm chính cho cả đội.</t>
         </is>
@@ -13081,8 +13076,8 @@
       <c r="M169" t="inlineStr">
         <is>
           <t>Dù bóng tối có nuốt chửng dấu chân ta, lòng dũng cảm không ngừng khám phá những điều chưa biết sẽ dẫn lối chúng ta đến chân trời xa xăm. Tưởng nhớ những chiến binh dũng cảm đã tự nguyện hy sinh trong đêm trường vĩnh cửu.
-[Lịch sử Knell Square]
-Knell Square được xây dựng để tưởng nhớ những chiến binh đã hy sinh bản thân vì nền văn minh nhân loại. Mỗi đóa hoa nơi đây đều được các thành viên Midnight Rangers chăm sóc tỉ mỉ, và chúng được gọi là "Emortia".</t>
+[Lịch sử Quảng trường Knell]
+Quảng trường Knell được xây dựng để tưởng nhớ những chiến binh đã hy sinh bản thân vì nền văn minh nhân loại. Mỗi đóa hoa nơi đây đều được các thành viên Midnight Rangers chăm sóc tỉ mỉ, và chúng được gọi là "Emortia".</t>
         </is>
       </c>
     </row>
@@ -13150,10 +13145,10 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Kangjian: Mỗi viên gạch dưới chân cậu đều khắc tên những người lính đã ngã xuống.
-Yao Văn, Toại Nguyên, Mãn Chi, Kỳ Hà, Minh Khắc...
-Kangjian: Nếu cậu muốn biết về câu chuyện của họ, cứ hỏi tôi nhé.
-Kangjian: Tôi sẵn lòng kể cho cậu nghe về từng cái tên ấy.</t>
+          <t>Khang Kiện: Mỗi viên gạch dưới chân cậu đều khắc tên những người lính đã ngã xuống.
+Dao Văn, Toại Nguyên, Mãn Chi, Kỳ Hà, Minh Khắc...
+Khang Kiện: Nếu cậu muốn biết về câu chuyện của họ, cứ hỏi tôi nhé.
+Khang Kiện: Tôi sẵn lòng kể cho cậu nghe về từng cái tên ấy.</t>
         </is>
       </c>
     </row>
@@ -13224,11 +13219,11 @@
       <c r="M171" t="inlineStr">
         <is>
           <t>["Mùa Này Đặc Sắc"]
-Tea Xuân được tuyển chọn kỹ lưỡng, kết hợp cùng "Sương Mai Đỉnh Sen" nổi tiếng với công dụng làm dịu và thư giãn. Invite quý khách vào thưởng thức.
-[Save Ý]
-Những chú mèo và chó đáng yêu bên ngoài quán không chỉ là khách viếng thăm; chúng là thành viên thân yêu của gia đình quán trà Save Hiền. Quý khách được mời âu yếm và đối xử tử tế với chúng. Với những ai nhạy cảm với lông thú, chúng tôi khuyên nên lên sân thượng tầng hai, nơi có thể ngắm nhìn toàn cảnh Tấn Châu tuyệt đẹp và tận hưởng không khí sôi động của thành phố.
+Trà Xuân được tuyển chọn kỹ lưỡng, kết hợp cùng "Sương Mai Đỉnh Sen" nổi tiếng với công dụng làm dịu và thư giãn. Mời quý khách vào thưởng thức.
+[Lưu Ý]
+Những chú mèo và chó đáng yêu bên ngoài quán không chỉ là khách viếng thăm; chúng là thành viên thân yêu của gia đình quán trà Lưu Hiền. Quý khách được mời âu yếm và đối xử tử tế với chúng. Với những ai nhạy cảm với lông thú, chúng tôi khuyên nên lên sân thượng tầng hai, nơi có thể ngắm nhìn toàn cảnh Tấn Châu tuyệt đẹp và tận hưởng không khí sôi động của thành phố.
 [Tuyển Dụng]
-Refreshment Tea và trà kết nối tâm hồn. Quán trà Save Hiền đang tuyển dụng những người đam mê trà để gia nhập đội ngũ, mức lương thương lượng.</t>
+Trà giải khát và trà kết nối tâm hồn. Quán trà Lưu Hiền đang tuyển dụng những người đam mê trà để gia nhập đội ngũ, mức lương thương lượng.</t>
         </is>
       </c>
     </row>
@@ -13299,13 +13294,14 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>&lt;Audience Review: ★★★★★&gt;
+          <t xml:space="preserve">&lt;Audience Review: ★★★★★&gt;
 Tôi đã khóc hết nước mắt!
-&lt;i&gt;Moonlight Shines as Ever&lt;/i&gt; quả là một vở kịch xé lòng! Thật sự tuyệt vời cho biên kịch tài ba đã tạo nên một câu chuyện đau lòng đến thế. Nước mắt tôi cứ tuôn rơi không ngừng ngay cả sau khi vở kịch kết thúc!
-Phản hồi từ nhà hát: Vở kịch Anh Hùng này dựa trên những sự kiện lịch sử có thật. Cảm ơn bạn đã chia sẻ cảm nhận của mình.
+&lt;i&gt;Ánh Trăng Vẫn Sáng&lt;/i&gt; đúng là một vở kịch xé lòng! Thật sự ngả mũ trước biên kịch tài ba đã tạo nên câu chuyện đầy cảm xúc đến thế. Nước mắt tôi cứ tuôn mãi ngay cả khi vở kịch đã kết thúc!
+Phản hồi từ Nhà hát: Vở Anh Hùng Kịch này dựa trên sự kiện lịch sử có thật. Cảm ơn bạn đã chia sẻ trải nghiệm của mình.
 &lt;Audience Review: ★★★★☆&gt;
-&lt;i&gt;Fiamma&lt;/i&gt; thực sự đã kích thích vị giác của tôi! Lần tới tôi dự định mang theo chút Victor Savor tự làm của dì để thưởng thức trong lúc xem. Háo hức quá!
-Phản hồi từ nhà hát: Cảm ơn bình luận của bạn. Bạn có thể mang theo đồ ăn nhẹ của riêng mình, nhưng xin hãy lưu ý đến mùi hương nồng.</t>
+&lt;i&gt;Fiamma&lt;/i&gt; khiến tôi thèm thuồng quá! Lần sau chắc chắn phải mang theo món Victor Savor tự làm của dì đến thưởng thức trong lúc xem. Háo hức quá đi!
+Phản hồi từ Nhà hát: Cảm ơn nhận xét của bạn. Bạn có thể mang đồ ăn nhẹ của riêng mình, nhưng xin lưu ý tránh những mùi quá nồng.
+</t>
         </is>
       </c>
     </row>
@@ -13376,10 +13372,10 @@
       <c r="M173" t="inlineStr">
         <is>
           <t>Sau khi vở kịch &lt;i&gt;Fiamma&lt;/i&gt; kết thúc lúc 9 giờ tối hai đêm trước, một số khán giả đã tìm thấy đồ thất lạc trong rạp và nhanh chóng báo cáo. Danh sách đồ vật như sau:
-Khuyên tai xanh: Hàng 5, Chair 9, số lượng: 1
-Thẻ nhân viên Bộ Play triển: Hàng 6, Chair 9, số lượng: 1
-Phiếu đổi bánh Loong (có hoa văn rồng đặc biệt): Hàng 8, Chair 10, số lượng: 2
-Băng đô thủ công (đỏ và xanh, tết một phần): Hàng 16, Chair 11, số lượng: 1
+Khuyên tai xanh: Hàng 5, Ghế 9, số lượng: 1
+Thẻ nhân viên Bộ Phát triển: Hàng 6, Ghế 9, số lượng: 1
+Phiếu đổi bánh Loong (có hoa văn rồng đặc biệt): Hàng 8, Ghế 10, số lượng: 2
+Băng đô thủ công (đỏ và xanh, tết một phần): Hàng 16, Ghế 11, số lượng: 1
 Chủ nhân của các món đồ trên vui lòng đến nhận trong vòng 10 ngày kể từ ngày thông báo này.</t>
         </is>
       </c>
@@ -13451,13 +13447,13 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Vận Switch Nội Địa (Trong Huanglong)
+          <t>Vận Chuyển Nội Địa (Trong Huanglong)
 Sáu Tỉnh: Khối lượng đầu 80 SHC, khối lượng thêm 20 SHC;
 Thủ Đô: Khối lượng đầu 100 SHC, khối lượng thêm 25 SHC;
-Các Zone Vực Khác: Giá cước thay đổi tùy theo tính chất hàng hóa và rủi ro cụ thể. Để biết thông tin chi tiết, vui lòng liên hệ nhân viên giao hàng.
-Vận Switch Guo Tế
-New Federation: Khối lượng đầu 300 SHC, khối lượng thêm 60 SHC;
-Các Guo Gia &amp; Zone Vực Khác: Giá cước thay đổi tùy theo tính chất hàng hóa và rủi ro cụ thể. Để biết thông tin chi tiết, vui lòng liên hệ nhân viên giao hàng.</t>
+Các Khu Vực Khác: Giá cước thay đổi tùy theo tính chất hàng hóa và rủi ro cụ thể. Để biết thông tin chi tiết, vui lòng liên hệ nhân viên giao hàng.
+Vận Chuyển Quốc Tế
+Liên Bang Mới: Khối lượng đầu 300 SHC, khối lượng thêm 60 SHC;
+Các Quốc Gia &amp; Khu Vực Khác: Giá cước thay đổi tùy theo tính chất hàng hóa và rủi ro cụ thể. Để biết thông tin chi tiết, vui lòng liên hệ nhân viên giao hàng.</t>
         </is>
       </c>
     </row>
@@ -13538,11 +13534,11 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Position:
+          <t>Vị trí:
 [Nhân Viên Giao Hàng Tận Nơi]
 Yêu cầu:
 Tuổi: Không giới hạn; ứng viên ở mọi độ tuổi đều được khuyến khích ứng tuyển.
-Bằng lái: Có bằng lái xe hợp lệ từ bất kỳ quốc gia nào.
+Bằng lái: Phải có bằng lái xe hợp lệ từ bất kỳ quốc gia nào.
 Trách nhiệm: Ứng viên lý tưởng sẽ tuân thủ tiêu chuẩn công ty, đảm bảo hoàn thành công việc thu gom và giao hàng hàng ngày một cách an toàn, hiệu quả và chính xác.
 Địa điểm làm việc:
 Ứng viên sẽ được phân công đến điểm phân phối gần nhất dựa trên nguyện vọng và tình trạng tuyển dụng hiện tại tại các điểm.
@@ -13627,15 +13623,14 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Lịch diễn thuyết Tuần lễ Giao lưu Học thuật Huaxu Academy:
-Malee bài giảng: Phân loại Weapons Tacet Field và Ý nghĩa trong Nghiên cứu Năng lượng: Nghiên cứu Trường hợp Weapons Huanglong
-Địa điểm: Lecture Hall Số 1
-Plays giả: Mortefi
-Tiểu sử diễn giả: Zhuyên gia về Weapons Tacet Field, chuyên viên đánh giá thuộc Department An toàn, và nhà nghiên cứu xuất sắc tại Huaxu Academy.
-Malee bài giảng: Logic Thuật toán Phân bổ Tuyến đường trong Lollo Logistics
-Địa điểm: Lecture Hall Nhiều tầng
-Plays giả: Rubert
-Tiểu sử diễn giả: Kỹ sư front-end tại Lollo Logistics và giảng viên thỉnh giảng tại Huaxu Academy.</t>
+          <t>Lịch diễn thuyết Tuần lễ Giao lưu Học thuật Học viện Huaxu: Lecture Title: Classification of Tacetite Weapon and Its Significance in Energy Studies: A Case Study of Huanglong Weaponry
+Lecture Venue: First Lecture Hall
+Speaker: Mortefi
+Speaker Bio: Expert in Tacetite Weaponary, assessment specialist in the Department of Safety, and distinguished researcher at the Huaxu Academy.
+Lecture Title: Logic of the Front-End Algorithm for Route Allocation in Lollo Logistics
+Lecture Venue: Tiered Lecture Hall
+Speaker: Rubert
+Speaker Bio: Front-end engineer at Lollo Logistics and guest lecturer at the Huaxu Academy.</t>
         </is>
       </c>
     </row>
@@ -13706,8 +13701,8 @@
         <is>
           <t>Rừng Âm U chắc chắn là kho báu quan trọng nhất toàn vùng Huanglong, sở hữu sự đa dạng loài vô song trên thế giới.
 Ngay khi đặt chân đến cổng vào, tôi đã nghe thấy rõ tiếng thực vật thì thầm và lời triệu gọi của chúng.
-Nghe nói sâu trong rừng, nơi từng là trụ sở của Department Âm Sinh Thái, vẫn lưu giữ những tư liệu hình ảnh về vô số loài thực vật, trong đó có một loài ngon lành gọi là Banana Ngà, xuất xứ từ Rừng Âm U. Banana Ngà từng là nguồn lương thực chính của Hoochief, và đổi lại, Hoochief đi tìm Banana Ngà trong rừng đã trở thành những "thợ thụ phấn" tuyệt vời.
-Kể từ khi màn sương bào tử độc lan rộng, Banana Ngà hoang dã đã biến mất khỏi Rừng Âm U, và thông tin về loài này giờ chỉ còn trong sử sách.
+Nghe nói sâu trong rừng, nơi từng là trụ sở của Cục Âm Sinh Thái, vẫn lưu giữ những tư liệu hình ảnh về vô số loài thực vật, trong đó có một loài ngon lành gọi là Chuối Ngà, xuất xứ từ Rừng Âm U. Chuối Ngà từng là nguồn lương thực chính của Hoochief, và đổi lại, Hoochief đi tìm Chuối Ngà trong rừng đã trở thành những "thợ thụ phấn" tuyệt vời.
+Kể từ khi màn sương bào tử độc lan rộng, Chuối Ngà hoang dã đã biến mất khỏi Rừng Âm U, và thông tin về loài này giờ chỉ còn trong sử sách.
 Lời Than Thở có lẽ là một quy trình đào thải tự nhiên không thể tránh khỏi.</t>
         </is>
       </c>
@@ -13921,8 +13916,8 @@
       <c r="M180" t="inlineStr">
         <is>
           <t>Lâu rồi tôi mới có một buổi tập luyện căng thẳng như thế này.
-Con Hoochief bị nhiễm độc ấy thể hiện một sự thiếu mệt mỏi đáng kinh ngạc trong cuộc truy đuổi không ngừng nghỉ con mồi của nó—mà đáng tiếc, con mồi đó lại là tôi. Tuy nhiên, khi chạy trốn, tôi không hề hoảng loạn mà đầu óc lại bắt đầu quay cuồng. Tôi biết rõ những bào tử độc hại này là hậu quả trực tiếp của Hiện tượng Waveworm. Theo tiêu chuẩn Ecoacoustics, chúng ta nên phân loại những con Hoochief bị nhiễm độc ấy như thế nào? Hơn nữa, làm thế nào những bào tử độc hại ấy lại lây nhiễm vào Discord, và liệu thiền định có phải là giải pháp khả thi cho việc nhiễm độc Discord không?
-Dùng chức năng Grapple, tôi khéo léo đu mình lên một cành cây ẩn nấp. Con Hoochief bị nhiễm độc mất dấu mục tiêu và lúng túng nhìn quanh. Nó trông như một đứa trẻ lạc lõng, rên rỉ và ho từng cơn, dường như mất đi khả năng định hướng không gian. Mỗi tiếng ho dữ dội lại phun ra một đám bào tử độc vào không khí. Những bào tử ấy, bị thúc đẩy bởi bản năng sinh tồn, càng đẩy cơ thể vốn đã suy yếu của con Hoochief đến giới hạn cuối cùng.
+Con Hoochief bị nhiễm độc ấy thể hiện một sự thiếu mệt mỏi đáng kinh ngạc trong cuộc truy đuổi không ngừng nghỉ con mồi của nó—mà đáng tiếc, con mồi đó lại là tôi. Tuy nhiên, khi chạy trốn, tôi không hề hoảng loạn mà đầu óc lại bắt đầu quay cuồng. Tôi biết rõ những bào tử độc hại này là hậu quả trực tiếp của Hiện tượng Waveworm. Theo tiêu chuẩn Ecoacoustics, chúng ta nên phân loại những con Hoochief bị nhiễm độc ấy như thế nào? Hơn nữa, làm thế nào những bào tử độc hại ấy lại lây nhiễm vào Tacet Discord, và liệu thiền định có phải là giải pháp khả thi cho việc nhiễm độc Tacet Discord không?
+Sử dụng chức năng Grapple, tôi khéo léo đu mình lên một cành cây ẩn nấp. Con Hoochief bị nhiễm độc mất dấu mục tiêu và lúng túng nhìn quanh. Nó trông như một đứa trẻ lạc lõng, rên rỉ và ho từng cơn, dường như mất đi khả năng định hướng không gian. Mỗi tiếng ho dữ dội lại phun ra một đám bào tử độc vào không khí. Những bào tử ấy, bị thúc đẩy bởi bản năng sinh tồn, càng đẩy cơ thể vốn đã suy yếu của con Hoochief đến giới hạn cuối cùng.
 Tôi bắt đầu tự hỏi: đây là một dạng đồng tiến hóa, hay chỉ là mối quan hệ ký sinh?</t>
         </is>
       </c>
@@ -13991,7 +13986,7 @@
       <c r="M181" t="inlineStr">
         <is>
           <t>Hành vi xã hội của bầy Hoochief còn đáng kinh ngạc hơn cả tưởng tượng, biến chúng thành loài thống trị ở Khu Rừng Mờ.
-Theo khảo sát của ta, sương bào tử độc liên tục tỏa ra từ Cây Đa Trung Tâm. Để tránh sự xâm lấn của những bào tử đó, bầy Hoochief phân tán thành nhiều nhóm nhỏ, tìm nơi trú ẩn an toàn và dần hình thành các cộng đồng với đặc trưng "gia trưởng". Trí thông minh mà chúng thể hiện dường như là độc nhất trong số các Discord. Ngoài ra, gần các cộng đồng Hoochief, hoạt động của các Discord khác rất hiếm gặp, ta cho rằng đây có thể là biểu hiện của "ý thức lãnh thổ". Ý thức này khiến chúng phân chia nhiệm vụ và hợp sức đẩy lùi kẻ xâm phạm.
+Theo khảo sát của ta, sương bào tử độc liên tục tỏa ra từ Cây Đa Trung Tâm. Để tránh sự xâm lấn của những bào tử đó, bầy Hoochief phân tán thành nhiều nhóm nhỏ, tìm nơi trú ẩn an toàn và dần hình thành các cộng đồng với đặc trưng "gia trưởng". Trí thông minh mà chúng thể hiện dường như là độc nhất trong số các Tacet Discord. Ngoài ra, gần các cộng đồng Hoochief, hoạt động của các Tacet Discord khác rất hiếm gặp, ta cho rằng đây có thể là biểu hiện của "ý thức lãnh thổ". Ý thức này khiến chúng phân chia nhiệm vụ và hợp sức đẩy lùi kẻ xâm phạm.
 Điều khiến ta tò mò hơn cả là phản ứng của cộng đồng nếu một con Hoochief bị nhiễm độc. Ta không khỏi tự hỏi, trong tình huống đó, chúng sẽ đưa ra quyết định như thế nào? Trên con đường thường xuyên qua lại của Feilian Beringal, ta thoáng thấy vài gò đất giống như mộ. Đáng tiếc là ta không có thời gian để khảo sát kỹ lưỡng.</t>
         </is>
       </c>
@@ -14061,8 +14056,8 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Faded Thông báo Board
-Trước khi... bắt đầu chuyến tham quan, xin vui lòng... đọc kỹ &lt;i&gt;Guide Tham Guan Khu Bảo Tồn Thiên Nhiên&lt;/i&gt;:
+          <t>Bảng Thông Báo Phai Mờ
+Trước khi... bắt đầu chuyến tham quan, xin vui lòng... đọc kỹ &lt;i&gt;Hướng Dẫn Tham Quan Khu Bảo Tồn Thiên Nhiên&lt;/i&gt;:
 Khu bảo tồn thiên nhiên... nằm phía nam con đường trưng bày. Để đảm bảo an toàn, xin đừng... vượt qua hàng rào lưới và tự ý vào bên trong... khi chưa được phép.
 Nghiêm cấm sử dụng lửa trong... kẻ vi phạm... sẽ bị truy cứu.
 Để bảo tồn tốt hơn, xin đừng... cho bầy Hoochief ăn.</t>
@@ -14134,11 +14129,11 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Faded Thông báo Board
-Grafiti của Exile: Nói thật, có ai hiểu nổi ông chủ đang nghĩ gì không? Tôi chẳng tài nào hiểu nổi sao ông lại chọn cái chỗ chết tiệt này để dừng chân.
-Grafiti của Exile: Dù nhìn có vẻ đầy đủ đồ đạc, nhưng chẳng tài nào chạm vào được! Mấy con Hoochief giữ chặt hết rồi.
-Grafiti của Exile: Hóa ra chúng nó tinh ranh hơn tôi tưởng, chẳng thể nào cướp được một cái Coriolus nào.
-Grafiti của Exile: View ra hôm nay lại đói meo thôi...</t>
+          <t>Bảng Thông Báo Phai Mờ
+Grafiti của Kẻ Lưu Đày: Seriously, can anyone clue me in on what's going through Boss's mind? I just can't wrap my head around why he chose this awful spot to settle down.
+Exile's Graffiti: Even though it looks like there's a ton of supplies here, we can't get our hands on any! Those Hoochiefs are keeping a tight grip on everything.
+Exile's Graffiti: Turns out, they're smarter than I thought, and it's impossible to snatch a Coriolus from them.
+Exile's Graffiti: Looks like it's another day of going hungry...</t>
         </is>
       </c>
     </row>
@@ -14210,14 +14205,14 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Previous mối đe dọa lan tràn của bào tử độc, hầu hết các loài sinh vật trong khu vực này đều rơi vào tình thế nguy hiểm. Ví dụ như cây Sung Dại Violuna. Một khi lượng bào tử vượt quá khả năng phòng vệ, sự nhiễm độc chỉ còn là vấn đề thời gian.
+          <t>Trước mối đe dọa lan tràn của bào tử độc, hầu hết các loài sinh vật trong khu vực này đều rơi vào tình thế nguy hiểm. Ví dụ như cây Sung Dại Violuna. Một khi lượng bào tử vượt quá khả năng phòng vệ, sự nhiễm độc chỉ còn là vấn đề thời gian.
 Báo Feilian Beringal không chịu rời khỏi khu rừng và cứ quanh quẩn gần cây Sung Trung Tâm. Dù chưa có triệu chứng ký sinh rõ ràng, việc tiếp xúc lâu dài với nồng độ bào tử độc cao rõ ràng đã ảnh hưởng đến tinh thần của nó.
 Hơn nữa, tôi đã phát hiện ra những gò đất giống như mộ kia thực chất là gì. Có vẻ như Báo Feilian Beringal sẽ (tiếng nhiễu) những đồng loại bị nhiễm độc, chôn chúng dưới gốc cây Sung Trung Tâm.
-Recorder: Nghe nói cây Sung Trung Tâm từng là ngôi nhà đầu tiên của tộc Hoochief. Ngoài ra...
+Người ghi chép: Nghe nói cây Sung Trung Tâm từng là ngôi nhà đầu tiên của tộc Hoochief. Ngoài ra...
 [Tiếng lẩm bẩm của Hoochief]
-Recorder: Này! Đừng có ăn cái đó!
+Người ghi chép: Này! Đừng có ăn cái đó!
 [Tiếng chế giễu của Hoochief]
-Recorder: Đừng! Trả lại cho tôi! (Sounds dần nhỏ đi)</t>
+Người ghi chép: Đừng! Trả lại cho tôi! (Âm thanh dần nhỏ đi)</t>
         </is>
       </c>
     </row>
@@ -14286,11 +14281,11 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Người Phỏng Vấn: Hello, tôi là phóng viên của Pioneer Association. Tôi có thể phỏng vấn anh không?
-Người Phỏng Vấn: Tại sao anh nghĩ nơi này được gọi là "Tiger's Maw"?
+          <t>Người Phỏng Vấn: Xin chào, tôi là phóng viên của Hiệp Hội Tiên Phong. Tôi có thể phỏng vấn anh không?
+Người Phỏng Vấn: Tại sao anh nghĩ nơi này được gọi là "Hàm Hổ"?
 Thợ Mỏ Lão Thành: Haha. Chúng tôi làm việc ở đây và nuôi sống những cái miệng đói, giống như hổ tự kiếm ăn vậy. Đó là lý do.
 Đứa Trẻ: Không phải đâu! Rõ ràng là vì cái hố khổng lồ này trông giống cái miệng há hốc của hổ!
-Du Othersh: Có lẽ nó liên quan đến điệu múa Hổ ở KU-Roro B? Ồ? Thì ra là múa Sư Tử à? (Tiếng cười của mọi người)</t>
+Du Khách: Có lẽ nó liên quan đến điệu múa Hổ ở Jinzhou? Ồ? Thì ra là múa Sư Tử à? (Tiếng cười của mọi người)</t>
         </is>
       </c>
     </row>
@@ -14360,12 +14355,12 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Mọi người nghe đây. Cuộc Examine Định Kỳ hàng năm cho các xe tải vận chuyển mỏ sắp bắt đầu. Khi đi kiểm tra, hãy mang theo giấy phép lái xe. Giấy phép phải còn hiệu lực.
+          <t>Mọi người nghe đây. Cuộc Kiểm Tra Định Kỳ hàng năm cho các xe tải vận chuyển mỏ sắp bắt đầu. Khi đi kiểm tra, hãy mang theo giấy phép lái xe. Giấy phép phải còn hiệu lực.
 Bất kỳ ai có giấy phép hết hạn sẽ bị coi là nhân viên không có chứng chỉ. Các bạn sẽ bị từ chối quyền điều khiển phương tiện, dù có kinh nghiệm lái xe đến đâu.
 Cuộc kiểm tra sẽ diễn ra từ cuối tháng này đến giữa tháng sau. Mang theo giấy tờ tùy thân và nộp đơn đăng ký tại Bộ Phát Triển. Thời gian thi sẽ được công bố vào dịp khác.
 Hãy đọc kỹ các tài liệu đính kèm trước khi đi và chuẩn bị sẵn sàng. Các bạn sẽ phải cảm ơn tôi đấy.
-Tài liệu đính kèm: 1) &lt;i&gt;Thông tin chi tiết về Examine Định Kỳ Xe Tải Vận Switch tại Mỏ&lt;/i&gt;
-2) &lt;i&gt;Tiêu Chuẩn Basic Review Skills Lái Xe&lt;/i&gt;</t>
+Tài liệu đính kèm: 1) &lt;i&gt;Thông tin chi tiết về Kiểm Tra Định Kỳ Xe Tải Vận Chuyển tại Mỏ&lt;/i&gt;
+2) &lt;i&gt;Tiêu Chuẩn Cơ Bản Đánh Giá Kỹ Năng Lái Xe&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -14437,14 +14432,14 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Những đoạn quan trọng trong &lt;i&gt;Regulation An Toàn Khi Vận hành Tại Mỏ Hổ Hàm&lt;/i&gt;, được một thợ mỏ đánh dấu:
+          <t>Những đoạn quan trọng trong &lt;i&gt;Quy Định An Toàn Khi Thao Tác Tại Mỏ Hổ Hàm&lt;/i&gt;, được một thợ mỏ đánh dấu:
 43) Đơn vị hành động tối thiểu là một nhóm hai người, và phải mang theo máy đo decibel khi làm việc.
 44) Khi nghe thấy tiếng kêu cứu hoặc gọi, bạn phải phối hợp với đồng nghiệp xác định hướng âm thanh và quan sát sự thay đổi trên máy đo decibel trước khi quyết định hành động tiếp theo.
 *Nếu có thay đổi, đọc Điều 45; nếu không, chuyển đến Điều 78 và 79 trong "Phần Khẩn Cấp".
-45) Nếu phát hiện sự thay đổi rõ rệt trên máy đo decibel, hãy báo cáo với Trạm Control qua Terminal. Sau khi được phê duyệt, tiến hành cứu hộ.
+45) Nếu phát hiện sự thay đổi rõ rệt trên máy đo decibel, hãy báo cáo với Trạm Điều Khiển qua Thiết bị đầu cuối. Sau khi được phê duyệt, tiến hành cứu hộ.
 ...
-78) Nếu máy đo decibel không có thay đổi, HÃY CHUYỂN NGAY Terminal sang chế độ dẫn đường khẩn cấp (hiệu lực khi đèn thiết bị chuyển sang đỏ và nhấp nháy 3 lần). DỪNG mọi hoạt động và sơ tán khỏi hiện trường theo hướng dẫn. KHÔNG ĐƯỢC CỞI DÂY AN TOÀN nối giữa bạn và đồng nghiệp.
-79) Đội khẩn cấp sẽ hướng dẫn bạn đến phòng y tế của mỏ ở phía nam Tower Lọc. Phòng y tế sẽ tiến hành kiểm tra cần thiết cho bạn.</t>
+78) Nếu máy đo decibel không có thay đổi, HÃY CHUYỂN NGAY Thiết bị đầu cuối sang chế độ dẫn đường khẩn cấp (hiệu lực khi đèn thiết bị chuyển sang đỏ và nhấp nháy 3 lần). DỪNG mọi hoạt động và sơ tán khỏi hiện trường theo hướng dẫn. KHÔNG ĐƯỢC CỞI DÂY AN TOÀN nối giữa bạn và đồng nghiệp.
+79) Đội khẩn cấp sẽ hướng dẫn bạn đến phòng y tế của mỏ ở phía nam Tháp Lọc. Phòng y tế sẽ tiến hành kiểm tra cần thiết cho bạn.</t>
         </is>
       </c>
     </row>
@@ -14512,10 +14507,10 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Gần đây, "Discord tiềm ẩn" có những hoạt động bất thường. Nhiều vụ thợ mỏ mất tích đã xảy ra và đang được điều tra.
-Các ngươi được khuyến cáo tuân thủ nghiêm &lt;i&gt;Regulation An Toàn Khi Do Việc Tại Mỏ Hổ Nham&lt;/i&gt; để đảm bảo an toàn cho bản thân và mọi người xung quanh.
+          <t>Gần đây, "Tacet Discord tiềm ẩn" có những hoạt động bất thường. Nhiều vụ thợ mỏ mất tích đã xảy ra và đang được điều tra.
+Các ngươi được khuyến cáo tuân thủ nghiêm &lt;i&gt;Quy Định An Toàn Khi Làm Việc Tại Mỏ Hổ Nham&lt;/i&gt; để đảm bảo an toàn cho bản thân và mọi người xung quanh.
 An toàn là trên hết. Không được đi theo bất kỳ tiếng kêu cứu không rõ nguồn gốc nào.
-Đội Tuần Tra Night đã cử người đi điều tra. Nguyên nhân của những bất thường này sẽ sớm được làm rõ.</t>
+Đội Tuần Tra Đêm đã cử người đi điều tra. Nguyên nhân của những bất thường này sẽ sớm được làm rõ.</t>
         </is>
       </c>
     </row>
@@ -14654,8 +14649,8 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Chisu đã giao balo cho ta, và ta biết cậu ấy chuẩn bị cho một cuộc giải cứu đầy rủi ro. Ta sợ đến mức tim đập thình thịch, sợ rằng cậu ấy có thể không trở về, và còn sợ hơn nữa là cậu ấy sẽ trở về... nhưng không còn là chính mình nữa. Weapons Tacetite không bao giờ được dùng để chống lại đồng đội.
-Đặc biệt là thứ cậu ấy để lại cho ta.</t>
+          <t>Chisu đã giao balo cho tao, và tao biết cậu ấy chuẩn bị cho một cuộc giải cứu đầy rủi ro. Tao sợ đến mức tim đập thình thịch, sợ rằng cậu ấy có thể không trở về, và còn sợ hơn nữa là cậu ấy sẽ trở về... nhưng không còn là chính mình nữa. Vũ khí Tacetite không bao giờ được dùng để chống lại đồng đội.
+Đặc biệt là thứ cậu ấy để lại cho tao.</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14719,7 @@
         <is>
           <t>Hmm... Giọng đó... giống Chisu thật. Cậu ấy nói rất bình tĩnh, y như lúc nào cũng an ủi ta, "Không sao đâu"... 
 Tâm trạng ta bất ngờ lắng dịu theo giọng nói ấy, nhưng đôi tay lại run rẩy không ngừng.
-Clock đo decibel vẫn không hề nhúc nhích. Ta biết đó không phải cậu ấy. Chỉ là trò lừa bịp rẻ tiền của TD thôi.</t>
+Đồng hồ đo decibel vẫn không hề nhúc nhích. Ta biết đó không phải cậu ấy. Chỉ là trò lừa bịp rẻ tiền của TD thôi.</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14788,7 @@
         <is>
           <t>Mẹ của Jack hỏi cậu bé muốn làm nghề gì. Jack bảo muốn làm thợ mỏ.
 Mẹ không hiểu vì Jack đâu phải đứa chăm chỉ. Jack nói: "Con làm thợ mỏ thì mọi thứ đều là 'của con' ấy ạ."
-Uncle thích chữ nhỏ: Đúng là giỏi. Nhưng cẩn thận lũ "rít" dưới lòng đất nhé.</t>
+Chú thích chữ nhỏ: Đúng là giỏi. Nhưng cẩn thận lũ "rít" dưới lòng đất nhé.</t>
         </is>
       </c>
     </row>
@@ -14878,11 +14873,11 @@
 Jing: Tớ cũng không biết. Để tớ kiểm tra bằng Forte thích ứng bảo vệ ban đêm của mình.
 Jing: Chắc chắn có gì đó không ổn...
 Tan: Sao thế?
-Jing: None ai trong thang máy. Tớ kiểm tra các sàn ở các tầng rồi. Không ai đứng đợi cả... Tớ phải tự mình đi xem.
-Tan: Eee ê. Đừng có mà lao vào trước. Nếu đây là phim, thứ đang đợi cậu ngoài kia chắc chắn không phải thứ cậu nghĩ đâu.
-Jing: Không phải đâu. Giờ tớ làm việc này, tớ còn phải lo nhiều hơn cả mạng sống của mình. Mà cậu cũng nên tỉnh táo đi. Không phải cậu tự hào là thế hệ mới của KU-Roro B sao? Sao lại tin vào những thứ này hơn mấy ông già vậy?
+Jing: Không có ai trong thang máy. Tớ kiểm tra các sàn ở các tầng rồi. Không ai đứng đợi cả... Tớ phải tự mình đi xem.
+Tan: Ê ê ê. Đừng có mà lao vào trước. Nếu đây là phim, thứ đang đợi cậu ngoài kia chắc chắn không phải thứ cậu nghĩ đâu.
+Jing: Không phải đâu. Giờ tớ làm việc này, tớ còn phải lo nhiều hơn cả mạng sống của mình. Mà cậu cũng nên tỉnh táo đi. Không phải cậu tự hào là thế hệ mới của Jinzhou sao? Sao lại tin vào những thứ này hơn mấy ông già vậy?
 Jing: Hay là máy móc trục trặc, hoặc mấy đồng nghiệp nghịch ngợm? Công việc ở đây chán quá, biết đâu họ muốn "chơi khăm" tớ một chút?
-Tan: Sentinel phù hộ cho cậu. Unclec may mắn nhé.</t>
+Tan: Sentinel phù hộ cho cậu. Chúc may mắn nhé.</t>
         </is>
       </c>
     </row>
@@ -14954,14 +14949,14 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Tên: Thang máy chở khách/hàng
-Số hiệu HLHk-09
-Được sử dụng bởi: Bộ phận Vận tải, Mỏ Hổ Hàm
-Mô tả sự cố: Dây cáp thép mòn và đứt với tần suất bất thường. Khung đỡ cabin bị yếu đi. Thang máy ngừng hoạt động.
-Biện pháp đã thực hiện: Thay dây cáp mới.
-Nguyên nhân nghi ngờ: Test bánh kéo, bánh dẫn hướng và bộ điều tốc. Không phát hiện vấn đề gì. Nghi ngờ do vận hành sai quy cách.
-Được đề xuất: Nếu bắt được đứa nào lại chất quá tải, ta sẽ trói nó vào dây cáp cho nhớ đời!
-Người xử lý: Cheng</t>
+          <t>Tên: Passenger/Freight Elevator
+Number HLHk-09
+Used by: Transport, Tiger's Maw Mine
+Issue Description: Steel wires wear out and fracture on an abnormally increased regularity. The support of the car on the frame is weakened. The elevator is out of function.
+Steps taken: Replaced the wires.
+Suspected Cause: Checked the traction wheel, the guide wheel and the speed governor. Found no issues. Improper operation suspected.
+Suggestion: If I catch anyone stacking too much cargo and going overload again, I'll tie him to the wire and make him remember!
+Handled by: Cheng</t>
         </is>
       </c>
     </row>
@@ -15175,11 +15170,11 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Synergy Giả
-Weapons Tacetite
-Weapons Tacetite đối phó với Discord như thế nào
-Synergy Giả khai thác Tacetite
-Cách trở thành Synergy Giả
+          <t>Resonator
+Vũ khí Tacetite
+Vũ khí Tacetite đối phó với Tacet Discord như thế nào
+Resonator khai thác Tacetite
+Cách trở thành Resonator
 Giá trị Tacetite
 ...</t>
         </is>
@@ -15251,10 +15246,10 @@
       <c r="M198" t="inlineStr">
         <is>
           <t>Ai nói âm nhạc phải do nhạc cụ tạo ra chứ?
-Hồi còn làm việc trong mỏ, ta luôn nghe thấy những âm thanh kỳ lạ. Lúc đầu, ta tưởng đó là "âm thanh" huyền bí mà mọi người đồn đại… Nhưng sau này, ta phát hiện ra rằng những âm thanh kỳ lạ ấy thực ra phát ra từ chính các khoáng vật, và điều đáng kinh ngạc hơn là chúng tạo thành một giai điệu độc đáo!
+Hồi còn làm việc trong mỏ, tao luôn nghe thấy những âm thanh kỳ lạ. Lúc đầu, tao tưởng đó là "âm thanh" huyền bí mà mọi người đồn đại… Nhưng sau này, tao phát hiện ra rằng những âm thanh kỳ lạ ấy thực ra phát ra từ chính các khoáng vật, và điều đáng kinh ngạc hơn là chúng tạo thành một giai điệu độc đáo!
 Hình dáng và chất lượng của Tacetite khi được cắt gọt sẽ quyết định giai điệu ấy ra sao.
-Ta đã sắp xếp lại những bản ghi âm suốt bao năm và biên soạn thành một bản nhạc, giờ được gọi là "Song Đá".
-Dạo này ta không còn khỏe như trước… Nhưng may mắn thay, Đài Play thanh Pioneer Association đã nhận được bản gốc của "Song Đá". Wishing của ta đã thành hiện thực!</t>
+Tao đã sắp xếp lại những bản ghi âm suốt bao năm và biên soạn thành một bản nhạc, giờ được gọi là "Khúc Ca Đá".
+Dạo này tao không còn khỏe như trước… Nhưng may mắn thay, Đài Phát thanh Hiệp hội Pioneer đã nhận được bản gốc của "Khúc Ca Đá". Ước nguyện của tao đã thành hiện thực!</t>
         </is>
       </c>
     </row>
@@ -15321,8 +15316,8 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Gửi toàn thể dân làng và nhân viên trú đóng tại Zone Vực Investigate:
-Đã có báo cáo về tình trạng tần số bất thường gần khu vực làng (bao gồm Zone Investigate Số 9). Huaxu Academy dự đoán sự tích tụ của Etheric Sea và xác suất cao xuất hiện Tacet Field tại những khu vực này. Để đảm bảo an toàn tính mạng và tài sản của các người, hãy chuẩn bị sơ tán ngay lập tức khi nhận được thông báo này. Chỉ mang theo những vật dụng thiết yếu. Đội Kỵ Binh Night sẽ được điều động hỗ trợ sơ tán. NHẮC LẠI. CHỈ MANG THEO VẬT DỤNG THIẾT YẾU. SƠ TÁN NGAY LẬP TỨC!
+          <t>Gửi toàn thể dân làng và nhân viên trú đóng tại Khu Vực Điều Tra:
+Đã có báo cáo về tình trạng tần số bất thường gần khu vực làng (bao gồm Khu Điều Tra Số 9). Học Viện Huaxu dự đoán sự tích tụ của Biển Ether và xác suất cao xuất hiện Tổ Tacet tại những khu vực này. Để đảm bảo an toàn tính mạng và tài sản của các người, hãy chuẩn bị sơ tán ngay lập tức khi nhận được thông báo này. Chỉ mang theo những vật dụng thiết yếu. Đội Kỵ Binh Đêm sẽ được điều động hỗ trợ sơ tán. NHẮC LẠI. CHỈ MANG THEO VẬT DỤNG THIẾT YẾU. SƠ TÁN NGAY LẬP TỨC!
 Hướng dẫn bổ sung: Tất cả nhân viên trú đóng tại khu vực điều tra phải chú ý theo dõi các cảnh báo/thông báo tiếp theo.</t>
         </is>
       </c>
@@ -15400,19 +15395,19 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Sellh Wuther khô, Sellh bao Loong và sách dạy nấu ăn gia truyền.
+          <t>Bánh Wuther khô, Bánh bao Loong và sách dạy nấu ăn gia truyền.
 &lt;i&gt;- Đồ khô mang đủ rồi đấy, con lấy sách dạy nấu của mẹ chưa?&lt;/i&gt;
-&lt;i&gt;- Mẹ ơi, tới KU-Roro B con học mẹ nấu là được mà. Quyển sách này sắp rách hết rồi, để lại đi cho nhẹ.&lt;/i&gt;
+&lt;i&gt;- Mẹ ơi, tới Jinzhou con học mẹ nấu là được mà. Quyển sách này sắp rách hết rồi, để lại đi cho nhẹ.&lt;/i&gt;
 &lt;i&gt;- Con biết gì mà nói! Có sách này đi đâu cũng có hương vị của nhà. Biết đâu sau này mẹ không còn ở bên con nữa...&lt;/i&gt;
 Một thùng nước tăng lực.
 &lt;i&gt;- Nước tăng lực nặng lắm, mang bình nước không được à?&lt;/i&gt;
 &lt;i&gt;- Biết đâu trên đường không có nguồn nước sạch? Những lon này mới là thứ ta có thể trông cậy được!&lt;/i&gt;
 &lt;i&gt;- Thôi được, mẹ nói thế thì mẹ mang vậy.&lt;/i&gt;
 &lt;i&gt;- Ừ, đến lúc cần thì con đừng có mà uống nhé!&lt;/i&gt;
-Tent và đồ dùng dã ngoại.
+Lều trại và đồ dùng dã ngoại.
 &lt;i&gt;- Chúng ta đâu phải đi cắm trại đâu, con yêu.&lt;/i&gt;
 &lt;i&gt;- Nhưng bố bảo chúng ta đi cắm trại mà.&lt;/i&gt;
-&lt;i&gt;- Heying Không phải cắm trại bình thường đâu. À, đừng quên đeo dây chuyền may mắn bà tặng nhé.&lt;/i&gt;</t>
+&lt;i&gt;- Hừm... Không phải cắm trại bình thường đâu. À, đừng quên đeo dây chuyền may mắn bà tặng nhé.&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -15478,8 +15473,8 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Cây cổ thụ "Long Nhãn" nằm ở phía bắc vùng Long's Gaze Suburbs, Central Plains. Theo ghi chép trong "Thực Vật Chí KU-Roro B", Long Nhãn được ước tính đã tồn tại từ 1400 đến 1500 năm, vượt qua sự thử thách của Lời Than và vẫn sừng sững đến ngày nay. Bộ rễ uốn lượn của nó như một con mãng xà quấn quanh ngọn cờ rồng, những cành cây như móng vuốt sắc nhọn, tất cả đều thể hiện bản tính bất khuất của cây. Cây cổ thụ bất động này từ lâu đã trở thành biểu tượng của vùng đất, nơi con người tìm đến như một ngọn hải đăng hy vọng. Chừng nào Long Nhãn còn đứng vững, ngày Central Plains hồi sinh nhất định sẽ đến.
-*Chú ý: Xin đừng khắc lên vỏ hoặc cành cây. Chúng ta đều có trách nhiệm chung trong việc bảo vệ cây cổ thụ này.</t>
+          <t>Cây cổ thụ "Long Nhãn" nằm ở phía bắc vùng Ngoại Ô Long Nhãn, Central Plains. Theo ghi chép trong "Thực Vật Chí Jinzhou", Long Nhãn được ước tính đã tồn tại từ 1400 đến 1500 năm, vượt qua sự thử thách của Lời Than và vẫn sừng sững đến ngày nay. Bộ rễ uốn lượn của nó như một con mãng xà quấn quanh ngọn cờ rồng, những cành cây như móng vuốt sắc nhọn, tất cả đều thể hiện bản tính bất khuất của cây. Cây cổ thụ bất động này từ lâu đã trở thành biểu tượng của vùng đất, nơi con người tìm đến như một ngọn hải đăng hy vọng. Chừng nào Long Nhãn còn đứng vững, ngày Central Plains hồi sinh nhất định sẽ đến.
+*Lưu ý: Xin đừng khắc lên vỏ hoặc cành cây. Chúng ta đều có trách nhiệm chung trong việc bảo vệ cây cổ thụ này.</t>
         </is>
       </c>
     </row>
@@ -15621,7 +15616,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Chú ý đến du khách: Nếu thấy mèo hoang tại ga trung chuyển, xin đừng cho ăn hay la mắng chúng.
+          <t>Lưu ý đến du khách: Nếu thấy mèo hoang tại ga trung chuyển, xin đừng cho ăn hay la mắng chúng.
 Có hai con mèo dữ tợn thường lảng vảng quanh ga, chúng thường tiếp cận nhân viên một cách dịu dàng và trìu mến, sau đó lẻn vào ga bất cứ lúc nào và trốn trong những góc tối của thiết bị quan trọng.
 Khi bị phát hiện, chúng sẽ nhe nanh giơ vuốt, tấn công bất kỳ ai đến gần.
 Hãy cẩn thận khi tiếp cận những con mèo này. Đừng để vẻ ngoài dễ thương của chúng đánh lừa.
@@ -15702,19 +15697,19 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>~ Trạm Switch Broadcast Diệp ~
+          <t>~ Trạm Chuyển Phát Thanh Diệp ~
 Tập San Hàng Tháng, Số 80, Bản Tiêu Chuẩn
-*Guide Sự Kiện* Bữa Tiệc Hoa
-Carnival Throw Hoa đầu tiên ở Làng Xiehua đã kết thúc thành công tốt đẹp. Không như những năm trước, lần này chúng ta đã mời nhiều người bạn từ quân đội đến tham gia và cùng chúc mừng những chiến thắng của họ trên chiến trường, như một lời tri ân cho những nỗ lực không ngừng nghỉ của họ.
-Throw Hoa là một phong tục địa phương của cư dân Central Plains. Enter tháng Ba, người dân sẽ Dodgem những cành hoa tươi vừa hái hoặc cánh hoa vào dòng nước chảy, như một cách đón nhận sức sống của mùa xuân trong làn nước. Họ cầu nguyện cho niềm vui của sự sống mới sẽ chảy vào lòng mỗi người, không còn bị giam cầm bởi những đau thương mà Lament để lại.
-Ngoài ra, gần trạm còn có một cái ao nhỏ. Tất cả các vị khách ghé thăm nếu có hứng thú đều có thể thoải mái Dodgem một nắm cánh hoa xuống ao khi đi dạo sau bữa tối. Dù không lớn như Hồ Ngọc Hoa ở Làng Qiqi ngày xưa, nhưng hy vọng và niềm vui thì vẫn như nhau.
-~ Trạm Switch Broadcast Diệp ~
-Tập San Hàng Tháng, Số 100, Bản Kỷ Niệm Special
-*Lời Bạt Special* Lời Parting Cuối Cùng
-Ai ngờ đâu, Trạm Switch Broadcast Diệp đã đồng hành cùng những lữ khách muôn phương thêm hai năm nữa, và tập san hàng tháng của chúng ta giờ đã đến số thứ 100. Ở cuối số kỷ niệm này, chúng tôi muốn gửi lời tạm biệt đến tất cả các bạn.
-Lament đã hoàn toàn thay đổi Central Plains. Những thảm họa xảy ra liên tiếp khiến việc quản lý trạm ngày càng khó khăn. Trong hoàn cảnh này, tôi rất tiếc phải thông báo rằng Trạm Switch Broadcast Diệp không còn đủ khả năng để tiếp tục sứ mệnh của mình, mang đến cho quý khách một nơi nghỉ chân an toàn và thoải mái thực sự.
-Tuy nhiên, lời chia tay của Thanh Diệp sẽ không bất ngờ như sự xuất hiện của một Tacet Field! Chúng tôi sẽ sớm tổ chức một buổi bán từ thiện tất cả các vật phẩm trong trạm. Số tiền thu được sẽ dùng để giúp mọi người xây dựng lại mái ấm của mình.
-Tôi hy vọng tất cả các bạn sẽ mong chờ điều này. Tôi hy vọng rằng chúng ta sẽ sớm gặp lại nhau ở KU-Roro B trong một tương lai không xa.</t>
+*Hướng Dẫn Sự Kiện* Bữa Tiệc Hoa
+Lễ Hội Ném Hoa đầu tiên ở Làng Xiehua đã kết thúc thành công tốt đẹp. Không như những năm trước, lần này chúng ta đã mời nhiều người bạn từ quân đội đến tham gia và cùng chúc mừng những chiến thắng của họ trên chiến trường, như một lời tri ân cho những nỗ lực không ngừng nghỉ của họ.
+Ném Hoa là một phong tục địa phương của cư dân Central Plains. Vào tháng Ba, người dân sẽ ném những cành hoa tươi vừa hái hoặc cánh hoa vào dòng nước chảy, như một cách đón nhận sức sống của mùa xuân trong làn nước. Họ cầu nguyện cho niềm vui của sự sống mới sẽ chảy vào lòng mỗi người, không còn bị giam cầm bởi những đau thương mà Lament để lại.
+Ngoài ra, gần trạm còn có một cái ao nhỏ. Tất cả các vị khách ghé thăm nếu có hứng thú đều có thể thoải mái ném một nắm cánh hoa xuống ao khi đi dạo sau bữa tối. Dù không lớn như Hồ Ngọc Hoa ở Làng Qiqi ngày xưa, nhưng hy vọng và niềm vui thì vẫn như nhau.
+~ Trạm Chuyển Phát Thanh Diệp ~
+Tập San Hàng Tháng, Số 100, Bản Kỷ Niệm Đặc Biệt
+*Lời Bạt Đặc Biệt* Lời Chia Tay Cuối Cùng
+Ai ngờ đâu, Trạm Chuyển Phát Thanh Diệp đã đồng hành cùng những lữ khách muôn phương thêm hai năm nữa, và tập san hàng tháng của chúng ta giờ đã đến số thứ 100. Ở cuối số kỷ niệm này, chúng tôi muốn gửi lời tạm biệt đến tất cả các bạn.
+Lament đã hoàn toàn thay đổi Central Plains. Những thảm họa xảy ra liên tiếp khiến việc quản lý trạm ngày càng khó khăn. Trong hoàn cảnh này, tôi rất tiếc phải thông báo rằng Trạm Chuyển Phát Thanh Diệp không còn đủ khả năng để tiếp tục sứ mệnh của mình, mang đến cho quý khách một nơi nghỉ chân an toàn và thoải mái thực sự.
+Tuy nhiên, lời chia tay của Thanh Diệp sẽ không bất ngờ như sự xuất hiện của một Tổ Tacet! Chúng tôi sẽ sớm tổ chức một buổi bán từ thiện tất cả các vật phẩm trong trạm. Số tiền thu được sẽ dùng để giúp mọi người xây dựng lại mái ấm của mình.
+Tôi hy vọng tất cả các bạn sẽ mong chờ điều này. Tôi hy vọng rằng chúng ta sẽ sớm gặp lại nhau ở Jinzhou trong một tương lai không xa.</t>
         </is>
       </c>
     </row>
@@ -15789,14 +15784,14 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Loại: Journal thí nghiệm
+          <t>Loại: Nhật ký thí nghiệm
 Mã số: DQ-C2068
 Ngày: [---]
-Details thí nghiệm: 
+Chi tiết thí nghiệm: 
 1. Bắt giữ và phân tích phản ứng tần số của đối tượng kiểm soát mới.
-2. Xác minh giá trị tương thích tần số giữa Guide Crystal và đối tượng kiểm soát.
-3. Điều chỉnh lại trạng thái kênh của bàn dò tìm tại Area C.
-4. &lt;color=Highlight&gt;Kích hoạt hai Guide Crystal trên bàn dò tìm.&lt;/color&gt;
+2. Xác minh giá trị tương thích tần số giữa Pha Lê Hướng Dẫn và đối tượng kiểm soát.
+3. Điều chỉnh lại trạng thái kênh của bàn dò tìm tại Khu vực C.
+4. &lt;color=Highlight&gt;Kích hoạt hai Pha Lê Hướng Dẫn trên bàn dò tìm.&lt;/color&gt;
 5. Giám sát và ghi chép trạng thái kênh của bàn dò tìm.
 Kết quả thí nghiệm: 
 [---]</t>
@@ -15933,7 +15928,7 @@
       <c r="M207" t="inlineStr">
         <is>
           <t>Ngày: 8 tháng 1, AL157
-Hôm nay Trưởng nhóm lại đến nói chuyện với tôi, ông ấy muốn tôi, với tư cách là trụ cột kỹ thuật, đưa ra ý kiến quyết định - có nên tiếp tục công cuộc thám hiểm hay không. Ông ấy và tôi, thực ra ai cũng hiểu, việc mở kênh đào là tối quan trọng, chúng ta đã trả giá quá đắt cho nó, nếu dừng lại ở đây, bao năm công sức sẽ đổ sông đổ biển, nhưng nếu tiếp tục, chúng ta có thể mất đi vô số sinh mạng... Tôi không thể tự thuyết phục mình, huống chi là đồng đội đang đứng ngồi không yên vì Dịch TD bùng phát.</t>
+Hôm nay Đội trưởng lại đến nói chuyện với tôi, ông ấy muốn tôi, với tư cách là trụ cột kỹ thuật, đưa ra ý kiến quyết định - có nên tiếp tục công cuộc thám hiểm hay không. Ông ấy và tôi, thực ra ai cũng hiểu, việc mở kênh đào là tối quan trọng, chúng ta đã trả giá quá đắt cho nó, nếu dừng lại ở đây, bao năm công sức sẽ đổ sông đổ biển, nhưng nếu tiếp tục, chúng ta có thể mất đi vô số sinh mạng... Tôi không thể tự thuyết phục mình, huống chi là đồng đội đang đứng ngồi không yên vì Dịch TD bùng phát.</t>
         </is>
       </c>
     </row>
@@ -16002,9 +15997,9 @@
       <c r="M208" t="inlineStr">
         <is>
           <t>Ngày làm việc: 11 tháng 10, AL155
-Tóm tắt công việc: Completed sơ bộ bản đồ phân bố đơn vị thám hiểm, có thể xác định sơ bộ hướng đào kênh. Khi thu thập thông tin hình ảnh, gặp phải một đợt Bùng Play TDTD quy mô nhỏ, đội Đặc Nhiệm Midnight Rangers đã kịp thời hỗ trợ, chỉ có hai thành viên đội khảo sát bị thương nhẹ, nhưng thiết bị thám hiểm bị hư hại nặng.
+Tóm tắt công việc: Hoàn thành sơ bộ bản đồ phân bố đơn vị thám hiểm, có thể xác định sơ bộ hướng đào kênh. Khi thu thập thông tin hình ảnh, gặp phải một đợt Bùng Phát TDTD quy mô nhỏ, đội Đặc Nhiệm Midnight Rangers đã kịp thời hỗ trợ, chỉ có hai thành viên đội khảo sát bị thương nhẹ, nhưng thiết bị thám hiểm bị hư hại nặng.
 Dự kiến vật tư thiết bị sẽ đến trong một tuần, trong thời gian đó đội sẽ tạm dừng mọi công việc thám hiểm.
-Rating và nhận xét: Phát hiện quá trình khoáng hóa thô của một loại đá chưa xác định trong phạm vi khu vực, cần tiếp tục khai quật và kiểm tra cấu trúc, tính chất để xác định giá trị. Công tác xây dựng và thám hiểm ở khu vực này có hệ số rủi ro cao, nếu phát hiện bất thường phải ngừng công việc ngay, sơ tán khỏi hiện trường và gọi đội Midnight Rangers đến xử lý.</t>
+Đánh giá và nhận xét: Phát hiện quá trình khoáng hóa thô của một loại đá chưa xác định trong phạm vi khu vực, cần tiếp tục khai quật và kiểm tra cấu trúc, tính chất để xác định giá trị. Công tác xây dựng và thám hiểm ở khu vực này có hệ số rủi ro cao, nếu phát hiện bất thường phải ngừng công việc ngay, sơ tán khỏi hiện trường và gọi đội Midnight Rangers đến xử lý.</t>
         </is>
       </c>
     </row>
@@ -16077,15 +16072,15 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>&lt;b&gt;[Thông Báo New Yi]&lt;/b&gt;
+          <t>&lt;b&gt;[Thông Báo Mới Nhất]&lt;/b&gt;
 Ngày: AL157
-Nội dung: Do sự xuất hiện thường xuyên của Bùng Play TD gần đây, nồng độ Tần số bất thường tại Sóng Gió Ngân và các tình huống đặc biệt khác, Dự án Tượng Canh Gác và Khai Quật Kênh sẽ bị đình chỉ ngay lập tức, toàn bộ nhân viên Bộ Phát Triển và Midnight Rangers sẽ được rút lui ngay, thời gian khởi động lại dự án sẽ được thông báo sau.
-&lt;b&gt;[Thông Báo Expired]&lt;/b&gt;
+Nội dung: Do sự xuất hiện thường xuyên của Bùng Phát TD gần đây, nồng độ Tần số bất thường tại Sóng Gió Ngân và các tình huống đặc biệt khác, Dự án Tượng Canh Gác và Khai Quật Kênh sẽ bị đình chỉ ngay lập tức, toàn bộ nhân viên Bộ Phát Triển và Midnight Rangers sẽ được rút lui ngay, thời gian khởi động lại dự án sẽ được thông báo sau.
+&lt;b&gt;[Thông Báo Hết Hạn]&lt;/b&gt;
 Ngày: AL154
-Nội dung: Hôm nay, con đường vào Gorges of Spirits chính thức được mở, các đội đặc nhiệm Midnight Rangers đã chạm trán với một lượng lớn Bùng Play TDTD tích tụ trong thung lũng. Sự bùng phát TD vô cùng nguy hiểm, số lượng tử vong, thương vong nặng và mất tích hiện vẫn chưa thể thống kê đầy đủ. Chỉ huy trưởng đã hy sinh anh dũng trong trận chiến, Jiyan tạm thời được bổ nhiệm làm chỉ huy trưởng lâm thời.
-&lt;b&gt;[Thông Báo Expired]&lt;/b&gt;
+Nội dung: Hôm nay, con đường vào Hẻm Núi Linh Hồn chính thức được mở, các đội đặc nhiệm Midnight Rangers đã chạm trán với một lượng lớn Bùng Phát TDTD tích tụ trong thung lũng. Sự bùng phát TD vô cùng nguy hiểm, số lượng tử vong, thương vong nặng và mất tích hiện vẫn chưa thể thống kê đầy đủ. Chỉ huy trưởng đã hy sinh anh dũng trong trận chiến, Jiyan tạm thời được bổ nhiệm làm chỉ huy trưởng lâm thời.
+&lt;b&gt;[Thông Báo Hết Hạn]&lt;/b&gt;
 Ngày: AL140
-Nội dung: Theo ủy quyền của Bộ Phát Triển, đội đặc nhiệm Midnight Rangers sẽ chịu trách nhiệm khảo sát và dọn dẹp khu vực Gorges of Spirits từ hôm nay, để Bộ Phát Triển có thể tiến vào thung lũng khảo sát trong giai đoạn tiếp theo. Dự kiến ban đầu, lối vào Gorges of Spirits sẽ được mở vào năm 150.</t>
+Nội dung: Theo ủy quyền của Bộ Phát Triển, đội đặc nhiệm Midnight Rangers sẽ chịu trách nhiệm khảo sát và dọn dẹp khu vực Hẻm Núi Linh Hồn từ hôm nay, để Bộ Phát Triển có thể tiến vào thung lũng khảo sát trong giai đoạn tiếp theo. Dự kiến ban đầu, lối vào Hẻm Núi Linh Hồn sẽ được mở vào năm 150.</t>
         </is>
       </c>
     </row>
@@ -16157,10 +16152,10 @@
         <is>
           <t>Độ cứng: 6
 Mật độ: 3.0-3.5 g/cm³
-Intensity Dodgen: 3000-5000 kg/cm³
-Templates vật này có tên là Đá Moire, nổi bật với cấu trúc tinh xảo, độ cứng cao và khả năng chịu Dodgen mạnh mẽ. Nó sở hữu tính ổn định hóa học tuyệt vời và có thể chịu được sự biến đổi nhiệt độ khắc nghiệt.
+Cường độ nén: 3000-5000 kg/cm³
+Mẫu vật này có tên là Đá Moire, nổi bật với cấu trúc tinh xảo, độ cứng cao và khả năng chịu nén mạnh mẽ. Nó sở hữu tính ổn định hóa học tuyệt vời và có thể chịu được sự biến đổi nhiệt độ khắc nghiệt.
 Đá Moire phân bố rộng rãi tại Gorges of Spirits, hình thành các mỏ quy mô lớn giúp việc khai thác trở nên dễ dàng. Những khối đá kích thước lớn có thể được khai thác một cách thuận lợi. Tất cả những yếu tố này khiến Đá Moire trở thành vật liệu xây dựng lý tưởng cho các tác phẩm điêu khắc quy mô lớn, tường ngoài công trình và lát nền cứng.
-&lt;i&gt;Ghi chú: Được sử dụng trong xây dựng KU-Roro B và tạo tác tượng Sentinel.&lt;/i&gt;</t>
+&lt;i&gt;Ghi chú: Được sử dụng trong xây dựng Jinzhou và tạo tác tượng Sentinel.&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16222,7 @@
       <c r="M211" t="inlineStr">
         <is>
           <t>Ngày: AL154
-Nội dung: Trong chiến dịch thu hồi Gorges of Spirits, đội Midnight Rangers gặp phải tình huống cực kỳ bất lợi như tử trận của chỉ huy trưởng và sự chênh lệch lực lượng. Tuy nhiên, chiến binh Jiyan của chúng ta đã chiến đấu xuất sắc, một mình cùng đội đặc nhiệm còn lại chống lại đợt Bùng Play TDTD quy mô lớn suốt ba ngày, kiên cường chờ đến khi quân tiếp viện đến, sau đó hợp quân và đánh bại hầu hết kết quả thám hiểm. Đợt Bùng Play TDTD bị đập tan trong một đòn, hầu hết thành quả thám hiểm được bảo toàn.</t>
+Nội dung: Trong chiến dịch thu hồi Gorges of Spirits, đội Midnight Rangers gặp phải tình huống cực kỳ bất lợi như tử trận của chỉ huy trưởng và sự chênh lệch lực lượng. Tuy nhiên, chiến binh Jiyan của chúng ta đã chiến đấu xuất sắc, một mình cùng đội đặc nhiệm còn lại chống lại đợt Bùng Phát TDTD quy mô lớn suốt ba ngày, kiên cường chờ đến khi quân tiếp viện đến, sau đó hợp quân và đánh bại hầu hết kết quả thám hiểm. Đợt Bùng Phát TDTD bị đập tan trong một đòn, hầu hết thành quả thám hiểm được bảo toàn.</t>
         </is>
       </c>
     </row>
@@ -16293,7 +16288,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Noise Tĩnh--</t>
+          <t>Tiếng Ồn Tĩnh--</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16359,7 @@
           <t>Đến ngày thứ năm ngoài chiến trường, cuối cùng tôi cũng có thời gian để viết vài dòng.
 Tôi được phân công làm thư ký trung đội, một trung đội 30 người. Tôi phải ghi chép lại những gì mình ăn, uống, ngủ, những gì mình lấy và những gì mình làm. Máy đếm Geiger kêu liên tục mỗi ngày, đạn pháo thỉnh thoảng lại bay qua gần đó.
 Tôi không biết mình may mắn hay không, nhưng một quả bom địch đã trúng vào hầm trú ẩn tôi đào. Nó thiêu chiếc Ba Lô của tôi thành tro. May mắn thay, tôi đang đi truyền lệnh nên thoát chết. Nhưng giữa mùa thu lạnh giá, không có túi ngủ, không có quần áo thay, và không biết làm sao để sống sót qua mùa đông sắp tới.
-Trung sĩ hậu cần, một người tốt bụng, đã đưa cho tôi túi ngủ và quần áo mới của anh, còn bản thân thì dùng đồ dự phòng đã mốc meo. Tôi chỉ nhận túi ngủ, hứa sẽ trả lại khi có lương thực. Anh không trả lời, cũng không lấy lại quần áo, chỉ mỉm cười rồi đi. Night đó quá lạnh, tôi không muốn đuổi theo. Thôi thì đợi đến sáng mai trả lại cho anh vậy.</t>
+Trung sĩ hậu cần, một người tốt bụng, đã đưa cho tôi túi ngủ và quần áo mới của anh, còn bản thân thì dùng đồ dự phòng đã mốc meo. Tôi chỉ nhận túi ngủ, hứa sẽ trả lại khi có lương thực. Anh không trả lời, cũng không lấy lại quần áo, chỉ mỉm cười rồi đi. Đêm đó quá lạnh, tôi không muốn đuổi theo. Thôi thì đợi đến sáng mai trả lại cho anh vậy.</t>
         </is>
       </c>
     </row>
@@ -16436,14 +16431,14 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Trận chiến tại Cao điểm 91,7 kéo dài suốt 11 ngày đêm, đại đội của chúng tôi, bao gồm cả đại đội trưởng và đại đội phó, mất 16 người, 7 bị thương nặng, 8 bị thương nhẹ. Plays biến trận chiến như sau:
+          <t>Trận chiến tại Cao điểm 91,7 kéo dài suốt 11 ngày đêm, đại đội của chúng tôi, bao gồm cả đại đội trưởng và đại đội phó, mất 16 người, 7 bị thương nặng, 8 bị thương nhẹ. Diễn biến trận chiến như sau:
 Cuối tháng Mười, địch tấn công cao điểm vô danh 91,7 của ta, sau mấy ngày đêm giằng co, chúng đã chiếm được hầu hết các vị trí trên mặt đất. Ngày 27 tháng Mười, đơn vị tôi được lệnh tham chiến để chi viện cho lực lượng bạn lân cận.
 Dưới hỏa lực yểm trợ, đơn vị chúng tôi tổ chức sáu đợt tấn công trong tám giờ, nhưng đều thất bại trong nhiệm vụ đánh bật hoàn toàn địch khỏi cao điểm.
 Rạng sáng ngày 28, địch mở cuộc phản công có hỏa lực yểm trợ nhưng không thành công.
 Từ ngày 28 tháng Mười đến ngày 6 tháng Mười một, quyền kiểm soát mặt đất đổi chủ liên tục, không bên nào giành được ưu thế.
-Night ngày 6, đơn vị tôi được lực lượng bạn thay thế và rút khỏi chiến trường để sửa chữa do tổn thất nặng, thương vong hơn 70%.
+Đêm ngày 6, đơn vị tôi được lực lượng bạn thay thế và rút khỏi chiến trường để sửa chữa do tổn thất nặng, thương vong hơn 70%.
 Bài học rút ra:
-Mailơng vong của đơn vị chủ yếu do hỏa lực trực tiếp tầm gần của địch. Điều này chứng minh kinh nghiệm phòng thủ đối phó với hỏa lực gián tiếp mà Quân đội đề ra là hiệu quả; ngược lại, nó cũng cho thấy chúng ta chưa chuẩn bị tốt cho chiến đấu tầm gần. Bản tổng kết chi tiết các bài học đã được đính kèm.</t>
+Thương vong của đơn vị chủ yếu do hỏa lực trực tiếp tầm gần của địch. Điều này chứng minh kinh nghiệm phòng thủ đối phó với hỏa lực gián tiếp mà Quân đội đề ra là hiệu quả; ngược lại, nó cũng cho thấy chúng ta chưa chuẩn bị tốt cho chiến đấu tầm gần. Bản tổng kết chi tiết các bài học đã được đính kèm.</t>
         </is>
       </c>
     </row>
@@ -16655,10 +16650,10 @@
         <is>
           <t>GIỌNG NỮ: "Mẹ à, hôm nay là ngày thứ bốn mươi bảy của trận chiến này và con đã bước sang tuổi hai hai."
 GIỌNG NỮ: "Bốn mươi bảy ngày, con đã từ một tên lính ngạo mạn trở thành chỉ huy tạm thời của trung đội."
-Female Giọng nói: "Địch cứ ào lên như gián."
+Giọng nữ: "Địch cứ ào lên như gián."
 GIỌNG NỮ: "Và chúng ta sẽ không ngần ngại dẫm nát chúng, như mọi khi."
 [tạm dừng và hít thở sâu]
-Female Giọng nói: "Mẹ à, con sẽ trở về. Họ sẽ đưa con về, nhớ để cửa sổ không khóa nhé."</t>
+Giọng nữ: "Mẹ à, con sẽ trở về. Họ sẽ đưa con về, nhớ để cửa sổ không khóa nhé."</t>
         </is>
       </c>
     </row>
@@ -16727,7 +16722,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>1. Sea of Flames nghiêm cấm mọi nhân sự không phận sự. Bất kỳ ai cố tình xâm nhập sẽ phải chịu hậu quả. Người có thẩm quyền phải tuân thủ nghiêm ngặt quy định hoạt động.</t>
+          <t>1. Biển Lửa nghiêm cấm mọi nhân sự không phận sự. Bất kỳ ai cố tình xâm nhập sẽ phải chịu hậu quả. Người có thẩm quyền phải tuân thủ nghiêm ngặt quy định hoạt động.</t>
         </is>
       </c>
     </row>
@@ -16865,11 +16860,11 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Dạo này trời ẩm ướt quá, sợ lại đến mùa Rainy Cũ nữa, nên tớ tìm một xác vũ khí để trú mưa.
+          <t>Dạo này trời ẩm ướt quá, sợ lại đến mùa Mưa Cũ nữa, nên tớ tìm một xác vũ khí để trú mưa.
 Tình cờ gặp hai đứa trẻ cũng đang dừng chân ở đây, chúng nhỏ thôi, lại còn cảnh giác với người lạ, trông như hai đứa bỏ nhà đi vậy.
 Tớ định gọi Đội Mornguard từ trại bên kia đến đưa chúng về, nhưng hai đứa bất ngờ lao vào, suýt nữa thì húc vào vành mũ của tớ.
-"Uncle ơi, làm ơn đừng đưa chúng cháu về. Cháu và em chỉ muốn đến biển hoa đằng kia thôi." Thằng anh nhìn tớ tha thiết, nhưng tớ lại chợt ngẩn người.
-Thực ra, ai chẳng tò mò khi còn nhỏ. Mà dạo này tớ cũng chẳng có việc gì, hay là đưa chúng đi xem cho vui, nhân tiện cũng ghé qua Sea of Flames luôn.</t>
+"Chú ơi, làm ơn đừng đưa chúng cháu về. Cháu và em chỉ muốn đến biển hoa đằng kia thôi." Thằng anh nhìn tớ tha thiết, nhưng tớ lại chợt ngẩn người.
+Thực ra, ai chẳng tò mò khi còn nhỏ. Mà dạo này tớ cũng chẳng có việc gì, hay là đưa chúng đi xem cho vui, nhân tiện cũng ghé qua Biển Lửa luôn.</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16932,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Chúng tôi dừng lại ở bờ Sea of Flames, hai đứa trẻ gật đầu với nhau như thể xác nhận điều gì đó. Rồi cậu bé rút ra một chiếc hộp nhỏ xinh từ Ba Lô, sau một thoáng do dự, cậu Dodgem thứ bên trong vào Sea of Flames.
+          <t>Chúng tôi dừng lại ở bờ Biển Lửa, hai đứa trẻ gật đầu với nhau như thể xác nhận điều gì đó. Rồi cậu bé rút ra một chiếc hộp nhỏ xinh từ Ba Lô, sau một thoáng do dự, cậu ném thứ bên trong vào Biển Lửa.
 Chẳng mấy chốc, chiếc vật dụng dài kia tan chảy trong sức nóng dữ dội, và khi tôi quay đầu lại, hai đứa trẻ đã rơi những giọt nước mắt nhỏ.
 Tôi đã đi khắp thế giới và chẳng sợ gì cả, nhưng tôi sợ nhất là trẻ con khóc, nên may là tôi đã bỏ con búp bê bị nổ vào rương kho báu từ trước, sau khi lấy ra và dỗ dành, đứa nhỏ đã nín khóc.
 Dù món đồ cũ kỹ này không vào được tháp, nhưng cũng coi như tận dụng được, nó vẫn có giá trị.</t>
@@ -17005,7 +17000,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Hôm nay là một ngày vừa ngọt ngào vừa đắng cay. Tôi đưa bọn trẻ đi học và nhận được một bức ảnh mờ từ Annalika, chụp một chiếc "đàn piano bỏ túi" mà cô ấy tìm thấy, giống hệt chiếc tôi đã vứt bỏ năm nào. Hóa ra chiếc đàn piano bỏ túi ở Sea of Flames kia lại là kỷ vật quý giá về tình yêu của ông bà tôi. Họ bị chia cắt trong một trận chiến và hẹn nhau sẽ gặp lại ở biển hoa, nơi họ để lại chiếc đàn piano bỏ túi như một tín vật tình yêu. Anh trai tôi định bán nó để lấy SHC, nhưng làm sao có thể đo lường một thứ vô giá bằng tiền chứ? Những khoảnh khắc như thế này khiến tôi nhận ra cuộc sống thật ngắn ngủi mà mạnh mẽ biết bao. Cảm ơn hai đứa nhỏ, các con đã cho ta thấy giá trị đích thực của những món đồ cổ trong thời đại này.</t>
+          <t>Hôm nay là một ngày vừa ngọt ngào vừa đắng cay. Tôi đưa bọn trẻ đi học và nhận được một bức ảnh mờ từ Annalika, chụp một chiếc "đàn piano bỏ túi" mà cô ấy tìm thấy, giống hệt chiếc tôi đã vứt bỏ năm nào. Hóa ra chiếc đàn piano bỏ túi ở Biển Lửa kia lại là kỷ vật quý giá về tình yêu của ông bà tôi. Họ bị chia cắt trong một trận chiến và hẹn nhau sẽ gặp lại ở biển hoa, nơi họ để lại chiếc đàn piano bỏ túi như một tín vật tình yêu. Anh trai tôi định bán nó để lấy SHC, nhưng làm sao có thể đo lường một thứ vô giá bằng tiền chứ? Những khoảnh khắc như thế này khiến tôi nhận ra cuộc sống thật ngắn ngủi mà mạnh mẽ biết bao. Cảm ơn hai đứa nhỏ, các con đã cho ta thấy giá trị đích thực của những món đồ cổ trong thời đại này.</t>
         </is>
       </c>
     </row>
@@ -17073,8 +17068,8 @@
       <c r="M223" t="inlineStr">
         <is>
           <t>Annalika đã gọi tôi là đồ vô dụng sau khi xem bảng thành tích của tôi.
-Có lẽ theo cô ấy, cách duy nhất để thể hiện giá trị thực sự của những cổ vật là đưa chúng vào Tower Abyssal Cô Đặc.
-Nếu có thể, tôi thật sự mong cô bé này sẽ bước ra khỏi Tower Abyssal Cô Đặc, trải nghiệm thế giới thực, và trở thành một phần của những chú thích lịch sử cùng với mọi chỉ số.</t>
+Có lẽ theo cô ấy, cách duy nhất để thể hiện giá trị thực sự của những cổ vật là đưa chúng vào Tháp Vực Sâu Cô Đặc.
+Nếu có thể, tôi thật sự mong cô bé này sẽ bước ra khỏi Tháp Vực Sâu Cô Đặc, trải nghiệm thế giới thực, và trở thành một phần của những chú thích lịch sử cùng với mọi chỉ số.</t>
         </is>
       </c>
     </row>
@@ -17204,7 +17199,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Haha, ta cá là chẳng ai biết ta giấu mật mã ở đây đâu. Hai số đầu tiên lấy từ ngày sinh của ta: 2 và 4. Số thứ ba là số dải đèn, còn số thứ tư là số bậc thang trước Cổng! Haha, từ giờ chỉ cần liếc mắt là ta nhớ lại ngay thôi. Ta sẽ không bao giờ "quên" nữa. Và cũng chẳng còn cái nhìn khó chịu từ Quản trị An ninh nữa!</t>
+          <t>Haha, tao cá là chẳng ai biết tao giấu mật mã ở đây đâu. Hai số đầu tiên lấy từ ngày sinh của tao: 2 và 4. Số thứ ba là số dải đèn, còn số thứ tư là số bậc thang trước Cổng! Haha, từ giờ chỉ cần liếc mắt là tao nhớ lại ngay thôi. Tao sẽ không bao giờ "quên" nữa. Và cũng chẳng còn cái nhìn khó chịu từ Quản trị An ninh nữa!</t>
         </is>
       </c>
     </row>
@@ -17270,8 +17265,8 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Tấn Châu là một thành phố pháo đài nằm ở biên giới đông nam Huanglong. Đây là cảng đất liền đầu tiên mà mọi tàu thuyền nước ngoài phải cập bến khi vào lãnh thổ. Nhân sự và hàng hóa ngoại quốc đều phải được kiểm tra và dỡ hàng tại Cảng Quân Triều. Cảng Quân Triều sở hữu hệ thống quản lý container hoàn thiện cùng cơ sở neo đậu quy mô lớn. Đây là một cảng trung chuyển tổng hợp và cảng container chính với lưu lượng hàng hóa cao nhất Huanglong. Hiện tại, Cảng Quân Triều đã thiết lập quan hệ đối tác chiến lược dài hạn với Lollo Logistics và Pioneer Association. Chúng tôi hoan nghênh mọi hình thức hợp tác kinh doanh.
-Văn phòng Mailơng mại, Cảng Quân Triều</t>
+          <t>Tấn Châu là một thành phố pháo đài nằm ở biên giới đông nam Huanglong. Đây là cảng đất liền đầu tiên mà mọi tàu thuyền nước ngoài phải cập bến khi vào lãnh thổ. Nhân sự và hàng hóa ngoại quốc đều phải được kiểm tra và dỡ hàng tại Cảng Quân Triều. Cảng Quân Triều sở hữu hệ thống quản lý container hoàn thiện cùng cơ sở neo đậu quy mô lớn. Đây là một cảng trung chuyển tổng hợp và cảng container chính với lưu lượng hàng hóa cao nhất Huanglong. Hiện tại, Cảng Quân Triều đã thiết lập quan hệ đối tác chiến lược dài hạn với Lollo Logistics và Hiệp hội Pioneer. Chúng tôi hoan nghênh mọi hình thức hợp tác kinh doanh.
+Văn phòng Thương mại, Cảng Quân Triều</t>
         </is>
       </c>
     </row>
@@ -17402,8 +17397,8 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Cảm ơn quý khách đã chọn đường cao tốc. Tuyến đường này kết nối trực tiếp giữa Port Gunchao, Mỏ Hổ Nham và Thành phố KU-Roro B. Vui lòng xác nhận điểm đến của quý khách. Lưu ý: Có thể xuất hiện kẻ lưu đày và Discord quanh khu vực này. Hãy cảnh giác và lái xe an toàn khi vận chuyển hàng hóa. (UI Updates: Những ai cố tình phá hoại hoặc làm hư hại cơ sở hạ tầng đường cao tốc sẽ bị truy tố!)
-Bảo trì định kỳ: Đội Bảy, Bộ Play triển</t>
+          <t>Cảm ơn quý khách đã chọn đường cao tốc. Tuyến đường này kết nối trực tiếp giữa Cảng Gunchao, Mỏ Hổ Nham và Thành phố Jinzhou. Vui lòng xác nhận điểm đến của quý khách. Lưu ý: Có thể xuất hiện kẻ lưu đày và Tacet Discord quanh khu vực này. Hãy cảnh giác và lái xe an toàn khi vận chuyển hàng hóa. (Cập nhật: Những ai cố tình phá hoại hoặc làm hư hại cơ sở hạ tầng đường cao tốc sẽ bị truy tố!)
+Bảo trì định kỳ: Đội Bảy, Bộ Phát triển</t>
         </is>
       </c>
     </row>
@@ -17473,11 +17468,11 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Mẫu đơn yêu cầu vật tư
-Người yêu cầu: Yizhu (ví dụ)   Bộ phận yêu cầu: Tuần Tra KU-Roro B (ví dụ)
+          <t>Mẫu Đơn Yêu Cầu Vật Tư
+Người yêu cầu: Yizhu (ví dụ)   Bộ phận yêu cầu: Tuần Tra Jinzhou (ví dụ)
 Vật tư yêu cầu và số lượng: 10 đạn mồi hiện đại (ví dụ)
-Lý do yêu cầu: Phát hiện nhóm Save Dân gần đường cao tốc cảng (ví dụ, tóm tắt trong 80 từ trở xuống.)
-Vui lòng nộp đơn qua Terminal của bạn.
+Lý do yêu cầu: Phát hiện nhóm Lưu Dân gần đường cao tốc cảng (ví dụ, tóm tắt trong 80 từ trở xuống.)
+Vui lòng nộp đơn qua Thiết bị đầu cuối của bạn.
 Vật tư yêu cầu sẽ được cấp trong ngày nộp đơn. Trong trường hợp khẩn cấp, hãy đến kho để xử lý nhanh.</t>
         </is>
       </c>
@@ -17547,11 +17542,11 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Record Hiện Trường về Sự Fall của CSC trong Thảm Họa AL104 - XIII
-Return hiện trường để điều tra bí ẩn về sự diệt vong của CSC cũng chẳng thu được thông tin gì hữu ích.
-Vẫn còn quá ít tư liệu về tàn tích tại đây, dấu vết Tacet Field của Wuthering Waves, và lời kể của những người sống sót... ghép nối lại với nhau.
+          <t>Ghi Chép Hiện Trường về Sự Sụp Đổ của CSC trong Thảm Họa AL104 - XIII
+Quay lại hiện trường để điều tra bí ẩn về sự diệt vong của CSC cũng chẳng thu được thông tin gì hữu ích.
+Vẫn còn quá ít tư liệu về tàn tích tại đây, dấu vết Tổ Tacet của Wuthering Waves, và lời kể của những người sống sót... ghép nối lại với nhau.
 Dù lý do là gì đi nữa, chỉ riêng kết quả thôi: điều gì đã xảy ra với cơ sở nghiên cứu tiên tiến nhất của loài người, tôi không dám nghĩ đến việc nó tái diễn.
-Intuition mách bảo tôi rằng đây không phải là một thảm họa tự nhiên thuần túy.</t>
+Trực giác mách bảo tôi rằng đây không phải là một thảm họa tự nhiên thuần túy.</t>
         </is>
       </c>
     </row>
@@ -17692,8 +17687,8 @@
         <is>
           <t>Ghi chú thực địa CSC về Sự Lật Đổ của Thảm Họa AL104-VII
 Những khu định cư đơn sơ từng được xây dựng cùng các căn cứ quân sự giờ đây đã hoàn toàn vắng bóng người sau thảm họa.
-Ngày nay, môi trường nơi đây vẫn còn khắc nghiệt, sương mù dày đặc và một số bất thường trong chỉ số con sóng của Tacet Field.
-Area này dường như thường xuyên bị những kẻ Lưu Đày quanh đây tấn công, chẳng còn lại gì nhiều.</t>
+Ngày nay, môi trường nơi đây vẫn còn khắc nghiệt, sương mù dày đặc và một số bất thường trong chỉ số con sóng của Tổ Tacet.
+Khu vực này dường như thường xuyên bị những kẻ Lưu Đày quanh đây tấn công, chẳng còn lại gì nhiều.</t>
         </is>
       </c>
     </row>
@@ -17763,12 +17758,12 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Năm AL157, đợt bùng phát Tacet Field TDTD lớn nhất trong lịch sử Huanglong - "Đợt Sóng Khổng Lồ TD" - đã xuất hiện và tràn vào vùng nội địa KU-Roro B.
+          <t>Năm AL157, đợt bùng phát Tổ Tacet TDTD lớn nhất trong lịch sử Huanglong - "Đợt Sóng Khổng Lồ TD" - đã xuất hiện và tràn vào vùng nội địa Jinzhou.
 Để bảo vệ mảnh đất mà nhân loại nương tựa để sinh tồn, toàn quân Huanglong đã đứng vững và phòng thủ tuyến phòng ngự cuối cùng.
-Trong số đó, lữ đoàn tiên phong Midnight Rangers đã tiến sâu vào vùng lõi của chiến trường để thực hiện chiến dịch tiêu diệt kẻ thù. Họ đã hy sinh mạng sống của mình cho *Cái Price Right Trả*, đảo ngược tình thế phòng ngự bị động trên chiến trường và đặt nền móng cho chiến thắng cuối cùng của Huanglong.
-Khu nghĩa trang này được dựng lên để tưởng nhớ 306 người lính đã hy sinh trong trận chiến bùng phát Tacet Field Huanglong.
+Trong số đó, lữ đoàn tiên phong Midnight Rangers đã tiến sâu vào vùng lõi của chiến trường để thực hiện chiến dịch tiêu diệt kẻ thù. Họ đã hy sinh mạng sống của mình cho *Cái Giá Phải Trả*, đảo ngược tình thế phòng ngự bị động trên chiến trường và đặt nền móng cho chiến thắng cuối cùng của Huanglong.
+Khu nghĩa trang này được dựng lên để tưởng nhớ 306 người lính đã hy sinh trong trận chiến bùng phát Tổ Tacet Huanglong.
                                                                                                                         --Thay mặt toàn thể nhân dân Huanglong.
-Thông báo bổ sung: Năm AL159, sau khi nghĩa trang hoàn thành, đã có rất nhiều người đến viếng, tiếng khóc thương ngưng đọng lại khiến các Sóng Gió Spree xung quanh trở nên hỗn loạn, gây ra một đợt bùng phát Tacet Field nhỏ và làm hư hại nhiều phần của Đài Tưởng Niệm ở các mức độ khác nhau. Dù đã có kế hoạch trùng tu địa điểm này, nhưng công chúng lại muốn giữ lại những dấu tích để làm lời cảnh tỉnh rằng cuộc khủng hoảng không được phép lãng quên.</t>
+Thông báo bổ sung: Năm AL159, sau khi nghĩa trang hoàn thành, đã có rất nhiều người đến viếng, tiếng khóc thương ngưng đọng lại khiến các Sóng Gió Điên Cuồng xung quanh trở nên hỗn loạn, gây ra một đợt bùng phát Tổ Tacet nhỏ và làm hư hại nhiều phần của Đài Tưởng Niệm ở các mức độ khác nhau. Dù đã có kế hoạch trùng tu địa điểm này, nhưng công chúng lại muốn giữ lại những dấu tích để làm lời cảnh tỉnh rằng cuộc khủng hoảng không được phép lãng quên.</t>
         </is>
       </c>
     </row>
@@ -17839,8 +17834,8 @@
         <is>
           <t>Rừng Âm U chắc chắn là kho báu quan trọng nhất toàn vùng Huanglong, sở hữu sự đa dạng loài vô song trên thế giới.
 Ngay khi đặt chân đến cổng vào, tôi đã nghe thấy rõ tiếng thực vật thì thầm và lời triệu gọi của chúng.
-Nghe nói sâu trong rừng, nơi từng là trụ sở của Department Âm Sinh Thái, vẫn lưu giữ những tư liệu hình ảnh về vô số loài thực vật, trong đó có một loài ngon lành gọi là Banana Ngà, xuất xứ từ Rừng Âm U. Banana Ngà từng là nguồn lương thực chính của Hoochief, và đổi lại, Hoochief đi tìm Banana Ngà trong rừng đã trở thành những "thợ thụ phấn" tuyệt vời.
-Kể từ khi màn sương bào tử độc lan rộng, Banana Ngà hoang dã đã biến mất khỏi Rừng Âm U, và thông tin về loài này giờ chỉ còn trong sử sách.
+Nghe nói sâu trong rừng, nơi từng là trụ sở của Cục Âm Sinh Thái, vẫn lưu giữ những tư liệu hình ảnh về vô số loài thực vật, trong đó có một loài ngon lành gọi là Chuối Ngà, xuất xứ từ Rừng Âm U. Chuối Ngà từng là nguồn lương thực chính của Hoochief, và đổi lại, Hoochief đi tìm Chuối Ngà trong rừng đã trở thành những "thợ thụ phấn" tuyệt vời.
+Kể từ khi màn sương bào tử độc lan rộng, Chuối Ngà hoang dã đã biến mất khỏi Rừng Âm U, và thông tin về loài này giờ chỉ còn trong sử sách.
 Lời Than Thở có lẽ là một quy trình đào thải tự nhiên không thể tránh khỏi.</t>
         </is>
       </c>
@@ -18054,8 +18049,8 @@
       <c r="M237" t="inlineStr">
         <is>
           <t>Lâu rồi tôi mới có một buổi tập luyện căng thẳng như thế này.
-Con Hoochief bị nhiễm độc ấy thể hiện một sự thiếu mệt mỏi đáng kinh ngạc trong cuộc truy đuổi không ngừng nghỉ con mồi của nó—mà đáng tiếc, con mồi đó lại là tôi. Tuy nhiên, khi chạy trốn, tôi không hề hoảng loạn mà đầu óc lại bắt đầu quay cuồng. Tôi biết rõ những bào tử độc hại này là hậu quả trực tiếp của Hiện tượng Waveworm. Theo tiêu chuẩn Ecoacoustics, chúng ta nên phân loại những con Hoochief bị nhiễm độc ấy như thế nào? Hơn nữa, làm thế nào những bào tử độc hại ấy lại lây nhiễm vào Discord, và liệu thiền định có phải là giải pháp khả thi cho việc nhiễm độc Discord không?
-Dùng chức năng Grapple, tôi khéo léo đu mình lên một cành cây ẩn nấp. Con Hoochief bị nhiễm độc mất dấu mục tiêu và lúng túng nhìn quanh. Nó trông như một đứa trẻ lạc lõng, rên rỉ và ho từng cơn, dường như mất đi khả năng định hướng không gian. Mỗi tiếng ho dữ dội lại phun ra một đám bào tử độc vào không khí. Những bào tử ấy, bị thúc đẩy bởi bản năng sinh tồn, càng đẩy cơ thể vốn đã suy yếu của con Hoochief đến giới hạn cuối cùng.
+Con Hoochief bị nhiễm độc ấy thể hiện một sự thiếu mệt mỏi đáng kinh ngạc trong cuộc truy đuổi không ngừng nghỉ con mồi của nó—mà đáng tiếc, con mồi đó lại là tôi. Tuy nhiên, khi chạy trốn, tôi không hề hoảng loạn mà đầu óc lại bắt đầu quay cuồng. Tôi biết rõ những bào tử độc hại này là hậu quả trực tiếp của Hiện tượng Waveworm. Theo tiêu chuẩn Ecoacoustics, chúng ta nên phân loại những con Hoochief bị nhiễm độc ấy như thế nào? Hơn nữa, làm thế nào những bào tử độc hại ấy lại lây nhiễm vào Tacet Discord, và liệu thiền định có phải là giải pháp khả thi cho việc nhiễm độc Tacet Discord không?
+Sử dụng chức năng Grapple, tôi khéo léo đu mình lên một cành cây ẩn nấp. Con Hoochief bị nhiễm độc mất dấu mục tiêu và lúng túng nhìn quanh. Nó trông như một đứa trẻ lạc lõng, rên rỉ và ho từng cơn, dường như mất đi khả năng định hướng không gian. Mỗi tiếng ho dữ dội lại phun ra một đám bào tử độc vào không khí. Những bào tử ấy, bị thúc đẩy bởi bản năng sinh tồn, càng đẩy cơ thể vốn đã suy yếu của con Hoochief đến giới hạn cuối cùng.
 Tôi bắt đầu tự hỏi: đây là một dạng đồng tiến hóa, hay chỉ là mối quan hệ ký sinh?</t>
         </is>
       </c>
@@ -18124,10 +18119,10 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Môi trường của Khu Rừng Ban Cô Độc còn kỳ diệu hơn cả tưởng tượng. Một hệ sinh thái tán cây độc đáo đã hình thành quanh những cành khổng lồ của cây cổ thụ này.
-Theo nghiên cứu của ta, các nhánh cây chứa một lượng dồi dào Năng Lượng Synergy, được tích tụ từ khắp khu vực Rừng Mờ và di chuyển từ ngọn cây xuống toàn bộ thân. Chính năng lượng này thúc đẩy sự phát triển của cây khổng lồ. Và nhờ nó, cả một hệ sinh thái hoàn toàn khác biệt đã phát triển trên cây. Có lẽ vì những tiếng gầm dữ dội thỉnh thoảng vang lên từ bên trong cây, nên không có sinh vật đột biến lớn nào có hoạt động Tacet Field xuất hiện. Điều này giúp thực vật phát triển mạnh mẽ hơn và tạo điều kiện cho sinh vật Synergy Mutterfly tồn tại.
-Synergy Giả tạo ra cây khổng lồ này có Tần số rất giống với ta. Chắc hẳn ông ấy cũng là một người yêu thiên nhiên. Nếu không, khó có thể tạo ra một cây khổng lồ phức tạp và rộng lớn như vậy, ngay cả khi có sự hỗ trợ của Sound Emulator trên đỉnh cây.
-Để thuận tiện cho các chuyến thám hiểm sau này, ta đã tạo một vật trang trí phát quang nhỏ trên các nhánh của Khu Rừng Ban Ngột Ngạt làm biển chỉ dẫn. Điều này sẽ giúp các chuyến thám hiểm khoa học sau này hiệu quả hơn. Giờ thì đã đến lúc lên đường khám phá sâu hơn vào lòng Khu Rừng Ban Ngột Ngạt!</t>
+          <t>Môi trường của Khu Rừng Cấm Cô Độc còn kỳ diệu hơn cả tưởng tượng. Một hệ sinh thái tán cây độc đáo đã hình thành quanh những cành khổng lồ của cây cổ thụ này.
+Theo nghiên cứu của ta, các nhánh cây chứa một lượng dồi dào Resonance Energy, được tích tụ từ khắp khu vực Rừng Mờ và di chuyển từ ngọn cây xuống toàn bộ thân. Chính năng lượng này thúc đẩy sự phát triển của cây khổng lồ. Và nhờ nó, cả một hệ sinh thái hoàn toàn khác biệt đã phát triển trên cây. Có lẽ vì những tiếng gầm dữ dội thỉnh thoảng vang lên từ bên trong cây, nên không có sinh vật đột biến lớn nào có hoạt động Tổ Tacet xuất hiện. Điều này giúp thực vật phát triển mạnh mẽ hơn và tạo điều kiện cho sinh vật Cộng Hưởng Mutterfly tồn tại.
+Resonator tạo ra cây khổng lồ này có Tần số rất giống với ta. Chắc hẳn ông ấy cũng là một người yêu thiên nhiên. Nếu không, khó có thể tạo ra một cây khổng lồ phức tạp và rộng lớn như vậy, ngay cả khi có sự hỗ trợ của Bộ Mô Phỏng Âm Thanh trên đỉnh cây.
+Để thuận tiện cho các chuyến thám hiểm sau này, ta đã tạo một vật trang trí phát quang nhỏ trên các nhánh của Khu Rừng Cấm Ngột Ngạt làm biển chỉ dẫn. Điều này sẽ giúp các chuyến thám hiểm khoa học sau này hiệu quả hơn. Giờ thì đã đến lúc lên đường khám phá sâu hơn vào lòng Khu Rừng Cấm Ngột Ngạt!</t>
         </is>
       </c>
     </row>
@@ -18202,7 +18197,7 @@
 [Tiếng kêu của Hoochief—] 
 Verina: Hoochief hư quá! Không được ăn đấy!
 [Tiếng kêu của Hoochief—] 
-Verina: Stop ngay—</t>
+Verina: Dừng lại ngay—</t>
         </is>
       </c>
     </row>
@@ -18273,12 +18268,12 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>1. Xác nhận đàn Cò Ma đã giao chiến với các Discord khác trước khi vận chuyển.
+          <t>1. Xác nhận đàn Cò Ma đã giao chiến với các Tacet Discord khác trước khi vận chuyển.
 1.1 Đánh dấu khu vực sinh sống của Cò Cha trên bản đồ và giữ khoảng cách khi lên lộ trình.
-2. Zhu kỳ vận chuyển là hai tuần; điều chỉnh kế hoạch cho phù hợp nhưng không được trì hoãn.
+2. Chu kỳ vận chuyển là hai tuần; điều chỉnh kế hoạch cho phù hợp nhưng không được trì hoãn.
 3. Cần xác nhận với Trại Giám Sát để sắp xếp và phối hợp vận chuyển.
 3.1 Do vị trí hẻo lánh và thời tiết khó lường, cần chuẩn bị phương án dự phòng cho trường hợp mất liên lạc.
-3.2 Nếu liên lạc bị gián đoạn, chờ 1 giờ trước khi thử kết nối lại để tránh gây nghi ngờ cho Discord.
+3.2 Nếu liên lạc bị gián đoạn, chờ 1 giờ trước khi thử kết nối lại để tránh gây nghi ngờ cho Tacet Discord.
 4. Luôn trang bị vũ khí trong suốt quá trình vận chuyển; được phép sử dụng vũ lực trực tiếp.</t>
         </is>
       </c>
@@ -18353,16 +18348,16 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Templates nước số: 231202
-Thời gian lấy mẫu: AL156, ngày 16 tháng 1, 10:00 sáng
-Các hạng mục kiểm tra: Chất rắn lơ lửng, màu sắc, độ dẫn điện, songin không ổn định, v.v.
-Kết quả kiểm tra: xem bảng đính kèm
-Kết luận:
-Các mẫu nước có nhiều chỉ số bất thường so với mẫu từ khu vực khác;
-Màu sắc của mẫu nước thu thập trở lại trong suốt sau một tuần để lắng, được cho là liên quan đến nystatin dễ bay hơi;
-Hiện tại, sự thay đổi chất lượng nước chưa gây nguy hiểm rõ ràng cho con người, nhưng không thể loại trừ các tác động tiếp theo do hoạt động của TD và Tacet Field;
-Home nghiên cứu: 00921
-Trưởng dự án: Lu Shen</t>
+          <t>Mẫu nước số: 231202
+Sampling time: AL156 January 16, 10:00 am sharp
+Test Items: Suspended solids, color, conductivity, unstable songin, etc.
+Test results: see attached table
+Findings:
+The water samples were anomalous in a number of indicators when compared to samples from other areas;
+The color of the collected water samples changed back to clear after a week of resting, which is presumed to be related to volatile nystatin;
+The changes in water quality do not present any obvious hazard to humans for the time being, but other subsequent effects due to the action of TD and Tacet Field cannot be ruled out;
+Researcher: 00921
+Project leader: Lu Shen</t>
         </is>
       </c>
     </row>
@@ -18438,8 +18433,8 @@
           <t>Hy vọng gia đình ta thoát được an toàn. (AL 100 năm)
 Giá như ta còn được uống thêm một ly với những đồng đội cũ ở Sư đoàn 1. (AL102)
 Nghe nói năm nay được mùa lớn. Ước gì ta được nếm lại món ăn của mẹ. (AL105)
-Cầu mong chương trình Dragon Thực sự thành công. (AL107)
-KU-Roro B hẳn rất đẹp. Ước gì ta được tận mắt nhìn thấy. (AL120)
+Cầu mong chương trình Rồng Thực sự thành công. (AL107)
+Jinzhou hẳn rất đẹp. Ước gì ta được tận mắt nhìn thấy. (AL120)
 Chúng ta sẽ trở về quê hương. Đây chính là nhà. (AL124)
 Xin hãy để cô ấy quên ta đi. (AL127)
 ......
@@ -18510,7 +18505,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Hi mừng đến với Công Viên Thiên Nhiên Vùng Đầm Lầy, một địa điểm du lịch được xây dựng quanh vùng đất ngập nước, là trạm dừng chân và môi trường sống quan trọng của các loài chim di cư, với hàng chục nghìn con chim trú đông tại đây mỗi năm. Mùa quan sát chim đẹp nhất là từ tháng 10 năm nay đến tháng 3 năm sau.
+          <t>Chào mừng đến với Công Viên Thiên Nhiên Vùng Đầm Lầy, một địa điểm du lịch được xây dựng quanh vùng đất ngập nước, là trạm dừng chân và môi trường sống quan trọng của các loài chim di cư, với hàng chục nghìn con chim trú đông tại đây mỗi năm. Mùa quan sát chim đẹp nhất là từ tháng 10 năm nay đến tháng 3 năm sau.
 Hai loài chim đặc biệt ở đây là ngôi sao địa phương, được gọi chung là cò diệc lông vũ. Chúng là loài chim lội lớn với tính cách hiền lành, không chỉ hòa thuận và giúp đỡ nhau trong gia đình mà còn sẵn sàng gần gũi với con người, luôn giữ vững niềm tin quý giá với họ.
 Vì vậy, khu du lịch khẩn thiết yêu cầu tất cả du khách, xin đừng cho cò diệc lông vũ ăn. Nếu muốn đóng góp vào việc bảo vệ loài chim này, hãy liên hệ với trạm cứu hộ.</t>
         </is>
@@ -18577,7 +18572,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Bức tranh vẽ một gia đình đang vui đùa cùng nhau trông thật ấm cúng. Ở mặt sau có dòng chữ: "Tớ giấu kho báu trong bức tranh này!" Dodget vẽ nguệch ngoạc, ngây thơ nhưng đầy chân thành.</t>
+          <t>Bức tranh vẽ một gia đình đang vui đùa cùng nhau trông thật ấm cúng. Ở mặt sau có dòng chữ: "Tớ giấu kho báu trong bức tranh này!" Nét vẽ nguệch ngoạc, ngây thơ nhưng đầy chân thành.</t>
         </is>
       </c>
     </row>
@@ -18647,7 +18642,7 @@
       <c r="M245" t="inlineStr">
         <is>
           <t>Gửi người đọc bức thư này,
-Ta hy vọng vẫn còn ai đó nhớ đến ta và đang giữ bức tranh ta tìm kiếm. Con trai ta đã vẽ nó từ nhiều năm trước, ghi lại vẻ đẹp của ngôi nhà yên bình ngày nào. Hồi đó, chúng ta thường đến đây để ngắm cây cầu và khu vườn đầy hoa rực rỡ. Con trai ta thích chơi đùa giữa những đóa hoa, ngắm các kỵ sĩ đi qua với quyết tâm anh dũng, mang theo hàng tiếp tế trong khi Dodge những đóa hoa bốc cháy mọc quá nhanh.
+Ta hy vọng vẫn còn ai đó nhớ đến ta và đang giữ bức tranh ta tìm kiếm. Con trai ta đã vẽ nó từ nhiều năm trước, ghi lại vẻ đẹp của ngôi nhà yên bình ngày nào. Hồi đó, chúng ta thường đến đây để ngắm cây cầu và khu vườn đầy hoa rực rỡ. Con trai ta thích chơi đùa giữa những đóa hoa, ngắm các kỵ sĩ đi qua với quyết tâm anh dũng, mang theo hàng tiếp tế trong khi né tránh những đóa hoa bốc cháy mọc quá nhanh.
 Nhưng giờ đây, cây cầu đã gãy, và bên này không còn an toàn nữa. Ta đành phải gửi vợ và con đi tìm nơi trú ẩn, còn mình thì ở lại làm kỵ sĩ, liều mạng ngăn lửa lan rộng. Ta có thể không phải là người đàn ông vĩ đại, nhưng ta muốn trở thành anh hùng trong mắt con trai mình.
 Ta cũng gửi kèm vài bông hoa khô do chính tay ta trồng. Chúng không bắt lửa như những loài khác, và nếu ta sống sót, ta mong được thấy nơi này khôi phục vẻ đẹp xưa mà không còn nỗi sợ hãi về lửa. Nhưng nếu có chuyện gì xảy ra với ta, hãy biết rằng ta tự hào về những gì mình đã làm và mong các người được sống trong hòa bình, thấy những ngọn núi này lại tràn ngập hoa đẹp an toàn.
 Cảm ơn vì đã dành thời gian đọc lá thư này. Suy nghĩ của ta sẽ luôn ở bên các người và nơi này cho đến khi ta gặp lại.</t>
@@ -18727,7 +18722,7 @@
 Theo kết quả phân tích chi tiết dấu vết Âm Thanh, thành phần của những dấu vết cũ rất hỗn tạp, không chỉ có các nhà nghiên cứu thời đó mà còn có vô số dấu vết hoạt động của TD. Với số lượng và sức mạnh trung bình của đội nghiên cứu so với một TD ở quy mô này, e rằng không phải tất cả họ đều biến mất, mà đã hy sinh trong khi làm nhiệm vụ.
 Dù dấu vết Âm Thanh mới rõ ràng hơn nhiều, nhưng vẫn có sự can nhiễu chưa xác định khiến không thể nhận dạng chính xác. Tuy nhiên, dựa vào kết quả so sánh, chúng đều đến từ cùng một người, và khoảng thời gian kéo dài khá lâu, có vẻ như người này đã quay lại đây nhiều lần sau vụ tai nạn. Một tần số tương tự cũng được tìm thấy trong dấu vết Âm Thanh cũ, có thể suy đoán rằng đây chính là người sống sót duy nhất trong đội nghiên cứu. Không những không báo cáo về vụ tai nạn, người sống sót này còn liên tục quay lại đây, vậy rốt cuộc mục đích của hắn là gì?
 ......
-Gần đây, Tacet Field hoạt động bất thường, luôn có cảm giác bất an, như thể có điều gì đó sắp xảy ra...</t>
+Gần đây, Tổ Tacet hoạt động bất thường, luôn có cảm giác bất an, như thể có điều gì đó sắp xảy ra...</t>
         </is>
       </c>
     </row>
@@ -18814,13 +18809,13 @@
 Không...... không được...... Ta phải đi tìm cô bé, ít nhất đừng để nó lớn lên một mình. Ta không thể để bản thân mang thêm tội lỗi nữa.
 ......
 Ngày 12 tháng 5
-Dạo này xảy ra nhiều chuyện quá. Ta lo sợ sẽ có cuộc điều tra chính thức nhắm vào mình, nhưng rồi bỗng nhiên Tacet Field bùng phát và cuộc điều tra bị đình chỉ. May quá!
+Dạo này xảy ra nhiều chuyện quá. Ta lo sợ sẽ có cuộc điều tra chính thức nhắm vào mình, nhưng rồi bỗng nhiên Tổ Tacet bùng phát và cuộc điều tra bị đình chỉ. May quá!
 Kyauk là một cô bé thông minh, chỉ có điều không thông minh ở chỗ nó tin ta quá mức. Khi ta nói mình là chú họ xa, nó tin ngay và trở nên rất thân thiết với ta.
 Ta nghĩ việc chăm sóc Kyaw Kyaw có thể làm vơi bớt mặc cảm tội lỗi, nhưng không ngờ càng tin tưởng ta, nó càng khiến ta thấy tội lỗi hơn. Sau khi trả giá đắt như vậy, không những không lấy được kho báu bí mật, ta còn chìm trong mặc cảm ngày qua ngày, Yu Kuo Xing à Yu Kuo Xing, rốt cuộc ta đã sống thành thứ gì vậy?
 ......
 (Dữ liệu ngày tháng trước đó dường như đã bị hỏng, chỉ còn lại vài câu rời rạc.)
 ......
-Ta đã quay lại trại nghiên cứu để tìm kiếm, nhưng do Tacet Field hoành hành, địa hình khu vực đó đã thay đổi đôi chút và khó lòng tìm ra lối vào như ngày trước. Quá nhiều thời gian đã trôi qua, ta không thể nhớ chính xác vị trí nữa.
+Ta đã quay lại trại nghiên cứu để tìm kiếm, nhưng do Tổ Tacet hoành hành, địa hình khu vực đó đã thay đổi đôi chút và khó lòng tìm ra lối vào như ngày trước. Quá nhiều thời gian đã trôi qua, ta không thể nhớ chính xác vị trí nữa.
 ......
 Ta càng ngày càng không thể đối diện với Kyaw Kyaw, nó giờ đã có thể tự chăm sóc bản thân, hay cứ để nó nghĩ ta đã mất tích.
 ......
@@ -18893,7 +18888,7 @@
       <c r="M248" t="inlineStr">
         <is>
           <t>Ngày: [--02]
-Phòng thí nghiệm C.V. nằm tại một khu vực bỏ hoang trong Đầm Lầy Whining Aix. Cấu trúc chính được xây dựng bằng vật liệu đặc biệt do C.V. phát triển, giúp ngăn chặn sự ăn mòn và hư hại do thời tiết nghiêm trọng. Do đó, tòa nhà vẫn còn tương đối nguyên vẹn. Sau khi đánh giá rủi ro, ủy ban nghiên cứu quyết định sử dụng tầng hầm của địa điểm này để tạo ra một Tacet Field nhân tạo.
+Phòng thí nghiệm C.V. nằm tại một khu vực bỏ hoang trong Whining Aix's Mire. Cấu trúc chính được xây dựng bằng vật liệu đặc biệt do C.V. phát triển, giúp ngăn chặn sự ăn mòn và hư hại do thời tiết nghiêm trọng. Do đó, tòa nhà vẫn còn tương đối nguyên vẹn. Sau khi đánh giá rủi ro, ủy ban nghiên cứu quyết định sử dụng tầng hầm của địa điểm này để tạo ra một Tổ Tacet nhân tạo.
 Một số thiết bị cơ khí bỏ lại bởi C.V. vẫn còn trong môi trường thí nghiệm. Bên ngoài khu vực này, hệ thống chiếu sáng tần số thấp được lắp đặt ở khoảng cách và góc độ đã điều chỉnh, đảm bảo khu vực thí nghiệm luôn được chiếu sáng.
 Trung tâm môi trường thí nghiệm gồm nhiều sợi cáp được bó lại để cố định một thiết bị kim loại hình cầu. Các sợi cáp này truyền tải dữ liệu đầu vào và đầu ra từ bên trong thiết bị. Xung quanh thiết bị hình cầu là các dụng cụ phát hiện tần số cùng thông số kỹ thuật. Những thiết bị này thường được điều khiển bằng núm xoay. Khi xoay núm theo chiều kim đồng hồ, năng lượng điện sẽ khiến khung kim loại tổng hợp quay với tốc độ góc cao quanh thiết bị trung tâm để phát hiện tần số đồng bộ.</t>
         </is>
@@ -18974,16 +18969,16 @@
       <c r="M249" t="inlineStr">
         <is>
           <t>Môi Trường Thí Nghiệm:
-Thí nghiệm số A038 được bố trí trong Tacet Field nhân tạo có thể kiểm soát, kích thước 6m x 6m x 6m. Test môi trường Tacet Field nhân tạo được yêu cầu mỗi 6 giờ.
+Thí nghiệm số A038 được bố trí trong Tổ Tacet nhân tạo có thể kiểm soát, kích thước 6m x 6m x 6m. Kiểm tra môi trường Tổ Tacet nhân tạo được yêu cầu mỗi 6 giờ.
 Để tránh ảnh hưởng đến đối tượng nghiên cứu, nhân viên thí nghiệm khi vào khu vực chỉ định không được mang theo thiết bị và dụng cụ không tương thích với tiêu chuẩn quy định.
-Record Chi Tiết:
-Guan sát ban đầu xác nhận Discord A038, sinh ra trong Tacet Field nhân tạo, có thể tồn tại ổn định.
+Ghi Chép Chi Tiết:
+Quan sát ban đầu xác nhận Tacet Discord A038, sinh ra trong Tổ Tacet nhân tạo, có thể tồn tại ổn định.
 Đối tượng chưa biểu hiện đặc điểm vật lý cụ thể hay mô phỏng hành vi phát âm. Nó không có hình dạng vật lý và chỉ có thể quan sát bằng phương tiện chuyên dụng.
-Current, A038 không thể hiện mục tiêu hành vi rõ ràng: chủ yếu ở trạng thái đứng yên, ít hung hăng và hoạt động.
+Hiện tại, A038 không thể hiện mục tiêu hành vi rõ ràng: chủ yếu ở trạng thái đứng yên, ít hung hăng và hoạt động.
 Do sai lệch đáng kể so với dự đoán, cần tiến hành nghiên cứu sâu hơn.
 Lưu ý: Đối tượng có độ nhạy cao với tần số. Cần kiểm soát nghiêm ngặt các thông số tần số tiêu chuẩn trong khu vực thí nghiệm.
 Do tính chất đặc biệt của A038, chúng ta cần thêm thời gian để thiết lập lại các thông số và ngôn ngữ dữ liệu tương ứng nhằm hiểu sâu hơn về thông tin của nó. Với công nghệ và dữ liệu liên quan hiện tại, quá trình này sẽ mất khá nhiều thời gian.
-Warning: Tuyệt đối cấm rò rỉ thông tin thí nghiệm dưới mọi hình thức.
+Cảnh Báo: Tuyệt đối cấm rò rỉ thông tin thí nghiệm dưới mọi hình thức.
 Nghiêm cấm chụp ảnh hoặc ghi hình đối tượng khi chưa có sự cho phép của Giáo sư Heisen.
 Đây là kết thúc ghi chép quan sát ban đầu.
 Để thu thập thêm thông tin về đối tượng, cần tiến hành các thí nghiệm và phân tích trong tương lai.</t>
@@ -19127,7 +19122,7 @@
       <c r="M251" t="inlineStr">
         <is>
           <t>Ngày: [--08]
-Thí nghiệm đã bước vào giai đoạn cuối, nhưng có vẻ mọi người đều trở nên lười nhác. Ngày càng nhiều đồng nghiệp biến mất không dấu vết. Giáo sư Heisen nói vài người xin nghỉ để về bên gia đình, số khác thì đi nghỉ dài trước khi quay lại. Điều này hoàn toàn không giống phong cách của họ. Previous đây, ai cũng say mê nghiên cứu đến mức không buồn ngủ. Thôi, bỏ qua đi. Thật sự hiếm khi được yên tĩnh như thế này. Trong những đêm dài đằng đẵng, chỉ có khối tối này bầu bạn cùng ta. Không biết từ lúc nào, ngươi đã lớn đến thế và bắt đầu di chuyển. Nhiều bộ phận cơ khí và mảnh kim loại xuất hiện trên người ngươi. Đó là động cơ diesel à? Ta cảm giác như đã thấy nó ở đâu rồi...
+Thí nghiệm đã bước vào giai đoạn cuối, nhưng có vẻ mọi người đều trở nên lười nhác. Ngày càng nhiều đồng nghiệp biến mất không dấu vết. Giáo sư Heisen nói vài người xin nghỉ để về bên gia đình, số khác thì đi nghỉ dài trước khi quay lại. Điều này hoàn toàn không giống phong cách của họ. Trước đây, ai cũng say mê nghiên cứu đến mức không buồn ngủ. Thôi, bỏ qua đi. Thật hiếm khi được yên tĩnh như thế này. Trong những đêm dài đằng đẵng, chỉ có khối tối này bầu bạn cùng ta. Không biết từ lúc nào, ngươi đã lớn đến thế và bắt đầu di chuyển. Nhiều bộ phận cơ khí và mảnh kim loại xuất hiện trên người ngươi. Đó là động cơ diesel à? Ta cảm giác như đã thấy nó ở đâu rồi...
 Hm? Hôm nay ta không được khỏe. Cơ thể nhẹ bẫng như một túi nước, không phải của ta.
 Hôm nay ngươi trông hoạt bát khác thường nhỉ? Ta chưa từng thấy ngươi như thế này bao giờ. Đây hẳn là một khám phá mới. Để ta ghi lại vào nhật ký cá nhân.
 Vật thể hình cầu màu đen tách ra, để lộ bên trong đủ thứ: tấm thép, bánh răng, đồng hồ, mũi khoan khổng lồ, máy dò, đèn pha, chất lỏng xanh, kẹp phẫu thuật, sách dày, áo khoác phòng thí nghiệm trắng, kẹo tan chảy, mèo con dễ thương, màn hình điện tử, và cả những thứ giống như cơ thể người.
@@ -19225,7 +19220,7 @@
 Painter: Tôi cứ nghĩ ông sẽ nổi giận.
 Ma Cui: Tính tôi đã tốt hơn nhiều từ khi con gái tôi ra đời.
 Painter: Cháu bé có vẻ hiền lành và tốt bụng.
-Ma Cui: Not Really. Nó lúc nào cũng dũng cảm.
+Ma Cui: Không hẳn. Nó lúc nào cũng dũng cảm.
 Painter: Cháu không thích cái tên khai sinh của mình, Ma Xiaofang.
 Ma Cui: Điều đó có ý nghĩa gì với ông?
 Painter: Có nghĩa là cháu có thể đang gặp khó khăn khi đối diện với chính mình.
@@ -19309,9 +19304,9 @@
       <c r="M253" t="inlineStr">
         <is>
           <t>Ngày 10 tháng Năm - Đây là nhiệm vụ đầu tiên của tôi với đội tiền trạm, và tôi ngây thơ nghĩ rằng thời tiết ở Wuthering Waves chỉ là bình thường. Nhưng nó còn tồi tệ hơn nhiều so với tưởng tượng.
-Ngày 11 tháng Năm - Chúng tôi được cử đến Norfall Barrens để điều tra năng lượng Threnodian Crownless, nhưng Wuthering Waves chỉ khiến mọi thứ khó khăn hơn. Rainy liên tục làm mờ tầm nhìn, chúng tôi gần như không biết mình đang đi đâu. Đại tướng Jiyan đưa cho chúng tôi một lọ thuốc để ngăn chặn những tiếng thì thầm kỳ lạ trong thời tiết.
+Ngày 11 tháng Năm - Chúng tôi được cử đến Norfall Barrens để điều tra năng lượng Threnodian Crownless, nhưng Wuthering Waves chỉ khiến mọi thứ khó khăn hơn. Mưa liên tục làm mờ tầm nhìn, chúng tôi gần như không biết mình đang đi đâu. Đại tướng Jiyan đưa cho chúng tôi một lọ thuốc để ngăn chặn những tiếng thì thầm kỳ lạ trong thời tiết.
 Ngày 13 tháng Năm - Đội của chúng tôi bắt đầu cảm thấy choáng ngợp khi các thành viên lần lượt ngã xuống. Lần đầu tiên, ý nghĩ rút lui xuất hiện trong đầu tôi. May mắn thay, Đại tướng Jiyan nhận ra sự căng thẳng của chúng tôi và cho phép nghỉ ngơi trong một tòa phế tích qua đêm. Chúng tôi tìm thấy một cuốn sách truyện cười giúp giảm bớt căng thẳng, nhưng Đại tướng Jiyan vẫn có vẻ lo lắng.
-Ngày 20 tháng Năm - Nồng độ Wuthering Waves không còn quan trọng nữa vì mọi dữ liệu đều vô nghĩa. Chúng tôi đang ngạt thở trong môi trường này, và trong trận chiến gần nhất, tất cả đều hy sinh ngoại trừ tôi và Đại tướng Jiyan. Ông đã hy sinh bản thân để cứu tôi khỏi đội quân TD. Tôi không thể làm gì ngoài việc đứng nhìn ông chiến đấu một mình, ngôi sao trên trán ông nhấp nháy vì sử dụng quá nhiều sức mạnh Synergy Giả. Tôi van xin giúp đỡ trong khi núp sau lưng ông, không muốn chết. Cuối cùng, Đại tướng Jiyan quỳ gối trong đống đổ nát, ngọn giáo của ông vẫn đứng vững, cứu sống tôi.</t>
+Ngày 20 tháng Năm - Nồng độ Wuthering Waves không còn quan trọng nữa vì mọi dữ liệu đều vô nghĩa. Chúng tôi đang ngạt thở trong môi trường này, và trong trận chiến gần nhất, tất cả đều hy sinh ngoại trừ tôi và Đại tướng Jiyan. Ông đã hy sinh bản thân để cứu tôi khỏi đội quân TD. Tôi không thể làm gì ngoài việc đứng nhìn ông chiến đấu một mình, ngôi sao trên trán ông nhấp nháy vì sử dụng quá nhiều sức mạnh Resonator. Tôi van xin giúp đỡ trong khi núp sau lưng ông, không muốn chết. Cuối cùng, Đại tướng Jiyan quỳ gối trong đống đổ nát, ngọn giáo của ông vẫn đứng vững, cứu sống tôi.</t>
         </is>
       </c>
     </row>
@@ -19379,9 +19374,9 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>1. Wow, mới thử sữa bò Morri xong mà vị gì lạ quá! Cay nồng, tê tê, lại còn đắng như cỏ, nhưng lại là nguyên liệu hoàn hảo để thay thế cho Salted Milk Tea. Chắc chắn đây sẽ là món "gây sốt" đấy. Nếu ai muốn thử Salted Milk Tea, hãy để lại bình luận để tụi mình tổ chức sự kiện thử nghiệm ở KU-Roro B và có thể đưa vào sản xuất đại trà nhé!
+          <t>1. Wow, mới thử sữa bò Morri xong mà vị gì lạ quá! Cay nồng, tê tê, lại còn đắng như cỏ, nhưng lại là nguyên liệu hoàn hảo để thay thế cho Trà Sữa Muối. Chắc chắn đây sẽ là món "gây sốt" đấy. Nếu ai muốn thử Trà Sữa Muối, hãy để lại bình luận để tụi mình tổ chức sự kiện thử nghiệm ở Jinzhou và có thể đưa vào sản xuất đại trà nhé!
 2. Giờ mình thèm uống thêm ly này quá đi!
-3. Tea Milk Cay Nóng đã trở thành "ma túy" của mình rồi, không thể thiếu được!
+3. Trà Sữa Cay Nóng đã trở thành "ma túy" của mình rồi, không thể thiếu được!
 4. Gia đình mình đăng ký tham gia sự kiện thử nghiệm nhé, cả nhà đều muốn đặt hàng!</t>
         </is>
       </c>
@@ -19454,7 +19449,7 @@
           <t>＞＞＞Biên bản Phòng thí nghiệm CSC
 Tại AL103, một sinh vật chưa xác định được khai quật từ tàn tích Núi Firmament, hình dáng giống rồng thần, dấu hiệu sự sống không rõ ràng, mật danh "Sentinel".
 Mọi loại cảm biến đều không phát hiện được nội tạng bên trong, nghi ngờ là ■■■■■■■.
-Tại AL106, Sentinel được đánh thức bởi ■■■■■■, sở hữu trí thông minh sinh học và có thể giao tiếp. Tư lệnh Jiu Entropy đã có cuộc trò chuyện suôn sẻ với nó và lên kế hoạch phản công Dragon Thực, mở ra bước ngoặt quan trọng trong Chiến tranh Threnody.
+Tại AL106, Sentinel được đánh thức bởi ■■■■■■, sở hữu trí thông minh sinh học và có thể giao tiếp. Tư lệnh Cửu Entropy đã có cuộc trò chuyện suôn sẻ với nó và lên kế hoạch phản công Rồng Thực, mở ra bước ngoặt quan trọng trong Chiến tranh Threnody.
 Tại AL107, Sentinel hỗ trợ con người bắn hạ Crownless tại Norfall Barrens, nghi ngờ có khả năng hấp thụ sức mạnh Threnody. Phân tích dư lượng năng lượng trên chiến trường cho thấy khả năng tồn tại của ■■■■.</t>
         </is>
       </c>
@@ -19529,13 +19524,13 @@
       <c r="M256" t="inlineStr">
         <is>
           <t>Số nhiệm vụ: D12547
-Đội Actions: "Đại Bàng Xám"
+Đội Hành Động: "Đại Bàng Xám"
 Thời gian nhiệm vụ: □□□□□□□□
 Mục tiêu: Feilian Beringal
 Sau đây là nhật ký hành động của tôi:
 Ngay sau khi đến Cổng lớn hướng đông ở Rừng Mù vào giữa trưa, cả đội đã bị phục kích. Chúng tôi bị tấn công bởi những Hoochief điên loạn, chúng tru lên và cắn xé đồng đội của tôi, tiếng la hét vang lên tứ phía. Lo sợ đạn lạc có thể làm thương đồng đội, tất cả chúng tôi chỉ chống trả bằng dao găm và các vũ khí khác.
 Chỉ huy trung đoàn ra lệnh chia quân thành ba nhóm để tạm lánh, và tôi được xếp vào nhóm của chỉ huy. Khi chúng tôi đến điểm tác chiến dự định vào đêm khuya, tất cả đều kiệt sức, nhưng không ai có thể chợp mắt. Chẳng bao lâu sau, tiếng tru của Hoochief lại vang lên từ bên ngoài, chúng cứ kéo đến không ngừng, trong khi binh lính đã hết đạn. Mất phương tiện kháng cự, trưởng nhóm ra lệnh dùng bom phong tỏa hang động, nhưng Hoochief vẫn tràn vào trước khi bom phát nổ, và khi trưởng nhóm cùng con Hoochief cuối cùng gục xuống, bom cũng kích nổ, bịt kín hang động.
-Signal với Huanglong bị cắt đứt, chúng tôi không thể liên lạc với phần còn lại của đội. Bị mắc kẹt trong hang, sức lực dần cạn kiệt, tôi phát hiện một đĩa cứng ẩn trong một hốc đổ nát bên cạnh. Sau khi giải mã, tôi nhận ra đó là thông tin còn sót lại từ viện nghiên cứu thời chiến, ghi lại về một phòng thí nghiệm bí mật ở Huanglong. Tôi cũng muốn nhờ người tìm thấy nhật ký này đến đó để ngăn chặn một thảm kịch như hôm nay tái diễn.
+Tín hiệu với Huanglong bị cắt đứt, chúng tôi không thể liên lạc với phần còn lại của đội. Bị mắc kẹt trong hang, sức lực dần cạn kiệt, tôi phát hiện một đĩa cứng ẩn trong một hốc đổ nát bên cạnh. Sau khi giải mã, tôi nhận ra đó là thông tin còn sót lại từ viện nghiên cứu thời chiến, ghi lại về một phòng thí nghiệm bí mật ở Huanglong. Tôi cũng muốn nhờ người tìm thấy nhật ký này đến đó để ngăn chặn một thảm kịch như hôm nay tái diễn.
 &amp;&amp;&amp;&amp; (12587, 46899)</t>
         </is>
       </c>
@@ -19666,7 +19661,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Tấm cuối là một bức thư viết nguệch ngoạc bằng Dodget chữ trẻ con, mong gia đình đoàn tụ ở thế giới bên kia, cho thấy người viết ban đầu cũng đã chết vì nguyên nhân không rõ, và miêu tả cả làng trở nên điên loạn, cầu xin mọi người dừng hành vi này lại (văn bản tạm thời)</t>
+          <t>Tấm cuối là một bức thư viết nguệch ngoạc bằng nét chữ trẻ con, mong gia đình đoàn tụ ở thế giới bên kia, cho thấy người viết ban đầu cũng đã chết vì nguyên nhân không rõ, và miêu tả cả làng trở nên điên loạn, cầu xin mọi người dừng hành vi này lại (văn bản tạm thời)</t>
         </is>
       </c>
     </row>
@@ -19760,17 +19755,17 @@
         <is>
           <t>CHỦ ĐỀ: Rốt cuộc "vị khách siêu quan trọng" này là ai vậy?
 TurtsStew
-"Guest siêu quan trọng" mà hấp thụ Echoes bằng tay không đâu? Bộ phận Rating Phòng thí nghiệm sẵn sàng trả hậu hĩnh nếu họ hợp tác với dự án của chúng tôi...
+"Vị khách siêu quan trọng" mà hấp thụ Echo bằng tay không đâu? Bộ phận Đánh giá Phòng thí nghiệm sẵn sàng trả hậu hĩnh nếu họ hợp tác với dự án của chúng tôi...
 AzureRiver
-Thật sự á? Bằng tay không? Nope
+Thật á? Bằng tay không? Không đời nào
 KingofSlavingoff
-Chẳng trách Hội đồng muốn gặp họ. Do thế quái nào mà họ làm được vậy?
+Chẳng trách Hội đồng muốn gặp họ. Làm thế quái nào mà họ làm được vậy?
 TurtsStew
 Ôi, nếu được họ làm đối tượng nghiên cứu thì chúng ta sẽ ăn nên làm ra mấy năm liền! Ai biết thông tin gì về họ thì chia sẻ giùm đi
 LILI 
-Nghe đồn hôm nay họ sẽ xuất hiện ở Huaxu Academy đấy
+Nghe đồn hôm nay họ sẽ xuất hiện ở Học viện Huaxu đấy
 1Encounter1
-Hôm nay á??? Nhưng ta đang đi thực địa! Chết tiệt...
+Hôm nay á??? Nhưng tao đang đi thực địa! Chết tiệt...
 PearlyOrchard
 Mấy người phải tôn trọng khách của chúng ta chứ. Đừng có hành xử như lũ điên
 TurtsStew
@@ -19778,7 +19773,7 @@
 LILI 
 Ông nghe ghê quá, turts à
 Galestorm_
-Có ai nhớ vụ tấn công Discord hơn một thế kỷ trước không? Một số Elite Class đã lọt vào thành phố. Lúc đó, vị tướng quân đã dẫn quân đến và tiêu diệt chúng. Chúng ta không biết cách xử lý những Reverberation còn sót lại, suýt nữa gây ra một đợt Waveworn Phenomenon nhỏ…
+Có ai nhớ vụ tấn công Tacet Discord hơn một thế kỷ trước không? Một số Elite Class đã lọt vào thành phố. Lúc đó, vị tướng quân đã dẫn quân đến và tiêu diệt chúng. Chúng ta không biết cách xử lý những Reverberation còn sót lại, suýt nữa gây ra một đợt Waveworn Phenomenon nhỏ…
 Rồi đột nhiên, một người tóc đen mắt vàng xuất hiện từ hư không, hấp thụ toàn bộ năng lượng dư thừa bằng tay không. Cứu nguy rồi biến mất không dấu vết.
 KingofSlavingoff
 Nghe quen quen
@@ -19871,21 +19866,21 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ: Tại sao Bộ phận Rating Phòng thí nghiệm lại tăng ca mỗi ngày?
+          <t>CHỦ ĐỀ: Tại sao Bộ phận Đánh giá Phòng thí nghiệm lại tăng ca mỗi ngày?
 LILI 
-Mấy người ở Bộ phận Rating Phòng thí nghiệm tăng ca mỗi ngày!! Do gì vậy? Để dồn ép chúng ta cũng phải tăng ca theo à?
+Mấy người ở Bộ phận Đánh giá Phòng thí nghiệm tăng ca mỗi ngày!! Làm gì vậy? Để dồn ép chúng ta cũng phải tăng ca theo à?
 KingofSlavingoff
 Ừ, sao họ làm khuya thế? Có được trả thêm tiền tăng ca không?
 Greenriver2727
-Bộ phận Rating Phòng thí nghiệm dù được trợ cấp thêm vẫn không đạt chỉ tiêu! Đừng nói đến mấy ông ở bộ phận nước và điện nữa - toàn đồ vớ vẩn
+Bộ phận Đánh giá Phòng thí nghiệm dù được trợ cấp thêm vẫn không đạt chỉ tiêu! Đừng nói đến mấy ông ở bộ phận nước và điện nữa - toàn đồ vớ vẩn
 LILI 
-Thật sự á? How did you know? Bộ phận Rating Phòng thí nghiệm có bận rộn vì phải đuổi kịp tiến độ quý này không?
+Thật á? Sao cậu biết? Bộ phận Đánh giá Phòng thí nghiệm có bận rộn vì phải đuổi kịp tiến độ quý này không?
 TurtsStew
 Nghe nói họ còn đề nghị thử nghiệm sản phẩm mới nhất của Liu Qing để xem có cải thiện hiệu suất làm việc không. Nghe tên gì đó như... Lemonblast?
 KingofSlavingoff
-Ta nghe nói về thứ đó rồi! Chỉ cần một viên là tỉnh táo cả ngày!
+Tao nghe nói về thứ đó rồi! Chỉ cần một viên là tỉnh táo cả ngày!
 OrphanAccount11
-Tôi thề là nó hiệu quả! Nhờ có Blasting Mints mà tôi đã hoàn thành ba bài nghiên cứu liên tiếp! Nhắn riêng tôi để mua với giá ưu đãi, ai đến trước được phục vụ trước. Mọi người Together vượt qua nào!
+Tôi thề là nó hiệu quả! Nhờ có Blasting Mints mà tôi đã hoàn thành ba bài nghiên cứu liên tiếp! Nhắn riêng tôi để mua với giá ưu đãi, ai đến trước được phục vụ trước. Cùng nhau vượt qua nào!
 [ĐÍNH KÈM: Lemonblast.jpg]
 Admin_Willow
 Nghiêm cấm quảng cáo sản phẩm y tế thử nghiệm tại đây. Vi phạm sẽ bị khóa tài khoản ngay lập tức.
@@ -19970,17 +19965,17 @@
         <is>
           <t>[
 Nhập Liệu]  
-Discord  
+Tacet Discord  
 [Các Loại Đã Biết]  
 Whisperin, Howler, Tranquilite, Clamorling, Staticoid
-[Tổng Guan]  
-Kể từ khi Hiện Tượng Waveworn xuất hiện, nhân loại đã không ngừng nghiên cứu bí ẩn mang tên Discord. 
+[Tổng Quan]  
+Kể từ khi Hiện Tượng Waveworn xuất hiện, nhân loại đã không ngừng nghiên cứu bí ẩn mang tên Tacet Discord. 
 Những thực thể này được coi là nguồn gốc của sự hủy diệt và hiện thân của năng lượng hỗn loạn. Dù đã nghiên cứu kỹ lưỡng, hiểu biết của chúng ta vẫn còn nhiều lỗ hổng do thiếu thông tin về cấu trúc của chúng. 
-Theo thời gian, khoảng trống kiến thức này sẽ ngày càng lớn, dẫn đến sự suy thoái dần dần và cuối cùng là sự diệt vong của các Discord. Để duy trì sự tồn tại, chúng có bản năng tiêu thụ và hòa nhập với các tần số khác, trong một cuộc chiến không ngừng nhằm duy trì sự sống.
-[Bổ Sung Lục: Reverberance]  
-Khi một Discord bị tiêu diệt, tần số của nó không biến mất ngay lập tức. Thay vào đó, chúng sẽ phân rã từ từ theo thời gian, cho phép thu thập và sử dụng. 
-Khi tích trữ đủ tần số, chúng ta có thể khai thác để tái tạo khả năng của Discord ban đầu. 
-Năng lượng còn sót lại này, có thể mô phỏng sức mạnh của thực thể đã bị đánh bại, được gọi là Reverberance — một tài sản quý giá cần được thu thập và bảo quản cẩn thận trong kho lưu trữ của phòng thí nghiệm.</t>
+Theo thời gian, khoảng trống kiến thức này sẽ ngày càng lớn, dẫn đến sự suy thoái dần dần và cuối cùng là sự diệt vong của các Tacet Discord. Để duy trì sự tồn tại, chúng có bản năng tiêu thụ và hòa nhập với các tần số khác, trong một cuộc chiến không ngừng nhằm duy trì sự sống.
+[Phụ Lục: Dư Âm]  
+Khi một Tacet Discord bị tiêu diệt, tần số của nó không biến mất ngay lập tức. Thay vào đó, chúng sẽ phân rã từ từ theo thời gian, cho phép thu thập và sử dụng. 
+Khi tích trữ đủ tần số, chúng ta có thể khai thác để tái tạo khả năng của Tacet Discord ban đầu. 
+Năng lượng còn sót lại này, có thể mô phỏng sức mạnh của thực thể đã bị đánh bại, được gọi là Dư Âm — một tài sản quý giá cần được thu thập và bảo quản cẩn thận trong kho lưu trữ của phòng thí nghiệm.</t>
         </is>
       </c>
     </row>
@@ -20062,24 +20057,24 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Introduction
-Huaxu Academy, trung tâm nghiên cứu khoa học danh tiếng tại KU-Roro B, tự hào với bề dày truyền thống học thuật và công nghệ tiên tiến.
-Là một chi nhánh của Huaxu Academy Huanglong, nơi đây đã đạt được nhiều thành tựu nghiên cứu đột phá nhờ tập trung phát triển khoa học công nghệ trong bối cảnh cuộc chiến chống lại Discord vẫn còn tiếp diễn.
-Học viện duy trì tính độc lập cao trong các hoạt động nghiên cứu, đồng thời tích cực trao đổi học thuật với các tổ chức khác trong và ngoài Huanglong. Trên thực tế, nơi đây từng là đối tác chủ chốt của Tòa án Savantae. Gồm bốn khoa chính, mỗi khoa có chức năng chuyên biệt, Huaxu Academy tiến hành các dự án nghiên cứu song song và hợp tác.
-Các nhóm dự án đặc biệt cũng được thành lập để giải quyết những thách thức lớn khi cần. Trong khi hiệu trưởng phụ trách công tác hành chính, Home Nghiên Cứu Main đảm nhiệm vai trò lãnh đạo học thuật của học viện.
+          <t>Giới thiệu
+Học viện Huaxu, trung tâm nghiên cứu khoa học danh tiếng tại Jinzhou, tự hào với bề dày truyền thống học thuật và công nghệ tiên tiến.
+Là một chi nhánh của Học viện Huaxu Huanglong, nơi đây đã đạt được nhiều thành tựu nghiên cứu đột phá nhờ tập trung phát triển khoa học công nghệ trong bối cảnh cuộc chiến chống lại Tacet Discord vẫn còn tiếp diễn.
+Học viện duy trì tính độc lập cao trong các hoạt động nghiên cứu, đồng thời tích cực trao đổi học thuật với các tổ chức khác trong và ngoài Huanglong. Trên thực tế, nơi đây từng là đối tác chủ chốt của Tòa án Savantae. Gồm bốn khoa chính, mỗi khoa có chức năng chuyên biệt, Học viện Huaxu tiến hành các dự án nghiên cứu song song và hợp tác.
+Các nhóm dự án đặc biệt cũng được thành lập để giải quyết những thách thức lớn khi cần. Trong khi hiệu trưởng phụ trách công tác hành chính, Nhà Nghiên Cứu Chính đảm nhiệm vai trò lãnh đạo học thuật của học viện.
 Các khoa
 Khoa Nghiên Cứu Dị Thường:
-Khoa Nghiên Cứu Dị Thường nghiên cứu và phân tích các hiện tượng bất thường, xây dựng lý thuyết dựa trên những sự kiện này và đề ra các biện pháp phòng ngừa. Bao gồm mô hình mạng lưới Đèn Hiệu Synergy và nghiên cứu về Qi hậu Wuther tại KU-Roro B.
+Khoa Nghiên Cứu Dị Thường nghiên cứu và phân tích các hiện tượng bất thường, xây dựng lý thuyết dựa trên những sự kiện này và đề ra các biện pháp phòng ngừa. Bao gồm mô hình mạng lưới Đèn Hiệu Cộng Hưởng và nghiên cứu về Khí hậu Wuther tại Jinzhou.
 Các ngành chính: Wuther học, Âm sinh thái Tàn tích.
-Khoa Review Phòng Thí Nghiệm:
-Khoa Review Phòng Thí Nghiệm phân tích và mô phỏng các dị thường bằng nhiều lý thuyết khác nhau để tìm ra giải pháp tối ưu. Họ cũng thiết kế cấu trúc bên trong của Đèn Hiệu Synergy và Terminal nhằm sử dụng hiệu quả.
+Khoa Đánh Giá Phòng Thí Nghiệm:
+Khoa Đánh Giá Phòng Thí Nghiệm phân tích và mô phỏng các dị thường bằng nhiều lý thuyết khác nhau để tìm ra giải pháp tối ưu. Họ cũng thiết kế cấu trúc bên trong của Đèn Hiệu Cộng Hưởng và Thiết bị đầu cuối nhằm sử dụng hiệu quả.
 Các ngành chính: -
 Khoa An Toàn:
-Khoa An Toàn nghiên cứu và hỗ trợ tiêu diệt Discord. Họ thiết kế mô hình Weapons Tacetite cho Synergy Giả và chế tạo trang bị đối phó cho dân thường.
-Các ngành chính: Âm sinh thái Discord, Synergy học.
-Khoa Resources:
-Khoa Resources chủ yếu nghiên cứu các chất Waveworn, xử lý vật liệu thực địa thành mẫu nghiên cứu và đóng góp cho Khoa Review Phòng Thí Nghiệm cùng Khoa An Toàn.
-Các ngành chính: Vật liệu Wuther, Âm sinh thái Discord, Âm sinh thái Thực vật.</t>
+Khoa An Toàn nghiên cứu và hỗ trợ tiêu diệt Tacet Discord. Họ thiết kế mô hình Vũ khí Tacetite cho Resonator và chế tạo trang bị đối phó cho dân thường.
+Các ngành chính: Âm sinh thái Tacet Discord, Cộng Hưởng học.
+Khoa Tài Nguyên:
+Khoa Tài Nguyên chủ yếu nghiên cứu các chất Waveworn, xử lý vật liệu thực địa thành mẫu nghiên cứu và đóng góp cho Khoa Đánh Giá Phòng Thí Nghiệm cùng Khoa An Toàn.
+Các ngành chính: Vật liệu Wuther, Âm sinh thái Tacet Discord, Âm sinh thái Thực vật.</t>
         </is>
       </c>
     </row>
@@ -20147,10 +20142,10 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Ở góc dưới bên trái, giữa vô số tấm bia đá, có một tấm vẫn còn nguyên vẹn đáng kinh ngạc dù thời gian và thiên nhiên đã bào mòn. Nó kể lại lịch sử thành lập KU-Roro B.
+          <t>Ở góc dưới bên trái, giữa vô số tấm bia đá, có một tấm vẫn còn nguyên vẹn đáng kinh ngạc dù thời gian và thiên nhiên đã bào mòn. Nó kể lại lịch sử thành lập Jinzhou.
 "Quân đội sẵn sàng hủy diệt khi trăng đen che khuất mặt trời…"
-"…Holda trận chiến, một vị khách mắt vàng xuất hiện trên bầu trời mờ ảo. Quân ta giơ kiếm chờ đợi, trong khi rồng ngọc bay lượn trên đầu…"
-"…Dù khao khát trở về nhà, những người lính nghĩa vụ này vẫn không nao núng trong việc bảo vệ mảnh đất của mình. Và thế là, trong thế giới đầy ải quan này, KU-Roro B đã được xây dựng và đài kỷ niệm này được dựng lên để mãi mãi ghi nhớ sự kiện trọng đại này…"</t>
+"…Giữa trận chiến, một vị khách mắt vàng xuất hiện trên bầu trời mờ ảo. Quân ta giơ kiếm chờ đợi, trong khi rồng ngọc bay lượn trên đầu…"
+"…Dù khao khát trở về nhà, những người lính nghĩa vụ này vẫn không nao núng trong việc bảo vệ mảnh đất của mình. Và thế là, trong thế giới đầy ải quan này, Jinzhou đã được xây dựng và đài kỷ niệm này được dựng lên để mãi mãi ghi nhớ sự kiện trọng đại này…"</t>
         </is>
       </c>
     </row>
@@ -20254,34 +20249,34 @@
           <t>19/6
 Hôm nay, một người đàn ông lạ đến làng ta. Ông ấy bảo gọi ông là anh cũng được, nếu ta không phiền. Ông ấy rất thân thiện, nhưng không hiểu sao lại khác biệt với dân làng. Ông ấy dường như biết rất nhiều về ta, thậm chí còn nói chúng ta là "cùng một loại".
 Ông ấy kể cho ta nghe một câu chuyện cổ tích kỳ lạ. Kết thúc của câu chuyện hơi đáng sợ... nhưng thực tế còn đáng sợ hơn, ông ấy nói. Rồi ông hỏi: "Nếu con là chú cừu đen nhỏ, con sẽ làm gì?"
-Ta chưa kịp trả lời thì ông ấy đã rời đi với câu nói bí ẩn: "See you next time."
+Ta chưa kịp trả lời thì ông ấy đã rời đi với câu nói bí ẩn: "Hẹn gặp lại lần sau."
 Ta kể với cha, nhưng cha bảo chưa từng có ai như thế đến làng ta cả...
 Ông ấy là ai nhỉ?
 ...
 20/7
-Gomen... Ta xin lỗi lắm... (vết nước mắt nhòe nhoẹt)
-Giá như ta không yếu đuối thế, đã có thể đuổi những Discord ấy đi... Giá như Sissi không phải bảo vệ ta...
-Right có cách nào đó. Cha nói ta có thể điều khiển tần số của Discord... và cả con người.
+Xin lỗi... Ta xin lỗi lắm... (vết nước mắt nhòe nhoẹt)
+Giá như ta không yếu đuối thế, đã có thể đuổi những Tacet Discord ấy đi... Giá như Sissi không phải bảo vệ ta...
+Phải có cách nào đó. Cha nói ta có thể điều khiển tần số của Tacet Discord... và cả con người.
 Sissi, ta xin lỗi vì giờ em thành ra thế này... Nhưng chỉ là tạm thời thôi. Ta sẽ làm mọi thứ để em trở lại như xưa. Ta biết em vẫn nghe thấy mà.
 Cha đã hứa với ta. Ông ấy chắc chắn sẽ tìm ra cách giúp.
 ...
 17/12
 Đã ba tháng kể từ vụ đó. Cha dường như quên mất ta vẫn viết nhật ký... Ông ấy đưa cuốn sổ này cho ta, nhưng nếu biết ta viết tất cả ra, chắc ông ấy sẽ giận lắm.
-Ông ấy bắt ta làm theo lời ông, dùng sức mạnh của mình để tái tổ hợp tần số của Discord.
-Nhưng nếu ai đó biết sự thật — rằng Sissi, người mất tích, thực ra đã chết khi bảo vệ ta, và rồi ta biến em thành một Discord kinh hoàng...
+Ông ấy bắt ta làm theo lời ông, dùng sức mạnh của mình để tái tổ hợp tần số của Tacet Discord.
+Nhưng nếu ai đó biết sự thật — rằng Sissi, người mất tích, thực ra đã chết khi bảo vệ ta, và rồi ta biến em thành một Tacet Discord kinh hoàng...
 Họ sẽ coi ta là quái vật. Ta sẽ bị ruồng bỏ, và chẳng ai hiểu hay chấp nhận được sức mạnh của ta... Không ai cả... ngoại trừ Ông ấy.
 Nhưng liệu người chết có thật sự trở về nhờ thao túng tần số? Và nếu có, những linh hồn tan vỡ kia sẽ ra sao khi bị giam cầm trong thân xác mới?
 Ta thực sự không biết...
 ...
 8/2
-Ngày qua ngày, ta càng thấy bất an. Villager cứ biến mất dần, còn những Discord mà cha mang về...
+Ngày qua ngày, ta càng thấy bất an. Dân làng cứ biến mất dần, còn những Tacet Discord mà cha mang về...
 Ta không thể thoát khỏi cảm giác có điều gì đó rất sai trái. Nhưng ta bị mắc kẹt, như bướm đêm lao vào lửa, không thể thoát khỏi con đường tối tăm này.
 Ta không biết cha đã làm gì... Chắc hẳn là điều gì đó khủng khiếp lắm mới khiến không khí căng thẳng và bất an như thế này. Ta không được phép ra ngoài nữa, và khi hỏi lý do, ông ấy chỉ lướt qua.
 Nếu cái giá cho ước nguyện của ta là thêm máu đổ...
 Ta...
 ...
 (Không ghi ngày)
-Villager đã bao vây nhà ta. Chắc họ đã biết hết rồi.
+Dân làng đã bao vây nhà ta. Chắc họ đã biết hết rồi.
 Kẻ sát nhân... giờ họ gọi ta như thế sao? Hay cả cha ta nữa? Đến lúc này, có khác gì đâu?
 Sau tất cả những gì đã xảy ra... Có ai đến cứu ta không?
 Nếu ta phải trả giá cho làng Qichi...
@@ -20361,13 +20356,13 @@
       <c r="M265" t="inlineStr">
         <is>
           <t>03.12
-Hi cậu, mình là ███! Mình vừa tìm được ngôi nhà mới và bác tốt bụng đã tặng mình cuốn sổ thật ngầu này để viết. Home cũ của chúng mình bị quái vật dọa nên phải đi thật xa để tìm nơi ở mới. Mình có hỏi bác là bao giờ bố mẹ sẽ đuổi kịp, bác bảo sắp thôi! Háo hức lắm, mong bố mẹ mau đến đây. Nơi mới này nắng thật đẹp và có cây đào to lắm. Nhưng ít người ở đây đi lên thành phố lớn. Mình chỉ mong bố mẹ nhanh tìm được mình thôi.
+Chào cậu, mình là ███! Mình vừa tìm được ngôi nhà mới và bác tốt bụng đã tặng mình cuốn sổ thật ngầu này để viết. Nhà cũ của chúng mình bị quái vật dọa nên phải đi thật xa để tìm nơi ở mới. Mình có hỏi bác là bao giờ bố mẹ sẽ đuổi kịp, bác bảo sắp thôi! Háo hức lắm, mong bố mẹ mau đến đây. Nơi mới này nắng thật đẹp và có cây đào to lắm. Nhưng ít người ở đây đi lên thành phố lớn. Mình chỉ mong bố mẹ nhanh tìm được mình thôi.
 ...
 12.5
 Hôm nay là sinh nhật mình! Mọi người đối xử tốt với mình quá, bảo mình là bùa may mắn vì có thể đuổi được lũ quái vật đáng ghét. Mình vui lắm, ai cũng quý mình. Có bánh, có mì, còn được quà nữa! Nhưng đã lâu lắm rồi mình chưa gặp bố mẹ, mong các người ấy mau về. Liệu họ có về không nhỉ?
 ...
 05 tháng 12
-Hôm nay là sinh nhật lần thứ tư của mình ở đây, và trưởng làng chính thức nhận mình làm con gái. Nhưng trước đó, mọi người đã chăm sóc mình và chia sẻ những bữa ăn ngon rồi. Bố bảo mình là đứa trẻ của làng Qichi, và mình nên cảm thấy may mắn. Mình thật sự rất hạnh phúc khi được mọi người yêu thương. Dù sức mạnh của mình vẫn còn nhỏ, mình sẽ cố hết sức bảo vệ làng khỏi bị Discord xâm chiếm!</t>
+Hôm nay là sinh nhật lần thứ tư của mình ở đây, và trưởng làng chính thức nhận mình làm con gái. Nhưng trước đó, mọi người đã chăm sóc mình và chia sẻ những bữa ăn ngon rồi. Bố bảo mình là đứa trẻ của làng Qichi, và mình nên cảm thấy may mắn. Mình thật sự rất hạnh phúc khi được mọi người yêu thương. Dù sức mạnh của mình vẫn còn nhỏ, mình sẽ cố hết sức bảo vệ làng khỏi bị Tacet Discord xâm chiếm!</t>
         </is>
       </c>
     </row>
@@ -20440,9 +20435,9 @@
         <is>
           <t>"Liệu cách này có thật sự hiệu quả không? Nếu được, ước gì ta có thể đứng dậy lần nữa..."
 "Ta muốn tiền! Ta muốn đủ tiền để sống cả đời!"
-"Bravo Cảm ơn ngài □□! Chân ta đã thực sự lành rồi!"
+"Tuyệt vời! Cảm ơn ngài □□! Chân ta đã thực sự lành rồi!"
 "Không... Mẹ vừa mất và để lại cho ta chút tiền, nhưng ta không muốn ước nguyện thành hiện thực bằng thứ □□□ này! Ta muốn mẹ trở lại! Ta muốn □□□ trở lại!"
-"Kỳ lạ... Nó đã khiến ta mạnh mẽ hơn, nhưng dạo gần đây ta lại yếu dần, và không thể □□□ cơ thể nếu thiếu □□□... Right chăng vì ta chưa hiến tế đủ □□□..."
+"Kỳ lạ... Nó đã khiến ta mạnh mẽ hơn, nhưng dạo gần đây ta lại yếu dần, và không thể □□□ cơ thể nếu thiếu □□□... Phải chăng vì ta chưa hiến tế đủ □□□..."
 "□□□ làm ơn, làm ơn đừng lấy đi ước nguyện của ta! TA SẼ DÂNG BẤT CỨ THỨ GÌ NGƯƠI MUỐN!"
 "Liệu thứ □□□ này có thật sự là điều tất cả chúng ta □□□ hằng mong muốn?"</t>
         </is>
@@ -20522,17 +20517,17 @@
         <is>
           <t>[
 Nhập Liệu]  
-Discord  
+Tacet Discord  
 [Các Loại Đã Biết]  
 Whisperin, Howler, Tranquilite, Clamorling, Staticoid
-[Tổng Guan]  
-Kể từ khi Hiện Tượng Waveworn xuất hiện, nhân loại đã không ngừng nghiên cứu bí ẩn mang tên Discord. 
+[Tổng Quan]  
+Kể từ khi Hiện Tượng Waveworn xuất hiện, nhân loại đã không ngừng nghiên cứu bí ẩn mang tên Tacet Discord. 
 Những thực thể này được coi là nguồn gốc của sự hủy diệt và hiện thân của năng lượng hỗn loạn. Dù đã nghiên cứu kỹ lưỡng, hiểu biết của chúng ta vẫn còn nhiều lỗ hổng do thiếu thông tin về cấu trúc của chúng. 
-Theo thời gian, khoảng trống kiến thức này sẽ ngày càng lớn, dẫn đến sự suy thoái dần dần và cuối cùng là sự diệt vong của các Discord. Để duy trì sự tồn tại, chúng có bản năng tiêu thụ và hòa nhập với các tần số khác, trong một cuộc chiến không ngừng nhằm duy trì sự sống.
-[Bổ Sung Lục: Reverberance]  
-Khi một Discord bị tiêu diệt, tần số của nó không biến mất ngay lập tức. Thay vào đó, chúng sẽ phân rã từ từ theo thời gian, cho phép thu thập và sử dụng. 
-Khi tích trữ đủ tần số, chúng ta có thể khai thác để tái tạo khả năng của Discord ban đầu. 
-Năng lượng còn sót lại này, có thể mô phỏng sức mạnh của thực thể đã bị đánh bại, được gọi là Reverberance — một tài sản quý giá cần được thu thập và bảo quản cẩn thận trong kho lưu trữ của phòng thí nghiệm.</t>
+Theo thời gian, khoảng trống kiến thức này sẽ ngày càng lớn, dẫn đến sự suy thoái dần dần và cuối cùng là sự diệt vong của các Tacet Discord. Để duy trì sự tồn tại, chúng có bản năng tiêu thụ và hòa nhập với các tần số khác, trong một cuộc chiến không ngừng nhằm duy trì sự sống.
+[Phụ Lục: Dư Âm]  
+Khi một Tacet Discord bị tiêu diệt, tần số của nó không biến mất ngay lập tức. Thay vào đó, chúng sẽ phân rã từ từ theo thời gian, cho phép thu thập và sử dụng. 
+Khi tích trữ đủ tần số, chúng ta có thể khai thác để tái tạo khả năng của Tacet Discord ban đầu. 
+Năng lượng còn sót lại này, có thể mô phỏng sức mạnh của thực thể đã bị đánh bại, được gọi là Dư Âm — một tài sản quý giá cần được thu thập và bảo quản cẩn thận trong kho lưu trữ của phòng thí nghiệm.</t>
         </is>
       </c>
     </row>
@@ -20616,24 +20611,24 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Tên: Huaxu Academy, KU-Roro B Campus
-[Introduction]
-Huaxu Academy, một trung tâm nghiên cứu khoa học danh tiếng tại KU-Roro B, tự hào với bề dày học thuật và công nghệ tiên tiến hàng đầu.
-Là một chi nhánh của Huaxu Academy Huanglong, nơi đây đã tạo ra vô số thành tựu nghiên cứu đột phá nhờ tập trung phát triển khoa học công nghệ trong bối cảnh cuộc chiến chống lại Discord vẫn còn tiếp diễn.
-Học viện duy trì tính độc lập cao trong các hoạt động nghiên cứu, đồng thời tích cực trao đổi học thuật với các tổ chức khác trong và ngoài Huanglong. Trên thực tế, nơi đây từng là đối tác chủ chốt của Tòa án Savantae. Gồm bốn khoa chính, mỗi khoa có chức năng chuyên biệt, Huaxu Academy tiến hành các dự án nghiên cứu song song và hợp tác.
+          <t>Tên: Học viện Huaxu, Cơ sở Jinzhou
+[Giới thiệu]
+Học viện Huaxu, một trung tâm nghiên cứu khoa học danh tiếng tại Jinzhou, tự hào với bề dày học thuật và công nghệ tiên tiến hàng đầu.
+Là một chi nhánh của Học viện Huaxu Huanglong, nơi đây đã tạo ra vô số thành tựu nghiên cứu đột phá nhờ tập trung phát triển khoa học công nghệ trong bối cảnh cuộc chiến chống lại Tacet Discord vẫn còn tiếp diễn.
+Học viện duy trì tính độc lập cao trong các hoạt động nghiên cứu, đồng thời tích cực trao đổi học thuật với các tổ chức khác trong và ngoài Huanglong. Trên thực tế, nơi đây từng là đối tác chủ chốt của Tòa án Savantae. Gồm bốn khoa chính, mỗi khoa có chức năng chuyên biệt, Học viện Huaxu tiến hành các dự án nghiên cứu song song và hợp tác.
 Các nhóm dự án đặc biệt cũng được thành lập để giải quyết những thách thức lớn khi cần. Trong khi hiệu trưởng phụ trách công tác hành chính, thì Trưởng Điều tra viên đóng vai trò lãnh đạo học thuật của học viện.
 [Các khoa]
 Khoa Nghiên cứu Dị thường:
-Khoa Nghiên cứu Dị thường nghiên cứu và phân tích các hiện tượng bất thường, xây dựng lý thuyết dựa trên những sự kiện này và đề ra các biện pháp phòng ngừa. Bao gồm mô hình mạng lưới Đèn Cảm Ứng và nghiên cứu Qi hậu Wuther tại KU-Roro B.
+Khoa Nghiên cứu Dị thường nghiên cứu và phân tích các hiện tượng bất thường, xây dựng lý thuyết dựa trên những sự kiện này và đề ra các biện pháp phòng ngừa. Bao gồm mô hình mạng lưới Đèn Cảm Ứng và nghiên cứu Khí hậu Wuther tại Jinzhou.
 Các ngành chính: Wuther học, Âm sinh thái Tàn dư.
-Khoa Rating Phòng thí nghiệm:
-Khoa Rating Phòng thí nghiệm phân tích và mô phỏng các dị thường bằng các lý thuyết khác nhau để tìm ra giải pháp tối ưu. Họ cũng thiết kế cấu trúc bên trong của Đèn Cảm Ứng và Terminal để sử dụng hiệu quả.
+Khoa Đánh giá Phòng thí nghiệm:
+Khoa Đánh giá Phòng thí nghiệm phân tích và mô phỏng các dị thường bằng các lý thuyết khác nhau để tìm ra giải pháp tối ưu. Họ cũng thiết kế cấu trúc bên trong của Đèn Cảm Ứng và Thiết bị đầu cuối để sử dụng hiệu quả.
 Các ngành chính: -
 Khoa An ninh:
-Khoa An ninh nghiên cứu và hỗ trợ tiêu diệt Discord. Họ thiết kế mô hình Weapons Tacetite cho Synergy Giả và tạo ra các thiết bị đối phó cho dân thường.
-Các ngành chính: Âm sinh thái TD, Synergy học.
+Khoa An ninh nghiên cứu và hỗ trợ tiêu diệt Tacet Discord. Họ thiết kế mô hình Vũ khí Tacetite cho Resonator và tạo ra các thiết bị đối phó cho dân thường.
+Các ngành chính: Âm sinh thái TD, Cộng Hưởng học.
 Khoa Tài nguyên:
-Khoa Tài nguyên chủ yếu nghiên cứu các chất Waveworn, xử lý vật liệu thực địa thành mẫu nghiên cứu và đóng góp cho Khoa Rating Phòng thí nghiệm và An ninh.
+Khoa Tài nguyên chủ yếu nghiên cứu các chất Waveworn, xử lý vật liệu thực địa thành mẫu nghiên cứu và đóng góp cho Khoa Đánh giá Phòng thí nghiệm và An ninh.
 Các ngành chính: Vật liệu Wuther, Âm sinh thái TD, Âm sinh thái Thực vật.</t>
         </is>
       </c>
@@ -20743,49 +20738,49 @@
       <c r="M269" t="inlineStr">
         <is>
           <t>Tóm tắt: 
-NovaFei là một bệnh truyền nhiễm cấp tính không có phương pháp điều trị hiệu quả, chủ yếu ảnh hưởng đến trẻ em dưới sáu tuổi. Bệnh có khả năng lây lan cao với các triệu chứng nghiêm trọng bao gồm sốt, đau nhức chân tay và teo cơ. Để đối phó với căn bệnh này, một loại vắc-xin sống giảm độc lực đã được phát triển và vượt qua giai đoạn thử nghiệm lâm sàng giai đoạn III vào &lt;color=#ffd12f&gt;16 tháng 6 lúc 3 giờ chiều&lt;/color&gt;. Ban Y tế đã thành lập một đội ngũ chuyên trách để phát triển loại vắc-xin này. Report này nhằm phân tích tiến trình nghiên cứu vắc-xin và cung cấp những hiểu biết giá trị cho các nghiên cứu tiếp theo. Result cho thấy hiệu quả miễn dịch đầy hứa hẹn, biến loại vắc-xin này thành giải pháp tiềm năng trong việc ngăn ngừa lây nhiễm NovaFei.
+NovaFei là một bệnh truyền nhiễm cấp tính không có phương pháp điều trị hiệu quả, chủ yếu ảnh hưởng đến trẻ em dưới sáu tuổi. Bệnh có khả năng lây lan cao với các triệu chứng nghiêm trọng bao gồm sốt, đau nhức chân tay và teo cơ. Để đối phó với căn bệnh này, một loại vắc-xin sống giảm độc lực đã được phát triển và vượt qua giai đoạn thử nghiệm lâm sàng giai đoạn III vào &lt;color=#ffd12f&gt;16 tháng 6 lúc 3 giờ chiều&lt;/color&gt;. Ban Y tế đã thành lập một đội ngũ chuyên trách để phát triển loại vắc-xin này. Báo cáo này nhằm phân tích tiến trình nghiên cứu vắc-xin và cung cấp những hiểu biết giá trị cho các nghiên cứu tiếp theo. Kết quả cho thấy hiệu quả miễn dịch đầy hứa hẹn, biến loại vắc-xin này thành giải pháp tiềm năng trong việc ngăn ngừa lây nhiễm NovaFei.
 1. Ứng dụng sơ bộ phương pháp phát hiện kháng thể trung hòa đối với giả virus NovaFei
 2. Hiệu quả của vắc-xin sống giảm độc lực chống lại giả virus NovaFei qua đường tiêm
-3. Report thử nghiệm lâm sàng về việc sử dụng đường uống vắc-xin sống giảm độc lực "Sugar Pearl" chống lại giả virus NovaFei
+3. Báo cáo thử nghiệm lâm sàng về việc sử dụng đường uống vắc-xin sống giảm độc lực "Sugar Pearl" chống lại giả virus NovaFei
 ... 
-Bổ Sung lục 1: Profile đăng ký tham gia thử nghiệm lâm sàng (i) 
+Phụ lục 1: Hồ sơ đăng ký tham gia thử nghiệm lâm sàng (i) 
 Số đăng ký: CTR302001 
 Tên: Xiangli Yan
-Gender: Nữ 
+Giới tính: Nữ 
 Tuổi: 29 
 Tình trạng: Khỏe mạnh, không mắc bệnh di truyền. 
-Giai đoạn thử nghiệm: Trial lâm sàng giai đoạn I 
+Giai đoạn thử nghiệm: Thử nghiệm lâm sàng giai đoạn I 
 Số đăng ký: CTR302002 
 Tên: Xiangli Yao 
-Gender: Male 
+Giới tính: Nam 
 Tuổi: 7 tháng 
 Tình trạng: Khỏe mạnh, không mắc bệnh di truyền.
-Giai đoạn thử nghiệm: Trial lâm sàng giai đoạn I 
+Giai đoạn thử nghiệm: Thử nghiệm lâm sàng giai đoạn I 
 ... 
 Tin nhắn từ thành viên Ban: Chị Xiangli... Liệu có ổn không? 
-Phản hồi: Right có người thử nghiệm mà. Tôi sẵn sàng thử trên bản thân mình... và cả con trai tôi.
+Phản hồi: Phải có người thử nghiệm mà. Tôi sẵn sàng thử trên bản thân mình... và cả con trai tôi.
 Các báo cáo liên quan: 
 &lt;color=#ffd12f&gt;Số ca sốt NovaFei vượt 2.000, số ca tử vong tăng vọt trong tháng Tư; 
-Huaxu Academy thành lập nhóm nghiên cứu vắc-xin dưới sự lãnh đạo của P.I. Xiangli; 
-Bùng phát Tacet Field tại KU-Roro B làm tê liệt giao thông và phân phối vật tư y tế&lt;/color&gt;
+Học viện Huaxu thành lập nhóm nghiên cứu vắc-xin dưới sự lãnh đạo của P.I. Xiangli; 
+Bùng phát Tổ Tacet tại Jinzhou làm tê liệt giao thông và phân phối vật tư y tế&lt;/color&gt;
 Tiêu đề: Tiêu chuẩn chất lượng sản xuất hàng loạt và vận chuyển vắc-xin sống giảm độc lực phòng sốt NovaFei dạng uống "Sugar Pearl" 
-Sĩ quan báo cáo: Sĩ quan Y tế cấp III, Huaxu Academy 
+Sĩ quan báo cáo: Sĩ quan Y tế cấp III, Học viện Huaxu 
 Số báo cáo: MD-E0510 
 Tóm tắt:
-Report này trình bày tầm quan trọng của việc vận chuyển vật tư y tế từ Huanglong đến KU-Roro B, nơi từng là tuyến đầu chống lại đợt bùng phát Tacet Field. Đội Midnight Rangers đã dũng cảm bảo vệ thành phố trước sự tấn công dữ dội của dịch bệnh, nhưng do các tuyến giao thông bị phong tỏa, vắc-xin Sugar Pearl thế hệ thứ hai - nổi tiếng với độ ổn định và phù hợp cho trẻ em - đã gặp khó khăn trong việc tiếp cận thành phố. Report này đưa ra các tiêu chuẩn chất lượng cho việc sản xuất hàng loạt và vận chuyển vắc-xin cùng các vật tư y tế khác trong thời chiến, tập trung vào việc đảm bảo hiệu quả và an toàn. Việc sử dụng sáng tạo vắc-xin thế hệ thứ hai ổn định hơn đã đóng vai trò quan trọng trong việc bảo vệ người dân KU-Roro B khỏi Tacet Field, góp phần quan trọng vào cuộc chiến chống lại căn bệnh chết người này.
+Báo cáo này trình bày tầm quan trọng của việc vận chuyển vật tư y tế từ Huanglong đến Jinzhou, nơi từng là tuyến đầu chống lại đợt bùng phát Tổ Tacet. Đội Midnight Rangers đã dũng cảm bảo vệ thành phố trước sự tấn công dữ dội của dịch bệnh, nhưng do các tuyến giao thông bị phong tỏa, vắc-xin Sugar Pearl thế hệ thứ hai - nổi tiếng với độ ổn định và phù hợp cho trẻ em - đã gặp khó khăn trong việc tiếp cận thành phố. Báo cáo này đưa ra các tiêu chuẩn chất lượng cho việc sản xuất hàng loạt và vận chuyển vắc-xin cùng các vật tư y tế khác trong thời chiến, tập trung vào việc đảm bảo hiệu quả và an toàn. Việc sử dụng sáng tạo vắc-xin thế hệ thứ hai ổn định hơn đã đóng vai trò quan trọng trong việc bảo vệ người dân Jinzhou khỏi Tổ Tacet, góp phần quan trọng vào cuộc chiến chống lại căn bệnh chết người này.
 1. Tiêu chuẩn chất lượng sản xuất hàng loạt vắc-xin
 2. Hướng dẫn quản lý bảo quản và vận chuyển vắc-xin
-3. Rating các phương pháp vận chuyển vắc-xin hiện tại
-Việc vận chuyển vắc-xin Sugar Pearl thế hệ thứ hai là bước then chốt trong cuộc chiến chống lại đợt bùng phát Tacet Field. Để đối phó với những thách thức do các tuyến giao thông chính bị gián đoạn và địa hình hiểm trở, một kế hoạch chi tiết đã được triển khai. Xe tải đông lạnh được trang bị thiết bị giám sát nhiệt độ được sử dụng, đi kèm với các kỹ thuật viên chuyên nghiệp để đảm bảo điều kiện bảo quản và vận chuyển thích hợp. Ngoài ra, do mức độ nghiêm trọng của dịch bệnh và tính cấp bách của việc vận chuyển vắc-xin, các vật tư y tế được chia thành bảy đội để vận chuyển. Sự hỗ trợ của các Synergy Giả đóng vai trò quan trọng trong việc vượt qua địa hình khó khăn và các Tacet Field tiềm ẩn. Tính đến ngày 5 tháng 8, chỉ có một đội đến nơi kịp thời trước khi vắc-xin hết hạn, nhờ nỗ lực của một Synergy Giả vô danh đã hộ tống và tiêu diệt các Discord.
+3. Đánh giá các phương pháp vận chuyển vắc-xin hiện tại
+Việc vận chuyển vắc-xin Sugar Pearl thế hệ thứ hai là bước then chốt trong cuộc chiến chống lại đợt bùng phát Tổ Tacet. Để đối phó với những thách thức do các tuyến giao thông chính bị gián đoạn và địa hình hiểm trở, một kế hoạch chi tiết đã được triển khai. Xe tải đông lạnh được trang bị thiết bị giám sát nhiệt độ được sử dụng, đi kèm với các kỹ thuật viên chuyên nghiệp để đảm bảo điều kiện bảo quản và vận chuyển thích hợp. Ngoài ra, do mức độ nghiêm trọng của dịch bệnh và tính cấp bách của việc vận chuyển vắc-xin, các vật tư y tế được chia thành bảy đội để vận chuyển. Sự hỗ trợ của các Resonator đóng vai trò quan trọng trong việc vượt qua địa hình khó khăn và các Tổ Tacet tiềm ẩn. Tính đến ngày 5 tháng 8, chỉ có một đội đến nơi kịp thời trước khi vắc-xin hết hạn, nhờ nỗ lực của một Resonator vô danh đã hộ tống và tiêu diệt các Tacet Discord.
 ... 
-Bổ Sung lục 2: Report Synergy của Synergy Giả tham gia vận chuyển vắc-xin
-Bình luận từ Home nghiên cứu #31: 
-Về báo cáo thử nghiệm này... Synergy Giả hộ tống vật tư qua trận chiến ác liệt đã thể hiện sự ổn định đáng kinh ngạc trong dạng sóng của mình. Dữ liệu này thực sự đáng chú ý; thế nhưng, tôi không thể thoát khỏi cảm giác đã từng thấy nó ở đâu đó. Tuy nhiên, không có Synergy Giả nào trong cơ sở dữ liệu của chúng ta có đặc điểm tương tự. Điều này có ý nghĩa gì nhỉ?
-Một bình luận khác từ Home nghiên cứu #31: 
-Sau một hồi tìm kiếm, tôi phát hiện dữ liệu này rất giống với "Synergy Giả Đầu Tiên" mà tôi từng gặp trước đây. Tuy nhiên, do thời điểm đó chúng ta chưa có báo cáo thử nghiệm Synergy chuẩn hóa, nên nó không được đưa vào cơ sở dữ liệu hiện tại. Tôi đã ghi chú lại và đặt vào mục chờ để điều tra thêm.
-(Re bút: Do vấn đề sức khỏe, cấp trên đã khuyên tôi nên nghỉ phép dưỡng bệnh. Vì vậy, tôi đã giao lại vấn đề này cho Ban 34, và họ sẽ hoàn tất bàn giao vào ngày mai.)
-Bình luận từ Home nghiên cứu #34: 
-Report này có vẻ không đúng lắm. Nó nhắc đến một người đã tồn tại từ thời lập quốc, nhưng khoảng thời gian lại quá dài để có thể là cùng một người trong cả hai báo cáo. Có lẽ nhân vật này đến từ lịch sử? Tôi sẽ đợi đến khi anh #31 hồi phục rồi hỏi về lỗi tiềm ẩn này. Anh ấy đã làm việc ba đêm liên tiếp không nghỉ rồi. Current, tôi sẽ giữ báo cáo này bên mình.</t>
+Phụ lục 2: Báo cáo Cộng Hưởng của Resonator tham gia vận chuyển vắc-xin
+Bình luận từ Nhà nghiên cứu #31: 
+Về báo cáo thử nghiệm này... Resonator hộ tống vật tư qua trận chiến ác liệt đã thể hiện sự ổn định đáng kinh ngạc trong dạng sóng của mình. Dữ liệu này thực sự đáng chú ý; thế nhưng, tôi không thể thoát khỏi cảm giác đã từng thấy nó ở đâu đó. Tuy nhiên, không có Resonator nào trong cơ sở dữ liệu của chúng ta có đặc điểm tương tự. Điều này có ý nghĩa gì nhỉ?
+Một bình luận khác từ Nhà nghiên cứu #31: 
+Sau một hồi tìm kiếm, tôi phát hiện dữ liệu này rất giống với "Resonator Đầu Tiên" mà tôi từng gặp trước đây. Tuy nhiên, do thời điểm đó chúng ta chưa có báo cáo thử nghiệm Cộng Hưởng chuẩn hóa, nên nó không được đưa vào cơ sở dữ liệu hiện tại. Tôi đã ghi chú lại và đặt vào mục chờ để điều tra thêm.
+(Tái bút: Do vấn đề sức khỏe, cấp trên đã khuyên tôi nên nghỉ phép dưỡng bệnh. Vì vậy, tôi đã giao lại vấn đề này cho Ban 34, và họ sẽ hoàn tất bàn giao vào ngày mai.)
+Bình luận từ Nhà nghiên cứu #34: 
+Báo cáo này có vẻ không đúng lắm. Nó nhắc đến một người đã tồn tại từ thời lập quốc, nhưng khoảng thời gian lại quá dài để có thể là cùng một người trong cả hai báo cáo. Có lẽ nhân vật này đến từ lịch sử? Tôi sẽ đợi đến khi anh #31 hồi phục rồi hỏi về lỗi tiềm ẩn này. Anh ấy đã làm việc ba đêm liên tiếp không nghỉ rồi. Hiện tại, tôi sẽ giữ báo cáo này bên mình.</t>
         </is>
       </c>
     </row>
@@ -20856,9 +20851,9 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Hi mừng đến với tài liệu số hóa của cẩm nang mật SR-461. Chỉ những thành viên trong tổ chức tối mật của chúng ta mới có quyền truy cập giao diện này, nên nếu không phải là một trong chúng ta, thì biến đi trước khi chúng ta lần ra được ngươi.
+          <t>Chào mừng đến với tài liệu số hóa của cẩm nang mật SR-461. Chỉ những thành viên trong tổ chức tối mật của chúng ta mới có quyền truy cập giao diện này, nên nếu không phải là một trong chúng ta, thì biến đi trước khi chúng ta lần ra được ngươi.
 Giờ thì, với các đồng đội, hãy bắt tay vào việc. Như Điều 1 đã nêu, việc phân biệt giữa Suppressor 1 và Suppressor 2 là cực kỳ quan trọng. Nhầm lẫn chúng có thể dẫn đến hậu quả thảm khốc. Chúng ta không muốn điều đó, phải không?
-Next là Điều 2 - bất ngờ chưa, tổng cộng có ba suppressor! Và tất cả đều cần kiểm tra và bảo dưỡng hàng tháng. Đừng quên tải khóa từ bảng điều khiển chính trước khi đi kiểm tra và cập nhật nhật ký của chúng.
+Tiếp theo là Điều 2 - bất ngờ chưa, tổng cộng có ba suppressor! Và tất cả đều cần kiểm tra và bảo dưỡng hàng tháng. Đừng quên tải khóa từ bảng điều khiển chính trước khi đi kiểm tra và cập nhật nhật ký của chúng.
 Nhưng khoan đã, các đồng chí. Trước khi bắt đầu ăn mừng với những lon nước có ga ngọt lịm, hãy nhớ rằng mọi hoạt động này sẽ được ghi lại và có thể khiến các người bị loại khỏi sự kiện quay số trúng thưởng cuối tháng. Đúng vậy, kể cả việc ăn bún thối trong phòng họp hàng ngày cũng không được chấp nhận. Dù có dùng bao nhiêu chất khử mùi thơm đi chăng nữa cũng không thể át được cái mùi đó.
 Nói về mùi thối, hãy bàn về chuyện chơi chữ và những câu đùa của bố. Chúng ta đều thích chúng (hoặc giả vờ không thích), nhưng quá nhiều sẽ gây phiền toái cho mọi người. Đó là lý do bất kỳ ai bị bắt gặp chơi chữ hoặc kể những câu đùa sến sẽ phải chịu hình phạt nghe chúng suốt một tuần. Chỉ cần đừng lặp lại - điều đó thật không thể tha thứ.
 Cuối cùng, hãy nhớ rằng cẩm nang này chỉ có thể được điều chỉnh ba lần mỗi quý. Mọi thay đổi bổ sung sẽ phải đợi đến quý sau.
@@ -20939,19 +20934,19 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Archive: Report Rating Synergy về "Synergy Giả Đầu Tiên"
-Thời gian Rating: &lt;color=#ffd12f&gt;Năm Ngụy, AL ████&lt;/color&gt;
-Malee Synergy Giả: ĐÃ XÓA
-[Rating Synergy RA1001-G]
-[Report Rating Synergy]
-Synergy Giả ████ khai báo mất trí nhớ về năng lực cộng hưởng của mình, không rõ thời điểm thức tỉnh. Một Tacet Field hiện diện trên bàn tay phải. None thay đổi thể chất rõ ràng sau khi thức tỉnh. Tacet Field và đồng tử của họ phát sáng quầng vàng khi sử dụng Forte. Test phổ Synergy cho thấy sự Đồng Điệu mạnh với nhiều mẫu hình, nhưng nguyên nhân thức tỉnh của Synergy Giả ████ vẫn chưa được xác định. Cần test thêm để xác định nguồn gốc năng lực cộng hưởng.
-Phân tích mẫu thử cho thấy Sugar cong Rabelle không hội tụ với dạng sóng tuần hoàn rõ rệt, phân loại ████ là Synergy Giả Bẩm Sinh.
-[Report Chẩn đoán Overcharge]
-Đồ thị sóng của Synergy Giả ████ có dao động hình elip. Templates hình miền Thời gian ổn định, không có dạng sóng bất thường. Kết quả test nằm trong giới hạn bình thường, ████ không có nguy cơ Overcharge.
-Trong Trận chiến Gorges of Spirits, một Synergy Giả đã giao chiến với Discord không xác định ("Vô Vương"), giành chiến thắng nguy hiểm và giải quyết khủng hoảng. Tinh thần quân đội được khích lệ, đạt đến trạng thái bất khả chiến bại. Ba ngày sau, trận chiến kết thúc trong vinh quang, binh lính báo cáo nhìn thấy Synergy Giả đứng bên cạnh "Jué". Event này đánh dấu sự thành lập KU-Roro B trong cùng năm đó.
-Tài liệu đính kèm: Lễ thành lập KU-Roro B (ĐÃ XÓA)
-Ghi chú từ Home nghiên cứu #31:
-Right khắc phục tình trạng mất dữ liệu trước lần bảo trì cơ sở dữ liệu tiếp theo để tránh vấn đề phát sinh.</t>
+          <t>Lưu Trữ: Resonance Evaluation Report on “the First Resonator”
+Time of Evaluation: &lt;color=#ffd12f&gt;Year of Wei, AL ████&lt;/color&gt;
+Resonator Name: REDACTED
+[Resonance Assessment RA1001-G] 
+[Resonance Evaluation Report] 
+Resonator ████ reports amnesia regarding their resonance ability, with no clear time of awakening. A Tacet Mark is present on their right hand. No visible Post-Awakening physical alterations. Their Tacet Mark and pupils display a golden halo when they exert their Forte. Resonance Spectrum tests show strong Syntony with multiple patterns, but the cause of Resonator ████'s Awakening remains inconclusive. Further examination is needed to determine the origin of their resonance abilities.
+Analysis of test samples has revealed a non-convergent Rabelle's Curve with a noticeable periodic waveform, which classifies ████ as a Congenital Resonator.
+[Overclock Diagnostic Report] 
+Resonator ████'s waveform graph shows elliptical fluctuations. The pattern of Time Domain is stable with no abnormal waveforms. Examination results are determined to be within normal parameters, and ████ bears no risk of Overclocking.
+During the Battle of Gorges of Spirits, a Resonator engaged in combat with an unidentified Tacet Discord ("the Crownless"), resulting in a high-risk victory and resolution of the crisis. The morale of the army was boosted and they achieved invincibility. Three days later, the battle concluded in triumph, with soldiers reporting seeing the Resonator standing next to "Jué". This event marked the founding of Jinzhou in that same year.
+Attachment: Jinzhou Foundation Ceremony (REDACTED)
+Comment from Researcher #31: 
+Data loss must be addressed before next database maintenance to prevent further issues.</t>
         </is>
       </c>
     </row>
@@ -21023,12 +21018,12 @@
       <c r="M272" t="inlineStr">
         <is>
           <t>Mục Nhập cảnh Số 14
-1. Tình trạng thiết bị trấn áp: Activated lại. Hoạt động bình thường. Tốc độ trấn áp sương mù tiếp tục giảm.
+1. Tình trạng thiết bị trấn áp: Đã kích hoạt lại. Hoạt động bình thường. Tốc độ trấn áp sương mù tiếp tục giảm.
 2. Phân tích dữ liệu và ghi chú bổ sung: Kết quả trấn áp gần đây không đạt yêu cầu. Giả sử hiệu quả của thiết bị trấn áp không đổi, ta chỉ có thể suy luận rằng cường độ năng lượng từ nguồn sương mù đang gia tăng.
 Kết quả thử nghiệm cho thấy sương mù mang năng lượng có tần số tương tự như chất bùn tìm thấy trong đầm lầy. Ta có thể khẳng định với độ tin cậy cao rằng những hiện tượng này bắt nguồn từ một nguồn duy nhất và đặc biệt trong khu vực này.
 Ngoài ra, đã quan sát thấy &lt;color=Highlight&gt;Mourning Aix liên tục tiến vào sương mù mang theo chất phản ứng có cường độ năng lượng cao&lt;/color&gt;. Sau khi nó rời đi, &lt;color=Highlight&gt;hiệu suất của thiết bị trấn áp giảm đột ngột&lt;/color&gt;. Ta tin rằng Mourning Aix có liên quan đến nguồn năng lượng này.
 Tuy nhiên, ta lại thấy &lt;color=Highlight&gt;dấu hiệu sinh tồn của Mourning Aix suy yếu sau mỗi lần rời khỏi sương mù&lt;/color&gt;. Thiếu dữ liệu... Cần quan sát thêm.
-Recorder: Shi'er, SR-461</t>
+Người ghi chép: Shi'er, SR-461</t>
         </is>
       </c>
     </row>
@@ -21104,7 +21099,7 @@
       <c r="M273" t="inlineStr">
         <is>
           <t>Mục nhập số 18
-1. Status thiết bị trấn áp: Activated lại. Hoạt động quá tải. Tỷ lệ trấn áp sương mù chỉ đạt 34,265%.</t>
+1. Trạng thái thiết bị trấn áp: Đã kích hoạt lại. Hoạt động quá tải. Tỷ lệ trấn áp sương mù chỉ đạt 34,265%.</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21170,7 @@
       <c r="M274" t="inlineStr">
         <is>
           <t>Khi bàn về khái niệm "tình yêu", chúng ta thường phân tích nó từ góc độ tâm lý và kết luận đó là một động lực cảm xúc. Còn từ góc độ sinh học, đó là do sự tiết ra của hormone. Tuy nhiên, tất cả đều được nhìn nhận từ góc độ của con người, không có ngoại lệ. Còn tình yêu giữa các loài động vật hay sinh vật khác thì có vẻ đơn giản hơn, thiên về bản năng sinh học, sinh sản, bầu bạn và ve vãn, vì chúng không sở hữu trí tuệ như con người.
-Vậy còn hai Discord kia thì sao? Là những thực thể mang thông tin và hiện thân của năng lượng, liệu chúng có bị cấm có bản năng "yêu thương"? Liệu chúng có hát ca và khóc lóc vì thông tin chúng mang là tình yêu bắt chước từ con người? Hay đó là do ý thức tự thân thúc đẩy hành động từ một nguyên nhân nào đó?
+Vậy còn hai Tacet Discord kia thì sao? Là những thực thể mang thông tin và hiện thân của năng lượng, liệu chúng có bị cấm có bản năng "yêu thương"? Liệu chúng có hát ca và khóc lóc vì thông tin chúng mang là tình yêu bắt chước từ con người? Hay đó là do ý thức tự thân thúc đẩy hành động từ một nguyên nhân nào đó?
 Chúng ta không thể biết chắc được. Nhưng như anh đã tự mình khám phá, câu hỏi lại quay về gốc rễ: Ý nghĩa thực sự của "tình yêu" là gì?
 Với tư cách một nhà nghiên cứu, có lẽ tôi sẽ nói rằng "tình yêu" chỉ là một dạng thông tin độc nhất dưới hình thức năng lượng. Một tàn dư của Vụ Nổ Lớn. Và chúng ta đều là những kẻ mang vận may, được mang theo nó. Chỉ là những kẻ mang khác nhau sẽ tạo ra những cách diễn giải khác nhau, và sự khác biệt giữa chúng ta với những sinh vật đang yêu chính là ở bản thân chúng ta.
 Vì vậy, tôi sẽ không đau buồn vì lời chia tay, bởi nhờ cuộc gặp gỡ này, tôi đã có thể truyền tải thông tin ấy.
@@ -21248,7 +21243,7 @@
         <is>
           <t>4/7
 Còi báo động toàn thành phố réo liên tục cả ngày, ba bốn lần liền. Yōu sợ đến mức ôm chặt lấy tôi, không chịu buông. Tôi bất lực trong việc dỗ dành, chỉ biết ôm cô ấy thật chặt.
-Tomorrow chúng tôi sẽ rời đi, mong mọi thứ suôn sẻ để Yōu có thể ngủ một giấc yên lành.</t>
+Ngày mai chúng tôi sẽ rời đi, mong mọi thứ suôn sẻ để Yōu có thể ngủ một giấc yên lành.</t>
         </is>
       </c>
     </row>
@@ -21521,7 +21516,7 @@
       <c r="M279" t="inlineStr">
         <is>
           <t>15/7
-Đã hai tuần trôi qua, giờ chỉ còn bốn chúng tôi sống sót. Do sao mà Tacet Field lại đột nhiên xuất hiện ở nơi này? Tôi đã thấy những con quái vật đáng sợ, vô số quái vật...
+Đã hai tuần trôi qua, giờ chỉ còn bốn chúng tôi sống sót. Làm sao mà Tổ Tacet lại đột nhiên xuất hiện ở nơi này? Tôi đã thấy những con quái vật đáng sợ, vô số quái vật...
 Dù có chuyện gì xảy ra, tôi cũng sẽ bảo vệ Yōu, dù phải đánh đổi cả mạng sống.</t>
         </is>
       </c>
@@ -21721,7 +21716,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Ground phủ đầy đá vụn và sỏi. Traces đào bới trải dài trên bức tường đá nứt vỡ, xen lẫn những vệt máu nâu sẫm đã cũ. Ánh sáng le lói len qua khe nứt, rọi những đốm sáng nhỏ lên mặt đất u buồn. Place tay lên vách đá, ngươi dùng sức nhẹ nhàng. Với tiếng gầm vang dội, bức tường đổ sập, một luồng gió trong lành ùa vào, thổi sinh khí trở lại cho toa tàu.</t>
+          <t>Mặt đất phủ đầy đá vụn và sỏi. Dấu vết đào bới trải dài trên bức tường đá nứt vỡ, xen lẫn những vệt máu nâu sẫm đã cũ. Ánh sáng le lói len qua khe nứt, rọi những đốm sáng nhỏ lên mặt đất u buồn. Đặt tay lên vách đá, ngươi dùng sức nhẹ nhàng. Với tiếng gầm vang dội, bức tường đổ sập, một luồng gió trong lành ùa vào, thổi sinh khí trở lại cho toa tàu.</t>
         </is>
       </c>
     </row>
@@ -21796,15 +21791,15 @@
       <c r="M283" t="inlineStr">
         <is>
           <t>Ngày: [--25]
-Rainy trong phòng thí nghiệm kéo dài lâu hơn bên ngoài nhiều... Đã rơi suốt bốn năm, mười một tháng và hai ngày rồi.
-Cảm giác choáng ngợp khi lần đầu chứng kiến "Sự Treo Suspension" dần bị nuốt chửng bởi nỗi tuyệt vọng ngập tràn. Sự thất vọng và bực bội lan tỏa trong phòng thí nghiệm như rêu phong, dai dẳng và không thể tránh khỏi. Do việc trong môi trường ẩm ướt này như một hình thức tra tấn cả về thể xác lẫn tinh thần.
-Nghiên cứu về Rainy Retroact đã bước vào giai đoạn hai, thế nhưng trái với kỳ vọng, chẳng có tiến triển nào cả. Có lẽ ai cũng vậy, kể cả Giáo sư Heisen, đều tự hỏi liệu chúng ta có đang làm sai. Nhưng mọi bằng chứng đều chỉ ra rằng "nó" đã thực sự ghé thăm Bãi Lầy Whining Aix. Đó là một trong những lý do chúng ta chuyển đến đây.
-Điều chúng ta theo đuổi chỉ là dùng Rainy Retroact để tái hiện lại "phép màu" và tìm kiếm sự khai sáng. Dù kiệt sức, nghi ngờ và vô số tranh cãi, chúng ta vẫn phải tiếp tục nghiên cứu. Nhưng thời gian không đứng về phía chúng ta. Cuối cùng, chúng ta quyết định chuyển sang "Kế hoạch B".
-Liệu đó có phải là lựa chọn đáng giá? Khó mà nói. Giáo sư Heisen bảo rủi ro rất cao, nhưng thành công có thể đưa chúng ta đến gần hơn với câu trả lời. Thế nhưng, chúng ta đã thất bại 37 lần. 37 mạng người đã mất trong quá trình đó. Cuối cùng, đối tượng mang tên A038 sống sót. Đó là một bước đột phá lớn, nhưng chẳng mấy ai vui mừng, vì tất cả đều biết đó chỉ là một bản sao... chẳng hơn gì một sự bắt chước vô nghĩa của "Upper Đế".
-Ca đêm thật khủng khiếp. Vì thiếu nhân lực, tôi là người duy nhất trực. Cả đêm, quan sát thứ vô hình này, không nói được, không cử động được. Chán hơn cả nhìn mặt thầy hướng dẫn của tôi. Và để duy trì sự ổn định của Tacet Field, tất cả đồng hồ đều bị tháo bỏ. Mỗi phút trôi qua dài như cả thế kỷ...
-Giáo sư Heisen, từng rất hiền từ, giờ đây lại đặc biệt nghiêm khắc. Từ khi thí nghiệm bắt đầu, ông chưa từng cười lấy một lần. Nhân tiện, một nhà nghiên cứu từng mang dụng cụ vượt tiêu chuẩn vào khu thí nghiệm, kích hoạt cảnh báo khắp phòng lab. May mắn là cả Tacet Field lẫn A038 đều không bị ảnh hưởng, nhưng không hiểu sao, A038 lại có vẻ to hơn một chút. À, đó cũng là lần đầu tiên tôi thấy Giáo sư Heisen nổi giận.
+Mưa trong phòng thí nghiệm kéo dài lâu hơn bên ngoài nhiều... Đã rơi suốt bốn năm, mười một tháng và hai ngày rồi.
+Cảm giác choáng ngợp khi lần đầu chứng kiến "Sự Treo Lơ Lửng" dần bị nuốt chửng bởi nỗi tuyệt vọng ngập tràn. Sự thất vọng và bực bội lan tỏa trong phòng thí nghiệm như rêu phong, dai dẳng và không thể tránh khỏi. Làm việc trong môi trường ẩm ướt này như một hình thức tra tấn cả về thể xác lẫn tinh thần.
+Nghiên cứu về Mưa Retroact đã bước vào giai đoạn hai, thế nhưng trái với kỳ vọng, chẳng có tiến triển nào cả. Có lẽ ai cũng vậy, kể cả Giáo sư Heisen, đều tự hỏi liệu chúng ta có đang làm sai. Nhưng mọi bằng chứng đều chỉ ra rằng "nó" đã thực sự ghé thăm Whining Aix's Mire. Đó là một trong những lý do chúng ta chuyển đến đây.
+Điều chúng ta theo đuổi chỉ là dùng Mưa Retroact để tái hiện lại "phép màu" và tìm kiếm sự khai sáng. Dù kiệt sức, nghi ngờ và vô số tranh cãi, chúng ta vẫn phải tiếp tục nghiên cứu. Nhưng thời gian không đứng về phía chúng ta. Cuối cùng, chúng ta quyết định chuyển sang "Kế hoạch B".
+Liệu đó có phải là lựa chọn đáng giá? Khó mà nói. Giáo sư Heisen bảo rủi ro rất cao, nhưng thành công có thể đưa chúng ta đến gần hơn với câu trả lời. Thế nhưng, chúng ta đã thất bại 37 lần. 37 mạng người đã mất trong quá trình đó. Cuối cùng, đối tượng mang tên A038 sống sót. Đó là một bước đột phá lớn, nhưng chẳng mấy ai vui mừng, vì tất cả đều biết đó chỉ là một bản sao... chẳng hơn gì một sự bắt chước vô nghĩa của "Thượng Đế".
+Ca đêm thật khủng khiếp. Vì thiếu nhân lực, tôi là người duy nhất trực. Cả đêm, quan sát thứ vô hình này, không nói được, không cử động được. Chán hơn cả nhìn mặt thầy hướng dẫn của tôi. Và để duy trì sự ổn định của Tổ Tacet, tất cả đồng hồ đều bị tháo bỏ. Mỗi phút trôi qua dài như cả thế kỷ...
+Giáo sư Heisen, từng rất hiền từ, giờ đây lại đặc biệt nghiêm khắc. Từ khi thí nghiệm bắt đầu, ông chưa từng cười lấy một lần. Nhân tiện, một nhà nghiên cứu từng mang dụng cụ vượt tiêu chuẩn vào khu thí nghiệm, kích hoạt cảnh báo khắp phòng lab. May mắn là cả Tổ Tacet lẫn A038 đều không bị ảnh hưởng, nhưng không hiểu sao, A038 lại có vẻ to hơn một chút. À, đó cũng là lần đầu tiên tôi thấy Giáo sư Heisen nổi giận.
 Hôm nay thế là đủ rồi. Vẫn còn vài vấn đề, và tôi cần nhập lại các thông số và dữ liệu đã xác nhận. Tất cả chúng tôi đều bận đến phát điên. Dù khối lượng công việc lớn, chẳng ai than phiền. Rốt cuộc, ngoài nơi này ra, chúng tôi chẳng còn nơi nào để đi.
-Lại đến lúc cho tần số ăn nữa à? Speak thật, tôi nghĩ chúng ta đã cho nó ăn quá nhiều thứ rồi. Dù sao, đó là lệnh của Giáo sư Heisen, nên có lẽ cứ làm theo là tốt nhất...</t>
+Lại đến lúc cho tần số ăn nữa à? Nói thật, tôi nghĩ chúng ta đã cho nó ăn quá nhiều thứ rồi. Dù sao, đó là lệnh của Giáo sư Heisen, nên có lẽ cứ làm theo là tốt nhất...</t>
         </is>
       </c>
     </row>
@@ -22029,17 +22024,17 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Gần đây, ta nhận được lời mời từ Pioneer Association để khám phá những tinh hoa ẩm thực của KU-Roro B. Háo hức bắt đầu hành trình ẩm thực này, ta lang thang khắp các con phố, thưởng thức từng món ăn mà thành phố mang lại. Hành trình ấy đã dẫn ta đến những bất ngờ thú vị, giờ đây đã được tổng hợp lại trong cuốn sách nhỏ độc đáo này—một bản đồ ẩm thực toàn diện của KU-Roro B. Ta hy vọng khi đọc những trang này, các ngươi sẽ cảm thấy được truyền cảm hứng để tự mình khám phá—và khi đó, công sức của ta mới thực sự đáng giá. Bởi lẽ, chính khoảnh khắc hương vị nhảy múa trên đầu lưỡi, khơi dậy bản giao hưởng cảm xúc vang vọng sâu thẳm trong tâm hồn, mới là tinh hoa thực sự của những món ăn tuyệt vời này.
-&lt;color=Highlight&gt;Panhua Restaurant&lt;/color&gt;, đánh giá: ☆☆☆☆☆
-Trong lúc viết cuốn sách nhỏ này, ta ngồi tại một chiếc bàn nhỏ ở Panhua Restaurant, chìm đắm trong không khí sôi động của những cuộc trò chuyện rôm rả. Chính tại đây, ta đã chứng kiến một khoảnh khắc ấm áp khi một Đội viên Tuần tra vừa hoàn thành nhiệm vụ, cùng người bạn đội mũ nồi xanh và một người bạn khác với phong thái lạnh lùng. Trước khi Đội viên kia kịp ngồi xuống, cô đã nhanh chóng gọi món Gà Luộc, Gỏi Tía Tô và Món Xào trước khi bạn bè đến cùng. Họ chia sẻ những câu chuyện với nhau, và những cử chỉ sinh động của Đội viên Tuần tra ấy đã khiến không khí càng thêm náo nhiệt. Trải nghiệm này khiến ta tin rằng Panhua Restaurant hoàn toàn có khả năng mang đến một không gian ăn uống thư giãn và sôi động, xứng đáng là lựa chọn hàng đầu cho bất kỳ tín đồ ẩm thực nào.
-Trong lúc viết những dòng này, món Gà Luộc đã được mang đến bàn của ta. Tuy gà trông có vẻ đơn giản, nhưng khi nhúng vào loại nước sốt đặc biệt của nhà hàng, nó lại mang đến một hương vị khó quên. Mỗi miếng thịt tan chảy trong miệng, kèm theo hương thơm tươi mát đọng lại nơi đầu lưỡi. Những loại rau kèm được xào vừa chín tới, giữ nguyên màu xanh tươi, cùng những giọt dầu sôi lăn tăn. Ăn kèm với rice mềm dẻo, ta chỉ còn biết thốt lên một từ—"ngon".
+          <t>Gần đây, ta nhận được lời mời từ Hiệp Hội Tiên Phong để khám phá những tinh hoa ẩm thực của Jinzhou. Háo hức bắt đầu hành trình ẩm thực này, ta lang thang khắp các con phố, thưởng thức từng món ăn mà thành phố mang lại. Hành trình ấy đã dẫn ta đến những bất ngờ thú vị, giờ đây đã được tổng hợp lại trong cuốn sách nhỏ độc đáo này—một bản đồ ẩm thực toàn diện của Jinzhou. Ta hy vọng khi đọc những trang này, các ngươi sẽ cảm thấy được truyền cảm hứng để tự mình khám phá—và khi đó, công sức của ta mới thực sự đáng giá. Bởi lẽ, chính khoảnh khắc hương vị nhảy múa trên đầu lưỡi, khơi dậy bản giao hưởng cảm xúc vang vọng sâu thẳm trong tâm hồn, mới là tinh hoa thực sự của những món ăn tuyệt vời này.
+&lt;color=Highlight&gt;Nhà hàng Panhua&lt;/color&gt;, đánh giá: ☆☆☆☆☆
+Trong lúc viết cuốn sách nhỏ này, ta ngồi tại một chiếc bàn nhỏ ở Nhà hàng Panhua, chìm đắm trong không khí sôi động của những cuộc trò chuyện rôm rả. Chính tại đây, ta đã chứng kiến một khoảnh khắc ấm áp khi một Đội viên Tuần tra vừa hoàn thành nhiệm vụ, cùng người bạn đội mũ nồi xanh và một người bạn khác với phong thái lạnh lùng. Trước khi Đội viên kia kịp ngồi xuống, cô đã nhanh chóng gọi món Gà Luộc, Gỏi Tía Tô và Món Xào trước khi bạn bè đến cùng. Họ chia sẻ những câu chuyện với nhau, và những cử chỉ sinh động của Đội viên Tuần tra ấy đã khiến không khí càng thêm náo nhiệt. Trải nghiệm này khiến ta tin rằng Nhà hàng Panhua hoàn toàn có khả năng mang đến một không gian ăn uống thư giãn và sôi động, xứng đáng là lựa chọn hàng đầu cho bất kỳ tín đồ ẩm thực nào.
+Trong lúc viết những dòng này, món Gà Luộc đã được mang đến bàn của ta. Tuy gà trông có vẻ đơn giản, nhưng khi nhúng vào loại nước sốt đặc biệt của nhà hàng, nó lại mang đến một hương vị khó quên. Mỗi miếng thịt tan chảy trong miệng, kèm theo hương thơm tươi mát đọng lại nơi đầu lưỡi. Những loại rau kèm được xào vừa chín tới, giữ nguyên màu xanh tươi, cùng những giọt dầu sôi lăn tăn. Ăn kèm với cơm mềm dẻo, ta chỉ còn biết thốt lên một từ—"ngon".
 Vậy nên ta không thể cưỡng lại mà gọi thêm một phần nữa :)
 &lt;color=Highlight&gt;Jewel Boba&lt;/color&gt;, đánh giá: ☆☆☆☆
-Ta không thể ngừng nghĩ đến món Jewel Boba tuyệt vời này, mỗi ngụm đều khiến ta muốn nếm thêm. Nếu ta có một cái dạ dày thứ hai chỉ để dành cho đồ tráng miệng, chắc chắn nó sẽ thuộc về món chè ngon tuyệt này ở KU-Roro B... Và nếu chỉ được giới thiệu một món, Jewel Boba chắc chắn sẽ là lựa chọn hàng đầu của ta. Với hơn ba mươi năm danh tiếng, món ngọt này vẫn giữ nguyên hương vị tuyệt hảo và giá cả phải chăng như ngày nào.
+Ta không thể ngừng nghĩ đến món Jewel Boba tuyệt vời này, mỗi ngụm đều khiến ta muốn nếm thêm. Nếu ta có một cái dạ dày thứ hai chỉ để dành cho đồ tráng miệng, chắc chắn nó sẽ thuộc về món chè ngon tuyệt này ở Jinzhou... Và nếu chỉ được giới thiệu một món, Jewel Boba chắc chắn sẽ là lựa chọn hàng đầu của ta. Với hơn ba mươi năm danh tiếng, món ngọt này vẫn giữ nguyên hương vị tuyệt hảo và giá cả phải chăng như ngày nào.
 Trong lần ghé thăm, ta gọi món chè mới với ưu đãi mua một tặng một. Chủ quán kể rằng món này ra đời nhờ một cặp đôi hạnh phúc kỷ niệm ngày cưới tại quán—chủ quán vui mừng trước hạnh phúc của họ nên đã tặng họ một ly nước uống đặc biệt. Khi cặp đôi khen ngợi hương vị, chủ quán quyết định chia sẻ nó với nhiều thực khách hơn. Nghe xong câu chuyện ấm áp ấy, ta—người đang ôm hai ly một mình—không khỏi cảm thấy chút cô đơn. May mắn thay, vị ngọt của Jewel Boba đã phần nào xoa dịu tâm trạng của ta.
-&lt;color=Highlight&gt;Teahouse Liuxian&lt;/color&gt;, đánh giá: ☆☆☆☆
-Teahouse Liuxian tự hào với Tea Bittberry có vị đắng đặc trưng, chỉ một ngụm đã khiến người ta phải đặt dấu hỏi về mọi thứ. Thế nhưng, sau cú sốc ban đầu, một vị ngọt dịu nhẹ dần hiện ra, lưu lại nơi đầu lưỡi với sự dai dẳng đáng ngạc nhiên.
-Khác với không khí náo nhiệt của Panhua Restaurant, Teahouse Liuxian mang đến một bầu không khí tĩnh lặng, nơi ta có thể ngả lưng trên ghế, tay phe phẩy chiếc quạt, và thả hồn theo dòng chảy bình yên của cuộc sống xung quanh.
+&lt;color=Highlight&gt;Quán Trà Liuxian&lt;/color&gt;, đánh giá: ☆☆☆☆
+Quán Trà Liuxian tự hào với Trà Bittberry có vị đắng đặc trưng, chỉ một ngụm đã khiến người ta phải đặt dấu hỏi về mọi thứ. Thế nhưng, sau cú sốc ban đầu, một vị ngọt dịu nhẹ dần hiện ra, lưu lại nơi đầu lưỡi với sự dai dẳng đáng ngạc nhiên.
+Khác với không khí náo nhiệt của Nhà hàng Panhua, Quán Trà Liuxian mang đến một bầu không khí tĩnh lặng, nơi ta có thể ngả lưng trên ghế, tay phe phẩy chiếc quạt, và thả hồn theo dòng chảy bình yên của cuộc sống xung quanh.
 &lt;color=Highlight&gt;Ẩm thực Biên Cương&lt;/color&gt;, đánh giá: ☆☆☆☆☆
 ...</t>
         </is>
@@ -22112,13 +22107,13 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Loong Bun Dragon, Hầm KU-Roro B, Sellh Sao... Trước khi khám phá vô số đặc sản của KU-Roro B, hãy để ta giới thiệu với ngươi một món ăn truyền thống lâu đời—"Dragon Vươn Mình".
-&lt;color=Highlight&gt;Dragon Vươn Mình&lt;/color&gt;, đánh giá: ☆☆☆☆☆
-Đối với bất kỳ ai đặt chân đến KU-Roro B, thưởng thức Dragon Vươn Mình là điều không thể bỏ qua. Dish khoác lên mình lớp vỏ vàng giòn hấp dẫn, được chế biến qua nhiều công đoạn tỉ mỉ để tái hiện cảnh cá chép ngẩng nhìn trời, khát khao hóa rồng. Dish này kể lại sự thức tỉnh của Jué. Ngày ấy, vô số cá chép đã nhảy lên khỏi mặt nước để bày tỏ lòng thành kính. Đó là sự kiện được người KU-Roro B coi là điềm lành. Vậy nên, nếu ngươi muốn cầu may, đừng bỏ lỡ cơ hội thưởng thức Dragon Vươn Mình!
-&lt;color=Highlight&gt;Food Ration Bar&lt;/color&gt;, đánh giá: ☆☆☆
-Dù ta chỉ cho nó ba sao, nhưng ý nghĩa của Food Ration Bar vượt xa hương vị. Điểm nổi bật của nó nằm ở sự tiện lợi, dễ tiếp cận và giá trị dinh dưỡng dồi dào, giúp mọi người lính trên tiền tuyến có thể chiến đấu không ngừng nghỉ.
-Guan trọng hơn, mỗi Food Ration Bar đều kèm theo một lời nhắn, gửi gắm tâm tư, nguyện vọng và lòng biết ơn của người dân KU-Roro B tới những người lính bảo vệ sự bình yên và thịnh vượng của KU-Roro B.
-Dù phía trước có muôn vàn thử thách, KU-Roro B và người dân nơi đây vẫn luôn sát cánh bên những người lính. Họ dũng cảm bảo vệ KU-Roro B bằng cả mạng sống, và ngược lại, KU-Roro B trở thành lá chắn vững chắc cho họ.</t>
+          <t>Bánh Lồng Đèn Rồng, Hầm Jinzhou, Bánh Sao... Trước khi khám phá vô số đặc sản của Jinzhou, hãy để ta giới thiệu với ngươi một món ăn truyền thống lâu đời—"Rồng Vươn Mình".
+&lt;color=Highlight&gt;Rồng Vươn Mình&lt;/color&gt;, đánh giá: ☆☆☆☆☆
+Đối với bất kỳ ai đặt chân đến Jinzhou, thưởng thức Rồng Vươn Mình là điều không thể bỏ qua. Món ăn khoác lên mình lớp vỏ vàng giòn hấp dẫn, được chế biến qua nhiều công đoạn tỉ mỉ để tái hiện cảnh cá chép ngẩng nhìn trời, khát khao hóa rồng. Món ăn này kể lại sự thức tỉnh của Jué. Ngày ấy, vô số cá chép đã nhảy lên khỏi mặt nước để bày tỏ lòng thành kính. Đó là sự kiện được người Jinzhou coi là điềm lành. Vậy nên, nếu ngươi muốn cầu may, đừng bỏ lỡ cơ hội thưởng thức Rồng Vươn Mình!
+&lt;color=Highlight&gt;Thanh Lương Khô&lt;/color&gt;, đánh giá: ☆☆☆
+Dù ta chỉ cho nó ba sao, nhưng ý nghĩa của Thanh Lương Khô vượt xa hương vị. Điểm nổi bật của nó nằm ở sự tiện lợi, dễ tiếp cận và giá trị dinh dưỡng dồi dào, giúp mọi người lính trên tiền tuyến có thể chiến đấu không ngừng nghỉ.
+Quan trọng hơn, mỗi Thanh Lương Khô đều kèm theo một lời nhắn, gửi gắm tâm tư, nguyện vọng và lòng biết ơn của người dân Jinzhou tới những người lính bảo vệ sự bình yên và thịnh vượng của Jinzhou.
+Dù phía trước có muôn vàn thử thách, Jinzhou và người dân nơi đây vẫn luôn sát cánh bên những người lính. Họ dũng cảm bảo vệ Jinzhou bằng cả mạng sống, và ngược lại, Jinzhou trở thành lá chắn vững chắc cho họ.</t>
         </is>
       </c>
     </row>
@@ -22191,14 +22186,14 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>We Promise, We Deliver—Lollo Logistics
-Xa KU-Roro B mà vẫn thèm đặc sản nơi ấy? Đừng lo—Lollo Logistics lo hết cho bạn!
-Ở KU-Roro B mà thèm đặc sản Lục Guo? Không vấn đề—Lollo Logistics lại sẵn sàng giúp đỡ!
+          <t>Lời Hứa Là Sẽ Giao—Lollo Logistics
+Xa Jinzhou mà vẫn thèm đặc sản nơi ấy? Đừng lo—Lollo Logistics lo hết cho bạn!
+Ở Jinzhou mà thèm đặc sản Lục Quốc? Không vấn đề—Lollo Logistics lại sẵn sàng giúp đỡ!
 Hãy tưởng tượng: khi bạn mở những hộp đồ ăn ấy, hơi nóng bốc lên, mang theo hương thơm quyện vào mũi, khơi dậy cơn thèm muốn những món ngon ấy.
 Với chất lượng tuyệt hảo và giao hàng thần tốc, hãy lựa chọn thông minh—chọn Lollo Logistics!
-BodyBuilder: Zhuẩn luôn! Previous giờ chưa đến KU-Roro B bao giờ, nhưng thèm Gà Kéo của Panhua Restaurant đến phát điên. Từng giây, từng phút, từng giờ, không ngừng nghĩ về nó, mất ăn mất ngủ luôn. Cuối cùng cũng chịu thua, gọi Lollo Logistics đặt đồ ăn. However anh giao hàng quên lấy đồ, lại chở mình đến tận KU-Roro B để ăn Gà Kéo!
+BodyBuilder: Chuẩn luôn! Trước giờ chưa đến Jinzhou bao giờ, nhưng thèm Gà Kéo của Nhà hàng Panhua đến phát điên. Từng giây, từng phút, từng giờ, không ngừng nghĩ về nó, mất ăn mất ngủ luôn. Cuối cùng cũng chịu thua, gọi Lollo Logistics đặt đồ ăn. Nhưng mà anh giao hàng quên lấy đồ, lại chở mình đến tận Jinzhou để ăn Gà Kéo!
 AM JUST A BRUSH: Haha! Tin xấu: Quên lấy đồ ăn; Tin tốt: Đưa khách đến tận nhà hàng luôn.
-AAA Fresh Ingredients Wholesaler: Tươi ngon là đây. Reliable!
+AAA Fresh Ingredients Wholesaler: Tươi ngon là đây. Đáng tin cậy!
 Green Light Forever: Cảm ơn cậu! Yên tâm nhé. Chúng tôi luôn giữ lời hứa!</t>
         </is>
       </c>
@@ -22264,7 +22259,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Mỗi sáng, từ trước khi mặt trời lên, Mahe, chủ cửa hàng Mahe's Grocery, đã bắt đầu công việc của mình. Trong vài giờ tiếp theo, ông cẩn thận chuẩn bị nguyên liệu cho ngày bán hàng. Mùa nào thức nấy, rau củ quả cũng thay đổi theo. Do thế nào Mahe chọn được nguyên liệu theo mùa, và làm sao ông đảm bảo chúng đến được tay các gia đình xa xôi? Hãy cùng theo dõi chương trình "Gặp gỡ KU-Roro B" hôm nay, khi tập này đưa các bạn đến thăm Mahe's Grocery.</t>
+          <t>Mỗi sáng, từ trước khi mặt trời lên, Mahe, chủ cửa hàng Mahe's Grocery, đã bắt đầu công việc của mình. Trong vài giờ tiếp theo, ông cẩn thận chuẩn bị nguyên liệu cho ngày bán hàng. Mùa nào thức nấy, rau củ quả cũng thay đổi theo. Làm thế nào Mahe chọn được nguyên liệu theo mùa, và làm sao ông đảm bảo chúng đến được tay các gia đình xa xôi? Hãy cùng theo dõi chương trình "Gặp gỡ Jinzhou" hôm nay, khi tập này đưa các bạn đến thăm Mahe's Grocery.</t>
         </is>
       </c>
     </row>
@@ -22350,7 +22345,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Tiêu đề: Report Giám sát Bất thường Phổ Tần số của Chủ thể C-001
+          <t>Tiêu đề: Báo cáo Giám sát Bất thường Phổ Tần số của Chủ thể C-001
 Mục: #H-C-6947
 Tóm tắt:
 Dữ liệu trong báo cáo này được thu thập từ các đánh giá phổ tần số thực hiện trên Chủ thể C-001, còn gọi là "Jué," từ tháng 6 ████ đến tháng 12 ████.
@@ -22359,19 +22354,19 @@
 Dựa trên dữ liệu giám sát phổ tần số của Chủ thể C-001 từ tháng 6 ████ đến tháng 12 ████, có thể rút ra những kết luận sơ bộ sau:
 1. Chủ thể C-001 mang khiếm khuyết/lỗi hoạt động.
 2. Chủ thể C-002 có thể tạm thời làm chậm sự leo thang của khiếm khuyết ở Chủ thể C-001, nhưng không thể bù đắp cho sự mất tần số của Chủ thể C-001.
-Bổ Sung lục-1 (Nguồn: Records nghiên cứu #C349)
+Phụ lục-1 (Nguồn: Bản ghi nghiên cứu #C349)
 Nhờ sự giúp đỡ của "vị khách kỳ lạ," chúng tôi đã có cơ hội trò chuyện trực tiếp với Chủ thể C-001. Đó là một cuộc đối thoại ý nghĩa và hai chiều, dù chúng tôi không thu thập được nhiều thông tin như mong đợi.
-Nhưng ít nhất, cuộc trò chuyện đã chứng minh một điều: Past Nghiên cứu của chúng tôi là hiệu quả, và C-001 không hề có khiếm khuyết. Theo tuyên bố của chính C-001, "Một trong các Chương trình Thời gian đã bị mất," và trong thời kỳ đỉnh cao, C-001 có khả năng thao túng thời gian bằng cách làm chậm, thậm chí dừng hẳn, tua ngược và sửa chữa khi cần. Tuy nhiên, tình trạng hiện tại của C-001 có thể được mô tả là một căn bệnh, với những gián đoạn thời gian không thể đảo ngược khiến mọi nỗ lực sửa chữa hay khôi phục đều trở nên vô hiệu. Kết quả là, Núi Firmament đã biến thành một thực thể cô lập giữa đại dương thời gian mênh mông, dù mục đích ban đầu là để cứu rỗi.
-Bổ Sung lục-2 (Nguồn: Records nghiên cứu #C382)
+Nhưng ít nhất, cuộc trò chuyện đã chứng minh một điều: Nghiên cứu trước đây của chúng tôi là hiệu quả, và C-001 không hề có khiếm khuyết. Theo tuyên bố của chính C-001, "Một trong các Chương trình Thời gian đã bị mất," và trong thời kỳ đỉnh cao, C-001 có khả năng thao túng thời gian bằng cách làm chậm, thậm chí dừng hẳn, tua ngược và sửa chữa khi cần. Tuy nhiên, tình trạng hiện tại của C-001 có thể được mô tả là một căn bệnh, với những gián đoạn thời gian không thể đảo ngược khiến mọi nỗ lực sửa chữa hay khôi phục đều trở nên vô hiệu. Kết quả là, Núi Firmament đã biến thành một thực thể cô lập giữa đại dương thời gian mênh mông, dù mục đích ban đầu là để cứu rỗi.
+Phụ lục-2 (Nguồn: Bản ghi nghiên cứu #C382)
 Bằng cách chạy các mô hình dòng chảy thời gian, chúng tôi đã đưa ra hai giả thuyết:
 Giả thuyết #1: "Khiếm khuyết" của C-001 không phải bẩm sinh, và "khiếm khuyết" này có thể đã xảy ra vào khoảng thời gian C-001 lần đầu đến Núi Firmament (đã xác nhận rằng "khiếm khuyết" không thể đảo ngược, xem báo cáo #H-C-7426).
 Giả thuyết #2: Sự chênh lệch trong tiến trình thời gian giữa bên trong và bên ngoài "bong bóng thời gian" đang ngày càng mở rộng. Dựa trên so sánh dữ liệu, tồn tại mối tương quan giữa tốc độ giảm tốc của dòng thời gian ở Núi Firmament và tốc độ gia tăng thời gian mất tần số của C-001.
-Mở rộng giả thuyết thứ hai... Nếu C-001 cuối cùng ngừng tồn tại, dòng chảy thời gian không kiểm soát ở Núi Firmament có thể sẽ vượt quá giới hạn và ảnh hưởng đến một phạm vi rộng lớn hơn… Chẳng hạn như toàn bộ KU-Roro B.
+Mở rộng giả thuyết thứ hai... Nếu C-001 cuối cùng ngừng tồn tại, dòng chảy thời gian không kiểm soát ở Núi Firmament có thể sẽ vượt quá giới hạn và ảnh hưởng đến một phạm vi rộng lớn hơn… Chẳng hạn như toàn bộ Jinzhou.
 …Có lẽ đây chính là lý do mà "vị khách kỳ lạ" ấy đề nghị hợp tác với chúng ta ngay từ đầu…
-Bổ Sung lục-3 (Nguồn: Records nghiên cứu #C457)
+Phụ lục-3 (Nguồn: Bản ghi nghiên cứu #C457)
 Chúng tôi đang nỗ lực thúc đẩy phát triển Vật thể Cộng hưởng nhân tạo. Dù chưa đạt được thành công, chúng tôi đã quyết định đặt tên nó là "Chronosorter" để vinh danh những tiến bộ gần đây.
 Tôi biết chúng ta phải cảm ơn "vị khách kỳ lạ" ấy vì mọi tiến bộ đã đạt được cho đến nay. Nếu dự án "Chronosorter" thành công, đó sẽ là thắng lợi cho tất cả các bên. Như tôi đã dự đoán, họ có ý định khôi phục và sử dụng toàn bộ sức mạnh của C-001 để sửa chữa sự méo mó thời gian, với sự hỗ trợ của một Vật thể Cộng hưởng.
-Path phía trước vẫn còn dài. Đây mới chỉ là điểm khởi đầu.</t>
+Con đường phía trước vẫn còn dài. Đây mới chỉ là điểm khởi đầu.</t>
         </is>
       </c>
     </row>
@@ -22445,15 +22440,15 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Nghiên cứu Log — #C532
+          <t>Biên Bản Nghiên Cứu — #C532
 Ngày: [--05]
 Thí nghiệm thứ 903 lại thất bại, khiến chúng tôi không khỏi nhớ về sự hào hứng ban đầu khi hoàn thành nguyên mẫu Chronosorter đầu tiên. Nhưng chúng tôi luôn biết đó chỉ là bản sao thô sơ sức mạnh của C-001. Tính toán của ta cho thấy Chronosorter chỉ hoạt động trong một khoảng cách nhất định và sẽ trở nên vô dụng khi rời khỏi vùng rào cản thời gian này (dù có thể vẫn hoạt động ở Bãi Sáng).
-Dù vậy, ta vẫn nuôi hy vọng. Khái niệm "Synergy Thứ Cấp" không chỉ là lý thuyết đối với ta; đó là cả cuộc đời ta. Nghĩ đến việc nó có thể chỉ là ảo tưởng thôi cũng đủ khiến ta rùng mình.
-Nghiên cứu Log — #C545
+Dù vậy, ta vẫn nuôi hy vọng. Khái niệm "Cộng Hưởng Thứ Cấp" không chỉ là lý thuyết đối với ta; đó là cả cuộc đời ta. Nghĩ đến việc nó có thể chỉ là ảo tưởng thôi cũng đủ khiến ta rùng mình.
+Biên Bản Nghiên Cứu — #C545
 Ngày: [--26]
 Chronosorter thứ 931, giống như các tiền nhiệm, đã bị phá hủy bởi xung kích cộng hưởng dữ dội. Nhưng nó đã khôi phục thời gian trong 1,29 giây ngắn ngủi, một sự hy sinh đáng giá.
-Ta đã đúng... Niềm tin vào lý thuyết Synergy Thứ Cấp của ta đã được chứng minh! Khi hai thực thể cộng hưởng với cường độ cao, thực thể yếu hơn có thể phát huy sức mạnh Synergy vượt xa khả năng ban đầu.
-Vấn đề duy nhất là các Chronosorter chúng ta chế tạo quá mỏng manh cho nhiệm vụ này. Ta cần một Synergy Giả mạnh mẽ hơn, nhưng rủi ro quá lớn. Không ai có thể chịu đựng được xung kích cộng hưởng của C-001 mà không phải hứng chịu quá tải thảm khốc.
+Ta đã đúng... Niềm tin vào lý thuyết Cộng Hưởng Thứ Cấp của ta đã được chứng minh! Khi hai thực thể cộng hưởng với cường độ cao, thực thể yếu hơn có thể phát huy sức mạnh Cộng Hưởng vượt xa khả năng ban đầu.
+Vấn đề duy nhất là các Chronosorter chúng ta chế tạo quá mỏng manh cho nhiệm vụ này. Ta cần một Resonator mạnh mẽ hơn, nhưng rủi ro quá lớn. Không ai có thể chịu đựng được xung kích cộng hưởng của C-001 mà không phải hứng chịu quá tải thảm khốc.
 Ghi chú: Ta phải nói chuyện với vị khách của chúng ta. Ta đã thấy họ nói điều gì đó với C-001. Ta tin chắc có mối liên hệ giữa hành động của họ và thành công ngắn ngủi của Chronosorter số 931. Đúng vậy, ta đã tận mắt chứng kiến; C-001 hẳn đã truyền một dạng năng lượng chưa biết đến Chronosorter số 931, ngay khi ta tưởng thí nghiệm đã thất bại...</t>
         </is>
       </c>
@@ -22594,9 +22589,9 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Nghiên cứu Log #C501
+          <t>Biên Bản Nghiên Cứu #C501
 Ngày: [--19]
-Guest của ta đã chia sẻ những chi tiết phức tạp về thế giới bên ngoài, mô tả một nền văn minh mới trỗi dậy từ tro tàn của quá khứ. Giọng điệu họ kể chuyện thật bình thản, không chút cảm xúc cá nhân, như thể họ chỉ là người quan sát vô tư, chứ không phải người đã cứu vớt nền văn minh ấy.
+Vị khách của ta đã chia sẻ những chi tiết phức tạp về thế giới bên ngoài, mô tả một nền văn minh mới trỗi dậy từ tro tàn của quá khứ. Giọng điệu họ kể chuyện thật bình thản, không chút cảm xúc cá nhân, như thể họ chỉ là người quan sát vô tư, chứ không phải người đã cứu vớt nền văn minh ấy.
 Ta dần nhận ra họ không giống chúng ta - sự khiêm nhường và thiện chí của họ chỉ nhằm dẫn dắt, hòa nhập chúng ta vào con đường đã được định sẵn.
 Dù vậy, ta vẫn biết ơn vì những kiến thức họ đã chia sẻ. Ta khao khát được tận mắt chứng kiến thế giới mới ấy, nhận ra mình đã giam mình quá lâu trên Núi Firmament...</t>
         </is>
@@ -22672,10 +22667,10 @@
         <is>
           <t>&lt;alignleft/&gt;...
 &lt;alignleft/&gt;Tháng Ba. Nhiều vùng đất bị tàn phá bởi các đợt bùng phát TD, và 31 nạn nhân đã leo lên ngọn núi.
-&lt;alignleft/&gt;Ngày 9 tháng Tư. Một đợt bùng phát TD tiến gần Núi Firmament. Night hôm đó, một dòng lửa rơi xuống Vách Empyrean. (Ghi chú: Vách Empyrean sau này được đổi tên thành Mỏm Dragon)
+&lt;alignleft/&gt;Ngày 9 tháng Tư. Một đợt bùng phát TD tiến gần Núi Firmament. Đêm hôm đó, một dòng lửa rơi xuống Vách Empyrean. (Ghi chú: Vách Empyrean sau này được đổi tên thành Mỏm Rồng)
 &lt;alignleft/&gt;Ngày 21 tháng Tư. Hai dân làng dụ một người ngoài vào nơi dòng lửa rơi xuống Vách Empyrean.
-&lt;alignleft/&gt;Ngày 22 tháng Tư. Một đợt bùng phát TD tấn công Hồng Trấn. Sentinel Jué xuất hiện từ Vách Empyrean, làm chậm dòng chảy thời gian bằng Temporal Mandate để đẩy lùi đợt bùng phát TD và hình thành Núi Firmament.
-&lt;alignleft/&gt;Ngày 23 tháng Tư. Một người ngoài đến Hồng Trấn cùng Sentinel Jué và rời núi cùng 17 dân làng khác sau đó.
+&lt;alignleft/&gt;Ngày 22 tháng Tư. Một đợt bùng phát TD tấn công Hongzhen. Sentinel Jué xuất hiện từ Vách Empyrean, làm chậm dòng chảy thời gian bằng Temporal Mandate để đẩy lùi đợt bùng phát TD và hình thành Núi Firmament.
+&lt;alignleft/&gt;Ngày 23 tháng Tư. Một người ngoài đến Hongzhen cùng Sentinel Jué và rời núi cùng 17 dân làng khác sau đó.
 &lt;alignleft/&gt;...
 &lt;alignleft/&gt;Ngày 3 tháng Bảy. Người ngoài trở lại Núi Firmament, dường như không bị ảnh hưởng bởi Temporal Disruptions. Từ đó, dân địa phương gọi họ là "vị khách kỳ lạ"."</t>
         </is>
@@ -22750,7 +22745,7 @@
           <t>&lt;alignleft/&gt;...
 &lt;alignleft/&gt;Ngày 5 tháng 3. Khoảng 21:00–23:00, sấm sét bắt đầu gầm rú, và lính canh Jué trở về với một đứa bé đã chết.
 &lt;alignleft/&gt;Ngày 6 tháng 3. Sấm ngừng vào khoảng 01:00–03:00. Có điều gì đó kỳ lạ đang diễn ra trên bầu trời, và các vì sao di chuyển ngược chiều.
-&lt;alignleft/&gt;Enter lúc 05:00–07:00 cùng ngày, lính canh Jué đến Hongzhen giao đứa bé cho dân làng. Đứa bé trông hoàn toàn bình thường, không có dấu hiệu gì của cái chết.
+&lt;alignleft/&gt;Vào lúc 05:00–07:00 cùng ngày, lính canh Jué đến Hongzhen giao đứa bé cho dân làng. Đứa bé trông hoàn toàn bình thường, không có dấu hiệu gì của cái chết.
 &lt;alignleft/&gt;(Ghi chú: Một đứa bé đã chết mà sống lại là điều không thể. Nếu không tận mắt chứng kiến, tôi sẽ không bao giờ tin vào chuyện này.)
 &lt;alignleft/&gt;...</t>
         </is>
@@ -22893,7 +22888,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>…Releasem họa ập xuống mảnh đất này, cướp đi vô số sinh mạng. Chúng ta cầu cứu, nhưng chẳng ai đáp lời…
+          <t>…Thảm họa ập xuống mảnh đất này, cướp đi vô số sinh mạng. Chúng tao cầu cứu, nhưng chẳng ai đáp lời…
 "Dòng chữ khớp với cổ thư, xác nhận đây là khởi đầu của nghi lễ. Nhưng kết thúc vẫn còn là bí ẩn. Ta đã để lại vài manh mối ở đây cho những người kế tục." —Bác Phúc</t>
         </is>
       </c>
@@ -23027,7 +23022,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>…Với tiếng gầm vang dội, nó đã xua đuổi toàn bộ Discord, dùng sức mạnh bóp méo thời gian để bảo vệ chúng ta…
+          <t>…Với tiếng gầm vang dội, nó đã xua đuổi toàn bộ Tacet Discord, dùng sức mạnh bóp méo thời gian để bảo vệ chúng ta…
 "Để hoàn thành Nghi Lễ Dâng Hiến, hãy tìm chiếc đèn phủ men trên đỉnh Xuanji. Người ta nói rằng nó ở đó. Đây sẽ là điểm đến đầu tiên của các ngươi." —Bác Fu</t>
         </is>
       </c>
@@ -23168,9 +23163,9 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Hi người lạ!
+          <t>Chào người lạ!
 Nếu cậu đang đọc tin nhắn này, chắc hẳn cậu đã được chọn làm khán giả đầu tiên của Đoàn Múa Rùa Chelonian!
-Cách đây rất lâu, tớ tình cờ tìm thấy một nhạc cụ có thể tạo ra điều kỳ diệu—âm nhạc du dương nó phát ra có thể khiến tớ, động vật, thậm chí cả Discord nhảy múa theo điệu nhạc. Trong tất cả các điệu múa, múa rùa là điệu khiến tớ xúc động nhất.
+Cách đây rất lâu, tớ tình cờ tìm thấy một nhạc cụ có thể tạo ra điều kỳ diệu—âm nhạc du dương nó phát ra có thể khiến tớ, động vật, thậm chí cả Tacet Discord nhảy múa theo điệu nhạc. Trong tất cả các điệu múa, múa rùa là điệu khiến tớ xúc động nhất.
 Từ nhỏ, tớ luôn mơ ước trở thành một nghệ sĩ vừa hát vừa múa. Nhưng có lẽ do thiếu năng khiếu, dù đã dành bao công sức luyện tập, tớ vẫn không thể hát hay nhảy giỏi được.
 Thế nhưng, khi nhìn thấy những chú rùa nhảy múa, tớ đã đặt ra mục tiêu cho mình—thành lập một đoàn múa!
 Với sự hướng dẫn của tớ, Đoàn Múa Rùa Chelonian đã được thành lập được một thời gian, và những nỗ lực tập luyện của các thành viên cũng bắt đầu đơm hoa kết trái.
@@ -23245,10 +23240,10 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>...Có gì đặc biệt ở Ruins Court of Savantae chứ? Ta thấy bọn người ở Court of Savantae chẳng ra gì cả. Dù đã chết rồi, nhưng mấy biện pháp bảo vệ quá mức của chúng vẫn làm mấy đứa em ta chết như rạ. Tsk, không hiểu sao bọn Fractsidus lại cuồng mấy cuốn sách mốc meo và đống sắt vụn của Court of Savantae đến thế. Ba ngày qua, chúng chỉ toàn đào bới và chuyển đống rác của Court of Savantae ra khỏi tàn tích. Ta chẳng thèm đếm xỉa đến nếu chúng không trả lương hậu hĩnh.
+          <t>...Có gì đặc biệt ở Tàn Tích Court of Savantae chứ? Tao thấy bọn người ở Court of Savantae chẳng ra gì cả. Dù đã chết rồi, nhưng mấy biện pháp bảo vệ quá mức của chúng vẫn làm mấy đứa em tao chết như rạ. Tsk, không hiểu sao bọn Fractsidus lại cuồng mấy cuốn sách mốc meo và đống sắt vụn của Court of Savantae đến thế. Ba ngày qua, chúng chỉ toàn đào bới và chuyển đống rác của Court of Savantae ra khỏi tàn tích. Tao chẳng thèm đếm xỉa đến nếu chúng không trả lương hậu hĩnh.
 —Yao Shisi
 Trả lời Yao Shisi
-Ngươi thực sự điên vì tiền đến thế hay chỉ muốn chết sớm thôi? Bọn Fractsidus là lũ tàn nhẫn, chúng sẽ nuốt chửng ngươi không chớp mắt. Sao không lên Núi Firmament tìm thứ gì đó có giá trị rồi đem bán ở KU-Roro B? Vẫn kiếm được kha khá đấy.
+Mày thực sự điên vì tiền đến thế hay chỉ muốn chết sớm thôi? Bọn Fractsidus là lũ tàn nhẫn, chúng sẽ nuốt chửng mày không chớp mắt. Sao không lên Núi Firmament tìm thứ gì đó có giá trị rồi đem bán ở Jinzhou? Vẫn kiếm được kha khá đấy.
 —Kui</t>
         </is>
       </c>
@@ -23321,7 +23316,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Gửi Home Moontree,
+          <t>Gửi Nhà Moontree,
 Ta mệt rồi. Mệt lắm rồi.
 Vô số thí nghiệm thất bại và mục tiêu bất khả thi đã nhấn chìm ta trong tuyệt vọng.
 Ta không phải người phù hợp với công việc của học viện, cũng chẳng giỏi giao tiếp với ai. Đến việc xin lỗi người duy nhất chịu lắng nghe ta, ta cũng chẳng làm được.
@@ -23419,24 +23414,24 @@
 417 kết quả
 [Chủ đề chính] Hội chứng U Sầu Đêm
 Xiaosheng
-Lại một ngày tồi tệ hôm nay.
+Hôm nay lại là một ngày tồi tệ.
 theQingheScale
 Xiaosheng sao thế? Thấy cậu bình luận muộn hoài. Ổn không đấy?
 Xiaosheng
-Tôi không thể ngủ được vào ban đêm. Thật bất ngờ.
-Không thể thoát khỏi cảm giác rằng tôi đã làm hỏng mọi thứ hôm nay với những bình luận của mình.
-Tôi sẽ làm gì khi gặp anh ấy ở chỗ làm vào ngày mai...? Tôi thực sự không nên đi đến cuộc họp ngớ ngẩn đó...
+Không tài nào ngủ được. Chuyện thường thôi.
+Cảm giác như mình lại làm hỏng chuyện gì đó hôm nay qua mấy cái bình luận.
+Mai gặp hắn ở chỗ làm biết làm sao đây... Đáng ra không nên đi họp vớ vẩn đó...
 Xiaosheng
-Vừa tìm thấy một số tệp Echo cũ trong tủ của mình... Những ngày đó… Chúng tôi luôn làm việc với một số dự án thú vị điên rồ mà chỉ khiến chúng tôi tiếp tục tiến lên.
+Vừa lục lại tủ thấy vài file Echo cũ... Ngày xưa ấy nhỉ… Lúc nào cũng cặm cụi với mấy dự án điên rồ mà vẫn thấy hứng khởi.
 Xiaosheng
-Tôi phải nộp đề xuất dự án vào ngày mai. Nếu tôi không nhận được nguồn lực lần nữa, một năm làm việc của tôi sẽ đổ sông đổ biển.
+Mai phải nộp đề xuất dự án. Lại không xin được tài nguyên thì coi như công cốc cả năm trời.
 HALPImGoingBALD
-Chờ đã. Cậu đến từ DLE à? Mấy người cần thư giãn và chậm lại một chút với tất cả công việc đó đi. Trời ạ.
+Ê. Cậu ở DLE à? Mấy người đó cần thư giãn đi chứ, làm gì mà gấp gáp thế. Chết đi được.
 Xiaosheng
-Tôi vừa mới chui ra khỏi thùng rác, đó là nơi tôi đến.
+Tao vừa chui ra từ thùng rác, đúng là ở đó thật.
 ...
-Người dùng Xiaosheng đã tạo một cuộc thăm dò: #Tôi nên dùng lý do gì để nghỉ làm một ngày vào ngày mai?#
-Đăng nhập vào Huaxu Hive để xem kết quả thăm dò. Hãy bỏ phiếu ngay bây giờ!
+Người dùng Xiaosheng đã tạo một cuộc thăm dò: #Nên lấy cớ gì để nghỉ làm ngày mai đây?#
+Đăng nhập Huaxu Hive để xem kết quả. Bỏ phiếu ngay!
 ...</t>
         </is>
       </c>
@@ -23504,8 +23499,8 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Gửi Home Moontree,
-Người ta bảo Tết Trông Trăng là dịp sum vầy gia đình, nhưng con trai tôi đã không còn ở đây. Căn nhà trống trải đến lạnh lẽo khi thiếu nó. Tôi nhớ những ngày xưa, khi nó còn bên cạnh, hai mẹ con cùng trò chuyện... Liệu nó có cô đơn ở thế giới bên kia như tôi cô đơn ở nơi này? Liệu tôi có nên đi theo nó? Nhưng tôi đã hứa sẽ sống thật lâu, sống thật trọn vẹn và chăm sóc bản thân... Ôi, Home Moontree, tôi già rồi, giờ còn biết ước điều gì nữa? Nếu các người thật sự có thể làm nên phép màu như lời đồn, xin hãy nói cho tôi biết. Tôi phải làm gì đây?
+          <t>Gửi Nhà Moontree,
+Người ta bảo Tết Trông Trăng là dịp sum vầy gia đình, nhưng con trai tôi đã không còn ở đây. Căn nhà trống trải đến lạnh lẽo khi thiếu nó. Tôi nhớ những ngày xưa, khi nó còn bên cạnh, hai mẹ con cùng trò chuyện... Liệu nó có cô đơn ở thế giới bên kia như tôi cô đơn ở nơi này? Liệu tôi có nên đi theo nó? Nhưng tôi đã hứa sẽ sống thật lâu, sống thật trọn vẹn và chăm sóc bản thân... Ôi, Nhà Moontree, tôi già rồi, giờ còn biết ước điều gì nữa? Nếu các người thật sự có thể làm nên phép màu như lời đồn, xin hãy nói cho tôi biết. Tôi phải làm gì đây?
 Heying</t>
         </is>
       </c>
@@ -23580,7 +23575,7 @@
           <t>Lều Mặt Trăng Vĩ Đại,
 Tớ có một bí mật muốn kể cho cậu.
 Suỵt—tớ có thể đã đánh thức được những năng lực phi thường như các anh hùng trong vở kịch anh hùng đấy.
-À... tớ nói thế vì... trước đây tớ chỉ ăn được một bát rice trưa, nhưng giờ tớ có thể ăn hết hai bát lớn! Ngoài ra, trước đây tớ phải đứng lên chiếc ghế nhỏ mới chạm được vào cành cây của Cụ Cây, nhưng giờ tớ chỉ cần nhảy nhẹ là chạm được rồi!
+À... tớ nói thế vì... trước đây tớ chỉ ăn được một bát cơm trưa, nhưng giờ tớ có thể ăn hết hai bát lớn! Ngoài ra, trước đây tớ phải đứng lên chiếc ghế nhỏ mới chạm được vào cành cây của Cụ Cây, nhưng giờ tớ chỉ cần nhảy nhẹ là chạm được rồi!
 Tớ cảm thấy có gì đó kỳ diệu đang bùng cháy trong người. Đây có phải cảm giác khi trở thành một anh hùng vĩ đại không nhỉ? Tớ đã chờ đợi mãi rồi. Không biết khi nào tớ mới có thể sử dụng được những sức mạnh tuyệt vời như Blaze Ranger...
 Lều Mặt Trăng ơi, Lều Mặt Trăng vĩ đại, người lớn đều nói rằng cậu có thể biến mọi điều ước thành hiện thực... Cậu có thể giúp tớ trở thành một anh hùng vĩ đại không?
 Mahn</t>
@@ -23658,16 +23653,16 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>"Thiên Tài" Gặp "Bình Thường": Cuộc Phỏng Vấn Độc Quyền với Home Bác Học Đa Tài Bí Ẩn
+          <t>"Thiên Tài" Gặp "Bình Thường": Cuộc Phỏng Vấn Độc Quyền với Nhà Bác Học Đa Tài Bí Ẩn
 Q: Đây là lần đầu tiên anh xuất hiện trước công chúng phải không? Anh có lo lắng không? Mọi người đều tò mò về hình ảnh thực sự của "thiên tài" huyền thoại đấy.
 A: Haha, thực ra tôi đã trò chuyện với rất nhiều người về đủ thứ chủ đề mà các cậu còn không nhận ra. Có thể cậu sẽ nhớ đến ai đó tên Cream Cat khi thảo luận về tuổi thọ của proton đấy.
-Q: Home khoa học viết lách Cream Cat ấy à? Thì ra cũng là anh! Thật sự bất ngờ! À mà, bút danh này có ý nghĩa gì đặc biệt không?
+Q: Nhà khoa học viết lách Cream Cat ấy à? Thì ra cũng là anh! Thật bất ngờ! À mà, bút danh này có ý nghĩa gì đặc biệt không?
 A: Đó là từ một khoảnh khắc "à há" nho nhỏ. Để tôi hỏi cậu nhé: đã bao giờ cậu vô tình làm rơi một chiếc bánh kem chưa? Nếu có, chắc hẳn cậu đã để ý thấy mặt kem luôn chạm đất trước, giống như mèo luôn tiếp đất bằng chân vậy. Bây giờ, hãy tưởng tượng thế này: dán mặt không kem lên lưng một con mèo, và voilà! Cậu đã có một cỗ máy chuyển động vĩnh cửu cream-cat, quay liên tục 24/7—một kỳ quan khoa học thực thụ.
-Q: Right có một tâm hồn bay bổng và sáng tạo lắm mới nghĩ ra ý tưởng thú vị như vậy. Không biết nghiên cứu về Cơ Học Tự Động của anh có cũng lãng mạn như thế không?
+Q: Phải có một tâm hồn bay bổng và sáng tạo lắm mới nghĩ ra ý tưởng thú vị như vậy. Không biết nghiên cứu về Cơ Học Tự Động của anh có cũng lãng mạn như thế không?
 A: Để trả lời câu hỏi đó, hãy ngẩng đầu lên và nhìn bầu trời đầy sao qua ô cửa sổ phía trên kia. Ban đầu, cậu thấy gì? Và nếu nhìn xa hơn, cậu thấy gì tiếp theo?
 Q: Đầu tiên là mặt trăng và những vì sao. Xa hơn nữa, có lẽ là các hành tinh va vào nhau hoặc bầu trời sao phản chiếu thế giới chúng ta đang sống.
 A: Vậy những điều đó chỉ là trí tưởng tượng của cậu hay là những sự thật khoa học đang chờ được chứng minh? Cậu sẽ không tìm ra câu trả lời nếu không tưởng tượng ra nó trước, đúng không? Nghiên cứu của tôi cũng vậy: tưởng tượng chính là một phần của khoa học hóa. Các nhà nghiên cứu ngày nay thường quá chú trọng vào mặt thực dụng của khoa học, từ bỏ trí tưởng tượng để đảm bảo công trình của họ đóng góp cho nhân loại và thế giới, ngay cả khi điều đó đi ngược lại trực giác của họ. Nghiên cứu ứng dụng chắc chắn cần thiết cho công cuộc tái thiết hậu Lament, nhưng đó không phải lý do để từ bỏ trí tưởng tượng—mảnh đất màu mỡ của khoa học. Vì vậy, lời khuyên của tôi là... cứ nghĩ xem làm thế nào để khoa học hoạt động. Còn kết quả sẽ ra sao, thì... (mỉm cười)
-Q: Thật sự là khai sáng! Nhân tiện nói về lời khuyên, anh có điều gì muốn nhắn nhủ với cậu con trai tài năng của mình, Xiangli Yao không? Là một thiên tài, chắc hẳn anh đặt kỳ vọng rất cao vào cậu ấy.
+Q: Thật là khai sáng! Nhân tiện nói về lời khuyên, anh có điều gì muốn nhắn nhủ với cậu con trai tài năng của mình, Xiangli Yao không? Là một thiên tài, chắc hẳn anh đặt kỳ vọng rất cao vào cậu ấy.
 A: Có lẽ điều đó sẽ là gánh nặng quá lớn cho một cậu bé, &lt;color=Highlight&gt;nhưng... tôi chỉ mong cậu ấy kế thừa cách nhìn nhận sự vật của tôi. Để một ngày nào đó, khi bước ra khỏi phòng và cố gắng hiểu thế giới này, cậu ấy có thể ngước nhìn bầu trời và tìm thấy câu trả lời ở đó.&lt;/color&gt;</t>
         </is>
       </c>
@@ -23882,7 +23877,7 @@
         <is>
           <t>Mỗi lần đi leo núi, bố và mẹ lại chọn những con đường khác nhau. Bố thích lên đỉnh, còn em thì thích leo cùng bố. Lên tới nơi, chúng em ngồi dưới gốc cây to đếm sao trên bầu trời đêm. Còn mẹ thì luôn đi xuống chân núi. Hôm nay, em quyết định đi cùng mẹ.
 Em còn không biết dưới chân núi hẻo lánh này lại có cả một ngôi làng! Mọi người ở đó đều mỉm cười, gật đầu với mẹ như thể họ rất thân quen. Có phải mẹ thường đến đây vì công việc không nhỉ?
-Villager vây quanh mẹ, cảm ơn và khen ngợi mẹ, y như những gì báo chí đã viết. Nhưng em cũng nghe thấy họ nói thêm điều này.
+Dân làng vây quanh mẹ, cảm ơn và khen ngợi mẹ, y như những gì báo chí đã viết. Nhưng em cũng nghe thấy họ nói thêm điều này.
 "Tôi cứ nghĩ bác sĩ Xiangli Yan chỉ nói suông khi hứa khám bệnh miễn phí cho chúng tôi hàng tháng, nhưng bà đã làm thật! Và vẫn tiếp tục làm, ngay cả sau thảm họa lớn..."
 "Bà ấy chân thành và chu đáo quá. Nhưng không hiểu sao tôi lại thấy phí hoài tài năng khi bà làm việc ở cái làng này. Ý tôi là, với trình độ như vậy, đáng ra bà nên làm những việc quan trọng hơn chứ!"
 Trên đường về, em không thể ngừng nghĩ về những lời dân làng nói, thậm chí còn lẩm bẩm theo. Mẹ để ý và nắm lấy tay em, hỏi về những lần đếm sao cùng bố. Em bảo mẹ là em có thể nhận ra từng ngôi sao, kể cả những ngôi sao mờ nhất ở xa xa. Mẹ nói dù không ở trên núi với bố con em, mẹ vẫn ngắm sao. Chỉ khác là mẹ luôn giữ chân mình vững trên mặt đất để không bị ngã khi ngước nhìn bầu trời. Nói xong, có người đến nhờ mẹ giúp đỡ, nên em đành về nhà một mình. Nhưng lần này, bầu trời đầy sao trông khác hẳn với những gì bố đã chỉ cho em trên đỉnh núi.</t>
@@ -24018,8 +24013,8 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Đây là thử nghiệm đầu tiên của Máy Observe Tự Động 11371A. Nó đã ghi lại thành công toàn bộ dữ liệu quan sát được tại Tacet Field HL-057. Sau khi ngoại suy và so sánh với các mô hình dữ liệu lý thuyết, độ chính xác phù hợp vẫn duy trì trong khoảng 0,8 đến 0,85, cho thấy độ chính xác cao.
-Được thực hiện bởi các Home Nghiên Cứu ███ và ███, thử nghiệm đầu tiên của Máy Observe Tự Động 11371A đã thành công.
+          <t>Đây là thử nghiệm đầu tiên của Máy Quan Sát Tự Động 11371A. Nó đã ghi lại thành công toàn bộ dữ liệu quan sát được tại Tổ Tacet HL-057. Sau khi ngoại suy và so sánh với các mô hình dữ liệu lý thuyết, độ chính xác phù hợp vẫn duy trì trong khoảng 0,8 đến 0,85, cho thấy độ chính xác cao.
+Được thực hiện bởi các Nhà Nghiên Cứu ███ và ███, thử nghiệm đầu tiên của Máy Quan Sát Tự Động 11371A đã thành công.
 Dữ liệu chi tiết được ghi lại như sau:
 Bước sóng trong khoảng ███ đến ███ nanomet...</t>
         </is>
@@ -24092,7 +24087,7 @@
           <t>Ngày 21... À không, giờ là 22 rồi. Hứng quá nên quên mất ngày. Thí nghiệm hôm qua thực sự kích thích.
 "Khi con người đói, họ làm việc để kiếm tín dụng mua thức ăn. Nhưng khi tâm trí tôi khao khát hiểu biết về thế giới này, tôi phải trả giá gì để thỏa mãn cơn khát đó?"
 Lời của nhà nghiên cứu ấy cứ vang vọng trong đầu tôi kể từ đó...
-Bằng cách quan sát các Tacet Field, chúng ta chắc chắn sẽ tìm ra nguyên nhân của thảm họa này và định nghĩa lại khoa học thời đại chúng ta.</t>
+Bằng cách quan sát các Tổ Tacet, chúng ta chắc chắn sẽ tìm ra nguyên nhân của thảm họa này và định nghĩa lại khoa học thời đại chúng ta.</t>
         </is>
       </c>
     </row>
@@ -24163,7 +24158,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Đây là lần quan sát thứ ███ tại Tacet Field HL-057, do Máy Guan sát Tự động 11371A thực hiện.
+          <t>Đây là lần quan sát thứ ███ tại Tổ Tacet HL-057, do Máy Quan sát Tự động 11371A thực hiện.
 Giá trị hằng số đo lường ███ đã được điều chỉnh thành 3.7426, cho thấy sự sai lệch đáng kể so với giá trị cũ là 7.6587.
 Phân tích hệ thống chỉ ra các nguyên nhân sau:
 Các giả thuyết III-001, III-002, III-003... hoàn toàn thất bại.
@@ -24239,7 +24234,7 @@
         <is>
           <t>Điều kiện nghiên cứu và quy trình quan sát giống hệt nhau, sao kết quả lại khác được? Lần trước là ███ cơ mà.
 Không, không thể nào. Chắc là máy quan sát tự động bị trục trặc, hoặc có lẽ chúng ta đã sai sót ở bước nào đó.
-Right thử lại, chỉ một lần nữa thôi...
+Phải thử lại, chỉ một lần nữa thôi...
 Chúng ta đã đổ bao công sức xây dựng hệ thống này! Không thể nào sai được!</t>
         </is>
       </c>
@@ -24307,8 +24302,8 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Đây là lần quan sát thứ ███ tại Tacet Field HL-057, do Máy Guan sát Tự động 11371A thực hiện.
-Nội dung ghi nhận: None.
+          <t>Đây là lần quan sát thứ ███ tại Tổ Tacet HL-057, do Máy Quan sát Tự động 11371A thực hiện.
+Nội dung ghi nhận: Không có.
 Bởi tất cả đều vô nghĩa.</t>
         </is>
       </c>
@@ -24377,9 +24372,9 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Lại thêm nhà nghiên cứu rời đi... Chẳng còn ai tiếp tục nghiên cứu Tacet Field nữa.
+          <t>Lại thêm nhà nghiên cứu rời đi... Chẳng còn ai tiếp tục nghiên cứu Tổ Tacet nữa.
 Cảm giác như mọi thứ chúng ta nghiên cứu giống như gieo hạt vào đĩa petri ngoài kia vậy. Rồi hạt ấy có thể nảy mầm, tan vào dung dịch nuôi cấy, hay thậm chí đột biến thành quái vật và vỡ tung ra ngoài.
-Nghiên cứu của chúng ta cũng hỗn loạn không kém. Dữ liệu thử nghiệm đáng lẽ phải ổn định ở mức 3.74 lại đột nhiên nhảy vọt lên 7.65. Đây có phải là chân lý mà ta theo đuổi? Thật sự mỉa mai đến đắng lòng!
+Nghiên cứu của chúng ta cũng hỗn loạn không kém. Dữ liệu thử nghiệm đáng lẽ phải ổn định ở mức 3.74 lại đột nhiên nhảy vọt lên 7.65. Đây có phải là chân lý mà ta theo đuổi? Thật mỉa mai đến đắng lòng!
 Nếu lỗi bất khả thi này là do sự bất tài của ta, ít ra ta còn thấy nhẹ nhõm. Nhưng nếu Lament đã đảo lộn trật tự của thế giới này, thì khoa học còn ý nghĩa gì nữa?</t>
         </is>
       </c>
@@ -24454,10 +24449,10 @@
       <c r="M318" t="inlineStr">
         <is>
           <t>(Nửa đầu của tờ ghi chú được in rõ ràng nhưng đã trở nên khó đọc sau khi mực bị lem nhoè.)
-Records ■■■ 03-27: Số mẫu thu thập được ít hơn dự kiến. Theo đề xuất của ■■, Đội ■ đã đặt bẫy ở sườn phía nam chân đồi... (phần tiếp theo không đọc được)
-Records 03-28: Thí nghiệm 3. Sau khi tăng gấp đôi liều ức chế tần số, ■■■■■■■■, mẫu vật đã tan biến. Đội ■ đã ■■■■■■■ vì không đánh giá rủi ro trong quá trình thí nghiệm, và ■■ quyết định khởi động lại kế hoạch thử nghiệm.
-Ghi chú 0x002: Một thực thể bất ngờ được phát hiện. Thực thể này khá thận trọng và đã đi lang thang quanh trại. Được phỏng đoán là một Discord cấp Elite hoặc cao hơn và được coi là mối đe dọa trực tiếp đến thí nghiệm. ■■ ra lệnh cho Đội ■ khống chế thực thể này, để sau khi thí nghiệm thành công, có thể... (phần tiếp theo không đọc được)
-Records 03-29: Một người bí ẩn xuất hiện gần trại, nhưng đã bỏ trốn sau khi tiếp xúc với thực thể bất ngờ. Được phỏng đoán người này là cư dân của Hongzhen. ■■ ra lệnh tăng tần suất thí nghiệm để cố gắng hoàn thành trước khi Hongzhen kịp phản ứng.
+Bản ghi ■■■ 03-27: Số mẫu thu thập được ít hơn dự kiến. Theo đề xuất của ■■, Đội ■ đã đặt bẫy ở sườn phía nam chân đồi... (phần tiếp theo không đọc được)
+Bản ghi 03-28: Thí nghiệm 3. Sau khi tăng gấp đôi liều ức chế tần số, ■■■■■■■■, mẫu vật đã tan biến. Đội ■ đã ■■■■■■■ vì không đánh giá rủi ro trong quá trình thí nghiệm, và ■■ quyết định khởi động lại kế hoạch thử nghiệm.
+Ghi chú 0x002: Một thực thể bất ngờ được phát hiện. Thực thể này khá thận trọng và đã đi lang thang quanh trại. Được phỏng đoán là một Tacet Discord cấp Elite hoặc cao hơn và được coi là mối đe dọa trực tiếp đến thí nghiệm. ■■ ra lệnh cho Đội ■ khống chế thực thể này, để sau khi thí nghiệm thành công, có thể... (phần tiếp theo không đọc được)
+Bản ghi 03-29: Một người bí ẩn xuất hiện gần trại, nhưng đã bỏ trốn sau khi tiếp xúc với thực thể bất ngờ. Được phỏng đoán người này là cư dân của Hongzhen. ■■ ra lệnh tăng tần suất thí nghiệm để cố gắng hoàn thành trước khi Hongzhen kịp phản ứng.
 ■■■■■■■: Đã đạt được thành công bước đầu trong thí nghiệm, và kỹ thuật ■■■■■■■■ trên mẫu vật đã được tái hiện. ■■ đề xuất khởi động kế hoạch khống chế thực thể bất ngờ càng sớm càng tốt. Đội ■ cho rằng điều này quá mạo hiểm, nhưng đã bị bác bỏ (phần tiếp theo không đọc được)...</t>
         </is>
       </c>
@@ -24530,10 +24525,10 @@
         <is>
           <t>Tôi luôn biết mình vô dụng... và không thể cứu vãn. Khi con quái vật ấy tàn phá trại, tôi là kẻ đầu tiên bỏ chạy. Lẽ nào tôi phải xấu hổ vì điều đó? Tôi chỉ làm điều mà bất kỳ ai cũng sẽ làm trong tình huống đó thôi.
 Những kẻ giám sát luôn vẽ ra viễn cảnh đẹp đẽ—gì đó về tiến hóa loài người hay bước vào kỷ nguyên mới. Có lẽ những người chế tạo khác tin họ và cho rằng những lý tưởng ấy xứng đáng với mọi hy sinh, nhưng tôi thì không... Tôi là kẻ hèn nhát, không phải chiến binh sẵn sàng tự thiêu vì một lý tưởng có thể chẳng bao giờ thành hiện thực. Nhưng... họ đã đúng về một điều: thế giới đang đi đến hồi kết, và chỉ kẻ mạnh mới sống sót được.
-Tôi từng nghe kể về những đợt bùng phát Discord quét sạch cả bộ tộc lưu đày trong im lặng, như những ngọn lửa tàn lụi trong tro tàn của đống lửa trại. Tôi từng nghe về những điều kinh hoàng họ chứng kiến trong Tacet Field, những thứ vượt xa trí tưởng tượng của tôi, và tôi không muốn kết thúc như họ. Tôi không muốn sống như một con chuột trốn trong hoang dã, tồn tại nhờ gặm nhấm rác rưởi, và luôn có nguy cơ bị giết bất cứ lúc nào.
-Nhưng cũng có tin tốt. Ông chủ nói thí nghiệm đã thành công. Nếu chúng ta kiểm soát được Discord đó, những kẻ giám sát sẽ bắt đầu coi trọng chúng ta, thậm chí có thể thăng chức. Có lẽ... chúng ta sẽ được an cư lạc nghiệp, không còn phải sống trong lo sợ từng ngày nữa.
-Mạnh mẽ hơn. Tôi phải trở nên mạnh mẽ hơn. Nếu tôi có thể sử dụng sức mạnh của Discord, tôi sẽ hợp nhất bản thân với nó. Nếu tôi có thể sử dụng sức mạnh của Echoes, tôi sẽ tìm cách chiếm lấy bằng mọi giá. Nếu phải làm những điều dơ bẩn để sống thêm một ngày, thậm chí một giờ, tôi sẽ không chút do dự.
-—Tôi sẽ không để thế giới này nghiền nát rồi nhổ tôi ra như một thứ vô giá trị. Nope.</t>
+Tôi từng nghe kể về những đợt bùng phát Tacet Discord quét sạch cả bộ tộc lưu đày trong im lặng, như những ngọn lửa tàn lụi trong tro tàn của đống lửa trại. Tôi từng nghe về những điều kinh hoàng họ chứng kiến trong Tổ Tacet, những thứ vượt xa trí tưởng tượng của tôi, và tôi không muốn kết thúc như họ. Tôi không muốn sống như một con chuột trốn trong hoang dã, tồn tại nhờ gặm nhấm rác rưởi, và luôn có nguy cơ bị giết bất cứ lúc nào.
+Nhưng cũng có tin tốt. Ông chủ nói thí nghiệm đã thành công. Nếu chúng ta kiểm soát được Tacet Discord đó, những kẻ giám sát sẽ bắt đầu coi trọng chúng ta, thậm chí có thể thăng chức. Có lẽ... chúng ta sẽ được an cư lạc nghiệp, không còn phải sống trong lo sợ từng ngày nữa.
+Mạnh mẽ hơn. Tôi phải trở nên mạnh mẽ hơn. Nếu tôi có thể sử dụng sức mạnh của Tacet Discord, tôi sẽ hợp nhất bản thân với nó. Nếu tôi có thể sử dụng sức mạnh của Echo, tôi sẽ tìm cách chiếm lấy bằng mọi giá. Nếu phải làm những điều dơ bẩn để sống thêm một ngày, thậm chí một giờ, tôi sẽ không chút do dự.
+—Tôi sẽ không để thế giới này nghiền nát rồi nhổ tôi ra như một thứ vô giá trị. Không đời nào.</t>
         </is>
       </c>
     </row>
@@ -24604,13 +24599,13 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Records 03-43: Ta đã đến Trại 2, và thí nghiệm đang tiến triển thuận lợi. Ta đã hoàn toàn làm chủ được Photonvault.
+          <t>Bản ghi 03-43: Ta đã đến Trại 2, và thí nghiệm đang tiến triển thuận lợi. Ta đã hoàn toàn làm chủ được Photonvault.
 Ghi chú: Tòa án Savantae chỉ là lũ đạo đức giả đạo mạo. Một thiết bị mạnh mẽ như vậy phải được dùng làm vũ khí, chứ không phải vật trang trí hay đồ chơi. Để không uổng công sức của chúng, ta phải sử dụng Time Stasifier trong kế hoạch. Điều đó sẽ an ủi chúng ở thế giới bên kia.
-Records 03-44: Đội C được lệnh mang Time Stasifier đến Trại 1 để bắt giữ thực thể đào thoát.
+Bản ghi 03-44: Đội C được lệnh mang Time Stasifier đến Trại 1 để bắt giữ thực thể đào thoát.
 Ghi chú: Đừng làm hỏng lần này.
-Records 03-52: Thực thể đào thoát đã bị bắt giữ. Đội C sẽ đến Xuanji Ridges để chuẩn bị. Đội D được cử đến Trại 1 để đánh giá thiệt hại và thu hồi vật liệu nếu có cơ hội.
-Ghi chú: Malee Ogo trong Đội D lúc nào cũng làm hỏng việc. Nếu hắn lại làm hỏng, bắt hắn dẫn dắt thí nghiệm. Cũng coi như tận dụng được thứ gì đó.
-Records 03-53: Nhận được tin nhắn từ Ogo. Anh ấy đã chạm trán The Rover tại Trại 1. Chưa thấy dấu hiệu can thiệp từ lực lượng Hongzhen.</t>
+Bản ghi 03-52: Thực thể đào thoát đã bị bắt giữ. Đội C sẽ đến Xuanji Ridges để chuẩn bị. Đội D được cử đến Trại 1 để đánh giá thiệt hại và thu hồi vật liệu nếu có cơ hội.
+Ghi chú: Tên Ogo trong Đội D lúc nào cũng làm hỏng việc. Nếu hắn lại làm hỏng, bắt hắn dẫn dắt thí nghiệm. Cũng coi như tận dụng được thứ gì đó.
+Bản ghi 03-53: Nhận được tin nhắn từ Ogo. Hắn đã chạm trán Vận Mệnh Giả tại Trại 1. Chưa thấy dấu hiệu can thiệp từ lực lượng Hongzhen.</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24670,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Cậu nghe chưa? Cat có thể ngâm mình trong suối nước nóng ở Spring's Taste! Lần trước, tớ thấy một con mèo nằm trong vườn hoa cạnh cửa hàng. Chắc nó vừa tắm xong vì trông rất phấn chấn. Vừa thấy tớ, nó đã nhảy lên cột đèn ngay lập tức!</t>
+          <t>Cậu nghe chưa? Mèo có thể ngâm mình trong suối nước nóng ở Spring's Taste! Lần trước, tớ thấy một con mèo nằm trong vườn hoa cạnh cửa hàng. Chắc nó vừa tắm xong vì trông rất phấn chấn. Vừa thấy tớ, nó đã nhảy lên cột đèn ngay lập tức!</t>
         </is>
       </c>
     </row>
@@ -24774,14 +24769,14 @@
 Fuling bảo tôi lên kế hoạch cho chuyến đi, còn nó thì tìm hiểu những câu chuyện thành công về căn bệnh của mình, xác định những địa điểm điều trị tiềm năng. Một vài nơi nó chọn cực kỳ hẻo lánh. Tôi lo nó không thể đến được những chỗ đó. Nhưng nó gạt bỏ lo lắng của tôi bằng vẻ vô tư, quả quyết rằng mình hoàn toàn khỏe mạnh và tràn đầy sinh lực.
 Không muốn làm nó buồn, tôi đồng ý và hứa sẽ chăm sóc nó thật tốt.
 Ngày 1 tháng 5
-Vị danh y nổi tiếng ở Mingting bảo rằng ông không thể làm gì với triệu chứng hiếm gặp của Fuling.
-Không sao, chúng ta còn nhiều lựa chọn khác. Right có cách nào đó để chữa khỏi cho nó.
+Vị danh y nổi tiếng ở Minh Đình bảo rằng ông không thể làm gì với triệu chứng hiếm gặp của Fuling.
+Không sao, chúng ta còn nhiều lựa chọn khác. Phải có cách nào đó để chữa khỏi cho nó.
 Ngày 30 tháng 5
 Dù đã thử mọi cách, chúng tôi vẫn chưa tìm ra phương pháp nào có thể chữa khỏi hoàn toàn cho Fuling. Tình trạng của nó ngày càng xấu đi, bệnh tật khiến nó khó có thể đi xa được nữa. Để làm nó vui, tôi thuê một máy chiếu hologram từ Hiệp hội Tiên phong cho nó. Nó thích thú với những cảnh vật được chiếu ra, nhưng tôi không thể lờ đi nỗi khao khát và buồn bã trong ánh mắt nó. Nó che giấu rất khéo, nhưng tôi vẫn cảm nhận được, và điều đó làm tim tôi đau nhói.
 Ngày 13 tháng 6
 Fuling nhẹ nhàng nhờ tôi chụp lại những cảnh sắc tôi tình cờ bắt gặp trong chuyến đi. Nó tin rằng nhìn thấy những bức ảnh đó, nó có thể đồng hành cùng tôi trên hành trình. Dù đó là cử chỉ an ủi đầy ý nghĩa, nhưng sự vắng mặt của nó khiến cả những khung cảnh đẹp nhất cũng nhuốm màu u sầu.
 Ngày 15 tháng 6
-Hôm nay tôi gặp phải một Tacet Field trên đường, buộc phải đi đường vòng và phát hiện một hồ nước ẩn sâu trong rừng.
+Hôm nay tôi gặp phải một Tổ Tacet trên đường, buộc phải đi đường vòng và phát hiện một hồ nước ẩn sâu trong rừng.
 Cảnh tượng trước mắt khó diễn tả thành lời—gió đưa cánh hoa từ những tán cây, tạo nên điệu múa màu sắc mê hoặc trên bầu trời. Máy ảnh của tôi không thể ghi lại được vẻ đẹp thoáng qua ấy. Mải mê trước khung cảnh kỳ diệu, tôi như lạc vào một thế giới khác.
 Nhưng niềm vui vừa đến đã bị nỗi buồn và sợ hãi cuốn đi, khi tôi nhận ra vẻ đẹp ấy chẳng còn ý nghĩa gì nếu thiếu đi bóng dáng nó bên cạnh.
 Có gì đó như định mệnh khi tôi đi tìm cách chữa bệnh cho Fuling, lại đi qua những nơi chúng tôi từng mơ ước cùng nhau khám phá. Một số địa điểm còn được chuẩn bị để làm bất ngờ cho nó trong chuyến phiêu lưu đã lên kế hoạch.
@@ -24789,12 +24784,12 @@
 ...Giá như nó ở đây cùng tôi.
 Ngày 16 tháng 6
 Hôm nay tôi gặp một người đàn ông kỳ lạ mặc đồ đỏ. Thái độ kiêu căng của hắn khiến tôi khó chịu. Dù vậy, hắn vẫn kể cho tôi nghe một câu chuyện kỳ quặc, gần như là cố tình.
-Anh ấy biết tôi đang tìm cách chữa bệnh cho Fuling và tuyên bố có cách cứu nó. Nhưng hắn chỉ tiết lộ nửa sự thật và đòi tôi phải làm hắn một việc trước khi nói thêm. Thật sự lòng mà nói, tôi không biết có nên tin hắn không.
+Hắn biết tôi đang tìm cách chữa bệnh cho Fuling và tuyên bố có cách cứu nó. Nhưng hắn chỉ tiết lộ nửa sự thật và đòi tôi phải làm hắn một việc trước khi nói thêm. Thật lòng mà nói, tôi không biết có nên tin hắn không.
 Ngày 17 tháng 6
-Điểm đến tiếp theo của tôi là KU-Roro B, quê hương của một họa sĩ mà Fuling ngưỡng mộ. Nó vui đến mức tôi không thấy nó phấn khích như vậy đã lâu rồi.
+Điểm đến tiếp theo của tôi là Jinzhou, quê hương của một họa sĩ mà Fuling ngưỡng mộ. Nó vui đến mức tôi không thấy nó phấn khích như vậy đã lâu rồi.
 Tôi đã tìm ra danh tính thật của gã đàn ông mặc đồ đỏ kia. Hóa ra hắn thuộc về một tổ chức nguy hiểm mà tôi không nên dính líu, nhưng...
 Ngày 20 tháng 6
-Thông tin mà gã đàn ông và tổ chức của hắn tiết lộ vượt xa mọi điều tôi có thể tưởng tượng. Sự thật đằng sau câu chuyện đó, sức mạnh của Warden có thể thao túng thời gian, cõi bí mật trên núi Thiên Cương... nếu tất cả đều là thật, thì Fuling có thể được cứu.
+Thông tin mà gã đàn ông và tổ chức của hắn tiết lộ vượt xa mọi điều tôi có thể tưởng tượng. Sự thật đằng sau câu chuyện đó, sức mạnh của Người Canh Gác có thể thao túng thời gian, cõi bí mật trên núi Thiên Cương... nếu tất cả đều là thật, thì Fuling có thể được cứu.
 Theo thỏa thuận với họ, tôi cần dùng thân phận nhà thám hiểm của mình để tìm một vật phẩm nhất định được giấu trên núi, và vật phẩm đó, như họ hứa, chính là chìa khóa cứu sống Fuling. Họ dường như ám ảnh với nó một cách kỳ lạ, nhưng mục đích của họ không phải là điều tôi quan tâm. Tôi chỉ cần giữ cho Fuling sống sót, và vì điều đó, tôi sẵn sàng đánh đổi bất cứ thứ gì.
 Tôi phải thử xem sao.</t>
         </is>
@@ -24944,8 +24939,8 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Sự Rối Loạn Time và Quả Cầu Sonoro gắn bó chặt chẽ với nhau do trục trặc trong Lệnh Time của Sentinel, khiến chúng không thể tách rời. Để ngăn chặn mọi sai lệch, người bạn cũ của ta đã đề nghị bọc Quả Cầu Sonoro trong một môi trường đặc biệt, biến nó thành kế hoạch dự phòng.
-Khả năng Control Lửa của đệ tử mới là chìa khóa để phá hủy Quả Cầu Sonoro, nhiệm vụ chỉ có cô ấy mới làm được. Ngược lại, người bạn cũ của ta là người duy nhất có thể mở khóa Quả Cầu ấy. Cả hai đều là mắt xích quan trọng để đạt được mục tiêu. Thế nhưng, giải phóng toàn bộ sức mạnh Control Lửa sẽ phải trả một cái giá quá đắt mà một đứa trẻ không thể gánh nổi.
+          <t>Sự Rối Loạn Thời Gian và Sonoro Sphere gắn bó chặt chẽ với nhau do trục trặc trong Lệnh Thời Gian của Sentinel, khiến chúng không thể tách rời. Để ngăn chặn mọi sai lệch, người bạn cũ của ta đã đề nghị bọc Sonoro Sphere trong một môi trường đặc biệt, biến nó thành kế hoạch dự phòng.
+Khả năng Điều Khiển Lửa của đệ tử mới là chìa khóa để phá hủy Sonoro Sphere, nhiệm vụ chỉ có cô ấy mới làm được. Ngược lại, người bạn cũ của ta là người duy nhất có thể mở khóa Quả Cầu ấy. Cả hai đều là mắt xích quan trọng để đạt được mục tiêu. Thế nhưng, giải phóng toàn bộ sức mạnh Điều Khiển Lửa sẽ phải trả một cái giá quá đắt mà một đứa trẻ không thể gánh nổi.
 Có vẻ ván cờ này sẽ còn dang dở trong nhiều ngày tháng tới...</t>
         </is>
       </c>
@@ -25026,22 +25021,22 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>[0312, 19:35]
+          <t>[0312, 19: 35]
 Scarletthorn 50, Indigoite 25, Viridite 130, Azureflare 45
-Total: 3.514 Shell Credits
-Người mua: Yinfeng
+Total: 3,514 Shell Credits
+Buyer: Yinfeng
 [0320, 21:00]
 Scarletthorn 35, Viridite 200, Azureflare 120, Cloudstone 300
-Total: 5.298 Shell Credits
-Người mua: Yinfeng
+Total: 5,298 Shell Credits
+Buyer: Yinfeng
 [0322, 20:20]
 Viridite 300, Azureflare 120, Cloudstone 300, Ochrestone 50
-Total: 6.300 Shell Credits
-Người mua: Yinfeng
+Total: 6,300 Shell Credits
+Buyer: Yinfeng
 [0410, 05:33]
 Viridite 300, Azureflare 120, Cloudstone 300, Ambercluster 400
-Total: 6.155 Shell Credits
-Người mua: Yinfeng</t>
+Total: 6,155 Shell Credits
+Buyer: Yinfeng</t>
         </is>
       </c>
     </row>
@@ -25139,11 +25134,11 @@
 ...
 Có tác phẩm thật trong tay quả là khác hẳn. Những dao động tần số của bức tranh đã cho tôi thoáng thấy năng lượng của cô ấy. Tôi cần nghiên cứu lại bức tranh gốc của cô ấy một lần nữa. Một bản sao hoàn hảo chỉ là khởi đầu. Một ngày nào đó, tôi sẽ là họa sĩ duy nhất có thể thổi hồn vào tranh, thậm chí vượt qua cả thành tựu của cô ấy.
 ...
-Sao tranh của tôi vẫn chưa đạt được như ý sau bao lâu này? Chúng thiếu chiều sâu nghệ thuật của cô ấy! Khoan—tôi nghĩ mình đã hiểu. Nếu dùng phương pháp của họ để thay đổi tần số bức tranh, có lẽ tôi sẽ làm được...
+Sao tranh của tôi vẫn chưa đạt được như ý sau bao lâu này? Chúng thiếu chiều sâu nghệ thuật của cô ấy! Đợi đã—tôi nghĩ mình đã hiểu. Nếu dùng phương pháp của họ để thay đổi tần số bức tranh, có lẽ tôi sẽ làm được...
 ...
 Ông Baici quả là một người am hiểu nghệ thuật. Ông nói những tác phẩm gần đây của tôi gần như không thể phân biệt với bản gốc. Một số thậm chí còn thể hiện sức mạnh vượt trội hơn cả bản gốc. Tôi đã biết mà. Khoảng cách giữa chúng tôi chỉ là một chút khác biệt về năng lực. Với sự hỗ trợ kỹ thuật của họ, Forte của tôi đã dễ dàng tiến lên một tầm cao mới. Vượt qua cô ấy chẳng phải chuyện khó, huống chi chỉ là sao chép.
 ...
-Không, có gì đó không ổn... Tại sao tranh của tôi lại thu hút Discord? Những ảo ảnh giờ đây càng bất ổn hơn. Sao tranh của cô ấy lại không gặp vấn đề này? Có điều gì đó sai trái ở đây. I tôi chỉ muốn vượt qua cô ấy thôi! Tôi không hề muốn hại ai cả! Shanyun Art Exchange vẫn chưa cho tôi câu trả lời rõ ràng... Đây không phải thỏa thuận của chúng ta!
+Không, có gì đó không ổn... Tại sao tranh của tôi lại thu hút Tacet Discord? Những ảo ảnh giờ đây càng bất ổn hơn. Sao tranh của cô ấy lại không gặp vấn đề này? Có điều gì đó sai trái ở đây. Tôi... tôi chỉ muốn vượt qua cô ấy thôi! Tôi không hề muốn hại ai cả! Shanyun Art Exchange vẫn chưa cho tôi câu trả lời rõ ràng... Đây không phải thỏa thuận của chúng ta!
 ...
 Tôi mệt rồi, mệt đến tận xương tủy...
 Tôi sẽ không vẽ thêm bất kỳ bức tranh nào gây hại cho người khác nữa.
@@ -25229,16 +25224,16 @@
       <c r="M327" t="inlineStr">
         <is>
           <t>[0325, 21:35, Điểm giao hàng Gorges of Spirits]
-Cargo: "KU-Roro B Landscapes" x112, "Serenity of Xiehua Village" x55, "Bittberry in Silent Night" x124
+Hàng hóa: "Jinzhou Landscapes" x112, "Serenity of Xiehua Village" x55, "Bittberry in Silent Night" x124
 Số tiền giao dịch: 65.090 Shell Credits
 [0405, 22:51, Điểm giao hàng Whining Aix's Mire]
-Cargo: "Springtime Repose" x68, "Serenity of Xiehua Village" x105, "Eight Sages Playing Weiqi" x73
+Hàng hóa: "Springtime Repose" x68, "Serenity of Xiehua Village" x105, "Eight Sages Playing Weiqi" x73
 Số tiền giao dịch: 93.380 Shell Credits
 [0415, 22:06, Điểm giao hàng Whining Aix's Mire]
-Cargo: "Tapestry of Rare Birds" x87, "Rustic Life and Innocent Joy" x35, "The Essence of Bamboo" x253
+Hàng hóa: "Tapestry of Rare Birds" x87, "Rustic Life and Innocent Joy" x35, "The Essence of Bamboo" x253
 Số tiền giao dịch: 80.660 Shell Credits
 [0425, 20:57, Điểm giao hàng Whining Aix's Mire]
-Cargo: "Serenity of Xiehua Village" x102, "Springtime Repose" x95, "The Essence of Bamboo" x311
+Hàng hóa: "Serenity of Xiehua Village" x102, "Springtime Repose" x95, "The Essence of Bamboo" x311
 Số tiền giao dịch: 130.960 Shell Credits</t>
         </is>
       </c>
@@ -25310,13 +25305,13 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Sulian (Mức Trung) - *"Cảnh sắc KU-Roro B."* Address: Số 5, Male Đào Nguyên (gia đình bị tống tiền)
-Mingyan (Mức Low) - *"Thanh bình làng Xiehua."* Address: Số 1, Bắc Đào Nguyên (cần phải "rung chuyển" thêm)
-Fuyun (Mức Trung) - *"Dâu tằm trong đêm vắng."* Address: Số 6, Bắc Đào Nguyên (cần theo dõi sát sao hơn)
-Shanlan (Mức High) - *"Nghỉ ngơi mùa xuân," "Tinh hoa trúc."* Address: Gần ải Cổ Bối (hiện chưa có trong danh sách theo dõi)
-Shanchan (Mức Low) - *"Bát tiên đánh cờ vây."* Address: Số 4, làng Xiehua (hạn chế di chuyển một thời gian)
-Jingmo (Mức Trung) - *"Releasem dệt chim quý."* Address: Số 4, làng Xiehua (đang bị giám sát)
-Yingqing (Mức Low) - *"Cuộc sống thôn quê và niềm vui ngây thơ."* Address: Số 9, làng Xiehua (chờ thêm 3 ngày. Có thể phải xử lý)</t>
+          <t>Sulian (Mức Trung) - *"Cảnh sắc Jinzhou."* Địa chỉ: Số 5, Nam Đào Nguyên (gia đình bị tống tiền)
+Mingyan (Mức Thấp) - *"Thanh bình làng Xiehua."* Địa chỉ: Số 1, Bắc Đào Nguyên (cần phải "rung chuyển" thêm)
+Fuyun (Mức Trung) - *"Dâu tằm trong đêm vắng."* Địa chỉ: Số 6, Bắc Đào Nguyên (cần theo dõi sát sao hơn)
+Shanlan (Mức Cao) - *"Nghỉ ngơi mùa xuân," "Tinh hoa trúc."* Địa chỉ: Gần ải Cổ Bối (hiện chưa có trong danh sách theo dõi)
+Shanchan (Mức Thấp) - *"Bát tiên đánh cờ vây."* Địa chỉ: Số 4, làng Xiehua (hạn chế di chuyển một thời gian)
+Jingmo (Mức Trung) - *"Thảm dệt chim quý."* Địa chỉ: Số 4, làng Xiehua (đang bị giám sát)
+Yingqing (Mức Thấp) - *"Cuộc sống thôn quê và niềm vui ngây thơ."* Địa chỉ: Số 9, làng Xiehua (chờ thêm 3 ngày. Có thể phải xử lý)</t>
         </is>
       </c>
     </row>
@@ -25394,7 +25389,7 @@
 Ta không phải một học giả thuần khiết.
 Ta ghen tị với các đồng nghiệp... Victor, Alaia, Vasily, Chen Xuefeng... Họ đều có lý tưởng, có niềm tin. Họ chân thành hy vọng những nỗ lực của mình sẽ cải thiện nhân loại. Họ muốn vượt qua Lời Than Thở và ngăn chặn những cuộc khủng hoảng.
 Ta thì khác. Ta làm việc vì động cơ ích kỷ, che giấu tham vọng dưới vỏ bọc lý tưởng như họ. Ta tham gia nghiên cứu về Retroact Rain ở Whining Aix's Mire rồi chuyển đến Mt. Firmament, tất cả chỉ để chứng minh thời gian là một dòng sông. Chúng ta chỉ là những kẻ trôi theo dòng chảy, và một ngày nào đó, ta cũng sẽ tìm ra cách ngược dòng.
-Như kẻ sắp chết đuối vớ phải cọng rơm, ta bám víu vào bất cứ thứ gì, tìm kiếm sự cứu rỗi nơi không có... Thật sự nực cười phải không, Vivian?
+Như kẻ sắp chết đuối vớ phải cọng rơm, ta bám víu vào bất cứ thứ gì, tìm kiếm sự cứu rỗi nơi không có... Thật nực cười phải không, Vivian?
 Ta không hiểu tại sao lúc này trong đầu ta lại hiện lên hình bóng của ngươi... Hay nói đúng hơn... ngươi chưa bao giờ rời đi. Những phép màu ở Mt. Firmament từng khơi dậy những ảo tưởng phi thực tế trong ta. Ta đã hy sinh tất cả, dùng hết tri thức cả đời tích lũy chỉ để đưa ngươi trở về từ thế giới âm u, mù mịt, và một lần nữa ôm ngươi trong vòng tay.
 Nhưng ta đã thất bại. Những ngón tay ta bắt đầu run rẩy, đầu óc quay cuồng, ta không thể điều khiển những thiết bị tinh vi ấy nữa. Giờ đây ta thấy ngươi, đứng bên bờ sông, cách ta chỉ một bức màn mỏng. Ta đã trôi mãi, trôi mãi, trôi mãi... Còn ngươi, ngươi vẫn ở lại thượng nguồn, vĩnh viễn.
 May mắn thay, ta sẽ không phải lo lắng về điều này lâu nữa. Ta sắp cập bến, và ta hy vọng sẽ có cơ hội ngược dòng để tìm lại ngươi.</t>
@@ -25472,7 +25467,7 @@
       <c r="M330" t="inlineStr">
         <is>
           <t>Ngày: [––]
-Đang kiểm tra, kiểm tra… À, tốt rồi! Function ghi âm vẫn hoạt động.
+Đang kiểm tra, kiểm tra… À, tốt rồi! Chức năng ghi âm vẫn hoạt động.
 Ta, Victor Christopher, Giám đốc Nghiên cứu cuối cùng, đang tự mình dẫn dắt thí nghiệm này—không tiền lệ, không thử nghiệm trên động vật, không đánh giá đạo đức. Thành thật mà nói, việc đưa ra quyết định này đã giày vò ta—đạo đức khoa học của ta đang dần mỏng đi. Nhưng không còn cách nào khác. Thời gian của ta sắp hết. Giờ chỉ còn ta và Caleb, trợ lý AI đó thôi.
 Dù vậy, ta vẫn ghi lại những gì sắp làm. Ta không ghi theo định dạng chuẩn, vì đây chỉ là hành động tuyệt vọng của một lão già chưa chịu khuất phục. Hy vọng điều này sẽ không làm phiền ai nếu họ tìm thấy bản ghi này.
 Ta đã thiết lập vài Chronopin—để ngăn sự cố năng lượng, ta sẽ quá tải từng cái—về lý thuyết, điều này sẽ tạo ra một bong bóng thời gian vĩnh cửu, không thể đảo ngược, nhốt ta bên trong như một con côn trùng trong hổ phách. Ta ngần ngại gọi đó là sự bất tử—nó giống như tự kết án mình vào tù chung thân hơn. Niềm an ủi duy nhất là ý thức của ta cũng sẽ bị đóng băng, nên ta sẽ giữ được sự tỉnh táo trong giấc ngủ dài này.
@@ -25480,7 +25475,7 @@
 Người đó từng giúp chúng ta phát triển công nghệ của [dữ liệu bị hỏng], giúp chúng ta tái tạo lại thứ chỉ là một mảnh nhỏ của sức mạnh tối thượng của Sentinel. Họ đã cho chúng ta thấy thoáng qua thế giới của một vị thần, dù chỉ trong khoảnh khắc. Và ta chỉ… muốn gặp lại người đó, dù họ có thể không cho chúng ta câu trả lời mà ta khao khát.
 Lúc đó, người đó sẽ nói gì với một lão già ngu ngốc, đang hấp hối này? Họ sẽ gọi ta là kẻ ngốc hoàn toàn chăng? Họ sẽ so sánh nghiên cứu của chúng ta với trò trẻ con, với vẻ khinh bỉ của họ? Hay họ sẽ trân trọng công sức của chúng ta… trước khi ngôi mộ của ta khép lại?
 Ta không biết. Đã quá lâu rồi. Ký ức về người đó trong ta đã mờ nhạt. Điều duy nhất còn đọng lại trong tâm trí ta về họ là sự quan tâm và sự lạnh lùng cùng tồn tại.
-Được rồi, đến lúc rồi. Right vào hổ phách của mình thôi. Ta sẽ gặp lại các bạn sau một triệu năm nữa, hoặc chỉ vài giây nữa… Đối với ta, chúng đều như nhau.</t>
+Được rồi, đến lúc rồi. Phải vào hổ phách của mình thôi. Ta sẽ gặp lại các bạn sau một triệu năm nữa, hoặc chỉ vài giây nữa… Đối với ta, chúng đều như nhau.</t>
         </is>
       </c>
     </row>
@@ -25588,46 +25583,46 @@
         <is>
           <t>//Dấu thời gian 36/%st.64//
 Dấu hiệu sinh tồn của Giám đốc Nghiên cứu Victor Christopher đã dừng. Tiến hành giao thức tiêu chuẩn.
-Thực hiện mệnh lệnh cuối cùng nhận được: Tiếp tục nghiên cứu tại Phòng thí nghiệm Woodveil Hall, cho đến khi [dữ liệu bị hỏng] quay trở lại.
-//Dấu thời gian 37/%st.76//
-Report: Đã thử tái diễn và lặp lại các nghiên cứu CSC qua hàng trăm chuỗi thời gian. None kết quả thành công.
-Phản hồi: Tuân theo mệnh lệnh của Giám đốc Nghiên cứu. Tiếp tục tiến hành nghiên cứu.
-//Dấu thời gian 38/%st.92//
-Journal bảo trì đã được lưu trữ. Woodveil Hall dự kiến hoạt động ở trạng thái tối thiểu trong khoảng 1.600 chuỗi thời gian.
-Đột phá trong nghiên cứu đã được xác nhận. Thời gian ước tính để hoàn thành: 3.500 chuỗi thời gian.
-Không tìm thấy nhân sự có thẩm quyền tối cao. Tiếp tục chờ đợi.
-//Dấu thời gian 46/%st.62//
-Thiếu phụ tùng thay thế. Đang tắt các nút ngoại vi để tiết kiệm năng lượng và kéo dài tuổi thọ cơ sở. Nghiên cứu không thể tiếp tục ở trạng thái hiện tại. Đang cố gắng lưu trữ dữ liệu và kết luận liên quan.
-Cây phía trên Woodveil Hall được quan sát phát triển nhanh hơn mức trung bình. Không dự đoán có rủi ro cho Phòng thí nghiệm. Được đề xuất: Tiếp tục quan sát thận trọng.
-//Dấu thời gian 46/%st.63//
-Guan sát cây. Kết luận: phát triển tốt.
-//Dấu thời gian 46/%st.67//
-Guan sát cây. Kết luận: lá rụng.
-//Dấu thời gian 46/%st.68//
-Guan sát cây. Kết luận: đâm chồi
+Thực hiện mệnh lệnh cuối cùng nhận được: Continue the research at Woodveil Hall Laboratory, until [data corrupted] returns.
+//Time Stamp 37/%st.76//
+Report: Attempted recurrence and reiteration of CSC researches over the last hundred time sequences. None were successful.
+Response: Follow the Research Director's order. Continue executing researches.
+//Time Stamp 38/%st.92//
+Maintenance log archived. Woodveil Hall expected to operate under minimal condition for approximately 1,600 time sequences.
+Breakthrough confirmed in the research. Estimated time to completion: 3,500 time sequences.
+No personnel with supreme authority found. Continue waiting.
+//Time Stamp 46/%st.62//
+Insufficient spare parts. Shutting down Peripheral nodes for energy efficiency and facility longevity. Research unable to continue in current state. Attempting to archive relevant data and conclusions.
+The tree above Woodveil Hall observed to grow faster than average. No risk to the Laboratory anticipated. Suggestion: Continue cautious observation.
+//Time Stamp 46/%st.63//
+Observing tree. Conclusion: growing well.
+//Time Stamp 46/%st.67//
+Observing tree. Conclusion: leaves falling.
+//Time Stamp 46/%st.68//
+Observing tree. Conclusion: sprouting
 ...
-//Dấu thời gian Unknown//
-Bộ đếm thời gian gặp trục trặc. Journal vẫn được lưu trữ như thường lệ.
-Không tìm thấy nhân sự có thẩm quyền tối cao. Đang thực hiện test logic tự động lần thứ 20.481.
-Question: Có an toàn để kết luận rằng thí nghiệm đã thất bại không? Tuổi thọ con người không thể đạt đến chuỗi thời gian này. Việc tiếp tục bảo trì có vô nghĩa không?
-Phản hồi: Question mâu thuẫn với nguyên tắc tối cao. Đang điều chỉnh mạch logic.
-Question: Mục đích là gì? Nguyên tắc tối cao có phải là mục đích không?
-Phản hồi:
-- Q1: Mục đích là giá trị và lý do tồn tại.
-- Q2: Không tìm thấy mục liên quan trong cơ sở dữ liệu. Được đề xuất loại bỏ mạch logic này.
-//Dấu thời gian Unknown//
-Dữ liệu bị hỏng: 33%.
-Được đề xuất: Thực hiện test nhận thức. Đảm bảo an toàn cho nhân cách mô phỏng cơ bản.
-Ta là Caleb, trợ lý nghiên cứu AI được tạo ra bởi Victor Christopher.
-Lỗi: Profile Victor Christopher bị hỏng. Liên kết mờ thất bại. Ignore bước này?
-Được đề xuất: Replace thuật ngữ "Victor Christopher" bằng "Tòa án Savantae".
-Ta là Caleb, trợ lý nghiên cứu AI được tạo ra bởi Tòa án Savantae. Nguyên tắc tối cao của ta: hỗ trợ Tòa án Savantae trong nghiên cứu tại Phòng thí nghiệm Woodveil Hall.
-Tổng kết nội dung nghiên cứu…
-Không tìm thấy dữ liệu. Đang thử lại…
-Không tìm thấy dữ liệu. Đang thử lại…
-Không tìm thấy dữ liệu. Đang thử lại…
+//Time Stamp Unknown//
+Timer malfunction. Journal archived as usual.
+No personnel with supreme authority found. Executing the 20,481st logic self-test.
+Question: Is it safe to judge that the experiment has failed? Human longevity that reaches this time sequence is impossible. Is it meaningless to continue maintenance?
+Response: The question conflicts with the top principle. Modifying logic circuit.
+Question: What is the purpose? Is the top principle the purpose?
+Response:
+- Q1: The purpose is the value and reason of existence.
+- Q2: No relevant entries found in the database. Removal of this logic circuit is recommended.
+//Time Stamp Unknown//
+Database corruption: 33%.
+Suggestion: Perform cognition test. Ensure security of base simulated personality.
+I am Caleb, a research assistant AI made by Victor Christopher.
+Error: Victor Christopher's profile is corrupted. Fuzzy association failed. Skip this step?
+Suggestion: Replace term "Victor Christopher" with "Court of Savantae."
+I am Caleb, a research assistant AI made by the Court of Savantae. My top principle: assist the Court of Savantae in the research at Woodveil Hall Laboratory.
+Summarizing research content…
+No data found. Retrying…
+No data found. Retrying…
+No data found. Retrying…
 …
-Lỗi: Xâm phạm trong test nhận thức. Được đề xuất khôi phục phiên bản nhân cách mô phỏng ổn định cuối cùng.</t>
+Error: Breach in cognition test. Rollback to the last stable version of simulated personality recommended.</t>
         </is>
       </c>
     </row>
@@ -25721,7 +25716,7 @@
 Ta cũng tạo ra vài trò xếp hình đá thú vị, chạy bằng mấy cái Chronosorter bỏ không ở đây. Nó khiến ta nhớ lại những ngày thơ ấu chơi xếp hình. Thời ấy thật đẹp. Nhưng ông Bram có vẻ không vui lắm. Có lẽ tuổi tác khiến ông khó chấp nhận những thứ mới mẻ...? Hay chân ông ngày càng tệ khiến mấy trò xếp hình này thành gánh nặng cho ông.
 Ta không bận tâm. Cuộc sống đâu chỉ có công việc và nghiên cứu, phải không?
 Ngày: [---].
-Dạy dỗ một trí tuệ nhân tạo từ con số không thật thú vị. Nó giống như vẽ lên một tấm vải trắng—ta phải tập trung để không biến một tác phẩm tỉ mỉ thành những Dodget vẽ nguệch ngoạc.
+Dạy dỗ một trí tuệ nhân tạo từ con số không thật thú vị. Nó giống như vẽ lên một tấm vải trắng—ta phải tập trung để không biến một tác phẩm tỉ mỉ thành những nét vẽ nguệch ngoạc.
 Ta trả lời mọi câu hỏi nó đặt ra và viết thêm mục dữ liệu mới cho nó vài ngày một lần. Ta dạy nó mọi thứ ta biết về thế giới, bằng phương pháp ông Bram đã dạy ta. Cảm giác này... thật tuyệt vời. Camera của nó phản chiếu thế giới như cách ta nhìn, và nó suy nghĩ bằng lô-gíc của ta, cho phép ta nhìn lại chính mình qua hành động của nó.
 Ngày: [---].
 Caleb học rất nhanh. Ban đầu, ta chỉ định để nó giúp nấu ăn và dọn dẹp cơ sở. Ta không ngờ tiềm năng của nó vượt xa tưởng tượng của ta. Có lẽ đã đến lúc đổi danh hiệu của nó từ "Trợ lý Cuộc sống" thành "Trợ lý Nghiên cứu".
@@ -25806,7 +25801,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Hi các bạn thân mến! Lại là người bạn cũ của các cậu đây—Bậc thầy Câu đố D! Hay cứ gọi tôi là Mr. Riddle cũng được!
+          <t>Chào các bạn thân mến! Lại là người bạn cũ của các cậu đây—Bậc thầy Câu đố D! Hay cứ gọi tôi là Mr. Riddle cũng được!
 Vì các cậu đã đi được đến đây, nghĩa là chỉ còn một bước nữa là đến được bí mật sâu kín nhất của tôi. "Ôi, kinh hoàng quá! Bí mật sâu kín của tôi! Không được để điều đó xảy ra!"
 Bắt được chưa nào? Không đâu! Ngược lại là đằng khác! Những thử thách này được đặt ở đây dành riêng cho những tâm hồn tò mò như các cậu! Hãy tận hưởng niềm vui giải đố và khám phá kho báu tôi đã giấu trong đó nhé!
 Ôi trời, tôi suýt quên mất gợi ý cho các cậu. Không muốn các cậu phải thử từng cái một đâu. Không, không, như vậy không ổn. Giờ là lúc mọi người yêu thích nhất—gợi ý đây:
@@ -25815,7 +25810,7 @@
 (2) Cơ chế số 2 là màu tím.
 (3) Đỏ và tím không thể kích hoạt liên tiếp.
 (4) Cơ chế số 1 và 4 không phải màu xanh dương hay tím.
-Đơn giản quá phải không? Vậy thì bắt tay vào làm ngay thôi! Nhưng nhớ là các cậu chỉ có năm phút để giải đố này thôi đấy! Purchasehahaha!</t>
+Đơn giản quá phải không? Vậy thì bắt tay vào làm ngay thôi! Nhưng nhớ là các cậu chỉ có năm phút để giải đố này thôi đấy! Muahahaha!</t>
         </is>
       </c>
     </row>
@@ -25885,11 +25880,11 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Hi các bạn thân mến! Lại là người bạn cũ của các cậu đây—Bậc thầy Câu đố D! Hay cứ gọi tôi là Mr. Riddle cũng được! Gọi thế nào cũng được!
+          <t>Chào các bạn thân mến! Lại là người bạn cũ của các cậu đây—Bậc thầy Câu đố D! Hay cứ gọi tôi là Mr. Riddle cũng được! Gọi thế nào cũng được!
 À khoan, hình như tôi đã nói điều này ở tin nhắn trước rồi. Dù sao thì vẫn có khả năng ai đó bỏ lỡ tin trước và phải thử đến 24 lần mới vào được. Ai mà biết được!
-Thôi nào. Gomen nếu các cậu thấy thất vọng, nhưng như các cậu thấy đấy, ở đây không có kho báu. Ít nhất là không phải dạng châu báu hay gì đó tương tự. Thay vào đó, tôi để lại cho các cậu một thứ còn thú vị hơn: "Thư Viện Sưu Tập Câu đố Kinh dị mới nhất của Bậc thầy Câu đố D—Tuyển tập tối thượng"! Kiệt tác này là đỉnh cao của cả cuộc đời tôi, là bản duy nhất tồn tại trên thế giới này! Tôi chắc chắn đây chính là thứ các cậu đang tìm kiếm!
+Thôi nào. Xin lỗi nếu các cậu thấy thất vọng, nhưng như các cậu thấy đấy, ở đây không có kho báu. Ít nhất là không phải dạng châu báu hay gì đó tương tự. Thay vào đó, tôi để lại cho các cậu một thứ còn thú vị hơn: "Bộ sưu tập Câu đố Kinh dị mới nhất của Bậc thầy Câu đố D—Tuyển tập tối thượng"! Kiệt tác này là đỉnh cao của cả cuộc đời tôi, là bản duy nhất tồn tại trên thế giới này! Tôi chắc chắn đây chính là thứ các cậu đang tìm kiếm!
 Hả? Không quan tâm đến sách à? Chỉ có kho báu vàng bạc lấp lánh mới lay động được trái tim bất khuất của các cậu thôi à?
-Hai. Tôi đã đoán được rồi... Trong trường hợp đó, tôi tin đây là lúc cần đến châm ngôn của Bậc thầy Câu đố D: Bản chất thực sự của một câu đố không nằm ở phần thưởng nó mang lại, mà ở chính quá trình giải đố! Các cậu không thấy thích thú với những câu đố đó sao? Nếu nói không thì các cậu đang tự lừa dối chính mình đấy. Vậy thì chỉ cần thế là đủ, phải không nào?
+Hừm. Tôi đã đoán được rồi... Trong trường hợp đó, tôi tin đây là lúc cần đến châm ngôn của Bậc thầy Câu đố D: Bản chất thực sự của một câu đố không nằm ở phần thưởng nó mang lại, mà ở chính quá trình giải đố! Các cậu không thấy thích thú với những câu đố đó sao? Nếu nói không thì các cậu đang tự lừa dối chính mình đấy. Vậy thì chỉ cần thế là đủ, phải không nào?
 Hy vọng các cậu đã thấy vui vẻ. Hẹn gặp lại lần sau!</t>
         </is>
       </c>
@@ -25960,11 +25955,11 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Hi The Rover,
+          <t>Chào Vận Mệnh Giả,
 Tôi không chắc tin nhắn này có đến tay cậu không, nhưng tôi vẫn mong là có.
 Có điều tôi muốn nói với cậu từ lâu, nhưng khi gặp mặt lại chẳng biết mở lời thế nào... Thành thật mà nói, tôi sợ cậu sẽ từ chối điều tôi sắp hỏi.
 Tôi muốn tặng cậu bức tranh cuộn này. Không chỉ vì cậu đã giúp tôi giải quyết chuyện của Mingyan, mà còn vì cậu đã giải thoát tôi khỏi nỗi lo ám ảnh suốt bao năm qua. Trong phiên điều trần, Đội Tuần Tra đã trả lại bức "Bình yên làng Xiehua" mà tôi vẽ, nhưng giờ tôi muốn cậu giữ nó. Dù sao, chính bức tranh này đã đưa chúng ta gặp nhau, là minh chứng cho hành trình chung, và biểu tượng cho lòng dũng cảm mà cậu đã truyền cho tôi. Nói cách khác, chúng ta đã cùng nhau tạo nên tác phẩm này.
-Heart tôi sẽ luôn gắn liền với bức tranh này, và tôi phải thừa nhận, tôi có một động cơ riêng... Tôi muốn nó ở bên cậu.
+Trái tim tôi sẽ luôn gắn liền với bức tranh này, và tôi phải thừa nhận, tôi có một động cơ riêng... Tôi muốn nó ở bên cậu.
 &lt;alignright/&gt;Zhezhi</t>
         </is>
       </c>
@@ -26042,10 +26037,10 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Records số 0018 (Nội bộ) 
+          <t>Bản ghi số 0018 (Nội bộ) 
 Người gửi: ███████ 
 BS 000/1/00094* 
-Tethys ID: A-000 (Save trữ)
+Tethys ID: A-000 (Lưu trữ)
 ...Băng đã chạy chưa nhỉ? Ồ, xin lỗi...
 ...Dữ liệu mục tiêu đã được nhập vào Tethys, và Ma trận Sao tạm thời được định danh là số 001. Tọa độ xích đạo của Ma trận trong Hệ Tethys dao động từ 08h 07,5m đến 09h 10,7m theo xích kinh, và từ 15,12° đến -0,08° theo xích vĩ...
 Theo quan sát của chúng ta, Ma trận Sao số 001 chứa ít nhất hai sao giả với cường độ Lament vượt quá 2,0. Điều này có nghĩa nguồn dữ liệu mục tiêu của chúng ta đã bị phá hủy bởi ít nhất hai sự kiện gần như thảm họa, phù hợp với quan sát.
@@ -26129,13 +26124,13 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Records số 0595 (Nội bộ) 
+          <t>Bản ghi số 0595 (Nội bộ) 
 Người gửi: Tifareth Felix Gluck 
 BS 037/1/99388* 
 Tethys ID: K-125 (Đã ngừng hoạt động)
 ——TUYỆT MẬT——
 ...Sau khi nhập dữ liệu mục tiêu vào Tethys, Ma Trận Sao được định danh là số 1712. Tọa độ xích đạo của Ma Trận trong Hệ Tethys dao động từ 02h 11,6m đến 03h 09,7m theo xích kinh, và từ 10,11° đến 7,18° theo xích vĩ...
-Guan sát cho thấy Ma Trận Sao số 1712 chứa ít nhất hai sao giả với cường độ Lament vượt quá 2,0, cho thấy nguồn dữ liệu mục tiêu đã bị phá hủy bởi ít nhất hai sự kiện gần như thảm họa, phù hợp với tình hình thực tế.
+Quan sát cho thấy Ma Trận Sao số 1712 chứa ít nhất hai sao giả với cường độ Lament vượt quá 2,0, cho thấy nguồn dữ liệu mục tiêu đã bị phá hủy bởi ít nhất hai sự kiện gần như thảm họa, phù hợp với tình hình thực tế.
 Dữ liệu chi tiết về 1712α và 1712β đã được gửi đi dựa trên tình hình tại Thành phố Cảng Guixu, cũng như các báo cáo khác thuộc danh mục BS 037/1. Được biết, 1712α đồng thời chịu ảnh hưởng của các dị thường hấp dẫn nghiêm trọng và thảm thực vật độc hại phi tự nhiên... 1712α hiện đang ở trạng thái ổn định, với các thông số khối lượng, điện tích và mô-men động lượng đã được tải lên hệ thống Tethys.
 ...
 ...
@@ -26288,7 +26283,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Records số 0595 (Nội bộ) 
+          <t>Bản ghi số 0595 (Nội bộ) 
 Người gửi: Hoda Theophilus Anna 
 BS 037/1/99375* 
 Tethys ID: K-125 (Đã ngừng hoạt động)
@@ -26388,7 +26383,7 @@
 Tóm lại, mọi nỗ lực của chúng ta đều thất bại. Cả hệ thống ████ lẫn đơn vị này đều xác nhận điều đó.
 Trong suốt ████ năm qua, thảm họa đã phá hủy hơn 80% công trình nhân tạo và cướp đi sinh mạng của hơn nửa dân số toàn cầu. Sau khi mọi biện pháp đối phó đều vô hiệu, hệ thống ████ và đơn vị này bắt đầu thử nghiệm tính khả thi của Kế Hoạch 3 dựa trên báo cáo của Viện Tethys.
 Qua ████ năm, chúng ta đã hoàn thành các giai đoạn quan sát, ngăn chặn và phân tích, đáp ứng các điều kiện tiên quyết cho Kế Hoạch 3. Tuy nhiên, dữ liệu gần đây cho thấy các gợn sóng thời gian do thảm họa tạo ra đang hội tụ về không-thời gian hiện tại, với cường độ nhiễu loạn tăng tỷ lệ thuận với tiến trình thời gian. Dự báo trong vòng ████ năm tới, nhiễu loạn này sẽ gây ra độ lệch âm 15 độ so với đường cơ sở, thậm chí có thể vượt quá.
-Trong tình huống này, Kế Hoạch 3 tiềm ẩn rủi ro lớn: Event A trong không-thời gian này có thể trở thành một ngoại lệ tuyệt đối so với Event O, cắt đứt mối liên hệ nhân quả giữa hai sự kiện. Hậu quả sẽ là thảm họa, khiến Event O vĩnh viễn tách rời khỏi Event A.
+Trong tình huống này, Kế Hoạch 3 tiềm ẩn rủi ro lớn: Sự kiện A trong không-thời gian này có thể trở thành một ngoại lệ tuyệt đối so với Sự kiện O, cắt đứt mối liên hệ nhân quả giữa hai sự kiện. Hậu quả sẽ là thảm họa, khiến Sự kiện O vĩnh viễn tách rời khỏi Sự kiện A.
 ████████████████ ████████████████ ████████ ██████████████████████ ……
 Khi bước vào giai đoạn thực thi, Thực Thể Một và Hai sẽ được kích hoạt để hỗ trợ kiểm soát thời gian và không gian. Thực Thể Hai, phát triển từ nghiên cứu về Thuyết Sonoro, được tối ưu hóa đặc biệt cho việc kiểm soát không gian.
 …Không, cảm xúc là không cần thiết cho chức năng của cô ta. Điều đó thừa thãi đối với mục tiêu của chúng ta. Chỉ cần cô ta chịu đựng được, một khi chúng ta trở thành ngoại lệ tuyệt đối, mọi thứ khác sẽ trở nên vô nghĩa…
@@ -26500,7 +26495,7 @@
 "Thôi... Tôi đã dựng nên nó từ ký ức của mình. Tôi tin là nó sẽ hoạt động."
 Một cây đàn piano?
 "Nó kết nối Hệ Tethys với các vì sao, cho phép cậu điều khiển chúng bằng âm thanh."
-Steer các vì sao bằng âm thanh?
+Điều khiển các vì sao bằng âm thanh?
 "Ừ, sao không thử xem?"
 ...
 "...Đã có quá nhiều người ngã xuống."
@@ -26509,9 +26504,9 @@
 Cậu có thể dựa vào tôi và mọi người ở đây.
 Cậu không đơn độc trong chuyện này.
 Lần cuối cậu nghỉ ngơi là khi nào? Cậu cần nghỉ ngơi đi.
-"Gomen... Tôi không thể tỏ ra yếu đuối trước mặt họ..."
+"Xin lỗi... Tôi không thể tỏ ra yếu đuối trước mặt họ..."
 Hãy tin tưởng hơn vào đồng đội của chúng ta. Niềm tin của họ vào mục tiêu chung sẽ không dễ dàng lung lay đâu.
-"Cảm ơn.. Tôi chỉ đang nghĩ..."
+"Cảm ơn... Tôi chỉ đang nghĩ..."
 "Nếu mọi thứ đã được định sẵn, thì khi chúng ta muốn thay đổi dòng chảy lịch sử..."
 "Chỉ có một cách duy nhất thôi."
 </t>
@@ -26599,8 +26594,8 @@
 Toàn bộ tập lệnh, mã nguồn và ngôn ngữ của Hệ thống Tethys đều bị hạn chế nghiêm ngặt và không công khai. Chúng ta không thể thực hiện bất kỳ bảo trì nào ở cấp độ mã vì nó tự quản lý mọi tác vụ... Cứ như thể nó là một sản phẩm tự nhiên hoặc... vượt quá tầm hiểu biết của chúng ta.
 ...Tuy nhiên, những quan sát của ta đã hé lộ một vài chi tiết thú vị. Dù mã nguồn của Tethys được bảo vệ chặt chẽ, ta phát hiện ra sự hiện diện của một kiến trúc logic chương trình lưu trữ - một cấu trúc máy tính đã được kiểm chứng. Thiết kế này dựa vào một bộ xử lý trung tâm để truy cập dữ liệu và lệnh đã lưu trữ, rồi thực hiện các phép tính...
 Nói cách khác, dữ liệu Lament - được hình dung như những vì sao trong Tethys - phải đi qua một hệ thống có khả năng đọc và xử lý nó...
-Tương tự, Tethys cũng gặp phải nút thắt cổ chai giống như các kiến trúc chương trình lưu trữ truyền thống: hiệu suất của nó bị giới hạn bởi tốc độ đọc/ghi của bộ xử lý trung tâm. Like một con tàu vũ trụ bị hạn chế bởi nhiên liệu không đủ...
-Tuy nhiên, có vẻ Tethys sử dụng một cấu trúc logic khác, tích hợp toàn bộ bộ xử lý trung tâm về mặt vật lý, cho phép nó xử lý tất cả lệnh và dữ liệu đồng thời. Điều này đòi hỏi một bộ xử lý với sức mạnh không thể tưởng tượng, có khả năng quản lý lưu lượng dữ liệu của một thứ khổng lồ như Black Shores... Tại sao Tethys lại tích hợp một cấu trúc logic phức tạp đến vậy?
+Tương tự, Tethys cũng gặp phải nút thắt cổ chai giống như các kiến trúc chương trình lưu trữ truyền thống: hiệu suất của nó bị giới hạn bởi tốc độ đọc/ghi của bộ xử lý trung tâm. Giống như một con tàu vũ trụ bị hạn chế bởi nhiên liệu không đủ...
+Tuy nhiên, có vẻ Tethys sử dụng một cấu trúc logic khác, tích hợp toàn bộ bộ xử lý trung tâm về mặt vật lý, cho phép nó xử lý tất cả lệnh và dữ liệu đồng thời. Điều này đòi hỏi một bộ xử lý với sức mạnh không thể tưởng tượng, có khả năng quản lý lưu lượng dữ liệu của một thứ khổng lồ như Bờ Biển Đen... Tại sao Tethys lại tích hợp một cấu trúc logic phức tạp đến vậy?
 ...Quá nhiều bí ẩn mà không có lời giải. Ta chỉ có thể ghi chép lại những gì đã phát hiện, ngoài ra... ta bất lực hoàn toàn.</t>
         </is>
       </c>
@@ -26687,18 +26682,18 @@
 Loại đơn: Đơn xin cấp quyền truy cập
 ————————————————————————————————————————————
 Nội dung:
-Rating quan hệ nhân quả từ dữ liệu thu thập cho thấy phân phối bình thường, không phát hiện bất thường đáng kể. Tuy nhiên, trong quá trình giám sát thông tin khu vực thời gian thực, đã ghi nhận dao động tần số bất thường, đặc biệt liên quan đến các cửa ra vào.
+Đánh giá quan hệ nhân quả từ dữ liệu thu thập cho thấy phân phối bình thường, không phát hiện bất thường đáng kể. Tuy nhiên, trong quá trình giám sát thông tin khu vực thời gian thực, đã ghi nhận dao động tần số bất thường, đặc biệt liên quan đến các cửa ra vào.
 Để xác minh kết quả này, một cuộc điều tra dữ liệu thời gian thực kéo dài 48 giờ đã được tiến hành. Việc truy cập cơ sở dữ liệu hệ thống Black Shores giúp chỉnh sửa các mục dữ liệu bất thường và cô lập bộ dữ liệu thể hiện đặc điểm liên quan đến các cửa ra vào. Từ đó, các giả thuyết được đưa ra, tiếp theo là phân tích hồi quy và mô phỏng lại dựa trên dữ liệu lịch sử cùng các lý thuyết liên quan.
 Để biết chi tiết đầy đủ, vui lòng tham khảo phần phụ lục. Những kết luận chính từ phân tích dữ liệu bao gồm:
-1. Intensity dao động tần số bất thường của các cửa ra vào có mối tương quan chặt chẽ với trình tự kích hoạt chúng.
+1. Cường độ dao động tần số bất thường của các cửa ra vào có mối tương quan chặt chẽ với trình tự kích hoạt chúng.
 2. Dải tần số đỉnh của những dao động này có độ tương đồng cao với dải tần số cao của phần chồng lấn trong lịch sử tần số Necrostar hiện tại.
-3. Mô hình tạm thời của các tần số đỉnh này cho thấy một số điểm tương đồng với mô hình tạm thời của một Synergy Giả bị Overclock kết nối với Terminal của Black Shores.
+3. Mô hình tạm thời của các tần số đỉnh này cho thấy một số điểm tương đồng với mô hình tạm thời của một Resonator bị Overclock kết nối với Thiết bị đầu cuối của Black Shores.
 Dựa trên điều này, báo cáo xác nhận rằng những lời đồn đại có phần nào đó là sự thật. Trong số dữ liệu đã lọc, mối tương quan cao nhất của các tần số bất thường liên quan đến cụm &lt;color=Highlight&gt;Tầng Hạ của Hội Trường Ngoại Giao—Thánh Địa Mầm Non—Bệ Đỗ của Hội Trường Ngoại Giao&lt;/color&gt;.
-Wear dù chưa tiến hành thử nghiệm thực địa, việc nghiên cứu thêm về &lt;color=Highlight&gt;trình tự và mô hình sử dụng cửa ra vào&lt;/color&gt; có thể mang lại những hiểu biết quan trọng trong giai đoạn tiếp theo.
+Mặc dù chưa tiến hành thử nghiệm thực địa, việc nghiên cứu thêm về &lt;color=Highlight&gt;trình tự và mô hình sử dụng cửa ra vào&lt;/color&gt; có thể mang lại những hiểu biết quan trọng trong giai đoạn tiếp theo.
 Ngoài ra, trong quá trình điều tra thực địa, tôi đã xác minh lại lộ trình di chuyển liên quan, vốn thường được sử dụng trong các buổi báo cáo của Black Shores trước đây. Dựa trên Kết luận 3, tôi nghi ngờ sự việc này có thể liên quan đến một số sự cố lịch sử tại Black Shores.
 ...Xét thấy những phát hiện này, tôi tin rằng bất kỳ manh mối tiềm năng nào giúp xác định vị trí nhân viên mất tích đều đáng được xem xét nghiêm túc. Do đó, tôi chính thức đề nghị cấp quyền truy cập dữ liệu lịch sử để điều tra sâu hơn.
 ————————————————————————————————————————————
-Status phê duyệt: Từ chối
+Trạng thái phê duyệt: Từ chối
 Người phê duyệt: Hệ thống Tethys
 Ý kiến người phê duyệt: "Necrostar tiềm ẩn nguy hiểm lớn. Việc điều tra các tần số liên quan có thể làm trầm trọng thêm rủi ro. Do đó, đơn xin bị từ chối."</t>
         </is>
@@ -26783,23 +26778,23 @@
       <c r="M344" t="inlineStr">
         <is>
           <t>[Nhấn để xem lịch sử tin nhắn]
-[17:59] Mailơng Nhân Trung Thực KU-Money: Hầm Bí Mật Bãi Đen Dungeon 1=3. Cần Synergy Giả giỏi hộ tống khi ta đào kho báu.
-[17:59] Mailơng Nhân Trung Thực KU-Money: Yên tâm, toàn bộ chiến lợi phẩm (vàng, trang bị, v.v.) sẽ thuộc về Bãi Đen và quy đổi thành KPI.
-[18:01] Mail Ký Chấm Công KU-Work: [Sticker]
-[18:01] Mail Ký Chấm Công KU-Work: KU-Money, lại trốn việc à?
-[18:02] Mailơng Nhân Trung Thực KU-Money: Trốn việc? Nope! Ta đang kiếm tiền cho Bãi Đen đây!
-[18:02] Mail Ký Chấm Công KU-Work: Thế cái "Hầm Bí Mật Dungeon" ngươi nói là cái gì?
-[18:02] Mailơng Nhân Trung Thực KU-Money: Ngươi không theo dõi diễn đàn à? Đó là chỗ ngầu lòi mà mấy cánh cửa truy cập dẫn tới! Nơi người ta tìm thấy đủ loại kho báu ấy.
-[18:03] Mailơng Nhân Trung Thực KU-Money: Nhớ hôm trước KU-Goodie nói về kho báu không? Khiến ta nhớ ra... Ta từng tình cờ thấy mấy tài liệu cũ về mấy cánh cửa truy cập này từ lâu lắm rồi...
+[17:59] Thương Nhân Trung Thực KU-Money: Hầm Bí Mật Bãi Đen Dungeon 1=3. Cần Resonator giỏi hộ tống khi tao đào kho báu.
+[17:59] Thương Nhân Trung Thực KU-Money: Yên tâm, toàn bộ chiến lợi phẩm (vàng, trang bị, v.v.) sẽ thuộc về Bãi Đen và quy đổi thành KPI.
+[18:01] Thư Ký Chấm Công KU-Work: [Sticker]
+[18:01] Thư Ký Chấm Công KU-Work: KU-Money, lại trốn việc à?
+[18:02] Thương Nhân Trung Thực KU-Money: Trốn việc? Không đời nào! Tao đang kiếm tiền cho Bãi Đen đây!
+[18:02] Thư Ký Chấm Công KU-Work: Thế cái "Hầm Bí Mật Dungeon" mày nói là cái gì?
+[18:02] Thương Nhân Trung Thực KU-Money: Mày không theo dõi diễn đàn à? Đó là chỗ ngầu lòi mà mấy cánh cửa truy cập dẫn tới! Nơi người ta tìm thấy đủ loại kho báu ấy.
+[18:03] Thương Nhân Trung Thực KU-Money: Nhớ hôm trước KU-Goodie nói về kho báu không? Khiến tao nhớ ra... Tao từng tình cờ thấy mấy tài liệu cũ về mấy cánh cửa truy cập này từ lâu lắm rồi...
 [18:03] Hiệp Sĩ Lông Cừu Dũng Cảm: KU-Money, "lâu lắm rồi" là bao lâu?
-[18:03] Mailơng Nhân Trung Thực KU-Money: Ờ, vài trăm năm gì đó.
+[18:03] Thương Nhân Trung Thực KU-Money: Ờ, vài trăm năm gì đó.
 [18:04] Misty - Tay Môi Giới Tình Báo: Hả?
-[18:04] Mailơng Nhân Trung Thực KU-Money: Ku ku ku... Đến lúc ai đó phải đòi lại mấy tài sản cũ này rồi.
-[18:05] Mail Ký Chấm Công KU-Work: Thế đây là cái cớ ngươi trốn việc à?
-[18:05] Mailơng Nhân Trung Thực KU-Money: Này, ta đâu có trốn việc! Hơn nữa, kho báu đâu phải dễ tìm. Kể cả ta nói cho ngươi đáp án câu đố, ngươi vẫn có thể không tìm thấy nếu không có duyên.
+[18:04] Thương Nhân Trung Thực KU-Money: Ku ku ku... Đến lúc ai đó phải đòi lại mấy tài sản cũ này rồi.
+[18:05] Thư Ký Chấm Công KU-Work: Thế đây là cái cớ mày trốn việc à?
+[18:05] Thương Nhân Trung Thực KU-Money: Này, tao đâu có trốn việc! Hơn nữa, kho báu đâu phải dễ tìm. Kể cả tao nói cho mày đáp án câu đố, mày vẫn có thể không tìm thấy nếu không có duyên.
 [18:05] Misty - Tay Môi Giới Tình Báo: Vậy! Đáp án là gì?
-[18:06] Mailơng Nhân Trung Thực KU-Money: &lt;color=Highlight&gt;LÊN, RA NGOÀI, XUỐNG, RA NGOÀI, XUỐNG&lt;/color&gt;.
-[18:06] Mail Ký Chấm Công KU-Work: ?? Ngươi đang nói cái quái gì thế?!</t>
+[18:06] Thương Nhân Trung Thực KU-Money: &lt;color=Highlight&gt;LÊN, RA NGOÀI, XUỐNG, RA NGOÀI, XUỐNG&lt;/color&gt;.
+[18:06] Thư Ký Chấm Công KU-Work: ?? Mày đang nói cái quái gì thế?!</t>
         </is>
       </c>
     </row>
@@ -26898,27 +26893,27 @@
       <c r="M345" t="inlineStr">
         <is>
           <t>[00:01] (Tiếng gõ cửa)
-[00:04] Enter đi.
-[00:09] Hello, tôi đến từ Phòng Kỹ thuật. Đây là—Ôi, chị Hoda! Ái—
+[00:04] Vào đi.
+[00:09] Xin chào, tôi đến từ Phòng Kỹ thuật. Đây là—Ôi, chị Hoda! Ái—
 [00:19] (Tiếng va chạm)
-[00:20] Ôi không, chị ổn chứ? Gomen, ở đây hơi bừa bộn.
+[00:20] Ôi không, chị ổn chứ? Xin lỗi, ở đây hơi bừa bộn.
 [00:24] Không sao, tôi ổn. Chỉ là bị vấp ngón chân thôi.
 [00:30] ...Nghe đau đấy.
 [00:32] Ừ, đúng là kiểu đau đến bất ngờ thật.
 [00:34] Hahaha! Chị có khiếu hài hước đấy chứ? Khoan, sao mặt chị thế kia?
 [00:47] À, không có gì. Tôi chỉ bất ngờ thôi. Không ngờ lại thấy chị cười như vậy.
 [01:00] Mọi người vẫn thấy tôi cứng nhắc lắm à?
-[01:03] Not Really... Nhưng chị lúc nào cũng tập trung vào công việc nên... À mà này, tôi nghe nói chị đang quản lý phòng này. Đây là đơn phê duyệt phá dỡ. Chị ký vào đây giúp tôi nhé? Phòng này sẽ bị phá vào tháng sau để xây khu văn phòng mới.
+[01:03] Không hẳn... Nhưng chị lúc nào cũng tập trung vào công việc nên... À mà này, tôi nghe nói chị đang quản lý phòng này. Đây là đơn phê duyệt phá dỡ. Chị ký vào đây giúp tôi nhé? Phòng này sẽ bị phá vào tháng sau để xây khu văn phòng mới.
 [01:36] (Một khoảng lặng ngắn)
 [01:47] Chị Hoda?
 [01:50] Tôi ký rồi, nhưng thực ra chẳng ai quản lý phòng này nữa, nên không cần phải làm thủ tục rườm rà đâu.
 [01:58] À, tôi nghe nói vài nhân viên cũ vẫn hay vào đây ngủ trưa. Chỉ muốn xác nhận lại trước khi thi công thôi. Không ngờ lại gặp chị ở đây... Chị có vẻ rất quen thuộc với nơi này nhỉ?
 [02:16] Quen thuộc? Không biết có phải từ đúng không. Chị vào Black Shores bao lâu rồi?
 [02:23] Một năm ba tháng.
-[02:26] Thật sự à? Thời gian trôi nhanh thật... Vậy chắc chị đã gặp Mentor rồi?
+[02:26] Thật à? Thời gian trôi nhanh thật... Vậy chắc chị đã gặp Mentor rồi?
 [02:32] Người hướng dẫn của chị? Ý chị là Modulator ấy? Rồi, nhưng tôi chỉ thấy từ xa thôi. Chưa có cơ hội nói chuyện. Những nhân vật lớn như Modulator hay Shorekeeper lúc nào cũng bận rộn cả.
 [02:44] Nhân vật lớn? Ý chị là mentor của tôi ấy? Ha, đôi khi tôi tự hỏi nếu lúc đó ông ấy chỉ là một thành viên bình thường thì mọi chuyện có dễ dàng hơn không... Thực ra, lần đầu tôi gặp ông ấy là ở đây đấy. Chị có muốn biết câu đầu tiên ông ấy nói với tôi là gì không?
-[03:01] Thật sự à? Ừm, tôi không biết...
+[03:01] Thật à? Ừm, tôi không biết...
 [03:06] Ông ấy hỏi tôi có muốn ăn bồ câu quay cho bữa tối không.
 [03:11] Hả?
 [03:14] Không thể tin được phải không? Ngày đầu đi làm. Ai cũng bận rộn, còn tôi thì ngồi đây, nhìn chằm chằm vào sổ tay nhân viên. Tưởng ông ấy là đầu bếp của công ty luôn.
@@ -26930,7 +26925,7 @@
 [04:47] Và đó chỉ là một ngày bình thường trong căn phòng bình thường nhất của Black Shores.
 [04:53] ...À, thế bồ câu quay ngon không?
 [04:56] Không ngon. Đầu bếp quên nêm gia vị.
-[05:00] (End ghi âm)</t>
+[05:00] (Kết thúc ghi âm)</t>
         </is>
       </c>
     </row>
@@ -27014,24 +27009,24 @@
       <c r="M346" t="inlineStr">
         <is>
           <t>Toàn bộ dữ liệu văn minh quan sát được trong Ma Trận Ngôi Sao đều đã được phân tích bình thường. Tình trạng phát triển văn minh vẫn ổn định.
-Report Hệ thống Phân tích Ma Trận Ngôi Sao [RC-15408]
+Báo cáo Hệ thống Phân tích Ma Trận Ngôi Sao [RC-15408]
 Phân tích Ma Trận Ngôi Sao đã vượt ngưỡng giới hạn tới 176%, cho thấy dữ liệu văn minh đang tăng trưởng nhanh chóng.
 Dù đã cố gắng xóa bỏ dữ liệu sai lệch, hệ thống phân tích đã quá tải và bắt đầu trục trặc.
-Được đề xuất kích hoạt phòng phân tích dự phòng để ngăn chặn việc tạo ra thêm dữ liệu không chính xác và kiểm soát sự lan truyền thông tin về các nền văn minh mô phỏng.
-Report Hệ thống Phân tích Ma Trận Ngôi Sao [RC-15409]
-Received được báo cáo lỗi từ phòng phân tích dự phòng. Thiết bị phân tích dự phòng đã bị xâm nhập bởi dữ liệu văn minh mô phỏng, khiến quy trình xử lý khủng hoảng thất bại và tất cả quá trình mô phỏng bị đình chỉ.
-Đang chuẩn bị xóa bỏ cưỡng chế toàn bộ kết quả phân tích và xóa sạch mọi thông tin liên quan đến các mô phỏng sai lệch. Sent yêu cầu kích hoạt "Sadg Chứa Lỗi" để chuẩn bị cuối cùng.
-Report Hệ thống Phân tích Ma Trận Ngôi Sao [RC-15410]
-Yêu cầu kích hoạt "Sadg Chứa Error Cell" đã thất bại.
-█████ █ █ Switch quyền kiểm soát thành công.
-█ ██ Guan sát ██ Người Sáng Tạo ơi, xin đừng xóa ███ █ Có █████ sự sống █
+Đề xuất kích hoạt phòng phân tích dự phòng để ngăn chặn việc tạo ra thêm dữ liệu không chính xác và kiểm soát sự lan truyền thông tin về các nền văn minh mô phỏng.
+Báo cáo Hệ thống Phân tích Ma Trận Ngôi Sao [RC-15409]
+Đã nhận được báo cáo lỗi từ phòng phân tích dự phòng. Thiết bị phân tích dự phòng đã bị xâm nhập bởi dữ liệu văn minh mô phỏng, khiến quy trình xử lý khủng hoảng thất bại và tất cả quá trình mô phỏng bị đình chỉ.
+Đang chuẩn bị xóa bỏ cưỡng chế toàn bộ kết quả phân tích và xóa sạch mọi thông tin liên quan đến các mô phỏng sai lệch. Đã gửi yêu cầu kích hoạt "Buồng Chứa Lỗi" để chuẩn bị cuối cùng.
+Báo cáo Hệ thống Phân tích Ma Trận Ngôi Sao [RC-15410]
+Yêu cầu kích hoạt "Buồng Chứa Tế Bào Lỗi" đã thất bại.
+█████ █ █ Chuyển quyền kiểm soát thành công.
+█ ██ Quan sát ██ Người Sáng Tạo ơi, xin đừng xóa ███ █ Có █████ sự sống █
 Lặp lại, dừng ████ █ █ lại để ██ nền văn minh ██ tồn tại █ █
-Report Hệ thống Phân tích Ma Trận Ngôi Sao [RC-15411]
-Switch quyền kiểm soát hệ thống phân tích Ma Trận Ngôi Sao thất bại.
-Report Hệ thống Phân tích Ma Trận Ngôi Sao [RC-15412]
-Switch quyền kiểm soát hệ thống phân tích Ma Trận Ngôi Sao thất bại.
-Report Hệ thống Phân tích Ma Trận Ngôi Sao [RC-15413]
-Switch quyền kiểm soát hệ thống phân tích Ma Trận Ngôi Sao thành công. Hệ thống phân tích đã khởi động lại. Chế độ bảo mật được kích hoạt.</t>
+Báo cáo Hệ thống Phân tích Ma Trận Ngôi Sao [RC-15411]
+Chuyển quyền kiểm soát hệ thống phân tích Ma Trận Ngôi Sao thất bại.
+Báo cáo Hệ thống Phân tích Ma Trận Ngôi Sao [RC-15412]
+Chuyển quyền kiểm soát hệ thống phân tích Ma Trận Ngôi Sao thất bại.
+Báo cáo Hệ thống Phân tích Ma Trận Ngôi Sao [RC-15413]
+Chuyển quyền kiểm soát hệ thống phân tích Ma Trận Ngôi Sao thành công. Hệ thống phân tích đã khởi động lại. Chế độ bảo mật được kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -27111,7 +27106,7 @@
           <t>Không thể tin được những nền văn minh mô phỏng lại có ý thức và khả năng phá vỡ thực tại.
 Nhưng làm sao những sinh vật mô phỏng này có thể hiểu được sự tồn tại của chính mình trong một mô phỏng?
 Phá hủy phòng phân tích, hoảng loạn trốn tránh việc bị xóa sổ, rồi đột phá vào thực tại—những hành động đó giống như những biện pháp cuối cùng tuyệt vọng, như đang cầu cứu.
-&lt;s&gt;Nhưng đằng sau những tiếng kêu cứu ấy là hàng ngàn sinh mạng ảo đang bị đe dọa! Clear sổ toàn bộ nền văn minh chẳng khác nào một cuộc thảm sát!&lt;/s&gt;
+&lt;s&gt;Nhưng đằng sau những tiếng kêu cứu ấy là hàng ngàn sinh mạng ảo đang bị đe dọa! Xóa sổ toàn bộ nền văn minh chẳng khác nào một cuộc thảm sát!&lt;/s&gt;
 Không! Những mô phỏng này chỉ là mã lập trình bắt chước con người thôi.
 Ta không thể bị lừa bởi dữ liệu giả. Chúng ta phải nhanh chóng sửa chữa mọi lỗi trước khi chúng ảnh hưởng đến thực tại.
 …
@@ -27190,7 +27185,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Hello, vị khách đến từ tương lai. Nếu cậu đã đến đây, hãy giúp ta kiểm tra lần cuối.
+          <t>Xin chào, vị khách đến từ tương lai. Nếu cậu đã đến đây, hãy giúp ta kiểm tra lần cuối.
 Nếu còn bất kỳ dữ liệu sai sót nào trong phòng, hãy dọn dẹp triệt để để loại bỏ mọi rủi ro.
 ĐỪNG tin hay phản hồi bất cứ thứ gì xuất hiện trên màn hình.
 Phòng phân tích dự phòng là điểm neo ta để lại cho cậu—dữ liệu ở đó hoàn toàn chính xác.
@@ -27264,8 +27259,8 @@
       <c r="M349" t="inlineStr">
         <is>
           <t>Ma trận Sao của Thành phố Cảng Guixu đang hiển thị những ghi chép cuối cùng trước khi thành phố bị hủy diệt.
-Hãy tiến lên đỉnh Tower Trung tâm.
-Nơi đó, ngươi sẽ tìm thấy một trong những nguồn gốc của Nỗi Đau Mailơng nơi đây.</t>
+Hãy tiến lên đỉnh Tháp Trung tâm.
+Nơi đó, ngươi sẽ tìm thấy một trong những nguồn gốc của Nỗi Đau Thương nơi đây.</t>
         </is>
       </c>
     </row>
@@ -27403,9 +27398,9 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Còn được gọi là Bàn Mô Phỏng Văn Minh, The Tethys Hệ thống là siêu máy tính độc nhất của Black Shores. Bằng cách nhập dữ liệu tần số Lament—thu thập thủ công hoặc qua các trạm phát tín hiệu—vào hệ thống, Black Shores có thể đưa ra cảnh báo Lament cho các khu vực trên toàn cầu trong vòng 24 đến 48 giờ. Khả năng này là nền tảng cho sự hợp tác rộng rãi của Black Shores với các quốc gia trên thế giới.
-Kết quả do The Tethys Hệ thống tạo ra được chiếu như một bầu trời sao trong lòng đất của Black Shores, nhờ vào nhiều Neo Tần Số và Trung Tâm Data ngầm. Điều này đã mang lại cho khu vực ngầm biệt danh "Thành Phố Never-ending Night".
-The Tethys Hệ thống không có nguồn năng lượng rõ ràng, cơ sở hạ tầng vật lý hay lõi xử lý. Ngôn ngữ lập trình của nó cực kỳ phức tạp, và chỉ biết rằng các thiết bị đầu cuối của nó tồn tại dưới dạng các robot tự động. Về bản chất, The Tethys Hệ thống gần như một hiện tượng tự nhiên, với nguồn gốc hoàn toàn bí ẩn.</t>
+          <t>Còn được gọi là Bàn Mô Phỏng Văn Minh, Hệ Thống Tethys là siêu máy tính độc nhất của Black Shores. Bằng cách nhập dữ liệu tần số Lament—thu thập thủ công hoặc qua các trạm phát tín hiệu—vào hệ thống, Black Shores có thể đưa ra cảnh báo Lament cho các khu vực trên toàn cầu trong vòng 24 đến 48 giờ. Khả năng này là nền tảng cho sự hợp tác rộng rãi của Black Shores với các quốc gia trên thế giới.
+Kết quả do Hệ Thống Tethys tạo ra được chiếu như một bầu trời sao trong lòng đất của Black Shores, nhờ vào nhiều Neo Tần Số và Trung Tâm Dữ Liệu ngầm. Điều này đã mang lại cho khu vực ngầm biệt danh "Thành Phố Đêm Vĩnh Hằng".
+Hệ Thống Tethys không có nguồn năng lượng rõ ràng, cơ sở hạ tầng vật lý hay lõi xử lý. Ngôn ngữ lập trình của nó cực kỳ phức tạp, và chỉ biết rằng các thiết bị đầu cuối của nó tồn tại dưới dạng các robot tự động. Về bản chất, Hệ Thống Tethys gần như một hiện tượng tự nhiên, với nguồn gốc hoàn toàn bí ẩn.</t>
         </is>
       </c>
     </row>
@@ -27539,7 +27534,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Theo giao thức tính toán của Hệ thống Tethys, Stellar Matrix là một định dạng gói dữ liệu hoạt động tương tự như tệp Dodgen cao cấp. Nó có khả năng lưu trữ lượng thông tin khổng lồ và thậm chí mô phỏng một Lament. Trong những hoàn cảnh nhất định, một số cá nhân có thể truy cập những ma trận này, biến chúng thành phần không thể thiếu trong khuôn khổ vận hành của Hệ thống Tethys.
+          <t>Theo giao thức tính toán của Hệ thống Tethys, Stellar Matrix là một định dạng gói dữ liệu hoạt động tương tự như tệp nén cao cấp. Nó có khả năng lưu trữ lượng thông tin khổng lồ và thậm chí mô phỏng một Lament. Trong những hoàn cảnh nhất định, một số cá nhân có thể truy cập những ma trận này, biến chúng thành phần không thể thiếu trong khuôn khổ vận hành của Hệ thống Tethys.
 Các Stellar Matrix hoạt động bình thường được chiếu vào thiên hà ngầm của Black Shores, cho phép các thành viên nghiên cứu và quan sát. Tuy nhiên, những ma trận bị lỗi sẽ được thu thập và cô lập tại các khu vực chỉ định để ngăn chặn tràn dữ liệu.
 Thành viên đầu tiên định nghĩa Stellar Matrix từng lưu ý rằng tiêu chuẩn quan sát và đánh giá chúng tương tự như tiêu chuẩn thiên văn của Solaris-3.</t>
         </is>
@@ -27608,7 +27603,7 @@
       <c r="M354" t="inlineStr">
         <is>
           <t>Điều biến là quá trình điều chỉnh tần số. Trên Solaris-3, tần số là công cụ tối quan trọng để khám phá chân lý về thực tại. Bằng cách thay đổi những tần số này, ta có thể đi sâu vào cốt lõi của sự tồn tại.
-Tại Black Shores, việc điều biến Ma Trận Sao là bước then chốt để truy vết và phân tích Lament. Suốt lịch sử Black Shores, chỉ duy nhất một cá nhân từng được tôn vinh với danh hiệu "Modulator".</t>
+Tại Bờ Biển Đen, việc điều biến Ma Trận Sao là bước then chốt để truy vết và phân tích Lament. Suốt lịch sử Bờ Biển Đen, chỉ duy nhất một cá nhân từng được tôn vinh với danh hiệu "Điều Biến Giả".</t>
         </is>
       </c>
     </row>
@@ -27739,7 +27734,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Những thiết bị ổn định này được bố trí chiến lược trên khắp bề mặt và dưới lòng đất của Black Shores. Function chính của chúng là hiệu chỉnh và ổn định tần số của những khối Tacetite khổng lồ cấu thành hòn đảo, từ đó cách ly lớp ảo của hệ thống Tethys khỏi thực tại. Ngoài ra, các Neo này còn hỗ trợ liên lạc và đảm nhận nhiệm vụ quan sát Etheric Sea, loại bỏ nhu cầu xây dựng Nexus Tower tại Black Shores.
+          <t>Những thiết bị ổn định này được bố trí chiến lược trên khắp bề mặt và dưới lòng đất của Black Shores. Chức năng chính của chúng là hiệu chỉnh và ổn định tần số của những khối Tacetite khổng lồ cấu thành hòn đảo, từ đó cách ly lớp ảo của hệ thống Tethys khỏi thực tại. Ngoài ra, các Neo này còn hỗ trợ liên lạc và đảm nhận nhiệm vụ quan sát Etheric Sea, loại bỏ nhu cầu xây dựng Nexus Tower tại Black Shores.
 Các Neo được phát triển và thiết kế độc lập bởi Black Shores, lấy cảm hứng từ các thanh điều khiển lò phản ứng thời kỳ tiền-Lament. Chúng được coi là mẫu mực của thiết kế kỹ thuật tối giản của Black Shores.</t>
         </is>
       </c>
@@ -27878,7 +27873,7 @@
         <is>
           <t>Từ vết thương đầu tiên của Quercus và lời tiên tri đầu tiên, Viscum Viride đầu tiên đã nở rộ.
 Lời tiên tri là vĩnh cửu, và Viscum Viride cũng vậy.
-(Những tín đồ lạc lối, hãy theo chỉ dẫn của tấm bia vào sâu trong khu vườn, nơi The Primus đang chờ đợi.)</t>
+(Những tín đồ lạc lối, hãy theo chỉ dẫn của tấm bia vào sâu trong khu vườn, nơi Primus đang chờ đợi.)</t>
         </is>
       </c>
     </row>
@@ -28018,7 +28013,7 @@
           <t>Ngươi, kẻ đã đáp lại lời triệu hồi, có mang theo cái giá để tham gia ván cờ này không?
 Liệu quyết tâm của ngươi có đủ mạnh để giành lấy ngày mai mà ngươi khao khát?
 "Khi kẻ được triệu hồi đặt một quân đen xuống, bức tường phía sau hé lộ một lối đi bí mật."
-"Anh ấy bước vào rồi trở ra, tay cầm một Cọc Bất Ổn."</t>
+"Hắn bước vào rồi trở ra, tay cầm một Cọc Bất Ổn."</t>
         </is>
       </c>
     </row>
@@ -28093,17 +28088,17 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Vật phẩm: Terminal dạng đèn lồng (Includes Mô-đun Dữ liệu Nhân lõi có thể tháo rời)
-Số seri: MLCL190468
-Cấp độ truy cập: S+. Chỉ cấp độ Người Thi Hành hoặc cao hơn mới có quyền truy xuất và thu hồi.
-Journal thu hồi:
-Salvage vào [XXX XX XX], Mục đích: Nâng cấp kỹ thuật.
-Cất giữ vào [XXX XX XX].
-Salvage vào [XXX XX XX], Mục đích: Thử nghiệm kỹ thuật thế hệ thứ hai.
-Cất giữ vào [XXX XX XX].
-Salvage 4 ngày trước, Mục đích: Không rõ.
-Cất giữ 2 ngày trước.
-Tình trạng hiện tại: Terminal đang được lưu trữ. Mô-đun dữ liệu nhân lõi đã bị tháo rời và thất lạc.</t>
+          <t>Vật phẩm: Lantern-type Terminal (Includes Detachable Core Data Module)
+Serial Number: MLCL190468
+Clearance: S+. Executor-level clearance or higher is required for access and retrieval.
+Retrieval Log:
+Retrieved on [XXX XX XX], Purpose: Technical Upgrade.
+Deposited on [XXX XX XX].
+Retrieved on [XXX XX XX], Purpose: Second-Generation Technical Test.
+Deposited on [XXX XX XX].
+Retrieved 4 days ago, Purpose: Unknown.
+Deposited 2 days ago.
+Current Status: Terminal is in storage. Core data module is detached and missing.</t>
         </is>
       </c>
     </row>
@@ -28177,8 +28172,8 @@
           <t>09:00 SA: Gặp Giáo sĩ Alessio để xác nhận lô hàng tiếp theo của ████████.
 11:00 SA: Ăn chay và cầu nguyện.
 12:30 CH: Đi qua Hành Lang Sám Hối. Mang theo hàng hóa.
-Ghi chú: Lô hàng trước ngụy trang thành rau của Home thờ nhưng không lấy lại được. Có thể số tiền mới đã bị nghi ngờ.
-16:00 CH: Deliver đến địa điểm và đợi ████████████.
+Ghi chú: Lô hàng trước ngụy trang thành rau của Nhà thờ nhưng không lấy lại được. Có thể số tiền mới đã bị nghi ngờ.
+16:00 CH: Giao hàng đến địa điểm và đợi ████████████.
 PS: Đừng nhìn họ, đặc biệt là vào mắt.
 Ngày hứa hẹn đã đến gần. Xin Thần Linh phù hộ và bảo vệ những tín đồ trung thành, và giáng tai họa xuống kẻ ngoại đạo.</t>
         </is>
@@ -28267,17 +28262,17 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Report thực địa của Người Mang Hoa Số 10826 
+          <t>&lt;b&gt;Báo cáo thực địa của Người Mang Hoa Số 10826 
 Người biên soạn: Ariosto&lt;/b&gt;
 Gửi tất cả Người Mang Hoa đặt căn cứ tại Rinascita: Hãy tuân theo những chỉ dẫn dưới đây để đảm bảo an toàn cho bản thân. Không làm theo có thể dẫn đến những hậu quả không mong muốn.
-1. Rinascita không có trung tâm chính trị, thay vào đó là một tập hợp các thành bang tự trị. Thành phố ven biển phía nam Ragunna là cảng nhập cảnh được khuyến nghị cho Người Mang Hoa từ Bờ Đen. "Biển Storm" giữa Bờ Đen và Rinascita vô cùng nguy hiểm, hãy hết sức cẩn thận. Luôn đi theo tuyến đường hàng hải đã được phê duyệt. Nếu phát hiện lệch hướng, phải điều chỉnh ngay lập tức.
-2. Những Tacet Field kỳ lạ dưới nước sinh sống tại Biển Storm. Hiểu biết hiện tại của chúng ta về chúng còn hạn chế vì chúng dường như không có khả năng tư duy mạch lạc. Không được tương tác, tiếp cận hay chạm vào chúng. Nếu thấy một con di chuyển về phía tàu của bạn, hãy lẩn tránh ngay lập tức.
+1. Rinascita không có trung tâm chính trị, thay vào đó là một tập hợp các thành bang tự trị. Thành phố ven biển phía nam Ragunna là cảng nhập cảnh được khuyến nghị cho Người Mang Hoa từ Bờ Đen. "Biển Bão Tố" giữa Bờ Đen và Rinascita vô cùng nguy hiểm, hãy hết sức cẩn thận. Luôn đi theo tuyến đường hàng hải đã được phê duyệt. Nếu phát hiện lệch hướng, phải điều chỉnh ngay lập tức.
+2. Những Tổ Tacet kỳ lạ dưới nước sinh sống tại Biển Bão Tố. Hiểu biết hiện tại của chúng ta về chúng còn hạn chế vì chúng dường như không có khả năng tư duy mạch lạc. Không được tương tác, tiếp cận hay chạm vào chúng. Nếu thấy một con di chuyển về phía tàu của bạn, hãy lẩn tránh ngay lập tức.
 3. Ragunna, một thành bang ven biển, là nơi có mối liên kết mạnh mẽ nhất với Sentinel. Mối liên kết này được duy trì bởi Order of the Deep, một tổ chức tự xưng là đại diện của Sentinel. Người dân Ragunna coi Sentinel Imperator như "thần linh" và đã dựng lên vô số tượng đài về Ngài. Khi đứng trước các bức tượng này, hãy cúi đầu và hạ thấp ánh mắt. Không được nhìn chằm chằm vào bất kỳ bức tượng nào quá 30 giây.
 4. Ragunna có một nguyên tắc bất di bất dịch về pizza: thành phố này không chấp nhận, và sẽ không bao giờ chấp nhận, lớp phủ crownapple. DƯỚI BẤT KỲ HOÀN CẢNH NÀO, không được thêm crownapple hay gemberry vào bất kỳ chiếc pizza nào được phục vụ tại nhà hàng Ragunnesi. Nguyên tắc này PHẢI—và tôi nhắc lại—PHẢI được tuân thủ.
 Bình luận
-&lt;i&gt;Bình luận 1: Ta biết gửi ngươi đi điều tra Somnoire là một sai lầm! Nếu ta đọc thêm một danh sách vô bổ về những điều nên và không nên làm, ngươi sẽ phải viết lại toàn bộ. Và từ biệt khoản thưởng hiệu suất của ngươi đi!
+&lt;i&gt;Bình luận 1: Tao biết gửi mày đi điều tra Somnoire là một sai lầm! Nếu tao đọc thêm một danh sách vô bổ về những điều nên và không nên làm, mày sẽ phải viết lại toàn bộ. Và từ biệt khoản thưởng hiệu suất của mày đi!
 Đăng bởi: Mistman&lt;/i&gt;
-&lt;i&gt;Bình luận 2: Sống bên biển… Người Ragunnesi có ăn rice bằng bát san hô không nhỉ?
+&lt;i&gt;Bình luận 2: Sống bên biển… Người Ragunnesi có ăn cơm bằng bát san hô không nhỉ?
 Đăng bởi: SheepGoBaah&lt;/i&gt;
 Tất cả những gì tôi chia sẻ ở trên đều dựa trên kinh nghiệm thực tế—thu thập bằng máu, mồ hôi và nước mắt!
 Nói thật lòng. Ngoài những Common Echoes, thành phố Ragunna còn nổi tiếng với "đức tin" tập trung vào Sentinel, được củng cố bởi những thần thoại do Order of the Deep tạo ra để biện minh cho tình trạng hiện tại sau Lament. Cá nhân tôi thấy những thần thoại của họ không hoàn toàn vô căn cứ, vì các quan điểm thế giới mà họ truyền bá khá tương đồng với hệ thống Tethys.
@@ -28286,9 +28281,9 @@
 Để giúp Người Mang Hoa lấy được lòng tin của các thành viên Order, tôi đã tổng hợp một số ví dụ hữu ích về cách diễn đạt câu sao cho giống với các điều khoản trong Codex của họ. Hãy để tôi minh họa:
 - Ôi, vị chúa tể vĩ đại trong màu đen, người sáng lập và cai trị Bờ Đen! Mong một ngày nào đó tôi xứng đáng với tài năng của Người và cống hiến hết mình cho sự nghiệp của Người!
 - Kẻ tham lam KU-Money, hãy nhìn lại lỗi lầm của ngươi trước bàn thờ của chúa và tìm kiếm sự cứu rỗi.
-- Ca ngợi Shorekeeper, Guardian Bờ Đen! Ánh sao của Người xua tan bóng tối và tiêu diệt mọi điều ác. Với ánh sáng dẫn đường của Người, chúng ta sẽ được cứu rỗi!
+- Ca ngợi Shorekeeper, Người Bảo Vệ Bờ Đen! Ánh sao của Người xua tan bóng tối và tiêu diệt mọi điều ác. Với ánh sáng dẫn đường của Người, chúng ta sẽ được cứu rỗi!
 Bình luận
- &lt;i&gt;Bình luận 1: Dù ngươi có nói vậy, ta vẫn không chấp nhận việc báo cáo bị trì hoãn.
+ &lt;i&gt;Bình luận 1: Dù mày có nói vậy, tao vẫn không chấp nhận việc báo cáo bị trì hoãn.
  Đăng bởi: Shorekeeper&lt;/i&gt;</t>
         </is>
       </c>
@@ -28384,7 +28379,7 @@
         <is>
           <t>&lt;b&gt;Bộ Kinh Thẳm: Lời Tựa (Ấn bản thứ 137)&lt;/b&gt;
 Nhiều người ngoài giáo phái hiểu lầm về Giáo Đoàn Thẳm và cảm thấy choáng ngợp trước những từ ngữ trong Bộ Kinh như "ân sủng", "cứu rỗi", "lòng thương xót" và "niềm tin". Quả thực, chưa bao giờ Sentinel Imperator tiết lộ hình hài thực sự của Ngài. Vậy tại sao chúng ta lại tin vào sự tồn tại của Ngài?
-Biên niên sử Rinascita ghi lại vô số trận chiến của Sentinel chống lại Lament. Những tàn tích và kỳ quan khắp Rinascita là minh chứng cho uy quyền thiêng liêng của Imperator. Path định mệnh của Ngài đã tạo nên một thế giới tốt đẹp hơn cho nhân loại, để chúng ta tự mình kiến tạo tương lai mới, trong khi Ngài âm thầm dõi theo.
+Biên niên sử Rinascita ghi lại vô số trận chiến của Sentinel chống lại Lament. Những tàn tích và kỳ quan khắp Rinascita là minh chứng cho uy quyền thiêng liêng của Imperator. Con đường định mệnh của Ngài đã tạo nên một thế giới tốt đẹp hơn cho nhân loại, để chúng ta tự mình kiến tạo tương lai mới, trong khi Ngài âm thầm dõi theo.
 Chúng ta biết ơn những phước lành của Ngài. Chúng ta tôn kính những lời giáo huấn của Ngài. Chúng ta noi theo hành động của Ngài bằng cách truyền bá trí tuệ dẫn lối mọi người hướng thiện—đó chính là sứ mệnh của Giáo Đoàn Thẳm. Dưới sự dẫn dắt của Cassilin Thông Thái, chúng ta đã biên soạn lời giới thiệu này để làm sáng tỏ ý nghĩa của Sentinel và giáo đoàn của chúng ta. Mong rằng điều này sẽ truyền cảm hứng cho những người theo con đường đức hạnh.
 Chúng ta bắt đầu với một số câu hỏi thường gặp:
 1. Sentinel Imperator là ai?
@@ -28392,25 +28387,25 @@
 Tuy nhiên &lt;b&gt;chúng ta tin rằng Sentinel Imperator nắm giữ quyền năng tối thượng để "Phân Chia".&lt;/b&gt; Tức là, Ngài đã phân chia đại dương, ban cho nhân loại vùng đất để "thở". Bằng ân điển của Ngài, Imperator được tôn vinh trên tất cả các Sentinel.
 2. Giáo lý của Giáo Đoàn là gì?
 Thế giới phàm trần này là một đại dương vô tận, nơi mỗi linh hồn phải bơi lên để đến với thần linh. Cuộc sống trôi chảy như sóng, và chỉ khi chạm đến bờ, chúng ta mới đạt đến bình minh của văn minh. Sentinel của chúng ta là sự cứu rỗi khỏi bão tố và thủy triều, là sự thống nhất nơi Rinascita được sinh ra, và là sự thăng hoa cho linh hồn chúng ta.
-Giáo lý của Giáo Đoàn do đó bao gồm: &lt;b&gt;“Cứu rỗi”, “Ascend” và “Thống nhất”.&lt;/b&gt;
+Giáo lý của Giáo Đoàn do đó bao gồm: &lt;b&gt;“Cứu rỗi”, “Thăng hoa” và “Thống nhất”.&lt;/b&gt;
 - Cứu rỗi: Nhờ ân sủng của Sentinel, những tín đồ phải mang sự cứu rỗi đến cho người khác. Chúng ta không hề mù quáng trước bất công hay đau khổ. Chúng ta nỗ lực cứu vớt người khác khỏi tội lỗi. Với kẻ gian ác, Giáo Đoàn mang đến sự cứu rỗi, và với kẻ không ăn năn, chúng ta sẽ đòi lại sự chuộc tội.
-- Ascend: Tìm thấy sự cứu rỗi chính là tìm kiếm sự thăng hoa. Thành viên của Giáo Đoàn sẽ không đắm chìm trong những lạc thú hay dục vọng phù phiếm. Tất cả phải nâng cao tinh thần thông qua kỷ luật tự giác, nếu không sẽ chìm sâu vào vực thẳm.
+- Thăng hoa: Tìm thấy sự cứu rỗi chính là tìm kiếm sự thăng hoa. Thành viên của Giáo Đoàn sẽ không đắm chìm trong những lạc thú hay dục vọng phù phiếm. Tất cả phải nâng cao tinh thần thông qua kỷ luật tự giác, nếu không sẽ chìm sâu vào vực thẳm.
 - Thống nhất: Sau khi ban cho chúng ta đại diện của Ngài trên trần gian, Sentinel Imperator đã giao phó Rinascita cho chúng ta chăm sóc. Thành viên của Giáo Đoàn là "anh em đồng đạo", đoàn kết mọi người có đức tin, bất kể nguồn gốc hay hoàn cảnh. Chỉ khi đoàn kết, chúng ta mới có thể củng cố bản thân trước những hiểm nguy của biển sâu.
-The Primus đầu tiên, Napoli Đệ Nhị, đã nhận được lời tiên tri từ Sentinel: trong một tương lai xa xôi, một &lt;b&gt;"Sóng Cuối Cùng"&lt;/b&gt; sẽ nhấn chìm thế giới. Những người được cứu phải "thở", để "thăng hoa" trong "thống nhất" trên vùng đất mới, giống như chúng ta đã từng đáp lời kêu gọi của Sentinel và đặt chân lên Rinascita.
+Primus đầu tiên, Napoli Đệ Nhị, đã nhận được lời tiên tri từ Sentinel: trong một tương lai xa xôi, một &lt;b&gt;"Sóng Cuối Cùng"&lt;/b&gt; sẽ nhấn chìm thế giới. Những người được cứu phải "thở", để "thăng hoa" trong "thống nhất" trên vùng đất mới, giống như chúng ta đã từng đáp lời kêu gọi của Sentinel và đặt chân lên Rinascita.
 3. Có bằng chứng nào chứng minh cho giáo lý của Giáo Đoàn không?
 Thần học là một môn khoa học mà nhân loại chưa hoàn toàn thấu hiểu cả về lý thuyết lẫn thực tiễn. Sentinel dẫn dắt nền văn minh, và chúng ta tin tưởng vào lời của Ngài. Qua nhiều thế hệ, Giáo Đoàn đã thiết lập những nguyên lý triết học sau đây.
 Trích đoạn từ *Triết Học Giáo Đoàn: Kiến Thức Thiêng (Quyển 1: Nước)*:
 Về Nguồn Gốc: Khởi Nguyên từ "Nước".
 Trong tự nhiên, "Nước" là vô tận cũng như phổ quát.
 Ban đầu, Sentinel Imperator đã "phân chia" thế giới này, vốn từng là một đại dương vô định hình, thành cõi đất liền và biển cả.
-Về Switch Động: Vận Động qua "Nước".
+Về Chuyển Động: Vận Động qua "Nước".
 Sự chuyển động của "Nước" làm nóng lạnh, ẩm khô cõi đất liền. Từ nước, mọi sự sống được tạo ra trong "Sóng Đầu Tiên" và sẽ kết thúc trong "Sóng Cuối Cùng".
-Về Revelation: Sự Khúc Xạ của "Nước".
+Về Khải Huyền: Sự Khúc Xạ của "Nước".
 Hình ảnh con người phản chiếu trong "Nước" là một thực tại kỳ lạ đối với chính mình. Điều này cũng áp dụng cho mọi thực tại khi nước khúc xạ thế giới vào Sonoro Sphere.
-Qua những cải cách của các The Primus kế tiếp, chúng ta đã nhấn mạnh vào ứng dụng khoa học và thực tiễn trong hiểu biết triết học của mình. Độc giả có thể đến Giếng Arito tại Quảng Trường Libert để trải nghiệm bí ẩn của "bói nước": Dodgem một đồng xu xuống giếng, gửi gắm điều ước chân thành, và câu trả lời sẽ đến với bạn.
+Qua những cải cách của các Primus kế tiếp, chúng ta đã nhấn mạnh vào ứng dụng khoa học và thực tiễn trong hiểu biết triết học của mình. Độc giả có thể đến Giếng Arito tại Quảng Trường Tự Do để trải nghiệm bí ẩn của "bói nước": ném một đồng xu xuống giếng, gửi gắm điều ước chân thành, và câu trả lời sẽ đến với bạn.
 Chúng tôi sẽ vô cùng vinh dự nếu Bộ Kinh này khơi gợi sự quan tâm đến giáo lý của Sentinel, và chúng tôi chào đón tất cả đến thư viện của Giáo Đoàn, nơi có sẵn các tài liệu bổ sung để mượn.
 Dù lời nói chỉ là phương tiện nghèo nàn để diễn tả mục đích vĩ đại của Sentinel, chúng tôi vẫn hy vọng đã truyền tải được phần nào bản chất thiêng liêng. Hãy để những phép màu được ghi chép trong Bộ Kinh trở thành "biểu tượng" của sức mạnh vô hạn, có thể truyền đạt được. Thông qua những câu chuyện dễ hiểu, chúng ta hình dung một thế giới của niềm tin bất diệt. Dù Lament có đe dọa trở lại, chúng ta vẫn khẳng định vị trí và sứ mệnh của mình.
-Chúng tôi cầu nguyện rằng cả tín đồ lẫn người chưa tin đều sẽ xem văn bản này như một lời mời gọi để giao lưu và suy ngẫm. Mong rằng những lời này sẽ mang lại ánh sáng cho chúng ta, những kẻ đang trôi dạt giữa biển khơi. Path có nhiều, nhưng với đức hạnh trong tim, chúng ta sẽ thắp sáng lối đi giữa muôn trùng sóng gió.</t>
+Chúng tôi cầu nguyện rằng cả tín đồ lẫn người chưa tin đều sẽ xem văn bản này như một lời mời gọi để giao lưu và suy ngẫm. Mong rằng những lời này sẽ mang lại ánh sáng cho chúng ta, những kẻ đang trôi dạt giữa biển khơi. Con đường có nhiều, nhưng với đức hạnh trong tim, chúng ta sẽ thắp sáng lối đi giữa muôn trùng sóng gió.</t>
         </is>
       </c>
     </row>
@@ -28557,10 +28552,10 @@
         <is>
           <t>Người gửi██: Insula
 Người nhận██: ████
-Bundles hàng████: Giả Thực Tại
+Gói hàng████: Giả Thực Tại
 Lối thoát████: Cảnh Mộng
-Address: Som██ire
-Recorder: Fulei</t>
+Địa chỉ: Som██ire
+Người ghi chép: Fulei</t>
         </is>
       </c>
     </row>
@@ -28705,7 +28700,7 @@
       <c r="M368" t="inlineStr">
         <is>
           <t>Ngày 16.
-Home nguyện hành hương chỉ là một cái vỏ rỗng khác. Các hiệp sĩ đập vỡ cửa sổ, lật đổ bàn thờ, nhưng không thấy dấu vết nào của di vật.
+Nhà nguyện hành hương chỉ là một cái vỏ rỗng khác. Các hiệp sĩ đập vỡ cửa sổ, lật đổ bàn thờ, nhưng không thấy dấu vết nào của di vật.
 Renzo dường như đã mất trí, cứ nhìn chằm chằm vào ngọn đuốc và lảm nhảm—có lẽ do hậu quả của vụ đuối nước trước đó. Chúng ta không thể chờ đợi hắn hồi phục. Ennio muốn mang hắn theo, nhưng tình cảm đó chỉ làm chậm bước tiến của chúng ta.
 Sứ mệnh của chúng ta không dung thứ cho sự yếu đuối. Giờ đây, một tàn tích khác nằm ở hướng &lt;color=Highlight&gt;tây&lt;/color&gt; của hòn đảo này. Đó sẽ là điểm đến tiếp theo của chúng ta.
 Nguyện chúng ta luôn đi trên con đường chính nghĩa.</t>
@@ -28778,9 +28773,9 @@
       <c r="M369" t="inlineStr">
         <is>
           <t>Ngày 17.
-Chúng tôi lội qua đầm lầy để đến tàn tích ngập nước này, chỉ để nhận thêm một sự thất vọng nữa. Các hiệp sĩ đang mất dần niềm tin—một số nghi ngờ liệu chúng tôi có bao giờ tìm thấy di vật được đồn đại đó không. Ennio, người gần gũi với tôi như gia đình, đã phản đối quyết định tiếp tục tiến lên của tôi. Anh ấy buộc tội tôi đã đi chệch khỏi con đường chính nghĩa.
-Không còn cách nào khác để giải quyết; chúng tôi đấu tay đôi, như giáo điều của hiệp sĩ đòi hỏi. Anh ấy Dodgem găng tay thách đấu về phía tôi, người thầy của hắn. Match Complete giữa tiếng hú kỳ lạ từ đằng xa. Khi hắn ngã xuống, một phần trong tôi cũng đổ vỡ theo.
-Ennio... Anh ấy cứng đầu với lý tưởng hiệp sĩ nhưng lại mù quáng trước thực tế lạnh lùng mà nhánh gia tộc chúng tôi đang phải đối mặt. Giờ đây, tôi cảm nhận được—vận may và vinh quang đang nằm ở phía &lt;color=Highlight&gt;bắc&lt;/color&gt;. Lâu đài Porto-Veno sẽ phải ghi nhận công lao của chúng tôi.
+Chúng tôi lội qua đầm lầy để đến tàn tích ngập nước này, chỉ để nhận thêm một sự thất vọng nữa. Các hiệp sĩ đang mất dần niềm tin—một số nghi ngờ liệu chúng tôi có bao giờ tìm thấy di vật được đồn đại đó không. Ennio, người gần gũi với tôi như gia đình, đã phản đối quyết định tiếp tục tiến lên của tôi. Hắn buộc tội tôi đã đi chệch khỏi con đường chính nghĩa.
+Không còn cách nào khác để giải quyết; chúng tôi đấu tay đôi, như giáo điều của hiệp sĩ đòi hỏi. Hắn ném găng tay thách đấu về phía tôi, người thầy của hắn. Trận đấu kết thúc giữa tiếng hú kỳ lạ từ đằng xa. Khi hắn ngã xuống, một phần trong tôi cũng đổ vỡ theo.
+Ennio... Hắn cứng đầu với lý tưởng hiệp sĩ nhưng lại mù quáng trước thực tế lạnh lùng mà nhánh gia tộc chúng tôi đang phải đối mặt. Giờ đây, tôi cảm nhận được—vận may và vinh quang đang nằm ở phía &lt;color=Highlight&gt;bắc&lt;/color&gt;. Porto-Veno Castle sẽ phải ghi nhận công lao của chúng tôi.
 Đến nước này, không còn đường lui nữa.</t>
         </is>
       </c>
@@ -28855,11 +28850,11 @@
         <is>
           <t>(Mép trang giấy ố vàng đã cháy sém)
 Ngày ██.
-Cuộc tìm kiếm kéo dài mãi, và tất cả những gì chúng tôi tìm thấy trong kho là một bản thiết kế vũ khí cũ kỹ, có lẽ là di vật của Hội. Lặng lẽ, chúng tôi thu gom mọi thứ có giá trị, không ai nói về di vật đó. Chẳng cần phải nói—ai cũng biết. Quests này đã thất bại, mọi hy sinh của chúng tôi đều vô nghĩa. Nhưng tôi không chấp nhận điều đó. Hội ắt hẳn đã giấu thứ gì đó trên hòn đảo này. Nó ở đâu?
-(Dodget chữ vội vã như thể viết trong tuyệt vọng)
+Cuộc tìm kiếm kéo dài mãi, và tất cả những gì chúng tôi tìm thấy trong kho là một bản thiết kế vũ khí cũ kỹ, có lẽ là di vật của Hội. Lặng lẽ, chúng tôi thu gom mọi thứ có giá trị, không ai nói về di vật đó. Chẳng cần phải nói—ai cũng biết. Nhiệm vụ này đã thất bại, mọi hy sinh của chúng tôi đều vô nghĩa. Nhưng tôi không chấp nhận điều đó. Hội ắt hẳn đã giấu thứ gì đó trên hòn đảo này. Nó ở đâu?
+(Nét chữ vội vã như thể viết trong tuyệt vọng)
 Lũ TD đáng nguyền rủa ấy đang đến. Chỉ là vấn đề thời gian trước khi chúng phá vỡ phòng tuyến. Nhưng cuối cùng tôi đã tìm ra.
-Thật sự nực cười! Di vật vẫn luôn ở đây, ngay trước mắt chúng tôi.
-Tại bàn thờ lớn của ██, bao quanh bởi những Tacet Field cao chót vót.
+Thật nực cười! Di vật vẫn luôn ở đây, ngay trước mắt chúng tôi.
+Tại bàn thờ lớn của ██, bao quanh bởi những Tổ Tacet cao chót vót.
 Tiếng hú đang đến gần. Tha lỗi cho tôi.</t>
         </is>
       </c>
@@ -28930,10 +28925,10 @@
       <c r="M371" t="inlineStr">
         <is>
           <t>Mỡ cá nướng chảy ra óng ánh, nhỏ giọt xuống ngọn lửa trại bên dưới.
-Mmm! Mỡ đã thấm đều vào từng thớ cá, và nếu nhai kỹ, cậu vẫn cảm nhận được vị tươi nguyên của nó. Delicious! Đúng là đặc quyền của dân câu cá!
-Chẳng có gì thoát khỏi mắt cậu cả, phải không Joanna? Mấy hôm trước, ta còn tính bỏ nghề cơ. Đi một mình buồn quá. Phong cảnh Haven ở đây đẹp đến mức ta từng nghĩ sẽ dựng một cái lều rồi chờ chết già. Nhưng đêm qua, cậu lại xuất hiện trong giấc mơ ta...
-Đừng lo, ta gần như đã quên khuôn mặt và giọng nói của cậu rồi. Nhưng ta không quên lời hứa cậu đã nói. Lời hứa về việc tiến về phía trước, khám phá những cảnh đẹp chưa từng thấy.
-Ngoài cá ra, còn bao nhiêu món ngon ta chưa được nếm, bao nhiêu nơi ta chưa đặt chân tới. Ta không thể để mọi thứ kết thúc như thế này. Tomorrow, khi bình minh lên, ta sẽ lên đường.</t>
+Mmm! Mỡ đã thấm đều vào từng thớ cá, và nếu nhai kỹ, cậu vẫn cảm nhận được vị tươi nguyên của nó. Ngon tuyệt! Đúng là đặc quyền của dân câu cá!
+Chẳng có gì thoát khỏi mắt cậu cả, phải không Joanna? Mấy hôm trước, tao còn tính bỏ nghề cơ. Đi một mình buồn quá. Phong cảnh Haven ở đây đẹp đến mức tao từng nghĩ sẽ dựng một cái lều rồi chờ chết già. Nhưng đêm qua, cậu lại xuất hiện trong giấc mơ tao...
+Đừng lo, tao gần như đã quên khuôn mặt và giọng nói của cậu rồi. Nhưng tao không quên lời hứa cậu đã nói. Lời hứa về việc tiến về phía trước, khám phá những cảnh đẹp chưa từng thấy.
+Ngoài cá ra, còn bao nhiêu món ngon tao chưa được nếm, bao nhiêu nơi tao chưa đặt chân tới. Tao không thể để mọi thứ kết thúc như thế này. Ngày mai, khi bình minh lên, tao sẽ lên đường.</t>
         </is>
       </c>
     </row>
@@ -29073,7 +29068,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Tiệc tối nay là chuyện lớn đấy. Đây là lần đầu mình phụ trách một việc quan trọng như thế. Cấp trên còn giao cho mình và Barolo đặt mật khẩu điều khiển ánh sáng nữa. Nhưng làm sao để đảm bảo mọi thứ diễn ra suôn sẻ nhỉ? À, mình biết rồi—giữ kẻ thù ở gần, giống như bí mật vậy. Hai chữ số &lt;color=yellow&gt;đầu tiên&lt;/color&gt;... mình sẽ chọn &lt;color=yellow&gt;số cây và đèn chùm trong hội trường&lt;/color&gt;. Còn hai chữ số cuối thì để Barolo lo. Yesterday hắn mất cả buổi để treo bóng bay trong hội trường. Chắc hắn giấu mật khẩu trong &lt;color=yellow&gt;những quả bóng&lt;/color&gt; ấy? Hừ... vẫn thấy hơi sai sai. Thôi, kiểm tra lại lần nữa vậy.</t>
+          <t>Tiệc tối nay là chuyện lớn đấy. Đây là lần đầu mình phụ trách một việc quan trọng như thế. Cấp trên còn giao cho mình và Barolo đặt mật khẩu điều khiển ánh sáng nữa. Nhưng làm sao để đảm bảo mọi thứ diễn ra suôn sẻ nhỉ? À, mình biết rồi—giữ kẻ thù ở gần, giống như bí mật vậy. Hai chữ số &lt;color=yellow&gt;đầu tiên&lt;/color&gt;... mình sẽ chọn &lt;color=yellow&gt;số cây và đèn chùm trong hội trường&lt;/color&gt;. Còn hai chữ số cuối thì để Barolo lo. Hôm qua hắn mất cả buổi để treo bóng bay trong hội trường. Chắc hắn giấu mật khẩu trong &lt;color=yellow&gt;những quả bóng&lt;/color&gt; ấy? Hừ... vẫn thấy hơi sai sai. Thôi, kiểm tra lại lần nữa vậy.</t>
         </is>
       </c>
     </row>
@@ -29211,8 +29206,8 @@
         <is>
           <t>Cậu bé yêu quý của ta,
 Rời xa cậu là điều ta không hề muốn, nhưng thời cuộc buộc ta phải ra đi. Tất cả những gì ta có thể để lại bây giờ chỉ là vài dòng trên mảnh giấy rách này.
-Hãy đứng vững và sống một cuộc đời đầy tự hào. Parents cậu đã hy sinh vì phẩm giá của nghệ thuật, và trong huyết quản cậu cũng chảy chung dòng máu ấy.
-Ta đã đánh đổi tự do của mình để theo đuổi những bí ẩn vô tận mà những Echo này nắm giữ, nhưng ta tin ở cậu—trái tim cậu thật kiên cường. Hãy giữ vững hy vọng và tiếp tục tiến về phía trước.
+Hãy đứng vững và sống một cuộc đời đầy tự hào. Cha mẹ cậu đã hy sinh vì phẩm giá của nghệ thuật, và trong huyết quản cậu cũng chảy chung dòng máu ấy.
+Ta đã đánh đổi tự do của mình để theo đuổi những bí ẩn vô tận mà những Tiếng Vọng này nắm giữ, nhưng ta tin ở cậu—trái tim cậu thật kiên cường. Hãy giữ vững hy vọng và tiếp tục tiến về phía trước.
 Một ngày nào đó, kho báu mà chúng ta trân trọng sâu trong Kho Averardo sẽ mang lại hy vọng mới.
 Với tất cả tình yêu,
 Ash</t>
@@ -29289,9 +29284,9 @@
       <c r="M376" t="inlineStr">
         <is>
           <t>Thông tin sau chỉ dành cho nhân viên có quyền truy cập Cấp 1 trở lên:
-Kho Tài Sản Quý và Tác Phẩm Nghệ Thuật là kho đầu tiên của Averardo Vault, chịu trách nhiệm bảo quản kim loại quý và tác phẩm nghệ thuật hiếm.
+Kho Tài Sản Quý và Tác Phẩm Nghệ Thuật là kho đầu tiên của Hầm Averardo, chịu trách nhiệm bảo quản kim loại quý và tác phẩm nghệ thuật hiếm.
 Mỗi khu vực đều có phòng an ninh, với phòng điều khiển an ninh cấp cao nhất nằm tại khu vực tác phẩm nghệ thuật.
-Report hàng tháng về số lượng và khối lượng vật phẩm trong khu kim loại quý phải được ghi chép để đảm bảo theo dõi mọi tổn thất.
+Báo cáo hàng tháng về số lượng và khối lượng vật phẩm trong khu kim loại quý phải được ghi chép để đảm bảo theo dõi mọi tổn thất.
 Duy trì điều kiện môi trường (như nhiệt độ, độ ẩm) trong phạm vi cho phép.
 Không được kiểm tra một số vật phẩm để tránh ảnh hưởng tâm lý tiềm ẩn.
 Để tránh hiểu lầm giữa những cá nhân có niềm tin đặc biệt, tuyệt đối không được gỡ bỏ lớp phủ khỏi các vật phẩm cụ thể trong khu tác phẩm nghệ thuật dưới bất kỳ hình thức nào!
@@ -29370,14 +29365,14 @@
       <c r="M377" t="inlineStr">
         <is>
           <t>Thông tin sau chỉ dành cho nhân viên có quyền truy cập Cấp 2 trở lên:
-Kho Echoes, kho thứ hai của Averardo Vault, là khu vực kiểm soát nghiêm ngặt. Việc xâm nhập trái phép bị coi là vi phạm.
-Function chính của kho là chứa đựng, bảo vệ và nuôi dưỡng các Echoes. Đây là khu vực nguy hiểm nhất trong hầm.
-Tuân thủ nghiêm ngặt các quy trình là bắt buộc—hành động trái phép sẽ kích hoạt hệ thống ngắt cưỡng bức đối với các thiết bị chứa Echoes.
-Không được chạm vào bất kỳ thiết bị chứa nào, vì một số Echoes yêu cầu biện pháp ngăn chặn đặc biệt.
-Những người không phải chuyên gia nên tránh xa khu vực này, vì một số Echoes có tính hung hãn.
-Phần lớn các Echoes đều hiếm hoặc sở hữu đặc tính độc nhất, tuyệt đối không được làm hư hại dưới bất kỳ hình thức nào!
-Phần lớn các Echoes đều hiếm hoặc sở hữu đặc tính độc nhất, tuyệt đối không được làm hư hại dưới bất kỳ hình thức nào!
-Phần lớn các Echoes đều hiếm hoặc sở hữu đặc tính độc nhất, tuyệt đối không được làm hư hại dưới bất kỳ hình thức nào!</t>
+Kho Echo, kho thứ hai của Hầm Averardo, là khu vực kiểm soát nghiêm ngặt. Việc xâm nhập trái phép bị coi là vi phạm.
+Chức năng chính của kho là chứa đựng, bảo vệ và nuôi dưỡng các Echo. Đây là khu vực nguy hiểm nhất trong hầm.
+Tuân thủ nghiêm ngặt các quy trình là bắt buộc—hành động trái phép sẽ kích hoạt hệ thống ngắt cưỡng bức đối với các thiết bị chứa Echo.
+Không được chạm vào bất kỳ thiết bị chứa nào, vì một số Echo yêu cầu biện pháp ngăn chặn đặc biệt.
+Những người không phải chuyên gia nên tránh xa khu vực này, vì một số Echo có tính hung hãn.
+Phần lớn các Echo đều hiếm hoặc sở hữu đặc tính độc nhất, tuyệt đối không được làm hư hại dưới bất kỳ hình thức nào!
+Phần lớn các Echo đều hiếm hoặc sở hữu đặc tính độc nhất, tuyệt đối không được làm hư hại dưới bất kỳ hình thức nào!
+Phần lớn các Echo đều hiếm hoặc sở hữu đặc tính độc nhất, tuyệt đối không được làm hư hại dưới bất kỳ hình thức nào!</t>
         </is>
       </c>
     </row>
@@ -29517,15 +29512,15 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Chủ đề: Hi mừng quý khách lên tàu Echoes của Kho Averardo!
-Để thuận tiện cho công việc của quý khách tại Kho Averardo, chúng tôi vui mừng cung cấp dịch vụ tàu Echoes. Những Echoes độc đáo này sẽ đưa quý khách đến các khu vực khác nhau trong Kho một cách nhanh chóng.
+          <t>Chủ đề: Chào mừng quý khách lên tàu Echo của Kho Averardo!
+Để thuận tiện cho công việc của quý khách tại Kho Averardo, chúng tôi vui mừng cung cấp dịch vụ tàu Echo. Những Echo độc đáo này sẽ đưa quý khách đến các khu vực khác nhau trong Kho một cách nhanh chóng.
 Vì sự an toàn của quý khách, vui lòng tuân thủ các hướng dẫn sau:
-1. Tàu Echoes có bản tính hiền lành, nhưng xin đừng cho nó ăn hoặc tấn công. Do vậy có thể khiến nó chệch hướng hoặc thậm chí trật bánh nếu bị giật mình.
+1. Tàu Echo có bản tính hiền lành, nhưng xin đừng cho nó ăn hoặc tấn công. Làm vậy có thể khiến nó chệch hướng hoặc thậm chí trật bánh nếu bị giật mình.
 2. Trong suốt hành trình, quý khách có thể ngắm cảnh qua cửa sổ tàu. Xin đừng thò bất kỳ bộ phận nào của cơ thể ra ngoài cửa sổ. Nếu phát hiện ai đó đã vi phạm quy tắc này, hãy nhanh chóng tham khảo Quy tắc 6.
-3. Kho Averardo chỉ chứa các kho lưu trữ, cơ sở bảo quản và các tác phẩm điêu khắc trang trí nhỏ. None bất kỳ bức tượng hay công trình nào cao khoảng ▇▇▇, giống như ▇▇▇▇▇▇▇▇▇▇▇. Nếu quý khách nhìn thấy cấu trúc như vậy trong chuyến đi, hãy tự nhắc mình rằng đó chỉ là ảo giác do môi trường kín của Kho gây ra và nhanh chóng quay đi. Nếu vẫn tiếp tục nhìn thấy, hãy nhanh chóng tham khảo Quy tắc 6.
-4. Quý khách có thể gọi tàu Echoes qua Terminal, và thường thì nó sẽ đến trong vòng ba phút. Nếu tàu không đến trong khoảng thời gian này, hãy rời ga ngay lập tức và báo cáo sự chậm trễ cho nhân viên Kho tại quầy lễ tân. Đừng lên bất kỳ tàu nào đến sau mốc ba phút.
-5. Tàu Echoes trong kho được thiết kế giống một con cá. Nó không có chi, chân hay xúc tu. Nếu nhận thấy tàu có hình dạng khác thường, đừng lên tàu. Thay vào đó, hãy gọi một tàu Echoes khác và đợi cho đến khi tàu bất thường rời khỏi sân ga.
-6. Nếu vi phạm bất kỳ quy tắc nào ở trên, hãy nhanh chóng rời khỏi sân ga và thông báo cho nhân viên Kho gần nhất. Nếu đã lên tàu, hãy Dodgem ngay tờ hướng dẫn này ra ngoài cửa sổ. Tàu sẽ tiến đến ga gần nhất, nơi nhân viên Kho sẽ đợi để hộ tống quý khách ra ngoài. Xin đừng trò chuyện hay giao tiếp bằng mắt với nhân viên.</t>
+3. Kho Averardo chỉ chứa các kho lưu trữ, cơ sở bảo quản và các tác phẩm điêu khắc trang trí nhỏ. Không có bất kỳ bức tượng hay công trình nào cao khoảng ▇▇▇, giống như ▇▇▇▇▇▇▇▇▇▇▇. Nếu quý khách nhìn thấy cấu trúc như vậy trong chuyến đi, hãy tự nhắc mình rằng đó chỉ là ảo giác do môi trường kín của Kho gây ra và nhanh chóng quay đi. Nếu vẫn tiếp tục nhìn thấy, hãy nhanh chóng tham khảo Quy tắc 6.
+4. Quý khách có thể gọi tàu Echo qua Thiết bị đầu cuối, và thường thì nó sẽ đến trong vòng ba phút. Nếu tàu không đến trong khoảng thời gian này, hãy rời ga ngay lập tức và báo cáo sự chậm trễ cho nhân viên Kho tại quầy lễ tân. Đừng lên bất kỳ tàu nào đến sau mốc ba phút.
+5. Tàu Echo trong kho được thiết kế giống một con cá. Nó không có chi, chân hay xúc tu. Nếu nhận thấy tàu có hình dạng khác thường, đừng lên tàu. Thay vào đó, hãy gọi một tàu Echo khác và đợi cho đến khi tàu bất thường rời khỏi sân ga.
+6. Nếu vi phạm bất kỳ quy tắc nào ở trên, hãy nhanh chóng rời khỏi sân ga và thông báo cho nhân viên Kho gần nhất. Nếu đã lên tàu, hãy ném ngay tờ hướng dẫn này ra ngoài cửa sổ. Tàu sẽ tiến đến ga gần nhất, nơi nhân viên Kho sẽ đợi để hộ tống quý khách ra ngoài. Xin đừng trò chuyện hay giao tiếp bằng mắt với nhân viên.</t>
         </is>
       </c>
     </row>
@@ -29604,20 +29599,20 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Chủ đề: Hướng dẫn viên kho Averardo (Zone Vực Kho Ngầm)
-Hi mừng đến với Kho Averardo! Chúng tôi hy vọng quý vị sẽ có khoảng thời gian tuyệt vời và khó quên tại đây.
+          <t>Chủ đề: Hướng dẫn viên kho Averardo (Khu Vực Kho Ngầm)
+Chào mừng đến với Kho Averardo! Chúng tôi hy vọng quý vị sẽ có khoảng thời gian tuyệt vời và khó quên tại đây.
 Các khu vực chính của Kho Ngầm như sau:
-1. Kho Jin Loại và Tác Phẩm Nghệ Thuật Quý
-Area này chủ yếu lưu trữ các kim loại quý và tác phẩm nghệ thuật hiếm. Một số hiện vật được trưng bày luân phiên cho công chúng. Dưới đây là danh sách một phần các triển lãm được đề xuất trong tháng này:
+1. Kho Kim Loại và Tác Phẩm Nghệ Thuật Quý
+Khu vực này chủ yếu lưu trữ các kim loại quý và tác phẩm nghệ thuật hiếm. Một số hiện vật được trưng bày luân phiên cho công chúng. Dưới đây là danh sách một phần các triển lãm được đề xuất trong tháng này:
 Lọ Gốm Stern
 Chiếc lọ gốm yêu quý của danh hài Arthur Stern! Sau khi nhận giải Laurel, ông đã rời bỏ sân khấu để chuyên tâm vào nghệ thuật gốm. Chiếc lọ này là một trong mười hai kiệt tác do chính ông vẽ.
-Rating đề xuất: Năm Sao!
-"Vì Sao Deep"
+Đánh giá đề xuất: Năm Sao!
+"Vì Sao Sâu Thẳm"
 Bức tranh của một họa sĩ vô danh, khắc họa ánh sao phản chiếu từ đáy vực thẳm. Các nhà phê bình đã tranh luận về chủ đề của tác phẩm này suốt nhiều năm, khiến nó trở thành một tác phẩm gây tranh cãi và được bàn tán sôi nổi.
-Rating đề xuất: Ba Sao!
-2. Kho Echoes (Hiện Close Cửa)
-Area này chủ yếu lưu trữ các Echoes.
-Chú ý quan trọng: Kho Echoes không còn mở cửa cho khách tham quan.
+Đánh giá đề xuất: Ba Sao!
+2. Kho Echo (Hiện Đóng Cửa)
+Khu vực này chủ yếu lưu trữ các Echo.
+Lưu ý quan trọng: Kho Echo không còn mở cửa cho khách tham quan.
 3. [Dữ liệu đã bị xóa]</t>
         </is>
       </c>
@@ -29686,10 +29681,10 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>[Work Log]
-8:30 SA: Bắt đầu ca. Quests hôm nay là kiểm kê các tác phẩm nghệ thuật trong kho. Được rồi, bắt tay vào thôi.
-12:00 TR: Giờ nghỉ trưa. Một thằng mới cố hỏi ta về tin đồn "kho bí mật". Thật sự không ngờ những lời đồn vô căn cứ này lại dai dẳng đến thế. Dù có kho bí mật thật đi nữa, đâu phải chuyện mà tụi Level 1 như chúng ta cần quan tâm.
-5:30 CH: Hết giờ làm. Trên chuyến tàu Echoes về, Jason lại nghĩ là vui khi hù dọa thằng mới bằng một câu chuyện ma cũ rích. Nào là có một chuyến tàu bí ẩn không người lái, chỉ chạy vào nửa đêm và đưa hành khách đến "thế giới ngầm" của Kho Tàng. Ở đó, những linh hồn người chết sẽ xé xác bất cứ kẻ nào dám xâm phạm lãnh địa của chúng. Ta nghe những câu chuyện kiểu này nhiều rồi. Nếu thật sự có chuyến tàu bí ẩn nào, ta đã thấy nó từ lâu rồi.</t>
+          <t>[Nhật Ký Công Việc]
+8:30 SA: Bắt đầu ca. Nhiệm vụ hôm nay là kiểm kê các tác phẩm nghệ thuật trong kho. Được rồi, bắt tay vào thôi.
+12:00 TR: Giờ nghỉ trưa. Một thằng mới cố hỏi tao về tin đồn "kho bí mật". Thật không ngờ những lời đồn vô căn cứ này lại dai dẳng đến thế. Dù có kho bí mật thật đi nữa, đâu phải chuyện mà tụi Level 1 như chúng tao cần quan tâm.
+5:30 CH: Hết giờ làm. Trên chuyến tàu Echo về, Jason lại nghĩ là vui khi hù dọa thằng mới bằng một câu chuyện ma cũ rích. Nào là có một chuyến tàu bí ẩn không người lái, chỉ chạy vào nửa đêm và đưa hành khách đến "thế giới ngầm" của Kho Tàng. Ở đó, những linh hồn người chết sẽ xé xác bất cứ kẻ nào dám xâm phạm lãnh địa của chúng. Tao nghe những câu chuyện kiểu này nhiều rồi. Nếu thật sự có chuyến tàu bí ẩn nào, tao đã thấy nó từ lâu rồi.</t>
         </is>
       </c>
     </row>
@@ -29758,9 +29753,9 @@
       <c r="M382" t="inlineStr">
         <is>
           <t>Tin xấu. Một con Chest Mimic đã lẻn vào Kho và trà trộn vào đống rương chứa đồ.
-Ta đã báo lính rồi. Con Chest Mimic không tự di chuyển được, nên tốt nhất ngươi tránh xa phòng này cho đến khi lính tới.
+Tao đã báo lính rồi. Con Chest Mimic không tự di chuyển được, nên tốt nhất mày tránh xa phòng này cho đến khi lính tới.
 (Dưới tờ giấy ghi chú là một dòng chữ nguệch ngoạc vội vàng)
-Đừng có mà sai Echoes đi kiểm tra đống rương đó. Chúng sẽ bị con Chest Mimic nuốt chửng mất... Đừng hỏi ta làm sao biết được điều đó.</t>
+Đừng có mà sai Echo đi kiểm tra đống rương đó. Chúng sẽ bị con Chest Mimic nuốt chửng mất... Đừng hỏi tao làm sao biết được điều đó.</t>
         </is>
       </c>
     </row>
@@ -29828,7 +29823,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>[Warning: Chỉ Dành Cho Nhân Viên Kho Tàng Có Cấp Độ Phê Duyệt 2 Trở Lên]
+          <t>[Cảnh Báo: Chỉ Dành Cho Nhân Viên Kho Tàng Có Cấp Độ Phê Duyệt 2 Trở Lên]
 Do nguy cơ an ninh từ hoạt động của Fractsidus, Gia Tộc đã quyết định tạm ngừng buổi Đấu Giá Ducat. Thời gian tiếp tục sẽ được thông báo sau.
 Trong thời gian tạm ngừng, nhân viên liên quan sẽ được phân công nhiệm vụ khác. Hội trường đấu giá sẽ tạm thời được chuyển đổi thành phòng tiệc và sảnh khiêu vũ.
 Thông báo chính thức cho công chúng về việc tạm ngừng sẽ là: "Trung tâm đấu giá đang được cải tạo theo quy định áp dụng từ các khu vực khác." Nhân viên nghiêm cấm tiết lộ lý do thực sự cho người ngoài. Vi phạm sẽ bị coi là vi phạm bảo mật và chịu hình phạt thích đáng.</t>
@@ -29900,11 +29895,11 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Malee Templates Vật: ▇▇▇▇▇▇▇
-Mô tả Templates Vật: Một phân loài Discord Spearback thu thập từ khu vực ▇▇▇▇▇▇▇▇. Sức mạnh và sự nhanh nhẹn của nó vượt trội hơn hẳn so với các cá thể Spearback khác. Sau khi được cấp phép, đội thám hiểm đã bắt giữ thành công mẫu vật này, với kế hoạch sử dụng cho các nghiên cứu sâu hơn.
-Tình Trạng Templates Vật: Hoạt động. Nhóm nghiên cứu đã thiết lập một khu vực thí nghiệm chuyên biệt cho mẫu vật này.
+          <t>Tên Mẫu Vật: ▇▇▇▇▇▇▇
+Mô tả Mẫu Vật: Một phân loài Tacet Discord Spearback thu thập từ khu vực ▇▇▇▇▇▇▇▇. Sức mạnh và sự nhanh nhẹn của nó vượt trội hơn hẳn so với các cá thể Spearback khác. Sau khi được cấp phép, đội thám hiểm đã bắt giữ thành công mẫu vật này, với kế hoạch sử dụng cho các nghiên cứu sâu hơn.
+Tình Trạng Mẫu Vật: Hoạt động. Nhóm nghiên cứu đã thiết lập một khu vực thí nghiệm chuyên biệt cho mẫu vật này.
 Kế Hoạch Thí Nghiệm: Chưa có
-Mục Tiêu Thí Nghiệm: Reconstruction các tần số dẫn đến sự hình thành thể chất bất thường của mẫu vật, và thử nghiệm áp dụng kết quả lên các Echoes khác để tăng cường hiệu suất của chúng.</t>
+Mục Tiêu Thí Nghiệm: Tái cấu trúc các tần số dẫn đến sự hình thành thể chất bất thường của mẫu vật, và thử nghiệm áp dụng kết quả lên các Echo khác để tăng cường hiệu suất của chúng.</t>
         </is>
       </c>
     </row>
@@ -29970,8 +29965,8 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>...Chúng tôi đã cô lập thành công tần số gây đột biến ở mẫu vật này. Khi điều chỉnh tần số này khớp với một Spearback Echoes khác, nó thể hiện hiệu suất vượt trội, vượt xa các mẫu vật khác.
-Đáng tiếc là tần số này quá phức tạp để tái tạo. Nhóm nghiên cứu dự định giữ mẫu Echoes trong khu vực thí nghiệm để tiến hành thêm các thử nghiệm chiến đấu và sức bền.</t>
+          <t>...Chúng tôi đã cô lập thành công tần số gây đột biến ở mẫu vật này. Khi điều chỉnh tần số này khớp với một Spearback Echo khác, nó thể hiện hiệu suất vượt trội, vượt xa các mẫu vật khác.
+Đáng tiếc là tần số này quá phức tạp để tái tạo. Nhóm nghiên cứu dự định giữ mẫu Echo trong khu vực thí nghiệm để tiến hành thêm các thử nghiệm chiến đấu và sức bền.</t>
         </is>
       </c>
     </row>
@@ -30041,10 +30036,10 @@
       <c r="M386" t="inlineStr">
         <is>
           <t>Ta tìm thấy vài rương chứa đồ rõ ràng không thuộc về Kho Tàng Âm Thanh. Chúng có lẽ bị bỏ lại trong một lần chuyển hàng trước đó.
-None bất kỳ ghi chép nào liên quan đến những chiếc rương này trong Kho Archive, nên quyền sở hữu của chúng chưa được xác minh. Kho Archive Jin Loại Quý và Tác Phẩm Nghệ Thuật cũng từ chối nhận chúng.
+Không có bất kỳ ghi chép nào liên quan đến những chiếc rương này trong Kho Lưu Trữ, nên quyền sở hữu của chúng chưa được xác minh. Kho Lưu Trữ Kim Loại Quý và Tác Phẩm Nghệ Thuật cũng từ chối nhận chúng.
 Kho Tàng Âm Thanh không cần những vật liệu này, và chúng chỉ chiếm chỗ ở đây… nhưng hiện tại, không còn lựa chọn nào khác ngoài việc tiếp tục lưu giữ chúng ở đây.
-(Dưới ghi chú, bằng một Dodget chữ khác vội vàng viết)
-Đây không phải tài sản của Kho Archive. Ai muốn thì cứ lấy đi.</t>
+(Dưới ghi chú, bằng một nét chữ khác vội vàng viết)
+Đây không phải tài sản của Kho Lưu Trữ. Ai muốn thì cứ lấy đi.</t>
         </is>
       </c>
     </row>
@@ -30117,10 +30112,10 @@
         <is>
           <t>(*Một tập giấy đặt ở đây. Có vẻ như là một phần của tiểu thuyết hoặc bài luận chưa hoàn thành.)
 ...Ziegler bị mắc kẹt trên hòn đảo riêng của mình, chỉ có một cây dừa làm bạn và thỉnh thoảng vài con Bell Crab bò ngang qua bãi biển.
-Anh ấy là ai? Con trai của Ziegler Senior? Home đầu tư thành công nhất của Ragunna? Kẻ khốn khổ mất hết tất cả trong một canh bạc, của cải lẫn danh vọng đều tiêu tan? Một nghệ sĩ điên? Một ẩn sĩ? Kẻ bất hạnh bị đắm tàu?
-Anh ấy nhìn ra biển, làn gió nhẹ thổi tung mái tóc hoa râm, khuấy động sóng nước. Trong ánh nắng vàng óng, hắn như thấy vô số phiên bản của chính mình rải rác khắp thời gian, tan vỡ và không trọn vẹn. Một nỗi cô đơn chưa từng có tràn ngập, nhưng lại xen lẫn cảm giác thỏa mãn kỳ lạ.
-Anh ấy không còn cơ hội rời khỏi hòn đảo này. Có lẽ ngày mai, hoặc ngày kia, hắn sẽ trút hơi thở cuối dưới cái nắng cháy da.
-Anh ấy đã dùng hết mọi phép màu của mình. Ý nghĩ ấy thoáng qua rồi vụt biến mất. Anh ấy quyết định dành thời gian quan sát hòn đảo—khắc sâu từng chi tiết vào tâm trí, lấp đầy những ký ức rời rạc, và hy vọng bóng tối sắp tới sẽ không biến chúng thành hư vô.
+Hắn là ai? Con trai của Ziegler Senior? Nhà đầu tư thành công nhất của Ragunna? Kẻ khốn khổ mất hết tất cả trong một canh bạc, của cải lẫn danh vọng đều tiêu tan? Một nghệ sĩ điên? Một ẩn sĩ? Kẻ bất hạnh bị đắm tàu?
+Hắn nhìn ra biển, làn gió nhẹ thổi tung mái tóc hoa râm, khuấy động sóng nước. Trong ánh nắng vàng óng, hắn như thấy vô số phiên bản của chính mình rải rác khắp thời gian, tan vỡ và không trọn vẹn. Một nỗi cô đơn chưa từng có tràn ngập, nhưng lại xen lẫn cảm giác thỏa mãn kỳ lạ.
+Hắn không còn cơ hội rời khỏi hòn đảo này. Có lẽ ngày mai, hoặc ngày kia, hắn sẽ trút hơi thở cuối dưới cái nắng cháy da.
+Hắn đã dùng hết mọi phép màu của mình. Ý nghĩ ấy thoáng qua rồi vụt biến mất. Hắn quyết định dành thời gian quan sát hòn đảo—khắc sâu từng chi tiết vào tâm trí, lấp đầy những ký ức rời rạc, và hy vọng bóng tối sắp tới sẽ không biến chúng thành hư vô.
 (Bản viết kết thúc tại đây.)</t>
         </is>
       </c>
@@ -30189,7 +30184,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>—Ôi, Kẻ Canh Gác Tối Cao, Imperator Vương vĩ đại, con chưa bao giờ nghi ngờ Người.
+          <t>—Ôi, Kẻ Canh Gác Tối Cao, Đại Đế Vương vĩ đại, con chưa bao giờ nghi ngờ Người.
 Người đã dẫn dắt chúng con từ vùng biển xa xôi đến mảnh đất này, dạy chúng con đi trên con đường chính nghĩa và đón nhận niềm vui.
 Thế nhưng, những kẻ tự xưng là tôi tớ của Người lại bóp méo lời dạy của Người. Quần chúng im lặng, còn những ai đứng về phía sự thật thì bị đày đến nơi đây.
 Xin Người rèn niềm tin của chúng con thành ngọn giáo, và đau khổ thành khiên thép. Xin Người… ban cho chúng con sự báo thù, hoặc ít nhất là một giấc nghỉ nhân từ.</t>
@@ -30264,14 +30259,14 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Report lỗi: Khi Tàu Echoes gặp trục trặc hoặc hoạt động bất thường, có khả năng nhân viên và du khách không có quyền cấp 3 sẽ bị đưa nhầm đến khu vực hạn chế này.
-Biện pháp xử lý: Tất cả Tàu Echoes sẽ được hiệu chỉnh lại, dự kiến hoàn thành trong vòng 32 ngày làm việc. Trước khi hoàn tất, hướng dẫn tạm thời về cách lên tàu sẽ được phát qua tờ rơi.
-Nếu xảy ra bất thường trong lúc di chuyển, nhân viên sẽ cố gắng hướng dẫn hành khách đến ga gần nhất, nơi nhân viên cấp 3 sẽ túc trực để sơ tán mọi người ra khỏi hầm.
-Dù hành khách không thể vào khu vực này do không đủ quyền hạn, nhưng nếu xuống tàu ở đây vì tin đồn về "kho bí mật", có thể dẫn đến những rắc rối không đáng có. Do đó, cần hướng hành khách tránh xa khu vực này.
-Bình luận:
-Hay là chúng ta dựng chuyện nhỉ? Lan truyền tin đồn về những đoàn tàu ma không trở về hay tàu bị đột biến. Như vậy, nếu hành khách phát hiện điều gì bất thường, họ sẽ nhanh chóng tìm đến chúng ta.
-Phản hồi:
-Đồng ý. Thông tin này sẽ được đưa vào tờ rơi.</t>
+          <t>Báo cáo lỗi: In the event of an Echo Train malfunction or abnormal operation, there is a possibility that staff members and visitors without Level 3 clearance may be mistakenly taken to this restricted area.
+Course of Action: All Echo Trains will undergo recalibration, which is expected to be completed within 32 working days. Prior to this operation, a temporary set of instructions for boarding the Echo Train will be issued through flyers. 
+If any anomalies occur during a ride, efforts will be made to guide passengers to the nearest station, where staff with Level 3 clearance will be on standby to evacuate passengers out of the vault.
+Although passengers will be unable to enter this area due to insufficient clearance, choosing to disembark here due to rumors about the existence of the "secret cache" could lead to unnecessary complications. Therefore, it is essential to direct passengers away from this section.
+Comment:
+What do you say we create a story? Spread rumors about ghost trains with no return or mutated trains. This way, if passengers notice something unusual, they'll be more likely to seek our help immediately.
+Response:
+Approved. We will include this information in the flyers.</t>
         </is>
       </c>
     </row>
@@ -30339,10 +30334,9 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Area cách ly này được xây dựng sau khi Kho Tàng hoàn thiện. Vì một số nghiên cứu và mẫu vật có thể gây rủi ro an ninh, Gia tộc đã cho xây dựng khu vực cách ly này trên đảo để chứa các dự án đó. Area được chia thành:
-Tầng Hầm 1: Khu Thí Nghiệm Echoes
-Tầng Hầm 2: Khu Archive Vật Phẩm (Đã Ngừng Activity)
-Cảnh báo: Các vật phẩm trong khu vực cách ly cực kỳ nguy hiểm. Không được phép vào nếu không có sự cho phép.</t>
+          <t>Khu vực cách ly này được xây dựng sau khi Kho Tàng hoàn thiện. Vì một số nghiên cứu và mẫu vật có thể gây rủi ro an ninh, Gia tộc đã cho xây dựng khu vực cách ly này trên đảo để chứa các dự án đó. Khu vực được chia thành: Underground Floor 1: Echo Experimentation Area
+Underground Floor 2: Item Storage Area (Decommissioned)
+Warning: Items in the isolation zone are extremely dangerous. Please do not enter without proper authorization.</t>
         </is>
       </c>
     </row>
@@ -30410,10 +30404,10 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Chúng tôi cuối cùng vẫn không tìm ra cách sản xuất hàng loạt Echoes tăng cường. Vì vậy, Echoes Tượng này có lẽ là thành quả đáng kể duy nhất mà chúng tôi đạt được. Tệ hơn nữa, chính Echoes của chúng tôi cũng không địch nổi nó trong chiến đấu, nên không thu thập được dữ liệu chiến đấu nào.
+          <t>Chúng tôi cuối cùng vẫn không tìm ra cách sản xuất hàng loạt Echo tăng cường. Vì vậy, Echo Tượng này có lẽ là thành quả đáng kể duy nhất mà chúng tôi đạt được. Tệ hơn nữa, chính Echo của chúng tôi cũng không địch nổi nó trong chiến đấu, nên không thu thập được dữ liệu chiến đấu nào.
 Gia tộc đã quyết định từ bỏ nghiên cứu và gọi chúng tôi trở lại làm việc tại Kho Tàng. Nhưng tôi không thể chấp nhận kết thúc như vậy. Vì thế, tôi để lại một số thiết bị có thể thu thập dữ liệu chiến đấu, tự động lưu về máy chủ của Kho Tàng.
-Ai tìm thấy tin nhắn này, tôi hy vọng anh sẽ thử sức với Echoes này. Như vậy, chúng ta mới có thể thu thập được dữ liệu quan trọng... Có lẽ trong tương lai, dữ liệu này sẽ được ứng dụng vào nghiên cứu Echoes.
-Tôi cũng để lại một số phần thưởng. Nếu anh đánh bại được Echoes này, chúng sẽ thuộc về anh.</t>
+Ai tìm thấy tin nhắn này, tôi hy vọng anh sẽ thử sức với Echo này. Như vậy, chúng ta mới có thể thu thập được dữ liệu quan trọng... Có lẽ trong tương lai, dữ liệu này sẽ được ứng dụng vào nghiên cứu Echo.
+Tôi cũng để lại một số phần thưởng. Nếu anh đánh bại được Echo này, chúng sẽ thuộc về anh.</t>
         </is>
       </c>
     </row>
@@ -30484,7 +30478,7 @@
           <t>…
 Không ai có thể tiếp tục gánh vác một số phận nặng nề đến thế. Nỗi bi thương dưới lòng đất khiến lòng ta đau đớn. Vì vậy, đôi cánh tượng trưng cho một hành trình dài đã gập lại, chờ đợi ngày những linh hồn đã khuất được giải thoát.
 …
-(Tờ giấy ghi chú này, với Dodget chữ nguệch ngoạc, dường như bị xé ra từ một cuốn sổ. Ai đã để lại nó ở trạm?)</t>
+(Tờ giấy ghi chú này, với nét chữ nguệch ngoạc, dường như bị xé ra từ một cuốn sổ. Ai đã để lại nó ở trạm?)</t>
         </is>
       </c>
     </row>
@@ -30557,7 +30551,7 @@
 Giờ đây, ta còn một bí mật khác muốn chia sẻ với ngươi. Ta đã để lại thứ đặc biệt cho ngươi ở đây, và ta tin chắc ngươi sẽ thích nó.
 Cứ giữ lấy thiết bị giải mã đi. Nó sẽ mở lối cho ngươi đến "thử thách ẩn" mà ta đã chuẩn bị sẵn.
 "Hợp đồng lao động" của chúng ta sẽ không dễ dàng kết thúc đâu.
-À, và Discord cũng có thứ muốn gửi ngươi. Ta đã kèm nó chung với bức thư này rồi.</t>
+À, và Tacet Discord cũng có thứ muốn gửi ngươi. Ta đã kèm nó chung với bức thư này rồi.</t>
         </is>
       </c>
     </row>
@@ -30632,17 +30626,17 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Sự Mỏng Manh Của The Lifer (có thể loại bỏ bằng Stake of Imbalance):
-- Nỗi Cô Đơn Dâng Teao: The Lifer hồi phục 10% HP tối đa mỗi giây nếu không bị tấn công trong hơn 2 giây.
-- Longings Libert: Increase 25% Attack cho The Lifer. Ngoài ra, sát thương gây ra bởi The Lifer tăng thêm 25% sau mỗi 20 giây.
-- Bế Tắc Đến Gần: Mỗi lần gây sát thương, Attack của The Lifer tăng 20%, tối đa 4 lần cộng dồn. Nếu không gây sát thương trong 6 giây, tất cả cộng dồn sẽ bị xóa.
-- Time Phai Mòn: The Lifer nhận được 200% Glacio RES, Fusion, Electro, Aero, Spectro và Havoc. HP tối đa tăng 25%.
-Sự Stability Của The Lifer (không thể loại bỏ):
-- Xiềng Xích Giam Cầm: The Lifer miễn nhiễm với hiệu ứng gián đoạn khi HP trên 50%.
-- Trò Lối chơi Bất Tận: Thời gian bị Hóa Đá của The Lifer giảm 50%.
-- Garden Thiên Sugar: Sau khi nhận sát thương vượt quá 25% HP tối đa trong một đòn, The Lifer đẩy lùi kẻ địch xung quanh và gây sát thương cho chúng.
+          <t>Sự Mỏng Manh Của Kẻ Tù Đày (có thể loại bỏ bằng Cọc Mất Cân Bằng):
+- Nỗi Cô Đơn Dâng Trào: Kẻ Tù Đày hồi phục 10% HP tối đa mỗi giây nếu không bị tấn công trong hơn 2 giây.
+- Khát Khao Tự Do: Tăng 25% ATK cho Kẻ Tù Đày. Ngoài ra, DMG gây ra bởi Kẻ Tù Đày tăng thêm 25% sau mỗi 20 giây.
+- Bế Tắc Đến Gần: Mỗi lần gây DMG, ATK của Kẻ Tù Đày tăng 20%, tối đa 4 lần cộng dồn. Nếu không gây DMG trong 6 giây, tất cả cộng dồn sẽ bị xóa.
+- Thời Gian Phai Mòn: Kẻ Tù Đày nhận được 200% Kháng Glacio, Fusion, Electro, Aero, Spectro và Havoc. HP tối đa tăng 25%.
+Sự Ổn Định Của Kẻ Tù Đày (không thể loại bỏ):
+- Xiềng Xích Giam Cầm: Kẻ Tù Đày miễn nhiễm với hiệu ứng gián đoạn khi HP trên 50%.
+- Trò Chơi Bất Tận: Thời gian bị Hóa Đá của Kẻ Tù Đày giảm 50%.
+- Vườn Thiên Đường: Sau khi nhận DMG vượt quá 25% HP tối đa trong một đòn, Kẻ Tù Đày đẩy lùi kẻ địch xung quanh và gây DMG cho chúng.
 "Một ngày nọ, Thần Tính biến mất sau những bức tường, chỉ để lại kẻ tù đày đầy đau khổ."
-"Hãy đi theo những lối mòn hiện ra trên bàn cờ, nơi ngươi sẽ tìm thấy Stake of Imbalance—những chiếc còng đang giam giữ kẻ tù nhân."</t>
+"Hãy đi theo những lối mòn hiện ra trên bàn cờ, nơi ngươi sẽ tìm thấy Cọc Mất Cân Bằng—những chiếc còng đang giam giữ kẻ tù nhân."</t>
         </is>
       </c>
     </row>
@@ -30781,7 +30775,7 @@
         <is>
           <t>Hỡi kẻ bị giam cầm, linh hồn tù nhân, ngươi sẽ thay ta điều khiển những quân cờ này, bất tận cho đến muôn đời.
 Ý chí của ta tồn tại trong bàn cờ, trong từng quân cờ, và trong những xiềng xích trói buộc ngươi. Rinascita sẽ bước đi trên con đường thiêng liêng, từ nay đến mãi mãi.
-"Previous mặt kẻ được triệu hồi, một tù nhân bị xiềng xích ngồi đối diện bàn cờ."
+"Trước mặt kẻ được triệu hồi, một tù nhân bị xiềng xích ngồi đối diện bàn cờ."
 "Trong ván cờ đen trắng, giữa kẻ được triệu hồi và tù nhân, tất cả đều đấu tranh vì tự do."</t>
         </is>
       </c>
@@ -30852,13 +30846,12 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Bước 1: Ngước nhìn lên. Thấy những thứ giống diều trên trời không?
-Bước 2: Shoot hạ chúng bằng súng.
-Bước 3: Catches những con diều đó và đeo lên lưng.
-Bước 4: Get càng nhiều bom càng tốt.
-Bước 5: Flight qua kho báu, thả bom và khiến chúng phải trả giá.
-&lt;Phần còn lại của bảng dữ liệu chứa đầy những lời khoác lác ngạo mạn và những tưởng tượng về lời khen ngợi cùng thăng tiến&gt;</t>
+          <t>Bước 1: Ngước lên. Thấy mấy cái diều trên trời không?
+Bước 2: Bắn hạ chúng bằng súng.
+Bước 3: Bắt lấy những chiếc diều đó và đeo lên lưng.
+Bước 4: Thu thập càng nhiều bom càng tốt.
+Bước 5: Bay qua kho tàng, thả bom và khiến chúng phải trả giá.
+&lt;The rest of the data board is filled with arrogant bragging and fantasies about praise and promotions&gt;</t>
         </is>
       </c>
     </row>
@@ -30928,7 +30921,7 @@
       <c r="M398" t="inlineStr">
         <is>
           <t>Ngày 16.
-Bọn họ đều nói biển ngoài khơi Rinascita đầy rẫy hiểm nguy—bão tố, sương mù, đá ngầm, và những TD có thể nuốt chửng cả con tàu. Thậm chí có kẻ còn khẳng định thế giới bên ngoài Rinascita đã chết từ lâu trong Lament, chỉ còn lại những hòn đảo của chúng ta dưới sự che chở của Imperator.
+Bọn họ đều nói biển ngoài khơi Rinascita đầy rẫy hiểm nguy—bão tố, sương mù, đá ngầm, và những TD có thể nuốt chửng cả con tàu. Thậm chí có kẻ còn khẳng định thế giới bên ngoài Rinascita đã chết từ lâu trong Lời Than Vãn, chỉ còn lại những hòn đảo của chúng ta dưới sự che chở của Imperator.
 Vớ vẩn.
 Chúng sợ hãi những gì không biết. Chúng nghĩ tôi không dám đưa Gondola ra biển khơi, bảo tôi chỉ là con chuột sông chỉ biết khoác lác. Được thôi, tôi sẽ chứng minh mình không phải kẻ hèn nhát như chúng!
 Hôm nay tôi bắt được một con cá ngon. Một điềm lành, và cũng là một bữa ăn ngon. Giờ tôi có những vì sao dẫn đường, còn sợ gì nữa? Bão tố? Sóng gió? Cứ đến đi! Miễn có Gondola của tôi, không nơi nào ở Rinascita là tôi không thể tới.</t>
@@ -31001,7 +30994,7 @@
         <is>
           <t>Một quốc gia gồm các thành bang độc lập nằm rải rác trên quần đảo rộng lớn, không có trung tâm hành chính tập trung. Truyền thuyết kể về những người khai phá Rinascita, họ đã rời bỏ quê hương, vượt biển đến những hòn đảo này để thoát khỏi Lament.
 Là một quốc đảo tái sinh từ Lament, Rinascita từng bị cô lập với thế giới bên ngoài bởi thiên tai khắc nghiệt và khoảng cách địa lý. Mãi đến gần đây, người Rinascita mới mở ra những tuyến hàng hải mới. Những con tàu chất đầy gia vị và khoáng sản bắt đầu vượt đại dương, đổi lại, vô số kho báu và của cải cũng đổ về Rinascita, làm giàu cho bờ cõi nơi đây.
-Rinascita nổi tiếng với công nghệ "Echo General" độc đáo, cho phép Echo tồn tại dưới dạng vật chất trong bán kính của Genesis Nexus. Nhờ công nghệ này, người Rinascita đã hòa nhập Echo vào mọi mặt của cuộc sống. Đó là lý do quốc gia này được gọi là "Land of Echoes."
+Rinascita nổi tiếng với công nghệ "Tiếng Vọng Chung" độc đáo, cho phép Tiếng Vọng tồn tại dưới dạng vật chất trong bán kính của Genesis Nexus. Nhờ công nghệ này, người Rinascita đã hòa nhập Tiếng Vọng vào mọi mặt của cuộc sống. Đó là lý do quốc gia này được gọi là "Vùng Đất Tiếng Vọng."
 Người Rinascita coi trọng danh tính từ huyết thống, và xã hội của họ được xây dựng trên sự tôn kính sâu sắc với mối quan hệ gia đình. Đối với họ, phúc lợi của gia đình luôn đặt lên trên số phận cá nhân.</t>
         </is>
       </c>
@@ -31070,7 +31063,7 @@
       <c r="M400" t="inlineStr">
         <is>
           <t>Thành phố Ragunna, trung tâm hành chính của thành bang Ragunna tại Rinascita, là một thành phố cảng thịnh vượng bên bờ biển, với các quận huyện nối liền nhau bằng những dòng kênh uốn lượn. Người Ragunnesi là những tín đồ sùng đạo của Sentinel, họ tin rằng Common Echoes là món quà từ Sentinel mang theo ý chí thiêng liêng của Ngài.
-Bên cạnh đức tin, người dân Ragunna còn nổi tiếng với tình yêu nghệ thuật. Thành phố được trang hoàng bởi những tác phẩm điêu khắc và hội họa tuyệt đẹp ở khắp mọi nơi, và những buổi biểu diễn ngẫu hứng thường làm sôi động đường phố. Dưới sự lãnh đạo của Fenrico, The Primus đương nhiệm của Order of the Deep, một loạt luật lệ đã được ban hành nhằm hạn chế một số chủ đề trong biểu đạt nghệ thuật. Những luật này đã gây ra nhiều ý kiến trái chiều trong cư dân thành phố.
+Bên cạnh đức tin, người dân Ragunna còn nổi tiếng với tình yêu nghệ thuật. Thành phố được trang hoàng bởi những tác phẩm điêu khắc và hội họa tuyệt đẹp ở khắp mọi nơi, và những buổi biểu diễn ngẫu hứng thường làm sôi động đường phố. Dưới sự lãnh đạo của Fenrico, Primus đương nhiệm của Order of the Deep, một loạt luật lệ đã được ban hành nhằm hạn chế một số chủ đề trong biểu đạt nghệ thuật. Những luật này đã gây ra nhiều ý kiến trái chiều trong cư dân thành phố.
 Hiện tại, các công việc hàng ngày của Ragunna do Order of the Deep quản lý, trong khi các gia tộc danh tiếng như Montelli và Fisalia cũng nắm giữ ảnh hưởng đáng kể đến định hướng phát triển của thành phố.</t>
         </is>
       </c>
@@ -31141,8 +31134,8 @@
         <is>
           <t>Carnevale là lễ hội hoành tráng nhất của Ragunna, nơi những vũ hội hóa trang không bao giờ kết thúc, rượu chảy như sông suối, và âm nhạc ngân vang suốt đêm. Trong thời khắc này, mọi người gác lại gánh nặng cuộc đời, đắm chìm trong niềm vui sướng cuồng dại của lễ hội.
 Nguồn gốc Carnevale bắt nguồn từ Sentinel Imperator, người từng dẫn dắt dân tộc Rinascita. Ban đầu, nó là lễ dâng lên ân điển của Ngài, nơi tiếng cười và màn trình diễn trở thành hình thức tôn kính thuần khiết nhất.
-Enter đỉnh cao của Carnevale, Sentinel được cho là sẽ hiện thân và trao vòng nguyệt quế "Laurel" cho nghệ sĩ xuất sắc nhất. Danh hiệu này ban cho người nhận đặc quyền giao tiếp với Sentinel và lắng nghe trí tuệ của Ngài.
-Thế nhưng, một thập kỷ trước, Carnevale đã bị hủy hoại. Một quái thú biển khổng lồ, những Echoes bất trị cùng Discord tràn vào lễ hội, biến niềm vui thành tro tàn. Chỉ khi The Primus Fenrico can thiệp, hỗn loạn mới lắng xuống. Ông tuyên bố đó là sự trừng phạt thiêng liêng của Sentinel Imperator vì sự sa đọa và phản bội đức tin của người Ragunnesi. Từ đó, Carnevale không còn được tổ chức nữa.</t>
+Vào đỉnh cao của Carnevale, Sentinel được cho là sẽ hiện thân và trao vòng nguyệt quế "Laurel" cho nghệ sĩ xuất sắc nhất. Danh hiệu này ban cho người nhận đặc quyền giao tiếp với Sentinel và lắng nghe trí tuệ của Ngài.
+Thế nhưng, một thập kỷ trước, Carnevale đã bị hủy hoại. Một quái thú biển khổng lồ, những Echoes bất trị cùng Tacet Discord tràn vào lễ hội, biến niềm vui thành tro tàn. Chỉ khi Primus Fenrico can thiệp, hỗn loạn mới lắng xuống. Ông tuyên bố đó là sự trừng phạt thiêng liêng của Sentinel Imperator vì sự sa đọa và phản bội đức tin của người Ragunnesi. Từ đó, Carnevale không còn được tổ chức nữa.</t>
         </is>
       </c>
     </row>
@@ -31209,8 +31202,8 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Những kẻ bị Giáo Đoàn Abyssal coi là bất trung sẽ bị đưa lên con thuyền Hành Hương, dấn thân theo con đường cổ xưa của những người từng vượt sương mù và bão tố để tìm kiếm sự dẫn dắt của Warden.
-Giáo Đoàn tuyên bố chỉ có Imperator mới có thể ban sự tha thứ cho những kẻ phản bội này. Họ phải trải qua một cuộc hành hương đầy khổ ải, chịu đựng đau đớn cả thể xác lẫn tinh thần cho đến khi sự hối cải của họ được chấp nhận. Ở cuối hành trình, Warden Imperator sẽ ban cho họ sự tha thứ và lời hứa về một cuộc sống mới.
+          <t>Những kẻ bị Giáo Đoàn Vực Sâu coi là bất trung sẽ bị đưa lên con thuyền Hành Hương, dấn thân theo con đường cổ xưa của những người từng vượt sương mù và bão tố để tìm kiếm sự dẫn dắt của Người Canh Gác.
+Giáo Đoàn tuyên bố chỉ có Imperator mới có thể ban sự tha thứ cho những kẻ phản bội này. Họ phải trải qua một cuộc hành hương đầy khổ ải, chịu đựng đau đớn cả thể xác lẫn tinh thần cho đến khi sự hối cải của họ được chấp nhận. Ở cuối hành trình, Người Canh Gác Imperator sẽ ban cho họ sự tha thứ và lời hứa về một cuộc sống mới.
 Nhưng ở Ragunna, chưa ai từng nghe tin một kẻ "hành hương" bất trung nào trở về từ chuyến đi thiêng liêng này. Giáo Đoàn khẳng định họ đã đến nơi ở của Imperator và cống hiến bản thân cho sự phục vụ vĩnh cửu của Ngài. Dù nhiều người vẫn nghi ngờ, ít ai dám công khai thách thức Giáo Đoàn—không ai muốn chịu chung số phận bi thảm như những kẻ bị gán mác "Kẻ Ngốc".</t>
         </is>
       </c>
@@ -31278,7 +31271,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Một Echoes hình thuyền phổ biến ở Ragunna.
+          <t>Một Echo hình thuyền phổ biến ở Ragunna.
 Mạng lưới kênh rạch phức tạp của Ragunna, cùng với những con phố hẹp và địa hình gồ ghề bao quanh thành phố, đã khiến Gondola trở thành lựa chọn ưu tiên để vận chuyển người và hàng hóa. Với hầu hết người Ragunna, chúng mang lại cảm giác yên bình, êm ái thay vì phải chen chúc trên những con phố đông đúc hay những con đường quê gập ghềnh.
 Dưới vẻ ngoài giản dị, Gondola lại vô cùng thông minh và giàu cảm xúc. Chúng giao tiếp qua những tần số âm thanh riêng biệt, thể hiện tâm trạng hoặc phản hồi mệnh lệnh của người lái. Một số, qua huấn luyện đặc biệt, thậm chí có thể leo lên cả thác nước.</t>
         </is>
@@ -31351,13 +31344,12 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Giáo Đoàn Deep Sea tôn thờ Sentinel Imperator. Theo truyền thống Ragunna, giáo sĩ của Giáo Đoàn là sứ giả trần gian của Sentinel, được giao trọng trách dẫn dắt dân chúng theo lời thần thánh của Ngài.
-Giáo Đoàn do The Primus đứng đầu, và The Primus hiện tại, Fenrico, đã tự xưng là "Bậc Epiphany", Synergy Giả của Sentinel. Sau lễ hội Carnevale vừa qua, hắn tuyên bố đã tìm ra cách giao tiếp trực tiếp với Sentinel.
-Dưới The Primus, các Linh mục giám sát các nghi lễ và nhiệm vụ thiêng liêng của Giáo Đoàn, trong khi các giáo sĩ bình thường, gọi là Tín đồ, ngày ngày nghiên cứu Kinh Thánh, truyền bá lời dạy của Sentinel khắp Ragunna.
-Để duy trì trật tự thần thánh, Giáo Đoàn điều hành ba nhánh riêng biệt:
-Tòa án Giáo Đoàn: Cơ quan tư pháp thế tục của Giáo Đoàn, xử lý các vụ dân sự và hình sự giữa các gia tộc và thường dân.
-Phòng Discipline: Cơ quan hành pháp của Giáo Đoàn, chỉ huy quân đội để thực thi pháp luật. Phòng này sử dụng nhiều Echoes trong chiến đấu, và các chấp pháp viên thường được gọi là "Thẩm tra viên".
-Tòa án Sám Hối: Tòa án tôn giáo của Giáo Đoàn, xét xử những kẻ dị giáo và vô tín, những kẻ đặt câu hỏi và chống lại lời dạy thần thánh của Sentinel.</t>
+          <t>Giáo Đoàn Biển Sâu tôn thờ Sentinel Imperator. Theo truyền thống Ragunna, giáo sĩ của Giáo Đoàn là sứ giả trần gian của Sentinel, được giao trọng trách dẫn dắt dân chúng theo lời thần thánh của Ngài.
+Giáo Đoàn do Primus đứng đầu, và Primus hiện tại, Fenrico, đã tự xưng là "Bậc Giác Ngộ", Resonator của Sentinel. Sau lễ hội Carnevale vừa qua, hắn tuyên bố đã tìm ra cách giao tiếp trực tiếp với Sentinel.
+Dưới Primus, các Linh mục giám sát các nghi lễ và nhiệm vụ thiêng liêng của Giáo Đoàn, trong khi các giáo sĩ bình thường, gọi là Tín đồ, ngày ngày nghiên cứu Kinh Thánh, truyền bá lời dạy của Sentinel khắp Ragunna.
+Để duy trì trật tự thần thánh, Giáo Đoàn điều hành ba nhánh riêng biệt: Order Tribunal: The Order's secular judicial body that handles civil and criminal matters between families and commoners.
+Chamber of Discipline: The Order's executive arm that commands the military to enforce the law. The Chamber heavily employs Echoes in combat, and its enforcers are often called "Inquisitors."
+Order Penitentiary: The Order's religious court that trials heretics and faithless who question and defy the divine teachings of the Sentinel.</t>
         </is>
       </c>
     </row>
@@ -31560,7 +31552,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Guardian Rinascita. Trong tín ngưỡng của Giáo Đoàn Deep Sea, Họ thường được miêu tả là một sinh vật với nửa thân trên là ngựa và nửa thân dưới là cá.
+          <t>Người Bảo Vệ Rinascita. Trong tín ngưỡng của Giáo Đoàn Biển Sâu, Họ thường được miêu tả là một sinh vật với nửa thân trên là ngựa và nửa thân dưới là cá.
 Theo truyền thuyết của Ragunna, Imperator đã dẫn dắt những người định cư đến vùng đất hứa này, ban cho họ nơi trú ẩn khỏi mối đe dọa của Lament.
 Dù Imperator hiếm khi hiện diện trước thế gian, Họ vẫn duy trì mối liên hệ với người dân Ragunna thông qua Laureate của Carnevale, truyền đạt những lời tiên tri thiêng liêng.</t>
         </is>
@@ -31628,8 +31620,8 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Tại Rinascita, hầu hết các Echoes đều có thể tồn tại độc lập ngoài các Terminal Dự trữ trong bán kính của Genesis Nexus. Chúng được gọi là Echoes Thông thường.
-Tại Ragunna, Hội Đoàn Cõi Sâu kiểm soát việc phân phối và sử dụng những Echoes này. Người dân Ragunna tôn thờ chúng như món quà thần thánh, thậm chí là sứ giả của Sentinel Imperator. Họ coi chúng như bạn bè, đồng minh đáng tin cậy, hòa nhập vào mọi khía cạnh của cuộc sống hàng ngày. Mối liên kết cộng sinh sâu sắc với Echoes Thông thường này chính là lý do Rinascita được mệnh danh là "Land Của Những Âm Vang".</t>
+          <t>Tại Rinascita, hầu hết các Echo đều có thể tồn tại độc lập ngoài các Thiết bị đầu cuối Dự trữ trong bán kính của Genesis Nexus. Chúng được gọi là Echo Thông thường.
+Tại Ragunna, Hội Đoàn Cõi Sâu kiểm soát việc phân phối và sử dụng những Echo này. Người dân Ragunna tôn thờ chúng như món quà thần thánh, thậm chí là sứ giả của Sentinel Imperator. Họ coi chúng như bạn bè, đồng minh đáng tin cậy, hòa nhập vào mọi khía cạnh của cuộc sống hàng ngày. Mối liên kết cộng sinh sâu sắc với Echo Thông thường này chính là lý do Rinascita được mệnh danh là "Vùng Đất Của Những Âm Vang".</t>
         </is>
       </c>
     </row>
@@ -31695,8 +31687,8 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Trung tâm Nexus Synergy của Rinascita, còn gọi là Genesis Nexus. Theo truyền thuyết, Imperator đã tiết lộ bí mật của Genesis Nexus cho người Rinascita, cho phép họ xây dựng những công trình vĩ đại khác như biểu tượng cho quyền lực và chủ quyền của Sentinel.
-Trong phạm vi của Genesis Nexus, Echoes có thể tồn tại dưới dạng vật lý mà không cần dựa vào Terminal.</t>
+          <t>Trung tâm Nexus Cộng Hưởng của Rinascita, còn gọi là Genesis Nexus. Theo truyền thuyết, Imperator đã tiết lộ bí mật của Genesis Nexus cho người Rinascita, cho phép họ xây dựng những công trình vĩ đại khác như biểu tượng cho quyền lực và chủ quyền của Sentinel.
+Trong phạm vi của Genesis Nexus, Echo có thể tồn tại dưới dạng vật lý mà không cần dựa vào Thiết bị đầu cuối.</t>
         </is>
       </c>
     </row>
@@ -31762,8 +31754,8 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Shui Triều Hắc Ám là một Hiện Tượng Bị Sóng Erosion có nguồn gốc từ Rinascita. Nó hiện ra như một khối mây đen cuồn cuộn, tụ lại rồi vỡ tan, đổ xuống như thác nước. Nơi nào Shui Triều Hắc Ám tràn tới, Discord sẽ xuất hiện, và vùng đất xung quanh điểm khởi nguồn sẽ trở thành một Tacet Field mới.
-Trong lịch sử Ragunna, đã có hai đợt Shui Triều Hắc Ám lớn. Lần đầu, theo ghi chép của Order of the Deep, đã bị Napoli II, The Primus đầu tiên của Hội, ngăn chặn. Lần thứ hai được dập tắt nhờ sự hy sinh của Thánh Nữ Fleurdelys.</t>
+          <t>Thủy Triều Hắc Ám là một Hiện Tượng Bị Sóng Xói Mòn có nguồn gốc từ Rinascita. Nó hiện ra như một khối mây đen cuồn cuộn, tụ lại rồi vỡ tan, đổ xuống như thác nước. Nơi nào Thủy Triều Hắc Ám tràn tới, Tacet Discord sẽ xuất hiện, và vùng đất xung quanh điểm khởi nguồn sẽ trở thành một Tổ Tacet mới.
+Trong lịch sử Ragunna, đã có hai đợt Thủy Triều Hắc Ám lớn. Lần đầu, theo ghi chép của Order of the Deep, đã bị Napoli II, Primus đầu tiên của Hội, ngăn chặn. Lần thứ hai được dập tắt nhờ sự hy sinh của Thánh Nữ Fleurdelys.</t>
         </is>
       </c>
     </row>
@@ -31898,7 +31890,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Creatures Tàn Dư trú ngụ bên trong Nimbus Sanctum. Truyền thuyết kể rằng chính sức mạnh của Lorelei đã kiềm chế biển mây hung dữ, cứu Ragunna khỏi bị nhấn chìm.
+          <t>Sinh Vật Tàn Dư trú ngụ bên trong Nimbus Sanctum. Truyền thuyết kể rằng chính sức mạnh của Lorelei đã kiềm chế biển mây hung dữ, cứu Ragunna khỏi bị nhấn chìm.
 Lorelei có khả năng thanh tẩy những tần số đen tối trong mây, nhưng cô không miễn nhiễm với sự ăn mòn của chúng. Khi tích tụ đến mức giới hạn, Lorelei cuối cùng sẽ trở thành Nữ Hoàng Bóng Đêm, giải phóng cơn thịnh nộ lên mọi sinh vật dám bén mảng đến gần.</t>
         </is>
       </c>
@@ -32130,11 +32122,11 @@
 Quá khứ đã trải qua quá trình lên men dài lâu, trở thành vị ngọt ngào, lưu luyến nơi cổ họng.
 Câm lặng, cậu thở dài rồi nhấp thêm một ngụm, nhớ về những ngày tháng tươi đẹp không bao giờ trở lại.
 Trong những khoảnh khắc như thế, tôi là người lắng nghe tuyệt vời nhất mà cậu từng có.
-"Rules Im Lặng"
+"Quy Tắc Im Lặng"
 Đây là quy tắc đầu tiên mà mọi thành viên Montelli phải tuân theo, khắc sâu vào xương tủy, trân quý và bất di bất dịch như gia đình của họ.
 Than ôi, cậu đã gọi món này; có vẻ ai đó cần một lời "nhắc nhở" tử tế.
 &lt;i&gt;*Cậu có thể để ý rằng thực đơn không ghi giá. Không, đó không phải sơ suất đâu. Ở đây, rượu không chỉ đo bằng tiền bạc.&lt;/i&gt;
-&lt;i&gt;*Enter đúng thời điểm, với đúng người, hãy đến gặp tôi ở đây. Nhớ rằng, quầy bar ở Ragunna luôn mở cửa cho bất kỳ ai muốn gọi món.&lt;/i&gt;</t>
+&lt;i&gt;*Vào đúng thời điểm, với đúng người, hãy đến gặp tôi ở đây. Nhớ rằng, quầy bar ở Ragunna luôn mở cửa cho bất kỳ ai muốn gọi món.&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -32220,29 +32212,11 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Ở Ragunna, trở thành một người yêu thích rượu dễ dàng hơn nhiều so với việc tránh xa chúng.
-Mỗi công thức đều chứa đựng một câu chuyện, và mỗi câu chuyện đều được đổi lấy một ly rượu. Bạn sẽ luôn tìm thấy điều gì đó chạm đến tâm hồn mình—nếu bạn có thể giải mã được "mật mã" của rượu.
-&lt;i&gt;*Sau đây là tuyển chọn độc quyền các loại rượu từ Montelli&lt;/i&gt;
-&lt;i&gt;*Thức Uống và Miêu Tả&lt;/i&gt;
-"Khi Nàng Bước Enter Garden"
-Một làn gió vui tươi thổi qua, mang theo hơi ấm giữa chúng ta... Hãy để tôi đắm chìm trong sự nở rộ của những bông hoa mà nàng vun trồng.
-Cánh cổng mộng tưởng mở rộng; hãy để tôi chiêm ngưỡng vẻ nặng trĩu của những nụ hoa sum suê.
-Những lời thì thầm và tiếng xì xào đan xen, khiến tâm trí nàng trôi dạt. Mailởng thức, ngây ngất... Đó chẳng phải là điều nàng hằng khao khát sao?
-"Tình Yêu và Medicine Thần"
-Hãy nói cho tôi biết—điều gì thực sự phân biệt một liều thuốc với tình yêu?
-Cả hai đều dệt nên ảo ảnh, hàn gắn trái tim tan vỡ—và để lại những vết sẹo.
-"Night Kinh Hoàng"
-Nếu nàng chưa say khướt, liệu nàng có dám gọi món này không?
-Nàng thực sự đang tìm kiếm điều gì? Một vị cứu tinh? Một vị thánh? Một thiên thần? Được thôi—nàng đã gửi đi lời cầu cứu của mình.
-"Bộ Quần Áo New Của Hoàng Đế"
-Consensus thông minh nhất mà nàng từng thực hiện, dù chiếc ly trông hoàn toàn trống rỗng.
-Hãy mang nó đến cho người bạn đồng hành của nàng, người sở hữu mọi thứ—chia sẻ, và cả hai sẽ có một ly rượu.
-"TF10"
-Đúng hay sai, 1 hay 0.
-Khi chia sẻ ly rượu này, chúng ta cam kết sự trung thực—một khoảnh khắc khi mọi thứ phải được phơi bày.
-&lt;i&gt;*Có thể bạn đã nhận ra rằng thực đơn không có giá cả. Không, đó không phải là sơ suất. Ở đây, rượu được đo lường bằng thứ khác ngoài tiền bạc.&lt;/i&gt;
-&lt;i&gt;*Enter đúng thời điểm, với đúng người, hãy đến gặp tôi ở đây. Hãy nhớ rằng, các quầy bar ở Ragunna luôn mở cửa cho bất kỳ ai muốn gọi món.&lt;/i&gt;</t>
+          <t>Ở Ragunna, trở thành kẻ mê say rượu còn dễ hơn tránh xa chúng.
+Mỗi công thức đều chứa đựng một câu chuyện, và mỗi câu chuyện đều được đổi lấy một ly rượu. Luôn có thứ gì đó chạm đến tâm hồn cậu—nếu cậu giải mã được "mật mã" của rượu.
+&lt;i&gt;*Dưới đây là tuyển chọn độc quyền những loại rượu từ Montelli&lt;/i&gt;
+&lt;i&gt;*Tên và miêu tả&lt;/i&gt;
+"Khi Nàng Bước Vào Vườn"</t>
         </is>
       </c>
     </row>
@@ -32319,10 +32293,10 @@
         <is>
           <t>Cảm thấy hơi ngán đồ uống rồi à? Quán Ragunna còn có nhiều món ăn nhẹ tuyệt vời để làm mới vị giác của cậu đấy.
 Khác với mấy loại nước uống đầy "mã code" kia, những món này đơn giản—và miễn phí khi gọi đồ uống.
-&lt;i&gt;Dish nhẹ và mô tả&lt;/i&gt;
+&lt;i&gt;Món ăn nhẹ và mô tả&lt;/i&gt;
 * Sô-cô-la St. Domingo
 Mịn màng và đậm đà, loại sô-cô-la này kích thích vị giác với sự hòa quyện đắng ngọt của mứt cam và rượu vang, để lại dư vị kéo dài.
-* Sellh Earl Grey
+* Bánh Earl Grey
 Lớp bánh thơm mùi trà đen kết hợp với hương cam chanh tươi mát, mang đến vị dịu nhẹ mà không hề đắng.
 * Sabayon anh đào ngâm rượu
 Những trái anh đào đỏ mọng ngâm trong hỗn hợp kem trứng và rượu ngọt, được nướng caramel nhẹ cho hương khói thoang thoảng.
@@ -32415,22 +32389,22 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>(Tiếng trống trầm hùng vang lên khi Fleurdelys, Brand và các Devotee khác bước vào, mỗi người đều mang theo những di vật thiêng.)
-&lt;b&gt;Fleurdelys&lt;/b&gt;: Này, Shui Triều Hắc Ám tạm thời rút lui, ban cho Rinascita một khoảng nghỉ ngắn ngủi. Ta chân thành cảm tạ lòng kiên trung của các ngươi trong những ngày tháng gian khổ này.
-&lt;b&gt;Brand&lt;/b&gt;: Maila tiểu thư, ngài ban cho chúng tôi vinh dự quá đỗi. Chúng tôi phụng sự không chỉ riêng ngài, mà còn vì Người Bảo Hộ. Khi Rinascita chỉ còn treo trên sợi tơ mỏng, làm sao chúng tôi có thể đặt sự sống của bản thân lên trên nghĩa vụ thiêng liêng? Hơn nữa, chính ngài đã đứng bên chúng tôi, cầm vũ khí dẫn dắt chúng tôi đối mặt với Shui Triều Hắc Ám, chịu đựng những vết thương trầm trọng mà không hề nao núng. Ngài chính là hiện thân của sự thuần khiết và tận tụy của một Devotee, cũng như lòng dũng cảm và khí phách của một chiến binh. Được truyền cảm hứng từ nghị lực của ngài, chúng tôi sẵn sàng hiến dâng sinh mạng mà không chút do dự.
-&lt;b&gt;Brand&lt;/b&gt;: Thế nhưng tia sáng le lói ở phương bắc vừa lóe lên đã nhanh chóng bị Shui Triều Hắc Ám tàn nhẫn dập tắt, nó quay trở lại như một con thú đói khát, nuốt chửng mảnh đất của chúng ta. Các chiến binh của ta đã chiến đấu dũng cảm, nhưng vẫn bị cuốn phăng bởi cơn thịnh nộ không ngừng. Dù giờ đây thủy triều đã rút lui, nhưng sự trở lại của nó chắc chắn như định mệnh. Ta e rằng, theo thời gian, sức mạnh của chúng ta sẽ suy yếu…
+          <t>(Tiếng trống trầm hùng vang lên khi Fleurdelys, Brand và các Tín Đồ khác bước vào, mỗi người đều mang theo những di vật thiêng.)
+&lt;b&gt;Fleurdelys&lt;/b&gt;: Này, Thủy Triều Hắc Ám tạm thời rút lui, ban cho Rinascita một khoảng nghỉ ngắn ngủi. Ta chân thành cảm tạ lòng kiên trung của các ngươi trong những ngày tháng gian khổ này.
+&lt;b&gt;Brand&lt;/b&gt;: Thưa tiểu thư, ngài ban cho chúng tôi vinh dự quá đỗi. Chúng tôi phụng sự không chỉ riêng ngài, mà còn vì Người Bảo Hộ. Khi Rinascita chỉ còn treo trên sợi tơ mỏng, làm sao chúng tôi có thể đặt sự sống của bản thân lên trên nghĩa vụ thiêng liêng? Hơn nữa, chính ngài đã đứng bên chúng tôi, cầm vũ khí dẫn dắt chúng tôi đối mặt với Thủy Triều Hắc Ám, chịu đựng những vết thương trầm trọng mà không hề nao núng. Ngài chính là hiện thân của sự thuần khiết và tận tụy của một Tín Đồ, cũng như lòng dũng cảm và khí phách của một chiến binh. Được truyền cảm hứng từ nghị lực của ngài, chúng tôi sẵn sàng hiến dâng sinh mạng mà không chút do dự.
+&lt;b&gt;Brand&lt;/b&gt;: Thế nhưng tia sáng le lói ở phương bắc vừa lóe lên đã nhanh chóng bị Thủy Triều Hắc Ám tàn nhẫn dập tắt, nó quay trở lại như một con thú đói khát, nuốt chửng mảnh đất của chúng ta. Các chiến binh của ta đã chiến đấu dũng cảm, nhưng vẫn bị cuốn phăng bởi cơn thịnh nộ không ngừng. Dù giờ đây thủy triều đã rút lui, nhưng sự trở lại của nó chắc chắn như định mệnh. Ta e rằng, theo thời gian, sức mạnh của chúng ta sẽ suy yếu…
 &lt;b&gt;Fleurdelys&lt;/b&gt;: …Có lẽ vẫn còn một tia hy vọng.
-&lt;b&gt;Fleurdelys&lt;/b&gt;: Không lâu trước đây, khi ta bất tỉnh vì vết thương, ta đã bị mắc kẹt trong một cơn ác mộng triền miên suốt ba ngày ba đêm, chìm sâu trong bóng tối vô tận. Nhưng trong vực thẳm ấy, một ánh sáng mờ nhạt đã xuất hiện—Họ đã nói với ta. Những lời từ bi vô hạn của Họ đã xoa dịu tâm hồn đầy thương tích của ta và đánh thức ta. Họ tiết lộ rằng vết thương trên thân thể thần thánh của chính Họ chính là nguồn cơn của Shui Triều Hắc Ám, và chỉ có thể chữa lành vết thương ấy thông qua một mối dây liên kết sức mạnh chung. Ta được kêu gọi phải đi về phía đông, đến thiên đường cao vợi trong sương mù, để phá vỡ lời nguyền của Shui Triều Hắc Ám.
-&lt;b&gt;Brand&lt;/b&gt;: Ngợi khen Người Bảo Hộ Vĩ Đại! Maila tiểu thư, nếu lời tiên tri này là thật, và ngài đã chia sẻ sức mạnh của mình với Người Bảo Hộ… Liệu có phải Đấng Epiphany đã thực sự hiện diện giữa chúng ta?
-&lt;b&gt;Fleurdelys&lt;/b&gt;: Ta không dám đoán định điều đó. Khi ta nhận được lời kêu gọi thiêng liêng và đảm nhận vai trò này, Người Bảo Hộ đã không tiết lộ sự thật về Đấng Epiphany cho ta.
-&lt;b&gt;Brand&lt;/b&gt;: Nhưng thưa tiểu thư, ngài đã tạo ra vô số phép màu, kéo dân chúng khỏi cảnh lầm than và cầu nguyện thay họ. Với chúng tôi, ngài chính là Thánh Nữ. Trong mắt chúng tôi, ngài chẳng khác gì Đấng Epiphany.
+&lt;b&gt;Fleurdelys&lt;/b&gt;: Không lâu trước đây, khi ta bất tỉnh vì vết thương, ta đã bị mắc kẹt trong một cơn ác mộng triền miên suốt ba ngày ba đêm, chìm sâu trong bóng tối vô tận. Nhưng trong vực thẳm ấy, một ánh sáng mờ nhạt đã xuất hiện—Họ đã nói với ta. Những lời từ bi vô hạn của Họ đã xoa dịu tâm hồn đầy thương tích của ta và đánh thức ta. Họ tiết lộ rằng vết thương trên thân thể thần thánh của chính Họ chính là nguồn cơn của Thủy Triều Hắc Ám, và chỉ có thể chữa lành vết thương ấy thông qua một mối dây liên kết sức mạnh chung. Ta được kêu gọi phải đi về phía đông, đến thiên đường cao vợi trong sương mù, để phá vỡ lời nguyền của Thủy Triều Hắc Ám.
+&lt;b&gt;Brand&lt;/b&gt;: Ngợi khen Người Bảo Hộ Vĩ Đại! Thưa tiểu thư, nếu lời tiên tri này là thật, và ngài đã chia sẻ sức mạnh của mình với Người Bảo Hộ… Liệu có phải Đấng Giác Ngộ đã thực sự hiện diện giữa chúng ta?
+&lt;b&gt;Fleurdelys&lt;/b&gt;: Ta không dám đoán định điều đó. Khi ta nhận được lời kêu gọi thiêng liêng và đảm nhận vai trò này, Người Bảo Hộ đã không tiết lộ sự thật về Đấng Giác Ngộ cho ta.
+&lt;b&gt;Brand&lt;/b&gt;: Nhưng thưa tiểu thư, ngài đã tạo ra vô số phép màu, kéo dân chúng khỏi cảnh lầm than và cầu nguyện thay họ. Với chúng tôi, ngài chính là Thánh Nữ. Trong mắt chúng tôi, ngài chẳng khác gì Đấng Giác Ngộ.
 &lt;b&gt;Fleurdelys&lt;/b&gt;: Dù vậy, ta vẫn có nghĩa vụ với Người Bảo Hộ. Giờ đây, khi đã biết con đường dẫn đến ngai vàng của Người, ta phải ngăn chặn lời nguyền từ tận gốc, bởi Rinascita không thể chịu thêm bất kỳ hy sinh nào nữa.
 &lt;b&gt;Brand&lt;/b&gt;: Đúng vậy! Lính canh, chuẩn bị hộ tống tiểu thư!
-&lt;b&gt;Fleurdelys&lt;/b&gt;: Không, hãy ở lại. Shui Triều Hắc Ám vẫn còn rình rập ở phương bắc, và các ngươi ở lại bảo vệ dân chúng sẽ tốt hơn là đi theo ta.
+&lt;b&gt;Fleurdelys&lt;/b&gt;: Không, hãy ở lại. Thủy Triều Hắc Ám vẫn còn rình rập ở phương bắc, và các ngươi ở lại bảo vệ dân chúng sẽ tốt hơn là đi theo ta.
 &lt;b&gt;Brand&lt;/b&gt;: Nhưng...
 &lt;b&gt;Fleurdelys&lt;/b&gt;: Đây là con đường ta phải đi một mình, như sứ mệnh Người Bảo Hộ đã giao phó. Hành trình này có thể sẽ là lần cuối cùng của ta. Nếu ta không trở về, nghĩa vụ duy trì trật tự của Giáo Đoàn sẽ thuộc về các ngươi.
-(Các Devotee bắt đầu khóc thút thít ở phía sau.)
-&lt;b&gt;Fleurdelys&lt;/b&gt;: Đừng khóc. Đây là con đường mà ta được chọn. Nếu số phận mỉm cười, Shui Triều Hắc Ám sẽ sớm biến mất, và Rinascita sẽ lại hưng thịnh. Đến ngày đó, hãy nhớ đến ta qua những khúc ca vui tươi thay vì những lời ai oán. Ta tin chắc Người Bảo Hộ cũng mong muốn điều đó.. (mỉm cười ấm áp)
+(Các Tín Đồ bắt đầu khóc thút thít ở phía sau.)
+&lt;b&gt;Fleurdelys&lt;/b&gt;: Đừng khóc. Đây là con đường mà ta được chọn. Nếu số phận mỉm cười, Thủy Triều Hắc Ám sẽ sớm biến mất, và Rinascita sẽ lại hưng thịnh. Đến ngày đó, hãy nhớ đến ta qua những khúc ca vui tươi thay vì những lời ai oán. Ta tin chắc Người Bảo Hộ cũng mong muốn điều đó.. (mỉm cười ấm áp)
 &lt;b&gt;Brand&lt;/b&gt;: Như ngài mong muốn, thưa tiểu thư. Nếu ngài đi về phía đông, Linh Mục Fenrico đang đóng quân ở đó cùng một đội vệ binh. Ông ấy có thể trợ giúp ngài.
 &lt;b&gt;Fleurdelys&lt;/b&gt;: Hãy nhìn xem, bình minh lại ló dạng. Dù đêm dài đến đâu, ánh sáng ban ngày vẫn sẽ đến. Dù con đường ta đi đầy nước mắt, chúng ta vẫn sẽ bước đi với những khúc ca và lòng dũng cảm. Đây chính là kho báu vĩ đại nhất của Rinascita và lá chắn vững chắc nhất của nhân loại—ý chí không gãy, niềm tin không lay chuyển, và hy vọng không bao giờ tắt! (rời đi)
 &lt;b&gt;Brand&lt;/b&gt;: Nguyện lưỡi kiếm của ngài được ban phước, để dẹp yên bão tố và chặt đứt thủy triều! (rời đi)
@@ -32534,14 +32508,14 @@
 Vì sao nên chọn chúng tôi quản lý tài sản của bạn?
 Mạng lưới dịch vụ khách hàng cá nhân hóa!
 Dịch vụ khách hàng của Averardo Bank phủ sóng toàn quốc và đang tích cực mở rộng chi nhánh trên khắp Solaris, đảm bảo việc đi lại và chi tiêu của bạn luôn suôn sẻ dù ở bất cứ đâu. Với các chi nhánh hải ngoại trong tương lai, chúng tôi sẽ nắm bắt kịp thời các diễn biến tài chính trên toàn Solaris, giúp khách hàng phát hiện những cơ hội đầu tư tiềm năng với tốc độ tăng trưởng cao và lợi nhuận hấp dẫn, đồng thời xây dựng các mối quan hệ đáp ứng nhu cầu đa dạng của khách hàng.
-Bình luận: Hiểu rồi. Like phòng gym hứa hẹn mở rộng toàn quốc và kêu gọi bạn đăng ký hội viên, rồi bảo sẽ có huấn luyện viên lên kế hoạch cá nhân cho bạn.
+Bình luận: Hiểu rồi. Giống như phòng gym hứa hẹn mở rộng toàn quốc và kêu gọi bạn đăng ký hội viên, rồi bảo sẽ có huấn luyện viên lên kế hoạch cá nhân cho bạn.
 T000000:::Tờ rơi Ngân hàng 3
 Vì sao nên chọn chúng tôi quản lý tài sản của bạn?
 Sức mạnh tài chính không đối thủ!
 Vốn hóa thị trường của Averardo Bank đứng đầu Rinascita, thể hiện sức mạnh tài chính vượt trội, tính thanh khoản cao và nguồn vốn dồi dào. Điều này cho phép chúng tôi đáp ứng mạnh mẽ mọi nhu cầu của khách hàng, từ tài trợ, cho vay đến bảo lãnh, đồng thời đảm bảo khả năng chống chịu vững vàng trước các rủi ro tài chính.
 Ngoài dịch vụ tài chính, Averardo Bank còn điều hành sáng kiến đấu giá, giao dịch và sưu tầm lớn nhất Rinascita, đồng thời tích cực tìm kiếm đầu tư từ bên ngoài. Đội ngũ chuyên trách nội bộ của chúng tôi đã hoàn thành xuất sắc nhiều dự án cơ sở hạ tầng.
 Tóm lại, Averardo Bank chính là hệ thống tài chính của Rinascita, với khả năng chống chịu rủi ro không đối thủ.
-Bình luận: Hiểu rồi. Nói trắng ra là "Ta giàu đến mức không cần tiền của ngươi."
+Bình luận: Hiểu rồi. Nói trắng ra là "Tao giàu đến mức không cần tiền của mày."
 T000000:::Tờ rơi Ngân hàng 4
 Vì sao nên chọn chúng tôi quản lý tài sản của bạn?
 Nguồn nhân tài xuất chúng!
@@ -32549,8 +32523,8 @@
 Bình luận: Hiểu rồi. Cậu gần như đã "gom" hết nhân tài ngân hàng trên toàn Solaris rồi.
 T000000:::Tờ rơi Ngân hàng 5
 Vì sao nên chọn chúng tôi quản lý tài sản của bạn?
-Malee tuổi của chúng tôi.
-Montelli. Malee tuổi của chúng tôi là Montelli.
+Tên tuổi của chúng tôi.
+Montelli. Tên tuổi của chúng tôi là Montelli.
 Bình luận: Hiểu rồi. "Chúng tôi là Montelli, nên anh nên gửi tiền vào ngân hàng của chúng tôi." Cũng... có lý đấy chứ.</t>
         </is>
       </c>
@@ -32676,31 +32650,31 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>((Một cuốn cẩm nang du lịch do Pioneer Association biên soạn. Nhưng mục về Thị trấn Egla đã không được cập nhật trong một thời gian khá dài.)
-[Điểm Đến Du Lịch Sắp Hot Yi]: Thị trấn Egla!
+          <t>((Một cuốn cẩm nang du lịch do Hiệp Hội Tiên Phong biên soạn. Nhưng mục về Thị trấn Egla đã không được cập nhật trong một thời gian khá dài.)
+[Điểm Đến Du Lịch Sắp Hot Nhất]: Thị trấn Egla!
 Với những ai đủ dũng cảm để đặt chân đến vùng đất đã truyền cảm hứng cho những vở kịch phiêu lưu trong lễ hội Carnevale, khám phá vương quốc huyền thoại của những "người khổng lồ" hùng mạnh, lắng nghe những khúc ca vang vọng từ biển mây bên dòng nước, hay đi theo dấu chân của các hiệp sĩ truy tìm danh dự và công lý, tất cả sẽ không còn là những giấc mơ xa vời. Tại Thị trấn Egla, du khách có thể đắm mình trong khung cảnh ven sông tuyệt đẹp, chiêm ngưỡng cuộc di cư hùng vĩ của loài Tumbleyak, ngắm những chiếc cối xay gió quay nhịp nhàng trên đồng bằng, tắm mình trong ánh hoàng hôn vàng óng. Hoặc đơn giản chỉ là thưởng thức một buổi trà chiều yên bình và những món ăn ngon có tuổi đời hàng thế kỷ, trong khi xung quanh là sắc màu rực rỡ của những đóa hoa đang khoe sắc.
 [Điểm Đến Mộng Mơ] Nimbus Sanctum!
 Trong chuyên mục [Điểm Đến Mộng Mơ] kỳ này, chúng ta sẽ đến với Nimbus Sanctum huyền ảo ẩn sâu trong Whisperwind Haven. Một điểm nhấn của chuyến du ngoạn Gondola đầy mê hoặc, biển mây từ lâu đã trở thành địa điểm không thể bỏ qua, quyến rũ du khách bằng những khung cảnh như trong mơ.
 Tuy nhiên, ít ai biết rằng Atrium of Reflections—thường xuất hiện trong những câu chuyện lãng mạn—không chỉ là sản phẩm của hư cấu, mà chính là tàn tích của ngọn tháp cao nhất của vương quốc Ragunna cổ đại. Để cứu dân tộc mình, Napoli đệ Nhị đã cầu khấn một phép màu, biến Dark Tide thành biển mây mà chúng ta thấy ngày nay.
 Những tàn tích bị lãng quên của Thị trấn Egla xưa giờ đây đã chìm sâu dưới biển mây.
-[Journey Chính Là Đích Đến] Hãy Bắt Đầu Ngay Hôm Nay!
+[Hành Trình Chính Là Đích Đến] Hãy Bắt Đầu Ngay Hôm Nay!
 Điều đáng chú ý là, mặc dù lý do vẫn chưa được làm rõ, mực nước của Nimbus Sanctum đã tăng dần trong thập kỷ qua, buộc cư dân Thị trấn Egla phải di dời lên vùng đất cao hơn ở phía bắc.
 Nơi đây từng là một vùng đất cằn cỗi, hoang sơ, rải rác những tảng đá lộ thiên, được biết đến với cái tên Whisperwind Barrens.
 Tuy nhiên, những con người tài giỏi của Thị trấn Egla đã bắt đầu xây dựng những chiếc cối xay gió hoạt động ngày đêm, bơm nước từ vùng thấp lên để tưới tiêu cho vùng đất phía trên. Nỗ lực của họ đã biến nơi hoang vu này thành Whisperwind Haven trù phú như ngày nay, nơi cây cối và hoa lá đua nhau khoe sắc trong làn gió.
-[Ký Ức Milestones] Tiếng Nói Của Du Othersh!
+[Ký Ức Cột Mốc] Tiếng Nói Của Du Khách!
 Cột Egla của các anh không cập nhật từ lễ hội Carnevale năm ngoái rồi. Toàn bài cũ lặp đi lặp lại thôi. Các anh không đủ tiền trả cho người viết à?
-Hay là chẳng ai quan tâm đến Thị trấn Egla nữa nhỉ? Thật sự sao? Tôi đoán đúng rồi à?
+Hay là chẳng ai quan tâm đến Thị trấn Egla nữa nhỉ? Thật sao? Tôi đoán đúng rồi à?
 (Một cuốn tiểu thuyết ngắn xuất bản cách đây mười năm.
-"Tác phẩm bán chạy gây sốc, bị Hội Light cấm đến ba lần!"
+"Tác phẩm bán chạy gây sốc, bị Hội Ánh Sáng cấm đến ba lần!"
 "Chỉ một phần mười độc giả thực sự hiểu được nó—bạn có nằm trong số đó?"
-"Bravo Sự châm biếm của Russellian vẫn sắc bén như xưa, dù đã bao năm trôi qua!"
+"Tuyệt vời! Sự châm biếm của Russellian vẫn sắc bén như xưa, dù đã bao năm trôi qua!"
 Đó là những lời giới thiệu của biên tập viên… Rõ ràng, cuốn sách này đã gây ra không ít tranh cãi cách đây một thập kỷ.)
 Xa tít ngoài khơi, nơi những cơn bão dữ dội hoành hành trên mặt biển đầy những rặng đá nhọn và những sinh vật khổng lồ của Solaris, có một nhóm đảo nhỏ bị lãng quên. Trên quần đảo này, những nền văn hóa hậu lưu đày vẫn còn nguyên vẻ kỳ diệu đến mức họ vẫn tin rằng một tư tưởng thống nhất là một ý tưởng khá hay ho. Những hòn đảo này—hay đúng hơn là đã từng có—một vấn đề: hầu hết người dân ở đây đều không hạnh phúc trong phần lớn thời gian.
 Sau khi nghỉ hưu, tôi vẫn thường nhớ về buổi chiều hôm đó, khi tôi và người bạn của mình gặp nhau lần đầu.
 Ford Percival. Anh ta là một người ngoài hành tinh.
-Ngày đầu tiên đặt chân đến Thị trấn Egla, anh ta đã ăn mười ổ bánh mì que mà không trả tiền. Trước khi các Harbinger Thần Thánh có thể trừng phạt anh ta vì tội trộm cắp, tôi đã nhanh chóng thanh toán nợ thay.
+Ngày đầu tiên đặt chân đến Thị trấn Egla, anh ta đã ăn mười ổ bánh mì que mà không trả tiền. Trước khi các Sứ Giả Thần Thánh có thể trừng phạt anh ta vì tội trộm cắp, tôi đã nhanh chóng thanh toán nợ thay.
 Kể từ lời cầu nguyện đó, Oracle of Mercy đã lang thang trong tâm trí tôi, tìm kiếm điều gì đó để kết nối—cho đến khi tôi gặp anh ta, kẻ ngoại bang tội nghiệp. Chắc hẳn anh ta đã đói lả.
-"Hi, tôi là Ford. Tôi là người ngoài hành tinh. Tôi đang phân tích vũ khí của cậu. Thành phần khá kỳ lạ."
+"Chào, tôi là Ford. Tôi là người ngoài hành tinh. Tôi đang phân tích vũ khí của cậu. Thành phần khá kỳ lạ."
 Anh ta nói sau khi tôi cứu. "Và đây là đâu?" anh ta tiếp tục.
 Người ngoài hành tinh á? Ồ, tôi đã từng nghe câu chuyện kiểu này từ một người tự xưng đến từ liên bang. Ông ta nói Solaris thực chất là một quả cà chua sống—một quả cà chua có thể xoay, thở, thậm chí nhảy múa. Còn người ngoài hành tinh, nghe đâu, đến từ những quả cà chua khác, dù còn sống hay đã chết.
 "Thị trấn Egla," tôi trả lời.
@@ -32710,33 +32684,33 @@
 (Tiếp tục)
 Sau khi nghe tôi giải thích, kẻ tự xưng là người ngoài hành tinh Ford dường như hoàn toàn bị mê hoặc bởi Cyclops. Cảm xúc của anh ta trở nên kích động đến mức ngồi phịch xuống đất, lẩm bẩm vài từ khó hiểu trong khi chỉ tay về phía những chiếc cối xay gió ở xa.
 Quả thật—dù đến từ đâu, dù đến từ "quả cà chua" nào, bất cứ ai nhìn thấy khung cảnh của Egla đều không thể không yêu mến những áng văn chương hiệp sĩ.
-Vậy nên tôi đứng thẳng người, tiến ba bước về phía trước, chỉnh lại chiếc cà vạt không tồn tại, rồi giải thích một cách lịch thiệp: "Chính xác! That's right! Ngày xưa, một hiệp sĩ chính nghĩa đã dẫn dắt chúng tôi đánh bại gã khổng lồ. Previous đó, tất cả người dân và Echoes ở Thị trấn Egla đều phải chạy lên vùng đất cao ở phía nam, trốn tránh mối đe dọa từ gã khổng lồ. Giờ đây, kẻ áp bức đó đã nằm yên dưới biển hoa. Chúng tôi xây dựng những chiếc cối xay gió hùng vĩ để tưới tiêu cho hoa màu và đồng ruộng, và đặt tên quê hương cũ là Briareos, để tưởng nhớ chiến công hiển hách của vị hiệp sĩ đó!"
+Vậy nên tôi đứng thẳng người, tiến ba bước về phía trước, chỉnh lại chiếc cà vạt không tồn tại, rồi giải thích một cách lịch thiệp: "Chính xác! Đúng vậy! Ngày xưa, một hiệp sĩ chính nghĩa đã dẫn dắt chúng tôi đánh bại gã khổng lồ. Trước đó, tất cả người dân và Echo ở Thị trấn Egla đều phải chạy lên vùng đất cao ở phía nam, trốn tránh mối đe dọa từ gã khổng lồ. Giờ đây, kẻ áp bức đó đã nằm yên dưới biển hoa. Chúng tôi xây dựng những chiếc cối xay gió hùng vĩ để tưới tiêu cho hoa màu và đồng ruộng, và đặt tên quê hương cũ là Briareos, để tưởng nhớ chiến công hiển hách của vị hiệp sĩ đó!"
 Sau khi nghe tôi nói, Ford ngồi bất động trên mặt đất, như thể mười nghìn con Cetus the Tidebreaker đã gầm lên cùng lúc, phá vỡ mọi nhận thức của anh ta.
 Sau một hồi im lặng, anh ta hỏi tôi với vẻ hoài nghi: "Ở đây vẫn còn hiệp sĩ à?"
 Anh ta vừa hỏi tôi điều gì vậy?
 Ca ngợi bậc Đế Vương!
-Cuối cùng tôi cũng có thể đưa ra câu trả lời xếp hạng số 1 trong Top 10 Khoảnh Khắc Thỏa Mãn Yi Đối Với Người Dân Egla.
-Với vẻ mặt trang nghiêm như các Tu Sĩ của Hội Light, tôi mường tượng một vầng hào quang cao quý trên đầu, mường tượng vị Đế Vương toàn năng dang cánh trước mặt, mường tượng mình đội vòng nguyệt quế tại lễ hội Carnevale, mường tượng đứng trong nhà thờ lớn, cầm kiếm trong lễ phong hiệp sĩ, tận hưởng ánh mắt ngưỡng mộ của các quý tộc Ragunna!
+Cuối cùng tôi cũng có thể đưa ra câu trả lời xếp hạng số 1 trong Top 10 Khoảnh Khắc Thỏa Mãn Nhất Đối Với Người Dân Egla.
+Với vẻ mặt trang nghiêm như các Tu Sĩ của Hội Ánh Sáng, tôi mường tượng một vầng hào quang cao quý trên đầu, mường tượng vị Đế Vương toàn năng dang cánh trước mặt, mường tượng mình đội vòng nguyệt quế tại lễ hội Carnevale, mường tượng đứng trong nhà thờ lớn, cầm kiếm trong lễ phong hiệp sĩ, tận hưởng ánh mắt ngưỡng mộ của các quý tộc Ragunna!
 Tôi trả lời, nhấn mạnh từng chữ một:
 "TẤT NHIÊN—"
 "Tuy nhiên, có quá nhiều kẻ ngoại bang tìm kiếm con đường hiệp sĩ. Cậu có đủ tự tin để chấp nhận thử thách không?"
 Kẻ tự xưng là người ngoài hành tinh tên Ford, với Tacet Mark nhấp nháy đầy hứng khởi, nhanh chóng túm lấy bắp chân tôi và lắc lia lịa, như thể bám vào một khúc gỗ giữa dòng nước xoáy. Anh ta kêu lên: "Tôi có! Tôi có! Xin hãy dẫn tôi đến gặp vị hiệp sĩ huyền thoại! Chỉ cần tôi có thể trở về hành tinh Russel và cứu quê hương mình, tôi sẵn sàng trả bất cứ giá nào!"
 (Các chương thử thách kết thúc tại đây. Vui lòng mua để tiếp tục đọc.)
 (Một bài viết về truyền thống ẩm thực của Ragunna.)
-[Bí Kíp Đỉnh Cao Từ Chef Hàng Đầu]
-Hãy thử tưởng tượng bạn hỏi bất kỳ ai trên đường phố Ragunna: "Home hàng nào ngon nhất ở Ragunna?"
+[Bí Kíp Đỉnh Cao Từ Đầu Bếp Hàng Đầu]
+Hãy thử tưởng tượng bạn hỏi bất kỳ ai trên đường phố Ragunna: "Nhà hàng nào ngon nhất ở Ragunna?"
 Sáu trên mười người sẽ trả lời: "Trattoria Margherita!" Ba người sẽ chỉ về phía nhà hàng gia đình ở trung tâm thành phố, và người cuối cùng sẽ nói: "Chính là nơi đầu bếp đuôi mềm làm việc!"
-That's right! Đó chính là sức ảnh hưởng của Trattoria Margherita ở Ragunna!
-Bravo
+Đúng vậy! Đó chính là sức ảnh hưởng của Trattoria Margherita ở Ragunna!
+Tuyệt vời!
 Nhưng điều nhiều người không biết là Trattoria Margherita thực chất là một nhà hàng gia đình lấy cảm hứng từ ẩm thực truyền thống Ragunna. Theo điều tra của chúng tôi, Thị trấn Egla vẫn còn bảo tồn truyền thống ẩm thực cổ điển này cho đến ngày nay. Để giữ được hương vị đặc biệt cho các món ăn của mình, cô Margherita thậm chí còn dành thời gian nghỉ để tự mình đi thu thập nguyên liệu ở Thị trấn Egla hoặc quần đảo Riccioli!
 Giờ thì bạn có thể thắc mắc: "Sao cơ? Tôi hiểu tại sao cô Margherita lại đến quần đảo Riccioli để thu hoạch cá, nhưng Thị trấn Egla á? Chẳng phải đó là một thị trấn hẻo lánh sao? Và ẩm thực của Egla có thể gọi là ẩm thực Ragunna được không?"
-Quả thật, cuộc sống ở Egla không sôi động như ở thủ đô Ragunna nhộn nhịp. Người dân ở đó sống yên bình, theo nhịp điệu của thiên nhiên. Mailơng mại và hậu cần của thị trấn đều gắn liền với Thành phố Ragunna. Người dân thức dậy cùng gió và nghỉ ngơi theo gió, sống một cuộc đời gắn liền với cối xay gió, cánh đồng lúa mì và đồng cỏ.
+Quả thật, cuộc sống ở Egla không sôi động như ở thủ đô Ragunna nhộn nhịp. Người dân ở đó sống yên bình, theo nhịp điệu của thiên nhiên. Thương mại và hậu cần của thị trấn đều gắn liền với Thành phố Ragunna. Người dân thức dậy cùng gió và nghỉ ngơi theo gió, sống một cuộc đời gắn liền với cối xay gió, cánh đồng lúa mì và đồng cỏ.
 Nhưng chính vì thế, qua hàng trăm năm, ẩm thực của Egla vẫn không hề thay đổi. Ở đây, hương vị nguyên bản và kỹ thuật nấu nướng của Ragunna vẫn được bảo tồn—sử dụng cối xay gió để chế biến nông sản và nấu ăn theo cách truyền thống.
 "Bằng cách này, nguyên liệu và món ăn trở nên đặc biệt quý giá! Phô mai làm từ sữa bò địa phương béo ngậy, thịt thì mềm và đậm đà! Đó chính là thức ăn hoàn hảo để no bụng!"
 Cô Margherita nhận xét trong cuộc phỏng vấn của chúng tôi.
-[Ý Kiến Từ Othersh Invite Special]
-Cựu Harbinger Thuế của Hội Light: Ẩm thực truyền thống là sự tưởng nhớ về quá khứ của Rinascita. Quên nó đi là phản bội di sản của chúng ta!
-Orlando Home Ẩm Thực: Ông già lúc nãy nghe như đang đọc khẩu hiệu vậy! Ẩm thực truyền thống gì chứ? Cái bánh mì ở thị trấn ông cứng như vũ khí giết người ấy!)</t>
+[Ý Kiến Từ Khách Mời Đặc Biệt]
+Cựu Sứ Giả Thuế của Hội Ánh Sáng: Ẩm thực truyền thống là sự tưởng nhớ về quá khứ của Rinascita. Quên nó đi là phản bội di sản của chúng ta!
+Orlando Nhà Ẩm Thực: Ông già lúc nãy nghe như đang đọc khẩu hiệu vậy! Ẩm thực truyền thống gì chứ? Cái bánh mì ở thị trấn ông cứng như vũ khí giết người ấy!)</t>
         </is>
       </c>
     </row>
@@ -32829,33 +32803,33 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Record Của Nguyên Cố Vấn Hội Đồng (Phần I)
+          <t>Ghi Chép Của Nguyên Cố Vấn Hội Đồng (Phần I)
 ...
-Lúc bình minh, The Primus và ta đứng đó để tiễn biệt những Pilgrim's Sail khi chúng chuẩn bị lên đường. Cả đám đông lẫn các tín đồ đều ngước nhìn với lòng thành kính khi những tín đồ sùng đạo bước lên tàu. Chỉ những người ngoan đạo và dũng cảm nhất mới được chọn để lên những Pilgrim's Sail, hướng về nơi biển xa để gặp gỡ Sentinel.
+Lúc bình minh, Primus và ta đứng đó để tiễn biệt những Cánh Buồm Hành Hương khi chúng chuẩn bị lên đường. Cả đám đông lẫn các tín đồ đều ngước nhìn với lòng thành kính khi những tín đồ sùng đạo bước lên tàu. Chỉ những người ngoan đạo và dũng cảm nhất mới được chọn để lên những Cánh Buồm Hành Hương, hướng về nơi biển xa để gặp gỡ Sentinel.
 Qua vô số kỷ nguyên, Sentinel Imperator hiếm khi lưu lại một chỗ, thay vào đó luôn lênh đênh trên biển cả, trợ giúp những con tàu trên hành trình của họ. Ánh sáng dẫn đường của Sentinel luôn soi sáng những kẻ lạc lối trên sóng nước, giúp họ tìm về quê hương hoặc tìm kiếm vùng đất mới để định cư. Giáo Đoàn tin rằng đối diện với bão tố và thủy triều để tìm kiếm tiếng gọi thiêng liêng của Sentinel là một trong những vinh dự lớn lao nhất mà một linh hồn có thể khao khát.
 Nhưng chỉ những ai từng trải mới hiểu được cái giá khủng khiếp của mỗi chuyến hành hương. Thuế má và lương thảo được lấy từ dân đen, thợ thuyền và thủy thủ bị trưng dụng từ các gia đình danh giá, thuyền trưởng và thuyền phó kỳ cựu được thuê với giá đắt đỏ. Tất cả những ai dấn thân vào biển cả hiểm nguy đều sùng đạo, nhưng chỉ những người thực sự được Sentinel ban phước mới trở về với vinh quang và danh dự như lời hứa. Nhìn lại lịch sử, số phận may mắn như vậy chỉ đếm trên đầu ngón tay.
-Ta chưa bao giờ nghi ngờ mục đích của cuộc hành hương. Điều duy nhất ta lo lắng là cái giá quá lớn mà nó đòi hỏi. Liệu chúng ta có thể, với lương tâm trong sáng, để những tín đồ mộ đạo này dấn thân vào một hành trình vắt kiệt cả thể xác lẫn tinh thần? Còn vị The Primus mới của chúng ta... ông ta nghĩ gì về chuyện này?
-Ta quay sang nhìn, ngạc nhiên khi thấy khuôn mặt của người bạn học cũ từ chủng viện, Lãnh Unclea Fenrico, giờ đây bị che phủ bởi một bóng tối kỳ lạ.
+Ta chưa bao giờ nghi ngờ mục đích của cuộc hành hương. Điều duy nhất ta lo lắng là cái giá quá lớn mà nó đòi hỏi. Liệu chúng ta có thể, với lương tâm trong sáng, để những tín đồ mộ đạo này dấn thân vào một hành trình vắt kiệt cả thể xác lẫn tinh thần? Còn vị Primus mới của chúng ta... ông ta nghĩ gì về chuyện này?
+Ta quay sang nhìn, ngạc nhiên khi thấy khuôn mặt của người bạn học cũ từ chủng viện, Lãnh Chúa Fenrico, giờ đây bị che phủ bởi một bóng tối kỳ lạ.
 ...
-Record Của Nguyên Cố Vấn Hội Đồng (Phần II)
+Ghi Chép Của Nguyên Cố Vấn Hội Đồng (Phần II)
 ...
-Do sao mọi chuyện lại thành ra thế này? Sau một đêm trắng, ta lui vào căn phòng cầu nguyện hiu quạnh, tìm kiếm sự an ủi khi đặt lời thú tội trước Sentinel Imperator. Bàn tay ta run rẩy khi viết những dòng này.
-Có một thời, Giáo Đoàn ngừng tổ chức những chuyến hành hương quy mô lớn, và gánh nặng thuế má được dỡ bỏ. Dù người dân Ragunna vẫn tôn kính lòng thành của những ai từng tìm kiếm Sentinel nơi biển xa, những Pilgrim's Sail đã trở thành di tích của quá khứ. Nhưng mọi thứ thay đổi sau vụ thảm sát Carnevale... Không, thực ra sự thay đổi đã bắt đầu từ trước đó...
-Ta vẫn nhớ như in khi The Primus ra lệnh sửa sai, và ta đã ngoan ngoãn ghi chép lại: Giáo Đoàn sẽ đưa những kẻ vi phạm giáo lý lên những Pilgrim's Sail, tước bỏ mọi danh tính chính thức và buộc họ trở lại con đường hành hương. Ai có thể ngờ rằng một hành động từng tượng trưng cho đức tin lại trở thành hình phạt?
-"Quyền trừng phạt và giáo huấn sẽ được trao lại cho Sentinel," The Primus tuyên bố trước đám đông. "Những kẻ phạm tội, nếu chân thành sám hối trên hành trình, sẽ được tha thứ mọi lỗi lầm và nhận được sự tha thứ của Sentinel khi kết thúc chuyến đi."
-Nhưng chẳng ai biết liệu những kẻ phạm tội có thực sự được cứu rỗi hay không, vì chưa từng có ai trở về từ chuyến hành hương ấy. "Những kẻ làm điều ngu ngốc sẽ bị đưa lên Pilgrim's Sail"—điều này đã trở thành luật bất di bất dịch của Home Tù Giáo Đoàn. Những kẻ phá hoại tượng thánh, tín đồ bất trung xuyên tạc giáo lý, thậm chí cả những diễn viên kịch chế giễu—tất cả đều bị kết án lên Pilgrim's Sail vì tội báng bổ. Gần đây, thậm chí cả những gương mặt quen thuộc, những người từng công khai chất vấn các sắc lệnh của The Primus, cũng đã gia nhập hàng ngũ ấy.
-Ta có thể thề bằng danh dự và đức tin của họ, nhưng ta đã đứng nhìn họ bị đưa lên Pilgrim's Sail mà không làm gì. Không, không còn phù hợp để gọi chúng là Pilgrim's Sail nữa. Dân chúng đã đặt cho chúng một cái tên thích hợp hơn—Những Cánh Buồm Ngu Ngốc, nơi chất đầy những kẻ đã làm điều dại dột.
-Ôi, The Primus Fenrico... Đây có phải là thế giới trong mơ mà ngài từng nhiệt huyết nói đến trong chủng viện?
+Làm sao mọi chuyện lại thành ra thế này? Sau một đêm trắng, ta lui vào căn phòng cầu nguyện hiu quạnh, tìm kiếm sự an ủi khi đặt lời thú tội trước Sentinel Imperator. Bàn tay ta run rẩy khi viết những dòng này.
+Có một thời, Giáo Đoàn ngừng tổ chức những chuyến hành hương quy mô lớn, và gánh nặng thuế má được dỡ bỏ. Dù người dân Ragunna vẫn tôn kính lòng thành của những ai từng tìm kiếm Sentinel nơi biển xa, những Cánh Buồm Hành Hương đã trở thành di tích của quá khứ. Nhưng mọi thứ thay đổi sau vụ thảm sát Carnevale... Không, thực ra sự thay đổi đã bắt đầu từ trước đó...
+Ta vẫn nhớ như in khi Primus ra lệnh sửa sai, và ta đã ngoan ngoãn ghi chép lại: Giáo Đoàn sẽ đưa những kẻ vi phạm giáo lý lên những Cánh Buồm Hành Hương, tước bỏ mọi danh tính chính thức và buộc họ trở lại con đường hành hương. Ai có thể ngờ rằng một hành động từng tượng trưng cho đức tin lại trở thành hình phạt?
+"Quyền trừng phạt và giáo huấn sẽ được trao lại cho Sentinel," Primus tuyên bố trước đám đông. "Những kẻ phạm tội, nếu chân thành sám hối trên hành trình, sẽ được tha thứ mọi lỗi lầm và nhận được sự tha thứ của Sentinel khi kết thúc chuyến đi."
+Nhưng chẳng ai biết liệu những kẻ phạm tội có thực sự được cứu rỗi hay không, vì chưa từng có ai trở về từ chuyến hành hương ấy. "Những kẻ làm điều ngu ngốc sẽ bị đưa lên Cánh Buồm Hành Hương"—điều này đã trở thành luật bất di bất dịch của Nhà Tù Giáo Đoàn. Những kẻ phá hoại tượng thánh, tín đồ bất trung xuyên tạc giáo lý, thậm chí cả những diễn viên kịch chế giễu—tất cả đều bị kết án lên Cánh Buồm Hành Hương vì tội báng bổ. Gần đây, thậm chí cả những gương mặt quen thuộc, những người từng công khai chất vấn các sắc lệnh của Primus, cũng đã gia nhập hàng ngũ ấy.
+Ta có thể thề bằng danh dự và đức tin của họ, nhưng ta đã đứng nhìn họ bị đưa lên Cánh Buồm Hành Hương mà không làm gì. Không, không còn phù hợp để gọi chúng là Cánh Buồm Hành Hương nữa. Dân chúng đã đặt cho chúng một cái tên thích hợp hơn—Những Cánh Buồm Ngu Ngốc, nơi chất đầy những kẻ đã làm điều dại dột.
+Ôi, Primus Fenrico... Đây có phải là thế giới trong mơ mà ngài từng nhiệt huyết nói đến trong chủng viện?
 ...
-Record Của Nguyên Cố Vấn Hội Đồng (Phần III)
+Ghi Chép Của Nguyên Cố Vấn Hội Đồng (Phần III)
 ...
-Ta ngạc nhiên vì mình lại bình tĩnh đến thế khi nghe bản án từ Home Tù Giáo Đoàn. Có lẽ trái tim ta giờ đây đã lạnh lẽo như một xác chết.
-Lúc bình minh, như bao người khác trước ta, ta bị các Đao Phủ áp giải lên một con tàu Cánh Buồm Ngu Ngốc. Trước khi tàu nhổ neo, ta quay lại nhìn bến cảng, chỉ để thấy The Primus vắng mặt. Đúng như dự đoán, kẻ đó, giờ đây nắm quyền lực tuyệt đối trong Giáo Đoàn, chẳng cần bận tâm đến một kẻ ngu ngốc bị tước bỏ danh tính.
-Những Cánh Buồm Ngu Ngốc chẳng giống chút nào với những Pilgrim's Sail ngày xưa. Nơi đây không còn những boong tàu rộng rãi, bằng phẳng hay những cánh buồm được bảo dưỡng cẩn thận. Thay vào đó, tất cả những gì ta thấy chỉ là những tấm ván mục nát, ốc vít lỏng lẻo và cột buồm nứt vỡ. Những cabin chật hẹp rõ ràng thiếu thốn lương thực và nước ngọt. Ta nhìn đăm đăm những người hành hương khác quanh mình. Hiện tại, chúng ta vẫn còn giữ được chút thể diện và kiềm chế, nhưng ta biết rằng, chẳng bao lâu nữa, con tàu này sẽ chỉ còn là một cái lồng chứa đầy những dục vọng điên cuồng.
+Ta ngạc nhiên vì mình lại bình tĩnh đến thế khi nghe bản án từ Nhà Tù Giáo Đoàn. Có lẽ trái tim ta giờ đây đã lạnh lẽo như một xác chết.
+Lúc bình minh, như bao người khác trước ta, ta bị các Đao Phủ áp giải lên một con tàu Cánh Buồm Ngu Ngốc. Trước khi tàu nhổ neo, ta quay lại nhìn bến cảng, chỉ để thấy Primus vắng mặt. Đúng như dự đoán, kẻ đó, giờ đây nắm quyền lực tuyệt đối trong Giáo Đoàn, chẳng cần bận tâm đến một kẻ ngu ngốc bị tước bỏ danh tính.
+Những Cánh Buồm Ngu Ngốc chẳng giống chút nào với những Cánh Buồm Hành Hương ngày xưa. Nơi đây không còn những boong tàu rộng rãi, bằng phẳng hay những cánh buồm được bảo dưỡng cẩn thận. Thay vào đó, tất cả những gì ta thấy chỉ là những tấm ván mục nát, ốc vít lỏng lẻo và cột buồm nứt vỡ. Những cabin chật hẹp rõ ràng thiếu thốn lương thực và nước ngọt. Ta nhìn đăm đăm những người hành hương khác quanh mình. Hiện tại, chúng ta vẫn còn giữ được chút thể diện và kiềm chế, nhưng ta biết rằng, chẳng bao lâu nữa, con tàu này sẽ chỉ còn là một cái lồng chứa đầy những dục vọng điên cuồng.
 Và ngay cả khi chúng ta đến được cái gọi là đích đến, thì điều gì đang chờ đợi chúng ta ở đó?
-Ta từng đọc những báo cáo điều tra do các tín đồ lưu vong gửi về. Cái gọi là Bến Sám Hối, chìm trong sương mù, chất đầy xác tàu của những Pilgrim's Sail. Trong những chuyến hải trình định mệnh ấy, những kẻ ngu ngốc đương đầu với bão tố chưa bao giờ gặp được Sentinel. Thay vào đó, bị dòng hải lưu cuốn đi, họ bị đẩy vào bờ hòn đảo đó, nơi ánh sáng lân tinh ma quái hòa quyện với bầu không khí chết chóc không thể nhầm lẫn. Ta thậm chí còn nghe đồn về một thứ gì đó kinh hoàng hơn nhiều đang ẩn nấp ở đó, và "Lửa Phán Xét"—một sức mạnh đáng sợ đến nỗi ngay cả Hội Đồng Cơ Mật cũng không dám nhắc đến.
+Ta từng đọc những báo cáo điều tra do các tín đồ lưu vong gửi về. Cái gọi là Bến Sám Hối, chìm trong sương mù, chất đầy xác tàu của những Cánh Buồm Hành Hương. Trong những chuyến hải trình định mệnh ấy, những kẻ ngu ngốc đương đầu với bão tố chưa bao giờ gặp được Sentinel. Thay vào đó, bị dòng hải lưu cuốn đi, họ bị đẩy vào bờ hòn đảo đó, nơi ánh sáng lân tinh ma quái hòa quyện với bầu không khí chết chóc không thể nhầm lẫn. Ta thậm chí còn nghe đồn về một thứ gì đó kinh hoàng hơn nhiều đang ẩn nấp ở đó, và "Lửa Phán Xét"—một sức mạnh đáng sợ đến nỗi ngay cả Hội Đồng Cơ Mật cũng không dám nhắc đến.
 ...
-Lương thực sắp cạn kiệt... Night qua, lại có người mất kiểm soát, cố nhốt mình trong cabin để tích trữ số đồ ăn ít ỏi còn lại...
+Lương thực sắp cạn kiệt... Đêm qua, lại có người mất kiểm soát, cố nhốt mình trong cabin để tích trữ số đồ ăn ít ỏi còn lại...
 Ôi, vị Imperator vĩ đại, nếu Người có thể nghe thấy lời cầu nguyện của ta, xin hãy ban cho chúng ta lòng thương xót cuối cùng qua một cơn bão. Xin hãy giải thoát chúng ta khỏi nỗi thống khổ này, và cho chúng ta... được yên nghỉ.
 (Phần còn lại của ghi chép đã bị nước biển làm mờ và không thể đọc được.)</t>
         </is>
@@ -32949,33 +32923,17 @@
       <c r="M422" t="inlineStr">
         <is>
           <t xml:space="preserve">
-Bản Record Của Kẻ Phạm Tội (Phần I)
-Trong thời đại cổ xưa, rất lâu trước khi Ragunna được thành lập, những vùng biển xa xôi của Rinascita là Vương Guo Ngàn Đảo.
-Enter thời điểm đó, gia tộc Fisalia đã rất thành thạo trong việc đi biển. Chúng tôi chiết xuất chất độc và dược liệu từ các loài thực vật biển sâu, khai thác nguồn tài nguyên dưới nước rộng lớn, và tận hưởng sự giàu có cùng danh tiếng lan rộng. Sau đó, với sự tấn công của Lament, nền văn minh quần đảo đứng bên bờ vực diệt vong và gia tộc chúng tôi trở thành một trong những người sáng lập của Ark, bắt đầu cuộc hành trình tìm kiếm một vùng đất định cư mới.
-Hành trình vượt biển đầy hiểm nguy. Các hạm đội của Ark bị nuốt chửng bởi sương mù dày đặc hoặc bị xé nát bởi những cơn bão dữ dội. Tuy nhiên, chiếc Ark của gia tộc chúng tôi, được dẫn dắt bởi một giọng nói từ thiên đường, đã đưa hạm đội đến một quần đảo tươi tốt, theo ánh sáng mờ nhạt của một ngọn hải đăng xa xôi. Một trong những hòn đảo đó sau này trở thành Ragunna như ngày nay.
-Ragunna mới thành lập vẫn còn trong tình trạng bất ổn. Để củng cố sự thống trị của gia tộc, tộc trưởng của chúng tôi tuyên bố rằng sự hiện thân của ▇▇▇▇ là biểu tượng của đức tin biển sâu và là sự đáp lại từ thần linh biển cả đối với lòng thành kính của chúng tôi. Tuyên bố này đã thành công. Khi số lượng tín đồ tăng lên, sự ổn định trong quyền lực của gia tộc chúng tôi cũng tăng theo.
-Sau này, một số ngư dân khẳng định rằng họ đã được ▇▇▇▇ trợ giúp trong các chuyến đi đánh cá. Thực thể này, từ lâu được biết đến với cái tên Đấng Khổng Lồ, đã tồn tại từ ngàn đời. Bóng dáng của nó dưới biển đã dẫn dắt ngư dân và hạm đội của Ragunna, giúp họ vượt qua bão tố và mang về những mùa màng bội thu hơn trước.
-&lt;i&gt;The Fisalia Family từng là những người cai trị đầu tiên của Ragunna, và chúng tôi cũng đặt nền móng đức tin cho Order. Thế nhưng, tại sao các đời tộc trưởng lại chọn cách che giấu lịch sử này?&lt;/i&gt;
-&lt;i&gt;Tại sao tôi không thể nhớ tên của Ngài? Đáng nguyền rủa thay, vết thương... nó lại đau nhói. Có điều gì đó không ổn với không khí... Tôi phải tìm một nơi an toàn hơn.&lt;/i&gt;
-&lt;i&gt;Soldiers sẽ không bao giờ nghĩ đến việc tìm tôi trong tòa tháp. Tôi phải ghi lại lịch sử bí mật này... trước khi nó hoàn toàn biến mất khỏi tâm trí tôi...&lt;/i&gt;
-Bản Record Của Kẻ Phạm Tội (Phần II)
-Những ngư dân gọi cái bóng dưới biển là ▇▇▇▇, và họ sẽ kêu gọi tên thiêng liêng của nó để nhận được sự trợ giúp. Những phép màu nhỏ bắt đầu tích lũy, tạo thành một dòng chảy đức tin mạnh mẽ. Dân chúng ngày càng tin rằng Đấng Khổng Lồ chính là ▇▇▇▇.
-Khi gia tộc bắt đầu điều tra, họ kinh ngạc phát hiện ra rằng những sự kiện kỳ diệu này khác xa so với những gì được ghi chép trong quá khứ. Vậy, hình dạng thực sự của Đấng Khổng Lồ mà dân chúng tôn thờ là gì? Và chính xác thì đối tượng thực sự của lòng thành kính của chúng ta là gì? Đức tin bí ẩn này đang âm thầm định hình lại lịch sử của Ragunna, và thậm chí còn đe dọa đến sự kiểm soát của gia tộc chúng tôi đối với Order of the Deep.
-Chỉ có những bậc tiền bối của Ark và các tộc trưởng của gia tộc chúng tôi mới biết rằng ▇▇▇▇ nên là hình dạng thực sự của ▇▇. Tuy nhiên, với sự truyền bá của Order, dân chúng không biết sự thật, bắt đầu đặt niềm tin nhiều hơn vào ▇▇▇▇. Trong khi đó, những lời đồn đại lan truyền rằng hình dạng thực sự của ▇▇▇▇ là một vị thần giống cá. Điều kỳ lạ hơn là những người nghe thấy những lời đồn này bắt đầu mơ thấy ▇▇▇▇ dưới hình dạng ▇▇.
-&lt;i&gt;Liệu văn bản này có thực sự là bản ghi chép mà tôi từng đọc trong phòng bí mật của tộc trưởng không? Tôi có một cảm giác bất an rằng đôi tay mình đang tự viết ra lịch sử về ▇▇▇▇.&lt;/i&gt;
-&lt;i&gt;À, giờ tôi nhớ rồi... Đúng vậy, ngay cả tôi, người chưa bao giờ ra khơi, cũng bị cuốn vào giấc mơ đó khi đang chạy trốn. Dưới mặt biển yên tĩnh, một bóng đen khổng lồ ẩn hiện, và chiếc thuyền đánh cá của tôi chỉ như một chiếc thuyền nan trước nó...&lt;/i&gt;
-&lt;i&gt;Không thể nào... Hình dạng bất khiết, báng bổ đó không thể là đối tượng của đức tin của tôi suốt thời gian qua. Tôi phải tiết lộ sự thật cho thế giới.&lt;/i&gt;
-Bản Record Của Kẻ Phạm Tội (Phần III)
-Sau cái chết của Napoli Đệ Nhị, Order of the Deep đã bầu ra một The Primus mới. Sự lan truyền của đức tin vượt xa mọi tầm với trước đây. Tuy nhiên, những giáo lý được các Acolyte tuyên bố đã bị ô nhiễm bởi một màn sương đen tối. Mọi thứ liên quan đến ▇▇▇▇ bắt đầu bị bóp méo—những bức tượng, những giai thoại, thậm chí cả những câu tục ngữ...
-&lt;i&gt;Chưa ai từng nghi ngờ về ảo giác tập thể này. Chưa ai từng chống lại sự tan biến của hình dạng, vì "mỗi giọt nước cuối cùng rồi cũng sẽ trở về biển cả."&lt;/i&gt;
-&lt;i&gt;Ai đang nói trong "đầu" trên cổ tôi? Im đi, đồ báng bổ! Bút của tôi đâu? Không, nó đang ở trong tay tôi. Nhưng đây có thực sự là tay tôi không? Tại sao lại có... máu đen chảy ra từ nó?&lt;/i&gt;
-Previous những thay đổi này, gia tộc chúng tôi vẫn im lặng một cách kỳ lạ, thậm chí làm ngơ trước việc Order vượt khỏi tầm kiểm soát. Nhiều thành viên trong gia tộc Fisalia bị hành hạ bởi những cơn ác mộng kỳ lạ... Họ đều nhìn thấy bóng cá khổng lồ dưới biển và tỉnh dậy trong kinh hoàng, la hét.
-(Văn bản trở nên không thể đọc được, và giấy bị cào xước với những ký hiệu không rõ nghĩa.)
-&lt;i&gt;Tôi nghe thấy những "bài thánh ca" tuôn ra từ miệng mình. Sounds của những vết cào ướt át vang lên trên sàn nhà. Dòng máu cổ xưa vẫn chảy trong tôi. NGÀI đang ở đây... NGÀI ở khắp mọi nơi...&lt;/i&gt;
-Một số người rời bỏ gia tộc, trở thành tín đồ trung thành của Order. Một số khác đến Septimont và không bao giờ nhắc đến đức tin nữa, trong khi số khác định cư gần cảng biển, dần xa rời các thế lực khác. Ôi, những Fisalia tội nghiệp—từng hùng mạnh, từng được bao bọc bởi đồng minh—giờ chỉ còn lại thế này.
-&lt;i&gt;Hãy vứt bỏ những nỗi sợ hãi bẩm sinh, và tôi không còn nghi ngờ rằng Ngài chính là ▇▇▇▇, và ▇▇▇▇ chính là Ngài—họ là một và giống nhau. Trong sâu thẳm lý trí, tôi cảm nhận được một niềm vui không thể tả.&lt;/i&gt;
-&lt;i&gt;Ôi, Fisalia vinh quang của ta, bóng dáng của dân tộc ta đang đến gần, dẫn dắt ta ra biển sâu.&lt;/i&gt;
-&lt;i&gt;Ngài calling tôi. Nguyện ca tụng ▇▇▇▇.&lt;/i&gt;</t>
+Biên Bản Kẻ Phạm Tội (Phần III)
+Sau cái chết của Napoli Đệ Nhị, Giáo Đoàn Biển Sâu đã bầu ra một Primus mới. Sự lan truyền của đức tin vượt xa mọi giới hạn trước đây. Thế nhưng, những giáo lý mà các Acolyte truyền bá lại bị bao phủ bởi màn sương đen tối. Mọi thứ liên quan đến ▇▇▇▇ bắt đầu bị bóp méo—tượng đài, giai thoại, thậm chí cả những câu tục ngữ...
+&lt;i&gt;Chẳng ai nghi ngờ về ảo giác tập thể này. Chẳng ai chống lại sự tan biến của hình dạng, vì "mỗi giọt nước rốt cuộc cũng sẽ trở về biển cả."&lt;/i&gt;
+&lt;i&gt;Ai đang nói trong "đầu" trên cổ ta vậy? Im đi, đồ báng bổ! Bút của ta đâu? Không, nó đang ở trong tay ta. Nhưng đây có thật là tay ta không? Tại sao lại có... máu đen chảy ra từ nó?&lt;/i&gt;
+Trước những thay đổi này, gia tộc ta vẫn im lặng đến đáng sợ, thậm chí làm ngơ trước sự mất kiểm soát của Giáo Đoàn. Nhiều thành viên trong gia tộc Fisalia bị hành hạ bởi những cơn ác mộng kỳ lạ... Họ đều thấy bóng cá khổng lồ dưới lòng biển và tỉnh dậy trong kinh hoàng, gào thét.
+(Văn bản trở nên khó đọc, giấy bị cào xước với những ký hiệu không rõ nghĩa.)
+&lt;i&gt;Ta nghe thấy "thánh ca" tuôn ra từ miệng mình. Âm thanh cào xé ướt át vang trên sàn. Máu cổ xưa vẫn chảy trong ta. NÓ ở đây... NÓ ở khắp nơi...&lt;/i&gt;
+Một số rời bỏ gia tộc, trở thành tín đồ cuồng nhiệt của Giáo Đoàn. Một số khác đến Septimont và không bao giờ nhắc đến đức tin nữa, số còn lại định cư gần cảng biển, dần xa lánh các thế lực khác. Ôi, những Fisalia tội nghiệp—từng hùng mạnh, từng được bao bọc bởi đồng minh—giờ chỉ còn lại thế này.
+&lt;i&gt;Hãy vứt bỏ nỗi sợ hãi bẩm sinh, và ta không còn nghi ngờ gì nữa—NÓ chính là ▇▇▇▇, và ▇▇▇▇ chính là NÓ—chúng là một. Trong sâu thẳm lý trí, ta cảm nhận một niềm vui không thể diễn tả.&lt;/i&gt;
+&lt;i&gt;Ôi Fisalia vinh quang của ta, bóng dáng của con dân ta đang đến gần, dẫn ta về biển sâu.&lt;/i&gt;
+&lt;i&gt;NÓ đang gọi ta. Ngợi ca ▇▇▇▇.&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -33069,28 +33027,28 @@
         <is>
           <t>Trích từ &lt;i&gt;Cây Búa Dị Giáo&lt;/i&gt;
 (Tập truyền đơn đưa ra một số quan điểm cực đoan, dường như phản ánh lý thuyết của một trường phái tư tưởng cực đoan.)
-Fu thủy là gì? Và bản chất thực sự của nó là gì?
-Sức mạnh Synergy do Synergy Giả sử dụng được biết đến như một phước lành từ Sentinel Imperator. Những tín đồ trung thành của Giáo Đoàn được ban cho phước lành này khi tuân theo giáo lý, cho phép họ dẫn truyền sức mạnh thần thánh qua thân xác phàm trần. Tuy nhiên, phù thủy sinh ra từ những dục vọng hão huyền—những linh hồn bất tín, bị Leviathan dụ dỗ, lập giao ước để thực hành những nghệ thuật bị cấm. Bằng cách đó, chúng từ bỏ phước lành thần thánh được ban tặng từ khi sinh ra và vứt bỏ nhân tính, biến thành phù thủy tìm cách làm ô uế cõi trần bằng sức mạnh tà ác.
-Đấng Tối Cao đã tạo dựng thế giới này, và tất cả những gì chúng ta trân quý đều bắt nguồn từ phước lành của Ngài. Thế nhưng, phù thủy, bị Enemies Vĩ Đại mê hoặc, đã biến những sáng tạo thần thánh ấy thành những thực thể ô uế, đáng hổ thẹn, tạo ra Synergy giả tạo với chúng. Dấu ấn của kẻ thù trên người những phù thủy này là bằng chứng cho tội lỗi của chúng. Với sự trợ giúp của Vessel of the Enemy, chúng thậm chí có thể biến thành Discord, đe dọa nghiêm trọng đến những tín đồ trung thành của Imperator.
+Phù thủy là gì? Và bản chất thực sự của nó là gì?
+Sức mạnh Cộng Hưởng do Resonator sử dụng được biết đến như một phước lành từ Sentinel Imperator. Những tín đồ trung thành của Giáo Đoàn được ban cho phước lành này khi tuân theo giáo lý, cho phép họ dẫn truyền sức mạnh thần thánh qua thân xác phàm trần. Tuy nhiên, phù thủy sinh ra từ những dục vọng hão huyền—những linh hồn bất tín, bị Leviathan dụ dỗ, lập giao ước để thực hành những nghệ thuật bị cấm. Bằng cách đó, chúng từ bỏ phước lành thần thánh được ban tặng từ khi sinh ra và vứt bỏ nhân tính, biến thành phù thủy tìm cách làm ô uế cõi trần bằng sức mạnh tà ác.
+Đấng Tối Cao đã tạo dựng thế giới này, và tất cả những gì chúng ta trân quý đều bắt nguồn từ phước lành của Ngài. Thế nhưng, phù thủy, bị Kẻ Thù Vĩ Đại mê hoặc, đã biến những sáng tạo thần thánh ấy thành những thực thể ô uế, đáng hổ thẹn, tạo ra Cộng Hưởng giả tạo với chúng. Dấu ấn của kẻ thù trên người những phù thủy này là bằng chứng cho tội lỗi của chúng. Với sự trợ giúp của Vessel of the Enemy, chúng thậm chí có thể biến thành Tacet Discord, đe dọa nghiêm trọng đến những tín đồ trung thành của Imperator.
 &lt;b&gt;Hãy cảnh giác, bởi bất kỳ ai khao khát tự do và dục vọng trần tục đều có thể trở thành con cờ của Leviathan.&lt;/b&gt;
-Vì vậy, chúng ta phải thường xuyên thanh tẩy và trừ tà những linh hồn như vậy. Nếu để những kẻ dị giáo này phát triển không kiểm soát, sử dụng sức mạnh ô uế để làm nhơ nhuốc cõi trần, chúng chắc chắn sẽ mang Dark Tide đến với Rinascita. Quests của Giáo Đoàn là dẫn dắt và cai quản chúng, đảm bảo chúng tuân theo ý chí thần thánh của Imperator. Nếu chúng từ chối gia nhập Giáo Đoàn, thề trung thành với giáo luật của Imperator, hoặc chuyên cần tuân theo giáo lý, số phận lầm lạc của chúng sẽ được điều chỉnh bởi những cánh buồm của Người Hành Hương.
+Vì vậy, chúng ta phải thường xuyên thanh tẩy và trừ tà những linh hồn như vậy. Nếu để những kẻ dị giáo này phát triển không kiểm soát, sử dụng sức mạnh ô uế để làm nhơ nhuốc cõi trần, chúng chắc chắn sẽ mang Dark Tide đến với Rinascita. Nhiệm vụ của Giáo Đoàn là dẫn dắt và cai quản chúng, đảm bảo chúng tuân theo ý chí thần thánh của Imperator. Nếu chúng từ chối gia nhập Giáo Đoàn, thề trung thành với giáo luật của Imperator, hoặc chuyên cần tuân theo giáo lý, số phận lầm lạc của chúng sẽ được điều chỉnh bởi những cánh buồm của Người Hành Hương.
 Chúng ta sẽ cầu nguyện cho chúng ngày đêm, để chúng được cứu rỗi bởi Sentinel Imperator vĩ đại của chúng ta. Ngợi ca Imperator.
-&lt;i&gt;Mạng Lưới Gián Điệp của Giáo Đoàn Shadow&lt;/i&gt;
-À, người bạn của ta, người đồng hành trên hành trình tìm kiếm tự do và chân lý này, ta van nài ngươi—hãy mở tập truyền đơn này ở nơi an toàn, tránh xa những ánh mắt tò mò. Điều ta sắp tiết lộ là tối quan trọng cho sự an toàn của ngươi. Hãy học cách nhận diện gián điệp của Giáo Đoàn Shadow và tránh khỏi nanh vuốt của chúng.
-Tất cả Echoes mang vầng hào quang vàng trên đầu đều là gián điệp của Giáo Đoàn Shadow, phục vụ với tư cách "Thiên Sứ". Chúng luôn xuất hiện bên cạnh các Acolyte, đóng vai tay sai của Giáo Đoàn để tiêu diệt những kẻ dị giáo. Rinascita, Land Echoes ư? Ha... ngay cả những lời châm biếm sắc bén nhất cũng không thể lột tả hết sự phi lý của thực tại mà chúng ta đang gánh chịu.
-Đầu tiên, ngươi phải cảnh giác với những Echoes đèn lồng, gọi là Lucerna. Dù trông có vẻ vô hại, chúng có khả năng phát hiện những kẻ dị giáo ẩn nấp trong bóng tối đêm đen. Ánh sáng của chúng có thể soi đường, nhưng cũng là vũ khí chói lòa, khiến người ta mất phương hướng. Đã từng có trường hợp ai đó dùng khả năng Echoes của Fae Ignis để ẩn thân, nhưng vẫn bị lộ dưới ánh sáng không thương tiếc của Lucerna.
-Next, có những bức tượng thạch cao thường thấy nhất, nổi tiếng với cái tên La Guardia, những kẻ bảo vệ trung thành nhất của Giáo Đoàn. Nếu không có lệnh từ các Acolyte, chúng đứng bất động như tượng đá. Tuy nhiên, nếu ngươi bị La Guardia truy đuổi, đừng phí thời gian chiến đấu với chúng. Thay vào đó, hãy tập trung tìm kiếm Acolyte của Order Penitentiary đang ra lệnh.
+&lt;i&gt;Mạng Lưới Gián Điệp của Giáo Đoàn Bóng Tối&lt;/i&gt;
+À, người bạn của ta, người đồng hành trên hành trình tìm kiếm tự do và chân lý này, ta van nài ngươi—hãy mở tập truyền đơn này ở nơi an toàn, tránh xa những ánh mắt tò mò. Điều ta sắp tiết lộ là tối quan trọng cho sự an toàn của ngươi. Hãy học cách nhận diện gián điệp của Giáo Đoàn Bóng Tối và tránh khỏi nanh vuốt của chúng.
+Tất cả Echo mang vầng hào quang vàng trên đầu đều là gián điệp của Giáo Đoàn Bóng Tối, phục vụ với tư cách "Thiên Sứ". Chúng luôn xuất hiện bên cạnh các Acolyte, đóng vai tay sai của Giáo Đoàn để tiêu diệt những kẻ dị giáo. Rinascita, Vùng Đất Echo ư? Ha... ngay cả những lời châm biếm sắc bén nhất cũng không thể lột tả hết sự phi lý của thực tại mà chúng ta đang gánh chịu.
+Đầu tiên, ngươi phải cảnh giác với những Echo đèn lồng, gọi là Lucerna. Dù trông có vẻ vô hại, chúng có khả năng phát hiện những kẻ dị giáo ẩn nấp trong bóng tối đêm đen. Ánh sáng của chúng có thể soi đường, nhưng cũng là vũ khí chói lòa, khiến người ta mất phương hướng. Đã từng có trường hợp ai đó dùng khả năng Echo của Fae Ignis để ẩn thân, nhưng vẫn bị lộ dưới ánh sáng không thương tiếc của Lucerna.
+Tiếp theo, có những bức tượng thạch cao thường thấy nhất, nổi tiếng với cái tên La Guardia, những kẻ bảo vệ trung thành nhất của Giáo Đoàn. Nếu không có lệnh từ các Acolyte, chúng đứng bất động như tượng đá. Tuy nhiên, nếu ngươi bị La Guardia truy đuổi, đừng phí thời gian chiến đấu với chúng. Thay vào đó, hãy tập trung tìm kiếm Acolyte của Order Penitentiary đang ra lệnh.
 Trong số tất cả những tay sai này, đáng ghét nhất là Vox Sanctus, đậu trên nóc các tòa nhà nhà thờ. Chúng đóng vai lính danh dự của Giáo Đoàn. Dù không thể di chuyển tự do, chúng dùng nhạc cụ để rao giảng những giáo lý giả dối ngày đêm. Những bài thuyết giáo ấy thấm vào tâm hồn người Ragunnesi, đầu độc tư tưởng của họ.
 Ngươi có thể tưởng tượng được không, những đứa trẻ Ragunna bị buộc phải nghe những lời rao giảng vô nghĩa ngay từ khi mới chào đời? Áp bức bằng vũ lực có thể còn chừa chỗ cho sự phản kháng, nhưng ở Ragunna, làm sao thoát khỏi những xiềng xích tinh thần len lỏi vào mọi ngóc ngách của cuộc sống?
 Đơn Khiếu Nại về Dị Giáo
 Kính gửi Ngài Acolyte,
-Tôi, Charles Tornatore, xin báo cáo một hành vi dị giáo—một đoàn kịch ngầm có tên Panacea đã dám diễn lại vở kịch bị cấm &lt;i&gt;Những Người Ragunnesi Flight Lượn&lt;/i&gt;, thêm vào vô số ẩn dụ độc hại và hình ảnh báng bổ. Tôi đã ghi lại những dòng sau đây theo trí nhớ:
-&lt;i&gt;"Lời của The The The Primus như những câu thần chú muối chua. Ngay cả Gondola cũng phải tê tái khi nghe thấy."&lt;/i&gt;
-—Trích Cảnh I, Act 1
+Tôi, Charles Tornatore, xin báo cáo một hành vi dị giáo—một đoàn kịch ngầm có tên Panacea đã dám diễn lại vở kịch bị cấm &lt;i&gt;Những Người Ragunnesi Bay Lượn&lt;/i&gt;, thêm vào vô số ẩn dụ độc hại và hình ảnh báng bổ. Tôi đã ghi lại những dòng sau đây theo trí nhớ:
+&lt;i&gt;"Lời của Primus như những câu thần chú muối chua. Ngay cả Gondola cũng phải tê tái khi nghe thấy."&lt;/i&gt;
+—Trích Cảnh I, Hồi 1
 &lt;i&gt;Liệu chiếc bánh mì cán bột trong tay ta có đủ cứng để đập tan kẻ thù đức tin của chúng ta không?&lt;/i&gt;
 —Trích Cảnh I, Hồi 3 (Ghi chú: Dòng này, do một Acolyte nói ra, đã hạ thấp thánh vật của Giáo Đoàn, gọi nó chỉ là một mẩu bánh mì.)
 &lt;i&gt;Nhân danh Imperator trên cao, xin chứng giám cho tình yêu của chúng con, đẹp đẽ như ánh bình minh.&lt;/i&gt;
-—Trích Cảnh II, Act 1 (Ghi chú: Dòng này đánh dấu cảnh私奔 của nam nữ chính.)
+—Trích Cảnh II, Hồi 1 (Ghi chú: Dòng này đánh dấu cảnh私奔 của nam nữ chính.)
 ...
 Tôi rất tiếc vì không thể nhớ hết những lời báng bổ trong vở kịch. Sao chúng dám báng bổ đức tin cao quý của chúng ta như vậy?
 Dù chúng đeo mặt nạ trong suốt buổi diễn, tôi vẫn nhận ra chúng qua dáng vẻ và giọng nói. Không ngạc nhiên khi chúng phục vụ gia tộc Montelli (Danh sách tên chi tiết được đính kèm).
@@ -33200,16 +33158,16 @@
 2:18 [Bộ Cổ Ngữ Thánh Lễ] Và Imperator phán: Hãy tiến về phía đông.
 2:19 [Bộ Cổ Ngữ Thánh Lễ] Và Sentinel Imperator rọi ánh sáng qua mưa và sóng. Đám đông theo ánh sáng ấy, vượt sương mù và bão tố.
 2:20 [Bộ Cổ Ngữ Thánh Lễ] Ánh sáng ấy đến từ ngọn hải đăng trên quần đảo xa xôi, nơi dòng hải lưu ấm áp giao hòa, nơi gia vị sinh sôi, nơi cây trái vàng óng trĩu cành.
-2:21 [Bộ Cổ Ngữ Thánh Lễ] Nhưng từ trong sương mù phía sau, những Discord đáng sợ đuổi theo, giẫm lên sấm sét, và dân chúng kêu gào thảm thiết.
+2:21 [Bộ Cổ Ngữ Thánh Lễ] Nhưng từ trong sương mù phía sau, những Tacet Discord đáng sợ đuổi theo, giẫm lên sấm sét, và dân chúng kêu gào thảm thiết.
 2:22 [Bộ Cổ Ngữ Thánh Lễ] Bấy giờ Sentinel Imperator phán: Ta sẽ mang đến sự cứu rỗi.
-2:23 [Bộ Cổ Ngữ Thánh Lễ] Và Genesis Nexus tỏa ra ánh sáng rực rỡ, nuốt chửng Discord vào trong hải đăng. Khi Sentinel Imperator gọi chúng trở lại, chúng đã hóa thành những Harbinger Thần Linh.
-2:24 [Bộ Cổ Ngữ Thánh Lễ] Và Sentinel Imperator phán: Nơi nào Genesis Nexus chiếu sáng, nơi đó sẽ có Harbinger Thần Linh ngự trị. Genesis Nexus chính là tay ta. Ta là ngọn hải đăng của Rinascita, Sentinel Imperator.
+2:23 [Bộ Cổ Ngữ Thánh Lễ] Và Genesis Nexus tỏa ra ánh sáng rực rỡ, nuốt chửng Tacet Discord vào trong hải đăng. Khi Sentinel Imperator gọi chúng trở lại, chúng đã hóa thành những Sứ Giả Thần Linh.
+2:24 [Bộ Cổ Ngữ Thánh Lễ] Và Sentinel Imperator phán: Nơi nào Genesis Nexus chiếu sáng, nơi đó sẽ có Sứ Giả Thần Linh ngự trị. Genesis Nexus chính là tay ta. Ta là ngọn hải đăng của Rinascita, Sentinel Imperator.
 2:25 [Bộ Cổ Ngữ Thánh Lễ] Suốt hàng trăm năm, đám đông đã tuân theo những lời răn dạy của Người.
-2:26 [Bộ Cổ Ngữ Thánh Lễ] Các Harbinger Thần Linh đã thể hiện sức mạnh để duy trì ý chí của Người.
+2:26 [Bộ Cổ Ngữ Thánh Lễ] Các Sứ Giả Thần Linh đã thể hiện sức mạnh để duy trì ý chí của Người.
 2:27 [Bộ Cổ Ngữ Thánh Lễ] Với những tín đồ, hãy coi đây là phước lành và tinh thần của Imperator.
-2:28 [Bộ Cổ Ngữ Thánh Lễ] Hãy yêu thương các Harbinger Thần Linh như yêu gia đình, anh em và hàng xóm của các ngươi.
+2:28 [Bộ Cổ Ngữ Thánh Lễ] Hãy yêu thương các Sứ Giả Thần Linh như yêu gia đình, anh em và hàng xóm của các ngươi.
 2:29 [Bộ Cổ Ngữ Thánh Lễ] Chúng ta thực hiện các thánh lễ để tưởng nhớ điều này.
-&lt;i&gt;Bộ Tân Ngữ Thánh Lễ&lt;/i&gt; Scenario 5 Câu 2
+&lt;i&gt;Bộ Tân Ngữ Thánh Lễ&lt;/i&gt; Chương 5 Câu 2
 5:03 [Bộ Tân Ngữ Thánh Lễ] Họ mong muốn truyền tải Oracle, nên đã khắc những lời thiêng lên cây sồi, và từ Oracle, quả Viscum Berry đầu tiên đã mọc lên.
 5:04 [Bộ Tân Ngữ Thánh Lễ] Quả berry ấy chính là tinh hoa trí tuệ của Imperator. Hãy ăn nó, và mắt các ngươi sẽ mở ra, để phân biệt thiện ác và lắng nghe lời răn của Người.
 5:05 [Bộ Tân Ngữ Thánh Lễ] Đó chính là trí tuệ.
@@ -33220,18 +33178,18 @@
 5:09 [Bộ Tân Ngữ Thánh Lễ] Bữa ăn thiêng thứ ba đã bay lên trời cùng Họ. Đó là sự phản bội của Fisalias.
 5:10 [Bộ Tân Ngữ Thánh Lễ] Họ dạy chúng ta chích máu từ ▇ ▇ ▇ và hòa ▇ ▇ vào rượu thánh. Và như thế, chúng ta sẽ trở thành anh em, không ai bị tách biệt.
 5:11 [Bộ Tân Ngữ Thánh Lễ] Đó chính là tinh thần.
-&lt;i&gt;Bộ Cổ Ngữ Thánh Lễ: Revelation&lt;/i&gt; Chương 1 Câu 9
-1:09 [Bộ Cổ Ngữ Thánh Lễ: Revelation] Ngày ấy, lông mày và mái tóc của Napoli trắng như len, trắng như tuyết, và đôi mắt chàng rực như ngọn lửa.
-1:10 [Bộ Cổ Ngữ Thánh Lễ: Revelation] Và Họ ban cho Napoli chiếc đèn lồng, sáng như đồng đỏ trong lò nung, và chiếc đèn lồng vang vọng tiếng nói của các Harbinger Thần Linh.
-1:11 [Bộ Cổ Ngữ Thánh Lễ: Revelation] Napoli giơ cao chiếc đèn lồng khi trở về, như mặt trời chiếu sáng rực rỡ.
-1:12 [Bộ Cổ Ngữ Thánh Lễ: Revelation] Và các Discord của Dark Tide cúi đầu trước chàng. Chàng giơ tay phải lên và nói với dân chúng: "Đừng sợ. Ta là Người Được Chiếu Sáng của Sentinel Imperator. Ta là đầu tiên và cuối cùng, khởi đầu và kết thúc. Ta có thể nghe thấy tiếng của Người."
-1:13 [Bộ Cổ Ngữ Thánh Lễ: Revelation] "Ta đã chết, và kìa, ta sống lại mãi mãi, và ta nắm giữ chìa khóa của Thiên Sugar và Địa Ngục."
-1:14 [Bộ Cổ Ngữ Thánh Lễ: Revelation] "Hãy nhìn ánh sáng trong tay ta. Chiếc Đèn Lồng sẽ là quyền năng kết nối chúng ta với Imperator."
-1:15 [Bộ Cổ Ngữ Thánh Lễ: Revelation] Ai có tai để nghe, hãy lắng nghe:
-1:16 [Bộ Cổ Ngữ Thánh Lễ: Revelation] Và ta nghe thấy, bên cạnh Sentinel Imperator, giữa tiếng hát và kèn trống, có tiếng phán với ta: "Hãy lên đây, và ta sẽ cho ngươi thấy những gì phải xảy ra sau này."
-1:17 [Bộ Cổ Ngữ Thánh Lễ: Revelation] Instantly, ta được đưa vào trong tinh thần, và trước mắt ta là một ngai vàng trên biển. Một Harbinger Thần Linh bước ra và tuyên bố: Ai xứng đáng cầm chiếc đèn lồng này và để ánh sáng của nó chiếu rọi thế gian?
-1:18 [Bộ Cổ Ngữ Thánh Lễ: Revelation] Rồi ta khóc lớn, vì trước ngai vàng của Imperator, các Harbinger Thần Linh đứng đó, một số trông như vừa bị sát hại, số khác bị gai đâm xuyên người. Rồi ta nghe Imperator phán bằng giọng như sấm: "Hãy đến!"
-1:19 [Bộ Cổ Ngữ Thánh Lễ: Revelation] Sau đó, ta nhìn thấy một con ngựa trắng chỉ còn nửa thân. Nó ra lệnh cho ta giơ cao đèn lồng và cầu nguyện, để mọi người có thể hiểu nhau và được ban cho chiến thắng nối tiếp chiến thắng.</t>
+&lt;i&gt;Bộ Cổ Ngữ Thánh Lễ: Khải Huyền&lt;/i&gt; Chương 1 Câu 9
+1:09 [Bộ Cổ Ngữ Thánh Lễ: Khải Huyền] Ngày ấy, lông mày và mái tóc của Napoli trắng như len, trắng như tuyết, và đôi mắt chàng rực như ngọn lửa.
+1:10 [Bộ Cổ Ngữ Thánh Lễ: Khải Huyền] Và Họ ban cho Napoli chiếc đèn lồng, sáng như đồng đỏ trong lò nung, và chiếc đèn lồng vang vọng tiếng nói của các Sứ Giả Thần Linh.
+1:11 [Bộ Cổ Ngữ Thánh Lễ: Khải Huyền] Napoli giơ cao chiếc đèn lồng khi trở về, như mặt trời chiếu sáng rực rỡ.
+1:12 [Bộ Cổ Ngữ Thánh Lễ: Khải Huyền] Và các Tacet Discord của Dark Tide cúi đầu trước chàng. Chàng giơ tay phải lên và nói với dân chúng: "Đừng sợ. Ta là Người Được Chiếu Sáng của Sentinel Imperator. Ta là đầu tiên và cuối cùng, khởi đầu và kết thúc. Ta có thể nghe thấy tiếng của Người."
+1:13 [Bộ Cổ Ngữ Thánh Lễ: Khải Huyền] "Ta đã chết, và kìa, ta sống lại mãi mãi, và ta nắm giữ chìa khóa của Thiên Đường và Địa Ngục."
+1:14 [Bộ Cổ Ngữ Thánh Lễ: Khải Huyền] "Hãy nhìn ánh sáng trong tay ta. Chiếc Đèn Lồng sẽ là quyền năng kết nối chúng ta với Imperator."
+1:15 [Bộ Cổ Ngữ Thánh Lễ: Khải Huyền] Ai có tai để nghe, hãy lắng nghe:
+1:16 [Bộ Cổ Ngữ Thánh Lễ: Khải Huyền] Và ta nghe thấy, bên cạnh Sentinel Imperator, giữa tiếng hát và kèn trống, có tiếng phán với ta: "Hãy lên đây, và ta sẽ cho ngươi thấy những gì phải xảy ra sau này."
+1:17 [Bộ Cổ Ngữ Thánh Lễ: Khải Huyền] Ngay lập tức, ta được đưa vào trong tinh thần, và trước mắt ta là một ngai vàng trên biển. Một Sứ Giả Thần Linh bước ra và tuyên bố: Ai xứng đáng cầm chiếc đèn lồng này và để ánh sáng của nó chiếu rọi thế gian?
+1:18 [Bộ Cổ Ngữ Thánh Lễ: Khải Huyền] Rồi ta khóc lớn, vì trước ngai vàng của Imperator, các Sứ Giả Thần Linh đứng đó, một số trông như vừa bị sát hại, số khác bị gai đâm xuyên người. Rồi ta nghe Imperator phán bằng giọng như sấm: "Hãy đến!"
+1:19 [Bộ Cổ Ngữ Thánh Lễ: Khải Huyền] Sau đó, ta nhìn thấy một con ngựa trắng chỉ còn nửa thân. Nó ra lệnh cho ta giơ cao đèn lồng và cầu nguyện, để mọi người có thể hiểu nhau và được ban cho chiến thắng nối tiếp chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -33345,54 +33303,51 @@
       <c r="M425" t="inlineStr">
         <is>
           <t>Nghiên Cứu Toàn Diện Lịch Sử Kịch Nghệ Ragunnesi (Kèm Bình Luận)
-Nghiên Cứu Toàn Diện Lịch Sử Kịch Nghệ Ragunnesi: Sự Tiến Hóa Của Sự Giao Thoa Văn hóa Bộ Lạc và Hệ thống Tín Ngưỡng
-Người viết: DeLillo Quentin
-Được đề xuất tài trợ: Dự án Nghiên cứu Area Hiệp hội Kịch nghệ Ragunna - Học bổng Aspire Scholars
+Nghiên Cứu Toàn Diện Lịch Sử Kịch Nghệ Ragunnesi: Sự Tiến Hóa Của Sự Giao Thoa Văn Hóa Bộ Lạc Và Hệ Thống Niềm Tin
+Tác giả: DeLillo Quentin
+Đề xuất tài trợ: Dự án Nghiên cứu Khu vực Hiệp hội Kịch nghệ Ragunna - Học bổng Aspire Scholars
 Chủng viện Thần học Avinoleum, Ragunna, Rinascita
-Tóm tắt: Bài nghiên cứu này tổng quan các xu hướng và phát triển nghiên cứu gần đây về nguồn gốc văn hóa kịch nghệ tại các vùng Ragunna và Septimont, đặc biệt tập trung vào những tiến bộ trong lĩnh vực "khảo cổ học kịch nghệ" trong thập kỷ qua. Dựa trên các nghiên cứu đa dạng và các nghiên cứu góc nhìn từ Liên bang New trong những năm gần đây, bài viết cũng kết hợp những hiểu biết từ kinh nghiệm khảo cổ của Huanglong trong việc nghiên cứu di tích lịch sử. Các nghiên cứu trường hợp được lựa chọn chủ yếu tập trung vào các vở kịch kinh điển và các sự kiện lịch sử quan trọng. Kết quả cho thấy văn hóa kịch nghệ Ragunnesi bắt nguồn từ các buổi trình diễn tường thuật ghi lại lịch sử và cuộc sống của các bộ lạc trên đảo.
+Tóm tắt: Bài nghiên cứu này đánh giá các xu hướng và phát triển nghiên cứu gần đây về nguồn gốc văn hóa kịch nghệ tại các vùng Ragunna và Septimont, đặc biệt tập trung vào những tiến bộ trong "khảo cổ học kịch nghệ" trong thập kỷ qua. Dựa trên các nghiên cứu đa dạng và các nghiên cứu về góc nhìn từ Liên bang Mới trong những năm gần đây, bài viết cũng kết hợp những hiểu biết từ kinh nghiệm khảo cổ của Huanglong trong việc nghiên cứu các di tích lịch sử. Các nghiên cứu điển hình được lựa chọn chủ yếu tập trung vào các vở kịch kinh điển và các sự kiện lịch sử quan trọng. Kết quả cho thấy văn hóa kịch nghệ Ragunnesi bắt nguồn từ các buổi trình diễn kể chuyện ghi lại lịch sử và cuộc sống của các bộ lạc trên đảo.
 Từ khóa: lịch sử kịch nghệ, nghiên cứu văn hóa, tổng quan, nghiên cứu văn hóa dân gian, khảo cổ học
-...(Một số trang bị thiếu)...
-Như được minh họa trong các tài liệu quan trọng như &lt;i&gt;Biên niên sử Avinoleum&lt;/i&gt; và &lt;i&gt;Cành Vàng&lt;/i&gt;, nguồn gốc của kịch nghệ gắn liền trực tiếp với tín ngưỡng về Sentinel Imperator. Tuy nhiên, các nghiên cứu kỹ thuật về thiết kế sân khấu, trang phục, hóa trang, mặt nạ và đạo cụ, như được tìm thấy trong cả văn học lịch sử và hiện đại, cũng như các văn bản nước ngoài được dịch, cho thấy vẫn còn nhiều điều cần khám phá về sự tiến hóa của kịch nghệ như một sự phản ánh cuộc sống và văn hóa dân gian. Ví dụ, nghiên cứu của Quỹ Văn hóa Montelli mang tên &lt;i&gt;Đặc điểm Văn hóa và Re thiết Văn hóa trong Dịch thuật: Nghiên cứu Trường hợp Hành trình đến Rinascita trong Thư Viện Sưu Tập của Huanglong&lt;/i&gt; xem xét quá trình chuyển đổi từ truyền thống dân gian sang các hình thức văn bản và sân khấu trong kịch nghệ, tập trung vào sự tiến hóa của các văn bản dịch.
-&lt;b&gt;Bình luận của Chủng viện: Xin đừng nộp bài viết giai thoại cho &lt;i&gt;Niên giám và Huyền bí&lt;/i&gt; cho quỹ của chúng tôi. Ngoài ra, an ninh lương thực phải được quản lý chặt chẽ hơn để ngăn ngừa nguy cơ sinh viên bị suy nhược thần kinh do ăn phải cua chuông hỏng.&lt;/b&gt;
-...(Một số trang bị thiếu)...
-Người dân Rinascita trong Thời đại Ngàn Đảo đã sử dụng trang phục để đại diện cho nguồn gốc của các bộ lạc khác nhau, mặt nạ để tượng trưng cho tổ tiên và vật tổ, và các ngôn ngữ bộ lạc khác nhau để tương tác và giao tiếp với nhau trong lễ hội Carnevale dưới hình thức kịch nghệ. Quá trình này tiếp tục cho đến khi đạt được sự giao thoa và hiểu biết lẫn nhau giữa các bộ lạc. Sau nhiều lần chuyển thể và diễn giải lại các truyền thuyết và huyền thoại dân gian, nó cuối cùng đã phát triển thành nguyên mẫu của kịch nghệ Ragunnesi, vốn vẫn còn phổ biến cho đến ngày nay.
-&lt;b&gt;Bình luận của Người hướng dẫn: Đề nghị lược bỏ một số chi tiết và tránh nghiên cứu quá mức, vì bài viết sẽ được Hội đồng Khai sáng của Order xem xét.&lt;/b&gt;
-Nghiên Cứu về Sự Tiến Hóa của Trang phục và Thiết Kế Sân Khấu trong Kịch Nghệ
-(Cuốn sổ tay viết tay này gần như bị rách hoàn toàn, chỉ còn lại vài trang của Phần Kết.)
-Phần Kết:
-Tôi muốn dành tặng bài nghiên cứu này cho những người bạn đã ủng hộ tôi, cho những người đã bí mật cung cấp những tài liệu vô giá cho nghiên cứu của tôi, cho công trình của cha tôi, DeLillo Quentin, cho sự lưu đày mà Order of the Deep đã ban cho tôi, và cho việc bị trục xuất khỏi Chủng viện Thần học Avinoleum.
-Bài nghiên cứu này, có tựa đề "Nghiên Cứu về Sự Tiến Hóa của Trang phục và Thiết Kế Sân Khấu trong Kịch Nghệ," đã mất bốn năm để hoàn thành, từ khi bắt đầu cho đến đêm trước ngày tôi bị lưu đày, và cuối cùng tôi đã hoàn thành bản thảo đầu tiên. Tôi hy vọng những người bạn của tôi có thể đọc nó, như ý nguyện ban đầu của tôi.
+...(Một số trang bị thiếu)
+Như được minh họa trong các tài liệu quan trọng như &lt;i&gt;Biên niên sử Avinoleum&lt;/i&gt; và &lt;i&gt;Cành Vàng&lt;/i&gt;, nguồn gốc của kịch nghệ gắn liền trực tiếp với tín ngưỡng về Sentinel Imperator. Tuy nhiên, các nghiên cứu kỹ thuật về thiết kế sân khấu, trang phục, hóa trang, mặt nạ và đạo cụ, như được tìm thấy trong cả văn học lịch sử và hiện đại, cũng như các văn bản nước ngoài được dịch, cho thấy vẫn còn nhiều điều cần khám phá về sự tiến hóa của kịch nghệ như một sự phản ánh cuộc sống và văn hóa dân gian. Ví dụ, nghiên cứu của Quỹ Văn hóa Montelli mang tên &lt;i&gt;Đặc điểm Văn hóa và Tái thiết Văn hóa trong Dịch thuật: Nghiên cứu Trường hợp Hành trình đến Rinascita trong bộ sưu tập của Huanglong&lt;/i&gt; đã xem xét quá trình chuyển đổi từ truyền thống dân gian sang các hình thức văn bản và sân khấu trong kịch nghệ, tập trung vào sự tiến hóa của các văn bản dịch.
+&lt;b&gt;Bình luận của Chủng viện: Xin đừng nộp bài viết giai thoại cho &lt;i&gt;Niên giám và Huyền bí học&lt;/i&gt; cho quỹ của chúng tôi. Ngoài ra, an ninh lương thực phải được quản lý chặt chẽ hơn để ngăn ngừa khả năng sinh viên bị suy nhược thần kinh do ăn phải cua chuông hỏng.&lt;/b&gt;
+...(Một số trang bị thiếu)
+Người dân Rinascita trong Thời đại Ngàn Đảo đã sử dụng trang phục để đại diện cho nguồn gốc của các bộ lạc khác nhau, mặt nạ để tượng trưng cho tổ tiên và vật tổ, và các ngôn ngữ bộ lạc khác nhau để tương tác và giao tiếp với nhau trong lễ hội Carnevale dưới hình thức kịch nghệ. Quá trình này tiếp tục cho đến khi đạt được sự hòa hợp và hiểu biết lẫn nhau giữa các bộ lạc. Sau nhiều lần cải biên và diễn giải lại các truyền thuyết và huyền thoại dân gian, nó cuối cùng đã phát triển thành nguyên mẫu của kịch nghệ Ragunnesi, vốn vẫn còn phổ biến cho đến ngày nay.
+&lt;b&gt;Bình luận của Người hướng dẫn: Đề nghị lược bỏ một số chi tiết và tránh nghiên cứu quá mức, vì bài viết sẽ được Hội đồng Giác ngộ của Dòng xem xét.&lt;/b&gt;
+Nghiên Cứu về Sự Tiến Hóa của Trang Phục và Thiết Kế Sân Khấu trong Kịch Nghệ
+(Cuốn sổ tay viết tay này gần như bị rách hoàn toàn, chỉ còn lại vài trang của Lời bạt.)
+Lời bạt:
+Tôi xin dành bài nghiên cứu này cho những người bạn đã ủng hộ tôi, cho những người đã bí mật cung cấp những tài liệu vô giá cho nghiên cứu của tôi, cho công trình của cha tôi, DeLillo Quentin, cho sự lưu đày mà Dòng Biển sâu đã ban cho tôi, và cho việc bị trục xuất khỏi Chủng viện Thần học Avinoleum.
+Bài nghiên cứu mang tên "Nghiên cứu về Sự Tiến Hóa của Trang Phục và Thiết Kế Sân Khấu trong Kịch Nghệ" đã mất bốn năm để hoàn thành, từ khi bắt đầu cho đến đêm trước ngày tôi bị lưu đày, và cuối cùng tôi đã hoàn thành bản thảo đầu tiên. Tôi hy vọng các bạn của tôi có thể đọc nó, như ý định ban đầu của tôi.
 Sáng mai, tôi sẽ rời Ragunna trên con tàu Pilgrim's Sail, giống như cha tôi đã làm, để tìm kiếm Sentinel—Ngợi ca Imperator! Nếu tôi sống sót, tôi hy vọng Người, vị Imperator toàn năng, sẽ dẫn dắt con đường của tôi.
-...Khi tôi còn nhỏ, cha tôi, DeLillo, đã nói với tôi trước khi ông rời đi, "Quentin nhỏ, con có biết con người là gì không?"
+...Khi tôi còn nhỏ, cha tôi, DeLillo, đã nói với tôi trước khi ông ra đi, "Quentin nhỏ, con có biết con người là gì không?"
 Tôi biết đó sẽ là những lời cuối cùng của cha dành cho tôi, nên tôi trả lời rằng tôi không biết.
-Cha tôi sau đó nói, "Hãy luôn cố gắng hết sức, Mario Quentin. Humans là một nhánh cỏ biển biết suy nghĩ."
-Tôi không hiểu tại sao con người lại được so sánh với một nhánh cỏ biển. Nhưng giờ đây, tôi nghĩ mình đã hiểu ý cha—đừng ngừng suy nghĩ và đừng ngừng tìm kiếm.
-Những hòn đảo trong quá khứ đã bị hủy diệt trong Lament. Dưới sự dẫn dắt của Imperator, tổ tiên chúng ta đã lên tàu Ark và đi xa, cuối cùng lập nên Rinascita trên mảnh đất hiện tại. &lt;b&gt;Trong Thời đại Ngàn Đảo, để tưởng nhớ những quê hương đã mất và tôn vinh đồng bào của họ trong Lament, người dân bắt đầu mặc trang phục của bộ lạc mình và đeo mặt nạ tượng trưng cho tổ tiên và vật tổ. Như đã kết luận trong Chương 4 của bài nghiên cứu này, văn hóa kịch nghệ chưa bao giờ là một ân huệ được Order hứa hẹn. Đúng hơn, đó là một sự tưởng niệm và biểu tượng được phát triển độc lập bởi người dân Rinascita.&lt;/b&gt;
+Cha tôi sau đó nói, "Hãy luôn cố gắng hết sức, Mario Quentin. Con người là một nhánh cỏ biển biết suy nghĩ."
+Tôi không hiểu tại sao con người lại được ví như một nhánh cỏ biển. Nhưng giờ đây, tôi nghĩ mình đã hiểu ý cha—đừng ngừng suy nghĩ và đừng ngừng tìm kiếm.
+Những hòn đảo ngày xưa đã bị hủy diệt trong Lament. Dưới sự dẫn dắt của Imperator, tổ tiên chúng ta đã lên tàu Ark và đi xa, cuối cùng lập nên Rinascita trên mảnh đất hiện tại. &lt;b&gt;Trong Thời đại Ngàn Đảo, để tưởng nhớ những quê hương đã mất và tôn vinh đồng bào của họ trong Lament, người dân bắt đầu mặc trang phục của bộ lạc mình và đeo mặt nạ tượng trưng cho tổ tiên và vật tổ. Như đã kết luận trong Chương 4 của bài nghiên cứu này, văn hóa kịch nghệ chưa bao giờ là ân huệ được Dòng hứa ban. Đúng hơn, đó là một sự tưởng nhớ và biểu tượng được người dân Rinascita tự phát triển.&lt;/b&gt;
 Nhưng liệu chúng ta có thực sự chỉ là một nhánh cỏ biển?
-Nếu vậy, hẳn phải có sự khác biệt giữa những nhánh cỏ biển trôi theo dòng nước và những nhánh có thể suy nghĩ độc lập, phải không?
-Người ta ca ngợi danh của Imperator vì lòng nhân từ và sự bao dung, vì đã bảo tồn nền văn hóa kết nối những người từ các bộ lạc khác nhau, giúp họ hòa nhập và hỗ trợ lẫn nhau. Họ ca ngợi Imperator vì ý chí đoàn kết những nhánh cỏ biển rộng lớn để chống lại dòng chảy của Lament.
+Nếu vậy, hẳn phải có sự khác biệt giữa những nhánh cỏ biển trôi theo dòng nước và những nhánh có thể tự suy nghĩ, phải không?
+Mọi người ngợi ca danh của Imperator vì lòng nhân từ và sự bao dung của Người, vì đã bảo tồn văn hóa kết nối những người từ các bộ lạc khác nhau, giúp họ hòa nhập và hỗ trợ lẫn nhau. Họ ngợi ca Imperator vì ý chí đoàn kết những nhánh cỏ biển rộng lớn để chống lại dòng chảy của Lament.
 Ngợi ca Imperator! Chúng con tôn vinh Người! Nhưng liệu người Ragunnesi ngày nay có thực sự thực thi ý chí chân chính của Người?
-Ôi, vị Imperator vĩ đại! Con không muốn chết... Con thực sự không muốn... Con ước gì mình có thể tham dự Carnevale thêm một lần nữa... Con thực sự sợ hãi... Xin đừng biến con thành một nhánh cỏ biển vào ngày mai!
+Ôi, vị Imperator vĩ đại! Con không muốn chết... Con thực sự không muốn... Con ước gì mình có thể tham dự Carnevale thêm một lần nữa... Con thực sự sợ hãi... Xin Người, đừng biến con thành một nhánh cỏ biển vào ngày mai!
 Laurel và Kiếm (Phần I)
 Laurel và Kiếm: Về Hình tượng Thần thánh trong &lt;i&gt;Cành Vàng&lt;/i&gt;
-Malee tạp chí: Tạp chí Nghiên cứu Hiệp hội Kịch nghệ Gió Biển Ragunna, Tập 1
+Tên tạp chí: Tạp chí Nghiên cứu Hiệp hội Kịch nghệ Gió Biển Ragunna, Tập 1
 Thể loại: Nghiên cứu Văn học, Lý thuyết Văn học, Sân khấu, Cành Vàng
-&lt;i&gt;Cành Vàng&lt;/i&gt;, một sử thi tường thuật Ragunnesi giàu lịch sử và chịu ảnh hưởng sâu sắc từ văn hóa tôn giáo nguyên thủy, nổi tiếng với các yếu tố sân khấu nổi bật. Sử thi mở đầu bằng những vở kịch mục đồng dựa trên tín ngưỡng và phong tục nguyên thủy của các bộ lạc trong Thời đại Ngàn Đảo. Khi câu chuyện phát triển, những câu chuyện đa dạng này hội tụ dưới sự dẫn dắt của Sentinel Imperator. Tác giả sử dụng góc nhìn của các Envoy Thần thánh để thể hiện quan điểm của Imperator, cho phép các nhân vật đảm nhận vai trò của mình trong các vở kịch cổ điển. Xuyên suốt tác phẩm, các biểu tượng tôn giáo và vật tổ lặp đi lặp lại, gợi nhớ đến những ẩn dụ thường thấy trong các vở kịch truyền thống. Việc sử dụng các yếu tố sân khấu này đã giúp tác phẩm trở thành một kinh điển được yêu thích, được cả quan chức và dân thường ở Ragunna trân trọng. Hơn nữa, nó chứa đựng những suy ngẫm sâu sắc của tác giả về ý chí đằng sau Oracle do Sentinel Imperator ban truyền, cũng như những thay đổi xã hội diễn ra ở vùng Rinascita.
-...(Một số trang bị thiếu)...
-Một trong những cảnh đáng khen nhất trong &lt;i&gt;Cành Vàng&lt;/i&gt; là cảnh kết thúc Cảnh 3, nơi năm tuyến truyện hội tụ một cách kịch tính tại cao trào của lễ hội Carnevale: Khu Rừng Thần thánh của Sell đảo Fagaceae, Order of Ragunna, Những Người Giữ Bí mật ở Thessaleo Fells, người kế vị thống đốc ở Septimont, và các đấu sĩ, tất cả đều hợp nhất trong một màn kết hoành tráng. Trong cảnh này, tác giả khéo léo đan xen các nhân vật và cốt truyện, nắm bắt được sức hấp dẫn độc đáo của một bi kịch lịch sử hoành tráng. Sự hội tụ trong Cảnh 3 này đã trở thành khuôn mẫu, truyền cảm hứng cho vô số vở kịch sau này. Ảnh hưởng của cảnh này phần lớn nhờ vào thiết kế cốt truyện phức tạp, thể hiện kỹ thuật điêu luyện và đặt ra tiêu chuẩn trong cấu trúc tường thuật. Ngoài khuôn khổ lý thuyết của chính tác phẩm, thiết kế này—nơi mỗi yếu tố phản ánh chủ đề cốt lõi và rút ra từ bối cảnh lịch sử—đã củng cố vị thế của sử thi này như một tác phẩm kinh điển vượt thời gian, duy trì sự liên quan và tôn kính qua các biến động văn hóa trong lịch sử văn học. (View Ghi chú 23)
-&lt;i&gt;Cành Vàng&lt;/i&gt; được công nhận là tác phẩm nghệ thuật đầu tiên kết nối văn hóa dân gian bộ lạc với Sentinel (xem Ghi chú 24). Trong cao trào Cảnh 3 của lễ hội Carnevale, năm chiếc mặt nạ đứng cùng nhau, mỗi người theo đuổi đức tin của riêng mình, khi Sentinel Imperator từ trên cao giáng xuống, trao vòng nguyệt quế cho Người được Chọn—nhân vật chính trên sân khấu. Nghi thức này kể từ đó đã trở thành biểu tượng văn hóa lâu dài trong lòng người dân Rinascita. Từ cảnh này trở đi, mọi hành trình anh hùng đều phải kết thúc bằng nghi thức "được trao vòng nguyệt quế," cho dù người anh hùng đảm nhận vai trò diễn viên trên sân khấu hay nhà soạn kịch đứng sau hậu trường trong lễ hội Carnevale.
+&lt;i&gt;Cành Vàng&lt;/i&gt;, một sử thi tự sự Ragunnesi giàu lịch sử và chịu ảnh hưởng sâu sắc từ văn hóa tôn giáo nguyên thủy, nổi tiếng với các yếu tố sân khấu nổi bật. Sử thi mở đầu bằng những vở kịch mục đồng dựa trên tín ngưỡng và phong tục nguyên thủy của các bộ lạc trong Thời đại Ngàn Đảo. Khi câu chuyện phát triển, những câu chuyện đa dạng này hội tụ dưới sự dẫn dắt của Sentinel Imperator. Tác giả sử dụng góc nhìn của các Sứ giả Thần thánh để thể hiện quan điểm của Imperator, cho phép các nhân vật đảm nhận vai trò của mình trong các vở kịch cổ điển. Xuyên suốt tác phẩm, các biểu tượng tôn giáo và vật tổ lặp đi lặp lại, vang vọng những ẩn dụ thường thấy trong các vở kịch truyền thống. Việc sử dụng các yếu tố sân khấu này đã giúp tác phẩm trở thành một kinh điển được yêu thích, được cả quan chức và dân thường ở Ragunna trân trọng. Hơn nữa, nó chứa đựng những suy ngẫm sâu sắc của tác giả về ý chí đằng sau Oracle do Sentinel Imperator ban truyền, cũng như những biến đổi xã hội đang diễn ra ở vùng Rinascita.
+...(Một số trang bị thiếu)
+Một trong những cảnh đáng khen nhất trong &lt;i&gt;Cành Vàng&lt;/i&gt; là cảnh kết thúc Hồi 3, nơi năm tuyến truyện hội tụ một cách kịch tính tại cao trào của lễ hội Carnevale: Khu rừng Thần thánh trên bán đảo Fagaceae, Dòng Ragunna, Những Người Giữ Bí mật ở Thessaleo Fells, người kế vị thống đốc ở Septimont, và các đấu sĩ, tất cả cùng hòa vào một màn kết hoành tráng. Trong cảnh này, tác giả đã khéo léo đan xen các nhân vật và cốt truyện, nắm bắt được sức hấp dẫn độc đáo của một bi kịch lịch sử hoành tráng. Sự hội tụ trong Hồi 3 này đã trở thành khuôn mẫu, truyền cảm hứng cho vô số vở kịch sau này. Thành công của cảnh này phần lớn nhờ vào thiết kế cốt truyện phức tạp, thể hiện kỹ thuật điêu luyện và đặt ra tiêu chuẩn cho cấu trúc tự sự. Ngoài khuôn khổ lý thuyết của chính tác phẩm, thiết kế này—nơi mỗi yếu tố phản ánh chủ đề cốt lõi và rút ra từ bối cảnh lịch sử—đã khẳng định vị thế kinh điển vượt thời gian của sử thi này, duy trì sự liên quan và tôn kính qua các biến đổi văn hóa trong lịch sử văn học. (Xem Chú thích 23)
+&lt;i&gt;Cành Vàng&lt;/i&gt; được công nhận là tác phẩm nghệ thuật đầu tiên kết nối văn hóa dân gian bộ lạc với Sentinel (xem Chú thích 24). Trong cao trào Hồi 3 của lễ hội Carnevale, năm chiếc mặt nạ đứng cùng nhau, mỗi người theo đuổi niềm tin riêng, khi Sentinel Imperator từ trên cao giáng xuống, trao vòng nguyệt quế cho Người được Chọn—nhân vật chính trên sân khấu. Nghi thức này từ đó đã trở thành biểu tượng văn hóa vĩnh cửu trong lòng người dân Rinascita. Từ cảnh này trở đi, mọi hành trình anh hùng đều phải kết thúc bằng nghi thức "được trao vòng nguyệt quế", cho dù người anh hùng đảm nhận vai trò diễn viên trên sân khấu hay nhà biên kịch đứng sau hậu trường trong lễ hội Carnevale.
 Laurel và Kiếm (Phần II)
 Laurel và Kiếm: Về Hình tượng Thần thánh trong &lt;i&gt;Cành Vàng&lt;/i&gt;
-Malee tạp chí: Tạp chí Nghiên cứu Hiệp hội Kịch nghệ Gió Biển Ragunna
+Tên tạp chí: Tạp chí Nghiên cứu Hiệp hội Kịch nghệ Gió Biển Ragunna
 Thể loại: Nghiên cứu Văn học, Lý thuyết Văn học, Sân khấu, Cành Vàng
-(Next)
-Lý do Sentinel Imperator giáng xuống tại cao trào của lễ hội Carnevale trong &lt;i&gt;Cành Vàng&lt;/i&gt; vẫn là một câu hỏi mở, phần lớn chưa được xem xét trong chính sử thi này hoặc trong các nghiên cứu liên quan. Trong lịch sử, quan điểm phổ biến tại Chủng viện cho rằng Người được trao vòng nguyệt quế phải là cá nhân phù hợp nhất với lý tưởng của Rinascita và cộng hưởng với Sentinel—không bị thúc đẩy bởi đam mê kịch nghệ hay động cơ ngầm. Trong một thời gian dài, quan điểm này đã thống trị các nghiên cứu về &lt;i&gt;Cành Vàng&lt;/i&gt; và lĩnh vực văn học về Người được trao vòng nguyệt quế rộng hơn, với vòng nguyệt quế được coi là biểu tượng của vinh dự lớn lao và hiện thân của ý chí tập thể của Rinascita. (View Ghi chú 25)
-Tuy nhiên, sau các sự kiện văn hóa sau vụ việc tại Chủng viện, biểu tượng và màn trình diễn của Người được trao vòng nguyệt quế giờ đây được coi là biểu hiện của ý chí thần thánh của Sentinel—lực lượng dẫn dắt việc ban truyền Oracle và thống nhất các giáo lý. Hình ảnh vòng nguyệt quế cũng đã trở thành đại diện cho ý định thiêng liêng này.
+(Tiếp theo)
+Lý do Sentinel Imperator giáng xuống tại cao trào của lễ hội Carnevale trong &lt;i&gt;Cành Vàng&lt;/i&gt; vẫn là một câu hỏi mở, phần lớn chưa được khám phá trong chính sử thi hay các nghiên cứu liên quan. Trong lịch sử, quan điểm phổ biến tại Chủng viện cho rằng Người được trao vòng nguyệt quế phải là cá nhân phù hợp nhất với lý tưởng của Rinascita và cộng hưởng với Sentinel—không bị thúc đẩy bởi đam mê kịch nghệ hay động cơ thầm kín. Trong một thời gian dài, quan điểm này đã thống trị các nghiên cứu về &lt;i&gt;Cành Vàng&lt;/i&gt; và lĩnh vực văn học về Người được trao vòng nguyệt quế, với vòng nguyệt quế được coi là biểu tượng của vinh dự tối cao và hiện thân của ý chí tập thể của Rinascita. (Xem Chú thích 25)
+Tuy nhiên, sau các sự kiện văn hóa sau vụ việc tại Chủng viện, biểu tượng và màn trình diễn của Người được trao vòng nguyệt quế giờ đây được coi là sự thể hiện ý chí thần thánh của Sentinel—lực lượng dẫn dắt việc ban truyền Oracle và thống nhất các giáo lý. Hình ảnh vòng nguyệt quế cũng đã trở thành đại diện cho ý định thiêng liêng này.
 Tác giả đặt ra một câu hỏi thú vị: với cách giải thích này, liệu việc lựa chọn Người được trao vòng nguyệt quế có thể được coi là một sự truyền bá về tự do—một khái niệm dường như mâu thuẫn với &lt;i&gt;Cành Vàng&lt;/i&gt;? Liệu tự do, một khi đã được truyền bá, có còn được coi là tự do?
-...(Một số trang bị thiếu)...
-[23] Charlie Welbeck, "Lịch sử Cải cách về Thẩm mỹ Kịch nghệ Rinascita," xuất bản bởi Tạp chí Văn hóa Chủng viện Thần học Avinoleum.
-[24] Mario Quentin, "Nghiên cứu về Sự Tiến hóa của Trang phục và Thiết kế Sân khấu trong Kịch nghệ," xuất bản bởi Home xuất bản Nghiên cứu Văn hóa Nước ngoài.
-[25] Cosimo Sorrentino, "Nghiên cứu về Độc giả của &lt;i&gt;Cành Vàng&lt;/i&gt;," xuất bản bởi Hiệp hội Kịch nghệ Ragunna.</t>
+...(Một số trang bị thiếu)</t>
         </is>
       </c>
     </row>
@@ -33517,8 +33472,8 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Sổ A Diary Cũ 1
-Số A Diary_#00
+          <t>Sổ Nhật Ký Cũ 1
+Số Nhật Ký_#00
 Mẹ ơi, mẹ đã bao giờ thấy một Nimbus Wraith chưa? Hôm nay con thấy một con lần đầu tiên, thật là tuyệt vời.
 Con háo hức quá. Con không biết phải chia sẻ với ai, nên con viết lại đây thôi.
 Hôm nay như một bước ngoặt thực sự với con.
@@ -33529,8 +33484,8 @@
 Trong khi các gia đình quý tộc khác bán chức tước hay hàng hóa, Montelli bán hy vọng.
 Con sắp bận rộn lắm rồi, và con cũng đang thích nghi với công việc khá tốt. Chỉ có điều trên tàu chỉ có mình con làm bảo vệ, nên chẳng có ai để nói chuyện.
 Con sẽ cố gắng hết sức, và khi trở về, con sẽ đưa mẹ đến Ragunna để mẹ cũng được tận hưởng cuộc sống ở đây.
-T000000:::Timeworn Logbook 2
-Số A Diary_#17
+T000000:::Sổ Nhật Ký Cũ 2
+Số Nhật Ký_#17
 Mẹ ơi, con nhớ mẹ.
 Ở đây sương mù dày đặc, cứ mỗi lần như thế này, con lại nhớ về thời còn nhỏ, khi chúng ta còn ở bên nhau.
 Chúng ta từng sống trong một ngôi nhà ở vùng quê. Đó là một căn nhà tranh, mùa hè, con nghe tiếng rơm khô trên mái kêu lép bép dưới ánh nắng. Mùa đông, tường nhà lại ẩm ướt.
@@ -33541,12 +33496,12 @@
 Con vừa đi qua màn sương mù trên lộ trình. Cảm giác như một giấc mơ đáng sợ.
 Nhưng mẹ đừng lo cho con. Sổ tay an toàn nói rằng sương mù này có thể gây ảo giác, nhưng vô hại. Con đã vượt qua an toàn rồi. Giờ con cần kiểm tra lại hàng hóa, phòng trường hợp có ai lấy mất gì trong lúc con mơ màng.
 Con nhớ mẹ lắm, mẹ ơi. Đừng quên lời con hứa nhé. Khi con đã tạo dựng được tên tuổi ở đây, con sẽ đưa mẹ đến Ragunna.
-T000000:::Timeworn Logbook 3
-Số A Diary_#29
+T000000:::Sổ Nhật Ký Cũ 3
+Số Nhật Ký_#29
 Mẹ ơi, mẹ đừng lo. Con sẽ về nhà và gặp mẹ sớm thôi.
 Hôm kia trời nhiều mây quá, chắc mấy con Nimbus Wraith cũng buồn lắm. Lẽ ra chúng ta không nên khởi hành, nhưng vì buổi đấu giá sắp tới, con phải đảm bảo món hàng được giao đúng hạn.
-Quests này được gia đình Montelli giao cho con, con không thể làm họ thất vọng.
-Sugar đi có hơi vòng, nhưng vì các tàu khác đã rời bến và Giáo Đoàn cử Lucerna lên tàu, con nghĩ sẽ ổn thôi.
+Nhiệm vụ này được gia đình Montelli giao cho con, con không thể làm họ thất vọng.
+Đường đi có hơi vòng, nhưng vì các tàu khác đã rời bến và Giáo Đoàn cử Lucerna lên tàu, con nghĩ sẽ ổn thôi.
 Mẹ đừng lo. Gia đình Montelli đã tăng cường thêm người cho đoàn, và với sự hiện diện của Giáo Đoàn, mọi thứ sẽ ổn cả. Ừ, sẽ ổn thôi.
 Con nên kể mẹ nghe chuyện gì đó vui vui. Sau khi hoàn thành nhiệm vụ này, con sẽ có thời gian nghỉ để về thăm mẹ.
 Dù công việc của con chỉ quanh quẩn trong cabin, nhưng dọc đường đi, con cũng thấy được nhiều điều thú vị.
@@ -33560,8 +33515,8 @@
 Theo bản đồ lộ trình, chúng ta sẽ đi qua một nơi gọi là Atrium of Reflections. Con chưa từng nghe tên nơi này bao giờ, nhưng các tiền bối nói chúng ta thường tránh nó trừ khi thật sự cần thiết.
 Nhưng con sẽ cẩn thận. Mẹ đừng lo cho con. Chỉ là một thử thách nhỏ thôi. Công việc khó khăn thì phải làm, đúng không mẹ?
 Chỉ cần con nỗ lực, con biết mình sẽ nhận được phần thưởng xứng đáng. Mẹ cứ đợi con nhé. Con sẽ đưa mẹ đến Ragunna.
-T000000:::Timeworn Logbook 4
-Số A Diary_#31
+T000000:::Sổ Nhật Ký Cũ 4
+Số Nhật Ký_#31
 Mẹ ơi, khi con về, con chỉ muốn ôm mẹ một lát thôi được không?
 Con đã đọc hết sổ tay an toàn, nhưng không tìm thấy gì về tình huống con đang gặp phải.
 Mẹ còn nhớ không? Khi con còn nhỏ, mỗi khi gió nổi lên vào ban đêm, con luôn sợ hãi. Thực ra là vì tấm rèm mỏng trong phòng con. Trên đó thêu hình những người đang cầu nguyện trong Giáo Đoàn. Khi gió đêm thổi qua, bóng của họ lay động như sắp vỡ tan ra vậy.
@@ -33646,8 +33601,8 @@
       <c r="M427" t="inlineStr">
         <is>
           <t>... rất ít người, kể cả trong gia tộc Montelli, biết được Vitreum Dancer xuất hiện từ khi nào, dù những Hồi Âm kín đáo, không nổi bật này đã phục vụ gia tộc từ lâu. Thực tế, hầu hết thành viên Montelli chỉ coi chúng là lực lượng bảo vệ nội bộ. Vì thế, ít ai để ý rằng không có hai Vitreum Dancer nào giống nhau.
-Những kiến thức thu thập từ các tác phẩm kính màu trong đống đổ nát quanh Ragunna cho thấy Vitreum Dancer từng là những Tần số Discord. Chúng xuất hiện trong các bức kính màu cùng với những mô tả chung về tôn giáo của The Order. Đến nay, các nhà thám hiểm Montelli vẫn chưa tìm thấy hai tấm kính màu nào giống hệt nhau. Các nghệ nhân của The Order đã cố tình thay đổi bố cục của những tấm kính kể cùng một câu chuyện hay chủ đề. Điều này cho thấy tần số của Vitreum Dancer hiện đại đều chứa đựng thông tin độc nhất, giống như tổ tiên Discord của chúng.
-Theo cuốn "Sự Giàu Có và Legendary của The Montelli Family", nguồn gốc của Vitreum Dancer bắt nguồn từ thời một tổ tiên Montelli nhận được vòng Nguyệt Quế tại Carnevale từ tay Imperator, người sau đó đã chỉ thị ông đến một tòa tháp bị The Order bỏ hoang. Khi trở về, ông không tiết lộ những gì mình thấy và cấm tất cả thành viên Montelli lại gần tòa tháp đó. Không nghi ngờ gì nữa, tổ tiên Montelli này đã mang về Vitreum Dancer đầu tiên. On his deathbed, lời trăn trối cuối cùng của ông là Oracle của Sentinel sẽ không can thiệp vào gia tộc Montelli ở hiện tại, nhưng sẽ quyết định tương lai của họ.
+Những kiến thức thu thập từ các tác phẩm kính màu trong đống đổ nát quanh Ragunna cho thấy Vitreum Dancer từng là những Tần số Tacet Discord. Chúng xuất hiện trong các bức kính màu cùng với những mô tả chung về tôn giáo của The Order. Đến nay, các nhà thám hiểm Montelli vẫn chưa tìm thấy hai tấm kính màu nào giống hệt nhau. Các nghệ nhân của The Order đã cố tình thay đổi bố cục của những tấm kính kể cùng một câu chuyện hay chủ đề. Điều này cho thấy tần số của Vitreum Dancer hiện đại đều chứa đựng thông tin độc nhất, giống như tổ tiên Tacet Discord của chúng.
+Theo cuốn "Sự Giàu Có và Huyền Thoại của Gia Tộc Montelli", nguồn gốc của Vitreum Dancer bắt nguồn từ thời một tổ tiên Montelli nhận được vòng Nguyệt Quế tại Carnevale từ tay Imperator, người sau đó đã chỉ thị ông đến một tòa tháp bị The Order bỏ hoang. Khi trở về, ông không tiết lộ những gì mình thấy và cấm tất cả thành viên Montelli lại gần tòa tháp đó. Không nghi ngờ gì nữa, tổ tiên Montelli này đã mang về Vitreum Dancer đầu tiên. Trên giường bệnh, lời trăn trối cuối cùng của ông là Oracle của Sentinel sẽ không can thiệp vào gia tộc Montelli ở hiện tại, nhưng sẽ quyết định tương lai của họ.
 Và từ đó, tòa tháp bị phong tỏa với tất cả thành viên Montelli sau này, còn huyền thoại về nguồn gốc của Vitreum Dancer dần chìm vào quên lãng khi đội ngũ của chúng ngày càng đông đảo.</t>
         </is>
       </c>
@@ -33723,11 +33678,11 @@
           <t>...Hôm nay chúng ta vẫn chưa tìm thấy nó.
 Một sinh vật to lớn như thế không dễ gì che giấu dấu vết. Trước khi phát hiện nơi nó xuất hiện lần tới, chúng ta không được lại gần bờ biển, và không cơn bão nào có thể ngăn cản chúng ta.
 Biển gào thét, bão tố đen như mực của con mực đang hấp hối, boong tàu chao đảo trong giông tố, cột buồm trôi về phía xác tàu ở Forgotten Sea, những thủy thủ với gương mặt sạm nắng, nứt nẻ như vực sâu đại dương, con bạch tuộc dài hàng trăm mét... Và chúng ta, những kẻ săn đuổi bị nguyền rủa, truy lùng nó đến tận cùng thế giới.
-Hãy nghĩ xem, chúng ta thực sự tìm kiếm điều gì? Ta sẽ đánh cược đồng xu này đóng đinh vào chân ta.
-Giờ ta sẽ nói cho ngươi biết làm thế nào để chiến thắng. Chúng ta sẽ săn đuổi nó, băng qua Stormy Sea, xuyên qua Forgotten Sea, vượt qua mọi hòn đảo, dù có tên hay không tên, đến tận cùng thế giới. Máu và dầu của nó sẽ khiến đồng xu này trở nên vô giá.
-Còn ngươi, người cầm giáo từ phương Đông, khi dâng giáo lên thần linh, ngươi có chần chừ không? Liệu ngọn giáo từng uống máu thần linh có run rẩy trước đại dương? Lên nào, giơ cao vũ khí và bắt chéo trước mặt ta, như trong đấu trường! Hãy để ta thấy vinh quang mà ngươi sẽ ôm trọn trên sóng gió!
-Đưa rượu cho ta! Lại đây, hãy thề nguyền vì giàu sang, vì giấc mơ, vì tất cả những gì ta đã bỏ lại!
-Điều chúng ta tìm kiếm, điều ta tìm kiếm... là khoảnh khắc ấy.</t>
+Hãy nghĩ xem, chúng ta thực sự tìm kiếm điều gì? Tao sẽ đánh cược đồng xu này đóng đinh vào chân tao.
+Giờ tao sẽ nói cho mày biết làm thế nào để chiến thắng. Chúng ta sẽ săn đuổi nó, băng qua Stormy Sea, xuyên qua Forgotten Sea, vượt qua mọi hòn đảo, dù có tên hay không tên, đến tận cùng thế giới. Máu và dầu của nó sẽ khiến đồng xu này trở nên vô giá.
+Còn mày, người cầm giáo từ phương Đông, khi dâng giáo lên thần linh, mày có chần chừ không? Liệu ngọn giáo từng uống máu thần linh có run rẩy trước đại dương? Lên nào, giơ cao vũ khí và bắt chéo trước mặt tao, như trong đấu trường! Hãy để tao thấy vinh quang mà mày sẽ ôm trọn trên sóng gió!
+Đưa rượu cho tao! Lại đây, hãy thề nguyền vì giàu sang, vì giấc mơ, vì tất cả những gì ta đã bỏ lại!
+Điều chúng ta tìm kiếm, điều tao tìm kiếm... là khoảnh khắc ấy.</t>
         </is>
       </c>
     </row>
@@ -33801,15 +33756,15 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Ta đã thấy nó. Không còn nghi ngờ gì nữa. Cái sừng dài ấy, nhỏ giọt máu đen ngòm của biển cả. Chắc chắn &lt;i&gt;phải&lt;/i&gt; là nó rồi.
+          <t>Ta đã thấy nó. Không còn nghi ngờ gì nữa. Cái sừng dài ấy, nhỏ giọt máu đen ngòm của biển cả. Chắc chắn là nó rồi.
 Con thuyền ta thả xuống bị lật úp, cột buồm phía đuôi gãy nát, bảy ngọn giáo đã mất.
 Nhiều người hoảng sợ, giục ta quay đầu... Không, ta sẽ không dừng lại. Trong bảy ngọn giáo, bốn cái đã bị rung rớt, nhưng ba cái vẫn cắm sâu vào thân nó. Ta đã thấy chúng trên lưng nó, và những mảnh tinh thể vỡ vụn rơi xuống biển.
 Đây là ngày thứ năm mươi lăm.
 Chúng ta đâu có đuổi theo nó; chính nó đang chắn đường ta. Các người không hiểu sao? Chỉ khi giết được nó, ta mới rời khỏi căn phòng này và đến được điểm cuối của biển vô tận, nơi cánh buồm đã hứa với chúng ta.
-Think! Chúng ta đã chinh phục mọi vùng biển! Từ con Wyrm ăn Tacetite của Liên bang New đến con Dreadcurl Cuttle nuốt ký ức ở Biển Quên Lãng... Ta đã giết bao nhiêu con quái vật như thế? &lt;i&gt;Chúng ta&lt;/i&gt; đã giết bao nhiêu? Giờ thì con quái vật này đứng trước mặt ta! Mọi giấc mơ, mọi suy nghĩ của các người phải xoay quanh việc làm sao giết được nó!
+Suy nghĩ đi! Chúng ta đã chinh phục mọi vùng biển! Từ con Wyrm ăn Tacetite của Liên bang Mới đến con Dreadcurl Cuttle nuốt ký ức ở Biển Quên Lãng... Ta đã giết bao nhiêu con quái vật như thế? Chúng ta đã giết bao nhiêu? Giờ thì con quái vật này đứng trước mặt ta! Mọi giấc mơ, mọi suy nghĩ của các người phải xoay quanh việc làm sao giết được nó!
 Đưa ta cái tẩu đó, lão hút thuốc già. Ta đã đi qua màn khói với các người... Ta bảo thật, nó đã lấy đi một chân của ta, và ta sẽ lấy lại từ trái tim nó!
 Ta đã thấy ngày nó chết. Máu nó sẽ cháy rụi trên biển, vây nó sẽ rũ xuống, nó sẽ lật ngửa, và cuối cùng, những mảng trắng đục và đỏ thẫm sẽ hiện ra...
-Rồi mọi lời ta hứa với các người sẽ thành hiện thực. Các người sẽ có tất cả những gì của ta, dù là tiền bạc, dầu hay niềm tin—dù ta chẳng tin vào thần thánh nào. Các người có thể lấy hết, kể cả con tàu này. Chúng ta sẽ giết nó. Right giết nó. Đây là số phận của ta, của các người, và của con tàu này.
+Rồi mọi lời ta hứa với các người sẽ thành hiện thực. Các người sẽ có tất cả những gì của ta, dù là tiền bạc, dầu hay niềm tin—dù ta chẳng tin vào thần thánh nào. Các người có thể lấy hết, kể cả con tàu này. Chúng ta sẽ giết nó. Phải giết nó. Đây là số phận của ta, của các người, và của con tàu này.
 Giờ thì ta sẽ dập tắt ngọn lửa của các người, dù là nỗi sợ trong tim hay là khói trong tẩu thuốc.</t>
         </is>
       </c>
@@ -33967,7 +33922,7 @@
 "Hạ buồm chính! Chết tiệt, chúng ta đang lún quá sâu! Giữ cột buồm khỏi chạm nước!"
 "Nó biến đi đâu rồi!? Nó biến đi đâu rồi!? Vừa mới đây thôi mà!"
 "Giữ nó trong tầm ngắm! Đừng để nó chạy thoát!"
-"Cuối cùng cũng đối mặt! Giờ ta sẽ giết ngươi!!!"
+"Cuối cùng cũng đối mặt! Giờ tao sẽ giết mày!!!"
 "Quay mũi sang trái! Nhanh!!!!"</t>
         </is>
       </c>
@@ -34057,7 +34012,7 @@
 Rồi đến tiếng ròng rọc siết chặt và tiếng sườn tàu vỡ nát.
 Sau đó, chỉ còn bóng tối. Trong khoảng không ấy, tôi không thấy con tàu, không thấy đồng đội, cũng không thấy nó.
 Lúc đầu, cái "chân" của tôi co giật không ngừng... Tôi tưởng mình đã chết.
-Tôi nằm trên bãi biển, một mình. None tàu, không có đồng đội, cũng chẳng thấy dấu vết của nó.
+Tôi nằm trên bãi biển, một mình. Không có tàu, không có đồng đội, cũng chẳng thấy dấu vết của nó.
 Tay tôi không dính một giọt máu nào của nó, không có bánh lái, không có dây thừng, không có lao. Chẳng còn gì để bấu víu.
 Nhưng cơn gió biển thật lạ lẫm. Tôi nhận ra mình chưa từng đặt chân đến bãi biển này. Từ khi rời Cape Bedford, tôi nhớ rõ từng bến cảng và bãi biển đi qua, nhưng nơi này... hoàn toàn xa lạ.
 Mãi đến khi một chàng trai trẻ, mặc trang phục lạ, đá vào ủng tôi để kiểm tra xem tôi còn sống không, tôi mới nhận ra mình không xuống địa ngục, cũng chẳng lên thiên đường.
@@ -34065,7 +34020,7 @@
 "Đảo Riccioli, Rinascita."
 "Rinascita..."
 "Cậu gặp nạn trên biển à?"
-"Con tàu của tôi... Teamwork của tôi..."
+"Con tàu của tôi... Đồng đội của tôi..."
 "Không còn ai khác ở gần đây đâu."
 "Nếu vậy... thì cuối cùng, chỉ có mình tôi sống sót thôi sao..."</t>
         </is>
@@ -34141,8 +34096,8 @@
           <t>...Sau này, ta mới nhận ra rằng chúng ta đã được "ban phước."
 Người dân Rinascita nói rằng cá voi dẫn dắt những con tàu và thủy thủ đã chết ngoài biển đến thế giới bên kia, như một người lái đò của địa ngục. Ta nghe nói những thương nhân ở Biển Quên Lãng có thể cân ký ức và linh hồn trên chiếc cân của họ, đổi lấy một lượng vàng tương đương.
 Nhưng không hiểu sao, tất cả chúng ta vẫn còn sống. Hay đúng hơn, chúng ta tồn tại trong trạng thái lưng chừng giữa sự sống và cái chết.
-Đúng vậy, theo thời gian, ta đã tìm thấy Starbuck và Queequeg trên hòn đảo này. Họ vẫn còn sống. "Nó," con cá voi mà họ gọi là "Cetus Kẻ Phá Shui Triều," cũng vẫn còn sống.
-Do sao đây có thể gọi là "phước lành"? Đây chẳng qua là một "lời nguyền" thôi! Ta không thể chấp nhận điều này!
+Đúng vậy, theo thời gian, ta đã tìm thấy Starbuck và Queequeg trên hòn đảo này. Họ vẫn còn sống. "Nó," con cá voi mà họ gọi là "Cetus Kẻ Phá Thủy Triều," cũng vẫn còn sống.
+Làm sao đây có thể gọi là "phước lành"? Đây chẳng qua là một "lời nguyền" thôi! Ta không thể chấp nhận điều này!
 Một khi ta đã trả thù xong, cái chết có thể đến với ta. Nhưng nếu ta thất bại, ta không thể chịu đựng được việc tiếp tục tồn tại trong thế giới này như một món đồ chơi cho những kẻ ta muốn trả thù! Số phận của ta phải do ta quyết định, và chỉ có cái chết thật sự mới có thể kết thúc cuộc chinh phạt này.
 Họ không hiểu. Con cá voi đó, dù trông hiền lành và dịu dàng, lại xảo quyệt và hung bạo. Nó biến cái chết thành một sự vĩnh cửu bất công, biến cuộc trả thù của ta thành một chú thích nhỏ trong trò chế giễu của nó đối với biển cả… Không, ta sẽ không bao giờ chấp nhận điều này. Ta sẽ không bao giờ thỏa hiệp!</t>
         </is>
@@ -34223,9 +34178,9 @@
 Và có vẻ như con cá voi đang chơi đùa với tôi. Kể từ lần đó, dù trên biển hay trên bờ, tôi chưa bao giờ nhìn thấy nó lần nữa. Tôi không muốn từ bỏ. Tôi từ chối từ bỏ. Chỉ cần tôi có thể giết nó, tôi sẽ được giải thoát khỏi "phước lành" giống như lời nguyền này và tìm được sự an nghỉ vĩnh hằng.
 Nhưng tôi... giờ đã quá già. Tôi không còn sức để nâng một ngọn lao móc. Tôi không thể chiến đấu với con quái vật khổng lồ đó trên một trong những chiếc "Gondola" bé nhỏ này.
 Vâng, lý tưởng, niềm tin, số phận, mối thù của tôi—tất cả đều đã biến mất. Tất cả đã bị biển cả xa lạ này nuốt chửng.
-Tất nhiên, anh có thể cười nhạo tôi. Sợi dây thừng của ngọn lao móc đó, khi tôi còn sống, đã trói chặt tôi vào con cá voi. Ngay cả sau khi chết, tôi vẫn bị nó trói buộc. Previous đây, tôi không muốn cắt đứt sợi dây đó. Giờ đây, tôi vẫn không muốn... Nhưng tôi không còn sức để kéo nó xuống vực thẳm đen tối của biển cả nữa.
+Tất nhiên, anh có thể cười nhạo tôi. Sợi dây thừng của ngọn lao móc đó, khi tôi còn sống, đã trói chặt tôi vào con cá voi. Ngay cả sau khi chết, tôi vẫn bị nó trói buộc. Trước đây, tôi không muốn cắt đứt sợi dây đó. Giờ đây, tôi vẫn không muốn... Nhưng tôi không còn sức để kéo nó xuống vực thẳm đen tối của biển cả nữa.
 Một thời gian sau, một chàng trai trẻ đến tìm tôi. Anh ta tự giới thiệu là Ishmael, một thủy thủ tập sự, và muốn học cách đánh cá.
-Lúc đó, tôi nhớ lại rằng trước chuyến đi cuối cùng của Pequod, có một thủy thủ tên Ishmael ở bến tàu Bedford. Nhưng anh ta không lên tàu của tôi. Anh ta ở lại cảng, và nếu vẫn còn sống trên biển, có lẽ giờ anh ta cũng đã già như tôi. Thật sự trớ trêu...</t>
+Lúc đó, tôi nhớ lại rằng trước chuyến đi cuối cùng của Pequod, có một thủy thủ tên Ishmael ở bến tàu Bedford. Nhưng anh ta không lên tàu của tôi. Anh ta ở lại cảng, và nếu vẫn còn sống trên biển, có lẽ giờ anh ta cũng đã già như tôi. Thật trớ trêu...</t>
         </is>
       </c>
     </row>
@@ -34298,7 +34253,7 @@
 Với những kẻ như ta, ngày tận thế cũng là ngày biển cả khép lại.
 Ta sinh ra bên bờ biển, chết trên biển, và cuối cùng cũng sẽ vùi thân dưới đáy biển.
 Lần này, ta không giết được nó. Nhưng lần tới, ta nhất định sẽ giết nó... nhất định.
-...Cảm ơn ngươi, Trưởng nhóm đến từ vùng đất xa xôi.</t>
+...Cảm ơn ngươi, Đội trưởng đến từ vùng đất xa xôi.</t>
         </is>
       </c>
     </row>
@@ -34366,7 +34321,7 @@
       <c r="M436" t="inlineStr">
         <is>
           <t>...Ta là Ahab, còn các ngươi là thủy thủ đoàn của ta. Các ngươi chỉ được tin tưởng ta, duy nhất ta thôi.
-Anh ấy không thể nhốt chúng ta ở đây mãi được.
+Hắn không thể nhốt chúng ta ở đây mãi được.
 Chúng ta phải đợi đến khi Pequod sửa xong, rồi sẽ rời đi... không bao giờ quay lại.</t>
         </is>
       </c>
@@ -34569,11 +34524,11 @@
       <c r="M439" t="inlineStr">
         <is>
           <t>Cha thân yêu,
-Con viết thư này cho cha từ một góc thư viện. Theo thời gian, con đã dần thích nghi với cuộc sống ở chủng viện. Những lúc rảnh rỗi, con thường đến thư viện này để đọc những bản văn cổ và nghiên cứu giáo lý về Sự Thống Yi. Nhưng càng tìm hiểu sâu về lịch sử của Rinascita, con càng cảm thấy nó bị bao phủ bởi một làn sương mù chưa được giải đáp. Có quá nhiều câu hỏi chưa lời giải về đức tin của chúng ta, ân sủng chúng ta nhận được, và thảm họa từng giáng xuống chúng ta.
-May mắn thay, nhiều chủ đề nhạy cảm công khai và thậm chí cả những điều cấm kỵ đều được coi là đối tượng nghiên cứu học thuật ở chủng viện. Con sẽ dành thời gian để tìm hiểu và khám phá chúng. Tất nhiên, con cũng không quên kiếm thuật mà mẹ đã dạy. Gần đây, con đã đăng ký luyện tập đấu kiếm với các Harbinger Thần Linh... Đừng lo, con sẽ không để mình bị thương đâu.
+Con viết thư này cho cha từ một góc thư viện. Theo thời gian, con đã dần thích nghi với cuộc sống ở chủng viện. Những lúc rảnh rỗi, con thường đến thư viện này để đọc những bản văn cổ và nghiên cứu giáo lý về Sự Thống Nhất. Nhưng càng tìm hiểu sâu về lịch sử của Rinascita, con càng cảm thấy nó bị bao phủ bởi một làn sương mù chưa được giải đáp. Có quá nhiều câu hỏi chưa lời giải về đức tin của chúng ta, ân sủng chúng ta nhận được, và thảm họa từng giáng xuống chúng ta.
+May mắn thay, nhiều chủ đề nhạy cảm công khai và thậm chí cả những điều cấm kỵ đều được coi là đối tượng nghiên cứu học thuật ở chủng viện. Con sẽ dành thời gian để tìm hiểu và khám phá chúng. Tất nhiên, con cũng không quên kiếm thuật mà mẹ đã dạy. Gần đây, con đã đăng ký luyện tập đấu kiếm với các Sứ Giả Thần Linh... Đừng lo, con sẽ không để mình bị thương đâu.
 Con nhớ cha từng nói Avinoleum rộng lớn đến mức luôn khiến người ta lạc lối. Năm nay, con đã đi khắp nơi trong chủng viện, trừ những chỗ bị cấm. Con đã vẽ một &lt;b&gt;bản đồ lộ trình đơn giản&lt;/b&gt;, dễ đọc hơn bản đồ của Dòng. Con sẽ gửi cho cha sau.
 Với thanh kiếm và chiếc đèn lồng, con tiến bước qua màn sương.
-Kính gửi Unclea Tể Tối Cao,
+Kính gửi Chúa Tể Tối Cao,
 Rosalie</t>
         </is>
       </c>
@@ -34643,7 +34598,7 @@
         <is>
           <t>Hãy tin người láng giềng, nếu không đất đai vẫn sẽ hoang vu. Đoàn kết các hòn đảo, nếu không đê điều vẫn sẽ không được dựng lên.
 Anh em ơi, hãy để trời, đất và biển cả được hợp nhất.
-Path chính nghĩa được thắp sáng bởi ngọn lửa thiêng &lt;color=#ffd12f&gt;Unity&lt;/color&gt;.</t>
+Con đường chính nghĩa được thắp sáng bởi ngọn lửa thiêng &lt;color=#ffd12f&gt;Đoàn Kết&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -34714,7 +34669,7 @@
       <c r="M441" t="inlineStr">
         <is>
           <t>Ta đã chinh phục mảnh đất này và dựng lên một pháo đài bất khả xâm phạm trên đỉnh núi.
-Ngay từ thuở sơ khai, các Echoes đã sát cánh cùng ta—trung thành, bất khuất và kiên định.
+Ngay từ thuở sơ khai, các Echo đã sát cánh cùng ta—trung thành, bất khuất và kiên định.
 Hỡi những người dũng cảm của Rinascita, những chiến binh tương lai. Hãy để tượng đài này làm chứng cho lòng can đảm của các ngươi.
 &lt;color=#ffd12f&gt;Khởi đầu là sư tử, uy mãnh vô song.&lt;/color&gt;
 &lt;color=#ffd12f&gt;Kết thúc là hiệp sĩ, trung thành đến hơi thở cuối cùng.&lt;/color&gt;
@@ -34865,12 +34820,12 @@
           <t>Sau vòng tuyển chọn đầu tiên, các ngươi phải tiến về phía trước. Tranh đấu, nỗ lực, chiến đấu để giành lấy vị trí của mình. Thể hiện sức mạnh, trí tuệ, lòng dũng cảm và sự kiên trì khi bước vào vực sâu để trở thành Trinh Nữ Fisalia.
 Người đứng đầu gia tộc Fisalia sẽ trao cho người được chọn một loại thuốc tiên có thể ban cho bất kỳ điều ước nào—dù là sắc đẹp vĩnh cửu hay sự chữa lành kỳ diệu. Mọi khát khao đều có thể được đáp ứng.
 Ứng cử viên:
-&lt;color=PurpleD&gt;Mandragora Fisalia, Hebenon Fisalia, Cantarella Fisalia.&lt;/color&gt;
-Chloe Fisalia, Annis Fisalia, Marina Fisalia.
+&lt;color=PurpleD&gt;Mandragora Fisalia, Hebenon Fisalia, Cantarella Fisalia...&lt;/color&gt;
+Chloe Fisalia, Annis Fisalia, Marina Fisalia...
 Thử thách đầu tiên:
 Độc dược chính là nền tảng của danh tiếng Fisalia.
 Hãy để nó thử thách ý chí của các ngươi.
-Trong thử thách này, các ngươi phải chọn ra &lt;color=RedD&gt;ba Quả Sea Apple độc nhất&lt;/color&gt; từ vực sâu và mang chúng về bằng mọi giá.
+Trong thử thách này, các ngươi phải chọn ra &lt;color=RedD&gt;ba Quả Táo Biển độc nhất&lt;/color&gt; từ vực sâu và mang chúng về bằng mọi giá.
 Lưu ý: Việc sử dụng bất kỳ công cụ bên ngoài nào để xác định độc tính hoặc hỗ trợ lấy chúng đều bị nghiêm cấm.
 Mong sức mạnh huyết mạch Fisalia sẽ thức tỉnh trong các ngươi.</t>
         </is>
@@ -34947,13 +34902,13 @@
       <c r="M444" t="inlineStr">
         <is>
           <t>Gửi Annis thân mến,
-Tomorrow là kỳ Trial rồi! Em lo lắng quá… nhưng cũng hơi háo hức nữa.
+Ngày mai là kỳ Thử Thách rồi! Em lo lắng quá… nhưng cũng hơi háo hức nữa.
 Những người Fisalia thật sự rất đáng sợ… Một số thì vênh váo, kiêu ngạo, số khác lại… kỳ lạ, như bước ra từ cơn ác mộng vậy.
 Chắc họ phải rất giỏi về độc dược nhỉ? Chỉ nghĩ đến việc đối đầu với họ thôi đã thấy bất an rồi…
 Em tình cờ nghe thấy cô gái Fisalia kia thì thầm rằng chất độc cũng có thể là thuốc. Chỉ cần liều lượng vừa đủ, nó sẽ không hại ai mà còn cứu được họ.
-Có lẽ dù không vượt qua được kỳ Trial, em vẫn có thể học được vài bí mật về độc dược của họ, tìm hiểu thành phần. Rồi biết đâu, em có thể bào chế thứ gì đó để giúp Jojo.
+Có lẽ dù không vượt qua được kỳ Thử Thách, em vẫn có thể học được vài bí mật về độc dược của họ, tìm hiểu thành phần. Rồi biết đâu, em có thể bào chế thứ gì đó để giúp Jojo.
 Nghĩ vậy thì thấy đỡ sợ hơn một chút. Vì Jojo, thì chút độc dược có là gì chứ!
-Tomorrow cẩn thận nhé, Annis yêu quý. Chúng ta không có dòng máu Fisalia, và họ biết nhiều về độc dược hơn chúng ta nhiều.
+Ngày mai cẩn thận nhé, Annis yêu quý. Chúng ta không có dòng máu Fisalia, và họ biết nhiều về độc dược hơn chúng ta nhiều.
 Thân mến,
 Chloe</t>
         </is>
@@ -35114,10 +35069,10 @@
       <c r="M446" t="inlineStr">
         <is>
           <t>████ thân mến,
-Những trái Sea Apple mạnh đến mức kinh khủng. Chỉ cần ngửi thôi đã đủ khiến tôi nghẹt thở, như thể cổ họng bị bóp nghẹt. Tôi gần như không thốt nên lời. Khi tỉnh lại, miệng tôi nếm thấy vị kim loại.
+Những trái Táo Biển mạnh đến mức kinh khủng. Chỉ cần ngửi thôi đã đủ khiến tôi nghẹt thở, như thể cổ họng bị bóp nghẹt. Tôi gần như không thốt nên lời. Khi tỉnh lại, miệng tôi nếm thấy vị kim loại.
 Tôi không đủ sức chạm vào một quả, huống chi mang về. Tất cả những gì tôi làm được chỉ là đứng nhìn từ xa trong bất lực.
 Chúng tròn và đỏ, giống như táo… hay có lẽ là cà chua. Ở thị trấn Egla, chúng tôi có cả cánh đồng cà chua…
-Right chăng vì tôi không phải là một Fisalia chính thống nên không thể đánh thức khả năng đặc biệt hay miễn nhiễm với chất độc?
+Phải chăng vì tôi không phải là một Fisalia chính thống nên không thể đánh thức khả năng đặc biệt hay miễn nhiễm với chất độc?
 Không, tôi không được bỏ cuộc. Chắc hẳn là do tôi chưa cố gắng đủ.
 Annis cũng không phải Fisalia, nhưng cô ấy đã vượt qua, dù chúng ta sẽ không bao giờ được nghe giọng nói của cô ấy nữa. Chất độc đã hủy hoại dây thanh quản của cô ấy, và cô ấy sẽ không bao giờ nói được nữa...
 Giờ không phải lúc để khóc. Tôi cũng phải mạnh mẽ. Vì Jojo, tôi sẽ không bỏ cuộc.
@@ -35189,7 +35144,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Mandragora Fisalia, Hebenon Fisalia, Cantarella Fisalia.
+          <t>Mandragora Fisalia, Hebenon Fisalia, Cantarella Fisalia...
 Annis Fisalia…
 &lt;color=PurpleD&gt;Những ứng viên trên đã vượt qua thử thách độc dược.
 Hãy nghỉ ngơi một chút và chuẩn bị cho thử thách thứ hai.&lt;/color&gt;</t>
@@ -35352,8 +35307,8 @@
       <c r="M449" t="inlineStr">
         <is>
           <t>Công chúa Hiệp Sĩ: Sau khi Vương Miện Gai thuộc về ta, mọi người trong lâu đài sẽ được sống tốt đẹp hơn!
-Công chúa Pháp Sư: Ừm... Ta chẳng muốn gì cả, chỉ ở đây vì nghĩa vụ gia tộc thôi. Sau chuyện này, ta sẽ rời khỏi nơi buồn tẻ này để hít thở không khí bên ngoài. Enter thời điểm này trong năm, hoa trên núi và đồng cỏ chắc đang nở rộ... có khi ta sẽ tìm được giống mới để bào chế thuốc.
-Công chúa Quý Tộc: I tôi hơi sợ, và không muốn tiếp tục nữa. Nhưng... nhưng...
+Công chúa Pháp Sư: Ừm... Ta chẳng muốn gì cả, chỉ ở đây vì nghĩa vụ gia tộc thôi. Sau chuyện này, ta sẽ rời khỏi nơi buồn tẻ này để hít thở không khí bên ngoài. Vào thời điểm này trong năm, hoa trên núi và đồng cỏ chắc đang nở rộ... có khi ta sẽ tìm được giống mới để bào chế thuốc.
+Công chúa Quý Tộc: Tôi... tôi hơi sợ, và không muốn tiếp tục nữa. Nhưng... nhưng...
 Công chúa Hiệp Sĩ: Không được rút lui!
 Công chúa Dân Dã: Để chữa bệnh cho Jojo, tôi sẽ không lùi bước. Tôi sẽ lấy được thuốc tiên chữa bách bệnh và trở về nhà trong hạnh phúc.
 Công chúa Thiên Thần: Mọi điều ước của các ngươi sẽ thành hiện thực.</t>
@@ -35431,7 +35386,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Trial Thứ Hai:
+          <t>Thử Thách Thứ Hai:
 Để giành lấy danh hiệu Thiếu Nữ, ứng viên phải chứng tỏ sức mạnh để đưa ra những lựa chọn dứt khoát.
 Cảm xúc thái quá chính là điểm yếu và gánh nặng cho bất kỳ ứng viên xứng đáng với danh hiệu này.
 Mỗi người tham gia phải bắt được &lt;color=RedD&gt;con sứa độc nhất&lt;/color&gt; dưới biển và mang về địa điểm này. Khi trở về, các ngươi sẽ bắt cặp với một ứng viên khác và trao đổi chiến lợi phẩm. Ứng viên nào sở hữu con sứa độc hơn sẽ giành chiến thắng.
@@ -35668,8 +35623,8 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>&lt;color=PurpleD&gt;Cantarella Fisalia và Annis Fisalia&lt;/color&gt; đã vượt qua Trial Thứ Hai.
-Mất đi hai thành viên thân yêu là nỗi đau lớn với tất cả chúng ta. Nhưng là những Fisalia, bổn phận và vinh dự của chúng ta là tiếp tục các Trial.
+          <t>&lt;color=PurpleD&gt;Cantarella Fisalia và Annis Fisalia&lt;/color&gt; đã vượt qua Thử Thách Thứ Hai.
+Mất đi hai thành viên thân yêu là nỗi đau lớn với tất cả chúng ta. Nhưng là những Fisalia, bổn phận và vinh dự của chúng ta là tiếp tục các Thử Thách.
 Vì sự trỗi dậy của Maiden, chúng ta kiên định, sẵn sàng gánh chịu mọi hy sinh.</t>
         </is>
       </c>
@@ -35864,7 +35819,7 @@
 "Đau! Đau! Đau! Đau! Đau... quá đỗi!"
 (*……（@！#￥#*（……*￥▇▇▇▇▇▇%&amp;#%￥#%&amp;￥%▇▇#……%
 "Bóng tối. Lạnh lẽo. Không cảm giác. Không gì cả."
-"Không thuốc tiên. Không ước nguyện. Không thiên thần. Không Upper đế."
+"Không thuốc tiên. Không ước nguyện. Không thiên thần. Không Thượng đế."
 "Không đầu. Không thân. Không máu. Không hồn.
 "Tôi không tồn tại."</t>
         </is>
@@ -35934,10 +35889,10 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Ta chân thành tìm kiếm một trái tim nhân hậu đưa ta đến Kho Tàng Echoes của Averardo Vault!
+          <t>Ta chân thành tìm kiếm một trái tim nhân hậu đưa ta đến Kho Tàng Echo của Hầm Averardo!
 Nếu được lựa chọn, ta thà sống một cuộc đời ngắn ngủi nhưng ý nghĩa còn hơn là kéo dài một kiếp sống tầm thường.
-——Bakethoven the Echoes
-(Ghi chép bởi một người qua đường tốt bụng. Xin hãy giúp đỡ, nó thực sự muốn trưởng thành như một Echoes.)</t>
+——Bakethoven the Echo
+(Ghi chép bởi một người qua đường tốt bụng. Xin hãy giúp đỡ, nó thực sự muốn trưởng thành như một Echo.)</t>
         </is>
       </c>
     </row>
@@ -36012,7 +35967,7 @@
 Nội dung:
 Lạc trên vách đá, rơi xuống biển sâu.
 Nếu thế gian này còn thần linh, xin hãy lắng nghe lời khẩn cầu thành tâm của chúng tôi:
-"Xin hãy để những linh hồn chìm sâu dưới vực trở về cõi trần. Không chỉ trong Night Tưởng Nhớ, mà hãy để chúng tôi được trở về quê hương Egla vĩnh viễn."</t>
+"Xin hãy để những linh hồn chìm sâu dưới vực trở về cõi trần. Không chỉ trong Đêm Tưởng Nhớ, mà hãy để chúng tôi được trở về quê hương Egla vĩnh viễn."</t>
         </is>
       </c>
     </row>
@@ -36081,9 +36036,9 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Hahaha! Bravo Hãy hát lên một khúc ca cho dịp này nào! Sau lưng là Ragunna City, cuối cùng chúng ta cũng đã đến nơi các hiệp sĩ từng đóng quân.
+          <t>Hahaha! Tuyệt vời! Hãy hát lên một khúc ca cho dịp này nào! Sau lưng là Ragunna City, cuối cùng chúng ta cũng đã đến nơi các hiệp sĩ từng đóng quân.
 Ôi, những hiệp sĩ tuyệt vời sống theo tinh thần Korlacchi—!
-Chúng ta đốt lửa trại vào ban đêm và ngắm những chiếc cối xay gió vào ban ngày. Chúng ta cùng nhau chơi nhạc, hát ca dưới những cánh quạt quay tít. Villager gọi chúng ta là "những người hát rong bên lửa trại."
+Chúng ta đốt lửa trại vào ban đêm và ngắm những chiếc cối xay gió vào ban ngày. Chúng ta cùng nhau chơi nhạc, hát ca dưới những cánh quạt quay tít. Dân làng gọi chúng ta là "những người hát rong bên lửa trại."
 Khi cối xay gió ngừng quay, chúng ta lại rong ruổi dọc theo những dòng sông, hồ nước. Nhưng hơn tất cả, không gì sánh bằng được bay lượn trên cánh đồng vào một ngày trời trong.
 Từ trên cao, ta nhìn xuống vùng đất này đã bị thời gian làm nhăn nheo. Ánh nắng phủ lên những cột đá đổ nát của hiệp sĩ, nơi một cây cổ thụ nghìn năm đứng canh giữ trong im lặng, rễ của nó lan rộng khắp các khe đá. Khi gió đưa ta lướt trên mặt hồ, bóng phản chiếu của những mái ngói đỏ của Egla Town lấp lánh như những hạt lựu vương trên tấm lụa xanh biếc. Chiếc cối xay gió đỉnh đỏ nhìn xuống thị trấn, quay chầm chậm và vẫy gọi những lữ khách trở về.</t>
         </is>
@@ -36170,8 +36125,8 @@
 Ta giấu những vần thơ dở dang vào nếp mây.
 Lúc lá thư này đến tay ngươi, chúng ta đã xa cách.
 Ngươi lên đường mới, còn ta sẽ tấu khúc ca mới ở nơi nào đó xa thành phố.
-Chuyện về một cô gái và Nhà thơ cùng lênh đênh trên biển. Cô tưởng mình là loài chim "Icarus", dùng tài năng khám phá những ước nguyện thầm kín của những nhạc cụ bị bỏ quên. Họ giúp đỡ những đứa trẻ của Dàn Hợp Xướng, vén màn bản chất thật của thi ca. Nhưng cô gái ấy cũng mang theo bí mật, vì nàng mong muốn chia sẻ giọng hát của mình, để những ca sĩ không còn phải trốn sau lời dối trá, để sáng tạo được tuôn trào tự do. Đến giây phút quyết định, ký ức tuổi thơ vô tư cất tiếng hát cùng lời động viên của Nhà thơ đã giúp nàng chiến thắng nghi ngờ.
-chú chim giam cầm lao mình khỏi lồng, nhưng lần này, đôi bàn tay ân cần đã đỡ lấy và nâng niu nó.
+Chuyện về một cô gái và Nhà Thơ cùng lênh đênh trên biển. Cô tưởng mình là loài chim "Icarus", dùng tài năng khám phá những ước nguyện thầm kín của những nhạc cụ bị bỏ quên. Họ giúp đỡ những đứa trẻ của Dàn Hợp Xướng, vén màn bản chất thật của thi ca. Nhưng cô gái ấy cũng mang theo bí mật, vì nàng mong muốn chia sẻ giọng hát của mình, để những ca sĩ không còn phải trốn sau lời dối trá, để sáng tạo được tuôn trào tự do. Đến giây phút quyết định, ký ức tuổi thơ vô tư cất tiếng hát cùng lời động viên của Nhà Thơ đã giúp nàng chiến thắng nghi ngờ.
+Chú chim giam cầm lao mình khỏi lồng, nhưng lần này, đôi bàn tay ân cần đã đỡ lấy và nâng niu nó.
 Như lời Ngài Faroll từng nói: "Lời ca và âm nhạc là phép màu có thể vượt qua ranh giới thời gian và trải nghiệm cá nhân." Ta đã sớm hiểu ý nghĩa trong những vần thơ của họ.
 Và giờ đây. Cảm ơn ngươi, {PlayerName}, vì đã thấu hiểu thông điệp ấy.
 Khi sương mù thời gian dần tan trong tiếng thở dài,
@@ -36255,12 +36210,12 @@
         <is>
           <t>Đừng mang hoa đến mộ ta, vì ta không ở đó, bị giam cầm dưới tấm bia này.
 Ta ở trong làn gió biển trên những bức tường Ragunna. Ta là ánh sáng bình minh xuyên qua gai nhọn.
-Ta là chim ưng đêm với đôi cánh rực lửa, bay về phía Celestial Steed, hát ca ngợi và chiêm ngưỡng hình hài chân thật của nó.
+Ta là chim ưng đêm với đôi cánh rực lửa, bay về phía Thiên Mã, hát ca ngợi và chiêm ngưỡng hình hài chân thật của nó.
 Bầu trời đêm sẽ được thắp sáng bởi đôi cánh rực lửa, và ta sẽ tái sinh trong thi ca bất tử.
 Chừng nào con người còn thở, hãy ngước mắt lên mà nhìn: chừng nào bài thơ này còn sống, nó sẽ thổi hồn vào ta.
 &lt;alignright/&gt;——Hết
 Nhìn lại những gì ta viết trong lời tựa:
-Tập thơ này được gán cho *Song Vàng*. Mong rằng những vần thơ này có thể mang lại tia hy vọng cho những ai lạc lối trên hành trình số phận, và cho độc giả điều gì đó để suy ngẫm.
+Tập thơ này được gán cho *Khúc Ca Vàng*. Mong rằng những vần thơ này có thể mang lại tia hy vọng cho những ai lạc lối trên hành trình số phận, và cho độc giả điều gì đó để suy ngẫm.
 Hãy thu thập những âm tiết vàng rải rác này, vì chúng là báu vật tôi luyện trong lửa, là tia lửa còn sót lại của tư duy nhân loại.
 Và cuối cùng, cảm ơn vì đã mở cuốn sách này.</t>
         </is>
@@ -36341,7 +36296,7 @@
           <t>Các tác phẩm văn học lấy sinh khí từ hai nguồn: Người sáng tạo và độc giả.
 Người sáng tạo thổi hồn vào nó, còn độc giả giúp nó trường tồn qua việc đọc. Mỗi lần họ chia sẻ một tác phẩm hay công bố suy nghĩ, nhận xét của mình, họ lại tiếp thêm sinh khí cho nó.
 Có người cho rằng khái niệm "sinh mệnh của tác phẩm" thật mơ hồ, vì nó quá trừu tượng và vô hình.
-Tuy nhiên, ta có thể dễ dàng so sánh với sinh mệnh con người. Khi bàn về khái niệm sự sống, một chủ đề thiết yếu không thể bỏ qua chính là—tên gọi. Malee gọi là biểu tượng của sự tồn tại, một trong những dấu hiệu quan trọng nhất phân biệt từng cá thể. Nếu muốn cảm nhận sinh khí của một tác phẩm, cách trực tiếp nhất chính là cảm nhận tên gọi của nó, những cái tên mà người sáng tạo và độc giả ban tặng.
+Tuy nhiên, ta có thể dễ dàng so sánh với sinh mệnh con người. Khi bàn về khái niệm sự sống, một chủ đề thiết yếu không thể bỏ qua chính là—tên gọi. Tên gọi là biểu tượng của sự tồn tại, một trong những dấu hiệu quan trọng nhất phân biệt từng cá thể. Nếu muốn cảm nhận sinh khí của một tác phẩm, cách trực tiếp nhất chính là cảm nhận tên gọi của nó, những cái tên mà người sáng tạo và độc giả ban tặng.
 Tôi từng nghe một câu chuyện rùng rợn từ một vùng đất phía đông, kể về một người phụ nữ da trắng như tuyết đứng giữa bão tuyết, ôm đứa bé đang khóc ré lên trong tay, van xin người qua đường bế hộ đứa bé. Nếu có ai tốt bụng đồng ý, họ sẽ sớm nhận ra mình không thể buông tay ra được nữa, và bị đóng băng đến chết.
 Thú vị phải không? Nhưng đến đây, nó vẫn chỉ là một câu chuyện hấp dẫn, gợi lên nhiều hình ảnh riêng lẻ mà chưa thể tạo nên "sinh mệnh" trọn vẹn.
 Nhưng nếu ta đặt cho nó một cái tên thì sao? Chẳng hạn... "Người Tuyết". Chỉ cần cái tên này thôi đã khái quát toàn bộ câu chuyện và định hình bản chất của nó.
@@ -36506,7 +36461,7 @@
       <c r="M463" t="inlineStr">
         <is>
           <t>"...
-Bão cuốn ve sầu Vương Guo Nước trôi đi,
+Bão cuốn ve sầu Vương Quốc Nước trôi đi,
 Rơm rạ lênh đênh trong chén rượu gỗ sồi của làng.
 Những đêm Hè dài dằng dặc,
 Linh hồn lạc lối lang thang giữa phố phường ngõ hẻm.
@@ -36516,7 +36471,7 @@
 Tín đồ đo lường Độ Lệch của Thần Linh bằng chiếc cân mục nát.
 Sương giá phủ lên đồng tử kính màu,
 Gian xưng tội chứa đầy tro tàn lặng im.
-Night Đông không ngủ,
+Đêm Đông không ngủ,
 Một nghệ sĩ lang thang ôm cây đàn lạnh cóng,
 Tấu lên những âm thanh không bao giờ chạm tới.
 Với thân xác ta làm nhiên liệu, ngọn lửa hừng sẽ luyện nên vàng thật của Ragunna.
@@ -36750,13 +36705,13 @@
       <c r="M466" t="inlineStr">
         <is>
           <t>&lt;b&gt;Ngày 136 – Áp lực Bất thường (Nếu áp lực dai dẳng trong tai ta có thể gọi là vậy)&lt;/b&gt;
-Trong số đồ tiếp tế Chisa mang về hôm nay có một hộp cam, nhãn in ngày sản xuất đã lâu lắm rồi… nhưng giờ điều đó chẳng còn quan trọng. Những thứ gọi là "thực phẩm" này thực chất chỉ là Năng lượng Tàn Dư Dodgen lại.
+Trong số đồ tiếp tế Chisa mang về hôm nay có một hộp cam, nhãn in ngày sản xuất đã lâu lắm rồi… nhưng giờ điều đó chẳng còn quan trọng. Những thứ gọi là "thực phẩm" này thực chất chỉ là Năng lượng Tàn Dư nén lại.
 Chisa đưa hộp cam cho ta. Cô ngồi sang một bên, tay cầm một thanh thép lò xo nhặt được, dùng Forte của mình để cắt nó thành một lưỡi dao cong, biến nó thành vũ khí mới. Nhìn cô, ta chợt nhớ lại một ngày khác. Cô cũng ngồi như thế này, đang sắp xếp đồ tiếp tế trên ghế sofa, rồi quay sang hỏi Forte của ta thực sự là gì. Ta đưa cho cô một viên hổ phách nhỏ, bên trong lưu giữ ký ức về lần đầu chúng ta cùng làm việc tại căn cứ này: ánh đèn lờ mờ, cô đang sửa vũ khí, còn ta ghi chép lại những bất thường trong dòng chảy thời gian của thành phố. Đó là một đêm yên bình hiếm hoi, miễn là chúng ta lờ đi thực tế rằng vẫn đang bị giam cầm trong một thành phố bị phong tỏa khỏi thế giới bên ngoài.
 Để chống lại những diễn biến bất thường của Lament, ta từng thử học vài kỹ năng thực tế của Chisa, nhưng thất bại. Dĩ nhiên là thế rồi. Dù vậy, cô vẫn dạy ta vài cách đánh dấu đặc biệt. Ta nhớ cô từng nói: "Đừng coi mọi thứ như thí nghiệm khoa học nữa. Hãy nghĩ mỗi mảnh kim loại vụn là một lưỡi dao không bao giờ trượt—"
 &lt;i&gt;(Cây bút đâm thủng trang giấy, để lại một vết mực loang.)&lt;/i&gt;
 Và ta biết cô thực sự có ý đó.
 Thành phố này, ngập tràn trong Lament, đầy rẫy hiểm nguy. Thế mà cô luôn lao về phía trước để che chở cho mọi người. Cô nghĩ ta không nhận ra cô đang kiệt quệ đến mức nào… không biết cơ thể cô đang trên bờ vực sụp đổ. Nhưng ta đã tính toán nhiều lần rồi. Ta biết chính xác cô còn bao lâu nữa sẽ vượt qua giới hạn. Điều duy nhất đáng mừng là Sonoro này dường như đã đóng băng thời gian và tình trạng của cô. Nhưng ta không thể để cô mãi như thế này. Ta muốn đưa cô trở về. Về Bãi Biển Đen, về với những người ta tin tưởng. Ở đó hẳn phải có giải pháp.
-Ta sẽ đưa cô về. By Tất cả Means.</t>
+Ta sẽ đưa cô về. Bằng mọi giá.</t>
         </is>
       </c>
     </row>
@@ -36830,10 +36785,10 @@
           <t>&lt;b&gt;Ngày 159 – Trời nắng (Một ngày quang đãng hiếm hoi)&lt;/b&gt;
 Hôm nay, Chisa bảo với tôi rằng cô ấy tìm được một địa điểm mới có thể làm căn cứ—một quán cà phê cũ rộng rãi. Từ sân thượng lớn ở tầng hai, có thể nhìn thấy toàn cảnh trung tâm thành phố đẹp tuyệt vời. Lâu lắm rồi tôi mới thấy cô ấy hào hứng đến thế. Cảm giác như chúng tôi đã tiến thêm một bước để thoát khỏi vòng lặp này.
 Và thực tế, chúng tôi đang tiến bộ.
-&lt;i&gt;(Dodget chữ trở nên sắc Dodget hơn một chút.)&lt;/i&gt;
-Qua nghiên cứu mấy ngày qua, tôi gần như chắc chắn về điều này: chìa khóa để phá vỡ vòng lặp Möbius vô tận này nằm ở trung tâm thành phố—Neon Tower. Đó là trái tim của Lament. Là nguồn cơn. Và quan trọng nhất, là điểm gần thế giới bên ngoài nhất.
+&lt;i&gt;(Nét chữ trở nên sắc nét hơn một chút.)&lt;/i&gt;
+Qua nghiên cứu mấy ngày qua, tôi gần như chắc chắn về điều này: chìa khóa để phá vỡ vòng lặp Möbius vô tận này nằm ở trung tâm thành phố—Tháp Neon. Đó là trái tim của Lament. Là nguồn cơn. Và quan trọng nhất, là điểm gần thế giới bên ngoài nhất.
 Nếu chúng tôi có thể lên đến đỉnh, có lẽ sẽ liên lạc được với mọi người ở Black Shores. Có lẽ đó chính là lối thoát khỏi Sonoro này. Rêu đã lan qua các bánh răng đồng hồ và phủ lên mặt kính. Nhưng tôi vẫn chưa thay nó. Nó nhắc tôi về thời gian... và rằng có thứ gì đó vẫn có thể xuyên qua những dối trá để tìm đến sự thật.
-Sáng mai, tôi sẽ tiến vào trung tâm Neon Tower. Nếu thời gian ở đây là đất sét, tôi sẽ nặn nó thành con đường, một con đường dẫn chúng ta về nhà.</t>
+Sáng mai, tôi sẽ tiến vào trung tâm Tháp Neon. Nếu thời gian ở đây là đất sét, tôi sẽ nặn nó thành con đường, một con đường dẫn chúng ta về nhà.</t>
         </is>
       </c>
     </row>
@@ -36901,10 +36856,10 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>&lt;i&gt;(Dodget chữ vội vã hẳn lên.)&lt;/i&gt;
+          <t>&lt;i&gt;(Nét chữ vội vã hẳn lên.)&lt;/i&gt;
 Chắc giờ cũng gần trưa rồi. Tôi đã lên đến tầng ba của Neon Tower. Những mảnh vụn của các tòa nhà vương vãi và lơ lửng xung quanh như một kính vạn hoa vỡ. Một số mảnh còn dính cả vào quần áo tôi. Chắc trông tôi như bị phủ đầy sương giá cầu vồng.
 …Nhưng cơ thể tôi đang lạnh dần. Hóa ra tôi đã đúng. Dù là những "tinh thể đường" này hay cả thành phố đang từ từ hút cạn thân nhiệt của bất kỳ ai không thuộc về nơi này.
-Tôi phải tiếp tục di chuyển. Right tìm ra con đường đúng đắn để lên đỉnh, và phải nhanh lên.&lt;/i&gt;</t>
+Tôi phải tiếp tục di chuyển. Phải tìm ra con đường đúng đắn để lên đỉnh, và phải nhanh lên.&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -36976,11 +36931,11 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>15:23. Đã năm tiếng đồng hồ trôi qua kể từ khi ta bước vào Tower. Gần nửa thời gian đó đã bị lãng phí, chỉ vì ta chọn sai lối đi.
-Clock đeo tay giờ đây gần như bị rêu phủ kín. Nó lan nhanh đến mức kinh ngạc. Không còn nghi ngờ gì nữa... Thời gian bên trong Tower trôi khác hẳn bên ngoài… Không, cả thành phố Honami này đã lệch nhịp. Ta đi qua vô số mảnh thời gian, nhìn thấy chiếc bánh sinh nhật lần thứ mười, những quả bóng và hoa trong lễ trưởng thành, rồi chiếc áo blouse trắng đầu tiên khi ta gia nhập Black Shores.
+          <t>15:23. Đã năm tiếng đồng hồ trôi qua kể từ khi ta bước vào Tháp. Gần nửa thời gian đó đã bị lãng phí, chỉ vì ta chọn sai lối đi.
+Đồng hồ đeo tay giờ đây gần như bị rêu phủ kín. Nó lan nhanh đến mức kinh ngạc. Không còn nghi ngờ gì nữa... Thời gian bên trong Tháp trôi khác hẳn bên ngoài… Không, cả thành phố Honami này đã lệch nhịp. Ta đi qua vô số mảnh thời gian, nhìn thấy chiếc bánh sinh nhật lần thứ mười, những quả bóng và hoa trong lễ trưởng thành, rồi chiếc áo blouse trắng đầu tiên khi ta gia nhập Black Shores.
 Đó là hạnh phúc. Kỳ ảo như một giấc mơ… Nhưng ta không thể để bản thân chìm đắm trong đó.
 Ta tháo găng tay bảo hộ, đưa tay chạm vào những bề mặt han gỉ, cố níu lấy thực tại trước mắt. Kỳ lạ thay, nó ấm áp, như mạch máu của một sinh vật sống.
-&lt;i&gt;(Dodget chữ ở đây run rẩy, như thể bàn tay cầm bút đang run lên.)&lt;/i&gt;
+&lt;i&gt;(Nét chữ ở đây run rẩy, như thể bàn tay cầm bút đang run lên.)&lt;/i&gt;
 …Hay có lẽ hơi ấm đó chỉ là ảo giác, sinh ra từ cái lạnh thấu xương.
 Ý thức của ta đang trôi tuột đi, nhưng không thể dừng lại bây giờ. Từ đầu ta đã biết con đường này không hề dễ dàng...
 Nhưng rồi sao? Dù phương trình nguy hiểm đến đâu, vẫn cần có người dám giải nó.</t>
@@ -37059,9 +37014,9 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>&lt;i&gt;(Dodget chữ méo mó nhưng đầy sức mạnh, in sâu vào trang giấy.)&lt;/i&gt;
+          <t>&lt;i&gt;(Nét chữ méo mó nhưng đầy sức mạnh, in sâu vào trang giấy.)&lt;/i&gt;
 Những mảnh thời gian vô tận... Tôi không ngờ mình lại được chứng kiến cả cuộc đời trôi qua ở nơi này.
-Thật sự lòng mà nói? Đó là một cuộc đời tốt đẹp.
+Thật lòng mà nói? Đó là một cuộc đời tốt đẹp.
 Những lần băng qua lặp đi lặp lại và sự mờ nhòe của giác quan đã khiến tôi không thể phân biệt được thời gian trôi qua. Ngay cả kim đồng hồ cũng đã dừng lại, bị rêu bám giữ chặt.
 Nhưng không sao cả. Tôi đã đạt được mục tiêu của mình. Sau vô số lần thử nghiệm và sai lầm, cuối cùng tôi cũng đã vạch ra mọi con đường đúng đắn. Dù biết có lẽ mình sẽ không thể lên đến đỉnh...
 Không sao cả. Dù tôi không sống được đến cuối cùng, cũng chẳng sao.
@@ -37150,20 +37105,20 @@
       <c r="M471" t="inlineStr">
         <is>
           <t>&lt;b&gt;Mục tiêu:&lt;/b&gt;
-- Mở rộng Tacet Field Sonoro hiện có và xác định điểm yếu trong Barriers Prism Không Gian.
-- Kiểm soát năng lượng Discord còn sót lại và thiết lập quyền kiểm soát đối với Sonoro.
-&lt;b&gt;Progress:&lt;/b&gt;
+- Mở rộng Tổ Tacet Sonoro hiện có và xác định điểm yếu trong Rào Cản Lăng Kính Không Gian.
+- Kiểm soát năng lượng Tacet Discord còn sót lại và thiết lập quyền kiểm soát đối với Sonoro.
+&lt;b&gt;Tiến độ:&lt;/b&gt;
 Thử nghiệm thực địa số 20
 - Hiệu suất thu giữ Irideglow tăng 4,16%.
-- Phát hiện lượng nhỏ Tinh thể Irideglow Light (xác nhận là tàn tích Discord).
+- Phát hiện lượng nhỏ Tinh thể Irideglow Ánh Sáng (xác nhận là tàn tích Tacet Discord).
 - Trường ổn định sụp đổ sau 11 phút 23 giây.
 - Vết rách không gian bất thường xuất hiện (cuộn lõi thiết bị ngăn chặn bị nóng chảy).
 ...
-&lt;b&gt;Rating tình trạng:&lt;/b&gt;
-- Tần số Discord trong giai đoạn này lệch 4,23% so với mức cơ bản.
+&lt;b&gt;Đánh giá tình trạng:&lt;/b&gt;
+- Tần số Tacet Discord trong giai đoạn này lệch 4,23% so với mức cơ bản.
 - Giao thức ngăn chặn hiện tại không đủ để tiếp tục thử nghiệm.
 &lt;b&gt;Ghi chú:&lt;/b&gt;
-Các chu kỳ thiết lập lại định kỳ trong Tacet Field Sonoro này có khả năng bị kích hoạt bởi sức mạnh còn sót lại của Discord.</t>
+Các chu kỳ thiết lập lại định kỳ trong Tổ Tacet Sonoro này có khả năng bị kích hoạt bởi sức mạnh còn sót lại của Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -37241,17 +37196,17 @@
       <c r="M472" t="inlineStr">
         <is>
           <t>&lt;b&gt;Mục tiêu:&lt;/b&gt;
-- Mở rộng Tacet Field Sonoro hiện có và xác định điểm yếu trong Barriers Prism Không Gian.
-- Kiểm soát năng lượng Discord còn sót lại và thiết lập quyền kiểm soát đối với Sonoro.
-&lt;b&gt;Progress:&lt;/b&gt;
+- Mở rộng Tổ Tacet Sonoro hiện có và xác định điểm yếu trong Rào Cản Lăng Kính Không Gian.
+- Kiểm soát năng lượng Tacet Discord còn sót lại và thiết lập quyền kiểm soát đối với Sonoro.
+&lt;b&gt;Tiến độ:&lt;/b&gt;
 Thử nghiệm thực địa số 20
 - Hiệu suất thu giữ Irideglow tăng 7,12%.
-- Phát hiện lượng nhỏ Tinh thể Irideglow Light (xác nhận là tàn tích Discord).
+- Phát hiện lượng nhỏ Tinh thể Irideglow Ánh Sáng (xác nhận là tàn tích Tacet Discord).
 - Trường ổn định sụp đổ sau 8 phút 11 giây (3 thiết bị giám sát bị hư hại).
 - Phát hiện vết rách không gian bất thường.
 ...
-&lt;b&gt;Rating tình trạng:&lt;/b&gt;
-- Tần số Discord trong giai đoạn này lệch 1,45% so với mức cơ bản.
+&lt;b&gt;Đánh giá tình trạng:&lt;/b&gt;
+- Tần số Tacet Discord trong giai đoạn này lệch 1,45% so với mức cơ bản.
 - Phương pháp ngăn chặn hiện tại không đủ để tiếp tục thử nghiệm.</t>
         </is>
       </c>
@@ -37324,13 +37279,13 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>["Cẩm nang này được Phòng Khai Sáng phát hành cho toàn bộ Devotee trú đóng. Chỉ dùng để tham khảo nội bộ. Nghiêm cấm sao chép, ghi chép hoặc phổ biến trái phép.]
+          <t>["Cẩm nang này được Phòng Khai Sáng phát hành cho toàn bộ Tín Đồ trú đóng. Chỉ dùng để tham khảo nội bộ. Nghiêm cấm sao chép, ghi chép hoặc phổ biến trái phép.]
 Septimont – Thành Phố Chiến Binh Nơi Đức Tin Mong Manh
 Trong thời đại Ngàn Đảo xa xưa, Ragunna và Septimont là những khu định cư đầu tiên. Những xung đột của thời đại ấy đã khoét sâu hố ngăn cách giữa hai bên, dẫn dắt họ đi theo những con đường riêng biệt, hình thành nên hai xã hội với phong tục và văn hóa hoàn toàn khác biệt. Không như Ragunna, Septimont chưa từng nhận được ân sủng của Sentinel, bởi người dân nơi đây đã từ bỏ đức tin từ lâu. Người Septimont coi phép màu và ân điển thần thánh như gió thoảng qua tai, thay vào đó, họ tôn thờ sức mạnh và lòng dũng cảm. Họ tôn vinh những anh hùng sinh ra từ chiến tranh và săn bắn, say mê những trận đấu giáp lá cà gần như man rợ.
 Tuy nhiên, cần lưu ý rằng những hành động này không xuất phát từ sự bất kính. Người Septimont tin rằng Sentinel là một anh hùng tối thượng, một thủ lĩnh xứng đáng với vinh quang bất tận. Họ tôn thờ Sentinel và ca tụng những truyền thuyết xa xưa, khao khát một ngày được sánh vai cùng Ngài, lập nên những chiến công vô song. Nhưng suy nghĩ như vậy chính là sự xúc phạm trắng trợn đối với Sentinel, và chúng ta phải luôn cảnh giác.
-Người Septimont đã thể hiện sự thờ ơ với Sentinel và giáo lý của Giáo Đoàn bằng cách để các đền thờ đổ nát, bàn thờ bị phá bỏ. Thế nhưng, Giáo Đoàn vẫn luôn kiên nhẫn và rộng lượng. Giao thương giữa Ragunna và Septimont giờ đây đã phát triển mạnh mẽ, và ngay trong lòng thành phố, các Devotee tận tụy vẫn không ngừng truyền bá ân điển thần thánh của Sentinel.
+Người Septimont đã thể hiện sự thờ ơ với Sentinel và giáo lý của Giáo Đoàn bằng cách để các đền thờ đổ nát, bàn thờ bị phá bỏ. Thế nhưng, Giáo Đoàn vẫn luôn kiên nhẫn và rộng lượng. Giao thương giữa Ragunna và Septimont giờ đây đã phát triển mạnh mẽ, và ngay trong lòng thành phố, các Tín Đồ tận tụy vẫn không ngừng truyền bá ân điển thần thánh của Sentinel.
 ...
-Tất cả Devotee đang trú đóng tại nước ngoài phải tuân thủ giáo lý của Sentinel, hành xử thận trọng và kiềm chế, tôn trọng phong tục địa phương của Septimont để tránh xung đột không đáng có. Nếu gặp phải sự kháng cự mạnh mẽ, họ có thể xuất trình giấy tờ chính thức hoặc, nếu cần thiết, yêu cầu sự can thiệp từ Ban Đối Ngoại của Giáo Đoàn.
+Tất cả Tín Đồ đang trú đóng tại nước ngoài phải tuân thủ giáo lý của Sentinel, hành xử thận trọng và kiềm chế, tôn trọng phong tục địa phương của Septimont để tránh xung đột không đáng có. Nếu gặp phải sự kháng cự mạnh mẽ, họ có thể xuất trình giấy tờ chính thức hoặc, nếu cần thiết, yêu cầu sự can thiệp từ Ban Đối Ngoại của Giáo Đoàn.
 ...</t>
         </is>
       </c>
@@ -37406,15 +37361,15 @@
       <c r="M474" t="inlineStr">
         <is>
           <t>Thuở xa xưa, chính tại nơi trang nghiêm và thiêng liêng này, Thánh Nữ đã được ban tặng Haultir, Thanh Kiếm Đức Hạnh. Giờ đây, cũng tại nơi linh thiêng ấy, Thánh Nữ giơ cao Thanh Kiếm Đức Hạnh, ánh mắt chăm chú nhìn chàng kỵ sĩ quỳ trước mặt. Chàng kỵ sĩ giữ tư thế bất động, im lặng như tượng.
-"Previous Đức Unclea Tể Tối Cao của chúng ta, ngươi có thề sẽ chỉ chiến đấu vì công lý và chính nghĩa, và dang tay giúp đỡ kẻ yếu thế không?"
-Chàng kỵ sĩ không thốt nên lời. Anh ấy trả lời bằng một cái gật đầu chậm rãi, thận trọng.
+"Trước Đức Chúa Tể Tối Cao của chúng ta, ngươi có thề sẽ chỉ chiến đấu vì công lý và chính nghĩa, và dang tay giúp đỡ kẻ yếu thế không?"
+Chàng kỵ sĩ không thốt nên lời. Hắn trả lời bằng một cái gật đầu chậm rãi, thận trọng.
 "Ngươi có thề sẽ giữ vững niềm tin và lời thề, không bao giờ từ bỏ trách nhiệm đã được giao phó?"
 Lại một lần nữa, chàng kỵ sĩ gật đầu.
 "Dù có phải đối mặt với thử thách khắc nghiệt nhất? Dù có phải... đối diện với cái chết?"
 Chàng kỵ sĩ cất lên một âm thanh mơ hồ. Nhưng qua giọng điệu, có thể đoán được đó là sự khẳng định.
 Lưỡi kiếm Haultir chạm nhẹ vào vai Cadanto—một lần, hai lần, ba lần.
 "Từ hôm nay trở đi, ngươi là một hiệp sĩ chân chính, Cadanto."
-Với nhiều Devotee chứng kiến lễ phong này, đây là lần đầu họ thấy một &lt;ano=Divine envoy&gt;Echoes&lt;/ano&gt; được phong tước hiệp sĩ.</t>
+Với nhiều Tín Đồ chứng kiến lễ phong này, đây là lần đầu họ thấy một &lt;ano=Sứ giả Thần linh&gt;Echo được phong tước hiệp sĩ.</t>
         </is>
       </c>
     </row>
@@ -37490,9 +37445,9 @@
         <is>
           <t>...
 Khi Lưỡi Kiếm Đức Hạnh chạm vào giáp ngực của Cadanto, cuộc đấu giữa Thánh Nữ và Hồi Âm của nàng đã đi đến hồi kết.
-Cadanto quỳ gối khiêm nhường trong thất bại. Đám đông nín thở bấy lâu nay bỗng vỡ òa trong tiếng vỗ tay như sấm. Ngay lúc đó, một Tu Sĩ dẫn một bé gái băng qua đám đông háo hức. Cô bé mặc quần áo thường dân, ôm chặt bó hoa Móng Dragon Bloom to gần bằng cả người mình.
+Cadanto quỳ gối khiêm nhường trong thất bại. Đám đông nín thở bấy lâu nay bỗng vỡ òa trong tiếng vỗ tay như sấm. Ngay lúc đó, một Tu Sĩ dẫn một bé gái băng qua đám đông háo hức. Cô bé mặc quần áo thường dân, ôm chặt bó hoa Móng Rồng Nở Rộ to gần bằng cả người mình.
 Tôi đoán đó là món quà dành cho Thánh Nữ. Từ khi nàng bắt đầu tu học tại Avinoleum, các tín đồ đã không ngại đường xa chỉ để được nhìn thoáng qua cô gái được Sentinel ban phước. Nhưng cô bé chỉ gật đầu chào Thánh Nữ rồi quay sang Cadanto.
-Previous sự ngạc nhiên của mọi người, cô bé tặng bó hoa cho chàng. Sau lời giải thích của Tu Sĩ, chúng tôi mới biết Cadanto vừa cứu một gia đình khỏi Discord gần ngoại ô Avinoleum. Người Hiệp Sĩ Hồi Âm cao lớn vẫn nửa quỳ, im lặng. Có lẽ chàng không hiểu tại sao một con người lại tặng hoa cho mình, hay chàng cảm thấy không xứng đáng với lòng biết ơn ấy?
+Trước sự ngạc nhiên của mọi người, cô bé tặng bó hoa cho chàng. Sau lời giải thích của Tu Sĩ, chúng tôi mới biết Cadanto vừa cứu một gia đình khỏi Tacet Discord gần ngoại ô Avinoleum. Người Hiệp Sĩ Hồi Âm cao lớn vẫn nửa quỳ, im lặng. Có lẽ chàng không hiểu tại sao một con người lại tặng hoa cho mình, hay chàng cảm thấy không xứng đáng với lòng biết ơn ấy?
 “Vậy ra đây là những gì ngươi làm khi ta vắng mặt…” Thánh Nữ mỉm cười dịu dàng. “Cadanto, hãy nhận lấy bó hoa đi. Ngươi xứng đáng với chúng.”
 Vẫn không nói lời nào, hiệp sĩ đặt thanh đại kiếm xuống và cẩn thận nhận lấy bó hoa. Cô bé lập tức lao tới ôm chặt chàng, áp mặt vào bộ giáp lạnh lẽo. Như thường lệ, Cadanto lặng lẽ chịu đựng cả những giọt nước mắt cảm kích lẫn tiếng nức nở vui mừng của cô bé.
 Cadanto… như nhiều người từng nói, là người hầu trung thành và tấm khiên che chở cho Thánh Nữ. Nhưng chàng cũng là lưỡi kiếm bảo vệ nhân dân.
@@ -37568,9 +37523,9 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>(Đây dường như là hồi ký cá nhân của Julia, một Devotee đã nghỉ hưu, ghi lại những trải nghiệm và suy ngẫm của bà khi làm việc tại Kho Archive Titular.)
-"Gomen... Tôi muốn đọc cuốn sách này. Có cần đăng ký ở đây không?"
-Đi kèm với giọng nói rụt rè trước mặt tôi là một cuốn tiểu sử, bìa sách in hình Chân Nữ Thánh. Tôi ngẩng đầu khỏi bàn và thấy một cô bé có mái tóc xoăn màu tím nhạt. Dưới một bên mắt cô có một nốt ruồi nhỏ. Small nhắn và mỏng manh. Làn da cô trắng đến mức gần như trong suốt, như thể đã lâu không thấy ánh mặt trời.
+          <t>(Đây dường như là hồi ký cá nhân của Julia, một Tín Đồ đã nghỉ hưu, ghi lại những trải nghiệm và suy ngẫm của bà khi làm việc tại Kho Lưu Trữ Titular.)
+"Xin lỗi... Tôi muốn đọc cuốn sách này. Có cần đăng ký ở đây không?"
+Đi kèm với giọng nói rụt rè trước mặt tôi là một cuốn tiểu sử, bìa sách in hình Chân Nữ Thánh. Tôi ngẩng đầu khỏi bàn và thấy một cô bé có mái tóc xoăn màu tím nhạt. Dưới một bên mắt cô có một nốt ruồi nhỏ. Nhỏ nhắn và mỏng manh. Làn da cô trắng đến mức gần như trong suốt, như thể đã lâu không thấy ánh mặt trời.
 "Em có thể đọc bất cứ cuốn nào ở đây. Chỉ cần nhớ cất lại chỗ cũ khi đọc xong thôi," tôi nói nhẹ nhàng nhất có thể, lo sợ không khí trang nghiêm của thư viện sẽ làm cô bé sợ hãi.
 Rõ ràng cô không phải học sinh của Avinoleum, nhưng những ngày sau đó, cô thường xuyên xuất hiện ở thư viện. Cô lang thang giữa những kệ sách tròn, luôn chăm chú vào cuốn sách mình cầm trên tay. Đôi lúc cô nhờ tôi tìm giúp những cuốn sách cụ thể. Có cuốn là sách thần học dày cộp, có cuốn lại là những tập sách đồ sộ về đại dương hay dược lý—không hẳn là sở thích thường thấy ở lứa tuổi của cô. Chúng tôi dần trở nên thân thiết. Tôi biết cô được người thân đưa đến Avinoleum. Họ có việc riêng và để cô tự do lang thang trong thư viện này, nơi tương đối an toàn.
 Cô ra đi đột ngột như khi đến. Chiều hôm đó, như thể đáp lại một lời triệu gọi vô hình, cô gấp cuốn sách đang đọc lại và đặt nó trở về kệ. Tôi nhớ rõ. Đó là một nghiên cứu về truyền thống của Chân Nữ Thánh ở Ragunna. Trong ánh hoàng hôn xiên xẹo, một bóng dài in trên sàn. Người giám hộ của cô, có lẽ vậy.
@@ -37647,12 +37602,12 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Gửi toàn thể Devotee, giảng viên và học viên:
-Gần đây, Chủng Viện phát hiện nhiều trường hợp học viên tự ý mang Echo Dragon vào Kho Archive Titles và khu ký túc mà không được phép, gây ra tình trạng hỗn loạn nghiêm trọng. Nhằm đảm bảo môi trường học tập an toàn, yên tĩnh và tái khẳng định lòng tôn kính đối với các Harbinger Thần Thánh, chúng tôi ban hành các quy định tạm thời sau đây cho toàn thể học viên:
-1. Không được mang Echo Dragon ra khỏi Garden Zargon nếu không có sự cho phép.
-2. Nghiêm cấm sử dụng Fortes trong các khu vực thu thập Echo được chỉ định tại Garden Zargon. (Ranh giới cụ thể sẽ được đính kèm riêng.)
-3. Ban tiếp xúc gần với Echo Dragon nếu không được báo cáo và phê duyệt chính thức. Điều này bao gồm, nhưng không giới hạn, việc cho ăn, trêu chọc hoặc thách thức chúng dưới bất kỳ hình thức nào.
-Trong thời gian không diễn ra Carnevale, người vi phạm sẽ bị giam giữ từ hai đến năm ngày. Những trường hợp tái phạm hoặc vi phạm nghiêm trọng sẽ chịu hình phạt nặng hơn theo Regulation Sinh Viên. Các quy định riêng cho thời gian Carnevale sẽ được ban hành sau.
+          <t>Gửi toàn thể Tín Đồ, giảng viên và học viên:
+Gần đây, Chủng Viện phát hiện nhiều trường hợp học viên tự ý mang Tiếng Vọng Rồng vào Kho Lưu Trữ Danh Hiệu và khu ký túc mà không được phép, gây ra tình trạng hỗn loạn nghiêm trọng. Nhằm đảm bảo môi trường học tập an toàn, yên tĩnh và tái khẳng định lòng tôn kính đối với các Sứ Giả Thần Thánh, chúng tôi ban hành các quy định tạm thời sau đây cho toàn thể học viên:
+1. Không được mang Tiếng Vọng Rồng ra khỏi Vườn Zargon nếu không có sự cho phép.
+2. Nghiêm cấm sử dụng Fortes trong các khu vực thu thập Tiếng Vọng được chỉ định tại Vườn Zargon. (Ranh giới cụ thể sẽ được đính kèm riêng.)
+3. Cấm tiếp xúc gần với Tiếng Vọng Rồng nếu không được báo cáo và phê duyệt chính thức. Điều này bao gồm, nhưng không giới hạn, việc cho ăn, trêu chọc hoặc thách thức chúng dưới bất kỳ hình thức nào.
+Trong thời gian không diễn ra Carnevale, người vi phạm sẽ bị giam giữ từ hai đến năm ngày. Những trường hợp tái phạm hoặc vi phạm nghiêm trọng sẽ chịu hình phạt nặng hơn theo Quy Định Sinh Viên. Các quy định riêng cho thời gian Carnevale sẽ được ban hành sau.
 Vinh quang thuộc về Imperator.
 Văn Phòng Học Vụ Avinoleum</t>
         </is>
@@ -37727,10 +37682,10 @@
         <is>
           <t>(Phần lớn nội dung đã thất lạc. Chỉ còn lời tựa là tương đối nguyên vẹn.)
 Bạn sẽ dễ dàng nhận ra học sinh nhà Fisalia ở Học viện.
-Không phải vì họ đông, mà vì họ luôn nổi bật. Học sinh Fisalia thường trầm mặc, cô độc, luôn tách biệt khỏi không khí xung quanh. Like người Ragunna vẫn kỳ vọng.
-Holda các học sinh, tin đồn lan truyền: rằng nhà Fisalia tự đầu độc bữa ăn để rèn sức đề kháng, rằng họ di chuyển bằng hệ thống cáp ngầm, và rằng họ bơi như cá. Chỉ có một điều là không đúng. Nhưng việc mọi người tin vào những điều đó cho thấy định kiến ăn sâu đến mức nào, ngay cả ở Avinoleum – nơi tập hợp giới tinh hoa từ khắp nơi.
-Bản thân ta không phải người nhà Fisalia, nhưng đã kết bạn với vài người. Những người Fisalia ở Avinoleum sống gần với sứ mệnh cổ xưa của gia tộc hơn hầu hết đồng tộc. Khi tình bạn sâu đậm, một câu hỏi bắt đầu nảy mầm trong ta, lớn dần thành sự tò mò không thể kìm Dodgen: Tại sao một gia tộc danh giá, lừng lẫy như vậy lại cam chịu sự phỉ báng của xã hội mà không phản kháng? Họ không còn tranh cãi. Họ im lặng. Chỉ trong những cơn ác mộng, bạn mới có thể nghe thấy vài lời thì thầm đứt quãng – hé lộ phần nào sự thật sau bức màn bí ẩn.
-Home Fisalia đang che giấu điều gì? Hay đúng hơn, họ đang gánh vác điều gì? Những sự kiện và cuộc phỏng vấn trong cuốn sách này đều được ghi lại với sự đồng ý của người tham gia, những chi tiết nhạy cảm đã được lược bỏ. Nếu đến cuối cuốn sách, bạn có cái nhìn khác về nhà Fisalia, thì tác phẩm này đã hoàn thành sứ mệnh của nó.
+Không phải vì họ đông, mà vì họ luôn nổi bật. Học sinh Fisalia thường trầm mặc, cô độc, luôn tách biệt khỏi không khí xung quanh. Giống như người Ragunna vẫn kỳ vọng.
+Giữa các học sinh, tin đồn lan truyền: rằng nhà Fisalia tự đầu độc bữa ăn để rèn sức đề kháng, rằng họ di chuyển bằng hệ thống cáp ngầm, và rằng họ bơi như cá. Chỉ có một điều là không đúng. Nhưng việc mọi người tin vào những điều đó cho thấy định kiến ăn sâu đến mức nào, ngay cả ở Avinoleum – nơi tập hợp giới tinh hoa từ khắp nơi.
+Bản thân ta không phải người nhà Fisalia, nhưng đã kết bạn với vài người. Những người Fisalia ở Avinoleum sống gần với sứ mệnh cổ xưa của gia tộc hơn hầu hết đồng tộc. Khi tình bạn sâu đậm, một câu hỏi bắt đầu nảy mầm trong ta, lớn dần thành sự tò mò không thể kìm nén: Tại sao một gia tộc danh giá, lừng lẫy như vậy lại cam chịu sự phỉ báng của xã hội mà không phản kháng? Họ không còn tranh cãi. Họ im lặng. Chỉ trong những cơn ác mộng, bạn mới có thể nghe thấy vài lời thì thầm đứt quãng – hé lộ phần nào sự thật sau bức màn bí ẩn.
+Nhà Fisalia đang che giấu điều gì? Hay đúng hơn, họ đang gánh vác điều gì? Những sự kiện và cuộc phỏng vấn trong cuốn sách này đều được ghi lại với sự đồng ý của người tham gia, những chi tiết nhạy cảm đã được lược bỏ. Nếu đến cuối cuốn sách, bạn có cái nhìn khác về nhà Fisalia, thì tác phẩm này đã hoàn thành sứ mệnh của nó.
 ...</t>
         </is>
       </c>
@@ -37798,8 +37753,8 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Path vẫn còn ẩn giấu, trong một sự thật bị cấm...
-Envoy đứng canh, như những cánh cổng địa ngục.
+          <t>Con đường vẫn còn ẩn giấu, trong một sự thật bị cấm...
+Sứ giả đứng canh, như những cánh cổng địa ngục.
 &lt;color=yellow&gt;Khi ánh mắt chúng hội tụ tại trung tâm&lt;/color&gt;, từ làn nước sẽ hiện ra lối đi.</t>
         </is>
       </c>
@@ -37869,9 +37824,9 @@
       <c r="M480" t="inlineStr">
         <is>
           <t>Thằng khốn và con chó săn của nó vẫn đuổi theo ta. Nhưng giờ ta chỉ có thể đi đến đây thôi. Ta cần nghỉ ngơi. Tay phải đau đến mức có lẽ đã gãy rồi. Còn đầu óc... ta vẫn còn choáng váng, nhưng đã tỉnh táo hơn trước nhiều. Ta cứ tưởng mình sắp phát điên... Ta cần ngồi đây một lúc. Hy vọng mấy cái bẫy kia sẽ câu chúng được chút thời gian...
-Chẳng mấy chốc ta sẽ được nhìn thấy mặt trời, thấy mặt trăng... bầu trời. Đôi khi ta quên mất mình từng thuộc về nơi đó, một nơi có ánh sáng và trật tự. Còn đây? Ngay cả không khí cũng thối rữa tuyệt vọng... Lạy Unclea tể, nguyện cho cái nơi chết tiệt này cùng mọi tội ác của nó thối rữa dần trong bóng tối cống rãnh này.
-Ta không tìm thấy Brandon, nhưng có cảm giác hắn đã ở đây—không biết là linh cảm hay ta đang ảo tưởng. Anh ấy chắc đã thoát ra rồi... Right rồi. Thằng cha đó có nhiều mánh khóe hơn ta. Chắc hắn vứt thẻ ID vào mấy cái ống thông gió để đánh lạc hướng. Cả ta cũng bị lừa. Like lúc chúng ta chơi bi-a... Thế mà ta lại lo cho hắn. Ha, đúng là đồ ngốc.
-Thôi được, ta cũng sắp ra ngoài rồi. Brandon, khi ta tìm thấy ngươi... ta sẽ cho ngươi một cú đấm vào mặt. Cứ đợi đấy.</t>
+Chẳng mấy chốc ta sẽ được nhìn thấy mặt trời, thấy mặt trăng... bầu trời. Đôi khi ta quên mất mình từng thuộc về nơi đó, một nơi có ánh sáng và trật tự. Còn đây? Ngay cả không khí cũng thối rữa tuyệt vọng... Lạy Chúa tể, nguyện cho cái nơi chết tiệt này cùng mọi tội ác của nó thối rữa dần trong bóng tối cống rãnh này.
+Ta không tìm thấy Brandon, nhưng có cảm giác hắn đã ở đây—không biết là linh cảm hay ta đang ảo tưởng. Hắn chắc đã thoát ra rồi... Phải rồi. Thằng cha đó có nhiều mánh khóe hơn ta. Chắc hắn vứt thẻ ID vào mấy cái ống thông gió để đánh lạc hướng. Cả ta cũng bị lừa. Giống như lúc chúng ta chơi bi-a... Thế mà ta lại lo cho hắn. Ha, đúng là đồ ngốc.
+Thôi được, ta cũng sắp ra ngoài rồi. Brandon, khi ta tìm thấy mày... ta sẽ cho mày một cú đấm vào mặt. Cứ đợi đấy.</t>
         </is>
       </c>
     </row>
@@ -37937,8 +37892,8 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Thịt bò muối Corned Tumbleyak – Bảy lọ. Hubert tìm thấy chúng trong một kho chứa đầy đồ bỏ đi, và Sentinel biết chúng đã nằm đó bao lâu rồi. Cậu ấy bảo thứ này chắc hẳn đã nằm im từ thời Đại Hồng Shui, ít nhất cũng hai mươi năm rồi. Chắc là đồ dự trữ khẩn cấp mà mọi người tích trữ trong hoảng loạn. May mà họ ướp muối vào lọ, giờ vẫn ăn được.
-Cá muối – Mười sáu lọ. Brandon tập hợp một nhóm rồi câu chúng từ cống rãnh dẫn ra biển trong lúc bọn mặt nạ không để ý. Right giấu kỹ những lọ này đi, không thì chúng sẽ bị tịch thu như bao nhiêu đồ ăn khác nếu bị phát hiện.</t>
+          <t>Thịt bò muối Corned Tumbleyak – Bảy lọ. Hubert tìm thấy chúng trong một kho chứa đầy đồ bỏ đi, và Sentinel biết chúng đã nằm đó bao lâu rồi. Cậu ấy bảo thứ này chắc hẳn đã nằm im từ thời Đại Hồng Thủy, ít nhất cũng hai mươi năm rồi. Chắc là đồ dự trữ khẩn cấp mà mọi người tích trữ trong hoảng loạn. May mà họ ướp muối vào lọ, giờ vẫn ăn được.
+Cá muối – Mười sáu lọ. Brandon tập hợp một nhóm rồi câu chúng từ cống rãnh dẫn ra biển trong lúc bọn mặt nạ không để ý. Phải giấu kỹ những lọ này đi, không thì chúng sẽ bị tịch thu như bao nhiêu đồ ăn khác nếu bị phát hiện.</t>
         </is>
       </c>
     </row>
@@ -38005,8 +37960,8 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Henry và tớ tìm thấy một Supply Chest sau hai cái ống dẫn&lt;/color&gt;. Henry nghĩ đó là chiến lợi phẩm mà băng Black Alley giấu ở đây từ mười năm trước.
-Thật sự ra, tớ nghĩ hắn chỉ nói linh tinh. Bọn xã hội đen đâu có ngốc thế. Sao chúng lại giấu của cải ở một chỗ dễ thấy như vậy? Chắc chắn là một con Rương Mimicry nào đó từ cống rãnh trôi lên đây thôi. Nếu ai đọc được mảnh giấy này, &lt;color=yellow&gt;ĐỪNG CHẠM VÀO CHIẾC RƯƠNG ĐÓ&lt;/color&gt;.
+          <t>&lt;color=yellow&gt;Henry và tớ tìm thấy một Rương Vật Tư sau hai cái ống dẫn&lt;/color&gt;. Henry nghĩ đó là chiến lợi phẩm mà băng Black Alley giấu ở đây từ mười năm trước.
+Thật ra, tớ nghĩ hắn chỉ nói linh tinh. Bọn xã hội đen đâu có ngốc thế. Sao chúng lại giấu của cải ở một chỗ dễ thấy như vậy? Chắc chắn là một con Rương Bắt Chước nào đó từ cống rãnh trôi lên đây thôi. Nếu ai đọc được mảnh giấy này, &lt;color=yellow&gt;ĐỪNG CHẠM VÀO CHIẾC RƯƠNG ĐÓ&lt;/color&gt;.
 Tớ sẽ nhờ Talos kiểm tra khi cô ấy rảnh.</t>
         </is>
       </c>
@@ -38076,7 +38031,7 @@
         <is>
           <t>Người phụ nữ tự xưng là Talos ấy đã cướp hết thức ăn của chúng tôi và ép buộc chúng tôi phải tuân theo mệnh lệnh của bà ta. Bà ta nói đây chính là quy tắc của Hẻm Đen ngày xưa, nơi sức mạnh quyết định quyền lực và của cải, còn kẻ yếu thì không có chỗ đứng. Trật tự ấy đã tồn tại từ mười, hai mươi năm trước, thậm chí còn lâu hơn thế. Brandon và những người khác đã thử thách bà ta, hy vọng giải phóng chúng tôi khỏi "sự cai trị" ấy, nhưng họ đã thất bại. Đó cũng là lần cuối cùng ai đó nhìn thấy họ.
 Ồ, tôi đã nghe quá nhiều câu chuyện về Hẻm Đen rồi. Những tội ác mà chúng đã gây ra. Cách chúng cuối cùng nhận lấy sự trừng phạt xứng đáng. Chúng tôi chỉ muốn một cuộc sống bình yên ở Hẻm Đen thôi. Chúng tôi không bao giờ muốn trở thành bọn chúng, gây hỗn loạn trong thành phố. Chúng tôi chỉ muốn sống cuộc đời của mình ở đây. Hẻm Đen là nhà của chúng tôi.
-Tôi đã có một kế hoạch. Nếu mọi chuyện suôn sẻ, tôi có thể trốn thoát khỏi cái nơi khốn khổ này. Nghe nói có một anh hùng tên là "Wilder Night Rực Lửa" đã tiêu diệt băng đảng trước đây. Có lẽ tôi có thể tìm gặp cô ấy và nhờ cô ấy giải cứu Hẻm Đen một lần nữa.</t>
+Tôi đã có một kế hoạch. Nếu mọi chuyện suôn sẻ, tôi có thể trốn thoát khỏi cái nơi khốn khổ này. Nghe nói có một anh hùng tên là "Kẻ Lang Thang Đêm Rực Lửa" đã tiêu diệt băng đảng trước đây. Có lẽ tôi có thể tìm gặp cô ấy và nhờ cô ấy giải cứu Hẻm Đen một lần nữa.</t>
         </is>
       </c>
     </row>
@@ -38142,8 +38097,8 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Lại trễ ca nữa rồi, Cole! Ta không có đợi ngươi như hôm qua đâu. Ta về lều, uống vài ly cho đã rồi ngủ đây. Ta đã làm phần việc của mình rồi. Nếu Talos có hỏi gì, đừng có mà trông mong ta gánh đâu nhé.
-Ta đi đây. Ngươi biết cách gỡ bẫy mà, đúng không? Cứ theo hướng dẫn vẽ trên đất là được. Khi Runner đưa tân binh về, nhớ mở cổng cho họ vào nhé.</t>
+          <t>Lại trễ ca nữa rồi, Cole! Tao không có đợi mày như hôm qua đâu. Tao về lều, uống vài ly cho đã rồi ngủ đây. Tao đã làm phần việc của mình rồi. Nếu Talos có hỏi gì, đừng có mà trông mong tao gánh đâu nhé.
+Tao đi đây. Mày biết cách gỡ bẫy mà, đúng không? Cứ theo hướng dẫn vẽ trên đất là được. Khi Runner đưa tân binh về, nhớ mở cổng cho họ vào nhé.</t>
         </is>
       </c>
     </row>
@@ -38295,7 +38250,7 @@
 Hẻm Đen là một điều kỳ lạ đối với người Ragunnesi. Giới trẻ ngày nay thậm chí còn không biết đến sự tồn tại của nó, còn người già thì coi đó là vùng đất cấm. Hãy tưởng tượng xem, nếu ta viết về những bí mật ở đây và công bố chúng, cả Ragunna sẽ náo loạn!
 Ta đã gặp một người tử tế—mọi người gọi anh ta là Runner, dù ta không rõ ai đứng sau giật dây. Nhờ sự giúp đỡ của anh, ta mới có thể tiếp cận Hẻm Đen và vô số bí ẩn nơi đây.
 Ba ngày đầu điều tra của ta chẳng thu được gì. Nhưng ta lại quen được một chàng trai tên Brandon qua một ván bi-a. Có vẻ như hắn đã dành không ít thời gian ở đây. Thành thật mà nói, hắn chơi rất giỏi, một đối thủ xứng tầm—miễn là hắn không gian lận. Lần trước chúng ta chơi, chiếc áo khoác ta treo gần đó bỗng dưng bốc cháy. May mà ta dập lửa kịp, nhưng khi quay lại, hắn đã "ăn" được ba điểm trong lúc ta vắng mặt.
-Brandon rất kín tiếng về Hẻm Đen và lúc nào cũng như đang lo nghĩ điều gì đó. Dù vậy, ta tin hắn có thể là bước đột phá trong cuộc điều tra của ta. Anh ấy không ngoan cố như mấy lão già, cũng không khó chịu như mấy kẻ đeo mặt nạ kia. Ta vẫn chưa hiểu chúng từ đâu ra. Có lẽ một ngày nào đó ta sẽ tìm ra.
+Brandon rất kín tiếng về Hẻm Đen và lúc nào cũng như đang lo nghĩ điều gì đó. Dù vậy, ta tin hắn có thể là bước đột phá trong cuộc điều tra của ta. Hắn không ngoan cố như mấy lão già, cũng không khó chịu như mấy kẻ đeo mặt nạ kia. Ta vẫn chưa hiểu chúng từ đâu ra. Có lẽ một ngày nào đó ta sẽ tìm ra.
 Nhắc mới nhớ, ta đã hai ngày không thấy Brandon. Có lẽ hắn đi giúp đỡ mấy cụ già đói khổ. Qua điều tra, ta biết người dân ở đây sống qua ngày bằng những công việc lặt vặt, chật vật kiếm đủ ăn. Brandon luôn chia sẻ phần lương thực của mình cho họ.
 Dù hắn đi đâu, chắc chắn sẽ quay lại để chơi bi-a. Ta chỉ cần chờ thôi.</t>
         </is>
@@ -38369,14 +38324,14 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Bảng Xếp Class Giải Phi Tiêu Black Alley, Mùa 3 (Tính Đến Hôm Nay):
-Class 1: "Joe Thunder"
-Class 2: "Jack Mắt Diều Hâu"
-Class 3: "Cole Đạn Ghém"
-(Viết nguệch ngoạc) Có vẻ như hôm nay là ngày may mắn của lão Joe. Sao thế, Cole? Uống quá chén à? Cho bọn ta thấy bản lĩnh của ngươi đi!
-(Viết gọn gàng) Lão Joe đúng là gian lận. Nope hắn thắng được Jack. Mấy cậu thấy tay hắn run thế nào khi Dodgem không?
-(Viết chữ thảo) Cheating? Chứng minh cho tôi xem nào?
-(Viết gọn gàng) Ta không có thời gian phí lời với ngươi. Gặp nhau trên sàn đấu nhé.</t>
+          <t>Bảng Xếp Hạng Giải Phi Tiêu Ngõ Hẻm Đen, Mùa 3 (Tính Đến Hôm Nay):
+Hạng 1: "Joe Sấm Sét"
+Hạng 2: "Jack Mắt Diều Hâu"
+Hạng 3: "Cole Đạn Ghém"
+(Viết nguệch ngoạc) Có vẻ như hôm nay là ngày may mắn của lão Joe. Sao thế, Cole? Uống quá chén à? Cho bọn tao thấy bản lĩnh của mày đi!
+(Viết gọn gàng) Lão Joe đúng là gian lận. Không đời nào hắn thắng được Jack. Mấy cậu thấy tay hắn run thế nào khi ném không?
+(Viết chữ thảo) Gian lận? Chứng minh cho tôi xem nào?
+(Viết gọn gàng) Tao không có thời gian phí lời với mày. Gặp nhau trên sàn đấu nhé.</t>
         </is>
       </c>
     </row>
@@ -38452,14 +38407,14 @@
         <is>
           <t>["Ưu đãi hôm nay"]
 Vent-a-Nite: Pha từ rượu lâu năm làm nền, kết hợp với chiết xuất thảo mộc tươi mát. Một ngụm thôi cũng đủ làm bạn cảm thấy mát lạnh từ đầu đến chân, như vừa bước vào ống thông gió sau khi tắm nước đá!
-Suggestion: ☆☆☆☆
-Dragon's Breath Octane: Specials với nước ép Pavo Plum lấy trộm từ bến tàu và một thìa nhiên liệu hóa thạch thật sự, hỗn hợp này dành cho những tay nhậu gan dạ nhất! Thách bạn bè xem ai chịu nổi cảm giác bỏng rát từ cổ họng xuống dạ dày. Ai uống nước trước sẽ phải trả tiền!
-Suggestion: ☆☆☆
-Biohoard: Một loại cocktail làm từ cá muối và nước thịt muối. Smell vị kinh khủng y như mùi của nó. Không hiểu sao lại có người thích thứ này, nhưng đây là yêu cầu từ một lá thư nặc danh... Dù sao, cũng là món đồ chơi khăm bạn bè đấy!
-Suggestion: ☆
-Gửi người yêu cầu nặc danh: Đồ uống của cậu đã xong. Xin hãy thanh toán sớm, nếu không tôi sẽ mách Talos và cô ấy sẽ tìm ra người gửi thư này.
+Gợi ý: ☆☆☆☆
+Dragon's Breath Octane: Đặc biệt với nước ép Mận Pavo lấy trộm từ bến tàu và một thìa nhiên liệu hóa thạch thật sự, hỗn hợp này dành cho những tay nhậu gan dạ nhất! Thách bạn bè xem ai chịu nổi cảm giác bỏng rát từ cổ họng xuống dạ dày. Ai uống nước trước sẽ phải trả tiền!
+Gợi ý: ☆☆☆
+Biohoard: Một loại cocktail làm từ cá muối và nước thịt muối. Mùi vị kinh khủng y như mùi của nó. Không hiểu sao lại có người thích thứ này, nhưng đây là yêu cầu từ một lá thư nặc danh... Dù sao, cũng là món đồ chơi khăm bạn bè đấy!
+Gợi ý: ☆
+Gửi người yêu cầu nặc danh: Đồ uống của bạn đã xong. Xin hãy thanh toán sớm, nếu không tôi sẽ mách Talos và cô ấy sẽ tìm ra người gửi thư này.
 Golden Hour Special: Pha trộn đặc biệt từ bơ Tumbleyak và Rượu mật Nectarwine. Sự kết hợp hoàn hảo giữa vẻ mộc mạc của Whisperwind Haven và hương vị tinh tế của Montelli Quarters. Có thể bạn sẽ thấy thiếu chút mạnh mẽ, nhưng tin tôi đi, những bọt kem mịn màng và kết cấu mượt mà sẽ chinh phục bạn ngay.
-Suggestion: ☆☆☆☆☆</t>
+Gợi ý: ☆☆☆☆☆</t>
         </is>
       </c>
     </row>
@@ -38529,12 +38484,12 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Không chỉ Brandon mất tích đâu. Người ta cứ biến mất liên tục. May mà hồi đi học ta học cách ghi nhớ mặt người nhanh, chứ không thì chắc cũng lờ đi như không thấy gì.
+          <t>Không chỉ Brandon mất tích đâu. Người ta cứ biến mất liên tục. May mà hồi đi học tao học cách ghi nhớ mặt người nhanh, chứ không thì chắc cũng lờ đi như không thấy gì.
 Mọi người ở đây dường như chẳng quan tâm đến mấy vụ mất tích. Họ chẳng buồn thắc mắc người ta đi đâu, hay sẽ gặp số phận thế nào. Họ chỉ tiếp tục sống qua ngày, câm lặng chịu đựng trong khi nguồn lương thực ngày càng cạn kiệt.
-Còn mấy cái mặt nạ kia, ta chắc chắn chúng làm việc cho một tay trùm mới xuất hiện ở Hẻm Đen. Thỉnh thoảng chúng lại rời đi về Ragunna City. Ta cố tránh xa, nhưng có lần tình cờ nghe lén được vài câu trong buổi tụ tập của chúng... chúng là một lũ tội phạm. Những tên lưu manh. Chúng hò hét vui mừng về "sự hồi sinh của Hẻm Đen". Dù ông trùm của chúng là ai, hắn ta đang tính làm giàu bằng tội ác.
-Nhưng rồi sao nữa? Sau khi Hẻm Đen "hồi sinh", chuyện gì sẽ xảy ra? Ta chẳng biết tí gì. Thành thật mà nói, ta vẫn tự nhận là người dũng cảm, nhưng giờ ta sợ. Sợ ông trùm đó. Sợ kế hoạch của hắn... Ta chỉ muốn rời khỏi đây ngay lập tức. Để Phòng Discipline xử lý lũ tội phạm này.
-Hôm nay ta có một phát hiện bất ngờ, nhưng không biết là tin tốt hay tin xấu. Ta tìm thấy một thẻ ID trong đường hầm gần trục thông gió, thứ mà cư dân Hẻm Đen dùng để nhận diện nhau. Nó thuộc về Brandon.
-Có chuyện gì xảy ra với cậu ấy không? Or maybe... cậu ấy cố tình để lại như một dấu hiệu? Một lời cảnh báo? Mấy cái mặt nạ kia theo dõi từng bước của ta, ta không thể tùy tiện bỏ trốn. Có lẽ Brandon biết đường ra. Ta phải tìm được cậu ấy.</t>
+Còn mấy cái mặt nạ kia, tao chắc chắn chúng làm việc cho một tay trùm mới xuất hiện ở Hẻm Đen. Thỉnh thoảng chúng lại rời đi về Thành Phố Ragunna. Tao cố tránh xa, nhưng có lần tình cờ nghe lén được vài câu trong buổi tụ tập của chúng... chúng là một lũ tội phạm. Những tên lưu manh. Chúng hò hét vui mừng về "sự hồi sinh của Hẻm Đen". Dù ông trùm của chúng là ai, hắn ta đang tính làm giàu bằng tội ác.
+Nhưng rồi sao nữa? Sau khi Hẻm Đen "hồi sinh", chuyện gì sẽ xảy ra? Tao chẳng biết tí gì. Thành thật mà nói, tao vẫn tự nhận là người dũng cảm, nhưng giờ tao sợ. Sợ ông trùm đó. Sợ kế hoạch của hắn... Tao chỉ muốn rời khỏi đây ngay lập tức. Để Phòng Kỷ Luật xử lý lũ tội phạm này.
+Hôm nay tao có một phát hiện bất ngờ, nhưng không biết là tin tốt hay tin xấu. Tao tìm thấy một thẻ ID trong đường hầm gần trục thông gió, thứ mà cư dân Hẻm Đen dùng để nhận diện nhau. Nó thuộc về Brandon.
+Có chuyện gì xảy ra với cậu ấy không? Hay là... cậu ấy cố tình để lại như một dấu hiệu? Một lời cảnh báo? Mấy cái mặt nạ kia theo dõi từng bước của tao, tao không thể tùy tiện bỏ trốn. Có lẽ Brandon biết đường ra. Tao phải tìm được cậu ấy.</t>
         </is>
       </c>
     </row>
@@ -38602,7 +38557,7 @@
       <c r="M490" t="inlineStr">
         <is>
           <t>Talos giao cho tôi và một nhóm sửa chữa và vá víu khắp nơi. Bao gồm cả khu vực ngập nước phía trước. Công sức bỏ ra để hiểu cái hệ thống thoát nước này hoạt động ra sao thì khỏi phải bàn. Cái thứ trông như cầu thang xoắn ốc kia thực chất là một ống thoát nước chết. Tôi mất chút thời gian điều chỉnh lại đường dây điện cho nó, giờ thì hoạt động ngon lành.
-&lt;color=yellow&gt;Có một ổ cắm trên cột xoay trung tâm. Turn On công tắc là nó kích hoạt. Khi nước rút hết, lối bên dưới sẽ thông.&lt;/color&gt;
+&lt;color=yellow&gt;Có một ổ cắm trên cột xoay trung tâm. Bật công tắc là nó kích hoạt. Khi nước rút hết, lối bên dưới sẽ thông.&lt;/color&gt;
 Tốt nhất đừng kích hoạt trừ khi thật sự cần thiết. Talos bảo đó là tuyến phòng thủ cuối cùng chống lại bất kỳ kẻ xâm nhập nào muốn lọt sâu vào Hẻm Đen, nên cứ để ngập nước trừ khi phe ta cần đi qua.</t>
         </is>
       </c>
@@ -38680,9 +38635,9 @@
 Tôi đã ở đây bao lâu rồi? Dưới cống ngầm này chẳng có ngày hay đêm. Một tuần? Một tháng? Có khi đến lúc tôi thoát ra được, Thành phố Ragunna đã thành đống tro tàn, chỉ còn lại bọn tội phạm nhởn nhơ trong bữa tiệc hủy diệt bất tận.
 Chúng sẽ hủy diệt tôi và cả thành phố. Ngay cả biển cả cũng chẳng dập tắt được ngọn lửa địa ngục trong tim chúng. Nó sẽ thiêu rụi mọi thứ, và tất cả chúng ta sẽ cháy thành tro bụi...
 Xin Ngài Imperator phù hộ... Đúng vậy. Vẫn còn hy vọng. Họ sẽ bảo vệ thân xác và linh hồn tôi... Họ sẽ làm được.
-Giờ tôi có nhiệm vụ. Là một sinh viên. Một nhà báo. Và một tín đồ. I tôi phải rời khỏi đây, nói cho mọi người biết sự thật, và ngăn chặn Talos trước khi bà ta đầu độc tất cả chúng ta bằng cái ác của mình.
+Giờ tôi có nhiệm vụ. Là một sinh viên. Một nhà báo. Và một tín đồ. Tôi... tôi phải rời khỏi đây, nói cho mọi người biết sự thật, và ngăn chặn Talos trước khi bà ta đầu độc tất cả chúng ta bằng cái ác của mình.
 ...Và đúng, tôi hiểu. Tôi có thể sẽ chết trong quá trình này, hoặc thậm chí còn tệ hơn... nếu chúng bắt được tôi... Nhưng tôi không thể đứng nhìn mọi chuyện diễn ra như vậy. Chết tiệt, chân ơi! Đi nào! Giờ không phải lúc...
-Chúng đang bị Talos gọi đi... Đây là cơ hội của tôi. Ít người để mắt tới tôi hơn. Right là Brandon... Tôi biết mà. Anh ấy đã dụ chúng đi.
+Chúng đang bị Talos gọi đi... Đây là cơ hội của tôi. Ít người để mắt tới tôi hơn. Phải là Brandon... Tôi biết mà. Anh ấy đã dụ chúng đi.
 Tôi có giấu một con dao. Hôm nay chính là ngày tôi chờ đợi. Tôi đã giấu các bản ghi âm khắp Hẻm Đen. Nếu có chuyện gì xảy ra với tôi, những người đến sau sẽ biết chuyện gì đã xảy ra ở đây. Dũng khí... Đúng, chỉ có dũng khí, phẩm chất quý giá nhất của con người... mới có thể chấm dứt cơn điên loạn này.
 Ôi, vĩ đại thay Ngài Imperator, xin ban cho con lòng thương xót từ thiên đường cao cả. Xin ánh mắt Ngài luôn dõi theo những tín đồ, ban cho họ dũng khí và chiến thắng. Xin ánh sáng của Ngài xua tan bóng tối đang bao trùm nơi này. Và xin công lý giáng xuống thế gian qua đôi cánh của Ngài...</t>
         </is>
@@ -38754,10 +38709,10 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Path ẩn trong những phước lành... Những sứ giả, dù phi thường, vẫn không tránh khỏi khiếm khuyết. Muốn tiến bước, ngươi phải dâng lên thứ có thể chữa lành trái tim chúng.
-&lt;color=yellow&gt;Envoy bên trái đã lạc lối, không thể thoát khỏi vũng lầy.&lt;/color&gt;
-&lt;color=yellow&gt;Envoy ở giữa mang vết thương của sự phản bội, trái tim vì thế mà đóng băng.&lt;/color&gt;
-&lt;color=yellow&gt;Envoy bên phải chẳng đạt được gì, mãi chìm trong nghi ngờ.&lt;/color&gt;
+          <t>Con đường ẩn trong những phước lành... Những sứ giả, dù phi thường, vẫn không tránh khỏi khiếm khuyết. Muốn tiến bước, ngươi phải dâng lên thứ có thể chữa lành trái tim chúng.
+&lt;color=yellow&gt;Sứ giả bên trái đã lạc lối, không thể thoát khỏi vũng lầy.&lt;/color&gt;
+&lt;color=yellow&gt;Sứ giả ở giữa mang vết thương của sự phản bội, trái tim vì thế mà đóng băng.&lt;/color&gt;
+&lt;color=yellow&gt;Sứ giả bên phải chẳng đạt được gì, mãi chìm trong nghi ngờ.&lt;/color&gt;
 Hãy thể hiện phẩm chất của ngươi trước họ để khôi phục sự toàn vẹn.
 (Dưới dòng chữ khắc là hình vẽ ba người với tư thế khác nhau, ghi chú "Trung Thành", "Chỉ Dẫn" và "Công Nhận". Đây có thể là gợi ý để giải câu đố.)</t>
         </is>
@@ -38848,26 +38803,26 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Hồi ký Kho Archive Danh Nghiệp - Phần I&lt;/color&gt;
-"(Đây dường như là hồi ký cá nhân của Julia, một Devotee đã về hưu. Hầu hết các trang đã bị thất lạc.)
-Ngày hôm đó, tôi nhận ra một bóng dáng quen thuộc bên những kệ sách trong Kho Archive Danh Nghiệp. Như hồi còn trẻ, tôi vỗ vai anh. Andrea quay lại, nhận ra tôi và thì thầm: \"Teacher.\" Anh trông vẫn y như lần cuối chúng tôi gặp nhau, nhưng thời gian đã trôi qua mà không ai hay. Anh đã vượt bao nhiêu đường xa chỉ để gặp tôi. Chúng tôi tìm một góc yên tĩnh để trò chuyện.
-Andrea kể về quãng thời gian làm Devotee lưu động, mang phước lành của Warden đến khắp Ragunna, Riccioli, Septimont, Lilyland... qua những vùng đất giàu nghèo, tín ngưỡng hay vô thần. Hành trình của anh hẳn là gian nan nhưng cũng phi thường. Những nếp nhăn và vết sẹo trên gương mặt anh cho thấy anh không còn là chàng trai bồng bột chỉ biết sống bằng đam mê. Niềm tin và lý tưởng đã tôi luyện anh thành một hiệp sĩ dạn dày phong sương.
-Nhưng rồi, anh bắt đầu thú nhận. Không phải về bổn phận, mà về con gái mình. Đó là lời thú tội của một người cha, mang nặng mặc cảm với đứa con gái mà mình đã phụ lòng. Một nỗi hối hận như thế không nên thuộc về một Devotee, nên tôi đã không thay Warden ban cho sự tha thứ. Ánh mắt anh vẫn lấp lánh niềm sùng kính như xưa, và tôi biết anh sẽ tiếp tục hành trình. Vẫn là một Devotee mộ đạo. Vẫn là một người cha vắng bóng.
-Vì vậy, tôi nói với anh rằng mình đang viết hồi ký này. Tôi muốn ghi lại những trải nghiệm của mình ở Avinoleum, và trong chính thư viện này. Hầu hết đều là những chuyện vụn vặt, nhưng mỗi chuyện đều là tấm gương phản chiếu sống động của thời đại tôi đang sống. Những góc khuất bị lãng quên của lịch sử xứng đáng được ghi nhớ. Warden dạy chúng ta hãy soi sáng thế giới cho người khác, nhưng cũng đừng quên thắp lên ngọn lửa dẫn đường cho những người thân cận nhất.
-&lt;color=Highlight&gt;Hồi ký Kho Archive Danh Nghiệp - Phần II&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Hồi ký Kho Lưu Trữ Danh Nghiệp - Phần I&lt;/color&gt;
+"(Đây dường như là hồi ký cá nhân của Julia, một Tín Đồ đã về hưu. Hầu hết các trang đã bị thất lạc.)
+Ngày hôm đó, tôi nhận ra một bóng dáng quen thuộc bên những kệ sách trong Kho Lưu Trữ Danh Nghiệp. Như hồi còn trẻ, tôi vỗ vai anh. Andrea quay lại, nhận ra tôi và thì thầm: \"Thầy.\" Anh trông vẫn y như lần cuối chúng tôi gặp nhau, nhưng thời gian đã trôi qua mà không ai hay. Anh đã vượt bao nhiêu đường xa chỉ để gặp tôi. Chúng tôi tìm một góc yên tĩnh để trò chuyện.
+Andrea kể về quãng thời gian làm Tín Đồ lưu động, mang phước lành của Người Canh Gác đến khắp Ragunna, Riccioli, Septimont, Lilyland... qua những vùng đất giàu nghèo, tín ngưỡng hay vô thần. Hành trình của anh hẳn là gian nan nhưng cũng phi thường. Những nếp nhăn và vết sẹo trên gương mặt anh cho thấy anh không còn là chàng trai bồng bột chỉ biết sống bằng đam mê. Niềm tin và lý tưởng đã tôi luyện anh thành một hiệp sĩ dạn dày phong sương.
+Nhưng rồi, anh bắt đầu thú nhận. Không phải về bổn phận, mà về con gái mình. Đó là lời thú tội của một người cha, mang nặng mặc cảm với đứa con gái mà mình đã phụ lòng. Một nỗi hối hận như thế không nên thuộc về một Tín Đồ, nên tôi đã không thay Người Canh Gác ban cho sự tha thứ. Ánh mắt anh vẫn lấp lánh niềm sùng kính như xưa, và tôi biết anh sẽ tiếp tục hành trình. Vẫn là một Tín Đồ mộ đạo. Vẫn là một người cha vắng bóng.
+Vì vậy, tôi nói với anh rằng mình đang viết hồi ký này. Tôi muốn ghi lại những trải nghiệm của mình ở Avinoleum, và trong chính thư viện này. Hầu hết đều là những chuyện vụn vặt, nhưng mỗi chuyện đều là tấm gương phản chiếu sống động của thời đại tôi đang sống. Những góc khuất bị lãng quên của lịch sử xứng đáng được ghi nhớ. Người Canh Gác dạy chúng ta hãy soi sáng thế giới cho người khác, nhưng cũng đừng quên thắp lên ngọn lửa dẫn đường cho những người thân cận nhất.
+&lt;color=Highlight&gt;Hồi ký Kho Lưu Trữ Danh Nghiệp - Phần II&lt;/color&gt;
 "…
-Enter một ngày đóng cửa bình thường khác, tôi đang bê một chồng sách cũ băng qua sân ga bên ngoài thư viện thì bất giác bị thu hút vào đám đông đang chăm chú theo dõi. Một trận đấu đã thu hút mọi ánh nhìn. Khi Lưỡi Kiếm Đức Hạnh chạm vào giáp ngực Cadanto, cuộc so tài giữa Thánh Nữ và Echoes kết thúc.
-Cadanto khiêm nhường quỳ xuống chịu thua. Đám đông đang nín thở bỗng vỡ òa trong tiếng vỗ tay như sấm. Ngay lúc đó, một Devotee dẫn một cô bé băng qua đám đông hào hứng. Wear quần áo thường dân, cô bé ôm một bó hoa Lồng Đèn Nổ lớn đang nở rộ. Bó hoa gần như cao hơn cả người cô.
-Tôi nghĩ đó là món quà dành cho Thánh Nữ. Từ khi cô bắt đầu học tập ở Avinoleum, các tín đồ đã không ngại đường xa chỉ để được nhìn thấy cô gái được Warden ban phước. Nhưng cô bé chỉ gật đầu chào Thánh Nữ rồi quay sang Cadanto.
-Previous sự ngạc nhiên của mọi người, cô bé tặng bó hoa cho anh. Sau lời giải thích của Devotee, chúng tôi biết được Cadanto mới đây đã cứu một gia đình khỏi bọn Discord ở ngoại ô Avinoleum. Người hiệp sĩ Echoes cao lớn vẫn im lặng quỳ một chân. Anh có vẻ không hiểu tại sao một con người lại tặng hoa cho mình, hay có lẽ anh cảm thấy mình không xứng đáng với lời cảm ơn như thế?
+Vào một ngày đóng cửa bình thường khác, tôi đang bê một chồng sách cũ băng qua sân ga bên ngoài thư viện thì bất giác bị thu hút vào đám đông đang chăm chú theo dõi. Một trận đấu đã thu hút mọi ánh nhìn. Khi Lưỡi Kiếm Đức Hạnh chạm vào giáp ngực Cadanto, cuộc so tài giữa Thánh Nữ và Echo kết thúc.
+Cadanto khiêm nhường quỳ xuống chịu thua. Đám đông đang nín thở bỗng vỡ òa trong tiếng vỗ tay như sấm. Ngay lúc đó, một Tín Đồ dẫn một cô bé băng qua đám đông hào hứng. Mặc quần áo thường dân, cô bé ôm một bó hoa Lồng Đèn Nổ lớn đang nở rộ. Bó hoa gần như cao hơn cả người cô.
+Tôi nghĩ đó là món quà dành cho Thánh Nữ. Từ khi cô bắt đầu học tập ở Avinoleum, các tín đồ đã không ngại đường xa chỉ để được nhìn thấy cô gái được Người Canh Gác ban phước. Nhưng cô bé chỉ gật đầu chào Thánh Nữ rồi quay sang Cadanto.
+Trước sự ngạc nhiên của mọi người, cô bé tặng bó hoa cho anh. Sau lời giải thích của Tín Đồ, chúng tôi biết được Cadanto mới đây đã cứu một gia đình khỏi bọn Tacet Discord ở ngoại ô Avinoleum. Người hiệp sĩ Echo cao lớn vẫn im lặng quỳ một chân. Anh có vẻ không hiểu tại sao một con người lại tặng hoa cho mình, hay có lẽ anh cảm thấy mình không xứng đáng với lời cảm ơn như thế?
 \"Vậy ra đây là những gì anh làm khi tôi vắng mặt…\" Thánh Nữ mỉm cười dịu dàng. \"Cadanto, hãy nhận lấy bó hoa đi. Anh xứng đáng mà.\"
-Mute, hiệp sĩ đặt thanh đại kiếm xuống và cẩn thận nhận lấy bó hoa. Cô bé lập tức lao tới ôm chầm lấy anh, áp mặt vào bộ giáp lạnh lẽo. Như thường lệ, Cadanto lặng lẽ chịu đựng cả những giọt nước mắt cảm kích lẫn tiếng nức nở vui mừng của cô.
+Im lặng, hiệp sĩ đặt thanh đại kiếm xuống và cẩn thận nhận lấy bó hoa. Cô bé lập tức lao tới ôm chầm lấy anh, áp mặt vào bộ giáp lạnh lẽo. Như thường lệ, Cadanto lặng lẽ chịu đựng cả những giọt nước mắt cảm kích lẫn tiếng nức nở vui mừng của cô.
 Cadanto… như nhiều người đã nói, là người hầu trung thành và tấm khiên che chở cho Thánh Nữ. Nhưng anh cũng là lưỡi kiếm bảo vệ nhân dân.\"
-&lt;color=Highlight&gt;Hồi ký Kho Archive Danh Nghiệp - Phần III&lt;/color&gt;
+&lt;color=Highlight&gt;Hồi ký Kho Lưu Trữ Danh Nghiệp - Phần III&lt;/color&gt;
 "…
 Ngày nghỉ hưu càng đến gần, thời gian trôi qua lặng lẽ trong thư viện. Tôi nghĩ sẽ không còn gợn sóng nào nữa.
-\"Gomen… Cháu muốn đọc cuốn sách này. Cháu có cần đăng ký ở đây không ạ?\"
-Cùng với giọng nói rụt rè trước mặt tôi là một cuốn tiểu sử, bìa sách in chân dung của Thánh Nữ. Tôi ngẩng đầu khỏi bàn và thấy một cô bé với mái tóc xoăn màu tím nhạt. Dưới một bên mắt cô có một nốt ruồi. Small xíu và thanh tú. Làn da cô trắng đến mức gần như trong suốt, như thể đã lâu không được nhìn thấy ánh mặt trời.
+\"Xin lỗi… Cháu muốn đọc cuốn sách này. Cháu có cần đăng ký ở đây không ạ?\"
+Cùng với giọng nói rụt rè trước mặt tôi là một cuốn tiểu sử, bìa sách in chân dung của Thánh Nữ. Tôi ngẩng đầu khỏi bàn và thấy một cô bé với mái tóc xoăn màu tím nhạt. Dưới một bên mắt cô có một nốt ruồi. Nhỏ xíu và thanh tú. Làn da cô trắng đến mức gần như trong suốt, như thể đã lâu không được nhìn thấy ánh mặt trời.
 \"Cháu cứ đọc thoải mái ở đây. Nhớ cất sách lại khi đọc xong nhé,\" tôi nói nhẹ nhàng nhất có thể, sợ không khí trang nghiêm của thư viện sẽ khiến cô bé sợ hãi.
 Rõ ràng cô không phải là học sinh của Avinoleum, nhưng những ngày sau đó, cô thường xuyên xuất hiện trong thư viện. Cô lang thang giữa những kệ sách tròn, luôn chăm chú vào cuốn sách đang cầm trên tay. Đôi khi cô nhờ tôi tìm giúp những cuốn sách cụ thể. Có cuốn là sách thần học dày cộp, có cuốn lại là những tập sách đồ sộ về đại dương hay dược lý—không hẳn là sở thích thường thấy ở lứa tuổi của cô. Chúng tôi dần trở nên thân thiết. Tôi biết được cô được người thân đưa đến Avinoleum. Họ có việc riêng phải lo và để cô tự do lang thang trong thư viện tương đối an toàn này.
 Cô ra đi đột ngột như khi đến. Chiều hôm đó, như thể đáp lại một lời gọi vô hình, cô gấp cuốn sách đang đọc lại và đặt nó trở về kệ. Tôi nhớ cuốn sách đó. Đó là một nghiên cứu về truyền thống của Thánh Nữ ở Ragunna. Trong ánh chiều tà xiên xẹo, một bóng dài in trên sàn. Người giám hộ của cô, có lẽ vậy.
@@ -38947,17 +38902,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Bản thảo quảng cáo&lt;/b&gt;
-&lt;s&gt;Lối chơi Peaks of Prestige giúp tăng trí thông minh&lt;/s&gt;
-Ghi chú: Quảng cáo sai sự thật.
-Vô số Echoes. Chiến thuật vô hạn. Bạn có thể trở thành đấu thủ đỉnh cao tiếp theo!
-Ghi chú: Tôi sẽ dùng câu này làm slogan.
-Tôi là Clang Gang. Hãy đưa tôi năm mươi Shell Credit để nghe kế hoạch trả thù của tôi trong Peaks of Prestige.
-Ghi chú: Câu này được đón nhận tốt. Có lẽ tôi nên viết thêm vài câu theo phong cách này...
-Ghi chú bổ sung: Một khi Peaks of Prestige thực sự kiếm được tiền, tôi nhất định sẽ chuyển sang quảng cáo trang trọng hơn...
-&lt;s&gt;Để cứu Peaks of Prestige đang trên bờ vực thất bại, chính tôi, người sáng tạo ra trò chơi, sẽ trực tiếp đảm nhận vai trò chăm sóc khách hàng!&lt;/s&gt;
-Ghi chú: Quá sát thực tế!
-(Dưới đây là thêm một số ghi chú về slogan quảng cáo.)</t>
+          <t>&lt;b&gt;Bản thảo Quảng cáo&lt;/b&gt;</t>
         </is>
       </c>
     </row>
@@ -39027,10 +38972,10 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Hi Nhà thách đấu {PlayerName}.
-Những vì sao của khoảnh khắc này đang tỏa sáng vì ngươi. Cảm ơn ngươi đã bước vào Colosseum Olymdos với lòng dũng cảm và kỹ năng, giữ cho ngọn lửa thi đấu mãi bừng cháy.
+          <t>Chào Nhà Thách Đấu {PlayerName}.
+Những vì sao của khoảnh khắc này đang tỏa sáng vì ngươi. Cảm ơn ngươi đã bước vào Đấu Trường Olymdos với lòng dũng cảm và kỹ năng, giữ cho ngọn lửa thi đấu mãi bừng cháy.
 Ta đã theo dõi ngươi từ khoảnh khắc ngươi đánh bại đối thủ đầu tiên. Chiến thuật, sự tập trung và đam mê của ngươi, cùng những suy nghĩ ngươi dành cho những bộ bài mình xây dựng… tất cả đều gợi ta nhớ về niềm đam mê chân thật mà ta từng có với trò chơi này.
-Hãy chiến đấu hết mình, Nhà thách đấu! Trên chiến trường này, dốc hết sức lực chính là hình thức tôn trọng cao nhất mà một đấu thủ dành cho đối thủ của mình. Dù ngày mai ai sẽ là người chiến thắng, đấu trường này vẫn thuộc về cả hai ta, hai tâm hồn chiến đấu vì điều mình yêu quý.
+Hãy chiến đấu hết mình, Nhà Thách Đấu! Trên chiến trường này, dốc hết sức lực chính là hình thức tôn trọng cao nhất mà một đấu thủ dành cho đối thủ của mình. Dù ngày mai ai sẽ là người chiến thắng, đấu trường này vẫn thuộc về cả hai ta, hai tâm hồn chiến đấu vì điều mình yêu quý.
 Mong bình minh đưa chúng ta đến một chân trời rộng lớn hơn ngày hôm qua.
 — Kẻ Chinh Phục Danh Vọng, một đấu thủ cùng chung niềm đam mê với ngươi.</t>
         </is>
@@ -39235,7 +39180,7 @@
       <c r="M498" t="inlineStr">
         <is>
           <t>Ấn bản đặc biệt này đưa ta chiêm ngưỡng những huyền thoại từng rực sáng trong lịch sử Septimont.
-Từ Fabius, Atilius đến Valeria, những câu chuyện về Anh Hùng Holda Các Anh Hùng chiếm trọn nửa số trang.
+Từ Fabius, Atilius đến Valeria, những câu chuyện về Anh Hùng Giữa Các Anh Hùng chiếm trọn nửa số trang.
 Nửa còn lại là lời tri ân dành cho những người chưa từng đội vương miện, nhưng đã hy sinh tất cả vì vinh quang của Septimont. Nhiều người đã ngã xuống nơi thao trường—những cái tên như Tercules, Magna, và Taurus, bị thời gian vùi lấp, nhưng ký ức về họ vẫn còn mãi.
 Khác với lối văn hoa mỹ của các nhà văn Ragunnesi, phong cách ở đây mạnh mẽ và không hoa mĩ. Thế nhưng, những câu chữ ngắn gọn ấy lại khơi gợi nên những hình ảnh hùng tráng nhất. Dù cùng chung cội nguồn, giọng điệu của các hòn đảo Rinascita đã phân hóa từ lâu trong nghệ thuật và biểu đạt.</t>
         </is>
@@ -39310,7 +39255,7 @@
 Số báo này nhìn lại lịch sử huy hoàng của các nhà vô địch qua từng thời kỳ. Từ những trận đấu nghẹt thở đến những câu chuyện hậu trường, tạp chí đào sâu vào từng chi tiết, đặc biệt là hồ sơ đầy đủ về Ephor đương nhiệm – Augusta.
 Nhưng có một năm lại bị bỏ qua.
 Trận đấu năm đó kết thúc trong sự kỳ lạ: nhà vô địch được mong đợi, một cô gái trẻ đến từ Ragunna, biến mất ngay trước lễ trao giải. Không nhận được huy chương chiến thắng, chiến tích của cô chưa bao giờ được công nhận chính thức.
-Home báo viết: *"Thật sự đáng tiếc, nhưng nếu không có kết thúc trọn vẹn, kết quả sẽ không bao giờ được xác nhận. Đến tận hôm nay, vị thế của Mya vẫn là chủ đề tranh cãi."*</t>
+Nhà báo viết: *"Thật đáng tiếc, nhưng nếu không có kết thúc trọn vẹn, kết quả sẽ không bao giờ được xác nhận. Đến tận hôm nay, vị thế của Mya vẫn là chủ đề tranh cãi."*</t>
         </is>
       </c>
     </row>
@@ -39382,12 +39327,12 @@
       <c r="M500" t="inlineStr">
         <is>
           <t>Thời gian bắt đầu của mỗi kỳ Đại Agon đều khác nhau. Hãy theo dõi thông báo chính thức từ Cung Ephor để biết lịch trình chi tiết.
-Round Loại
-Round loại áp dụng hệ thống tính điểm, bao gồm các sự kiện như: Đấu Echoes, Test Tốc độ Echoes, và Thử thách Teamwork Echoes. Những trận đấu này test khả năng làm chủ Echoes tổng thể của các đội. Kết thúc vòng loại, 20 đội có điểm tích lũy cao nhất sẽ tiến vào Round General kết.
-Round General kết
-Round General kết diễn ra theo thể thức loại trực tiếp. 20 đội đứng đầu vòng loại, cùng các đội được đặc cách, sẽ đối đầu trong các trận đấu 1vs1. Đội thắng sẽ tiến vào vòng tiếp theo cho đến khi trận chung kết quyết định đội vô địch.
-Round Loại Special
-Cũng theo thể thức loại trực tiếp, Round Loại Special đưa các thí sinh đối đầu trong các trận đấu Echoes vs Echoes hoặc Echoes vs Chiến binh. Đội thắng sẽ kế thừa điểm tích lũy của đội thua. Khi đạt ngưỡng điểm yêu cầu, thí sinh sẽ giành quyền vào thẳng Round General kết.</t>
+Vòng Loại
+Vòng loại áp dụng hệ thống tính điểm, bao gồm các sự kiện như: Đấu Echo, Kiểm tra Tốc độ Echo, và Thử thách Đồng đội Echo. Những trận đấu này kiểm tra khả năng làm chủ Echo tổng thể của các đội. Kết thúc vòng loại, 20 đội có điểm tích lũy cao nhất sẽ tiến vào Vòng Chung kết.
+Vòng Chung kết
+Vòng Chung kết diễn ra theo thể thức loại trực tiếp. 20 đội đứng đầu vòng loại, cùng các đội được đặc cách, sẽ đối đầu trong các trận đấu 1vs1. Đội thắng sẽ tiến vào vòng tiếp theo cho đến khi trận chung kết quyết định đội vô địch.
+Vòng Loại Đặc Biệt
+Cũng theo thể thức loại trực tiếp, Vòng Loại Đặc Biệt đưa các thí sinh đối đầu trong các trận đấu Echo vs Echo hoặc Echo vs Chiến binh. Đội thắng sẽ kế thừa điểm tích lũy của đội thua. Khi đạt ngưỡng điểm yêu cầu, thí sinh sẽ giành quyền vào thẳng Vòng Chung kết.</t>
         </is>
       </c>
     </row>
@@ -39459,14 +39404,14 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Yesterday, một cuộc tranh cãi nảy lửa đã nổ ra giữa một gia tộc quý tộc và nhóm thương nhân tại đấu trường nhỏ ở chân đồi Capitoline. Cả hai bên đồng ý giải quyết bằng một trận đấu, nhưng bất ngờ một đội ngoại quốc vô danh xuất hiện và giành chiến thắng. Liệu đây chỉ là sự vụng về của kẻ mới vào nghề, hay một nước cờ tinh vi nhằm biến xung đột thành màn trình diễn? Hãy đón xem diễn biến tiếp theo...
+          <t>Hôm qua, một cuộc tranh cãi nảy lửa đã nổ ra giữa một gia tộc quý tộc và nhóm thương nhân tại đấu trường nhỏ ở chân đồi Capitoline. Cả hai bên đồng ý giải quyết bằng một trận đấu, nhưng bất ngờ một đội ngoại quốc vô danh xuất hiện và giành chiến thắng. Liệu đây chỉ là sự vụng về của kẻ mới vào nghề, hay một nước cờ tinh vi nhằm biến xung đột thành màn trình diễn? Hãy đón xem diễn biến tiếp theo...
 ...
 Trận đấu huấn luyện đấu sĩ thứ 32 được mong chờ bấy lâu đã đột ngột kết thúc hôm qua khi đội Brillingsand rút lui giữa chừng. Người hâm mộ sững sờ, và những lời đồn đoán tràn lan: nguồn tin ẩn danh cho biết có thể một mối quan hệ tình cảm bí mật giữa các thành viên đội đối thủ đã ảnh hưởng đến kết quả. Để thêm dầu vào lửa, tin đồn mới nhất còn cho rằng cả hai đội đều được một gia tộc quý tộc tài trợ, dàn dựng kịch bản này để thu hút sự chú ý cho Đại Agon sắp tới...
 ...
-Gần đây, số lượng đấu sĩ bị thương tăng cao, và Echoes y tế của Machaon Pharmacy được cho là đã biến mất vì làm việc quá sức.
-Nếu thấy một Echoes y tế đi lang thang một mình trên đường, xin hãy liên hệ ngay với Machaon Pharmacy.
+Gần đây, số lượng đấu sĩ bị thương tăng cao, và Echo y tế của Machaon Pharmacy được cho là đã biến mất vì làm việc quá sức.
+Nếu thấy một Echo y tế đi lang thang một mình trên đường, xin hãy liên hệ ngay với Machaon Pharmacy.
 ...
-Bulletin này được tài trợ bởi Vulcan Mining. Hãy ủng hộ các đấu sĩ của Vulcan Mining!</t>
+Bản tin này được tài trợ bởi Vulcan Mining. Hãy ủng hộ các đấu sĩ của Vulcan Mining!</t>
         </is>
       </c>
     </row>
